--- a/Design/Excel/ET/Datas/Game/SkillGraph.xlsx
+++ b/Design/Excel/ET/Datas/Game/SkillGraph.xlsx
@@ -1113,7 +1113,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>{"guid":"cde57fb8-b693-4da8-a4a8-fd61e56c5dcd","nodeType":12,"position":{"x":677.5999755859375,"y":-1998.4000244140625},"targetType":1,"requiredTags":{"_tags":[]},"immunityTags":{"_tags":[]},"destroyWithNode":false,"positionSource":0,"particlePrefab":{"instanceID":46136},"particleBindingName":"down","particleOffset":{"x":0.0,"y":0.0,"z":0.0},"particleScale":{"x":1.0,"y":1.0,"z":1.0},"attachToTarget":false,"particleLoop":false}</t>
+          <t>{"guid":"cde57fb8-b693-4da8-a4a8-fd61e56c5dcd","nodeType":12,"position":{"x":677.5999755859375,"y":-1998.4000244140625},"targetType":1,"requiredTags":{"_tags":[]},"immunityTags":{"_tags":[]},"destroyWithNode":false,"positionSource":0,"particlePrefab":{"instanceID":56272},"particleBindingName":"down","particleOffset":{"x":0.0,"y":0.0,"z":0.0},"particleScale":{"x":1.0,"y":1.0,"z":1.0},"attachToTarget":false,"particleLoop":false}</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -1273,7 +1273,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>{"guid":"432ff1e3-b18d-476d-af80-d39ddc07402a","nodeType":20,"position":{"x":-472.0,"y":-2380.800048828125},"targetType":1,"skeletonDataAsset":{"instanceID":45066},"animationName":"Attack_02","animationDuration":"22","isAnimationLooping":false,"timeEffects":[{"triggerTime":7,"portId":"de0ba361-3aba-4ef0-bb07-9b418fcae591"},{"triggerTime":22,"portId":"97dc121c-84b7-4f94-9997-02e0e5b2ea6c"}],"timeCues":[{"startTime":7,"endTime":48,"portId":"8dea1941-c520-4f9a-aee0-40932c8542ef"}]}</t>
+          <t>{"guid":"432ff1e3-b18d-476d-af80-d39ddc07402a","nodeType":20,"position":{"x":-472.0,"y":-2380.800048828125},"targetType":1,"skeletonDataAsset":{"instanceID":0},"animationName":"Attack_02","animationDuration":"22","isAnimationLooping":false,"timeEffects":[{"triggerTime":7,"portId":"de0ba361-3aba-4ef0-bb07-9b418fcae591"},{"triggerTime":22,"portId":"97dc121c-84b7-4f94-9997-02e0e5b2ea6c"}],"timeCues":[{"startTime":7,"endTime":48,"portId":"8dea1941-c520-4f9a-aee0-40932c8542ef"}]}</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -1395,7 +1395,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>{"guid":"432ff1e3-b18d-476d-af80-d39ddc07402a","nodeType":20,"position":{"x":-491.33331298828127,"y":-2478.66650390625},"targetType":1,"skeletonDataAsset":{"instanceID":45210},"animationName":"Attack","animationDuration":"24","isAnimationLooping":false,"timeEffects":[{"triggerTime":11,"portId":"de0ba361-3aba-4ef0-bb07-9b418fcae591"},{"triggerTime":24,"portId":"7ecf9fe6-7c5e-46ae-bade-7922214225e2"}],"timeCues":[]}</t>
+          <t>{"guid":"432ff1e3-b18d-476d-af80-d39ddc07402a","nodeType":20,"position":{"x":-491.33331298828127,"y":-2478.66650390625},"targetType":1,"skeletonDataAsset":{"instanceID":60590},"animationName":"Attack","animationDuration":"24","isAnimationLooping":false,"timeEffects":[{"triggerTime":11,"portId":"de0ba361-3aba-4ef0-bb07-9b418fcae591"},{"triggerTime":24,"portId":"7ecf9fe6-7c5e-46ae-bade-7922214225e2"}],"timeCues":[]}</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -1415,7 +1415,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>{"guid":"90bacd9f-d882-4bba-aaa8-41ed993ac3ff","nodeType":8,"position":{"x":-401.33331298828127,"y":-1826.666748046875},"targetType":2,"assetTags":{"_tags":[]},"grantedTags":{"_tags":[]},"applicationRequiredTags":{"_tags":[]},"applicationImmunityTags":{"_tags":[]},"removeGameEffectsWithTags":{"_tags":[]},"durationType":2,"duration":"0","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"_tags":[]},"cancelOnAbilityEnd":false,"launchPositionSource":0,"launchBindingName":"center","targetPositionSource":1,"targetBindingName":"center","projectileTargetType":0,"flyOver":false,"offsetAngle":0.0,"curveHeight":0.0,"projectilePrefab":{"instanceID":46040},"speed":3.0,"maxDistance":10.0,"collisionRadius":0.5,"isPiercing":false,"maxPierceCount":1,"collisionTargetTags":{"_tags":[]},"collisionExcludeTags":{"_tags":[]},"isBouncing":false,"bounceTargetMode":0,"maxBounceCount":3,"bounceSearchRadius":10.0,"canBounceToSameTarget":false,"bounceAngleOffset":0.0}</t>
+          <t>{"guid":"90bacd9f-d882-4bba-aaa8-41ed993ac3ff","nodeType":8,"position":{"x":-401.33331298828127,"y":-1826.666748046875},"targetType":2,"assetTags":{"_tags":[]},"grantedTags":{"_tags":[]},"applicationRequiredTags":{"_tags":[]},"applicationImmunityTags":{"_tags":[]},"removeGameEffectsWithTags":{"_tags":[]},"durationType":2,"duration":"0","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"_tags":[]},"cancelOnAbilityEnd":false,"launchPositionSource":0,"launchBindingName":"center","targetPositionSource":1,"targetBindingName":"center","projectileTargetType":0,"flyOver":false,"offsetAngle":0.0,"curveHeight":0.0,"projectilePrefab":{"instanceID":56274},"speed":3.0,"maxDistance":10.0,"collisionRadius":0.5,"isPiercing":false,"maxPierceCount":1,"collisionTargetTags":{"_tags":[]},"collisionExcludeTags":{"_tags":[]},"isBouncing":false,"bounceTargetMode":0,"maxBounceCount":3,"bounceSearchRadius":10.0,"canBounceToSameTarget":false,"bounceAngleOffset":0.0}</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -1557,7 +1557,7 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>{"guid":"432ff1e3-b18d-476d-af80-d39ddc07402a","nodeType":20,"position":{"x":-491.33331298828127,"y":-2478.66650390625},"targetType":1,"skeletonDataAsset":{"instanceID":45066},"animationName":"Attack_01","animationDuration":"18","isAnimationLooping":false,"timeEffects":[{"triggerTime":11,"portId":"de0ba361-3aba-4ef0-bb07-9b418fcae591"},{"triggerTime":24,"portId":"7ecf9fe6-7c5e-46ae-bade-7922214225e2"}],"timeCues":[]}</t>
+          <t>{"guid":"432ff1e3-b18d-476d-af80-d39ddc07402a","nodeType":20,"position":{"x":-491.33331298828127,"y":-2478.66650390625},"targetType":1,"skeletonDataAsset":{"instanceID":60588},"animationName":"Attack_01","animationDuration":"18","isAnimationLooping":false,"timeEffects":[{"triggerTime":11,"portId":"de0ba361-3aba-4ef0-bb07-9b418fcae591"},{"triggerTime":24,"portId":"7ecf9fe6-7c5e-46ae-bade-7922214225e2"}],"timeCues":[]}</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -1617,7 +1617,7 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>{"guid":"90bacd9f-d882-4bba-aaa8-41ed993ac3ff","nodeType":8,"position":{"x":-400.6666564941406,"y":-1836.666748046875},"targetType":2,"assetTags":{"_tags":[]},"grantedTags":{"_tags":[]},"applicationRequiredTags":{"_tags":[]},"applicationImmunityTags":{"_tags":[]},"removeGameEffectsWithTags":{"_tags":[]},"durationType":2,"duration":"0","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"_tags":[]},"cancelOnAbilityEnd":false,"launchPositionSource":0,"launchBindingName":"center","targetPositionSource":1,"targetBindingName":"center","projectileTargetType":0,"flyOver":false,"offsetAngle":0.0,"curveHeight":0.0,"projectilePrefab":{"instanceID":46040},"speed":3.0,"maxDistance":10.0,"collisionRadius":0.5,"isPiercing":false,"maxPierceCount":1,"collisionTargetTags":{"_tags":[]},"collisionExcludeTags":{"_tags":[]},"isBouncing":true,"bounceTargetMode":0,"maxBounceCount":2,"bounceSearchRadius":10.0,"canBounceToSameTarget":false,"bounceAngleOffset":50.0}</t>
+          <t>{"guid":"90bacd9f-d882-4bba-aaa8-41ed993ac3ff","nodeType":8,"position":{"x":-400.6666564941406,"y":-1836.666748046875},"targetType":2,"assetTags":{"_tags":[]},"grantedTags":{"_tags":[]},"applicationRequiredTags":{"_tags":[]},"applicationImmunityTags":{"_tags":[]},"removeGameEffectsWithTags":{"_tags":[]},"durationType":2,"duration":"0","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"_tags":[]},"cancelOnAbilityEnd":false,"launchPositionSource":0,"launchBindingName":"center","targetPositionSource":1,"targetBindingName":"center","projectileTargetType":0,"flyOver":false,"offsetAngle":0.0,"curveHeight":0.0,"projectilePrefab":{"instanceID":56274},"speed":3.0,"maxDistance":10.0,"collisionRadius":0.5,"isPiercing":false,"maxPierceCount":1,"collisionTargetTags":{"_tags":[]},"collisionExcludeTags":{"_tags":[]},"isBouncing":true,"bounceTargetMode":0,"maxBounceCount":2,"bounceSearchRadius":10.0,"canBounceToSameTarget":false,"bounceAngleOffset":50.0}</t>
         </is>
       </c>
       <c r="G35"/>
@@ -1679,7 +1679,7 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>{"guid":"cde57fb8-b693-4da8-a4a8-fd61e56c5dcd","nodeType":12,"position":{"x":677.3333740234375,"y":-1998.666748046875},"targetType":1,"requiredTags":{"_tags":[]},"immunityTags":{"_tags":[]},"destroyWithNode":false,"positionSource":0,"particlePrefab":{"instanceID":46138},"particleBindingName":"down","particleOffset":{"x":0.0,"y":0.0,"z":0.0},"particleScale":{"x":1.0,"y":1.0,"z":1.0},"attachToTarget":false,"particleLoop":false}</t>
+          <t>{"guid":"cde57fb8-b693-4da8-a4a8-fd61e56c5dcd","nodeType":12,"position":{"x":677.3333740234375,"y":-1998.666748046875},"targetType":1,"requiredTags":{"_tags":[]},"immunityTags":{"_tags":[]},"destroyWithNode":false,"positionSource":0,"particlePrefab":{"instanceID":56280},"particleBindingName":"down","particleOffset":{"x":0.0,"y":0.0,"z":0.0},"particleScale":{"x":1.0,"y":1.0,"z":1.0},"attachToTarget":false,"particleLoop":false}</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -1759,7 +1759,7 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>{"guid":"432ff1e3-b18d-476d-af80-d39ddc07402a","nodeType":20,"position":{"x":-646.0,"y":-2456.0},"targetType":1,"skeletonDataAsset":{"instanceID":45066},"animationName":"Skill_attack_1009","animationDuration":"25","isAnimationLooping":false,"timeEffects":[{"triggerTime":4,"portId":"de0ba361-3aba-4ef0-bb07-9b418fcae591"},{"triggerTime":25,"portId":"f41c85e0-7f26-494e-9ffc-4a06c980f811"}],"timeCues":[{"startTime":0,"endTime":75,"portId":"8dea1941-c520-4f9a-aee0-40932c8542ef"}]}</t>
+          <t>{"guid":"432ff1e3-b18d-476d-af80-d39ddc07402a","nodeType":20,"position":{"x":-646.0,"y":-2456.0},"targetType":1,"skeletonDataAsset":{"instanceID":60588},"animationName":"Skill_attack_1009","animationDuration":"25","isAnimationLooping":false,"timeEffects":[{"triggerTime":4,"portId":"de0ba361-3aba-4ef0-bb07-9b418fcae591"},{"triggerTime":25,"portId":"f41c85e0-7f26-494e-9ffc-4a06c980f811"}],"timeCues":[{"startTime":0,"endTime":75,"portId":"8dea1941-c520-4f9a-aee0-40932c8542ef"}]}</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -1901,7 +1901,7 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>{"guid":"cde57fb8-b693-4da8-a4a8-fd61e56c5dcd","nodeType":12,"position":{"x":-304.0,"y":-2072.0},"targetType":1,"requiredTags":{"_tags":[]},"immunityTags":{"_tags":[]},"destroyWithNode":false,"positionSource":0,"particlePrefab":{"instanceID":45954},"particleBindingName":"down","particleOffset":{"x":0.0,"y":0.0,"z":0.0},"particleScale":{"x":1.0,"y":1.0,"z":1.0},"attachToTarget":false,"particleLoop":false}</t>
+          <t>{"guid":"cde57fb8-b693-4da8-a4a8-fd61e56c5dcd","nodeType":12,"position":{"x":-304.0,"y":-2072.0},"targetType":1,"requiredTags":{"_tags":[]},"immunityTags":{"_tags":[]},"destroyWithNode":false,"positionSource":0,"particlePrefab":{"instanceID":56276},"particleBindingName":"down","particleOffset":{"x":0.0,"y":0.0,"z":0.0},"particleScale":{"x":1.0,"y":1.0,"z":1.0},"attachToTarget":false,"particleLoop":false}</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -1983,7 +1983,7 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>{"guid":"cde57fb8-b693-4da8-a4a8-fd61e56c5dcd","nodeType":12,"position":{"x":677.5999755859375,"y":-1998.4000244140625},"targetType":1,"requiredTags":{"_tags":[]},"immunityTags":{"_tags":[]},"destroyWithNode":false,"positionSource":0,"particlePrefab":{"instanceID":46100},"particleBindingName":"down","particleOffset":{"x":0.0,"y":0.0,"z":0.0},"particleScale":{"x":1.0,"y":1.0,"z":1.0},"attachToTarget":false,"particleLoop":false}</t>
+          <t>{"guid":"cde57fb8-b693-4da8-a4a8-fd61e56c5dcd","nodeType":12,"position":{"x":677.5999755859375,"y":-1998.4000244140625},"targetType":1,"requiredTags":{"_tags":[]},"immunityTags":{"_tags":[]},"destroyWithNode":false,"positionSource":0,"particlePrefab":{"instanceID":56266},"particleBindingName":"down","particleOffset":{"x":0.0,"y":0.0,"z":0.0},"particleScale":{"x":1.0,"y":1.0,"z":1.0},"attachToTarget":false,"particleLoop":false}</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
@@ -2023,7 +2023,7 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>{"guid":"93ec5a43-cc34-4e4a-acb3-39da2f2c3010","nodeType":12,"position":{"x":468.79998779296877,"y":-1749.5999755859375},"targetType":1,"requiredTags":{"_tags":[]},"immunityTags":{"_tags":[]},"destroyWithNode":true,"positionSource":2,"particlePrefab":{"instanceID":46228},"particleBindingName":"head","particleOffset":{"x":0.0,"y":0.0,"z":0.0},"particleScale":{"x":1.0,"y":1.0,"z":1.0},"attachToTarget":true,"particleLoop":true}</t>
+          <t>{"guid":"93ec5a43-cc34-4e4a-acb3-39da2f2c3010","nodeType":12,"position":{"x":468.79998779296877,"y":-1749.5999755859375},"targetType":1,"requiredTags":{"_tags":[]},"immunityTags":{"_tags":[]},"destroyWithNode":true,"positionSource":2,"particlePrefab":{"instanceID":56268},"particleBindingName":"head","particleOffset":{"x":0.0,"y":0.0,"z":0.0},"particleScale":{"x":1.0,"y":1.0,"z":1.0},"attachToTarget":true,"particleLoop":true}</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
@@ -2083,7 +2083,7 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>{"guid":"432ff1e3-b18d-476d-af80-d39ddc07402a","nodeType":20,"position":{"x":-452.0,"y":-2375.199951171875},"targetType":1,"skeletonDataAsset":{"instanceID":45066},"animationName":"Skill_attack_1005","animationDuration":"16","isAnimationLooping":false,"timeEffects":[{"triggerTime":7,"portId":"de0ba361-3aba-4ef0-bb07-9b418fcae591"},{"triggerTime":16,"portId":"f41c85e0-7f26-494e-9ffc-4a06c980f811"}],"timeCues":[{"startTime":6,"endTime":55,"portId":"8dea1941-c520-4f9a-aee0-40932c8542ef"}]}</t>
+          <t>{"guid":"432ff1e3-b18d-476d-af80-d39ddc07402a","nodeType":20,"position":{"x":-452.0,"y":-2375.199951171875},"targetType":1,"skeletonDataAsset":{"instanceID":0},"animationName":"Skill_attack_1005","animationDuration":"16","isAnimationLooping":false,"timeEffects":[{"triggerTime":7,"portId":"de0ba361-3aba-4ef0-bb07-9b418fcae591"},{"triggerTime":16,"portId":"f41c85e0-7f26-494e-9ffc-4a06c980f811"}],"timeCues":[{"startTime":6,"endTime":55,"portId":"8dea1941-c520-4f9a-aee0-40932c8542ef"}]}</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
@@ -2165,7 +2165,7 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>{"guid":"432ff1e3-b18d-476d-af80-d39ddc07402a","nodeType":20,"position":{"x":-502.6666564941406,"y":-2384.0},"targetType":1,"skeletonDataAsset":{"instanceID":45066},"animationName":"Stand","animationDuration":"24","isAnimationLooping":false,"timeEffects":[{"triggerTime":25,"portId":"f41c85e0-7f26-494e-9ffc-4a06c980f811"}],"timeCues":[]}</t>
+          <t>{"guid":"432ff1e3-b18d-476d-af80-d39ddc07402a","nodeType":20,"position":{"x":-502.6666564941406,"y":-2384.0},"targetType":1,"skeletonDataAsset":{"instanceID":60588},"animationName":"Stand","animationDuration":"24","isAnimationLooping":false,"timeEffects":[{"triggerTime":25,"portId":"f41c85e0-7f26-494e-9ffc-4a06c980f811"}],"timeCues":[]}</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
@@ -2243,11 +2243,11 @@
       </c>
       <c r="D66"/>
       <c r="E66">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>{"guid":"c28fb88d-51b1-47b2-be59-859e0ac638e3","nodeType":10,"position":{"x":-1130.6666259765625,"y":-2232.0},"targetType":1,"assetTags":{"_tags":[]},"grantedTags":{"_tags":[{"_name":"CD.Sweep","_hashCode":-303359587,"_shortName":"Sweep","_ancestorHashCodes":[-1137859925],"_ancestorNames":["CD"]}]},"applicationRequiredTags":{"_tags":[]},"applicationImmunityTags":{"_tags":[]},"removeGameEffectsWithTags":{"_tags":[]},"durationType":1,"duration":"1","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"_tags":[]},"cancelOnAbilityEnd":false,"cooldownType":0,"maxCharges":2,"chargeTime":"10"}</t>
+          <t>{"guid":"2cfdacd2-0186-49dd-b177-4eb8c0ad87bd","nodeType":7,"position":{"x":731.3333740234375,"y":-2080.0},"targetType":1,"endType":0}</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
@@ -2263,11 +2263,11 @@
       <c r="C67"/>
       <c r="D67"/>
       <c r="E67">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>{"guid":"9d6f459d-b588-4b64-843b-1b71e8f299ae","nodeType":3,"position":{"x":-1130.6666259765625,"y":-2479.333251953125},"targetType":1,"assetTags":{"_tags":[]},"grantedTags":{"_tags":[]},"applicationRequiredTags":{"_tags":[]},"applicationImmunityTags":{"_tags":[]},"removeGameEffectsWithTags":{"_tags":[]},"durationType":0,"duration":"0","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[{"attrType":100,"operation":0,"magnitudeSourceType":0,"fixedValue":-10.0,"formula":"","mmcType":0,"setByCallerKey":"","mmcCaptureAttribute":200,"mmcAttributeSource":0,"mmcCoefficient":1.0,"mmcUseSnapshot":true}],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"_tags":[]},"cancelOnAbilityEnd":true}</t>
+          <t>{"guid":"e33ab94c-1496-4d6a-ba5e-1afd38bb0c30","nodeType":4,"position":{"x":731.3333740234375,"y":-2344.0},"targetType":1,"searchShapeType":1,"searchLineType":0,"positionSource":0,"positionBindingName":"center","searchCircleRadius":5.0,"searchSectorRadius":2.0,"searchSectorAngle":180.0,"searchLineDirectionOffsetAngle":0.0,"searchLineDirectionWidth":1.0,"searchLineDirectionLength":10.0,"lineStartPositionSource":0,"lineStartBindingName":"","lineEndPositionSource":1,"lineEndBindingName":"","searchLineBetweenWidth":1.0,"searchLineAbsoluteAngle":0.0,"searchLineAbsoluteWidth":1.0,"searchLineAbsoluteLength":10.0,"maxTargets":999,"searchTargetTags":{"_tags":[{"_name":"unitType.monster","_hashCode":-2021655864,"_shortName":"monster","_ancestorHashCodes":[1600484460],"_ancestorNames":["unitType"]}]},"searchExcludeTags":{"_tags":[]}}</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
@@ -2283,11 +2283,11 @@
       <c r="C68"/>
       <c r="D68"/>
       <c r="E68">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>{"guid":"432ff1e3-b18d-476d-af80-d39ddc07402a","nodeType":20,"position":{"x":-416.6666564941406,"y":-2824.66650390625},"targetType":1,"skeletonDataAsset":{"instanceID":45066},"animationName":"Skill_attack_1001","animationDuration":"18","isAnimationLooping":true,"timeEffects":[{"triggerTime":7,"portId":"de0ba361-3aba-4ef0-bb07-9b418fcae591"},{"triggerTime":18,"portId":"84e238a8-5baf-470e-829f-186695064945"}],"timeCues":[{"startTime":7,"endTime":48,"portId":"8dea1941-c520-4f9a-aee0-40932c8542ef"}]}</t>
+          <t>{"guid":"cde57fb8-b693-4da8-a4a8-fd61e56c5dcd","nodeType":12,"position":{"x":731.3333740234375,"y":-2488.66650390625},"targetType":1,"requiredTags":{"_tags":[]},"immunityTags":{"_tags":[]},"destroyWithNode":false,"positionSource":0,"particlePrefab":{"instanceID":56272},"particleBindingName":"down","particleOffset":{"x":0.0,"y":0.0,"z":0.0},"particleScale":{"x":1.0,"y":1.0,"z":1.0},"attachToTarget":false,"particleLoop":false}</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
@@ -2303,11 +2303,11 @@
       <c r="C69"/>
       <c r="D69"/>
       <c r="E69">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>{"guid":"2cfdacd2-0186-49dd-b177-4eb8c0ad87bd","nodeType":7,"position":{"x":731.3333740234375,"y":-2080.0},"targetType":1,"endType":0}</t>
+          <t>{"guid":"f8947676-1084-4228-b991-1509cc7fe851","nodeType":1,"position":{"x":994.666748046875,"y":-2344.0},"targetType":0,"assetTags":{"_tags":[]},"grantedTags":{"_tags":[]},"applicationRequiredTags":{"_tags":[]},"applicationImmunityTags":{"_tags":[]},"removeGameEffectsWithTags":{"_tags":[]},"durationType":0,"duration":"0","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"_tags":[]},"cancelOnAbilityEnd":true,"damageType":0,"damageSourceType":0,"damageFixedValue":10.0,"damageFormula":"","damageMMCType":0,"damageSetByCallerKey":"","damageMMCCaptureAttribute":200,"damageMMCAttributeSource":0,"damageMMCCoefficient":1.0,"damageMMCUseSnapshot":true,"damageMultiplyByStackCount":false,"damageCalculationType":0}</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
@@ -2323,11 +2323,11 @@
       <c r="C70"/>
       <c r="D70"/>
       <c r="E70">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>{"guid":"e33ab94c-1496-4d6a-ba5e-1afd38bb0c30","nodeType":4,"position":{"x":731.3333740234375,"y":-2344.0},"targetType":1,"searchShapeType":1,"searchLineType":0,"positionSource":0,"positionBindingName":"center","searchCircleRadius":5.0,"searchSectorRadius":2.0,"searchSectorAngle":180.0,"searchLineDirectionOffsetAngle":0.0,"searchLineDirectionWidth":1.0,"searchLineDirectionLength":10.0,"lineStartPositionSource":0,"lineStartBindingName":"","lineEndPositionSource":1,"lineEndBindingName":"","searchLineBetweenWidth":1.0,"searchLineAbsoluteAngle":0.0,"searchLineAbsoluteWidth":1.0,"searchLineAbsoluteLength":10.0,"maxTargets":999,"searchTargetTags":{"_tags":[{"_name":"unitType.monster","_hashCode":-2021655864,"_shortName":"monster","_ancestorHashCodes":[1600484460],"_ancestorNames":["unitType"]}]},"searchExcludeTags":{"_tags":[]}}</t>
+          <t>{"guid":"c353e286-8ef0-460a-b917-887f2aeb390a","nodeType":14,"position":{"x":1190.0,"y":-2344.0},"targetType":1,"requiredTags":{"_tags":[]},"immunityTags":{"_tags":[]},"destroyWithNode":false,"positionSource":2,"positionBindingName":"head","textType":0,"fixedText":"","contextDataKey":"DamageResult","textColor":{"r":1.0,"g":0.0,"b":0.0,"a":1.0},"criticalColor":{"r":1.0,"g":0.5,"b":0.0,"a":1.0},"missColor":{"r":0.5,"g":0.5,"b":0.5,"a":1.0},"fontSize":45.0,"criticalFontSize":60.0,"duration":1.5,"offset":{"x":0.0,"y":0.0},"moveDirection":{"x":0.0,"y":1.0}}</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
@@ -2343,11 +2343,11 @@
       <c r="C71"/>
       <c r="D71"/>
       <c r="E71">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>{"guid":"cde57fb8-b693-4da8-a4a8-fd61e56c5dcd","nodeType":12,"position":{"x":731.3333740234375,"y":-2488.66650390625},"targetType":1,"requiredTags":{"_tags":[]},"immunityTags":{"_tags":[]},"destroyWithNode":false,"positionSource":0,"particlePrefab":{"instanceID":46136},"particleBindingName":"down","particleOffset":{"x":0.0,"y":0.0,"z":0.0},"particleScale":{"x":1.0,"y":1.0,"z":1.0},"attachToTarget":false,"particleLoop":false}</t>
+          <t>{"guid":"9d6f459d-b588-4b64-843b-1b71e8f299ae","nodeType":3,"position":{"x":-1130.6666259765625,"y":-2479.333251953125},"targetType":1,"assetTags":{"_tags":[]},"grantedTags":{"_tags":[]},"applicationRequiredTags":{"_tags":[]},"applicationImmunityTags":{"_tags":[]},"removeGameEffectsWithTags":{"_tags":[]},"durationType":0,"duration":"0","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[{"attrType":100,"operation":0,"magnitudeSourceType":0,"fixedValue":-10.0,"formula":"","mmcType":0,"setByCallerKey":"","mmcCaptureAttribute":200,"mmcAttributeSource":0,"mmcCoefficient":1.0,"mmcUseSnapshot":true}],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"_tags":[]},"cancelOnAbilityEnd":true}</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
@@ -2363,11 +2363,11 @@
       <c r="C72"/>
       <c r="D72"/>
       <c r="E72">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>{"guid":"f8947676-1084-4228-b991-1509cc7fe851","nodeType":1,"position":{"x":994.666748046875,"y":-2344.0},"targetType":0,"assetTags":{"_tags":[]},"grantedTags":{"_tags":[]},"applicationRequiredTags":{"_tags":[]},"applicationImmunityTags":{"_tags":[]},"removeGameEffectsWithTags":{"_tags":[]},"durationType":0,"duration":"0","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"_tags":[]},"cancelOnAbilityEnd":true,"damageType":0,"damageSourceType":0,"damageFixedValue":10.0,"damageFormula":"","damageMMCType":0,"damageSetByCallerKey":"","damageMMCCaptureAttribute":200,"damageMMCAttributeSource":0,"damageMMCCoefficient":1.0,"damageMMCUseSnapshot":true,"damageMultiplyByStackCount":false,"damageCalculationType":0}</t>
+          <t>{"guid":"c28fb88d-51b1-47b2-be59-859e0ac638e3","nodeType":10,"position":{"x":-1130.6666259765625,"y":-2232.0},"targetType":1,"assetTags":{"_tags":[]},"grantedTags":{"_tags":[{"_name":"CD.Sweep","_hashCode":-303359587,"_shortName":"Sweep","_ancestorHashCodes":[-1137859925],"_ancestorNames":["CD"]}]},"applicationRequiredTags":{"_tags":[]},"applicationImmunityTags":{"_tags":[]},"removeGameEffectsWithTags":{"_tags":[]},"durationType":1,"duration":"1","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"_tags":[]},"cancelOnAbilityEnd":false,"cooldownType":0,"maxCharges":2,"chargeTime":"10"}</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
@@ -2383,11 +2383,11 @@
       <c r="C73"/>
       <c r="D73"/>
       <c r="E73">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>{"guid":"c353e286-8ef0-460a-b917-887f2aeb390a","nodeType":14,"position":{"x":1190.0,"y":-2344.0},"targetType":1,"requiredTags":{"_tags":[]},"immunityTags":{"_tags":[]},"destroyWithNode":false,"positionSource":2,"positionBindingName":"head","textType":0,"fixedText":"","contextDataKey":"DamageResult","textColor":{"r":1.0,"g":0.0,"b":0.0,"a":1.0},"criticalColor":{"r":1.0,"g":0.5,"b":0.0,"a":1.0},"missColor":{"r":0.5,"g":0.5,"b":0.5,"a":1.0},"fontSize":45.0,"criticalFontSize":60.0,"duration":1.5,"offset":{"x":0.0,"y":0.0},"moveDirection":{"x":0.0,"y":1.0}}</t>
+          <t>{"guid":"356907e0-1488-4128-bfcc-7ff73cfc3330","nodeType":0,"position":{"x":-797.3333740234375,"y":-2479.333251953125},"targetType":1,"skillId":1001,"assetTags":{"_tags":[]},"cancelAbilitiesWithTags":{"_tags":[]},"blockAbilitiesWithTags":{"_tags":[]},"activationOwnedTags":{"_tags":[]},"activationRequiredTags":{"_tags":[]},"activationBlockedTags":{"_tags":[{"_name":"CD.Sweep","_hashCode":-303359587,"_shortName":"Sweep","_ancestorHashCodes":[-1137859925],"_ancestorNames":["CD"]}]},"ongoingBlockedTags":{"_tags":[]},"eventOutputPorts":[]}</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
@@ -2403,11 +2403,11 @@
       <c r="C74"/>
       <c r="D74"/>
       <c r="E74">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>{"guid":"356907e0-1488-4128-bfcc-7ff73cfc3330","nodeType":0,"position":{"x":-797.3333740234375,"y":-2479.333251953125},"targetType":1,"skillId":1001,"assetTags":{"_tags":[]},"cancelAbilitiesWithTags":{"_tags":[]},"blockAbilitiesWithTags":{"_tags":[]},"activationOwnedTags":{"_tags":[]},"activationRequiredTags":{"_tags":[]},"activationBlockedTags":{"_tags":[{"_name":"CD.Sweep","_hashCode":-303359587,"_shortName":"Sweep","_ancestorHashCodes":[-1137859925],"_ancestorNames":["CD"]}]},"ongoingBlockedTags":{"_tags":[]},"eventOutputPorts":[]}</t>
+          <t>{"guid":"432ff1e3-b18d-476d-af80-d39ddc07402a","nodeType":20,"position":{"x":-414.0,"y":-2824.66650390625},"targetType":1,"skeletonDataAsset":{"instanceID":0},"animationName":"Skill_attack_1001","animationDuration":"18","isAnimationLooping":true,"timeEffects":[{"triggerTime":7,"portId":"de0ba361-3aba-4ef0-bb07-9b418fcae591"},{"triggerTime":18,"portId":"84e238a8-5baf-470e-829f-186695064945"}],"timeCues":[{"startTime":7,"endTime":48,"portId":"8dea1941-c520-4f9a-aee0-40932c8542ef"}]}</t>
         </is>
       </c>
       <c r="G74"/>
@@ -2549,7 +2549,7 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>{"guid":"432ff1e3-b18d-476d-af80-d39ddc07402a","nodeType":20,"position":{"x":-238.66665649414063,"y":-2405.333251953125},"targetType":1,"skeletonDataAsset":{"instanceID":45066},"animationName":"Attack_01","animationDuration":"18","isAnimationLooping":false,"timeEffects":[{"triggerTime":7,"portId":"de0ba361-3aba-4ef0-bb07-9b418fcae591"},{"triggerTime":18,"portId":"84e238a8-5baf-470e-829f-186695064945"}],"timeCues":[]}</t>
+          <t>{"guid":"432ff1e3-b18d-476d-af80-d39ddc07402a","nodeType":20,"position":{"x":-238.66665649414063,"y":-2405.333251953125},"targetType":1,"skeletonDataAsset":{"instanceID":60588},"animationName":"Attack_01","animationDuration":"18","isAnimationLooping":false,"timeEffects":[{"triggerTime":7,"portId":"de0ba361-3aba-4ef0-bb07-9b418fcae591"},{"triggerTime":18,"portId":"84e238a8-5baf-470e-829f-186695064945"}],"timeCues":[]}</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
@@ -2569,7 +2569,7 @@
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>{"guid":"ce857360-de7e-4457-b348-9c124ce98879","nodeType":8,"position":{"x":1040.666748046875,"y":-2305.333251953125},"targetType":2,"assetTags":{"_tags":[]},"grantedTags":{"_tags":[]},"applicationRequiredTags":{"_tags":[]},"applicationImmunityTags":{"_tags":[]},"removeGameEffectsWithTags":{"_tags":[]},"durationType":2,"duration":"0","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"_tags":[]},"cancelOnAbilityEnd":false,"launchPositionSource":0,"launchBindingName":"center","targetPositionSource":1,"targetBindingName":"center","projectileTargetType":0,"flyOver":true,"offsetAngle":30.0,"curveHeight":0.0,"projectilePrefab":{"instanceID":45938},"speed":10.0,"maxDistance":10.0,"collisionRadius":0.5,"isPiercing":false,"maxPierceCount":1,"collisionTargetTags":{"_tags":[]},"collisionExcludeTags":{"_tags":[]},"isBouncing":false,"bounceTargetMode":0,"maxBounceCount":3,"bounceSearchRadius":10.0,"canBounceToSameTarget":false,"bounceAngleOffset":0.0}</t>
+          <t>{"guid":"ce857360-de7e-4457-b348-9c124ce98879","nodeType":8,"position":{"x":1040.666748046875,"y":-2305.333251953125},"targetType":2,"assetTags":{"_tags":[]},"grantedTags":{"_tags":[]},"applicationRequiredTags":{"_tags":[]},"applicationImmunityTags":{"_tags":[]},"removeGameEffectsWithTags":{"_tags":[]},"durationType":2,"duration":"0","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"_tags":[]},"cancelOnAbilityEnd":false,"launchPositionSource":0,"launchBindingName":"center","targetPositionSource":1,"targetBindingName":"center","projectileTargetType":0,"flyOver":true,"offsetAngle":30.0,"curveHeight":0.0,"projectilePrefab":{"instanceID":56282},"speed":10.0,"maxDistance":10.0,"collisionRadius":0.5,"isPiercing":false,"maxPierceCount":1,"collisionTargetTags":{"_tags":[]},"collisionExcludeTags":{"_tags":[]},"isBouncing":false,"bounceTargetMode":0,"maxBounceCount":3,"bounceSearchRadius":10.0,"canBounceToSameTarget":false,"bounceAngleOffset":0.0}</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
@@ -2589,7 +2589,7 @@
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>{"guid":"9a695e91-e218-425e-82ed-1e157bf1b014","nodeType":8,"position":{"x":1022.666748046875,"y":-2131.333251953125},"targetType":2,"assetTags":{"_tags":[]},"grantedTags":{"_tags":[]},"applicationRequiredTags":{"_tags":[]},"applicationImmunityTags":{"_tags":[]},"removeGameEffectsWithTags":{"_tags":[]},"durationType":2,"duration":"0","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"_tags":[]},"cancelOnAbilityEnd":false,"launchPositionSource":0,"launchBindingName":"center","targetPositionSource":1,"targetBindingName":"center","projectileTargetType":0,"flyOver":true,"offsetAngle":0.0,"curveHeight":0.0,"projectilePrefab":{"instanceID":45938},"speed":10.0,"maxDistance":10.0,"collisionRadius":0.5,"isPiercing":false,"maxPierceCount":1,"collisionTargetTags":{"_tags":[]},"collisionExcludeTags":{"_tags":[]},"isBouncing":false,"bounceTargetMode":0,"maxBounceCount":3,"bounceSearchRadius":10.0,"canBounceToSameTarget":false,"bounceAngleOffset":0.0}</t>
+          <t>{"guid":"9a695e91-e218-425e-82ed-1e157bf1b014","nodeType":8,"position":{"x":1022.666748046875,"y":-2131.333251953125},"targetType":2,"assetTags":{"_tags":[]},"grantedTags":{"_tags":[]},"applicationRequiredTags":{"_tags":[]},"applicationImmunityTags":{"_tags":[]},"removeGameEffectsWithTags":{"_tags":[]},"durationType":2,"duration":"0","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"_tags":[]},"cancelOnAbilityEnd":false,"launchPositionSource":0,"launchBindingName":"center","targetPositionSource":1,"targetBindingName":"center","projectileTargetType":0,"flyOver":true,"offsetAngle":0.0,"curveHeight":0.0,"projectilePrefab":{"instanceID":56282},"speed":10.0,"maxDistance":10.0,"collisionRadius":0.5,"isPiercing":false,"maxPierceCount":1,"collisionTargetTags":{"_tags":[]},"collisionExcludeTags":{"_tags":[]},"isBouncing":false,"bounceTargetMode":0,"maxBounceCount":3,"bounceSearchRadius":10.0,"canBounceToSameTarget":false,"bounceAngleOffset":0.0}</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
@@ -2609,7 +2609,7 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>{"guid":"d897a922-5756-42cf-ac65-90a48c1e5a17","nodeType":8,"position":{"x":1022.666748046875,"y":-1978.0},"targetType":2,"assetTags":{"_tags":[]},"grantedTags":{"_tags":[]},"applicationRequiredTags":{"_tags":[]},"applicationImmunityTags":{"_tags":[]},"removeGameEffectsWithTags":{"_tags":[]},"durationType":2,"duration":"0","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"_tags":[]},"cancelOnAbilityEnd":false,"launchPositionSource":0,"launchBindingName":"center","targetPositionSource":1,"targetBindingName":"center","projectileTargetType":0,"flyOver":true,"offsetAngle":-30.0,"curveHeight":0.0,"projectilePrefab":{"instanceID":45938},"speed":10.0,"maxDistance":10.0,"collisionRadius":0.5,"isPiercing":false,"maxPierceCount":1,"collisionTargetTags":{"_tags":[]},"collisionExcludeTags":{"_tags":[]},"isBouncing":false,"bounceTargetMode":0,"maxBounceCount":3,"bounceSearchRadius":10.0,"canBounceToSameTarget":false,"bounceAngleOffset":0.0}</t>
+          <t>{"guid":"d897a922-5756-42cf-ac65-90a48c1e5a17","nodeType":8,"position":{"x":1022.666748046875,"y":-1978.0},"targetType":2,"assetTags":{"_tags":[]},"grantedTags":{"_tags":[]},"applicationRequiredTags":{"_tags":[]},"applicationImmunityTags":{"_tags":[]},"removeGameEffectsWithTags":{"_tags":[]},"durationType":2,"duration":"0","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"_tags":[]},"cancelOnAbilityEnd":false,"launchPositionSource":0,"launchBindingName":"center","targetPositionSource":1,"targetBindingName":"center","projectileTargetType":0,"flyOver":true,"offsetAngle":-30.0,"curveHeight":0.0,"projectilePrefab":{"instanceID":56282},"speed":10.0,"maxDistance":10.0,"collisionRadius":0.5,"isPiercing":false,"maxPierceCount":1,"collisionTargetTags":{"_tags":[]},"collisionExcludeTags":{"_tags":[]},"isBouncing":false,"bounceTargetMode":0,"maxBounceCount":3,"bounceSearchRadius":10.0,"canBounceToSameTarget":false,"bounceAngleOffset":0.0}</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
@@ -2729,7 +2729,7 @@
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>{"guid":"cde57fb8-b693-4da8-a4a8-fd61e56c5dcd","nodeType":12,"position":{"x":677.5999755859375,"y":-1998.4000244140625},"targetType":1,"requiredTags":{"_tags":[]},"immunityTags":{"_tags":[]},"destroyWithNode":false,"positionSource":0,"particlePrefab":{"instanceID":46012},"particleBindingName":"down","particleOffset":{"x":0.0,"y":0.0,"z":0.0},"particleScale":{"x":1.0,"y":1.0,"z":1.0},"attachToTarget":false,"particleLoop":false}</t>
+          <t>{"guid":"cde57fb8-b693-4da8-a4a8-fd61e56c5dcd","nodeType":12,"position":{"x":677.5999755859375,"y":-1998.4000244140625},"targetType":1,"requiredTags":{"_tags":[]},"immunityTags":{"_tags":[]},"destroyWithNode":false,"positionSource":0,"particlePrefab":{"instanceID":56270},"particleBindingName":"down","particleOffset":{"x":0.0,"y":0.0,"z":0.0},"particleScale":{"x":1.0,"y":1.0,"z":1.0},"attachToTarget":false,"particleLoop":false}</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
@@ -2769,7 +2769,7 @@
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>{"guid":"432ff1e3-b18d-476d-af80-d39ddc07402a","nodeType":20,"position":{"x":-502.3999938964844,"y":-2384.0},"targetType":1,"skeletonDataAsset":{"instanceID":45066},"animationName":"Skill_attack_1009","animationDuration":"25","isAnimationLooping":false,"timeEffects":[{"triggerTime":4,"portId":"de0ba361-3aba-4ef0-bb07-9b418fcae591"},{"triggerTime":25,"portId":"f41c85e0-7f26-494e-9ffc-4a06c980f811"}],"timeCues":[{"startTime":0,"endTime":75,"portId":"8dea1941-c520-4f9a-aee0-40932c8542ef"}]}</t>
+          <t>{"guid":"432ff1e3-b18d-476d-af80-d39ddc07402a","nodeType":20,"position":{"x":-502.3999938964844,"y":-2384.0},"targetType":1,"skeletonDataAsset":{"instanceID":60588},"animationName":"Skill_attack_1009","animationDuration":"25","isAnimationLooping":false,"timeEffects":[{"triggerTime":4,"portId":"de0ba361-3aba-4ef0-bb07-9b418fcae591"},{"triggerTime":25,"portId":"f41c85e0-7f26-494e-9ffc-4a06c980f811"}],"timeCues":[{"startTime":0,"endTime":75,"portId":"8dea1941-c520-4f9a-aee0-40932c8542ef"}]}</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
@@ -2871,7 +2871,7 @@
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>{"guid":"cde57fb8-b693-4da8-a4a8-fd61e56c5dcd","nodeType":12,"position":{"x":677.5999755859375,"y":-1998.4000244140625},"targetType":1,"requiredTags":{"_tags":[]},"immunityTags":{"_tags":[]},"destroyWithNode":true,"positionSource":0,"particlePrefab":{"instanceID":46308},"particleBindingName":"down","particleOffset":{"x":0.0,"y":0.0,"z":0.0},"particleScale":{"x":1.0,"y":1.0,"z":1.0},"attachToTarget":true,"particleLoop":true}</t>
+          <t>{"guid":"cde57fb8-b693-4da8-a4a8-fd61e56c5dcd","nodeType":12,"position":{"x":677.5999755859375,"y":-1998.4000244140625},"targetType":1,"requiredTags":{"_tags":[]},"immunityTags":{"_tags":[]},"destroyWithNode":true,"positionSource":0,"particlePrefab":{"instanceID":56278},"particleBindingName":"down","particleOffset":{"x":0.0,"y":0.0,"z":0.0},"particleScale":{"x":1.0,"y":1.0,"z":1.0},"attachToTarget":true,"particleLoop":true}</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>{"guid":"432ff1e3-b18d-476d-af80-d39ddc07402a","nodeType":20,"position":{"x":-452.0,"y":-2375.199951171875},"targetType":1,"skeletonDataAsset":{"instanceID":45066},"animationName":"Skill_attack_1011","animationDuration":"12","isAnimationLooping":true,"timeEffects":[{"triggerTime":250,"portId":"f41c85e0-7f26-494e-9ffc-4a06c980f811"}],"timeCues":[{"startTime":0,"endTime":255,"portId":"8dea1941-c520-4f9a-aee0-40932c8542ef"}]}</t>
+          <t>{"guid":"432ff1e3-b18d-476d-af80-d39ddc07402a","nodeType":20,"position":{"x":-452.0,"y":-2375.199951171875},"targetType":1,"skeletonDataAsset":{"instanceID":60588},"animationName":"Skill_attack_1011","animationDuration":"12","isAnimationLooping":true,"timeEffects":[{"triggerTime":250,"portId":"f41c85e0-7f26-494e-9ffc-4a06c980f811"}],"timeCues":[{"startTime":0,"endTime":255,"portId":"8dea1941-c520-4f9a-aee0-40932c8542ef"}]}</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">

--- a/Design/Excel/ET/Datas/Game/SkillGraph.xlsx
+++ b/Design/Excel/ET/Datas/Game/SkillGraph.xlsx
@@ -1113,7 +1113,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>{"guid":"cde57fb8-b693-4da8-a4a8-fd61e56c5dcd","nodeType":12,"position":{"x":677.5999755859375,"y":-1998.4000244140625},"targetType":1,"requiredTags":{"_tags":[]},"immunityTags":{"_tags":[]},"destroyWithNode":false,"positionSource":0,"particlePrefab":{"instanceID":56272},"particleBindingName":"down","particleOffset":{"x":0.0,"y":0.0,"z":0.0},"particleScale":{"x":1.0,"y":1.0,"z":1.0},"attachToTarget":false,"particleLoop":false}</t>
+          <t>{"guid":"cde57fb8-b693-4da8-a4a8-fd61e56c5dcd","nodeType":12,"position":{"x":677.3333740234375,"y":-1998.666748046875},"targetType":1,"requiredTags":{"_tags":[]},"immunityTags":{"_tags":[]},"destroyWithNode":false,"positionSource":0,"particlePrefab":{"instanceID":56272},"particleBindingName":"down","particleOffset":{"x":0.0,"y":0.0,"z":0.0},"particleScale":{"x":1.0,"y":1.0,"z":1.0},"attachToTarget":false,"particleLoop":false}</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -1133,7 +1133,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>{"guid":"9d6f459d-b588-4b64-843b-1b71e8f299ae","nodeType":3,"position":{"x":-1186.4000244140625,"y":-2019.199951171875},"targetType":1,"assetTags":{"_tags":[]},"grantedTags":{"_tags":[]},"applicationRequiredTags":{"_tags":[]},"applicationImmunityTags":{"_tags":[]},"removeGameEffectsWithTags":{"_tags":[]},"durationType":0,"duration":"0","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[{"attrType":100,"operation":0,"magnitudeSourceType":0,"fixedValue":10.0,"formula":"","mmcType":0,"setByCallerKey":"","mmcCaptureAttribute":200,"mmcAttributeSource":0,"mmcCoefficient":1.0,"mmcUseSnapshot":true}],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"_tags":[]},"cancelOnAbilityEnd":true}</t>
+          <t>{"guid":"9d6f459d-b588-4b64-843b-1b71e8f299ae","nodeType":3,"position":{"x":-1186.6666259765625,"y":-2019.3333740234375},"targetType":1,"assetTags":{"_tags":[]},"grantedTags":{"_tags":[]},"applicationRequiredTags":{"_tags":[]},"applicationImmunityTags":{"_tags":[]},"removeGameEffectsWithTags":{"_tags":[]},"durationType":0,"duration":"0","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[{"attrType":100,"operation":0,"magnitudeSourceType":0,"fixedValue":10.0,"formula":"","mmcType":0,"setByCallerKey":"","mmcCaptureAttribute":200,"mmcAttributeSource":0,"mmcCoefficient":1.0,"mmcUseSnapshot":true}],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"_tags":[]},"cancelOnAbilityEnd":true}</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -1153,7 +1153,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>{"guid":"c28fb88d-51b1-47b2-be59-859e0ac638e3","nodeType":10,"position":{"x":-1186.4000244140625,"y":-1825.5999755859375},"targetType":1,"assetTags":{"_tags":[]},"grantedTags":{"_tags":[{"_name":"CD.Blood","_hashCode":274000851,"_shortName":"Blood","_ancestorHashCodes":[-1137859925],"_ancestorNames":["CD"]}]},"applicationRequiredTags":{"_tags":[]},"applicationImmunityTags":{"_tags":[]},"removeGameEffectsWithTags":{"_tags":[]},"durationType":1,"duration":"3","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"_tags":[]},"cancelOnAbilityEnd":false,"cooldownType":0,"maxCharges":2,"chargeTime":"10"}</t>
+          <t>{"guid":"c28fb88d-51b1-47b2-be59-859e0ac638e3","nodeType":10,"position":{"x":-1186.6666259765625,"y":-1825.3333740234375},"targetType":1,"assetTags":{"_tags":[]},"grantedTags":{"_tags":[{"_name":"CD.Blood","_hashCode":274000851,"_shortName":"Blood","_ancestorHashCodes":[-1137859925],"_ancestorNames":["CD"]}]},"applicationRequiredTags":{"_tags":[]},"applicationImmunityTags":{"_tags":[]},"removeGameEffectsWithTags":{"_tags":[]},"durationType":1,"duration":"3","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"_tags":[]},"cancelOnAbilityEnd":false,"cooldownType":0,"maxCharges":2,"chargeTime":"10"}</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -1173,7 +1173,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>{"guid":"c353e286-8ef0-460a-b917-887f2aeb390a","nodeType":14,"position":{"x":383.20001220703127,"y":-1531.199951171875},"targetType":1,"requiredTags":{"_tags":[]},"immunityTags":{"_tags":[]},"destroyWithNode":false,"positionSource":2,"positionBindingName":"head","textType":0,"fixedText":"","contextDataKey":"DamageResult","textColor":{"r":1.0,"g":0.0,"b":0.0,"a":1.0},"criticalColor":{"r":1.0,"g":0.5,"b":0.0,"a":1.0},"missColor":{"r":0.5,"g":0.5,"b":0.5,"a":1.0},"fontSize":45.0,"criticalFontSize":60.0,"duration":1.5,"offset":{"x":0.0,"y":0.0},"moveDirection":{"x":0.0,"y":1.0}}</t>
+          <t>{"guid":"c353e286-8ef0-460a-b917-887f2aeb390a","nodeType":14,"position":{"x":383.3333435058594,"y":-1531.3333740234375},"targetType":1,"requiredTags":{"_tags":[]},"immunityTags":{"_tags":[]},"destroyWithNode":false,"positionSource":2,"positionBindingName":"head","textType":0,"fixedText":"","contextDataKey":"DamageResult","textColor":{"r":1.0,"g":0.0,"b":0.0,"a":1.0},"criticalColor":{"r":1.0,"g":0.5,"b":0.0,"a":1.0},"missColor":{"r":0.5,"g":0.5,"b":0.5,"a":1.0},"fontSize":45.0,"criticalFontSize":60.0,"duration":1.5,"offset":{"x":0.0,"y":0.0},"moveDirection":{"x":0.0,"y":1.0}}</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -1193,7 +1193,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>{"guid":"011aad56-e96c-41eb-9d85-e793d74a40bb","nodeType":7,"position":{"x":677.5999755859375,"y":-1879.199951171875},"targetType":1,"endType":0}</t>
+          <t>{"guid":"011aad56-e96c-41eb-9d85-e793d74a40bb","nodeType":7,"position":{"x":677.3333740234375,"y":-1879.3333740234375},"targetType":1,"endType":0}</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -1213,7 +1213,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>{"guid":"f8947676-1084-4228-b991-1509cc7fe851","nodeType":1,"position":{"x":195.20001220703126,"y":-1761.5999755859375},"targetType":0,"assetTags":{"_tags":[]},"grantedTags":{"_tags":[]},"applicationRequiredTags":{"_tags":[]},"applicationImmunityTags":{"_tags":[]},"removeGameEffectsWithTags":{"_tags":[]},"durationType":0,"duration":"0","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"_tags":[]},"cancelOnAbilityEnd":true,"damageType":0,"damageSourceType":0,"damageFixedValue":3.0,"damageFormula":"","damageMMCType":0,"damageSetByCallerKey":"","damageMMCCaptureAttribute":200,"damageMMCAttributeSource":0,"damageMMCCoefficient":1.0,"damageMMCUseSnapshot":true,"damageMultiplyByStackCount":true,"damageCalculationType":0}</t>
+          <t>{"guid":"f8947676-1084-4228-b991-1509cc7fe851","nodeType":1,"position":{"x":195.33334350585938,"y":-1761.3333740234375},"targetType":0,"assetTags":{"_tags":[]},"grantedTags":{"_tags":[]},"applicationRequiredTags":{"_tags":[]},"applicationImmunityTags":{"_tags":[]},"removeGameEffectsWithTags":{"_tags":[]},"durationType":0,"duration":"0","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"_tags":[]},"cancelOnAbilityEnd":true,"damageType":0,"damageSourceType":0,"damageFixedValue":3.0,"damageFormula":"","damageMMCType":0,"damageSetByCallerKey":"","damageMMCCaptureAttribute":200,"damageMMCAttributeSource":0,"damageMMCCoefficient":1.0,"damageMMCUseSnapshot":true,"damageMultiplyByStackCount":true,"damageCalculationType":0}</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -1233,7 +1233,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>{"guid":"cb1df36f-5729-423e-9d1a-287db5a433f0","nodeType":11,"position":{"x":-160.8000030517578,"y":-1761.5999755859375},"targetType":0,"assetTags":{"_tags":[{"_name":"Buff.DeBuff.Dot","_hashCode":-637848644,"_shortName":"Dot","_ancestorHashCodes":[937056111,321157895],"_ancestorNames":["Buff","Buff.DeBuff"]}]},"grantedTags":{"_tags":[]},"applicationRequiredTags":{"_tags":[]},"applicationImmunityTags":{"_tags":[]},"removeGameEffectsWithTags":{"_tags":[]},"durationType":1,"duration":"10","isPeriodic":true,"period":"1","executeOnApplication":false,"attributeModifiers":[],"stackType":1,"stackLimit":3,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":1,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"_tags":[]},"cancelOnAbilityEnd":false,"buffId":0}</t>
+          <t>{"guid":"cb1df36f-5729-423e-9d1a-287db5a433f0","nodeType":11,"position":{"x":-160.66665649414063,"y":-1761.3333740234375},"targetType":0,"assetTags":{"_tags":[{"_name":"Buff.DeBuff.Dot","_hashCode":-637848644,"_shortName":"Dot","_ancestorHashCodes":[937056111,321157895],"_ancestorNames":["Buff","Buff.DeBuff"]}]},"grantedTags":{"_tags":[]},"applicationRequiredTags":{"_tags":[]},"applicationImmunityTags":{"_tags":[]},"removeGameEffectsWithTags":{"_tags":[]},"durationType":1,"duration":"10","isPeriodic":true,"period":"1","executeOnApplication":false,"attributeModifiers":[],"stackType":1,"stackLimit":3,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":1,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"_tags":[]},"cancelOnAbilityEnd":false,"buffId":0}</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -1253,7 +1253,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>{"guid":"e33ab94c-1496-4d6a-ba5e-1afd38bb0c30","nodeType":4,"position":{"x":-452.0,"y":-1786.4000244140625},"targetType":1,"searchShapeType":1,"searchLineType":0,"positionSource":0,"positionBindingName":"center","searchCircleRadius":5.0,"searchSectorRadius":2.0,"searchSectorAngle":180.0,"searchLineDirectionOffsetAngle":0.0,"searchLineDirectionWidth":1.0,"searchLineDirectionLength":10.0,"lineStartPositionSource":0,"lineStartBindingName":"","lineEndPositionSource":1,"lineEndBindingName":"","searchLineBetweenWidth":1.0,"searchLineAbsoluteAngle":0.0,"searchLineAbsoluteWidth":1.0,"searchLineAbsoluteLength":10.0,"maxTargets":999,"searchTargetTags":{"_tags":[{"_name":"unitType.monster","_hashCode":-2021655864,"_shortName":"monster","_ancestorHashCodes":[1600484460],"_ancestorNames":["unitType"]}]},"searchExcludeTags":{"_tags":[]}}</t>
+          <t>{"guid":"e33ab94c-1496-4d6a-ba5e-1afd38bb0c30","nodeType":4,"position":{"x":-452.0,"y":-1786.666748046875},"targetType":1,"searchShapeType":1,"searchLineType":0,"positionSource":0,"positionBindingName":"center","searchCircleRadius":5.0,"searchSectorRadius":2.0,"searchSectorAngle":180.0,"searchLineDirectionOffsetAngle":0.0,"searchLineDirectionWidth":1.0,"searchLineDirectionLength":10.0,"lineStartPositionSource":0,"lineStartBindingName":"","lineEndPositionSource":1,"lineEndBindingName":"","searchLineBetweenWidth":1.0,"searchLineAbsoluteAngle":0.0,"searchLineAbsoluteWidth":1.0,"searchLineAbsoluteLength":10.0,"maxTargets":999,"searchTargetTags":{"_tags":[{"_name":"unitType.monster","_hashCode":-2021655864,"_shortName":"monster","_ancestorHashCodes":[1600484460],"_ancestorNames":["unitType"]}]},"searchExcludeTags":{"_tags":[]}}</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -1273,7 +1273,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>{"guid":"432ff1e3-b18d-476d-af80-d39ddc07402a","nodeType":20,"position":{"x":-472.0,"y":-2380.800048828125},"targetType":1,"skeletonDataAsset":{"instanceID":0},"animationName":"Attack_02","animationDuration":"22","isAnimationLooping":false,"timeEffects":[{"triggerTime":7,"portId":"de0ba361-3aba-4ef0-bb07-9b418fcae591"},{"triggerTime":22,"portId":"97dc121c-84b7-4f94-9997-02e0e5b2ea6c"}],"timeCues":[{"startTime":7,"endTime":48,"portId":"8dea1941-c520-4f9a-aee0-40932c8542ef"}]}</t>
+          <t>{"guid":"432ff1e3-b18d-476d-af80-d39ddc07402a","nodeType":20,"position":{"x":-472.0,"y":-2380.66650390625},"targetType":1,"skeletonDataAsset":{"instanceID":60588},"animationName":"Attack_02","animationDuration":"22","isAnimationLooping":false,"timeEffects":[{"triggerTime":7,"portId":"de0ba361-3aba-4ef0-bb07-9b418fcae591"},{"triggerTime":22,"portId":"97dc121c-84b7-4f94-9997-02e0e5b2ea6c"}],"timeCues":[{"startTime":7,"endTime":48,"portId":"8dea1941-c520-4f9a-aee0-40932c8542ef"}]}</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -1293,7 +1293,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>{"guid":"356907e0-1488-4128-bfcc-7ff73cfc3330","nodeType":0,"position":{"x":-878.4000244140625,"y":-1853.5999755859375},"targetType":1,"skillId":1002,"assetTags":{"_tags":[]},"cancelAbilitiesWithTags":{"_tags":[]},"blockAbilitiesWithTags":{"_tags":[]},"activationOwnedTags":{"_tags":[{"_name":"Skill.Running","_hashCode":-51601538,"_shortName":"Running","_ancestorHashCodes":[1312877309],"_ancestorNames":["Skill"]}]},"activationRequiredTags":{"_tags":[]},"activationBlockedTags":{"_tags":[{"_name":"CD.Blood","_hashCode":274000851,"_shortName":"Blood","_ancestorHashCodes":[-1137859925],"_ancestorNames":["CD"]},{"_name":"Skill.Running","_hashCode":-51601538,"_shortName":"Running","_ancestorHashCodes":[1312877309],"_ancestorNames":["Skill"]}]},"ongoingBlockedTags":{"_tags":[]},"eventOutputPorts":[]}</t>
+          <t>{"guid":"356907e0-1488-4128-bfcc-7ff73cfc3330","nodeType":0,"position":{"x":-878.6666259765625,"y":-1853.3333740234375},"targetType":1,"skillId":1002,"assetTags":{"_tags":[]},"cancelAbilitiesWithTags":{"_tags":[]},"blockAbilitiesWithTags":{"_tags":[]},"activationOwnedTags":{"_tags":[{"_name":"Skill.Running","_hashCode":-51601538,"_shortName":"Running","_ancestorHashCodes":[1312877309],"_ancestorNames":["Skill"]}]},"activationRequiredTags":{"_tags":[]},"activationBlockedTags":{"_tags":[{"_name":"CD.Blood","_hashCode":274000851,"_shortName":"Blood","_ancestorHashCodes":[-1137859925],"_ancestorNames":["CD"]},{"_name":"Skill.Running","_hashCode":-51601538,"_shortName":"Running","_ancestorHashCodes":[1312877309],"_ancestorNames":["Skill"]}]},"ongoingBlockedTags":{"_tags":[]},"eventOutputPorts":[]}</t>
         </is>
       </c>
       <c r="G19"/>
@@ -1943,7 +1943,7 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>{"guid":"9d6f459d-b588-4b64-843b-1b71e8f299ae","nodeType":3,"position":{"x":-1186.4000244140625,"y":-2011.199951171875},"targetType":1,"assetTags":{"_tags":[]},"grantedTags":{"_tags":[]},"applicationRequiredTags":{"_tags":[]},"applicationImmunityTags":{"_tags":[]},"removeGameEffectsWithTags":{"_tags":[]},"durationType":0,"duration":"0","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[{"attrType":100,"operation":0,"magnitudeSourceType":0,"fixedValue":10.0,"formula":"","mmcType":0,"setByCallerKey":"","mmcCaptureAttribute":200,"mmcAttributeSource":0,"mmcCoefficient":1.0,"mmcUseSnapshot":true}],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"_tags":[]},"cancelOnAbilityEnd":true}</t>
+          <t>{"guid":"9d6f459d-b588-4b64-843b-1b71e8f299ae","nodeType":3,"position":{"x":-1186.6666259765625,"y":-2011.3333740234375},"targetType":1,"assetTags":{"_tags":[]},"grantedTags":{"_tags":[]},"applicationRequiredTags":{"_tags":[]},"applicationImmunityTags":{"_tags":[]},"removeGameEffectsWithTags":{"_tags":[]},"durationType":0,"duration":"0","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[{"attrType":100,"operation":0,"magnitudeSourceType":0,"fixedValue":10.0,"formula":"","mmcType":0,"setByCallerKey":"","mmcCaptureAttribute":200,"mmcAttributeSource":0,"mmcCoefficient":1.0,"mmcUseSnapshot":true}],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"_tags":[]},"cancelOnAbilityEnd":true}</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -1963,7 +1963,7 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>{"guid":"c28fb88d-51b1-47b2-be59-859e0ac638e3","nodeType":10,"position":{"x":-1186.4000244140625,"y":-1747.199951171875},"targetType":1,"assetTags":{"_tags":[]},"grantedTags":{"_tags":[{"_name":"CD.RuFood","_hashCode":-1045902856,"_shortName":"RuFood","_ancestorHashCodes":[-1137859925],"_ancestorNames":["CD"]}]},"applicationRequiredTags":{"_tags":[]},"applicationImmunityTags":{"_tags":[]},"removeGameEffectsWithTags":{"_tags":[]},"durationType":1,"duration":"5","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"_tags":[]},"cancelOnAbilityEnd":false,"cooldownType":0,"maxCharges":2,"chargeTime":"10"}</t>
+          <t>{"guid":"c28fb88d-51b1-47b2-be59-859e0ac638e3","nodeType":10,"position":{"x":-1186.6666259765625,"y":-1747.3333740234375},"targetType":1,"assetTags":{"_tags":[]},"grantedTags":{"_tags":[{"_name":"CD.RuFood","_hashCode":-1045902856,"_shortName":"RuFood","_ancestorHashCodes":[-1137859925],"_ancestorNames":["CD"]}]},"applicationRequiredTags":{"_tags":[]},"applicationImmunityTags":{"_tags":[]},"removeGameEffectsWithTags":{"_tags":[]},"durationType":1,"duration":"5","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"_tags":[]},"cancelOnAbilityEnd":false,"cooldownType":0,"maxCharges":2,"chargeTime":"10"}</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -1983,7 +1983,7 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>{"guid":"cde57fb8-b693-4da8-a4a8-fd61e56c5dcd","nodeType":12,"position":{"x":677.5999755859375,"y":-1998.4000244140625},"targetType":1,"requiredTags":{"_tags":[]},"immunityTags":{"_tags":[]},"destroyWithNode":false,"positionSource":0,"particlePrefab":{"instanceID":56266},"particleBindingName":"down","particleOffset":{"x":0.0,"y":0.0,"z":0.0},"particleScale":{"x":1.0,"y":1.0,"z":1.0},"attachToTarget":false,"particleLoop":false}</t>
+          <t>{"guid":"cde57fb8-b693-4da8-a4a8-fd61e56c5dcd","nodeType":12,"position":{"x":677.3333740234375,"y":-1998.666748046875},"targetType":1,"requiredTags":{"_tags":[]},"immunityTags":{"_tags":[]},"destroyWithNode":false,"positionSource":0,"particlePrefab":{"instanceID":56266},"particleBindingName":"down","particleOffset":{"x":0.0,"y":0.0,"z":0.0},"particleScale":{"x":1.0,"y":1.0,"z":1.0},"attachToTarget":false,"particleLoop":false}</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
@@ -2003,7 +2003,7 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>{"guid":"f73ba91e-a76b-456c-b19c-a5176809d5f5","nodeType":7,"position":{"x":700.0,"y":-1856.800048828125},"targetType":1,"endType":0}</t>
+          <t>{"guid":"f73ba91e-a76b-456c-b19c-a5176809d5f5","nodeType":7,"position":{"x":700.0,"y":-1856.666748046875},"targetType":1,"endType":0}</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
@@ -2023,7 +2023,7 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>{"guid":"93ec5a43-cc34-4e4a-acb3-39da2f2c3010","nodeType":12,"position":{"x":468.79998779296877,"y":-1749.5999755859375},"targetType":1,"requiredTags":{"_tags":[]},"immunityTags":{"_tags":[]},"destroyWithNode":true,"positionSource":2,"particlePrefab":{"instanceID":56268},"particleBindingName":"head","particleOffset":{"x":0.0,"y":0.0,"z":0.0},"particleScale":{"x":1.0,"y":1.0,"z":1.0},"attachToTarget":true,"particleLoop":true}</t>
+          <t>{"guid":"93ec5a43-cc34-4e4a-acb3-39da2f2c3010","nodeType":12,"position":{"x":468.6666564941406,"y":-1749.3333740234375},"targetType":1,"requiredTags":{"_tags":[]},"immunityTags":{"_tags":[]},"destroyWithNode":true,"positionSource":2,"particlePrefab":{"instanceID":56268},"particleBindingName":"head","particleOffset":{"x":0.0,"y":0.0,"z":0.0},"particleScale":{"x":1.0,"y":1.0,"z":1.0},"attachToTarget":true,"particleLoop":true}</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
@@ -2043,7 +2043,7 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>{"guid":"cb1df36f-5729-423e-9d1a-287db5a433f0","nodeType":11,"position":{"x":18.399993896484376,"y":-1786.4000244140625},"targetType":0,"assetTags":{"_tags":[{"_name":"Buff.DeBuff.Stun","_hashCode":1791562953,"_shortName":"Stun","_ancestorHashCodes":[937056111,321157895],"_ancestorNames":["Buff","Buff.DeBuff"]}]},"grantedTags":{"_tags":[{"_name":"Buff.DeBuff.Stun","_hashCode":1791562953,"_shortName":"Stun","_ancestorHashCodes":[937056111,321157895],"_ancestorNames":["Buff","Buff.DeBuff"]}]},"applicationRequiredTags":{"_tags":[]},"applicationImmunityTags":{"_tags":[]},"removeGameEffectsWithTags":{"_tags":[]},"durationType":1,"duration":"4","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[],"stackType":1,"stackLimit":1,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":1,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"_tags":[]},"cancelOnAbilityEnd":false,"buffId":0}</t>
+          <t>{"guid":"cb1df36f-5729-423e-9d1a-287db5a433f0","nodeType":11,"position":{"x":18.66668701171875,"y":-1786.666748046875},"targetType":0,"assetTags":{"_tags":[{"_name":"Buff.DeBuff.Stun","_hashCode":1791562953,"_shortName":"Stun","_ancestorHashCodes":[937056111,321157895],"_ancestorNames":["Buff","Buff.DeBuff"]}]},"grantedTags":{"_tags":[{"_name":"Buff.DeBuff.Stun","_hashCode":1791562953,"_shortName":"Stun","_ancestorHashCodes":[937056111,321157895],"_ancestorNames":["Buff","Buff.DeBuff"]}]},"applicationRequiredTags":{"_tags":[]},"applicationImmunityTags":{"_tags":[]},"removeGameEffectsWithTags":{"_tags":[]},"durationType":1,"duration":"4","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[],"stackType":1,"stackLimit":1,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":1,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"_tags":[]},"cancelOnAbilityEnd":false,"buffId":0}</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
@@ -2063,7 +2063,7 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>{"guid":"e33ab94c-1496-4d6a-ba5e-1afd38bb0c30","nodeType":4,"position":{"x":-452.0,"y":-1786.4000244140625},"targetType":1,"searchShapeType":0,"searchLineType":0,"positionSource":0,"positionBindingName":"center","searchCircleRadius":2.5,"searchSectorRadius":2.0,"searchSectorAngle":180.0,"searchLineDirectionOffsetAngle":0.0,"searchLineDirectionWidth":1.0,"searchLineDirectionLength":10.0,"lineStartPositionSource":0,"lineStartBindingName":"","lineEndPositionSource":1,"lineEndBindingName":"","searchLineBetweenWidth":1.0,"searchLineAbsoluteAngle":0.0,"searchLineAbsoluteWidth":1.0,"searchLineAbsoluteLength":10.0,"maxTargets":999,"searchTargetTags":{"_tags":[{"_name":"unitType.monster","_hashCode":-2021655864,"_shortName":"monster","_ancestorHashCodes":[1600484460],"_ancestorNames":["unitType"]}]},"searchExcludeTags":{"_tags":[]}}</t>
+          <t>{"guid":"e33ab94c-1496-4d6a-ba5e-1afd38bb0c30","nodeType":4,"position":{"x":-452.0,"y":-1786.666748046875},"targetType":1,"searchShapeType":0,"searchLineType":0,"positionSource":0,"positionBindingName":"center","searchCircleRadius":2.5,"searchSectorRadius":2.0,"searchSectorAngle":180.0,"searchLineDirectionOffsetAngle":0.0,"searchLineDirectionWidth":1.0,"searchLineDirectionLength":10.0,"lineStartPositionSource":0,"lineStartBindingName":"","lineEndPositionSource":1,"lineEndBindingName":"","searchLineBetweenWidth":1.0,"searchLineAbsoluteAngle":0.0,"searchLineAbsoluteWidth":1.0,"searchLineAbsoluteLength":10.0,"maxTargets":999,"searchTargetTags":{"_tags":[{"_name":"unitType.monster","_hashCode":-2021655864,"_shortName":"monster","_ancestorHashCodes":[1600484460],"_ancestorNames":["unitType"]}]},"searchExcludeTags":{"_tags":[]}}</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
@@ -2083,7 +2083,7 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>{"guid":"432ff1e3-b18d-476d-af80-d39ddc07402a","nodeType":20,"position":{"x":-452.0,"y":-2375.199951171875},"targetType":1,"skeletonDataAsset":{"instanceID":0},"animationName":"Skill_attack_1005","animationDuration":"16","isAnimationLooping":false,"timeEffects":[{"triggerTime":7,"portId":"de0ba361-3aba-4ef0-bb07-9b418fcae591"},{"triggerTime":16,"portId":"f41c85e0-7f26-494e-9ffc-4a06c980f811"}],"timeCues":[{"startTime":6,"endTime":55,"portId":"8dea1941-c520-4f9a-aee0-40932c8542ef"}]}</t>
+          <t>{"guid":"432ff1e3-b18d-476d-af80-d39ddc07402a","nodeType":20,"position":{"x":-452.0,"y":-2375.333251953125},"targetType":1,"skeletonDataAsset":{"instanceID":60588},"animationName":"Skill_attack_1005","animationDuration":"16","isAnimationLooping":false,"timeEffects":[{"triggerTime":7,"portId":"de0ba361-3aba-4ef0-bb07-9b418fcae591"},{"triggerTime":16,"portId":"f41c85e0-7f26-494e-9ffc-4a06c980f811"}],"timeCues":[{"startTime":6,"endTime":55,"portId":"8dea1941-c520-4f9a-aee0-40932c8542ef"}]}</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
@@ -2103,7 +2103,7 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>{"guid":"356907e0-1488-4128-bfcc-7ff73cfc3330","nodeType":0,"position":{"x":-878.4000244140625,"y":-1853.5999755859375},"targetType":1,"skillId":1003,"assetTags":{"_tags":[]},"cancelAbilitiesWithTags":{"_tags":[]},"blockAbilitiesWithTags":{"_tags":[]},"activationOwnedTags":{"_tags":[{"_name":"Skill.Running","_hashCode":-51601538,"_shortName":"Running","_ancestorHashCodes":[1312877309],"_ancestorNames":["Skill"]}]},"activationRequiredTags":{"_tags":[]},"activationBlockedTags":{"_tags":[{"_name":"CD.RuFood","_hashCode":-1045902856,"_shortName":"RuFood","_ancestorHashCodes":[-1137859925],"_ancestorNames":["CD"]},{"_name":"Skill.Running","_hashCode":-51601538,"_shortName":"Running","_ancestorHashCodes":[1312877309],"_ancestorNames":["Skill"]}]},"ongoingBlockedTags":{"_tags":[]},"eventOutputPorts":[]}</t>
+          <t>{"guid":"356907e0-1488-4128-bfcc-7ff73cfc3330","nodeType":0,"position":{"x":-878.6666259765625,"y":-1853.3333740234375},"targetType":1,"skillId":1003,"assetTags":{"_tags":[]},"cancelAbilitiesWithTags":{"_tags":[]},"blockAbilitiesWithTags":{"_tags":[]},"activationOwnedTags":{"_tags":[{"_name":"Skill.Running","_hashCode":-51601538,"_shortName":"Running","_ancestorHashCodes":[1312877309],"_ancestorNames":["Skill"]}]},"activationRequiredTags":{"_tags":[]},"activationBlockedTags":{"_tags":[{"_name":"CD.RuFood","_hashCode":-1045902856,"_shortName":"RuFood","_ancestorHashCodes":[-1137859925],"_ancestorNames":["CD"]},{"_name":"Skill.Running","_hashCode":-51601538,"_shortName":"Running","_ancestorHashCodes":[1312877309],"_ancestorNames":["Skill"]}]},"ongoingBlockedTags":{"_tags":[]},"eventOutputPorts":[]}</t>
         </is>
       </c>
       <c r="G59"/>
@@ -2407,7 +2407,7 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>{"guid":"432ff1e3-b18d-476d-af80-d39ddc07402a","nodeType":20,"position":{"x":-414.0,"y":-2824.66650390625},"targetType":1,"skeletonDataAsset":{"instanceID":0},"animationName":"Skill_attack_1001","animationDuration":"18","isAnimationLooping":true,"timeEffects":[{"triggerTime":7,"portId":"de0ba361-3aba-4ef0-bb07-9b418fcae591"},{"triggerTime":18,"portId":"84e238a8-5baf-470e-829f-186695064945"}],"timeCues":[{"startTime":7,"endTime":48,"portId":"8dea1941-c520-4f9a-aee0-40932c8542ef"}]}</t>
+          <t>{"guid":"432ff1e3-b18d-476d-af80-d39ddc07402a","nodeType":20,"position":{"x":-414.0,"y":-2826.0},"targetType":1,"skeletonDataAsset":{"instanceID":60588},"animationName":"Skill_attack_1001","animationDuration":"18","isAnimationLooping":true,"timeEffects":[{"triggerTime":7,"portId":"de0ba361-3aba-4ef0-bb07-9b418fcae591"},{"triggerTime":18,"portId":"84e238a8-5baf-470e-829f-186695064945"}],"timeCues":[{"startTime":7,"endTime":48,"portId":"8dea1941-c520-4f9a-aee0-40932c8542ef"}]}</t>
         </is>
       </c>
       <c r="G74"/>

--- a/Design/Excel/ET/Datas/Game/SkillGraph.xlsx
+++ b/Design/Excel/ET/Datas/Game/SkillGraph.xlsx
@@ -1113,7 +1113,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>{"guid":"cde57fb8-b693-4da8-a4a8-fd61e56c5dcd","nodeType":12,"position":{"x":677.3333740234375,"y":-1998.666748046875},"targetType":1,"requiredTags":{"_tags":[]},"immunityTags":{"_tags":[]},"destroyWithNode":false,"positionSource":0,"particlePrefab":{"instanceID":56272},"particleBindingName":"down","particleOffset":{"x":0.0,"y":0.0,"z":0.0},"particleScale":{"x":1.0,"y":1.0,"z":1.0},"attachToTarget":false,"particleLoop":false}</t>
+          <t>{"guid":"cde57fb8-b693-4da8-a4a8-fd61e56c5dcd","nodeType":12,"position":{"x":677.3333740234375,"y":-1998.666748046875},"targetType":1,"requiredTags":{"_tags":[]},"immunityTags":{"_tags":[]},"destroyWithNode":false,"positionSource":0,"particlePrefab":{"instanceID":52512},"particleBindingName":"down","particleOffset":{"x":0.0,"y":0.0,"z":0.0},"particleScale":{"x":1.0,"y":1.0,"z":1.0},"attachToTarget":false,"particleLoop":false}</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -1273,7 +1273,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>{"guid":"432ff1e3-b18d-476d-af80-d39ddc07402a","nodeType":20,"position":{"x":-472.0,"y":-2380.66650390625},"targetType":1,"skeletonDataAsset":{"instanceID":60588},"animationName":"Attack_02","animationDuration":"22","isAnimationLooping":false,"timeEffects":[{"triggerTime":7,"portId":"de0ba361-3aba-4ef0-bb07-9b418fcae591"},{"triggerTime":22,"portId":"97dc121c-84b7-4f94-9997-02e0e5b2ea6c"}],"timeCues":[{"startTime":7,"endTime":48,"portId":"8dea1941-c520-4f9a-aee0-40932c8542ef"}]}</t>
+          <t>{"guid":"432ff1e3-b18d-476d-af80-d39ddc07402a","nodeType":20,"position":{"x":-472.0,"y":-2380.66650390625},"targetType":1,"skeletonDataAsset":{"instanceID":51576},"animationName":"Attack_02","animationDuration":"22","isAnimationLooping":false,"timeEffects":[{"triggerTime":7,"portId":"de0ba361-3aba-4ef0-bb07-9b418fcae591"},{"triggerTime":22,"portId":"97dc121c-84b7-4f94-9997-02e0e5b2ea6c"}],"timeCues":[{"startTime":7,"endTime":48,"portId":"8dea1941-c520-4f9a-aee0-40932c8542ef"}]}</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -1395,7 +1395,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>{"guid":"432ff1e3-b18d-476d-af80-d39ddc07402a","nodeType":20,"position":{"x":-491.33331298828127,"y":-2478.66650390625},"targetType":1,"skeletonDataAsset":{"instanceID":60590},"animationName":"Attack","animationDuration":"24","isAnimationLooping":false,"timeEffects":[{"triggerTime":11,"portId":"de0ba361-3aba-4ef0-bb07-9b418fcae591"},{"triggerTime":24,"portId":"7ecf9fe6-7c5e-46ae-bade-7922214225e2"}],"timeCues":[]}</t>
+          <t>{"guid":"432ff1e3-b18d-476d-af80-d39ddc07402a","nodeType":20,"position":{"x":-491.33331298828127,"y":-2478.66650390625},"targetType":1,"skeletonDataAsset":{"instanceID":51714},"animationName":"Attack","animationDuration":"24","isAnimationLooping":false,"timeEffects":[{"triggerTime":11,"portId":"de0ba361-3aba-4ef0-bb07-9b418fcae591"},{"triggerTime":24,"portId":"7ecf9fe6-7c5e-46ae-bade-7922214225e2"}],"timeCues":[]}</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -1415,7 +1415,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>{"guid":"90bacd9f-d882-4bba-aaa8-41ed993ac3ff","nodeType":8,"position":{"x":-401.33331298828127,"y":-1826.666748046875},"targetType":2,"assetTags":{"_tags":[]},"grantedTags":{"_tags":[]},"applicationRequiredTags":{"_tags":[]},"applicationImmunityTags":{"_tags":[]},"removeGameEffectsWithTags":{"_tags":[]},"durationType":2,"duration":"0","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"_tags":[]},"cancelOnAbilityEnd":false,"launchPositionSource":0,"launchBindingName":"center","targetPositionSource":1,"targetBindingName":"center","projectileTargetType":0,"flyOver":false,"offsetAngle":0.0,"curveHeight":0.0,"projectilePrefab":{"instanceID":56274},"speed":3.0,"maxDistance":10.0,"collisionRadius":0.5,"isPiercing":false,"maxPierceCount":1,"collisionTargetTags":{"_tags":[]},"collisionExcludeTags":{"_tags":[]},"isBouncing":false,"bounceTargetMode":0,"maxBounceCount":3,"bounceSearchRadius":10.0,"canBounceToSameTarget":false,"bounceAngleOffset":0.0}</t>
+          <t>{"guid":"90bacd9f-d882-4bba-aaa8-41ed993ac3ff","nodeType":8,"position":{"x":-401.33331298828127,"y":-1826.666748046875},"targetType":2,"assetTags":{"_tags":[]},"grantedTags":{"_tags":[]},"applicationRequiredTags":{"_tags":[]},"applicationImmunityTags":{"_tags":[]},"removeGameEffectsWithTags":{"_tags":[]},"durationType":2,"duration":"0","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"_tags":[]},"cancelOnAbilityEnd":false,"launchPositionSource":0,"launchBindingName":"center","targetPositionSource":1,"targetBindingName":"center","projectileTargetType":0,"flyOver":false,"offsetAngle":0.0,"curveHeight":0.0,"projectilePrefab":{"instanceID":52550},"speed":3.0,"maxDistance":10.0,"collisionRadius":0.5,"isPiercing":false,"maxPierceCount":1,"collisionTargetTags":{"_tags":[]},"collisionExcludeTags":{"_tags":[]},"isBouncing":false,"bounceTargetMode":0,"maxBounceCount":3,"bounceSearchRadius":10.0,"canBounceToSameTarget":false,"bounceAngleOffset":0.0}</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -1557,7 +1557,7 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>{"guid":"432ff1e3-b18d-476d-af80-d39ddc07402a","nodeType":20,"position":{"x":-491.33331298828127,"y":-2478.66650390625},"targetType":1,"skeletonDataAsset":{"instanceID":60588},"animationName":"Attack_01","animationDuration":"18","isAnimationLooping":false,"timeEffects":[{"triggerTime":11,"portId":"de0ba361-3aba-4ef0-bb07-9b418fcae591"},{"triggerTime":24,"portId":"7ecf9fe6-7c5e-46ae-bade-7922214225e2"}],"timeCues":[]}</t>
+          <t>{"guid":"432ff1e3-b18d-476d-af80-d39ddc07402a","nodeType":20,"position":{"x":-491.33331298828127,"y":-2478.66650390625},"targetType":1,"skeletonDataAsset":{"instanceID":51576},"animationName":"Attack_01","animationDuration":"18","isAnimationLooping":false,"timeEffects":[{"triggerTime":11,"portId":"de0ba361-3aba-4ef0-bb07-9b418fcae591"},{"triggerTime":24,"portId":"7ecf9fe6-7c5e-46ae-bade-7922214225e2"}],"timeCues":[]}</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -1617,7 +1617,7 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>{"guid":"90bacd9f-d882-4bba-aaa8-41ed993ac3ff","nodeType":8,"position":{"x":-400.6666564941406,"y":-1836.666748046875},"targetType":2,"assetTags":{"_tags":[]},"grantedTags":{"_tags":[]},"applicationRequiredTags":{"_tags":[]},"applicationImmunityTags":{"_tags":[]},"removeGameEffectsWithTags":{"_tags":[]},"durationType":2,"duration":"0","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"_tags":[]},"cancelOnAbilityEnd":false,"launchPositionSource":0,"launchBindingName":"center","targetPositionSource":1,"targetBindingName":"center","projectileTargetType":0,"flyOver":false,"offsetAngle":0.0,"curveHeight":0.0,"projectilePrefab":{"instanceID":56274},"speed":3.0,"maxDistance":10.0,"collisionRadius":0.5,"isPiercing":false,"maxPierceCount":1,"collisionTargetTags":{"_tags":[]},"collisionExcludeTags":{"_tags":[]},"isBouncing":true,"bounceTargetMode":0,"maxBounceCount":2,"bounceSearchRadius":10.0,"canBounceToSameTarget":false,"bounceAngleOffset":50.0}</t>
+          <t>{"guid":"90bacd9f-d882-4bba-aaa8-41ed993ac3ff","nodeType":8,"position":{"x":-400.6666564941406,"y":-1836.666748046875},"targetType":2,"assetTags":{"_tags":[]},"grantedTags":{"_tags":[]},"applicationRequiredTags":{"_tags":[]},"applicationImmunityTags":{"_tags":[]},"removeGameEffectsWithTags":{"_tags":[]},"durationType":2,"duration":"0","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"_tags":[]},"cancelOnAbilityEnd":false,"launchPositionSource":0,"launchBindingName":"center","targetPositionSource":1,"targetBindingName":"center","projectileTargetType":0,"flyOver":false,"offsetAngle":0.0,"curveHeight":0.0,"projectilePrefab":{"instanceID":52550},"speed":3.0,"maxDistance":10.0,"collisionRadius":0.5,"isPiercing":false,"maxPierceCount":1,"collisionTargetTags":{"_tags":[]},"collisionExcludeTags":{"_tags":[]},"isBouncing":true,"bounceTargetMode":0,"maxBounceCount":2,"bounceSearchRadius":10.0,"canBounceToSameTarget":false,"bounceAngleOffset":50.0}</t>
         </is>
       </c>
       <c r="G35"/>
@@ -1679,7 +1679,7 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>{"guid":"cde57fb8-b693-4da8-a4a8-fd61e56c5dcd","nodeType":12,"position":{"x":677.3333740234375,"y":-1998.666748046875},"targetType":1,"requiredTags":{"_tags":[]},"immunityTags":{"_tags":[]},"destroyWithNode":false,"positionSource":0,"particlePrefab":{"instanceID":56280},"particleBindingName":"down","particleOffset":{"x":0.0,"y":0.0,"z":0.0},"particleScale":{"x":1.0,"y":1.0,"z":1.0},"attachToTarget":false,"particleLoop":false}</t>
+          <t>{"guid":"cde57fb8-b693-4da8-a4a8-fd61e56c5dcd","nodeType":12,"position":{"x":677.3333740234375,"y":-1998.666748046875},"targetType":1,"requiredTags":{"_tags":[]},"immunityTags":{"_tags":[]},"destroyWithNode":false,"positionSource":0,"particlePrefab":{"instanceID":52610},"particleBindingName":"down","particleOffset":{"x":0.0,"y":0.0,"z":0.0},"particleScale":{"x":1.0,"y":1.0,"z":1.0},"attachToTarget":false,"particleLoop":false}</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -1759,7 +1759,7 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>{"guid":"432ff1e3-b18d-476d-af80-d39ddc07402a","nodeType":20,"position":{"x":-646.0,"y":-2456.0},"targetType":1,"skeletonDataAsset":{"instanceID":60588},"animationName":"Skill_attack_1009","animationDuration":"25","isAnimationLooping":false,"timeEffects":[{"triggerTime":4,"portId":"de0ba361-3aba-4ef0-bb07-9b418fcae591"},{"triggerTime":25,"portId":"f41c85e0-7f26-494e-9ffc-4a06c980f811"}],"timeCues":[{"startTime":0,"endTime":75,"portId":"8dea1941-c520-4f9a-aee0-40932c8542ef"}]}</t>
+          <t>{"guid":"432ff1e3-b18d-476d-af80-d39ddc07402a","nodeType":20,"position":{"x":-646.0,"y":-2456.0},"targetType":1,"skeletonDataAsset":{"instanceID":51576},"animationName":"Skill_attack_1009","animationDuration":"25","isAnimationLooping":false,"timeEffects":[{"triggerTime":4,"portId":"de0ba361-3aba-4ef0-bb07-9b418fcae591"},{"triggerTime":25,"portId":"f41c85e0-7f26-494e-9ffc-4a06c980f811"}],"timeCues":[{"startTime":0,"endTime":75,"portId":"8dea1941-c520-4f9a-aee0-40932c8542ef"}]}</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -1901,7 +1901,7 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>{"guid":"cde57fb8-b693-4da8-a4a8-fd61e56c5dcd","nodeType":12,"position":{"x":-304.0,"y":-2072.0},"targetType":1,"requiredTags":{"_tags":[]},"immunityTags":{"_tags":[]},"destroyWithNode":false,"positionSource":0,"particlePrefab":{"instanceID":56276},"particleBindingName":"down","particleOffset":{"x":0.0,"y":0.0,"z":0.0},"particleScale":{"x":1.0,"y":1.0,"z":1.0},"attachToTarget":false,"particleLoop":false}</t>
+          <t>{"guid":"cde57fb8-b693-4da8-a4a8-fd61e56c5dcd","nodeType":12,"position":{"x":-304.0,"y":-2072.0},"targetType":1,"requiredTags":{"_tags":[]},"immunityTags":{"_tags":[]},"destroyWithNode":false,"positionSource":0,"particlePrefab":{"instanceID":52706},"particleBindingName":"down","particleOffset":{"x":0.0,"y":0.0,"z":0.0},"particleScale":{"x":1.0,"y":1.0,"z":1.0},"attachToTarget":false,"particleLoop":false}</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -1983,7 +1983,7 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>{"guid":"cde57fb8-b693-4da8-a4a8-fd61e56c5dcd","nodeType":12,"position":{"x":677.3333740234375,"y":-1998.666748046875},"targetType":1,"requiredTags":{"_tags":[]},"immunityTags":{"_tags":[]},"destroyWithNode":false,"positionSource":0,"particlePrefab":{"instanceID":56266},"particleBindingName":"down","particleOffset":{"x":0.0,"y":0.0,"z":0.0},"particleScale":{"x":1.0,"y":1.0,"z":1.0},"attachToTarget":false,"particleLoop":false}</t>
+          <t>{"guid":"cde57fb8-b693-4da8-a4a8-fd61e56c5dcd","nodeType":12,"position":{"x":677.3333740234375,"y":-1998.666748046875},"targetType":1,"requiredTags":{"_tags":[]},"immunityTags":{"_tags":[]},"destroyWithNode":false,"positionSource":0,"particlePrefab":{"instanceID":52772},"particleBindingName":"down","particleOffset":{"x":0.0,"y":0.0,"z":0.0},"particleScale":{"x":1.0,"y":1.0,"z":1.0},"attachToTarget":false,"particleLoop":false}</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
@@ -2023,7 +2023,7 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>{"guid":"93ec5a43-cc34-4e4a-acb3-39da2f2c3010","nodeType":12,"position":{"x":468.6666564941406,"y":-1749.3333740234375},"targetType":1,"requiredTags":{"_tags":[]},"immunityTags":{"_tags":[]},"destroyWithNode":true,"positionSource":2,"particlePrefab":{"instanceID":56268},"particleBindingName":"head","particleOffset":{"x":0.0,"y":0.0,"z":0.0},"particleScale":{"x":1.0,"y":1.0,"z":1.0},"attachToTarget":true,"particleLoop":true}</t>
+          <t>{"guid":"93ec5a43-cc34-4e4a-acb3-39da2f2c3010","nodeType":12,"position":{"x":468.6666564941406,"y":-1749.3333740234375},"targetType":1,"requiredTags":{"_tags":[]},"immunityTags":{"_tags":[]},"destroyWithNode":true,"positionSource":2,"particlePrefab":{"instanceID":52774},"particleBindingName":"head","particleOffset":{"x":0.0,"y":0.0,"z":0.0},"particleScale":{"x":1.0,"y":1.0,"z":1.0},"attachToTarget":true,"particleLoop":true}</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
@@ -2083,7 +2083,7 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>{"guid":"432ff1e3-b18d-476d-af80-d39ddc07402a","nodeType":20,"position":{"x":-452.0,"y":-2375.333251953125},"targetType":1,"skeletonDataAsset":{"instanceID":60588},"animationName":"Skill_attack_1005","animationDuration":"16","isAnimationLooping":false,"timeEffects":[{"triggerTime":7,"portId":"de0ba361-3aba-4ef0-bb07-9b418fcae591"},{"triggerTime":16,"portId":"f41c85e0-7f26-494e-9ffc-4a06c980f811"}],"timeCues":[{"startTime":6,"endTime":55,"portId":"8dea1941-c520-4f9a-aee0-40932c8542ef"}]}</t>
+          <t>{"guid":"432ff1e3-b18d-476d-af80-d39ddc07402a","nodeType":20,"position":{"x":-452.0,"y":-2375.333251953125},"targetType":1,"skeletonDataAsset":{"instanceID":51576},"animationName":"Skill_attack_1005","animationDuration":"16","isAnimationLooping":false,"timeEffects":[{"triggerTime":7,"portId":"de0ba361-3aba-4ef0-bb07-9b418fcae591"},{"triggerTime":16,"portId":"f41c85e0-7f26-494e-9ffc-4a06c980f811"}],"timeCues":[{"startTime":6,"endTime":55,"portId":"8dea1941-c520-4f9a-aee0-40932c8542ef"}]}</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
@@ -2165,7 +2165,7 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>{"guid":"432ff1e3-b18d-476d-af80-d39ddc07402a","nodeType":20,"position":{"x":-502.6666564941406,"y":-2384.0},"targetType":1,"skeletonDataAsset":{"instanceID":60588},"animationName":"Stand","animationDuration":"24","isAnimationLooping":false,"timeEffects":[{"triggerTime":25,"portId":"f41c85e0-7f26-494e-9ffc-4a06c980f811"}],"timeCues":[]}</t>
+          <t>{"guid":"432ff1e3-b18d-476d-af80-d39ddc07402a","nodeType":20,"position":{"x":-502.6666564941406,"y":-2384.0},"targetType":1,"skeletonDataAsset":{"instanceID":51576},"animationName":"Stand","animationDuration":"24","isAnimationLooping":false,"timeEffects":[{"triggerTime":25,"portId":"f41c85e0-7f26-494e-9ffc-4a06c980f811"}],"timeCues":[]}</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
@@ -2287,7 +2287,7 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>{"guid":"cde57fb8-b693-4da8-a4a8-fd61e56c5dcd","nodeType":12,"position":{"x":731.3333740234375,"y":-2488.66650390625},"targetType":1,"requiredTags":{"_tags":[]},"immunityTags":{"_tags":[]},"destroyWithNode":false,"positionSource":0,"particlePrefab":{"instanceID":56272},"particleBindingName":"down","particleOffset":{"x":0.0,"y":0.0,"z":0.0},"particleScale":{"x":1.0,"y":1.0,"z":1.0},"attachToTarget":false,"particleLoop":false}</t>
+          <t>{"guid":"cde57fb8-b693-4da8-a4a8-fd61e56c5dcd","nodeType":12,"position":{"x":731.3333740234375,"y":-2488.66650390625},"targetType":1,"requiredTags":{"_tags":[]},"immunityTags":{"_tags":[]},"destroyWithNode":false,"positionSource":0,"particlePrefab":{"instanceID":52512},"particleBindingName":"down","particleOffset":{"x":0.0,"y":0.0,"z":0.0},"particleScale":{"x":1.0,"y":1.0,"z":1.0},"attachToTarget":false,"particleLoop":false}</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
@@ -2407,7 +2407,7 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>{"guid":"432ff1e3-b18d-476d-af80-d39ddc07402a","nodeType":20,"position":{"x":-414.0,"y":-2826.0},"targetType":1,"skeletonDataAsset":{"instanceID":60588},"animationName":"Skill_attack_1001","animationDuration":"18","isAnimationLooping":true,"timeEffects":[{"triggerTime":7,"portId":"de0ba361-3aba-4ef0-bb07-9b418fcae591"},{"triggerTime":18,"portId":"84e238a8-5baf-470e-829f-186695064945"}],"timeCues":[{"startTime":7,"endTime":48,"portId":"8dea1941-c520-4f9a-aee0-40932c8542ef"}]}</t>
+          <t>{"guid":"432ff1e3-b18d-476d-af80-d39ddc07402a","nodeType":20,"position":{"x":-414.0,"y":-2826.0},"targetType":1,"skeletonDataAsset":{"instanceID":51576},"animationName":"Skill_attack_1001","animationDuration":"18","isAnimationLooping":true,"timeEffects":[{"triggerTime":7,"portId":"de0ba361-3aba-4ef0-bb07-9b418fcae591"},{"triggerTime":18,"portId":"84e238a8-5baf-470e-829f-186695064945"}],"timeCues":[{"startTime":7,"endTime":48,"portId":"8dea1941-c520-4f9a-aee0-40932c8542ef"}]}</t>
         </is>
       </c>
       <c r="G74"/>
@@ -2549,7 +2549,7 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>{"guid":"432ff1e3-b18d-476d-af80-d39ddc07402a","nodeType":20,"position":{"x":-238.66665649414063,"y":-2405.333251953125},"targetType":1,"skeletonDataAsset":{"instanceID":60588},"animationName":"Attack_01","animationDuration":"18","isAnimationLooping":false,"timeEffects":[{"triggerTime":7,"portId":"de0ba361-3aba-4ef0-bb07-9b418fcae591"},{"triggerTime":18,"portId":"84e238a8-5baf-470e-829f-186695064945"}],"timeCues":[]}</t>
+          <t>{"guid":"432ff1e3-b18d-476d-af80-d39ddc07402a","nodeType":20,"position":{"x":-238.66665649414063,"y":-2405.333251953125},"targetType":1,"skeletonDataAsset":{"instanceID":51576},"animationName":"Attack_01","animationDuration":"18","isAnimationLooping":false,"timeEffects":[{"triggerTime":7,"portId":"de0ba361-3aba-4ef0-bb07-9b418fcae591"},{"triggerTime":18,"portId":"84e238a8-5baf-470e-829f-186695064945"}],"timeCues":[]}</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
@@ -2569,7 +2569,7 @@
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>{"guid":"ce857360-de7e-4457-b348-9c124ce98879","nodeType":8,"position":{"x":1040.666748046875,"y":-2305.333251953125},"targetType":2,"assetTags":{"_tags":[]},"grantedTags":{"_tags":[]},"applicationRequiredTags":{"_tags":[]},"applicationImmunityTags":{"_tags":[]},"removeGameEffectsWithTags":{"_tags":[]},"durationType":2,"duration":"0","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"_tags":[]},"cancelOnAbilityEnd":false,"launchPositionSource":0,"launchBindingName":"center","targetPositionSource":1,"targetBindingName":"center","projectileTargetType":0,"flyOver":true,"offsetAngle":30.0,"curveHeight":0.0,"projectilePrefab":{"instanceID":56282},"speed":10.0,"maxDistance":10.0,"collisionRadius":0.5,"isPiercing":false,"maxPierceCount":1,"collisionTargetTags":{"_tags":[]},"collisionExcludeTags":{"_tags":[]},"isBouncing":false,"bounceTargetMode":0,"maxBounceCount":3,"bounceSearchRadius":10.0,"canBounceToSameTarget":false,"bounceAngleOffset":0.0}</t>
+          <t>{"guid":"ce857360-de7e-4457-b348-9c124ce98879","nodeType":8,"position":{"x":1040.666748046875,"y":-2305.333251953125},"targetType":2,"assetTags":{"_tags":[]},"grantedTags":{"_tags":[]},"applicationRequiredTags":{"_tags":[]},"applicationImmunityTags":{"_tags":[]},"removeGameEffectsWithTags":{"_tags":[]},"durationType":2,"duration":"0","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"_tags":[]},"cancelOnAbilityEnd":false,"launchPositionSource":0,"launchBindingName":"center","targetPositionSource":1,"targetBindingName":"center","projectileTargetType":0,"flyOver":true,"offsetAngle":30.0,"curveHeight":0.0,"projectilePrefab":{"instanceID":52994},"speed":10.0,"maxDistance":10.0,"collisionRadius":0.5,"isPiercing":false,"maxPierceCount":1,"collisionTargetTags":{"_tags":[]},"collisionExcludeTags":{"_tags":[]},"isBouncing":false,"bounceTargetMode":0,"maxBounceCount":3,"bounceSearchRadius":10.0,"canBounceToSameTarget":false,"bounceAngleOffset":0.0}</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
@@ -2589,7 +2589,7 @@
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>{"guid":"9a695e91-e218-425e-82ed-1e157bf1b014","nodeType":8,"position":{"x":1022.666748046875,"y":-2131.333251953125},"targetType":2,"assetTags":{"_tags":[]},"grantedTags":{"_tags":[]},"applicationRequiredTags":{"_tags":[]},"applicationImmunityTags":{"_tags":[]},"removeGameEffectsWithTags":{"_tags":[]},"durationType":2,"duration":"0","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"_tags":[]},"cancelOnAbilityEnd":false,"launchPositionSource":0,"launchBindingName":"center","targetPositionSource":1,"targetBindingName":"center","projectileTargetType":0,"flyOver":true,"offsetAngle":0.0,"curveHeight":0.0,"projectilePrefab":{"instanceID":56282},"speed":10.0,"maxDistance":10.0,"collisionRadius":0.5,"isPiercing":false,"maxPierceCount":1,"collisionTargetTags":{"_tags":[]},"collisionExcludeTags":{"_tags":[]},"isBouncing":false,"bounceTargetMode":0,"maxBounceCount":3,"bounceSearchRadius":10.0,"canBounceToSameTarget":false,"bounceAngleOffset":0.0}</t>
+          <t>{"guid":"9a695e91-e218-425e-82ed-1e157bf1b014","nodeType":8,"position":{"x":1022.666748046875,"y":-2131.333251953125},"targetType":2,"assetTags":{"_tags":[]},"grantedTags":{"_tags":[]},"applicationRequiredTags":{"_tags":[]},"applicationImmunityTags":{"_tags":[]},"removeGameEffectsWithTags":{"_tags":[]},"durationType":2,"duration":"0","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"_tags":[]},"cancelOnAbilityEnd":false,"launchPositionSource":0,"launchBindingName":"center","targetPositionSource":1,"targetBindingName":"center","projectileTargetType":0,"flyOver":true,"offsetAngle":0.0,"curveHeight":0.0,"projectilePrefab":{"instanceID":52994},"speed":10.0,"maxDistance":10.0,"collisionRadius":0.5,"isPiercing":false,"maxPierceCount":1,"collisionTargetTags":{"_tags":[]},"collisionExcludeTags":{"_tags":[]},"isBouncing":false,"bounceTargetMode":0,"maxBounceCount":3,"bounceSearchRadius":10.0,"canBounceToSameTarget":false,"bounceAngleOffset":0.0}</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
@@ -2609,7 +2609,7 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>{"guid":"d897a922-5756-42cf-ac65-90a48c1e5a17","nodeType":8,"position":{"x":1022.666748046875,"y":-1978.0},"targetType":2,"assetTags":{"_tags":[]},"grantedTags":{"_tags":[]},"applicationRequiredTags":{"_tags":[]},"applicationImmunityTags":{"_tags":[]},"removeGameEffectsWithTags":{"_tags":[]},"durationType":2,"duration":"0","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"_tags":[]},"cancelOnAbilityEnd":false,"launchPositionSource":0,"launchBindingName":"center","targetPositionSource":1,"targetBindingName":"center","projectileTargetType":0,"flyOver":true,"offsetAngle":-30.0,"curveHeight":0.0,"projectilePrefab":{"instanceID":56282},"speed":10.0,"maxDistance":10.0,"collisionRadius":0.5,"isPiercing":false,"maxPierceCount":1,"collisionTargetTags":{"_tags":[]},"collisionExcludeTags":{"_tags":[]},"isBouncing":false,"bounceTargetMode":0,"maxBounceCount":3,"bounceSearchRadius":10.0,"canBounceToSameTarget":false,"bounceAngleOffset":0.0}</t>
+          <t>{"guid":"d897a922-5756-42cf-ac65-90a48c1e5a17","nodeType":8,"position":{"x":1022.666748046875,"y":-1978.0},"targetType":2,"assetTags":{"_tags":[]},"grantedTags":{"_tags":[]},"applicationRequiredTags":{"_tags":[]},"applicationImmunityTags":{"_tags":[]},"removeGameEffectsWithTags":{"_tags":[]},"durationType":2,"duration":"0","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"_tags":[]},"cancelOnAbilityEnd":false,"launchPositionSource":0,"launchBindingName":"center","targetPositionSource":1,"targetBindingName":"center","projectileTargetType":0,"flyOver":true,"offsetAngle":-30.0,"curveHeight":0.0,"projectilePrefab":{"instanceID":52994},"speed":10.0,"maxDistance":10.0,"collisionRadius":0.5,"isPiercing":false,"maxPierceCount":1,"collisionTargetTags":{"_tags":[]},"collisionExcludeTags":{"_tags":[]},"isBouncing":false,"bounceTargetMode":0,"maxBounceCount":3,"bounceSearchRadius":10.0,"canBounceToSameTarget":false,"bounceAngleOffset":0.0}</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
@@ -2729,7 +2729,7 @@
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>{"guid":"cde57fb8-b693-4da8-a4a8-fd61e56c5dcd","nodeType":12,"position":{"x":677.5999755859375,"y":-1998.4000244140625},"targetType":1,"requiredTags":{"_tags":[]},"immunityTags":{"_tags":[]},"destroyWithNode":false,"positionSource":0,"particlePrefab":{"instanceID":56270},"particleBindingName":"down","particleOffset":{"x":0.0,"y":0.0,"z":0.0},"particleScale":{"x":1.0,"y":1.0,"z":1.0},"attachToTarget":false,"particleLoop":false}</t>
+          <t>{"guid":"cde57fb8-b693-4da8-a4a8-fd61e56c5dcd","nodeType":12,"position":{"x":677.5999755859375,"y":-1998.4000244140625},"targetType":1,"requiredTags":{"_tags":[]},"immunityTags":{"_tags":[]},"destroyWithNode":false,"positionSource":0,"particlePrefab":{"instanceID":53034},"particleBindingName":"down","particleOffset":{"x":0.0,"y":0.0,"z":0.0},"particleScale":{"x":1.0,"y":1.0,"z":1.0},"attachToTarget":false,"particleLoop":false}</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
@@ -2769,7 +2769,7 @@
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>{"guid":"432ff1e3-b18d-476d-af80-d39ddc07402a","nodeType":20,"position":{"x":-502.3999938964844,"y":-2384.0},"targetType":1,"skeletonDataAsset":{"instanceID":60588},"animationName":"Skill_attack_1009","animationDuration":"25","isAnimationLooping":false,"timeEffects":[{"triggerTime":4,"portId":"de0ba361-3aba-4ef0-bb07-9b418fcae591"},{"triggerTime":25,"portId":"f41c85e0-7f26-494e-9ffc-4a06c980f811"}],"timeCues":[{"startTime":0,"endTime":75,"portId":"8dea1941-c520-4f9a-aee0-40932c8542ef"}]}</t>
+          <t>{"guid":"432ff1e3-b18d-476d-af80-d39ddc07402a","nodeType":20,"position":{"x":-502.3999938964844,"y":-2384.0},"targetType":1,"skeletonDataAsset":{"instanceID":51576},"animationName":"Skill_attack_1009","animationDuration":"25","isAnimationLooping":false,"timeEffects":[{"triggerTime":4,"portId":"de0ba361-3aba-4ef0-bb07-9b418fcae591"},{"triggerTime":25,"portId":"f41c85e0-7f26-494e-9ffc-4a06c980f811"}],"timeCues":[{"startTime":0,"endTime":75,"portId":"8dea1941-c520-4f9a-aee0-40932c8542ef"}]}</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
@@ -2871,7 +2871,7 @@
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>{"guid":"cde57fb8-b693-4da8-a4a8-fd61e56c5dcd","nodeType":12,"position":{"x":677.5999755859375,"y":-1998.4000244140625},"targetType":1,"requiredTags":{"_tags":[]},"immunityTags":{"_tags":[]},"destroyWithNode":true,"positionSource":0,"particlePrefab":{"instanceID":56278},"particleBindingName":"down","particleOffset":{"x":0.0,"y":0.0,"z":0.0},"particleScale":{"x":1.0,"y":1.0,"z":1.0},"attachToTarget":true,"particleLoop":true}</t>
+          <t>{"guid":"cde57fb8-b693-4da8-a4a8-fd61e56c5dcd","nodeType":12,"position":{"x":677.5999755859375,"y":-1998.4000244140625},"targetType":1,"requiredTags":{"_tags":[]},"immunityTags":{"_tags":[]},"destroyWithNode":true,"positionSource":0,"particlePrefab":{"instanceID":53122},"particleBindingName":"down","particleOffset":{"x":0.0,"y":0.0,"z":0.0},"particleScale":{"x":1.0,"y":1.0,"z":1.0},"attachToTarget":true,"particleLoop":true}</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>{"guid":"432ff1e3-b18d-476d-af80-d39ddc07402a","nodeType":20,"position":{"x":-452.0,"y":-2375.199951171875},"targetType":1,"skeletonDataAsset":{"instanceID":60588},"animationName":"Skill_attack_1011","animationDuration":"12","isAnimationLooping":true,"timeEffects":[{"triggerTime":250,"portId":"f41c85e0-7f26-494e-9ffc-4a06c980f811"}],"timeCues":[{"startTime":0,"endTime":255,"portId":"8dea1941-c520-4f9a-aee0-40932c8542ef"}]}</t>
+          <t>{"guid":"432ff1e3-b18d-476d-af80-d39ddc07402a","nodeType":20,"position":{"x":-452.0,"y":-2375.199951171875},"targetType":1,"skeletonDataAsset":{"instanceID":51576},"animationName":"Skill_attack_1011","animationDuration":"12","isAnimationLooping":true,"timeEffects":[{"triggerTime":250,"portId":"f41c85e0-7f26-494e-9ffc-4a06c980f811"}],"timeCues":[{"startTime":0,"endTime":255,"portId":"8dea1941-c520-4f9a-aee0-40932c8542ef"}]}</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">

--- a/Design/Excel/ET/Datas/Game/SkillGraph.xlsx
+++ b/Design/Excel/ET/Datas/Game/SkillGraph.xlsx
@@ -1011,7 +1011,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>{"guid":"a8c2d6c0-65f1-4bed-8a6a-70197e84bb56","nodeType":2,"position":{"x":933.3333740234375,"y":226.6666717529297},"targetType":1,"assetTags":{"_tags":[]},"grantedTags":{"_tags":[]},"applicationRequiredTags":{"_tags":[]},"applicationImmunityTags":{"_tags":[]},"removeGameEffectsWithTags":{"_tags":[]},"durationType":0,"duration":"0","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"_tags":[]},"cancelOnAbilityEnd":false,"healSourceType":0,"healFixedValue":2.0,"healFormula":"","healMMCType":0,"healSetByCallerKey":"","healMMCCaptureAttribute":202,"healMMCAttributeSource":0,"healMMCCoefficient":1.0,"healMMCUseSnapshot":true,"healMultiplyByStackCount":false,"healCalculationType":0}</t>
+          <t>{"guid":"a8c2d6c0-65f1-4bed-8a6a-70197e84bb56","nodeType":2,"position":{"x":933.3333740234375,"y":226.66667175292969},"targetType":1,"assetTags":{"_tags":[]},"grantedTags":{"_tags":[]},"applicationRequiredTags":{"_tags":[]},"applicationImmunityTags":{"_tags":[]},"removeGameEffectsWithTags":{"_tags":[]},"durationType":0,"duration":"0","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"_tags":[]},"cancelOnAbilityEnd":false,"healSourceType":0,"healFixedValue":2.0,"healFormula":"","healMMCType":0,"healSetByCallerKey":"","healMMCCaptureAttribute":202,"healMMCAttributeSource":0,"healMMCCoefficient":1.0,"healMMCUseSnapshot":true,"healMultiplyByStackCount":false,"healCalculationType":0}</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -1031,7 +1031,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>{"guid":"d086a8c9-8557-4a61-8fd2-64b3c1e543a3","nodeType":14,"position":{"x":1148.666748046875,"y":208.00001525878907},"targetType":1,"requiredTags":{"_tags":[]},"immunityTags":{"_tags":[]},"destroyWithNode":false,"positionSource":0,"positionBindingName":"head","textType":1,"fixedText":"","contextDataKey":"Heal","textColor":{"r":0.04063582420349121,"g":1.0,"b":0.0,"a":1.0},"criticalColor":{"r":1.0,"g":0.5,"b":0.0,"a":1.0},"missColor":{"r":0.5,"g":0.5,"b":0.5,"a":1.0},"fontSize":45.0,"criticalFontSize":60.0,"duration":1.5,"offset":{"x":0.0,"y":0.0},"moveDirection":{"x":0.0,"y":1.0}}</t>
+          <t>{"guid":"d086a8c9-8557-4a61-8fd2-64b3c1e543a3","nodeType":14,"position":{"x":1148.666748046875,"y":208.00001525878906},"targetType":1,"requiredTags":{"_tags":[]},"immunityTags":{"_tags":[]},"destroyWithNode":false,"positionSource":0,"positionBindingName":"head","textType":1,"fixedText":"","contextDataKey":"Heal","textColor":{"r":0.040635824203491211,"g":1.0,"b":0.0,"a":1.0},"criticalColor":{"r":1.0,"g":0.5,"b":0.0,"a":1.0},"missColor":{"r":0.5,"g":0.5,"b":0.5,"a":1.0},"fontSize":45.0,"criticalFontSize":60.0,"duration":1.5,"offset":{"x":0.0,"y":0.0},"moveDirection":{"x":0.0,"y":1.0}}</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -1051,7 +1051,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>{"guid":"7eefd9ae-c57e-439d-b1b6-e7f4e52f2f6f","nodeType":10,"position":{"x":370.6666564941406,"y":484.6666564941406},"targetType":1,"assetTags":{"_tags":[]},"grantedTags":{"_tags":[{"_name":"CD.BeRecBlood","_hashCode":-1099994396,"_shortName":"被动回血","_ancestorHashCodes":[-1137859925],"_ancestorNames":["CD"]}]},"applicationRequiredTags":{"_tags":[]},"applicationImmunityTags":{"_tags":[]},"removeGameEffectsWithTags":{"_tags":[]},"durationType":1,"duration":"3","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"_tags":[]},"cancelOnAbilityEnd":false,"cooldownType":0,"maxCharges":2,"chargeTime":"10"}</t>
+          <t>{"guid":"7eefd9ae-c57e-439d-b1b6-e7f4e52f2f6f","nodeType":10,"position":{"x":370.66665649414063,"y":484.66665649414063},"targetType":1,"assetTags":{"_tags":[]},"grantedTags":{"_tags":[{"_name":"CD.BeRecBlood","_hashCode":-1099994396,"_shortName":"被动回血","_ancestorHashCodes":[-1137859925],"_ancestorNames":["CD"]}]},"applicationRequiredTags":{"_tags":[]},"applicationImmunityTags":{"_tags":[]},"removeGameEffectsWithTags":{"_tags":[]},"durationType":1,"duration":"3","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"_tags":[]},"cancelOnAbilityEnd":false,"cooldownType":0,"maxCharges":2,"chargeTime":"10"}</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>{"guid":"d5809887-df6e-4604-bd09-36cef191ce83","nodeType":0,"position":{"x":210.66668701171876,"y":114.66667175292969},"targetType":1,"skillId":2001,"assetTags":{"_tags":[]},"cancelAbilitiesWithTags":{"_tags":[]},"blockAbilitiesWithTags":{"_tags":[]},"activationOwnedTags":{"_tags":[]},"activationRequiredTags":{"_tags":[]},"activationBlockedTags":{"_tags":[]},"ongoingBlockedTags":{"_tags":[]},"eventOutputPorts":[{"eventType":2,"customEventTag":""}]}</t>
+          <t>{"guid":"d5809887-df6e-4604-bd09-36cef191ce83","nodeType":0,"position":{"x":210.66668701171875,"y":114.66667175292969},"targetType":1,"skillId":2001,"assetTags":{"_tags":[]},"cancelAbilitiesWithTags":{"_tags":[]},"blockAbilitiesWithTags":{"_tags":[]},"activationOwnedTags":{"_tags":[]},"activationRequiredTags":{"_tags":[]},"activationBlockedTags":{"_tags":[]},"ongoingBlockedTags":{"_tags":[]},"eventOutputPorts":[{"eventType":2,"customEventTag":""}]}</t>
         </is>
       </c>
       <c r="G9"/>
@@ -1113,7 +1113,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>{"guid":"cde57fb8-b693-4da8-a4a8-fd61e56c5dcd","nodeType":12,"position":{"x":677.3333740234375,"y":-1998.666748046875},"targetType":1,"requiredTags":{"_tags":[]},"immunityTags":{"_tags":[]},"destroyWithNode":false,"positionSource":0,"particlePrefab":{"instanceID":52512},"particleBindingName":"down","particleOffset":{"x":0.0,"y":0.0,"z":0.0},"particleScale":{"x":1.0,"y":1.0,"z":1.0},"attachToTarget":false,"particleLoop":false}</t>
+          <t>{"guid":"cde57fb8-b693-4da8-a4a8-fd61e56c5dcd","nodeType":12,"position":{"x":677.3333740234375,"y":-1998.666748046875},"targetType":1,"requiredTags":{"_tags":[]},"immunityTags":{"_tags":[]},"destroyWithNode":false,"positionSource":0,"particlePrefab":null,"particlePrefabPath":"Assets/Res/Prefab/Effect/ef_Zhanshi_attack_02.prefab","particleBindingName":"down","particleOffset":{"x":0.0,"y":0.0,"z":0.0},"particleScale":{"x":1.0,"y":1.0,"z":1.0},"attachToTarget":false,"particleLoop":false}</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -1173,7 +1173,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>{"guid":"c353e286-8ef0-460a-b917-887f2aeb390a","nodeType":14,"position":{"x":383.3333435058594,"y":-1531.3333740234375},"targetType":1,"requiredTags":{"_tags":[]},"immunityTags":{"_tags":[]},"destroyWithNode":false,"positionSource":2,"positionBindingName":"head","textType":0,"fixedText":"","contextDataKey":"DamageResult","textColor":{"r":1.0,"g":0.0,"b":0.0,"a":1.0},"criticalColor":{"r":1.0,"g":0.5,"b":0.0,"a":1.0},"missColor":{"r":0.5,"g":0.5,"b":0.5,"a":1.0},"fontSize":45.0,"criticalFontSize":60.0,"duration":1.5,"offset":{"x":0.0,"y":0.0},"moveDirection":{"x":0.0,"y":1.0}}</t>
+          <t>{"guid":"c353e286-8ef0-460a-b917-887f2aeb390a","nodeType":14,"position":{"x":383.33334350585938,"y":-1531.3333740234375},"targetType":1,"requiredTags":{"_tags":[]},"immunityTags":{"_tags":[]},"destroyWithNode":false,"positionSource":2,"positionBindingName":"head","textType":0,"fixedText":"","contextDataKey":"DamageResult","textColor":{"r":1.0,"g":0.0,"b":0.0,"a":1.0},"criticalColor":{"r":1.0,"g":0.5,"b":0.0,"a":1.0},"missColor":{"r":0.5,"g":0.5,"b":0.5,"a":1.0},"fontSize":45.0,"criticalFontSize":60.0,"duration":1.5,"offset":{"x":0.0,"y":0.0},"moveDirection":{"x":0.0,"y":1.0}}</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -1273,7 +1273,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>{"guid":"432ff1e3-b18d-476d-af80-d39ddc07402a","nodeType":20,"position":{"x":-472.0,"y":-2380.66650390625},"targetType":1,"skeletonDataAsset":{"instanceID":51576},"animationName":"Attack_02","animationDuration":"22","isAnimationLooping":false,"timeEffects":[{"triggerTime":7,"portId":"de0ba361-3aba-4ef0-bb07-9b418fcae591"},{"triggerTime":22,"portId":"97dc121c-84b7-4f94-9997-02e0e5b2ea6c"}],"timeCues":[{"startTime":7,"endTime":48,"portId":"8dea1941-c520-4f9a-aee0-40932c8542ef"}]}</t>
+          <t>{"guid":"432ff1e3-b18d-476d-af80-d39ddc07402a","nodeType":20,"position":{"x":-472.0,"y":-2380.66650390625},"targetType":1,"skeletonDataAsset":null,"skeletonDataAssetPath":"Assets/Res/Spine/SP_Zhanshi/SP_Zhanshi_SkeletonData.asset","animationName":"Attack_02","animationDuration":"22","isAnimationLooping":false,"timeEffects":[{"triggerTime":7,"portId":"de0ba361-3aba-4ef0-bb07-9b418fcae591"},{"triggerTime":22,"portId":"97dc121c-84b7-4f94-9997-02e0e5b2ea6c"}],"timeCues":[{"startTime":7,"endTime":48,"portId":"8dea1941-c520-4f9a-aee0-40932c8542ef"}]}</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -1355,7 +1355,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>{"guid":"2d7e41c4-8e90-4b61-879c-4b2e5b9486db","nodeType":14,"position":{"x":408.6666564941406,"y":-1747.3333740234375},"targetType":1,"requiredTags":{"_tags":[]},"immunityTags":{"_tags":[]},"destroyWithNode":false,"positionSource":2,"positionBindingName":"head","textType":0,"fixedText":"","contextDataKey":"DamageResult","textColor":{"r":0.0,"g":0.323091983795166,"b":1.0,"a":1.0},"criticalColor":{"r":1.0,"g":0.5,"b":0.0,"a":1.0},"missColor":{"r":0.5,"g":0.5,"b":0.5,"a":1.0},"fontSize":45.0,"criticalFontSize":60.0,"duration":1.5,"offset":{"x":0.0,"y":0.0},"moveDirection":{"x":0.0,"y":1.0}}</t>
+          <t>{"guid":"2d7e41c4-8e90-4b61-879c-4b2e5b9486db","nodeType":14,"position":{"x":408.66665649414063,"y":-1747.3333740234375},"targetType":1,"requiredTags":{"_tags":[]},"immunityTags":{"_tags":[]},"destroyWithNode":false,"positionSource":2,"positionBindingName":"head","textType":0,"fixedText":"","contextDataKey":"DamageResult","textColor":{"r":0.0,"g":0.323091983795166,"b":1.0,"a":1.0},"criticalColor":{"r":1.0,"g":0.5,"b":0.0,"a":1.0},"missColor":{"r":0.5,"g":0.5,"b":0.5,"a":1.0},"fontSize":45.0,"criticalFontSize":60.0,"duration":1.5,"offset":{"x":0.0,"y":0.0},"moveDirection":{"x":0.0,"y":1.0}}</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -1395,7 +1395,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>{"guid":"432ff1e3-b18d-476d-af80-d39ddc07402a","nodeType":20,"position":{"x":-491.33331298828127,"y":-2478.66650390625},"targetType":1,"skeletonDataAsset":{"instanceID":51714},"animationName":"Attack","animationDuration":"24","isAnimationLooping":false,"timeEffects":[{"triggerTime":11,"portId":"de0ba361-3aba-4ef0-bb07-9b418fcae591"},{"triggerTime":24,"portId":"7ecf9fe6-7c5e-46ae-bade-7922214225e2"}],"timeCues":[]}</t>
+          <t>{"guid":"432ff1e3-b18d-476d-af80-d39ddc07402a","nodeType":20,"position":{"x":-491.33331298828125,"y":-2478.66650390625},"targetType":1,"skeletonDataAsset":null,"skeletonDataAssetPath":"Assets/Res/Spine/SP_Xiyiguai/SP_Xiyiguai_SkeletonData.asset","animationName":"Attack","animationDuration":"24","isAnimationLooping":false,"timeEffects":[{"triggerTime":11,"portId":"de0ba361-3aba-4ef0-bb07-9b418fcae591"},{"triggerTime":24,"portId":"7ecf9fe6-7c5e-46ae-bade-7922214225e2"}],"timeCues":[]}</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -1415,7 +1415,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>{"guid":"90bacd9f-d882-4bba-aaa8-41ed993ac3ff","nodeType":8,"position":{"x":-401.33331298828127,"y":-1826.666748046875},"targetType":2,"assetTags":{"_tags":[]},"grantedTags":{"_tags":[]},"applicationRequiredTags":{"_tags":[]},"applicationImmunityTags":{"_tags":[]},"removeGameEffectsWithTags":{"_tags":[]},"durationType":2,"duration":"0","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"_tags":[]},"cancelOnAbilityEnd":false,"launchPositionSource":0,"launchBindingName":"center","targetPositionSource":1,"targetBindingName":"center","projectileTargetType":0,"flyOver":false,"offsetAngle":0.0,"curveHeight":0.0,"projectilePrefab":{"instanceID":52550},"speed":3.0,"maxDistance":10.0,"collisionRadius":0.5,"isPiercing":false,"maxPierceCount":1,"collisionTargetTags":{"_tags":[]},"collisionExcludeTags":{"_tags":[]},"isBouncing":false,"bounceTargetMode":0,"maxBounceCount":3,"bounceSearchRadius":10.0,"canBounceToSameTarget":false,"bounceAngleOffset":0.0}</t>
+          <t>{"guid":"90bacd9f-d882-4bba-aaa8-41ed993ac3ff","nodeType":8,"position":{"x":-401.33331298828125,"y":-1826.666748046875},"targetType":2,"assetTags":{"_tags":[]},"grantedTags":{"_tags":[]},"applicationRequiredTags":{"_tags":[]},"applicationImmunityTags":{"_tags":[]},"removeGameEffectsWithTags":{"_tags":[]},"durationType":2,"duration":"0","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"_tags":[]},"cancelOnAbilityEnd":false,"launchPositionSource":0,"launchBindingName":"center","targetPositionSource":1,"targetBindingName":"center","projectileTargetType":0,"flyOver":false,"offsetAngle":0.0,"curveHeight":0.0,"projectilePrefab":null,"projectilePrefabPath":"Assets/Res/Prefab/Effect/ef_fashi_gandian_buff.prefab","speed":3.0,"maxDistance":10.0,"collisionRadius":0.5,"isPiercing":false,"maxPierceCount":1,"collisionTargetTags":{"_tags":[]},"collisionExcludeTags":{"_tags":[]},"isBouncing":false,"bounceTargetMode":0,"maxBounceCount":3,"bounceSearchRadius":10.0,"canBounceToSameTarget":false,"bounceAngleOffset":0.0}</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -1517,7 +1517,7 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>{"guid":"2d7e41c4-8e90-4b61-879c-4b2e5b9486db","nodeType":14,"position":{"x":408.6666564941406,"y":-1747.3333740234375},"targetType":1,"requiredTags":{"_tags":[]},"immunityTags":{"_tags":[]},"destroyWithNode":false,"positionSource":2,"positionBindingName":"head","textType":0,"fixedText":"","contextDataKey":"DamageResult","textColor":{"r":0.0,"g":0.323091983795166,"b":1.0,"a":1.0},"criticalColor":{"r":1.0,"g":0.5,"b":0.0,"a":1.0},"missColor":{"r":0.5,"g":0.5,"b":0.5,"a":1.0},"fontSize":45.0,"criticalFontSize":60.0,"duration":1.5,"offset":{"x":0.0,"y":0.0},"moveDirection":{"x":0.0,"y":1.0}}</t>
+          <t>{"guid":"2d7e41c4-8e90-4b61-879c-4b2e5b9486db","nodeType":14,"position":{"x":408.66665649414063,"y":-1747.3333740234375},"targetType":1,"requiredTags":{"_tags":[]},"immunityTags":{"_tags":[]},"destroyWithNode":false,"positionSource":2,"positionBindingName":"head","textType":0,"fixedText":"","contextDataKey":"DamageResult","textColor":{"r":0.0,"g":0.323091983795166,"b":1.0,"a":1.0},"criticalColor":{"r":1.0,"g":0.5,"b":0.0,"a":1.0},"missColor":{"r":0.5,"g":0.5,"b":0.5,"a":1.0},"fontSize":45.0,"criticalFontSize":60.0,"duration":1.5,"offset":{"x":0.0,"y":0.0},"moveDirection":{"x":0.0,"y":1.0}}</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -1557,7 +1557,7 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>{"guid":"432ff1e3-b18d-476d-af80-d39ddc07402a","nodeType":20,"position":{"x":-491.33331298828127,"y":-2478.66650390625},"targetType":1,"skeletonDataAsset":{"instanceID":51576},"animationName":"Attack_01","animationDuration":"18","isAnimationLooping":false,"timeEffects":[{"triggerTime":11,"portId":"de0ba361-3aba-4ef0-bb07-9b418fcae591"},{"triggerTime":24,"portId":"7ecf9fe6-7c5e-46ae-bade-7922214225e2"}],"timeCues":[]}</t>
+          <t>{"guid":"432ff1e3-b18d-476d-af80-d39ddc07402a","nodeType":20,"position":{"x":-491.33331298828125,"y":-2478.66650390625},"targetType":1,"skeletonDataAsset":null,"skeletonDataAssetPath":"Assets/Res/Spine/SP_Zhanshi/SP_Zhanshi_SkeletonData.asset","animationName":"Attack_01","animationDuration":"18","isAnimationLooping":false,"timeEffects":[{"triggerTime":11,"portId":"de0ba361-3aba-4ef0-bb07-9b418fcae591"},{"triggerTime":24,"portId":"7ecf9fe6-7c5e-46ae-bade-7922214225e2"}],"timeCues":[]}</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -1617,7 +1617,7 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>{"guid":"90bacd9f-d882-4bba-aaa8-41ed993ac3ff","nodeType":8,"position":{"x":-400.6666564941406,"y":-1836.666748046875},"targetType":2,"assetTags":{"_tags":[]},"grantedTags":{"_tags":[]},"applicationRequiredTags":{"_tags":[]},"applicationImmunityTags":{"_tags":[]},"removeGameEffectsWithTags":{"_tags":[]},"durationType":2,"duration":"0","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"_tags":[]},"cancelOnAbilityEnd":false,"launchPositionSource":0,"launchBindingName":"center","targetPositionSource":1,"targetBindingName":"center","projectileTargetType":0,"flyOver":false,"offsetAngle":0.0,"curveHeight":0.0,"projectilePrefab":{"instanceID":52550},"speed":3.0,"maxDistance":10.0,"collisionRadius":0.5,"isPiercing":false,"maxPierceCount":1,"collisionTargetTags":{"_tags":[]},"collisionExcludeTags":{"_tags":[]},"isBouncing":true,"bounceTargetMode":0,"maxBounceCount":2,"bounceSearchRadius":10.0,"canBounceToSameTarget":false,"bounceAngleOffset":50.0}</t>
+          <t>{"guid":"90bacd9f-d882-4bba-aaa8-41ed993ac3ff","nodeType":8,"position":{"x":-400.66665649414063,"y":-1836.666748046875},"targetType":2,"assetTags":{"_tags":[]},"grantedTags":{"_tags":[]},"applicationRequiredTags":{"_tags":[]},"applicationImmunityTags":{"_tags":[]},"removeGameEffectsWithTags":{"_tags":[]},"durationType":2,"duration":"0","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"_tags":[]},"cancelOnAbilityEnd":false,"launchPositionSource":0,"launchBindingName":"center","targetPositionSource":1,"targetBindingName":"center","projectileTargetType":0,"flyOver":false,"offsetAngle":0.0,"curveHeight":0.0,"projectilePrefab":null,"projectilePrefabPath":"Assets/Res/Prefab/Effect/ef_fashi_gandian_buff.prefab","speed":3.0,"maxDistance":10.0,"collisionRadius":0.5,"isPiercing":false,"maxPierceCount":1,"collisionTargetTags":{"_tags":[]},"collisionExcludeTags":{"_tags":[]},"isBouncing":true,"bounceTargetMode":0,"maxBounceCount":2,"bounceSearchRadius":10.0,"canBounceToSameTarget":false,"bounceAngleOffset":50.0}</t>
         </is>
       </c>
       <c r="G35"/>
@@ -1679,7 +1679,7 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>{"guid":"cde57fb8-b693-4da8-a4a8-fd61e56c5dcd","nodeType":12,"position":{"x":677.3333740234375,"y":-1998.666748046875},"targetType":1,"requiredTags":{"_tags":[]},"immunityTags":{"_tags":[]},"destroyWithNode":false,"positionSource":0,"particlePrefab":{"instanceID":52610},"particleBindingName":"down","particleOffset":{"x":0.0,"y":0.0,"z":0.0},"particleScale":{"x":1.0,"y":1.0,"z":1.0},"attachToTarget":false,"particleLoop":false}</t>
+          <t>{"guid":"cde57fb8-b693-4da8-a4a8-fd61e56c5dcd","nodeType":12,"position":{"x":677.3333740234375,"y":-1998.666748046875},"targetType":1,"requiredTags":{"_tags":[]},"immunityTags":{"_tags":[]},"destroyWithNode":false,"positionSource":0,"particlePrefab":null,"particlePrefabPath":"Assets/Res/Prefab/Effect/ef_Zhanshi_zhandounuhou_01.prefab","particleBindingName":"down","particleOffset":{"x":0.0,"y":0.0,"z":0.0},"particleScale":{"x":1.0,"y":1.0,"z":1.0},"attachToTarget":false,"particleLoop":false}</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -1719,7 +1719,7 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>{"guid":"091ecddb-f80b-4c00-aa06-f9bc718618d2","nodeType":22,"position":{"x":-93.33332824707031,"y":-1708.666748046875},"targetType":0,"assetTags":{"_tags":[]},"grantedTags":{"_tags":[]},"applicationRequiredTags":{"_tags":[]},"applicationImmunityTags":{"_tags":[]},"removeGameEffectsWithTags":{"_tags":[]},"durationType":1,"duration":"0.5","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"_tags":[]},"cancelOnAbilityEnd":false,"displaceType":1,"speed":10.0,"distance":3.0,"minDistance":0.5,"pointSource":0,"pointBindingName":""}</t>
+          <t>{"guid":"091ecddb-f80b-4c00-aa06-f9bc718618d2","nodeType":22,"position":{"x":-93.333328247070313,"y":-1708.666748046875},"targetType":0,"assetTags":{"_tags":[]},"grantedTags":{"_tags":[]},"applicationRequiredTags":{"_tags":[]},"applicationImmunityTags":{"_tags":[]},"removeGameEffectsWithTags":{"_tags":[]},"durationType":1,"duration":"0.5","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"_tags":[]},"cancelOnAbilityEnd":false,"displaceType":1,"speed":10.0,"distance":3.0,"minDistance":0.5,"pointSource":0,"pointBindingName":""}</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -1759,7 +1759,7 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>{"guid":"432ff1e3-b18d-476d-af80-d39ddc07402a","nodeType":20,"position":{"x":-646.0,"y":-2456.0},"targetType":1,"skeletonDataAsset":{"instanceID":51576},"animationName":"Skill_attack_1009","animationDuration":"25","isAnimationLooping":false,"timeEffects":[{"triggerTime":4,"portId":"de0ba361-3aba-4ef0-bb07-9b418fcae591"},{"triggerTime":25,"portId":"f41c85e0-7f26-494e-9ffc-4a06c980f811"}],"timeCues":[{"startTime":0,"endTime":75,"portId":"8dea1941-c520-4f9a-aee0-40932c8542ef"}]}</t>
+          <t>{"guid":"432ff1e3-b18d-476d-af80-d39ddc07402a","nodeType":20,"position":{"x":-646.0,"y":-2456.0},"targetType":1,"skeletonDataAsset":null,"skeletonDataAssetPath":"Assets/Res/Spine/SP_Zhanshi/SP_Zhanshi_SkeletonData.asset","animationName":"Skill_attack_1009","animationDuration":"25","isAnimationLooping":false,"timeEffects":[{"triggerTime":4,"portId":"de0ba361-3aba-4ef0-bb07-9b418fcae591"},{"triggerTime":25,"portId":"f41c85e0-7f26-494e-9ffc-4a06c980f811"}],"timeCues":[{"startTime":0,"endTime":75,"portId":"8dea1941-c520-4f9a-aee0-40932c8542ef"}]}</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -1821,7 +1821,7 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>{"guid":"5fb21a71-2fff-4477-b79b-4c1a8bc10f9a","nodeType":2,"position":{"x":-571.2000122070313,"y":-1987.199951171875},"targetType":1,"assetTags":{"_tags":[]},"grantedTags":{"_tags":[]},"applicationRequiredTags":{"_tags":[]},"applicationImmunityTags":{"_tags":[]},"removeGameEffectsWithTags":{"_tags":[]},"durationType":0,"duration":"0","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"_tags":[]},"cancelOnAbilityEnd":false,"healSourceType":0,"healFixedValue":10.0,"healFormula":"","healMMCType":0,"healSetByCallerKey":"","healMMCCaptureAttribute":202,"healMMCAttributeSource":0,"healMMCCoefficient":1.0,"healMMCUseSnapshot":true,"healMultiplyByStackCount":false,"healCalculationType":0}</t>
+          <t>{"guid":"5fb21a71-2fff-4477-b79b-4c1a8bc10f9a","nodeType":2,"position":{"x":-571.20001220703125,"y":-1987.199951171875},"targetType":1,"assetTags":{"_tags":[]},"grantedTags":{"_tags":[]},"applicationRequiredTags":{"_tags":[]},"applicationImmunityTags":{"_tags":[]},"removeGameEffectsWithTags":{"_tags":[]},"durationType":0,"duration":"0","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"_tags":[]},"cancelOnAbilityEnd":false,"healSourceType":0,"healFixedValue":10.0,"healFormula":"","healMMCType":0,"healSetByCallerKey":"","healMMCCaptureAttribute":202,"healMMCAttributeSource":0,"healMMCCoefficient":1.0,"healMMCUseSnapshot":true,"healMultiplyByStackCount":false,"healCalculationType":0}</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -1841,7 +1841,7 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>{"guid":"011aad56-e96c-41eb-9d85-e793d74a40bb","nodeType":7,"position":{"x":-333.6000061035156,"y":-1780.0},"targetType":1,"endType":0}</t>
+          <t>{"guid":"011aad56-e96c-41eb-9d85-e793d74a40bb","nodeType":7,"position":{"x":-333.60000610351563,"y":-1780.0},"targetType":1,"endType":0}</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -1901,7 +1901,7 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>{"guid":"cde57fb8-b693-4da8-a4a8-fd61e56c5dcd","nodeType":12,"position":{"x":-304.0,"y":-2072.0},"targetType":1,"requiredTags":{"_tags":[]},"immunityTags":{"_tags":[]},"destroyWithNode":false,"positionSource":0,"particlePrefab":{"instanceID":52706},"particleBindingName":"down","particleOffset":{"x":0.0,"y":0.0,"z":0.0},"particleScale":{"x":1.0,"y":1.0,"z":1.0},"attachToTarget":false,"particleLoop":false}</t>
+          <t>{"guid":"cde57fb8-b693-4da8-a4a8-fd61e56c5dcd","nodeType":12,"position":{"x":-304.0,"y":-2072.0},"targetType":1,"requiredTags":{"_tags":[]},"immunityTags":{"_tags":[]},"destroyWithNode":false,"positionSource":0,"particlePrefab":null,"particlePrefabPath":"Assets/Res/Prefab/Effect/ef_skill_zhanshi_huifunengliang.prefab","particleBindingName":"down","particleOffset":{"x":0.0,"y":0.0,"z":0.0},"particleScale":{"x":1.0,"y":1.0,"z":1.0},"attachToTarget":false,"particleLoop":false}</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>{"guid":"becb4d53-8a9e-4dc0-95a3-618d1e79ecc7","nodeType":14,"position":{"x":-313.6000061035156,"y":-1951.199951171875},"targetType":1,"requiredTags":{"_tags":[]},"immunityTags":{"_tags":[]},"destroyWithNode":false,"positionSource":2,"positionBindingName":"head","textType":1,"fixedText":"","contextDataKey":"Heal","textColor":{"r":0.0,"g":1.0,"b":0.10971927642822266,"a":1.0},"criticalColor":{"r":1.0,"g":0.5,"b":0.0,"a":1.0},"missColor":{"r":0.5,"g":0.5,"b":0.5,"a":1.0},"fontSize":45.0,"criticalFontSize":60.0,"duration":1.5,"offset":{"x":0.0,"y":0.0},"moveDirection":{"x":0.0,"y":1.0}}</t>
+          <t>{"guid":"becb4d53-8a9e-4dc0-95a3-618d1e79ecc7","nodeType":14,"position":{"x":-313.60000610351563,"y":-1951.199951171875},"targetType":1,"requiredTags":{"_tags":[]},"immunityTags":{"_tags":[]},"destroyWithNode":false,"positionSource":2,"positionBindingName":"head","textType":1,"fixedText":"","contextDataKey":"Heal","textColor":{"r":0.0,"g":1.0,"b":0.10971927642822266,"a":1.0},"criticalColor":{"r":1.0,"g":0.5,"b":0.0,"a":1.0},"missColor":{"r":0.5,"g":0.5,"b":0.5,"a":1.0},"fontSize":45.0,"criticalFontSize":60.0,"duration":1.5,"offset":{"x":0.0,"y":0.0},"moveDirection":{"x":0.0,"y":1.0}}</t>
         </is>
       </c>
       <c r="G50"/>
@@ -1983,7 +1983,7 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>{"guid":"cde57fb8-b693-4da8-a4a8-fd61e56c5dcd","nodeType":12,"position":{"x":677.3333740234375,"y":-1998.666748046875},"targetType":1,"requiredTags":{"_tags":[]},"immunityTags":{"_tags":[]},"destroyWithNode":false,"positionSource":0,"particlePrefab":{"instanceID":52772},"particleBindingName":"down","particleOffset":{"x":0.0,"y":0.0,"z":0.0},"particleScale":{"x":1.0,"y":1.0,"z":1.0},"attachToTarget":false,"particleLoop":false}</t>
+          <t>{"guid":"cde57fb8-b693-4da8-a4a8-fd61e56c5dcd","nodeType":12,"position":{"x":677.3333740234375,"y":-1998.666748046875},"targetType":1,"requiredTags":{"_tags":[]},"immunityTags":{"_tags":[]},"destroyWithNode":false,"positionSource":0,"particlePrefab":null,"particlePrefabPath":"Assets/Res/Prefab/Effect/ef_zhanshi_jcjt_01.prefab","particleBindingName":"down","particleOffset":{"x":0.0,"y":0.0,"z":0.0},"particleScale":{"x":1.0,"y":1.0,"z":1.0},"attachToTarget":false,"particleLoop":false}</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
@@ -2023,7 +2023,7 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>{"guid":"93ec5a43-cc34-4e4a-acb3-39da2f2c3010","nodeType":12,"position":{"x":468.6666564941406,"y":-1749.3333740234375},"targetType":1,"requiredTags":{"_tags":[]},"immunityTags":{"_tags":[]},"destroyWithNode":true,"positionSource":2,"particlePrefab":{"instanceID":52774},"particleBindingName":"head","particleOffset":{"x":0.0,"y":0.0,"z":0.0},"particleScale":{"x":1.0,"y":1.0,"z":1.0},"attachToTarget":true,"particleLoop":true}</t>
+          <t>{"guid":"93ec5a43-cc34-4e4a-acb3-39da2f2c3010","nodeType":12,"position":{"x":468.66665649414063,"y":-1749.3333740234375},"targetType":1,"requiredTags":{"_tags":[]},"immunityTags":{"_tags":[]},"destroyWithNode":true,"positionSource":2,"particlePrefab":null,"particlePrefabPath":"Assets/Res/Prefab/Effect/ef_Xuanyun_01.prefab","particleBindingName":"head","particleOffset":{"x":0.0,"y":0.0,"z":0.0},"particleScale":{"x":1.0,"y":1.0,"z":1.0},"attachToTarget":true,"particleLoop":true}</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
@@ -2083,7 +2083,7 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>{"guid":"432ff1e3-b18d-476d-af80-d39ddc07402a","nodeType":20,"position":{"x":-452.0,"y":-2375.333251953125},"targetType":1,"skeletonDataAsset":{"instanceID":51576},"animationName":"Skill_attack_1005","animationDuration":"16","isAnimationLooping":false,"timeEffects":[{"triggerTime":7,"portId":"de0ba361-3aba-4ef0-bb07-9b418fcae591"},{"triggerTime":16,"portId":"f41c85e0-7f26-494e-9ffc-4a06c980f811"}],"timeCues":[{"startTime":6,"endTime":55,"portId":"8dea1941-c520-4f9a-aee0-40932c8542ef"}]}</t>
+          <t>{"guid":"432ff1e3-b18d-476d-af80-d39ddc07402a","nodeType":20,"position":{"x":-452.0,"y":-2375.333251953125},"targetType":1,"skeletonDataAsset":null,"skeletonDataAssetPath":"Assets/Res/Spine/SP_Zhanshi/SP_Zhanshi_SkeletonData.asset","animationName":"Skill_attack_1005","animationDuration":"16","isAnimationLooping":false,"timeEffects":[{"triggerTime":7,"portId":"de0ba361-3aba-4ef0-bb07-9b418fcae591"},{"triggerTime":16,"portId":"f41c85e0-7f26-494e-9ffc-4a06c980f811"}],"timeCues":[{"startTime":6,"endTime":55,"portId":"8dea1941-c520-4f9a-aee0-40932c8542ef"}]}</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
@@ -2165,7 +2165,7 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>{"guid":"432ff1e3-b18d-476d-af80-d39ddc07402a","nodeType":20,"position":{"x":-502.6666564941406,"y":-2384.0},"targetType":1,"skeletonDataAsset":{"instanceID":51576},"animationName":"Stand","animationDuration":"24","isAnimationLooping":false,"timeEffects":[{"triggerTime":25,"portId":"f41c85e0-7f26-494e-9ffc-4a06c980f811"}],"timeCues":[]}</t>
+          <t>{"guid":"432ff1e3-b18d-476d-af80-d39ddc07402a","nodeType":20,"position":{"x":-502.66665649414063,"y":-2384.0},"targetType":1,"skeletonDataAsset":null,"skeletonDataAssetPath":"Assets/Res/Spine/SP_Zhanshi/SP_Zhanshi_SkeletonData.asset","animationName":"Stand","animationDuration":"24","isAnimationLooping":false,"timeEffects":[{"triggerTime":25,"portId":"f41c85e0-7f26-494e-9ffc-4a06c980f811"}],"timeCues":[]}</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
@@ -2287,7 +2287,7 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>{"guid":"cde57fb8-b693-4da8-a4a8-fd61e56c5dcd","nodeType":12,"position":{"x":731.3333740234375,"y":-2488.66650390625},"targetType":1,"requiredTags":{"_tags":[]},"immunityTags":{"_tags":[]},"destroyWithNode":false,"positionSource":0,"particlePrefab":{"instanceID":52512},"particleBindingName":"down","particleOffset":{"x":0.0,"y":0.0,"z":0.0},"particleScale":{"x":1.0,"y":1.0,"z":1.0},"attachToTarget":false,"particleLoop":false}</t>
+          <t>{"guid":"cde57fb8-b693-4da8-a4a8-fd61e56c5dcd","nodeType":12,"position":{"x":731.3333740234375,"y":-2488.66650390625},"targetType":1,"requiredTags":{"_tags":[]},"immunityTags":{"_tags":[]},"destroyWithNode":false,"positionSource":0,"particlePrefab":null,"particlePrefabPath":"Assets/Res/Prefab/Effect/ef_Zhanshi_attack_02.prefab","particleBindingName":"down","particleOffset":{"x":0.0,"y":0.0,"z":0.0},"particleScale":{"x":1.0,"y":1.0,"z":1.0},"attachToTarget":false,"particleLoop":false}</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
@@ -2407,7 +2407,7 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>{"guid":"432ff1e3-b18d-476d-af80-d39ddc07402a","nodeType":20,"position":{"x":-414.0,"y":-2826.0},"targetType":1,"skeletonDataAsset":{"instanceID":51576},"animationName":"Skill_attack_1001","animationDuration":"18","isAnimationLooping":true,"timeEffects":[{"triggerTime":7,"portId":"de0ba361-3aba-4ef0-bb07-9b418fcae591"},{"triggerTime":18,"portId":"84e238a8-5baf-470e-829f-186695064945"}],"timeCues":[{"startTime":7,"endTime":48,"portId":"8dea1941-c520-4f9a-aee0-40932c8542ef"}]}</t>
+          <t>{"guid":"432ff1e3-b18d-476d-af80-d39ddc07402a","nodeType":20,"position":{"x":-414.0,"y":-2826.0},"targetType":1,"skeletonDataAsset":null,"skeletonDataAssetPath":"Assets/Res/Spine/SP_Zhanshi/SP_Zhanshi_SkeletonData.asset","animationName":"Skill_attack_1001","animationDuration":"18","isAnimationLooping":true,"timeEffects":[{"triggerTime":7,"portId":"de0ba361-3aba-4ef0-bb07-9b418fcae591"},{"triggerTime":18,"portId":"84e238a8-5baf-470e-829f-186695064945"}],"timeCues":[{"startTime":7,"endTime":48,"portId":"8dea1941-c520-4f9a-aee0-40932c8542ef"}]}</t>
         </is>
       </c>
       <c r="G74"/>
@@ -2549,7 +2549,7 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>{"guid":"432ff1e3-b18d-476d-af80-d39ddc07402a","nodeType":20,"position":{"x":-238.66665649414063,"y":-2405.333251953125},"targetType":1,"skeletonDataAsset":{"instanceID":51576},"animationName":"Attack_01","animationDuration":"18","isAnimationLooping":false,"timeEffects":[{"triggerTime":7,"portId":"de0ba361-3aba-4ef0-bb07-9b418fcae591"},{"triggerTime":18,"portId":"84e238a8-5baf-470e-829f-186695064945"}],"timeCues":[]}</t>
+          <t>{"guid":"432ff1e3-b18d-476d-af80-d39ddc07402a","nodeType":20,"position":{"x":-238.66665649414063,"y":-2405.333251953125},"targetType":1,"skeletonDataAsset":null,"skeletonDataAssetPath":"Assets/Res/Spine/SP_Zhanshi/SP_Zhanshi_SkeletonData.asset","animationName":"Attack_01","animationDuration":"18","isAnimationLooping":false,"timeEffects":[{"triggerTime":7,"portId":"de0ba361-3aba-4ef0-bb07-9b418fcae591"},{"triggerTime":18,"portId":"84e238a8-5baf-470e-829f-186695064945"}],"timeCues":[]}</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
@@ -2569,7 +2569,7 @@
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>{"guid":"ce857360-de7e-4457-b348-9c124ce98879","nodeType":8,"position":{"x":1040.666748046875,"y":-2305.333251953125},"targetType":2,"assetTags":{"_tags":[]},"grantedTags":{"_tags":[]},"applicationRequiredTags":{"_tags":[]},"applicationImmunityTags":{"_tags":[]},"removeGameEffectsWithTags":{"_tags":[]},"durationType":2,"duration":"0","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"_tags":[]},"cancelOnAbilityEnd":false,"launchPositionSource":0,"launchBindingName":"center","targetPositionSource":1,"targetBindingName":"center","projectileTargetType":0,"flyOver":true,"offsetAngle":30.0,"curveHeight":0.0,"projectilePrefab":{"instanceID":52994},"speed":10.0,"maxDistance":10.0,"collisionRadius":0.5,"isPiercing":false,"maxPierceCount":1,"collisionTargetTags":{"_tags":[]},"collisionExcludeTags":{"_tags":[]},"isBouncing":false,"bounceTargetMode":0,"maxBounceCount":3,"bounceSearchRadius":10.0,"canBounceToSameTarget":false,"bounceAngleOffset":0.0}</t>
+          <t>{"guid":"ce857360-de7e-4457-b348-9c124ce98879","nodeType":8,"position":{"x":1040.666748046875,"y":-2305.333251953125},"targetType":2,"assetTags":{"_tags":[]},"grantedTags":{"_tags":[]},"applicationRequiredTags":{"_tags":[]},"applicationImmunityTags":{"_tags":[]},"removeGameEffectsWithTags":{"_tags":[]},"durationType":2,"duration":"0","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"_tags":[]},"cancelOnAbilityEnd":false,"launchPositionSource":0,"launchBindingName":"center","targetPositionSource":1,"targetBindingName":"center","projectileTargetType":0,"flyOver":true,"offsetAngle":30.0,"curveHeight":0.0,"projectilePrefab":null,"projectilePrefabPath":"Assets/Res/Prefab/Effect/ef_fashi_huoyandan01.prefab","speed":10.0,"maxDistance":10.0,"collisionRadius":0.5,"isPiercing":false,"maxPierceCount":1,"collisionTargetTags":{"_tags":[]},"collisionExcludeTags":{"_tags":[]},"isBouncing":false,"bounceTargetMode":0,"maxBounceCount":3,"bounceSearchRadius":10.0,"canBounceToSameTarget":false,"bounceAngleOffset":0.0}</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
@@ -2589,7 +2589,7 @@
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>{"guid":"9a695e91-e218-425e-82ed-1e157bf1b014","nodeType":8,"position":{"x":1022.666748046875,"y":-2131.333251953125},"targetType":2,"assetTags":{"_tags":[]},"grantedTags":{"_tags":[]},"applicationRequiredTags":{"_tags":[]},"applicationImmunityTags":{"_tags":[]},"removeGameEffectsWithTags":{"_tags":[]},"durationType":2,"duration":"0","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"_tags":[]},"cancelOnAbilityEnd":false,"launchPositionSource":0,"launchBindingName":"center","targetPositionSource":1,"targetBindingName":"center","projectileTargetType":0,"flyOver":true,"offsetAngle":0.0,"curveHeight":0.0,"projectilePrefab":{"instanceID":52994},"speed":10.0,"maxDistance":10.0,"collisionRadius":0.5,"isPiercing":false,"maxPierceCount":1,"collisionTargetTags":{"_tags":[]},"collisionExcludeTags":{"_tags":[]},"isBouncing":false,"bounceTargetMode":0,"maxBounceCount":3,"bounceSearchRadius":10.0,"canBounceToSameTarget":false,"bounceAngleOffset":0.0}</t>
+          <t>{"guid":"9a695e91-e218-425e-82ed-1e157bf1b014","nodeType":8,"position":{"x":1022.666748046875,"y":-2131.333251953125},"targetType":2,"assetTags":{"_tags":[]},"grantedTags":{"_tags":[]},"applicationRequiredTags":{"_tags":[]},"applicationImmunityTags":{"_tags":[]},"removeGameEffectsWithTags":{"_tags":[]},"durationType":2,"duration":"0","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"_tags":[]},"cancelOnAbilityEnd":false,"launchPositionSource":0,"launchBindingName":"center","targetPositionSource":1,"targetBindingName":"center","projectileTargetType":0,"flyOver":true,"offsetAngle":0.0,"curveHeight":0.0,"projectilePrefab":null,"projectilePrefabPath":"Assets/Res/Prefab/Effect/ef_fashi_huoyandan01.prefab","speed":10.0,"maxDistance":10.0,"collisionRadius":0.5,"isPiercing":false,"maxPierceCount":1,"collisionTargetTags":{"_tags":[]},"collisionExcludeTags":{"_tags":[]},"isBouncing":false,"bounceTargetMode":0,"maxBounceCount":3,"bounceSearchRadius":10.0,"canBounceToSameTarget":false,"bounceAngleOffset":0.0}</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
@@ -2609,7 +2609,7 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>{"guid":"d897a922-5756-42cf-ac65-90a48c1e5a17","nodeType":8,"position":{"x":1022.666748046875,"y":-1978.0},"targetType":2,"assetTags":{"_tags":[]},"grantedTags":{"_tags":[]},"applicationRequiredTags":{"_tags":[]},"applicationImmunityTags":{"_tags":[]},"removeGameEffectsWithTags":{"_tags":[]},"durationType":2,"duration":"0","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"_tags":[]},"cancelOnAbilityEnd":false,"launchPositionSource":0,"launchBindingName":"center","targetPositionSource":1,"targetBindingName":"center","projectileTargetType":0,"flyOver":true,"offsetAngle":-30.0,"curveHeight":0.0,"projectilePrefab":{"instanceID":52994},"speed":10.0,"maxDistance":10.0,"collisionRadius":0.5,"isPiercing":false,"maxPierceCount":1,"collisionTargetTags":{"_tags":[]},"collisionExcludeTags":{"_tags":[]},"isBouncing":false,"bounceTargetMode":0,"maxBounceCount":3,"bounceSearchRadius":10.0,"canBounceToSameTarget":false,"bounceAngleOffset":0.0}</t>
+          <t>{"guid":"d897a922-5756-42cf-ac65-90a48c1e5a17","nodeType":8,"position":{"x":1022.666748046875,"y":-1978.0},"targetType":2,"assetTags":{"_tags":[]},"grantedTags":{"_tags":[]},"applicationRequiredTags":{"_tags":[]},"applicationImmunityTags":{"_tags":[]},"removeGameEffectsWithTags":{"_tags":[]},"durationType":2,"duration":"0","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"_tags":[]},"cancelOnAbilityEnd":false,"launchPositionSource":0,"launchBindingName":"center","targetPositionSource":1,"targetBindingName":"center","projectileTargetType":0,"flyOver":true,"offsetAngle":-30.0,"curveHeight":0.0,"projectilePrefab":null,"projectilePrefabPath":"Assets/Res/Prefab/Effect/ef_fashi_huoyandan01.prefab","speed":10.0,"maxDistance":10.0,"collisionRadius":0.5,"isPiercing":false,"maxPierceCount":1,"collisionTargetTags":{"_tags":[]},"collisionExcludeTags":{"_tags":[]},"isBouncing":false,"bounceTargetMode":0,"maxBounceCount":3,"bounceSearchRadius":10.0,"canBounceToSameTarget":false,"bounceAngleOffset":0.0}</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
@@ -2689,7 +2689,7 @@
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>{"guid":"091ecddb-f80b-4c00-aa06-f9bc718618d2","nodeType":22,"position":{"x":-93.60000610351563,"y":-1708.800048828125},"targetType":0,"assetTags":{"_tags":[]},"grantedTags":{"_tags":[]},"applicationRequiredTags":{"_tags":[]},"applicationImmunityTags":{"_tags":[]},"removeGameEffectsWithTags":{"_tags":[]},"durationType":1,"duration":"0.5","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"_tags":[]},"cancelOnAbilityEnd":false,"displaceType":0,"speed":10.0,"distance":3.0,"minDistance":0.5,"pointSource":0,"pointBindingName":""}</t>
+          <t>{"guid":"091ecddb-f80b-4c00-aa06-f9bc718618d2","nodeType":22,"position":{"x":-93.600006103515625,"y":-1708.800048828125},"targetType":0,"assetTags":{"_tags":[]},"grantedTags":{"_tags":[]},"applicationRequiredTags":{"_tags":[]},"applicationImmunityTags":{"_tags":[]},"removeGameEffectsWithTags":{"_tags":[]},"durationType":1,"duration":"0.5","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"_tags":[]},"cancelOnAbilityEnd":false,"displaceType":0,"speed":10.0,"distance":3.0,"minDistance":0.5,"pointSource":0,"pointBindingName":""}</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
@@ -2729,7 +2729,7 @@
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>{"guid":"cde57fb8-b693-4da8-a4a8-fd61e56c5dcd","nodeType":12,"position":{"x":677.5999755859375,"y":-1998.4000244140625},"targetType":1,"requiredTags":{"_tags":[]},"immunityTags":{"_tags":[]},"destroyWithNode":false,"positionSource":0,"particlePrefab":{"instanceID":53034},"particleBindingName":"down","particleOffset":{"x":0.0,"y":0.0,"z":0.0},"particleScale":{"x":1.0,"y":1.0,"z":1.0},"attachToTarget":false,"particleLoop":false}</t>
+          <t>{"guid":"cde57fb8-b693-4da8-a4a8-fd61e56c5dcd","nodeType":12,"position":{"x":677.5999755859375,"y":-1998.4000244140625},"targetType":1,"requiredTags":{"_tags":[]},"immunityTags":{"_tags":[]},"destroyWithNode":false,"positionSource":0,"particlePrefab":null,"particlePrefabPath":"Assets/Res/Prefab/Effect/ef_Zhanshi_zhentianpaoxiao_01.prefab","particleBindingName":"down","particleOffset":{"x":0.0,"y":0.0,"z":0.0},"particleScale":{"x":1.0,"y":1.0,"z":1.0},"attachToTarget":false,"particleLoop":false}</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
@@ -2769,7 +2769,7 @@
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>{"guid":"432ff1e3-b18d-476d-af80-d39ddc07402a","nodeType":20,"position":{"x":-502.3999938964844,"y":-2384.0},"targetType":1,"skeletonDataAsset":{"instanceID":51576},"animationName":"Skill_attack_1009","animationDuration":"25","isAnimationLooping":false,"timeEffects":[{"triggerTime":4,"portId":"de0ba361-3aba-4ef0-bb07-9b418fcae591"},{"triggerTime":25,"portId":"f41c85e0-7f26-494e-9ffc-4a06c980f811"}],"timeCues":[{"startTime":0,"endTime":75,"portId":"8dea1941-c520-4f9a-aee0-40932c8542ef"}]}</t>
+          <t>{"guid":"432ff1e3-b18d-476d-af80-d39ddc07402a","nodeType":20,"position":{"x":-502.39999389648438,"y":-2384.0},"targetType":1,"skeletonDataAsset":null,"skeletonDataAssetPath":"Assets/Res/Spine/SP_Zhanshi/SP_Zhanshi_SkeletonData.asset","animationName":"Skill_attack_1009","animationDuration":"25","isAnimationLooping":false,"timeEffects":[{"triggerTime":4,"portId":"de0ba361-3aba-4ef0-bb07-9b418fcae591"},{"triggerTime":25,"portId":"f41c85e0-7f26-494e-9ffc-4a06c980f811"}],"timeCues":[{"startTime":0,"endTime":75,"portId":"8dea1941-c520-4f9a-aee0-40932c8542ef"}]}</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
@@ -2851,7 +2851,7 @@
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>{"guid":"a32d1135-94db-4f81-95ba-9d5f105ef8d0","nodeType":1,"position":{"x":308.79998779296877,"y":-1720.0},"targetType":0,"assetTags":{"_tags":[]},"grantedTags":{"_tags":[]},"applicationRequiredTags":{"_tags":[]},"applicationImmunityTags":{"_tags":[]},"removeGameEffectsWithTags":{"_tags":[]},"durationType":0,"duration":"0","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"_tags":[]},"cancelOnAbilityEnd":true,"damageType":0,"damageSourceType":0,"damageFixedValue":1.0,"damageFormula":"","damageMMCType":0,"damageSetByCallerKey":"","damageMMCCaptureAttribute":200,"damageMMCAttributeSource":0,"damageMMCCoefficient":1.0,"damageMMCUseSnapshot":true,"damageMultiplyByStackCount":false,"damageCalculationType":0}</t>
+          <t>{"guid":"a32d1135-94db-4f81-95ba-9d5f105ef8d0","nodeType":1,"position":{"x":308.79998779296875,"y":-1720.0},"targetType":0,"assetTags":{"_tags":[]},"grantedTags":{"_tags":[]},"applicationRequiredTags":{"_tags":[]},"applicationImmunityTags":{"_tags":[]},"removeGameEffectsWithTags":{"_tags":[]},"durationType":0,"duration":"0","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"_tags":[]},"cancelOnAbilityEnd":true,"damageType":0,"damageSourceType":0,"damageFixedValue":1.0,"damageFormula":"","damageMMCType":0,"damageSetByCallerKey":"","damageMMCCaptureAttribute":200,"damageMMCAttributeSource":0,"damageMMCCoefficient":1.0,"damageMMCUseSnapshot":true,"damageMultiplyByStackCount":false,"damageCalculationType":0}</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
@@ -2871,7 +2871,7 @@
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>{"guid":"cde57fb8-b693-4da8-a4a8-fd61e56c5dcd","nodeType":12,"position":{"x":677.5999755859375,"y":-1998.4000244140625},"targetType":1,"requiredTags":{"_tags":[]},"immunityTags":{"_tags":[]},"destroyWithNode":true,"positionSource":0,"particlePrefab":{"instanceID":53122},"particleBindingName":"down","particleOffset":{"x":0.0,"y":0.0,"z":0.0},"particleScale":{"x":1.0,"y":1.0,"z":1.0},"attachToTarget":true,"particleLoop":true}</t>
+          <t>{"guid":"cde57fb8-b693-4da8-a4a8-fd61e56c5dcd","nodeType":12,"position":{"x":677.5999755859375,"y":-1998.4000244140625},"targetType":1,"requiredTags":{"_tags":[]},"immunityTags":{"_tags":[]},"destroyWithNode":true,"positionSource":0,"particlePrefab":null,"particlePrefabPath":"Assets/Res/Prefab/Effect/ef_zhanshi_xfz_01.prefab","particleBindingName":"down","particleOffset":{"x":0.0,"y":0.0,"z":0.0},"particleScale":{"x":1.0,"y":1.0,"z":1.0},"attachToTarget":true,"particleLoop":true}</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>{"guid":"d8847c3e-459e-4589-a96b-37ebb5ec458b","nodeType":21,"position":{"x":-308.79998779296877,"y":-1769.5999755859375},"targetType":1,"assetTags":{"_tags":[]},"grantedTags":{"_tags":[]},"applicationRequiredTags":{"_tags":[]},"applicationImmunityTags":{"_tags":[]},"removeGameEffectsWithTags":{"_tags":[]},"durationType":2,"duration":"0","isPeriodic":true,"period":"0.3","executeOnApplication":false,"attributeModifiers":[],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"_tags":[]},"cancelOnAbilityEnd":true}</t>
+          <t>{"guid":"d8847c3e-459e-4589-a96b-37ebb5ec458b","nodeType":21,"position":{"x":-308.79998779296875,"y":-1769.5999755859375},"targetType":1,"assetTags":{"_tags":[]},"grantedTags":{"_tags":[]},"applicationRequiredTags":{"_tags":[]},"applicationImmunityTags":{"_tags":[]},"removeGameEffectsWithTags":{"_tags":[]},"durationType":2,"duration":"0","isPeriodic":true,"period":"0.3","executeOnApplication":false,"attributeModifiers":[],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"_tags":[]},"cancelOnAbilityEnd":true}</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>{"guid":"432ff1e3-b18d-476d-af80-d39ddc07402a","nodeType":20,"position":{"x":-452.0,"y":-2375.199951171875},"targetType":1,"skeletonDataAsset":{"instanceID":51576},"animationName":"Skill_attack_1011","animationDuration":"12","isAnimationLooping":true,"timeEffects":[{"triggerTime":250,"portId":"f41c85e0-7f26-494e-9ffc-4a06c980f811"}],"timeCues":[{"startTime":0,"endTime":255,"portId":"8dea1941-c520-4f9a-aee0-40932c8542ef"}]}</t>
+          <t>{"guid":"432ff1e3-b18d-476d-af80-d39ddc07402a","nodeType":20,"position":{"x":-452.0,"y":-2375.199951171875},"targetType":1,"skeletonDataAsset":null,"skeletonDataAssetPath":"Assets/Res/Spine/SP_Zhanshi/SP_Zhanshi_SkeletonData.asset","animationName":"Skill_attack_1011","animationDuration":"12","isAnimationLooping":true,"timeEffects":[{"triggerTime":250,"portId":"f41c85e0-7f26-494e-9ffc-4a06c980f811"}],"timeCues":[{"startTime":0,"endTime":255,"portId":"8dea1941-c520-4f9a-aee0-40932c8542ef"}]}</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">

--- a/Design/Excel/ET/Datas/Game/SkillGraph.xlsx
+++ b/Design/Excel/ET/Datas/Game/SkillGraph.xlsx
@@ -1016,7 +1016,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>{"outputNodeGuid":"426755b7-c39a-4524-9cb5-960a31a19c10","outputPortName":"每周期执行","inputNodeGuid":"a8c2d6c0-65f1-4bed-8a6a-70197e84bb56","inputPortName":"输入"}</t>
+          <t>{"outputNodeGuid":"426755b7-c39a-4524-9cb5-960a31a19c10","outputPortId":3002,"legacyOutputPortName":"每周期执行","inputNodeGuid":"a8c2d6c0-65f1-4bed-8a6a-70197e84bb56","inputPortId":7001,"inputPortName":"输入"}</t>
         </is>
       </c>
       <c r="H5"/>
@@ -1036,7 +1036,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>{"outputNodeGuid":"a8c2d6c0-65f1-4bed-8a6a-70197e84bb56","outputPortName":"完成效果","inputNodeGuid":"d086a8c9-8557-4a61-8fd2-64b3c1e543a3","inputPortName":"输入"}</t>
+          <t>{"outputNodeGuid":"a8c2d6c0-65f1-4bed-8a6a-70197e84bb56","outputPortId":3004,"legacyOutputPortName":"完成效果","inputNodeGuid":"d086a8c9-8557-4a61-8fd2-64b3c1e543a3","inputPortId":7001,"inputPortName":"输入"}</t>
         </is>
       </c>
       <c r="H6"/>
@@ -1056,7 +1056,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>{"outputNodeGuid":"d5809887-df6e-4604-bd09-36cef191ce83","outputPortName":"激活","inputNodeGuid":"426755b7-c39a-4524-9cb5-960a31a19c10","inputPortName":"输入"}</t>
+          <t>{"outputNodeGuid":"d5809887-df6e-4604-bd09-36cef191ce83","outputPortId":1001,"legacyOutputPortName":"激活","inputNodeGuid":"426755b7-c39a-4524-9cb5-960a31a19c10","inputPortId":7001,"inputPortName":"输入"}</t>
         </is>
       </c>
       <c r="H7"/>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>{"outputNodeGuid":"7eefd9ae-c57e-439d-b1b6-e7f4e52f2f6f","outputPortName":"完成效果","inputNodeGuid":"426755b7-c39a-4524-9cb5-960a31a19c10","inputPortName":"输入"}</t>
+          <t>{"outputNodeGuid":"7eefd9ae-c57e-439d-b1b6-e7f4e52f2f6f","outputPortId":3004,"legacyOutputPortName":"完成效果","inputNodeGuid":"426755b7-c39a-4524-9cb5-960a31a19c10","inputPortId":7001,"inputPortName":"输入"}</t>
         </is>
       </c>
       <c r="H8"/>
@@ -1091,7 +1091,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>{"guid":"d5809887-df6e-4604-bd09-36cef191ce83","nodeType":0,"position":{"x":210.66668701171875,"y":114.66667175292969},"targetType":1,"skillId":2001,"assetTags":{"_tags":[]},"cancelAbilitiesWithTags":{"_tags":[]},"blockAbilitiesWithTags":{"_tags":[]},"activationOwnedTags":{"_tags":[]},"activationRequiredTags":{"_tags":[]},"activationBlockedTags":{"_tags":[]},"ongoingBlockedTags":{"_tags":[]},"eventOutputPorts":[{"eventType":2,"customEventTag":""}]}</t>
+          <t>{"guid":"d5809887-df6e-4604-bd09-36cef191ce83","nodeType":0,"position":{"x":210.66668701171875,"y":114.66667175292969},"targetType":1,"skillId":2001,"assetTags":{"_tags":[]},"cancelAbilitiesWithTags":{"_tags":[]},"blockAbilitiesWithTags":{"_tags":[]},"activationOwnedTags":{"_tags":[]},"activationRequiredTags":{"_tags":[]},"activationBlockedTags":{"_tags":[]},"ongoingBlockedTags":{"_tags":[]},"eventOutputPorts":[{"eventType":2,"portIdValue":1103,"legacyPortId":"","customEventTag":""}]}</t>
         </is>
       </c>
       <c r="G9"/>
@@ -1118,7 +1118,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>{"outputNodeGuid":"432ff1e3-b18d-476d-af80-d39ddc07402a","outputPortName":"8dea1941-c520-4f9a-aee0-40932c8542ef","inputNodeGuid":"cde57fb8-b693-4da8-a4a8-fd61e56c5dcd","inputPortName":"输入"}</t>
+          <t>{"outputNodeGuid":"432ff1e3-b18d-476d-af80-d39ddc07402a","outputPortId":2287012,"legacyOutputPortName":"8dea1941-c520-4f9a-aee0-40932c8542ef","inputNodeGuid":"cde57fb8-b693-4da8-a4a8-fd61e56c5dcd","inputPortId":7001,"inputPortName":"输入"}</t>
         </is>
       </c>
       <c r="H10"/>
@@ -1138,7 +1138,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>{"outputNodeGuid":"356907e0-1488-4128-bfcc-7ff73cfc3330","outputPortName":"动画","inputNodeGuid":"432ff1e3-b18d-476d-af80-d39ddc07402a","inputPortName":"输入"}</t>
+          <t>{"outputNodeGuid":"356907e0-1488-4128-bfcc-7ff73cfc3330","outputPortId":1002,"legacyOutputPortName":"动画","inputNodeGuid":"432ff1e3-b18d-476d-af80-d39ddc07402a","inputPortId":7001,"inputPortName":"输入"}</t>
         </is>
       </c>
       <c r="H11"/>
@@ -1158,7 +1158,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>{"outputNodeGuid":"356907e0-1488-4128-bfcc-7ff73cfc3330","outputPortName":"冷却","inputNodeGuid":"c28fb88d-51b1-47b2-be59-859e0ac638e3","inputPortName":"输入"}</t>
+          <t>{"outputNodeGuid":"356907e0-1488-4128-bfcc-7ff73cfc3330","outputPortId":1004,"legacyOutputPortName":"冷却","inputNodeGuid":"c28fb88d-51b1-47b2-be59-859e0ac638e3","inputPortId":7001,"inputPortName":"输入"}</t>
         </is>
       </c>
       <c r="H12"/>
@@ -1178,7 +1178,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>{"outputNodeGuid":"356907e0-1488-4128-bfcc-7ff73cfc3330","outputPortName":"消耗","inputNodeGuid":"9d6f459d-b588-4b64-843b-1b71e8f299ae","inputPortName":"输入"}</t>
+          <t>{"outputNodeGuid":"356907e0-1488-4128-bfcc-7ff73cfc3330","outputPortId":1003,"legacyOutputPortName":"消耗","inputNodeGuid":"9d6f459d-b588-4b64-843b-1b71e8f299ae","inputPortId":7001,"inputPortName":"输入"}</t>
         </is>
       </c>
       <c r="H13"/>
@@ -1198,7 +1198,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>{"outputNodeGuid":"432ff1e3-b18d-476d-af80-d39ddc07402a","outputPortName":"de0ba361-3aba-4ef0-bb07-9b418fcae591","inputNodeGuid":"e33ab94c-1496-4d6a-ba5e-1afd38bb0c30","inputPortName":"输入"}</t>
+          <t>{"outputNodeGuid":"432ff1e3-b18d-476d-af80-d39ddc07402a","outputPortId":2315086,"legacyOutputPortName":"de0ba361-3aba-4ef0-bb07-9b418fcae591","inputNodeGuid":"e33ab94c-1496-4d6a-ba5e-1afd38bb0c30","inputPortId":7001,"inputPortName":"输入"}</t>
         </is>
       </c>
       <c r="H14"/>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>{"outputNodeGuid":"f8947676-1084-4228-b991-1509cc7fe851","outputPortName":"完成效果","inputNodeGuid":"c353e286-8ef0-460a-b917-887f2aeb390a","inputPortName":"输入"}</t>
+          <t>{"outputNodeGuid":"f8947676-1084-4228-b991-1509cc7fe851","outputPortId":3004,"legacyOutputPortName":"完成效果","inputNodeGuid":"c353e286-8ef0-460a-b917-887f2aeb390a","inputPortId":7001,"inputPortName":"输入"}</t>
         </is>
       </c>
       <c r="H15"/>
@@ -1238,7 +1238,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>{"outputNodeGuid":"e33ab94c-1496-4d6a-ba5e-1afd38bb0c30","outputPortName":"对每个目标","inputNodeGuid":"cb1df36f-5729-423e-9d1a-287db5a433f0","inputPortName":"输入"}</t>
+          <t>{"outputNodeGuid":"e33ab94c-1496-4d6a-ba5e-1afd38bb0c30","outputPortId":4001,"legacyOutputPortName":"对每个目标","inputNodeGuid":"cb1df36f-5729-423e-9d1a-287db5a433f0","inputPortId":7001,"inputPortName":"输入"}</t>
         </is>
       </c>
       <c r="H16"/>
@@ -1258,7 +1258,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>{"outputNodeGuid":"cb1df36f-5729-423e-9d1a-287db5a433f0","outputPortName":"每周期执行","inputNodeGuid":"f8947676-1084-4228-b991-1509cc7fe851","inputPortName":"输入"}</t>
+          <t>{"outputNodeGuid":"cb1df36f-5729-423e-9d1a-287db5a433f0","outputPortId":3002,"legacyOutputPortName":"每周期执行","inputNodeGuid":"f8947676-1084-4228-b991-1509cc7fe851","inputPortId":7001,"inputPortName":"输入"}</t>
         </is>
       </c>
       <c r="H17"/>
@@ -1273,12 +1273,12 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>{"guid":"432ff1e3-b18d-476d-af80-d39ddc07402a","nodeType":20,"position":{"x":-472.0,"y":-2380.66650390625},"targetType":1,"skeletonDataAsset":null,"skeletonDataAssetPath":"Assets/Res/Spine/SP_Zhanshi/SP_Zhanshi_SkeletonData.asset","animationName":"Attack_02","animationDuration":"22","isAnimationLooping":false,"timeEffects":[{"triggerTime":7,"portId":"de0ba361-3aba-4ef0-bb07-9b418fcae591"},{"triggerTime":22,"portId":"97dc121c-84b7-4f94-9997-02e0e5b2ea6c"}],"timeCues":[{"startTime":7,"endTime":48,"portId":"8dea1941-c520-4f9a-aee0-40932c8542ef"}]}</t>
+          <t>{"guid":"432ff1e3-b18d-476d-af80-d39ddc07402a","nodeType":20,"position":{"x":-472.0,"y":-2380.66650390625},"targetType":1,"skeletonDataAsset":null,"skeletonDataAssetPath":"Assets/Res/Spine/SP_Zhanshi/SP_Zhanshi_SkeletonData.asset","animationName":"Attack_02","animationDuration":"22","isAnimationLooping":false,"timeEffects":[{"triggerTime":7,"portIdValue":2315086,"legacyPortId":"de0ba361-3aba-4ef0-bb07-9b418fcae591"},{"triggerTime":22,"portIdValue":2821173,"legacyPortId":"97dc121c-84b7-4f94-9997-02e0e5b2ea6c"}],"timeCues":[{"startTime":7,"endTime":48,"portIdValue":2287012,"legacyPortId":"8dea1941-c520-4f9a-aee0-40932c8542ef"}]}</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>{"outputNodeGuid":"432ff1e3-b18d-476d-af80-d39ddc07402a","outputPortName":"97dc121c-84b7-4f94-9997-02e0e5b2ea6c","inputNodeGuid":"011aad56-e96c-41eb-9d85-e793d74a40bb","inputPortName":"输入"}</t>
+          <t>{"outputNodeGuid":"432ff1e3-b18d-476d-af80-d39ddc07402a","outputPortId":2821173,"legacyOutputPortName":"97dc121c-84b7-4f94-9997-02e0e5b2ea6c","inputNodeGuid":"011aad56-e96c-41eb-9d85-e793d74a40bb","inputPortId":7001,"inputPortName":"输入"}</t>
         </is>
       </c>
       <c r="H18"/>
@@ -1320,7 +1320,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>{"outputNodeGuid":"356907e0-1488-4128-bfcc-7ff73cfc3330","outputPortName":"动画","inputNodeGuid":"432ff1e3-b18d-476d-af80-d39ddc07402a","inputPortName":"输入"}</t>
+          <t>{"outputNodeGuid":"356907e0-1488-4128-bfcc-7ff73cfc3330","outputPortId":1002,"legacyOutputPortName":"动画","inputNodeGuid":"432ff1e3-b18d-476d-af80-d39ddc07402a","inputPortId":7001,"inputPortName":"输入"}</t>
         </is>
       </c>
       <c r="H20"/>
@@ -1340,7 +1340,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>{"outputNodeGuid":"356907e0-1488-4128-bfcc-7ff73cfc3330","outputPortName":"冷却","inputNodeGuid":"c28fb88d-51b1-47b2-be59-859e0ac638e3","inputPortName":"输入"}</t>
+          <t>{"outputNodeGuid":"356907e0-1488-4128-bfcc-7ff73cfc3330","outputPortId":1004,"legacyOutputPortName":"冷却","inputNodeGuid":"c28fb88d-51b1-47b2-be59-859e0ac638e3","inputPortId":7001,"inputPortName":"输入"}</t>
         </is>
       </c>
       <c r="H21"/>
@@ -1360,7 +1360,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>{"outputNodeGuid":"356907e0-1488-4128-bfcc-7ff73cfc3330","outputPortName":"消耗","inputNodeGuid":"9d6f459d-b588-4b64-843b-1b71e8f299ae","inputPortName":"输入"}</t>
+          <t>{"outputNodeGuid":"356907e0-1488-4128-bfcc-7ff73cfc3330","outputPortId":1003,"legacyOutputPortName":"消耗","inputNodeGuid":"9d6f459d-b588-4b64-843b-1b71e8f299ae","inputPortId":7001,"inputPortName":"输入"}</t>
         </is>
       </c>
       <c r="H22"/>
@@ -1380,7 +1380,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>{"outputNodeGuid":"432ff1e3-b18d-476d-af80-d39ddc07402a","outputPortName":"de0ba361-3aba-4ef0-bb07-9b418fcae591","inputNodeGuid":"90bacd9f-d882-4bba-aaa8-41ed993ac3ff","inputPortName":"输入"}</t>
+          <t>{"outputNodeGuid":"432ff1e3-b18d-476d-af80-d39ddc07402a","outputPortId":2315086,"legacyOutputPortName":"de0ba361-3aba-4ef0-bb07-9b418fcae591","inputNodeGuid":"90bacd9f-d882-4bba-aaa8-41ed993ac3ff","inputPortId":7001,"inputPortName":"输入"}</t>
         </is>
       </c>
       <c r="H23"/>
@@ -1395,12 +1395,12 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>{"guid":"432ff1e3-b18d-476d-af80-d39ddc07402a","nodeType":20,"position":{"x":-491.33331298828125,"y":-2478.66650390625},"targetType":1,"skeletonDataAsset":null,"skeletonDataAssetPath":"Assets/Res/Spine/SP_Xiyiguai/SP_Xiyiguai_SkeletonData.asset","animationName":"Attack","animationDuration":"24","isAnimationLooping":false,"timeEffects":[{"triggerTime":11,"portId":"de0ba361-3aba-4ef0-bb07-9b418fcae591"},{"triggerTime":24,"portId":"7ecf9fe6-7c5e-46ae-bade-7922214225e2"}],"timeCues":[]}</t>
+          <t>{"guid":"432ff1e3-b18d-476d-af80-d39ddc07402a","nodeType":20,"position":{"x":-491.33331298828125,"y":-2478.66650390625},"targetType":1,"skeletonDataAsset":null,"skeletonDataAssetPath":"Assets/Res/Spine/SP_Xiyiguai/SP_Xiyiguai_SkeletonData.asset","animationName":"Attack","animationDuration":"24","isAnimationLooping":false,"timeEffects":[{"triggerTime":11,"portIdValue":2315086,"legacyPortId":"de0ba361-3aba-4ef0-bb07-9b418fcae591"},{"triggerTime":24,"portIdValue":2715463,"legacyPortId":"7ecf9fe6-7c5e-46ae-bade-7922214225e2"}],"timeCues":[]}</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>{"outputNodeGuid":"90bacd9f-d882-4bba-aaa8-41ed993ac3ff","outputPortName":"碰撞时","inputNodeGuid":"eae41233-d297-46fe-a6c8-0b5c876fbb2a","inputPortName":"输入"}</t>
+          <t>{"outputNodeGuid":"90bacd9f-d882-4bba-aaa8-41ed993ac3ff","outputPortId":5001,"legacyOutputPortName":"碰撞时","inputNodeGuid":"eae41233-d297-46fe-a6c8-0b5c876fbb2a","inputPortId":7001,"inputPortName":"输入"}</t>
         </is>
       </c>
       <c r="H24"/>
@@ -1420,7 +1420,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>{"outputNodeGuid":"eae41233-d297-46fe-a6c8-0b5c876fbb2a","outputPortName":"完成效果","inputNodeGuid":"2d7e41c4-8e90-4b61-879c-4b2e5b9486db","inputPortName":"输入"}</t>
+          <t>{"outputNodeGuid":"eae41233-d297-46fe-a6c8-0b5c876fbb2a","outputPortId":3004,"legacyOutputPortName":"完成效果","inputNodeGuid":"2d7e41c4-8e90-4b61-879c-4b2e5b9486db","inputPortId":7001,"inputPortName":"输入"}</t>
         </is>
       </c>
       <c r="H25"/>
@@ -1440,7 +1440,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>{"outputNodeGuid":"432ff1e3-b18d-476d-af80-d39ddc07402a","outputPortName":"7ecf9fe6-7c5e-46ae-bade-7922214225e2","inputNodeGuid":"3aafa9a5-4766-4204-91ab-d797aeb3c0e1","inputPortName":"输入"}</t>
+          <t>{"outputNodeGuid":"432ff1e3-b18d-476d-af80-d39ddc07402a","outputPortId":2715463,"legacyOutputPortName":"7ecf9fe6-7c5e-46ae-bade-7922214225e2","inputNodeGuid":"3aafa9a5-4766-4204-91ab-d797aeb3c0e1","inputPortId":7001,"inputPortName":"输入"}</t>
         </is>
       </c>
       <c r="H26"/>
@@ -1482,7 +1482,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>{"outputNodeGuid":"356907e0-1488-4128-bfcc-7ff73cfc3330","outputPortName":"动画","inputNodeGuid":"432ff1e3-b18d-476d-af80-d39ddc07402a","inputPortName":"输入"}</t>
+          <t>{"outputNodeGuid":"356907e0-1488-4128-bfcc-7ff73cfc3330","outputPortId":1002,"legacyOutputPortName":"动画","inputNodeGuid":"432ff1e3-b18d-476d-af80-d39ddc07402a","inputPortId":7001,"inputPortName":"输入"}</t>
         </is>
       </c>
       <c r="H28"/>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>{"outputNodeGuid":"356907e0-1488-4128-bfcc-7ff73cfc3330","outputPortName":"冷却","inputNodeGuid":"c28fb88d-51b1-47b2-be59-859e0ac638e3","inputPortName":"输入"}</t>
+          <t>{"outputNodeGuid":"356907e0-1488-4128-bfcc-7ff73cfc3330","outputPortId":1004,"legacyOutputPortName":"冷却","inputNodeGuid":"c28fb88d-51b1-47b2-be59-859e0ac638e3","inputPortId":7001,"inputPortName":"输入"}</t>
         </is>
       </c>
       <c r="H29"/>
@@ -1522,7 +1522,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>{"outputNodeGuid":"356907e0-1488-4128-bfcc-7ff73cfc3330","outputPortName":"消耗","inputNodeGuid":"9d6f459d-b588-4b64-843b-1b71e8f299ae","inputPortName":"输入"}</t>
+          <t>{"outputNodeGuid":"356907e0-1488-4128-bfcc-7ff73cfc3330","outputPortId":1003,"legacyOutputPortName":"消耗","inputNodeGuid":"9d6f459d-b588-4b64-843b-1b71e8f299ae","inputPortId":7001,"inputPortName":"输入"}</t>
         </is>
       </c>
       <c r="H30"/>
@@ -1542,7 +1542,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>{"outputNodeGuid":"432ff1e3-b18d-476d-af80-d39ddc07402a","outputPortName":"de0ba361-3aba-4ef0-bb07-9b418fcae591","inputNodeGuid":"90bacd9f-d882-4bba-aaa8-41ed993ac3ff","inputPortName":"输入"}</t>
+          <t>{"outputNodeGuid":"432ff1e3-b18d-476d-af80-d39ddc07402a","outputPortId":2315086,"legacyOutputPortName":"de0ba361-3aba-4ef0-bb07-9b418fcae591","inputNodeGuid":"90bacd9f-d882-4bba-aaa8-41ed993ac3ff","inputPortId":7001,"inputPortName":"输入"}</t>
         </is>
       </c>
       <c r="H31"/>
@@ -1557,12 +1557,12 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>{"guid":"432ff1e3-b18d-476d-af80-d39ddc07402a","nodeType":20,"position":{"x":-491.33331298828125,"y":-2478.66650390625},"targetType":1,"skeletonDataAsset":null,"skeletonDataAssetPath":"Assets/Res/Spine/SP_Zhanshi/SP_Zhanshi_SkeletonData.asset","animationName":"Attack_01","animationDuration":"18","isAnimationLooping":false,"timeEffects":[{"triggerTime":11,"portId":"de0ba361-3aba-4ef0-bb07-9b418fcae591"},{"triggerTime":24,"portId":"7ecf9fe6-7c5e-46ae-bade-7922214225e2"}],"timeCues":[]}</t>
+          <t>{"guid":"432ff1e3-b18d-476d-af80-d39ddc07402a","nodeType":20,"position":{"x":-491.33331298828125,"y":-2478.66650390625},"targetType":1,"skeletonDataAsset":null,"skeletonDataAssetPath":"Assets/Res/Spine/SP_Zhanshi/SP_Zhanshi_SkeletonData.asset","animationName":"Attack_01","animationDuration":"18","isAnimationLooping":false,"timeEffects":[{"triggerTime":11,"portIdValue":2315086,"legacyPortId":"de0ba361-3aba-4ef0-bb07-9b418fcae591"},{"triggerTime":24,"portIdValue":2715463,"legacyPortId":"7ecf9fe6-7c5e-46ae-bade-7922214225e2"}],"timeCues":[]}</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>{"outputNodeGuid":"90bacd9f-d882-4bba-aaa8-41ed993ac3ff","outputPortName":"碰撞时","inputNodeGuid":"eae41233-d297-46fe-a6c8-0b5c876fbb2a","inputPortName":"输入"}</t>
+          <t>{"outputNodeGuid":"90bacd9f-d882-4bba-aaa8-41ed993ac3ff","outputPortId":5001,"legacyOutputPortName":"碰撞时","inputNodeGuid":"eae41233-d297-46fe-a6c8-0b5c876fbb2a","inputPortId":7001,"inputPortName":"输入"}</t>
         </is>
       </c>
       <c r="H32"/>
@@ -1582,7 +1582,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>{"outputNodeGuid":"eae41233-d297-46fe-a6c8-0b5c876fbb2a","outputPortName":"完成效果","inputNodeGuid":"2d7e41c4-8e90-4b61-879c-4b2e5b9486db","inputPortName":"输入"}</t>
+          <t>{"outputNodeGuid":"eae41233-d297-46fe-a6c8-0b5c876fbb2a","outputPortId":3004,"legacyOutputPortName":"完成效果","inputNodeGuid":"2d7e41c4-8e90-4b61-879c-4b2e5b9486db","inputPortId":7001,"inputPortName":"输入"}</t>
         </is>
       </c>
       <c r="H33"/>
@@ -1602,7 +1602,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>{"outputNodeGuid":"432ff1e3-b18d-476d-af80-d39ddc07402a","outputPortName":"7ecf9fe6-7c5e-46ae-bade-7922214225e2","inputNodeGuid":"3aafa9a5-4766-4204-91ab-d797aeb3c0e1","inputPortName":"输入"}</t>
+          <t>{"outputNodeGuid":"432ff1e3-b18d-476d-af80-d39ddc07402a","outputPortId":2715463,"legacyOutputPortName":"7ecf9fe6-7c5e-46ae-bade-7922214225e2","inputNodeGuid":"3aafa9a5-4766-4204-91ab-d797aeb3c0e1","inputPortId":7001,"inputPortName":"输入"}</t>
         </is>
       </c>
       <c r="H34"/>
@@ -1644,7 +1644,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>{"outputNodeGuid":"356907e0-1488-4128-bfcc-7ff73cfc3330","outputPortName":"动画","inputNodeGuid":"432ff1e3-b18d-476d-af80-d39ddc07402a","inputPortName":"输入"}</t>
+          <t>{"outputNodeGuid":"356907e0-1488-4128-bfcc-7ff73cfc3330","outputPortId":1002,"legacyOutputPortName":"动画","inputNodeGuid":"432ff1e3-b18d-476d-af80-d39ddc07402a","inputPortId":7001,"inputPortName":"输入"}</t>
         </is>
       </c>
       <c r="H36"/>
@@ -1664,7 +1664,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>{"outputNodeGuid":"356907e0-1488-4128-bfcc-7ff73cfc3330","outputPortName":"冷却","inputNodeGuid":"c28fb88d-51b1-47b2-be59-859e0ac638e3","inputPortName":"输入"}</t>
+          <t>{"outputNodeGuid":"356907e0-1488-4128-bfcc-7ff73cfc3330","outputPortId":1004,"legacyOutputPortName":"冷却","inputNodeGuid":"c28fb88d-51b1-47b2-be59-859e0ac638e3","inputPortId":7001,"inputPortName":"输入"}</t>
         </is>
       </c>
       <c r="H37"/>
@@ -1684,7 +1684,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>{"outputNodeGuid":"356907e0-1488-4128-bfcc-7ff73cfc3330","outputPortName":"消耗","inputNodeGuid":"9d6f459d-b588-4b64-843b-1b71e8f299ae","inputPortName":"输入"}</t>
+          <t>{"outputNodeGuid":"356907e0-1488-4128-bfcc-7ff73cfc3330","outputPortId":1003,"legacyOutputPortName":"消耗","inputNodeGuid":"9d6f459d-b588-4b64-843b-1b71e8f299ae","inputPortId":7001,"inputPortName":"输入"}</t>
         </is>
       </c>
       <c r="H38"/>
@@ -1704,7 +1704,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>{"outputNodeGuid":"432ff1e3-b18d-476d-af80-d39ddc07402a","outputPortName":"f41c85e0-7f26-494e-9ffc-4a06c980f811","inputNodeGuid":"f73ba91e-a76b-456c-b19c-a5176809d5f5","inputPortName":"输入"}</t>
+          <t>{"outputNodeGuid":"432ff1e3-b18d-476d-af80-d39ddc07402a","outputPortId":2000539,"legacyOutputPortName":"f41c85e0-7f26-494e-9ffc-4a06c980f811","inputNodeGuid":"f73ba91e-a76b-456c-b19c-a5176809d5f5","inputPortId":7001,"inputPortName":"输入"}</t>
         </is>
       </c>
       <c r="H39"/>
@@ -1724,7 +1724,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>{"outputNodeGuid":"432ff1e3-b18d-476d-af80-d39ddc07402a","outputPortName":"de0ba361-3aba-4ef0-bb07-9b418fcae591","inputNodeGuid":"e33ab94c-1496-4d6a-ba5e-1afd38bb0c30","inputPortName":"输入"}</t>
+          <t>{"outputNodeGuid":"432ff1e3-b18d-476d-af80-d39ddc07402a","outputPortId":2315086,"legacyOutputPortName":"de0ba361-3aba-4ef0-bb07-9b418fcae591","inputNodeGuid":"e33ab94c-1496-4d6a-ba5e-1afd38bb0c30","inputPortId":7001,"inputPortName":"输入"}</t>
         </is>
       </c>
       <c r="H40"/>
@@ -1744,7 +1744,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>{"outputNodeGuid":"432ff1e3-b18d-476d-af80-d39ddc07402a","outputPortName":"8dea1941-c520-4f9a-aee0-40932c8542ef","inputNodeGuid":"cde57fb8-b693-4da8-a4a8-fd61e56c5dcd","inputPortName":"输入"}</t>
+          <t>{"outputNodeGuid":"432ff1e3-b18d-476d-af80-d39ddc07402a","outputPortId":2287012,"legacyOutputPortName":"8dea1941-c520-4f9a-aee0-40932c8542ef","inputNodeGuid":"cde57fb8-b693-4da8-a4a8-fd61e56c5dcd","inputPortId":7001,"inputPortName":"输入"}</t>
         </is>
       </c>
       <c r="H41"/>
@@ -1759,12 +1759,12 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>{"guid":"432ff1e3-b18d-476d-af80-d39ddc07402a","nodeType":20,"position":{"x":-646.0,"y":-2456.0},"targetType":1,"skeletonDataAsset":null,"skeletonDataAssetPath":"Assets/Res/Spine/SP_Zhanshi/SP_Zhanshi_SkeletonData.asset","animationName":"Skill_attack_1009","animationDuration":"25","isAnimationLooping":false,"timeEffects":[{"triggerTime":4,"portId":"de0ba361-3aba-4ef0-bb07-9b418fcae591"},{"triggerTime":25,"portId":"f41c85e0-7f26-494e-9ffc-4a06c980f811"}],"timeCues":[{"startTime":0,"endTime":75,"portId":"8dea1941-c520-4f9a-aee0-40932c8542ef"}]}</t>
+          <t>{"guid":"432ff1e3-b18d-476d-af80-d39ddc07402a","nodeType":20,"position":{"x":-646.0,"y":-2456.0},"targetType":1,"skeletonDataAsset":null,"skeletonDataAssetPath":"Assets/Res/Spine/SP_Zhanshi/SP_Zhanshi_SkeletonData.asset","animationName":"Skill_attack_1009","animationDuration":"25","isAnimationLooping":false,"timeEffects":[{"triggerTime":4,"portIdValue":2315086,"legacyPortId":"de0ba361-3aba-4ef0-bb07-9b418fcae591"},{"triggerTime":25,"portIdValue":2000539,"legacyPortId":"f41c85e0-7f26-494e-9ffc-4a06c980f811"}],"timeCues":[{"startTime":0,"endTime":75,"portIdValue":2287012,"legacyPortId":"8dea1941-c520-4f9a-aee0-40932c8542ef"}]}</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>{"outputNodeGuid":"e33ab94c-1496-4d6a-ba5e-1afd38bb0c30","outputPortName":"对每个目标","inputNodeGuid":"091ecddb-f80b-4c00-aa06-f9bc718618d2","inputPortName":"输入"}</t>
+          <t>{"outputNodeGuid":"e33ab94c-1496-4d6a-ba5e-1afd38bb0c30","outputPortId":4001,"legacyOutputPortName":"对每个目标","inputNodeGuid":"091ecddb-f80b-4c00-aa06-f9bc718618d2","inputPortId":7001,"inputPortName":"输入"}</t>
         </is>
       </c>
       <c r="H42"/>
@@ -1806,7 +1806,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>{"outputNodeGuid":"356907e0-1488-4128-bfcc-7ff73cfc3330","outputPortName":"冷却","inputNodeGuid":"c28fb88d-51b1-47b2-be59-859e0ac638e3","inputPortName":"输入"}</t>
+          <t>{"outputNodeGuid":"356907e0-1488-4128-bfcc-7ff73cfc3330","outputPortId":1004,"legacyOutputPortName":"冷却","inputNodeGuid":"c28fb88d-51b1-47b2-be59-859e0ac638e3","inputPortId":7001,"inputPortName":"输入"}</t>
         </is>
       </c>
       <c r="H44"/>
@@ -1826,7 +1826,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>{"outputNodeGuid":"356907e0-1488-4128-bfcc-7ff73cfc3330","outputPortName":"消耗","inputNodeGuid":"9d6f459d-b588-4b64-843b-1b71e8f299ae","inputPortName":"输入"}</t>
+          <t>{"outputNodeGuid":"356907e0-1488-4128-bfcc-7ff73cfc3330","outputPortId":1003,"legacyOutputPortName":"消耗","inputNodeGuid":"9d6f459d-b588-4b64-843b-1b71e8f299ae","inputPortId":7001,"inputPortName":"输入"}</t>
         </is>
       </c>
       <c r="H45"/>
@@ -1846,7 +1846,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>{"outputNodeGuid":"356907e0-1488-4128-bfcc-7ff73cfc3330","outputPortName":"激活","inputNodeGuid":"5fb21a71-2fff-4477-b79b-4c1a8bc10f9a","inputPortName":"输入"}</t>
+          <t>{"outputNodeGuid":"356907e0-1488-4128-bfcc-7ff73cfc3330","outputPortId":1001,"legacyOutputPortName":"激活","inputNodeGuid":"5fb21a71-2fff-4477-b79b-4c1a8bc10f9a","inputPortId":7001,"inputPortName":"输入"}</t>
         </is>
       </c>
       <c r="H46"/>
@@ -1866,7 +1866,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>{"outputNodeGuid":"5fb21a71-2fff-4477-b79b-4c1a8bc10f9a","outputPortName":"初始效果","inputNodeGuid":"cde57fb8-b693-4da8-a4a8-fd61e56c5dcd","inputPortName":"输入"}</t>
+          <t>{"outputNodeGuid":"5fb21a71-2fff-4477-b79b-4c1a8bc10f9a","outputPortId":3001,"legacyOutputPortName":"初始效果","inputNodeGuid":"cde57fb8-b693-4da8-a4a8-fd61e56c5dcd","inputPortId":7001,"inputPortName":"输入"}</t>
         </is>
       </c>
       <c r="H47"/>
@@ -1886,7 +1886,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>{"outputNodeGuid":"5fb21a71-2fff-4477-b79b-4c1a8bc10f9a","outputPortName":"完成效果","inputNodeGuid":"011aad56-e96c-41eb-9d85-e793d74a40bb","inputPortName":"输入"}</t>
+          <t>{"outputNodeGuid":"5fb21a71-2fff-4477-b79b-4c1a8bc10f9a","outputPortId":3004,"legacyOutputPortName":"完成效果","inputNodeGuid":"011aad56-e96c-41eb-9d85-e793d74a40bb","inputPortId":7001,"inputPortName":"输入"}</t>
         </is>
       </c>
       <c r="H48"/>
@@ -1906,7 +1906,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>{"outputNodeGuid":"5fb21a71-2fff-4477-b79b-4c1a8bc10f9a","outputPortName":"完成效果","inputNodeGuid":"becb4d53-8a9e-4dc0-95a3-618d1e79ecc7","inputPortName":"输入"}</t>
+          <t>{"outputNodeGuid":"5fb21a71-2fff-4477-b79b-4c1a8bc10f9a","outputPortId":3004,"legacyOutputPortName":"完成效果","inputNodeGuid":"becb4d53-8a9e-4dc0-95a3-618d1e79ecc7","inputPortId":7001,"inputPortName":"输入"}</t>
         </is>
       </c>
       <c r="H49"/>
@@ -1948,7 +1948,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>{"outputNodeGuid":"356907e0-1488-4128-bfcc-7ff73cfc3330","outputPortName":"动画","inputNodeGuid":"432ff1e3-b18d-476d-af80-d39ddc07402a","inputPortName":"输入"}</t>
+          <t>{"outputNodeGuid":"356907e0-1488-4128-bfcc-7ff73cfc3330","outputPortId":1002,"legacyOutputPortName":"动画","inputNodeGuid":"432ff1e3-b18d-476d-af80-d39ddc07402a","inputPortId":7001,"inputPortName":"输入"}</t>
         </is>
       </c>
       <c r="H51"/>
@@ -1968,7 +1968,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>{"outputNodeGuid":"356907e0-1488-4128-bfcc-7ff73cfc3330","outputPortName":"冷却","inputNodeGuid":"c28fb88d-51b1-47b2-be59-859e0ac638e3","inputPortName":"输入"}</t>
+          <t>{"outputNodeGuid":"356907e0-1488-4128-bfcc-7ff73cfc3330","outputPortId":1004,"legacyOutputPortName":"冷却","inputNodeGuid":"c28fb88d-51b1-47b2-be59-859e0ac638e3","inputPortId":7001,"inputPortName":"输入"}</t>
         </is>
       </c>
       <c r="H52"/>
@@ -1988,7 +1988,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>{"outputNodeGuid":"356907e0-1488-4128-bfcc-7ff73cfc3330","outputPortName":"消耗","inputNodeGuid":"9d6f459d-b588-4b64-843b-1b71e8f299ae","inputPortName":"输入"}</t>
+          <t>{"outputNodeGuid":"356907e0-1488-4128-bfcc-7ff73cfc3330","outputPortId":1003,"legacyOutputPortName":"消耗","inputNodeGuid":"9d6f459d-b588-4b64-843b-1b71e8f299ae","inputPortId":7001,"inputPortName":"输入"}</t>
         </is>
       </c>
       <c r="H53"/>
@@ -2008,7 +2008,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>{"outputNodeGuid":"e33ab94c-1496-4d6a-ba5e-1afd38bb0c30","outputPortName":"对每个目标","inputNodeGuid":"cb1df36f-5729-423e-9d1a-287db5a433f0","inputPortName":"输入"}</t>
+          <t>{"outputNodeGuid":"e33ab94c-1496-4d6a-ba5e-1afd38bb0c30","outputPortId":4001,"legacyOutputPortName":"对每个目标","inputNodeGuid":"cb1df36f-5729-423e-9d1a-287db5a433f0","inputPortId":7001,"inputPortName":"输入"}</t>
         </is>
       </c>
       <c r="H54"/>
@@ -2028,7 +2028,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>{"outputNodeGuid":"cb1df36f-5729-423e-9d1a-287db5a433f0","outputPortName":"初始效果","inputNodeGuid":"93ec5a43-cc34-4e4a-acb3-39da2f2c3010","inputPortName":"输入"}</t>
+          <t>{"outputNodeGuid":"cb1df36f-5729-423e-9d1a-287db5a433f0","outputPortId":3001,"legacyOutputPortName":"初始效果","inputNodeGuid":"93ec5a43-cc34-4e4a-acb3-39da2f2c3010","inputPortId":7001,"inputPortName":"输入"}</t>
         </is>
       </c>
       <c r="H55"/>
@@ -2048,7 +2048,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>{"outputNodeGuid":"432ff1e3-b18d-476d-af80-d39ddc07402a","outputPortName":"f41c85e0-7f26-494e-9ffc-4a06c980f811","inputNodeGuid":"f73ba91e-a76b-456c-b19c-a5176809d5f5","inputPortName":"输入"}</t>
+          <t>{"outputNodeGuid":"432ff1e3-b18d-476d-af80-d39ddc07402a","outputPortId":2000539,"legacyOutputPortName":"f41c85e0-7f26-494e-9ffc-4a06c980f811","inputNodeGuid":"f73ba91e-a76b-456c-b19c-a5176809d5f5","inputPortId":7001,"inputPortName":"输入"}</t>
         </is>
       </c>
       <c r="H56"/>
@@ -2068,7 +2068,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>{"outputNodeGuid":"432ff1e3-b18d-476d-af80-d39ddc07402a","outputPortName":"de0ba361-3aba-4ef0-bb07-9b418fcae591","inputNodeGuid":"e33ab94c-1496-4d6a-ba5e-1afd38bb0c30","inputPortName":"输入"}</t>
+          <t>{"outputNodeGuid":"432ff1e3-b18d-476d-af80-d39ddc07402a","outputPortId":2315086,"legacyOutputPortName":"de0ba361-3aba-4ef0-bb07-9b418fcae591","inputNodeGuid":"e33ab94c-1496-4d6a-ba5e-1afd38bb0c30","inputPortId":7001,"inputPortName":"输入"}</t>
         </is>
       </c>
       <c r="H57"/>
@@ -2083,12 +2083,12 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>{"guid":"432ff1e3-b18d-476d-af80-d39ddc07402a","nodeType":20,"position":{"x":-452.0,"y":-2375.333251953125},"targetType":1,"skeletonDataAsset":null,"skeletonDataAssetPath":"Assets/Res/Spine/SP_Zhanshi/SP_Zhanshi_SkeletonData.asset","animationName":"Skill_attack_1005","animationDuration":"16","isAnimationLooping":false,"timeEffects":[{"triggerTime":7,"portId":"de0ba361-3aba-4ef0-bb07-9b418fcae591"},{"triggerTime":16,"portId":"f41c85e0-7f26-494e-9ffc-4a06c980f811"}],"timeCues":[{"startTime":6,"endTime":55,"portId":"8dea1941-c520-4f9a-aee0-40932c8542ef"}]}</t>
+          <t>{"guid":"432ff1e3-b18d-476d-af80-d39ddc07402a","nodeType":20,"position":{"x":-452.0,"y":-2375.333251953125},"targetType":1,"skeletonDataAsset":null,"skeletonDataAssetPath":"Assets/Res/Spine/SP_Zhanshi/SP_Zhanshi_SkeletonData.asset","animationName":"Skill_attack_1005","animationDuration":"16","isAnimationLooping":false,"timeEffects":[{"triggerTime":7,"portIdValue":2315086,"legacyPortId":"de0ba361-3aba-4ef0-bb07-9b418fcae591"},{"triggerTime":16,"portIdValue":2000539,"legacyPortId":"f41c85e0-7f26-494e-9ffc-4a06c980f811"}],"timeCues":[{"startTime":6,"endTime":55,"portIdValue":2287012,"legacyPortId":"8dea1941-c520-4f9a-aee0-40932c8542ef"}]}</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>{"outputNodeGuid":"432ff1e3-b18d-476d-af80-d39ddc07402a","outputPortName":"8dea1941-c520-4f9a-aee0-40932c8542ef","inputNodeGuid":"cde57fb8-b693-4da8-a4a8-fd61e56c5dcd","inputPortName":"输入"}</t>
+          <t>{"outputNodeGuid":"432ff1e3-b18d-476d-af80-d39ddc07402a","outputPortId":2287012,"legacyOutputPortName":"8dea1941-c520-4f9a-aee0-40932c8542ef","inputNodeGuid":"cde57fb8-b693-4da8-a4a8-fd61e56c5dcd","inputPortId":7001,"inputPortName":"输入"}</t>
         </is>
       </c>
       <c r="H58"/>
@@ -2130,7 +2130,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>{"outputNodeGuid":"356907e0-1488-4128-bfcc-7ff73cfc3330","outputPortName":"动画","inputNodeGuid":"432ff1e3-b18d-476d-af80-d39ddc07402a","inputPortName":"输入"}</t>
+          <t>{"outputNodeGuid":"356907e0-1488-4128-bfcc-7ff73cfc3330","outputPortId":1002,"legacyOutputPortName":"动画","inputNodeGuid":"432ff1e3-b18d-476d-af80-d39ddc07402a","inputPortId":7001,"inputPortName":"输入"}</t>
         </is>
       </c>
       <c r="H60"/>
@@ -2150,7 +2150,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>{"outputNodeGuid":"356907e0-1488-4128-bfcc-7ff73cfc3330","outputPortName":"冷却","inputNodeGuid":"c28fb88d-51b1-47b2-be59-859e0ac638e3","inputPortName":"输入"}</t>
+          <t>{"outputNodeGuid":"356907e0-1488-4128-bfcc-7ff73cfc3330","outputPortId":1004,"legacyOutputPortName":"冷却","inputNodeGuid":"c28fb88d-51b1-47b2-be59-859e0ac638e3","inputPortId":7001,"inputPortName":"输入"}</t>
         </is>
       </c>
       <c r="H61"/>
@@ -2165,12 +2165,12 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>{"guid":"432ff1e3-b18d-476d-af80-d39ddc07402a","nodeType":20,"position":{"x":-502.66665649414063,"y":-2384.0},"targetType":1,"skeletonDataAsset":null,"skeletonDataAssetPath":"Assets/Res/Spine/SP_Zhanshi/SP_Zhanshi_SkeletonData.asset","animationName":"Stand","animationDuration":"24","isAnimationLooping":false,"timeEffects":[{"triggerTime":25,"portId":"f41c85e0-7f26-494e-9ffc-4a06c980f811"}],"timeCues":[]}</t>
+          <t>{"guid":"432ff1e3-b18d-476d-af80-d39ddc07402a","nodeType":20,"position":{"x":-502.66665649414063,"y":-2384.0},"targetType":1,"skeletonDataAsset":null,"skeletonDataAssetPath":"Assets/Res/Spine/SP_Zhanshi/SP_Zhanshi_SkeletonData.asset","animationName":"Stand","animationDuration":"24","isAnimationLooping":false,"timeEffects":[{"triggerTime":25,"portIdValue":2000539,"legacyPortId":"f41c85e0-7f26-494e-9ffc-4a06c980f811"}],"timeCues":[]}</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>{"outputNodeGuid":"356907e0-1488-4128-bfcc-7ff73cfc3330","outputPortName":"消耗","inputNodeGuid":"9d6f459d-b588-4b64-843b-1b71e8f299ae","inputPortName":"输入"}</t>
+          <t>{"outputNodeGuid":"356907e0-1488-4128-bfcc-7ff73cfc3330","outputPortId":1003,"legacyOutputPortName":"消耗","inputNodeGuid":"9d6f459d-b588-4b64-843b-1b71e8f299ae","inputPortId":7001,"inputPortName":"输入"}</t>
         </is>
       </c>
       <c r="H62"/>
@@ -2190,7 +2190,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>{"outputNodeGuid":"432ff1e3-b18d-476d-af80-d39ddc07402a","outputPortName":"f41c85e0-7f26-494e-9ffc-4a06c980f811","inputNodeGuid":"f73ba91e-a76b-456c-b19c-a5176809d5f5","inputPortName":"输入"}</t>
+          <t>{"outputNodeGuid":"432ff1e3-b18d-476d-af80-d39ddc07402a","outputPortId":2000539,"legacyOutputPortName":"f41c85e0-7f26-494e-9ffc-4a06c980f811","inputNodeGuid":"f73ba91e-a76b-456c-b19c-a5176809d5f5","inputPortId":7001,"inputPortName":"输入"}</t>
         </is>
       </c>
       <c r="H63"/>
@@ -2210,7 +2210,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>{"outputNodeGuid":"356907e0-1488-4128-bfcc-7ff73cfc3330","outputPortName":"激活","inputNodeGuid":"632c75e2-152b-4376-8e9e-62c0e74f92d0","inputPortName":"输入"}</t>
+          <t>{"outputNodeGuid":"356907e0-1488-4128-bfcc-7ff73cfc3330","outputPortId":1001,"legacyOutputPortName":"激活","inputNodeGuid":"632c75e2-152b-4376-8e9e-62c0e74f92d0","inputPortId":7001,"inputPortName":"输入"}</t>
         </is>
       </c>
       <c r="H64"/>
@@ -2252,7 +2252,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>{"outputNodeGuid":"432ff1e3-b18d-476d-af80-d39ddc07402a","outputPortName":"8dea1941-c520-4f9a-aee0-40932c8542ef","inputNodeGuid":"cde57fb8-b693-4da8-a4a8-fd61e56c5dcd","inputPortName":"输入"}</t>
+          <t>{"outputNodeGuid":"432ff1e3-b18d-476d-af80-d39ddc07402a","outputPortId":2287012,"legacyOutputPortName":"8dea1941-c520-4f9a-aee0-40932c8542ef","inputNodeGuid":"cde57fb8-b693-4da8-a4a8-fd61e56c5dcd","inputPortId":7001,"inputPortName":"输入"}</t>
         </is>
       </c>
       <c r="H66"/>
@@ -2272,7 +2272,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>{"outputNodeGuid":"356907e0-1488-4128-bfcc-7ff73cfc3330","outputPortName":"动画","inputNodeGuid":"432ff1e3-b18d-476d-af80-d39ddc07402a","inputPortName":"输入"}</t>
+          <t>{"outputNodeGuid":"356907e0-1488-4128-bfcc-7ff73cfc3330","outputPortId":1002,"legacyOutputPortName":"动画","inputNodeGuid":"432ff1e3-b18d-476d-af80-d39ddc07402a","inputPortId":7001,"inputPortName":"输入"}</t>
         </is>
       </c>
       <c r="H67"/>
@@ -2292,7 +2292,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>{"outputNodeGuid":"356907e0-1488-4128-bfcc-7ff73cfc3330","outputPortName":"冷却","inputNodeGuid":"c28fb88d-51b1-47b2-be59-859e0ac638e3","inputPortName":"输入"}</t>
+          <t>{"outputNodeGuid":"356907e0-1488-4128-bfcc-7ff73cfc3330","outputPortId":1004,"legacyOutputPortName":"冷却","inputNodeGuid":"c28fb88d-51b1-47b2-be59-859e0ac638e3","inputPortId":7001,"inputPortName":"输入"}</t>
         </is>
       </c>
       <c r="H68"/>
@@ -2312,7 +2312,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>{"outputNodeGuid":"356907e0-1488-4128-bfcc-7ff73cfc3330","outputPortName":"消耗","inputNodeGuid":"9d6f459d-b588-4b64-843b-1b71e8f299ae","inputPortName":"输入"}</t>
+          <t>{"outputNodeGuid":"356907e0-1488-4128-bfcc-7ff73cfc3330","outputPortId":1003,"legacyOutputPortName":"消耗","inputNodeGuid":"9d6f459d-b588-4b64-843b-1b71e8f299ae","inputPortId":7001,"inputPortName":"输入"}</t>
         </is>
       </c>
       <c r="H69"/>
@@ -2332,7 +2332,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>{"outputNodeGuid":"432ff1e3-b18d-476d-af80-d39ddc07402a","outputPortName":"de0ba361-3aba-4ef0-bb07-9b418fcae591","inputNodeGuid":"e33ab94c-1496-4d6a-ba5e-1afd38bb0c30","inputPortName":"输入"}</t>
+          <t>{"outputNodeGuid":"432ff1e3-b18d-476d-af80-d39ddc07402a","outputPortId":2315086,"legacyOutputPortName":"de0ba361-3aba-4ef0-bb07-9b418fcae591","inputNodeGuid":"e33ab94c-1496-4d6a-ba5e-1afd38bb0c30","inputPortId":7001,"inputPortName":"输入"}</t>
         </is>
       </c>
       <c r="H70"/>
@@ -2352,7 +2352,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>{"outputNodeGuid":"e33ab94c-1496-4d6a-ba5e-1afd38bb0c30","outputPortName":"对每个目标","inputNodeGuid":"f8947676-1084-4228-b991-1509cc7fe851","inputPortName":"输入"}</t>
+          <t>{"outputNodeGuid":"e33ab94c-1496-4d6a-ba5e-1afd38bb0c30","outputPortId":4001,"legacyOutputPortName":"对每个目标","inputNodeGuid":"f8947676-1084-4228-b991-1509cc7fe851","inputPortId":7001,"inputPortName":"输入"}</t>
         </is>
       </c>
       <c r="H71"/>
@@ -2372,7 +2372,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>{"outputNodeGuid":"f8947676-1084-4228-b991-1509cc7fe851","outputPortName":"完成效果","inputNodeGuid":"c353e286-8ef0-460a-b917-887f2aeb390a","inputPortName":"输入"}</t>
+          <t>{"outputNodeGuid":"f8947676-1084-4228-b991-1509cc7fe851","outputPortId":3004,"legacyOutputPortName":"完成效果","inputNodeGuid":"c353e286-8ef0-460a-b917-887f2aeb390a","inputPortId":7001,"inputPortName":"输入"}</t>
         </is>
       </c>
       <c r="H72"/>
@@ -2392,7 +2392,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>{"outputNodeGuid":"432ff1e3-b18d-476d-af80-d39ddc07402a","outputPortName":"84e238a8-5baf-470e-829f-186695064945","inputNodeGuid":"2cfdacd2-0186-49dd-b177-4eb8c0ad87bd","inputPortName":"输入"}</t>
+          <t>{"outputNodeGuid":"432ff1e3-b18d-476d-af80-d39ddc07402a","outputPortId":2649436,"legacyOutputPortName":"84e238a8-5baf-470e-829f-186695064945","inputNodeGuid":"2cfdacd2-0186-49dd-b177-4eb8c0ad87bd","inputPortId":7001,"inputPortName":"输入"}</t>
         </is>
       </c>
       <c r="H73"/>
@@ -2407,7 +2407,7 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>{"guid":"432ff1e3-b18d-476d-af80-d39ddc07402a","nodeType":20,"position":{"x":-414.0,"y":-2826.0},"targetType":1,"skeletonDataAsset":null,"skeletonDataAssetPath":"Assets/Res/Spine/SP_Zhanshi/SP_Zhanshi_SkeletonData.asset","animationName":"Skill_attack_1001","animationDuration":"18","isAnimationLooping":true,"timeEffects":[{"triggerTime":7,"portId":"de0ba361-3aba-4ef0-bb07-9b418fcae591"},{"triggerTime":18,"portId":"84e238a8-5baf-470e-829f-186695064945"}],"timeCues":[{"startTime":7,"endTime":48,"portId":"8dea1941-c520-4f9a-aee0-40932c8542ef"}]}</t>
+          <t>{"guid":"432ff1e3-b18d-476d-af80-d39ddc07402a","nodeType":20,"position":{"x":-414.0,"y":-2826.0},"targetType":1,"skeletonDataAsset":null,"skeletonDataAssetPath":"Assets/Res/Spine/SP_Zhanshi/SP_Zhanshi_SkeletonData.asset","animationName":"Skill_attack_1001","animationDuration":"18","isAnimationLooping":true,"timeEffects":[{"triggerTime":7,"portIdValue":2315086,"legacyPortId":"de0ba361-3aba-4ef0-bb07-9b418fcae591"},{"triggerTime":18,"portIdValue":2649436,"legacyPortId":"84e238a8-5baf-470e-829f-186695064945"}],"timeCues":[{"startTime":7,"endTime":48,"portIdValue":2287012,"legacyPortId":"8dea1941-c520-4f9a-aee0-40932c8542ef"}]}</t>
         </is>
       </c>
       <c r="G74"/>
@@ -2434,7 +2434,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>{"outputNodeGuid":"356907e0-1488-4128-bfcc-7ff73cfc3330","outputPortName":"动画","inputNodeGuid":"432ff1e3-b18d-476d-af80-d39ddc07402a","inputPortName":"输入"}</t>
+          <t>{"outputNodeGuid":"356907e0-1488-4128-bfcc-7ff73cfc3330","outputPortId":1002,"legacyOutputPortName":"动画","inputNodeGuid":"432ff1e3-b18d-476d-af80-d39ddc07402a","inputPortId":7001,"inputPortName":"输入"}</t>
         </is>
       </c>
       <c r="H75"/>
@@ -2454,7 +2454,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>{"outputNodeGuid":"356907e0-1488-4128-bfcc-7ff73cfc3330","outputPortName":"冷却","inputNodeGuid":"c28fb88d-51b1-47b2-be59-859e0ac638e3","inputPortName":"输入"}</t>
+          <t>{"outputNodeGuid":"356907e0-1488-4128-bfcc-7ff73cfc3330","outputPortId":1004,"legacyOutputPortName":"冷却","inputNodeGuid":"c28fb88d-51b1-47b2-be59-859e0ac638e3","inputPortId":7001,"inputPortName":"输入"}</t>
         </is>
       </c>
       <c r="H76"/>
@@ -2474,7 +2474,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>{"outputNodeGuid":"356907e0-1488-4128-bfcc-7ff73cfc3330","outputPortName":"消耗","inputNodeGuid":"9d6f459d-b588-4b64-843b-1b71e8f299ae","inputPortName":"输入"}</t>
+          <t>{"outputNodeGuid":"356907e0-1488-4128-bfcc-7ff73cfc3330","outputPortId":1003,"legacyOutputPortName":"消耗","inputNodeGuid":"9d6f459d-b588-4b64-843b-1b71e8f299ae","inputPortId":7001,"inputPortName":"输入"}</t>
         </is>
       </c>
       <c r="H77"/>
@@ -2494,7 +2494,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>{"outputNodeGuid":"f8947676-1084-4228-b991-1509cc7fe851","outputPortName":"完成效果","inputNodeGuid":"c353e286-8ef0-460a-b917-887f2aeb390a","inputPortName":"输入"}</t>
+          <t>{"outputNodeGuid":"f8947676-1084-4228-b991-1509cc7fe851","outputPortId":3004,"legacyOutputPortName":"完成效果","inputNodeGuid":"c353e286-8ef0-460a-b917-887f2aeb390a","inputPortId":7001,"inputPortName":"输入"}</t>
         </is>
       </c>
       <c r="H78"/>
@@ -2514,7 +2514,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>{"outputNodeGuid":"ce857360-de7e-4457-b348-9c124ce98879","outputPortName":"碰撞时","inputNodeGuid":"f8947676-1084-4228-b991-1509cc7fe851","inputPortName":"输入"}</t>
+          <t>{"outputNodeGuid":"ce857360-de7e-4457-b348-9c124ce98879","outputPortId":5001,"legacyOutputPortName":"碰撞时","inputNodeGuid":"f8947676-1084-4228-b991-1509cc7fe851","inputPortId":7001,"inputPortName":"输入"}</t>
         </is>
       </c>
       <c r="H79"/>
@@ -2534,7 +2534,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>{"outputNodeGuid":"9a695e91-e218-425e-82ed-1e157bf1b014","outputPortName":"碰撞时","inputNodeGuid":"f8947676-1084-4228-b991-1509cc7fe851","inputPortName":"输入"}</t>
+          <t>{"outputNodeGuid":"9a695e91-e218-425e-82ed-1e157bf1b014","outputPortId":5001,"legacyOutputPortName":"碰撞时","inputNodeGuid":"f8947676-1084-4228-b991-1509cc7fe851","inputPortId":7001,"inputPortName":"输入"}</t>
         </is>
       </c>
       <c r="H80"/>
@@ -2549,12 +2549,12 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>{"guid":"432ff1e3-b18d-476d-af80-d39ddc07402a","nodeType":20,"position":{"x":-238.66665649414063,"y":-2405.333251953125},"targetType":1,"skeletonDataAsset":null,"skeletonDataAssetPath":"Assets/Res/Spine/SP_Zhanshi/SP_Zhanshi_SkeletonData.asset","animationName":"Attack_01","animationDuration":"18","isAnimationLooping":false,"timeEffects":[{"triggerTime":7,"portId":"de0ba361-3aba-4ef0-bb07-9b418fcae591"},{"triggerTime":18,"portId":"84e238a8-5baf-470e-829f-186695064945"}],"timeCues":[]}</t>
+          <t>{"guid":"432ff1e3-b18d-476d-af80-d39ddc07402a","nodeType":20,"position":{"x":-238.66665649414063,"y":-2405.333251953125},"targetType":1,"skeletonDataAsset":null,"skeletonDataAssetPath":"Assets/Res/Spine/SP_Zhanshi/SP_Zhanshi_SkeletonData.asset","animationName":"Attack_01","animationDuration":"18","isAnimationLooping":false,"timeEffects":[{"triggerTime":7,"portIdValue":2315086,"legacyPortId":"de0ba361-3aba-4ef0-bb07-9b418fcae591"},{"triggerTime":18,"portIdValue":2649436,"legacyPortId":"84e238a8-5baf-470e-829f-186695064945"}],"timeCues":[]}</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>{"outputNodeGuid":"d897a922-5756-42cf-ac65-90a48c1e5a17","outputPortName":"碰撞时","inputNodeGuid":"f8947676-1084-4228-b991-1509cc7fe851","inputPortName":"输入"}</t>
+          <t>{"outputNodeGuid":"d897a922-5756-42cf-ac65-90a48c1e5a17","outputPortId":5001,"legacyOutputPortName":"碰撞时","inputNodeGuid":"f8947676-1084-4228-b991-1509cc7fe851","inputPortId":7001,"inputPortName":"输入"}</t>
         </is>
       </c>
       <c r="H81"/>
@@ -2574,7 +2574,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>{"outputNodeGuid":"432ff1e3-b18d-476d-af80-d39ddc07402a","outputPortName":"84e238a8-5baf-470e-829f-186695064945","inputNodeGuid":"2cfdacd2-0186-49dd-b177-4eb8c0ad87bd","inputPortName":"输入"}</t>
+          <t>{"outputNodeGuid":"432ff1e3-b18d-476d-af80-d39ddc07402a","outputPortId":2649436,"legacyOutputPortName":"84e238a8-5baf-470e-829f-186695064945","inputNodeGuid":"2cfdacd2-0186-49dd-b177-4eb8c0ad87bd","inputPortId":7001,"inputPortName":"输入"}</t>
         </is>
       </c>
       <c r="H82"/>
@@ -2594,7 +2594,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>{"outputNodeGuid":"432ff1e3-b18d-476d-af80-d39ddc07402a","outputPortName":"de0ba361-3aba-4ef0-bb07-9b418fcae591","inputNodeGuid":"ce857360-de7e-4457-b348-9c124ce98879","inputPortName":"输入"}</t>
+          <t>{"outputNodeGuid":"432ff1e3-b18d-476d-af80-d39ddc07402a","outputPortId":2315086,"legacyOutputPortName":"de0ba361-3aba-4ef0-bb07-9b418fcae591","inputNodeGuid":"ce857360-de7e-4457-b348-9c124ce98879","inputPortId":7001,"inputPortName":"输入"}</t>
         </is>
       </c>
       <c r="H83"/>
@@ -2614,7 +2614,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>{"outputNodeGuid":"432ff1e3-b18d-476d-af80-d39ddc07402a","outputPortName":"de0ba361-3aba-4ef0-bb07-9b418fcae591","inputNodeGuid":"9a695e91-e218-425e-82ed-1e157bf1b014","inputPortName":"输入"}</t>
+          <t>{"outputNodeGuid":"432ff1e3-b18d-476d-af80-d39ddc07402a","outputPortId":2315086,"legacyOutputPortName":"de0ba361-3aba-4ef0-bb07-9b418fcae591","inputNodeGuid":"9a695e91-e218-425e-82ed-1e157bf1b014","inputPortId":7001,"inputPortName":"输入"}</t>
         </is>
       </c>
       <c r="H84"/>
@@ -2628,7 +2628,7 @@
       <c r="F85"/>
       <c r="G85" t="inlineStr">
         <is>
-          <t>{"outputNodeGuid":"432ff1e3-b18d-476d-af80-d39ddc07402a","outputPortName":"de0ba361-3aba-4ef0-bb07-9b418fcae591","inputNodeGuid":"d897a922-5756-42cf-ac65-90a48c1e5a17","inputPortName":"输入"}</t>
+          <t>{"outputNodeGuid":"432ff1e3-b18d-476d-af80-d39ddc07402a","outputPortId":2315086,"legacyOutputPortName":"de0ba361-3aba-4ef0-bb07-9b418fcae591","inputNodeGuid":"d897a922-5756-42cf-ac65-90a48c1e5a17","inputPortId":7001,"inputPortName":"输入"}</t>
         </is>
       </c>
       <c r="H85"/>
@@ -2654,7 +2654,7 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>{"outputNodeGuid":"356907e0-1488-4128-bfcc-7ff73cfc3330","outputPortName":"动画","inputNodeGuid":"432ff1e3-b18d-476d-af80-d39ddc07402a","inputPortName":"输入"}</t>
+          <t>{"outputNodeGuid":"356907e0-1488-4128-bfcc-7ff73cfc3330","outputPortId":1002,"legacyOutputPortName":"动画","inputNodeGuid":"432ff1e3-b18d-476d-af80-d39ddc07402a","inputPortId":7001,"inputPortName":"输入"}</t>
         </is>
       </c>
       <c r="H86"/>
@@ -2674,7 +2674,7 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>{"outputNodeGuid":"356907e0-1488-4128-bfcc-7ff73cfc3330","outputPortName":"冷却","inputNodeGuid":"c28fb88d-51b1-47b2-be59-859e0ac638e3","inputPortName":"输入"}</t>
+          <t>{"outputNodeGuid":"356907e0-1488-4128-bfcc-7ff73cfc3330","outputPortId":1004,"legacyOutputPortName":"冷却","inputNodeGuid":"c28fb88d-51b1-47b2-be59-859e0ac638e3","inputPortId":7001,"inputPortName":"输入"}</t>
         </is>
       </c>
       <c r="H87"/>
@@ -2694,7 +2694,7 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>{"outputNodeGuid":"356907e0-1488-4128-bfcc-7ff73cfc3330","outputPortName":"消耗","inputNodeGuid":"9d6f459d-b588-4b64-843b-1b71e8f299ae","inputPortName":"输入"}</t>
+          <t>{"outputNodeGuid":"356907e0-1488-4128-bfcc-7ff73cfc3330","outputPortId":1003,"legacyOutputPortName":"消耗","inputNodeGuid":"9d6f459d-b588-4b64-843b-1b71e8f299ae","inputPortId":7001,"inputPortName":"输入"}</t>
         </is>
       </c>
       <c r="H88"/>
@@ -2714,7 +2714,7 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>{"outputNodeGuid":"432ff1e3-b18d-476d-af80-d39ddc07402a","outputPortName":"f41c85e0-7f26-494e-9ffc-4a06c980f811","inputNodeGuid":"f73ba91e-a76b-456c-b19c-a5176809d5f5","inputPortName":"输入"}</t>
+          <t>{"outputNodeGuid":"432ff1e3-b18d-476d-af80-d39ddc07402a","outputPortId":2000539,"legacyOutputPortName":"f41c85e0-7f26-494e-9ffc-4a06c980f811","inputNodeGuid":"f73ba91e-a76b-456c-b19c-a5176809d5f5","inputPortId":7001,"inputPortName":"输入"}</t>
         </is>
       </c>
       <c r="H89"/>
@@ -2734,7 +2734,7 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>{"outputNodeGuid":"432ff1e3-b18d-476d-af80-d39ddc07402a","outputPortName":"de0ba361-3aba-4ef0-bb07-9b418fcae591","inputNodeGuid":"e33ab94c-1496-4d6a-ba5e-1afd38bb0c30","inputPortName":"输入"}</t>
+          <t>{"outputNodeGuid":"432ff1e3-b18d-476d-af80-d39ddc07402a","outputPortId":2315086,"legacyOutputPortName":"de0ba361-3aba-4ef0-bb07-9b418fcae591","inputNodeGuid":"e33ab94c-1496-4d6a-ba5e-1afd38bb0c30","inputPortId":7001,"inputPortName":"输入"}</t>
         </is>
       </c>
       <c r="H90"/>
@@ -2754,7 +2754,7 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>{"outputNodeGuid":"432ff1e3-b18d-476d-af80-d39ddc07402a","outputPortName":"8dea1941-c520-4f9a-aee0-40932c8542ef","inputNodeGuid":"cde57fb8-b693-4da8-a4a8-fd61e56c5dcd","inputPortName":"输入"}</t>
+          <t>{"outputNodeGuid":"432ff1e3-b18d-476d-af80-d39ddc07402a","outputPortId":2287012,"legacyOutputPortName":"8dea1941-c520-4f9a-aee0-40932c8542ef","inputNodeGuid":"cde57fb8-b693-4da8-a4a8-fd61e56c5dcd","inputPortId":7001,"inputPortName":"输入"}</t>
         </is>
       </c>
       <c r="H91"/>
@@ -2769,12 +2769,12 @@
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>{"guid":"432ff1e3-b18d-476d-af80-d39ddc07402a","nodeType":20,"position":{"x":-502.39999389648438,"y":-2384.0},"targetType":1,"skeletonDataAsset":null,"skeletonDataAssetPath":"Assets/Res/Spine/SP_Zhanshi/SP_Zhanshi_SkeletonData.asset","animationName":"Skill_attack_1009","animationDuration":"25","isAnimationLooping":false,"timeEffects":[{"triggerTime":4,"portId":"de0ba361-3aba-4ef0-bb07-9b418fcae591"},{"triggerTime":25,"portId":"f41c85e0-7f26-494e-9ffc-4a06c980f811"}],"timeCues":[{"startTime":0,"endTime":75,"portId":"8dea1941-c520-4f9a-aee0-40932c8542ef"}]}</t>
+          <t>{"guid":"432ff1e3-b18d-476d-af80-d39ddc07402a","nodeType":20,"position":{"x":-502.39999389648438,"y":-2384.0},"targetType":1,"skeletonDataAsset":null,"skeletonDataAssetPath":"Assets/Res/Spine/SP_Zhanshi/SP_Zhanshi_SkeletonData.asset","animationName":"Skill_attack_1009","animationDuration":"25","isAnimationLooping":false,"timeEffects":[{"triggerTime":4,"portIdValue":2315086,"legacyPortId":"de0ba361-3aba-4ef0-bb07-9b418fcae591"},{"triggerTime":25,"portIdValue":2000539,"legacyPortId":"f41c85e0-7f26-494e-9ffc-4a06c980f811"}],"timeCues":[{"startTime":0,"endTime":75,"portIdValue":2287012,"legacyPortId":"8dea1941-c520-4f9a-aee0-40932c8542ef"}]}</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>{"outputNodeGuid":"e33ab94c-1496-4d6a-ba5e-1afd38bb0c30","outputPortName":"对每个目标","inputNodeGuid":"091ecddb-f80b-4c00-aa06-f9bc718618d2","inputPortName":"输入"}</t>
+          <t>{"outputNodeGuid":"e33ab94c-1496-4d6a-ba5e-1afd38bb0c30","outputPortId":4001,"legacyOutputPortName":"对每个目标","inputNodeGuid":"091ecddb-f80b-4c00-aa06-f9bc718618d2","inputPortId":7001,"inputPortName":"输入"}</t>
         </is>
       </c>
       <c r="H92"/>
@@ -2816,7 +2816,7 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>{"outputNodeGuid":"356907e0-1488-4128-bfcc-7ff73cfc3330","outputPortName":"动画","inputNodeGuid":"432ff1e3-b18d-476d-af80-d39ddc07402a","inputPortName":"输入"}</t>
+          <t>{"outputNodeGuid":"356907e0-1488-4128-bfcc-7ff73cfc3330","outputPortId":1002,"legacyOutputPortName":"动画","inputNodeGuid":"432ff1e3-b18d-476d-af80-d39ddc07402a","inputPortId":7001,"inputPortName":"输入"}</t>
         </is>
       </c>
       <c r="H94"/>
@@ -2836,7 +2836,7 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>{"outputNodeGuid":"356907e0-1488-4128-bfcc-7ff73cfc3330","outputPortName":"冷却","inputNodeGuid":"c28fb88d-51b1-47b2-be59-859e0ac638e3","inputPortName":"输入"}</t>
+          <t>{"outputNodeGuid":"356907e0-1488-4128-bfcc-7ff73cfc3330","outputPortId":1004,"legacyOutputPortName":"冷却","inputNodeGuid":"c28fb88d-51b1-47b2-be59-859e0ac638e3","inputPortId":7001,"inputPortName":"输入"}</t>
         </is>
       </c>
       <c r="H95"/>
@@ -2856,7 +2856,7 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>{"outputNodeGuid":"356907e0-1488-4128-bfcc-7ff73cfc3330","outputPortName":"消耗","inputNodeGuid":"9d6f459d-b588-4b64-843b-1b71e8f299ae","inputPortName":"输入"}</t>
+          <t>{"outputNodeGuid":"356907e0-1488-4128-bfcc-7ff73cfc3330","outputPortId":1003,"legacyOutputPortName":"消耗","inputNodeGuid":"9d6f459d-b588-4b64-843b-1b71e8f299ae","inputPortId":7001,"inputPortName":"输入"}</t>
         </is>
       </c>
       <c r="H96"/>
@@ -2876,7 +2876,7 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>{"outputNodeGuid":"356907e0-1488-4128-bfcc-7ff73cfc3330","outputPortName":"激活","inputNodeGuid":"d8847c3e-459e-4589-a96b-37ebb5ec458b","inputPortName":"输入"}</t>
+          <t>{"outputNodeGuid":"356907e0-1488-4128-bfcc-7ff73cfc3330","outputPortId":1001,"legacyOutputPortName":"激活","inputNodeGuid":"d8847c3e-459e-4589-a96b-37ebb5ec458b","inputPortId":7001,"inputPortName":"输入"}</t>
         </is>
       </c>
       <c r="H97"/>
@@ -2896,7 +2896,7 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>{"outputNodeGuid":"d8847c3e-459e-4589-a96b-37ebb5ec458b","outputPortName":"每周期执行","inputNodeGuid":"e33ab94c-1496-4d6a-ba5e-1afd38bb0c30","inputPortName":"输入"}</t>
+          <t>{"outputNodeGuid":"d8847c3e-459e-4589-a96b-37ebb5ec458b","outputPortId":3002,"legacyOutputPortName":"每周期执行","inputNodeGuid":"e33ab94c-1496-4d6a-ba5e-1afd38bb0c30","inputPortId":7001,"inputPortName":"输入"}</t>
         </is>
       </c>
       <c r="H98"/>
@@ -2916,7 +2916,7 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>{"outputNodeGuid":"e33ab94c-1496-4d6a-ba5e-1afd38bb0c30","outputPortName":"对每个目标","inputNodeGuid":"a32d1135-94db-4f81-95ba-9d5f105ef8d0","inputPortName":"输入"}</t>
+          <t>{"outputNodeGuid":"e33ab94c-1496-4d6a-ba5e-1afd38bb0c30","outputPortId":4001,"legacyOutputPortName":"对每个目标","inputNodeGuid":"a32d1135-94db-4f81-95ba-9d5f105ef8d0","inputPortId":7001,"inputPortName":"输入"}</t>
         </is>
       </c>
       <c r="H99"/>
@@ -2936,7 +2936,7 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>{"outputNodeGuid":"a32d1135-94db-4f81-95ba-9d5f105ef8d0","outputPortName":"完成效果","inputNodeGuid":"764289ea-065e-4f48-afc0-0f6963d18d57","inputPortName":"输入"}</t>
+          <t>{"outputNodeGuid":"a32d1135-94db-4f81-95ba-9d5f105ef8d0","outputPortId":3004,"legacyOutputPortName":"完成效果","inputNodeGuid":"764289ea-065e-4f48-afc0-0f6963d18d57","inputPortId":7001,"inputPortName":"输入"}</t>
         </is>
       </c>
       <c r="H100"/>
@@ -2956,7 +2956,7 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>{"outputNodeGuid":"432ff1e3-b18d-476d-af80-d39ddc07402a","outputPortName":"8dea1941-c520-4f9a-aee0-40932c8542ef","inputNodeGuid":"cde57fb8-b693-4da8-a4a8-fd61e56c5dcd","inputPortName":"输入"}</t>
+          <t>{"outputNodeGuid":"432ff1e3-b18d-476d-af80-d39ddc07402a","outputPortId":2287012,"legacyOutputPortName":"8dea1941-c520-4f9a-aee0-40932c8542ef","inputNodeGuid":"cde57fb8-b693-4da8-a4a8-fd61e56c5dcd","inputPortId":7001,"inputPortName":"输入"}</t>
         </is>
       </c>
       <c r="H101"/>
@@ -2971,12 +2971,12 @@
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>{"guid":"432ff1e3-b18d-476d-af80-d39ddc07402a","nodeType":20,"position":{"x":-452.0,"y":-2375.199951171875},"targetType":1,"skeletonDataAsset":null,"skeletonDataAssetPath":"Assets/Res/Spine/SP_Zhanshi/SP_Zhanshi_SkeletonData.asset","animationName":"Skill_attack_1011","animationDuration":"12","isAnimationLooping":true,"timeEffects":[{"triggerTime":250,"portId":"f41c85e0-7f26-494e-9ffc-4a06c980f811"}],"timeCues":[{"startTime":0,"endTime":255,"portId":"8dea1941-c520-4f9a-aee0-40932c8542ef"}]}</t>
+          <t>{"guid":"432ff1e3-b18d-476d-af80-d39ddc07402a","nodeType":20,"position":{"x":-452.0,"y":-2375.199951171875},"targetType":1,"skeletonDataAsset":null,"skeletonDataAssetPath":"Assets/Res/Spine/SP_Zhanshi/SP_Zhanshi_SkeletonData.asset","animationName":"Skill_attack_1011","animationDuration":"12","isAnimationLooping":true,"timeEffects":[{"triggerTime":250,"portIdValue":2000539,"legacyPortId":"f41c85e0-7f26-494e-9ffc-4a06c980f811"}],"timeCues":[{"startTime":0,"endTime":255,"portIdValue":2287012,"legacyPortId":"8dea1941-c520-4f9a-aee0-40932c8542ef"}]}</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>{"outputNodeGuid":"432ff1e3-b18d-476d-af80-d39ddc07402a","outputPortName":"f41c85e0-7f26-494e-9ffc-4a06c980f811","inputNodeGuid":"f73ba91e-a76b-456c-b19c-a5176809d5f5","inputPortName":"输入"}</t>
+          <t>{"outputNodeGuid":"432ff1e3-b18d-476d-af80-d39ddc07402a","outputPortId":2000539,"legacyOutputPortName":"f41c85e0-7f26-494e-9ffc-4a06c980f811","inputNodeGuid":"f73ba91e-a76b-456c-b19c-a5176809d5f5","inputPortId":7001,"inputPortName":"输入"}</t>
         </is>
       </c>
       <c r="H102"/>

--- a/Design/Excel/ET/Datas/Game/SkillGraph.xlsx
+++ b/Design/Excel/ET/Datas/Game/SkillGraph.xlsx
@@ -1213,7 +1213,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>{"guid":"f8947676-1084-4228-b991-1509cc7fe851","nodeType":1,"position":{"x":195.33334350585938,"y":-1761.3333740234375},"targetType":0,"assetTags":{"_tags":[]},"grantedTags":{"_tags":[]},"applicationRequiredTags":{"_tags":[]},"applicationImmunityTags":{"_tags":[]},"removeGameEffectsWithTags":{"_tags":[]},"durationType":0,"duration":"0","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"_tags":[]},"cancelOnAbilityEnd":true,"damageType":0,"damageSourceType":0,"damageFixedValue":3.0,"damageFormula":"","damageMMCType":0,"damageSetByCallerKey":"","damageMMCCaptureAttribute":200,"damageMMCAttributeSource":0,"damageMMCCoefficient":1.0,"damageMMCUseSnapshot":true,"damageMultiplyByStackCount":true,"damageCalculationType":0}</t>
+          <t>{"guid":"f8947676-1084-4228-b991-1509cc7fe851","nodeType":1,"position":{"x":195.33334350585938,"y":-1761.3333740234375},"targetType":0,"assetTags":{"_tags":[]},"grantedTags":{"_tags":[]},"applicationRequiredTags":{"_tags":[]},"applicationImmunityTags":{"_tags":[]},"removeGameEffectsWithTags":{"_tags":[]},"durationType":0,"duration":"0","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"_tags":[]},"cancelOnAbilityEnd":true,"damageType":0,"damageSourceType":0,"damageFixedValue":3.0,"damageFormula":"","damageMMCType":0,"damageSetByCallerKey":"","damageMMCCaptureAttribute":200,"damageMMCAttributeSource":0,"damageMMCCoefficient":1.0,"damageMMCUseSnapshot":true,"damageMultiplyByStackCount":true,"damageCalculationType":0,"enableHitKnockback":false,"knockbackDistance":1.0,"knockbackSpeed":12.0}</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -1320,7 +1320,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>{"outputNodeGuid":"356907e0-1488-4128-bfcc-7ff73cfc3330","outputPortId":1002,"legacyOutputPortName":"动画","inputNodeGuid":"432ff1e3-b18d-476d-af80-d39ddc07402a","inputPortId":7001,"inputPortName":"输入"}</t>
+          <t>{"outputNodeGuid":"356907e0-1488-4128-bfcc-7ff73cfc3330","outputPortId":1002,"legacyOutputPortName":"","inputNodeGuid":"432ff1e3-b18d-476d-af80-d39ddc07402a","inputPortId":7001,"inputPortName":"输入"}</t>
         </is>
       </c>
       <c r="H20"/>
@@ -1331,16 +1331,16 @@
       <c r="C21"/>
       <c r="D21"/>
       <c r="E21">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>{"guid":"eae41233-d297-46fe-a6c8-0b5c876fbb2a","nodeType":1,"position":{"x":46.66668701171875,"y":-1808.666748046875},"targetType":0,"assetTags":{"_tags":[]},"grantedTags":{"_tags":[]},"applicationRequiredTags":{"_tags":[]},"applicationImmunityTags":{"_tags":[]},"removeGameEffectsWithTags":{"_tags":[]},"durationType":0,"duration":"0","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"_tags":[]},"cancelOnAbilityEnd":true,"damageType":0,"damageSourceType":0,"damageFixedValue":10.0,"damageFormula":"","damageMMCType":0,"damageSetByCallerKey":"","damageMMCCaptureAttribute":200,"damageMMCAttributeSource":0,"damageMMCCoefficient":1.0,"damageMMCUseSnapshot":true,"damageMultiplyByStackCount":false,"damageCalculationType":0}</t>
+          <t>{"guid":"2d7e41c4-8e90-4b61-879c-4b2e5b9486db","nodeType":14,"position":{"x":408.66665649414063,"y":-1747.3333740234375},"targetType":1,"requiredTags":{"_tags":[]},"immunityTags":{"_tags":[]},"destroyWithNode":false,"positionSource":2,"positionBindingName":"head","textType":0,"fixedText":"","contextDataKey":"DamageResult","textColor":{"r":0.0,"g":0.323091983795166,"b":1.0,"a":1.0},"criticalColor":{"r":1.0,"g":0.5,"b":0.0,"a":1.0},"missColor":{"r":0.5,"g":0.5,"b":0.5,"a":1.0},"fontSize":45.0,"criticalFontSize":60.0,"duration":1.5,"offset":{"x":0.0,"y":0.0},"moveDirection":{"x":0.0,"y":1.0}}</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>{"outputNodeGuid":"356907e0-1488-4128-bfcc-7ff73cfc3330","outputPortId":1004,"legacyOutputPortName":"冷却","inputNodeGuid":"c28fb88d-51b1-47b2-be59-859e0ac638e3","inputPortId":7001,"inputPortName":"输入"}</t>
+          <t>{"outputNodeGuid":"356907e0-1488-4128-bfcc-7ff73cfc3330","outputPortId":1004,"legacyOutputPortName":"","inputNodeGuid":"c28fb88d-51b1-47b2-be59-859e0ac638e3","inputPortId":7001,"inputPortName":"输入"}</t>
         </is>
       </c>
       <c r="H21"/>
@@ -1351,16 +1351,16 @@
       <c r="C22"/>
       <c r="D22"/>
       <c r="E22">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>{"guid":"2d7e41c4-8e90-4b61-879c-4b2e5b9486db","nodeType":14,"position":{"x":408.66665649414063,"y":-1747.3333740234375},"targetType":1,"requiredTags":{"_tags":[]},"immunityTags":{"_tags":[]},"destroyWithNode":false,"positionSource":2,"positionBindingName":"head","textType":0,"fixedText":"","contextDataKey":"DamageResult","textColor":{"r":0.0,"g":0.323091983795166,"b":1.0,"a":1.0},"criticalColor":{"r":1.0,"g":0.5,"b":0.0,"a":1.0},"missColor":{"r":0.5,"g":0.5,"b":0.5,"a":1.0},"fontSize":45.0,"criticalFontSize":60.0,"duration":1.5,"offset":{"x":0.0,"y":0.0},"moveDirection":{"x":0.0,"y":1.0}}</t>
+          <t>{"guid":"3aafa9a5-4766-4204-91ab-d797aeb3c0e1","nodeType":7,"position":{"x":580.6666259765625,"y":-1987.3333740234375},"targetType":1,"endType":0}</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>{"outputNodeGuid":"356907e0-1488-4128-bfcc-7ff73cfc3330","outputPortId":1003,"legacyOutputPortName":"消耗","inputNodeGuid":"9d6f459d-b588-4b64-843b-1b71e8f299ae","inputPortId":7001,"inputPortName":"输入"}</t>
+          <t>{"outputNodeGuid":"356907e0-1488-4128-bfcc-7ff73cfc3330","outputPortId":1003,"legacyOutputPortName":"","inputNodeGuid":"9d6f459d-b588-4b64-843b-1b71e8f299ae","inputPortId":7001,"inputPortName":"输入"}</t>
         </is>
       </c>
       <c r="H22"/>
@@ -1371,16 +1371,16 @@
       <c r="C23"/>
       <c r="D23"/>
       <c r="E23">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>{"guid":"3aafa9a5-4766-4204-91ab-d797aeb3c0e1","nodeType":7,"position":{"x":580.6666259765625,"y":-1987.3333740234375},"targetType":1,"endType":0}</t>
+          <t>{"guid":"432ff1e3-b18d-476d-af80-d39ddc07402a","nodeType":20,"position":{"x":-491.33331298828125,"y":-2478.66650390625},"targetType":1,"skeletonDataAsset":null,"skeletonDataAssetPath":"Assets/Res/Spine/SP_Xiyiguai/SP_Xiyiguai_SkeletonData.asset","animationName":"Attack","animationDuration":"24","isAnimationLooping":false,"timeEffects":[{"triggerTime":11,"portIdValue":2315086,"legacyPortId":"de0ba361-3aba-4ef0-bb07-9b418fcae591"},{"triggerTime":24,"portIdValue":2715463,"legacyPortId":"7ecf9fe6-7c5e-46ae-bade-7922214225e2"}],"timeCues":[]}</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>{"outputNodeGuid":"432ff1e3-b18d-476d-af80-d39ddc07402a","outputPortId":2315086,"legacyOutputPortName":"de0ba361-3aba-4ef0-bb07-9b418fcae591","inputNodeGuid":"90bacd9f-d882-4bba-aaa8-41ed993ac3ff","inputPortId":7001,"inputPortName":"输入"}</t>
+          <t>{"outputNodeGuid":"432ff1e3-b18d-476d-af80-d39ddc07402a","outputPortId":2315086,"legacyOutputPortName":"","inputNodeGuid":"90bacd9f-d882-4bba-aaa8-41ed993ac3ff","inputPortId":7001,"inputPortName":"输入"}</t>
         </is>
       </c>
       <c r="H23"/>
@@ -1391,16 +1391,16 @@
       <c r="C24"/>
       <c r="D24"/>
       <c r="E24">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>{"guid":"432ff1e3-b18d-476d-af80-d39ddc07402a","nodeType":20,"position":{"x":-491.33331298828125,"y":-2478.66650390625},"targetType":1,"skeletonDataAsset":null,"skeletonDataAssetPath":"Assets/Res/Spine/SP_Xiyiguai/SP_Xiyiguai_SkeletonData.asset","animationName":"Attack","animationDuration":"24","isAnimationLooping":false,"timeEffects":[{"triggerTime":11,"portIdValue":2315086,"legacyPortId":"de0ba361-3aba-4ef0-bb07-9b418fcae591"},{"triggerTime":24,"portIdValue":2715463,"legacyPortId":"7ecf9fe6-7c5e-46ae-bade-7922214225e2"}],"timeCues":[]}</t>
+          <t>{"guid":"90bacd9f-d882-4bba-aaa8-41ed993ac3ff","nodeType":8,"position":{"x":-401.33331298828125,"y":-1826.666748046875},"targetType":2,"assetTags":{"_tags":[]},"grantedTags":{"_tags":[]},"applicationRequiredTags":{"_tags":[]},"applicationImmunityTags":{"_tags":[]},"removeGameEffectsWithTags":{"_tags":[]},"durationType":2,"duration":"0","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"_tags":[]},"cancelOnAbilityEnd":false,"launchPositionSource":0,"launchBindingName":"center","targetPositionSource":1,"targetBindingName":"center","projectileTargetType":0,"flyOver":false,"offsetAngle":0.0,"curveHeight":0.0,"projectilePrefab":null,"projectilePrefabPath":"Assets/Res/Prefab/Effect/ef_fashi_gandian_buff.prefab","speed":3.0,"maxDistance":10.0,"collisionRadius":0.5,"isPiercing":false,"maxPierceCount":1,"collisionTargetTags":{"_tags":[]},"collisionExcludeTags":{"_tags":[]},"isBouncing":false,"bounceTargetMode":0,"maxBounceCount":3,"bounceSearchRadius":10.0,"canBounceToSameTarget":false,"bounceAngleOffset":0.0}</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>{"outputNodeGuid":"90bacd9f-d882-4bba-aaa8-41ed993ac3ff","outputPortId":5001,"legacyOutputPortName":"碰撞时","inputNodeGuid":"eae41233-d297-46fe-a6c8-0b5c876fbb2a","inputPortId":7001,"inputPortName":"输入"}</t>
+          <t>{"outputNodeGuid":"90bacd9f-d882-4bba-aaa8-41ed993ac3ff","outputPortId":5001,"legacyOutputPortName":"","inputNodeGuid":"eae41233-d297-46fe-a6c8-0b5c876fbb2a","inputPortId":7001,"inputPortName":"输入"}</t>
         </is>
       </c>
       <c r="H24"/>
@@ -1411,16 +1411,16 @@
       <c r="C25"/>
       <c r="D25"/>
       <c r="E25">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>{"guid":"90bacd9f-d882-4bba-aaa8-41ed993ac3ff","nodeType":8,"position":{"x":-401.33331298828125,"y":-1826.666748046875},"targetType":2,"assetTags":{"_tags":[]},"grantedTags":{"_tags":[]},"applicationRequiredTags":{"_tags":[]},"applicationImmunityTags":{"_tags":[]},"removeGameEffectsWithTags":{"_tags":[]},"durationType":2,"duration":"0","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"_tags":[]},"cancelOnAbilityEnd":false,"launchPositionSource":0,"launchBindingName":"center","targetPositionSource":1,"targetBindingName":"center","projectileTargetType":0,"flyOver":false,"offsetAngle":0.0,"curveHeight":0.0,"projectilePrefab":null,"projectilePrefabPath":"Assets/Res/Prefab/Effect/ef_fashi_gandian_buff.prefab","speed":3.0,"maxDistance":10.0,"collisionRadius":0.5,"isPiercing":false,"maxPierceCount":1,"collisionTargetTags":{"_tags":[]},"collisionExcludeTags":{"_tags":[]},"isBouncing":false,"bounceTargetMode":0,"maxBounceCount":3,"bounceSearchRadius":10.0,"canBounceToSameTarget":false,"bounceAngleOffset":0.0}</t>
+          <t>{"guid":"c28fb88d-51b1-47b2-be59-859e0ac638e3","nodeType":10,"position":{"x":-1220.6666259765625,"y":-1747.3333740234375},"targetType":1,"assetTags":{"_tags":[]},"grantedTags":{"_tags":[{"_name":"CD.FireCircle","_hashCode":522143731,"_shortName":"FireCircle","_ancestorHashCodes":[-1137859925],"_ancestorNames":["CD"]}]},"applicationRequiredTags":{"_tags":[]},"applicationImmunityTags":{"_tags":[]},"removeGameEffectsWithTags":{"_tags":[]},"durationType":1,"duration":"1","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"_tags":[]},"cancelOnAbilityEnd":false,"cooldownType":0,"maxCharges":2,"chargeTime":"10"}</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>{"outputNodeGuid":"eae41233-d297-46fe-a6c8-0b5c876fbb2a","outputPortId":3004,"legacyOutputPortName":"完成效果","inputNodeGuid":"2d7e41c4-8e90-4b61-879c-4b2e5b9486db","inputPortId":7001,"inputPortName":"输入"}</t>
+          <t>{"outputNodeGuid":"eae41233-d297-46fe-a6c8-0b5c876fbb2a","outputPortId":3004,"legacyOutputPortName":"","inputNodeGuid":"2d7e41c4-8e90-4b61-879c-4b2e5b9486db","inputPortId":7001,"inputPortName":"输入"}</t>
         </is>
       </c>
       <c r="H25"/>
@@ -1431,16 +1431,16 @@
       <c r="C26"/>
       <c r="D26"/>
       <c r="E26">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>{"guid":"c28fb88d-51b1-47b2-be59-859e0ac638e3","nodeType":10,"position":{"x":-1220.6666259765625,"y":-1747.3333740234375},"targetType":1,"assetTags":{"_tags":[]},"grantedTags":{"_tags":[{"_name":"CD.FireCircle","_hashCode":522143731,"_shortName":"FireCircle","_ancestorHashCodes":[-1137859925],"_ancestorNames":["CD"]}]},"applicationRequiredTags":{"_tags":[]},"applicationImmunityTags":{"_tags":[]},"removeGameEffectsWithTags":{"_tags":[]},"durationType":1,"duration":"1","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"_tags":[]},"cancelOnAbilityEnd":false,"cooldownType":0,"maxCharges":2,"chargeTime":"10"}</t>
+          <t>{"guid":"356907e0-1488-4128-bfcc-7ff73cfc3330","nodeType":0,"position":{"x":-880.6666259765625,"y":-1851.3333740234375},"targetType":1,"skillId":7001,"assetTags":{"_tags":[]},"cancelAbilitiesWithTags":{"_tags":[]},"blockAbilitiesWithTags":{"_tags":[]},"activationOwnedTags":{"_tags":[]},"activationRequiredTags":{"_tags":[]},"activationBlockedTags":{"_tags":[{"_name":"CD.Wind","_hashCode":1982736573,"_shortName":"Wind","_ancestorHashCodes":[-1137859925],"_ancestorNames":["CD"]}]},"ongoingBlockedTags":{"_tags":[{"_name":"Buff.DeBuff.Stun","_hashCode":1791562953,"_shortName":"Stun","_ancestorHashCodes":[937056111,321157895],"_ancestorNames":["Buff","Buff.DeBuff"]}]},"eventOutputPorts":[]}</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>{"outputNodeGuid":"432ff1e3-b18d-476d-af80-d39ddc07402a","outputPortId":2715463,"legacyOutputPortName":"7ecf9fe6-7c5e-46ae-bade-7922214225e2","inputNodeGuid":"3aafa9a5-4766-4204-91ab-d797aeb3c0e1","inputPortId":7001,"inputPortName":"输入"}</t>
+          <t>{"outputNodeGuid":"432ff1e3-b18d-476d-af80-d39ddc07402a","outputPortId":2715463,"legacyOutputPortName":"","inputNodeGuid":"3aafa9a5-4766-4204-91ab-d797aeb3c0e1","inputPortId":7001,"inputPortName":"输入"}</t>
         </is>
       </c>
       <c r="H26"/>
@@ -1451,11 +1451,11 @@
       <c r="C27"/>
       <c r="D27"/>
       <c r="E27">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>{"guid":"356907e0-1488-4128-bfcc-7ff73cfc3330","nodeType":0,"position":{"x":-880.6666259765625,"y":-1851.3333740234375},"targetType":1,"skillId":7001,"assetTags":{"_tags":[]},"cancelAbilitiesWithTags":{"_tags":[]},"blockAbilitiesWithTags":{"_tags":[]},"activationOwnedTags":{"_tags":[]},"activationRequiredTags":{"_tags":[]},"activationBlockedTags":{"_tags":[{"_name":"CD.Wind","_hashCode":1982736573,"_shortName":"Wind","_ancestorHashCodes":[-1137859925],"_ancestorNames":["CD"]}]},"ongoingBlockedTags":{"_tags":[{"_name":"Buff.DeBuff.Stun","_hashCode":1791562953,"_shortName":"Stun","_ancestorHashCodes":[937056111,321157895],"_ancestorNames":["Buff","Buff.DeBuff"]}]},"eventOutputPorts":[]}</t>
+          <t>{"guid":"eae41233-d297-46fe-a6c8-0b5c876fbb2a","nodeType":1,"position":{"x":46.66668701171875,"y":-1808.666748046875},"targetType":0,"assetTags":{"_tags":[]},"grantedTags":{"_tags":[]},"applicationRequiredTags":{"_tags":[]},"applicationImmunityTags":{"_tags":[]},"removeGameEffectsWithTags":{"_tags":[]},"durationType":0,"duration":"0","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"_tags":[]},"cancelOnAbilityEnd":true,"damageType":0,"damageSourceType":0,"damageFixedValue":10.0,"damageFormula":"","damageMMCType":0,"damageSetByCallerKey":"","damageMMCCaptureAttribute":200,"damageMMCAttributeSource":0,"damageMMCCoefficient":1.0,"damageMMCUseSnapshot":true,"damageMultiplyByStackCount":false,"damageCalculationType":0,"enableHitKnockback":true,"knockbackDistance":1.0,"knockbackSpeed":12.0}</t>
         </is>
       </c>
       <c r="G27"/>
@@ -1497,7 +1497,7 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>{"guid":"eae41233-d297-46fe-a6c8-0b5c876fbb2a","nodeType":1,"position":{"x":46.66668701171875,"y":-1808.666748046875},"targetType":0,"assetTags":{"_tags":[]},"grantedTags":{"_tags":[]},"applicationRequiredTags":{"_tags":[]},"applicationImmunityTags":{"_tags":[]},"removeGameEffectsWithTags":{"_tags":[]},"durationType":0,"duration":"0","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"_tags":[]},"cancelOnAbilityEnd":true,"damageType":0,"damageSourceType":0,"damageFixedValue":10.0,"damageFormula":"","damageMMCType":0,"damageSetByCallerKey":"","damageMMCCaptureAttribute":200,"damageMMCAttributeSource":0,"damageMMCCoefficient":1.0,"damageMMCUseSnapshot":true,"damageMultiplyByStackCount":false,"damageCalculationType":0}</t>
+          <t>{"guid":"eae41233-d297-46fe-a6c8-0b5c876fbb2a","nodeType":1,"position":{"x":46.66668701171875,"y":-1808.666748046875},"targetType":0,"assetTags":{"_tags":[]},"grantedTags":{"_tags":[]},"applicationRequiredTags":{"_tags":[]},"applicationImmunityTags":{"_tags":[]},"removeGameEffectsWithTags":{"_tags":[]},"durationType":0,"duration":"0","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"_tags":[]},"cancelOnAbilityEnd":true,"damageType":0,"damageSourceType":0,"damageFixedValue":10.0,"damageFormula":"","damageMMCType":0,"damageSetByCallerKey":"","damageMMCCaptureAttribute":200,"damageMMCAttributeSource":0,"damageMMCCoefficient":1.0,"damageMMCUseSnapshot":true,"damageMultiplyByStackCount":false,"damageCalculationType":0,"enableHitKnockback":false,"knockbackDistance":1.0,"knockbackSpeed":12.0}</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -2252,7 +2252,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>{"outputNodeGuid":"432ff1e3-b18d-476d-af80-d39ddc07402a","outputPortId":2287012,"legacyOutputPortName":"8dea1941-c520-4f9a-aee0-40932c8542ef","inputNodeGuid":"cde57fb8-b693-4da8-a4a8-fd61e56c5dcd","inputPortId":7001,"inputPortName":"输入"}</t>
+          <t>{"outputNodeGuid":"432ff1e3-b18d-476d-af80-d39ddc07402a","outputPortId":2287012,"legacyOutputPortName":"","inputNodeGuid":"cde57fb8-b693-4da8-a4a8-fd61e56c5dcd","inputPortId":7001,"inputPortName":"输入"}</t>
         </is>
       </c>
       <c r="H66"/>
@@ -2272,7 +2272,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>{"outputNodeGuid":"356907e0-1488-4128-bfcc-7ff73cfc3330","outputPortId":1002,"legacyOutputPortName":"动画","inputNodeGuid":"432ff1e3-b18d-476d-af80-d39ddc07402a","inputPortId":7001,"inputPortName":"输入"}</t>
+          <t>{"outputNodeGuid":"356907e0-1488-4128-bfcc-7ff73cfc3330","outputPortId":1002,"legacyOutputPortName":"","inputNodeGuid":"432ff1e3-b18d-476d-af80-d39ddc07402a","inputPortId":7001,"inputPortName":"输入"}</t>
         </is>
       </c>
       <c r="H67"/>
@@ -2292,7 +2292,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>{"outputNodeGuid":"356907e0-1488-4128-bfcc-7ff73cfc3330","outputPortId":1004,"legacyOutputPortName":"冷却","inputNodeGuid":"c28fb88d-51b1-47b2-be59-859e0ac638e3","inputPortId":7001,"inputPortName":"输入"}</t>
+          <t>{"outputNodeGuid":"356907e0-1488-4128-bfcc-7ff73cfc3330","outputPortId":1004,"legacyOutputPortName":"","inputNodeGuid":"c28fb88d-51b1-47b2-be59-859e0ac638e3","inputPortId":7001,"inputPortName":"输入"}</t>
         </is>
       </c>
       <c r="H68"/>
@@ -2303,16 +2303,16 @@
       <c r="C69"/>
       <c r="D69"/>
       <c r="E69">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>{"guid":"f8947676-1084-4228-b991-1509cc7fe851","nodeType":1,"position":{"x":994.666748046875,"y":-2344.0},"targetType":0,"assetTags":{"_tags":[]},"grantedTags":{"_tags":[]},"applicationRequiredTags":{"_tags":[]},"applicationImmunityTags":{"_tags":[]},"removeGameEffectsWithTags":{"_tags":[]},"durationType":0,"duration":"0","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"_tags":[]},"cancelOnAbilityEnd":true,"damageType":0,"damageSourceType":0,"damageFixedValue":10.0,"damageFormula":"","damageMMCType":0,"damageSetByCallerKey":"","damageMMCCaptureAttribute":200,"damageMMCAttributeSource":0,"damageMMCCoefficient":1.0,"damageMMCUseSnapshot":true,"damageMultiplyByStackCount":false,"damageCalculationType":0}</t>
+          <t>{"guid":"c353e286-8ef0-460a-b917-887f2aeb390a","nodeType":14,"position":{"x":1190.0,"y":-2344.0},"targetType":1,"requiredTags":{"_tags":[]},"immunityTags":{"_tags":[]},"destroyWithNode":false,"positionSource":2,"positionBindingName":"head","textType":0,"fixedText":"","contextDataKey":"DamageResult","textColor":{"r":1.0,"g":0.0,"b":0.0,"a":1.0},"criticalColor":{"r":1.0,"g":0.5,"b":0.0,"a":1.0},"missColor":{"r":0.5,"g":0.5,"b":0.5,"a":1.0},"fontSize":45.0,"criticalFontSize":60.0,"duration":1.5,"offset":{"x":0.0,"y":0.0},"moveDirection":{"x":0.0,"y":1.0}}</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>{"outputNodeGuid":"356907e0-1488-4128-bfcc-7ff73cfc3330","outputPortId":1003,"legacyOutputPortName":"消耗","inputNodeGuid":"9d6f459d-b588-4b64-843b-1b71e8f299ae","inputPortId":7001,"inputPortName":"输入"}</t>
+          <t>{"outputNodeGuid":"356907e0-1488-4128-bfcc-7ff73cfc3330","outputPortId":1003,"legacyOutputPortName":"","inputNodeGuid":"9d6f459d-b588-4b64-843b-1b71e8f299ae","inputPortId":7001,"inputPortName":"输入"}</t>
         </is>
       </c>
       <c r="H69"/>
@@ -2323,16 +2323,16 @@
       <c r="C70"/>
       <c r="D70"/>
       <c r="E70">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>{"guid":"c353e286-8ef0-460a-b917-887f2aeb390a","nodeType":14,"position":{"x":1190.0,"y":-2344.0},"targetType":1,"requiredTags":{"_tags":[]},"immunityTags":{"_tags":[]},"destroyWithNode":false,"positionSource":2,"positionBindingName":"head","textType":0,"fixedText":"","contextDataKey":"DamageResult","textColor":{"r":1.0,"g":0.0,"b":0.0,"a":1.0},"criticalColor":{"r":1.0,"g":0.5,"b":0.0,"a":1.0},"missColor":{"r":0.5,"g":0.5,"b":0.5,"a":1.0},"fontSize":45.0,"criticalFontSize":60.0,"duration":1.5,"offset":{"x":0.0,"y":0.0},"moveDirection":{"x":0.0,"y":1.0}}</t>
+          <t>{"guid":"9d6f459d-b588-4b64-843b-1b71e8f299ae","nodeType":3,"position":{"x":-1130.6666259765625,"y":-2479.333251953125},"targetType":1,"assetTags":{"_tags":[]},"grantedTags":{"_tags":[]},"applicationRequiredTags":{"_tags":[]},"applicationImmunityTags":{"_tags":[]},"removeGameEffectsWithTags":{"_tags":[]},"durationType":0,"duration":"0","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[{"attrType":100,"operation":0,"magnitudeSourceType":0,"fixedValue":-10.0,"formula":"","mmcType":0,"setByCallerKey":"","mmcCaptureAttribute":200,"mmcAttributeSource":0,"mmcCoefficient":1.0,"mmcUseSnapshot":true}],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"_tags":[]},"cancelOnAbilityEnd":true}</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>{"outputNodeGuid":"432ff1e3-b18d-476d-af80-d39ddc07402a","outputPortId":2315086,"legacyOutputPortName":"de0ba361-3aba-4ef0-bb07-9b418fcae591","inputNodeGuid":"e33ab94c-1496-4d6a-ba5e-1afd38bb0c30","inputPortId":7001,"inputPortName":"输入"}</t>
+          <t>{"outputNodeGuid":"432ff1e3-b18d-476d-af80-d39ddc07402a","outputPortId":2315086,"legacyOutputPortName":"","inputNodeGuid":"e33ab94c-1496-4d6a-ba5e-1afd38bb0c30","inputPortId":7001,"inputPortName":"输入"}</t>
         </is>
       </c>
       <c r="H70"/>
@@ -2343,16 +2343,16 @@
       <c r="C71"/>
       <c r="D71"/>
       <c r="E71">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>{"guid":"9d6f459d-b588-4b64-843b-1b71e8f299ae","nodeType":3,"position":{"x":-1130.6666259765625,"y":-2479.333251953125},"targetType":1,"assetTags":{"_tags":[]},"grantedTags":{"_tags":[]},"applicationRequiredTags":{"_tags":[]},"applicationImmunityTags":{"_tags":[]},"removeGameEffectsWithTags":{"_tags":[]},"durationType":0,"duration":"0","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[{"attrType":100,"operation":0,"magnitudeSourceType":0,"fixedValue":-10.0,"formula":"","mmcType":0,"setByCallerKey":"","mmcCaptureAttribute":200,"mmcAttributeSource":0,"mmcCoefficient":1.0,"mmcUseSnapshot":true}],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"_tags":[]},"cancelOnAbilityEnd":true}</t>
+          <t>{"guid":"c28fb88d-51b1-47b2-be59-859e0ac638e3","nodeType":10,"position":{"x":-1130.6666259765625,"y":-2232.0},"targetType":1,"assetTags":{"_tags":[]},"grantedTags":{"_tags":[{"_name":"CD.Sweep","_hashCode":-303359587,"_shortName":"Sweep","_ancestorHashCodes":[-1137859925],"_ancestorNames":["CD"]}]},"applicationRequiredTags":{"_tags":[]},"applicationImmunityTags":{"_tags":[]},"removeGameEffectsWithTags":{"_tags":[]},"durationType":1,"duration":"1","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"_tags":[]},"cancelOnAbilityEnd":false,"cooldownType":0,"maxCharges":2,"chargeTime":"10"}</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>{"outputNodeGuid":"e33ab94c-1496-4d6a-ba5e-1afd38bb0c30","outputPortId":4001,"legacyOutputPortName":"对每个目标","inputNodeGuid":"f8947676-1084-4228-b991-1509cc7fe851","inputPortId":7001,"inputPortName":"输入"}</t>
+          <t>{"outputNodeGuid":"e33ab94c-1496-4d6a-ba5e-1afd38bb0c30","outputPortId":4001,"legacyOutputPortName":"","inputNodeGuid":"f8947676-1084-4228-b991-1509cc7fe851","inputPortId":7001,"inputPortName":"输入"}</t>
         </is>
       </c>
       <c r="H71"/>
@@ -2363,16 +2363,16 @@
       <c r="C72"/>
       <c r="D72"/>
       <c r="E72">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>{"guid":"c28fb88d-51b1-47b2-be59-859e0ac638e3","nodeType":10,"position":{"x":-1130.6666259765625,"y":-2232.0},"targetType":1,"assetTags":{"_tags":[]},"grantedTags":{"_tags":[{"_name":"CD.Sweep","_hashCode":-303359587,"_shortName":"Sweep","_ancestorHashCodes":[-1137859925],"_ancestorNames":["CD"]}]},"applicationRequiredTags":{"_tags":[]},"applicationImmunityTags":{"_tags":[]},"removeGameEffectsWithTags":{"_tags":[]},"durationType":1,"duration":"1","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"_tags":[]},"cancelOnAbilityEnd":false,"cooldownType":0,"maxCharges":2,"chargeTime":"10"}</t>
+          <t>{"guid":"356907e0-1488-4128-bfcc-7ff73cfc3330","nodeType":0,"position":{"x":-797.3333740234375,"y":-2479.333251953125},"targetType":1,"skillId":1001,"assetTags":{"_tags":[]},"cancelAbilitiesWithTags":{"_tags":[]},"blockAbilitiesWithTags":{"_tags":[]},"activationOwnedTags":{"_tags":[]},"activationRequiredTags":{"_tags":[]},"activationBlockedTags":{"_tags":[{"_name":"CD.Sweep","_hashCode":-303359587,"_shortName":"Sweep","_ancestorHashCodes":[-1137859925],"_ancestorNames":["CD"]}]},"ongoingBlockedTags":{"_tags":[]},"eventOutputPorts":[]}</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>{"outputNodeGuid":"f8947676-1084-4228-b991-1509cc7fe851","outputPortId":3004,"legacyOutputPortName":"完成效果","inputNodeGuid":"c353e286-8ef0-460a-b917-887f2aeb390a","inputPortId":7001,"inputPortName":"输入"}</t>
+          <t>{"outputNodeGuid":"f8947676-1084-4228-b991-1509cc7fe851","outputPortId":3004,"legacyOutputPortName":"","inputNodeGuid":"c353e286-8ef0-460a-b917-887f2aeb390a","inputPortId":7001,"inputPortName":"输入"}</t>
         </is>
       </c>
       <c r="H72"/>
@@ -2383,16 +2383,16 @@
       <c r="C73"/>
       <c r="D73"/>
       <c r="E73">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>{"guid":"356907e0-1488-4128-bfcc-7ff73cfc3330","nodeType":0,"position":{"x":-797.3333740234375,"y":-2479.333251953125},"targetType":1,"skillId":1001,"assetTags":{"_tags":[]},"cancelAbilitiesWithTags":{"_tags":[]},"blockAbilitiesWithTags":{"_tags":[]},"activationOwnedTags":{"_tags":[]},"activationRequiredTags":{"_tags":[]},"activationBlockedTags":{"_tags":[{"_name":"CD.Sweep","_hashCode":-303359587,"_shortName":"Sweep","_ancestorHashCodes":[-1137859925],"_ancestorNames":["CD"]}]},"ongoingBlockedTags":{"_tags":[]},"eventOutputPorts":[]}</t>
+          <t>{"guid":"432ff1e3-b18d-476d-af80-d39ddc07402a","nodeType":20,"position":{"x":-414.0,"y":-2826.0},"targetType":1,"skeletonDataAsset":null,"skeletonDataAssetPath":"Assets/Res/Spine/SP_Zhanshi/SP_Zhanshi_SkeletonData.asset","animationName":"Skill_attack_1001","animationDuration":"18","isAnimationLooping":true,"timeEffects":[{"triggerTime":7,"portIdValue":2315086,"legacyPortId":"de0ba361-3aba-4ef0-bb07-9b418fcae591"},{"triggerTime":18,"portIdValue":2649436,"legacyPortId":"84e238a8-5baf-470e-829f-186695064945"}],"timeCues":[{"startTime":7,"endTime":48,"portIdValue":2287012,"legacyPortId":"8dea1941-c520-4f9a-aee0-40932c8542ef"}]}</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>{"outputNodeGuid":"432ff1e3-b18d-476d-af80-d39ddc07402a","outputPortId":2649436,"legacyOutputPortName":"84e238a8-5baf-470e-829f-186695064945","inputNodeGuid":"2cfdacd2-0186-49dd-b177-4eb8c0ad87bd","inputPortId":7001,"inputPortName":"输入"}</t>
+          <t>{"outputNodeGuid":"432ff1e3-b18d-476d-af80-d39ddc07402a","outputPortId":2649436,"legacyOutputPortName":"","inputNodeGuid":"2cfdacd2-0186-49dd-b177-4eb8c0ad87bd","inputPortId":7001,"inputPortName":"输入"}</t>
         </is>
       </c>
       <c r="H73"/>
@@ -2403,11 +2403,11 @@
       <c r="C74"/>
       <c r="D74"/>
       <c r="E74">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>{"guid":"432ff1e3-b18d-476d-af80-d39ddc07402a","nodeType":20,"position":{"x":-414.0,"y":-2826.0},"targetType":1,"skeletonDataAsset":null,"skeletonDataAssetPath":"Assets/Res/Spine/SP_Zhanshi/SP_Zhanshi_SkeletonData.asset","animationName":"Skill_attack_1001","animationDuration":"18","isAnimationLooping":true,"timeEffects":[{"triggerTime":7,"portIdValue":2315086,"legacyPortId":"de0ba361-3aba-4ef0-bb07-9b418fcae591"},{"triggerTime":18,"portIdValue":2649436,"legacyPortId":"84e238a8-5baf-470e-829f-186695064945"}],"timeCues":[{"startTime":7,"endTime":48,"portIdValue":2287012,"legacyPortId":"8dea1941-c520-4f9a-aee0-40932c8542ef"}]}</t>
+          <t>{"guid":"f8947676-1084-4228-b991-1509cc7fe851","nodeType":1,"position":{"x":994.666748046875,"y":-2344.0},"targetType":0,"assetTags":{"_tags":[]},"grantedTags":{"_tags":[]},"applicationRequiredTags":{"_tags":[]},"applicationImmunityTags":{"_tags":[]},"removeGameEffectsWithTags":{"_tags":[]},"durationType":0,"duration":"0","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"_tags":[]},"cancelOnAbilityEnd":true,"damageType":0,"damageSourceType":0,"damageFixedValue":10.0,"damageFormula":"","damageMMCType":0,"damageSetByCallerKey":"","damageMMCCaptureAttribute":200,"damageMMCAttributeSource":0,"damageMMCCoefficient":1.0,"damageMMCUseSnapshot":true,"damageMultiplyByStackCount":false,"damageCalculationType":0,"enableHitKnockback":true,"knockbackDistance":1.0,"knockbackSpeed":12.0}</t>
         </is>
       </c>
       <c r="G74"/>
@@ -2449,7 +2449,7 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>{"guid":"f8947676-1084-4228-b991-1509cc7fe851","nodeType":1,"position":{"x":1452.666748046875,"y":-2239.333251953125},"targetType":0,"assetTags":{"_tags":[]},"grantedTags":{"_tags":[]},"applicationRequiredTags":{"_tags":[]},"applicationImmunityTags":{"_tags":[]},"removeGameEffectsWithTags":{"_tags":[]},"durationType":0,"duration":"0","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"_tags":[]},"cancelOnAbilityEnd":true,"damageType":0,"damageSourceType":0,"damageFixedValue":10.0,"damageFormula":"","damageMMCType":0,"damageSetByCallerKey":"","damageMMCCaptureAttribute":200,"damageMMCAttributeSource":0,"damageMMCCoefficient":1.0,"damageMMCUseSnapshot":true,"damageMultiplyByStackCount":false,"damageCalculationType":0}</t>
+          <t>{"guid":"f8947676-1084-4228-b991-1509cc7fe851","nodeType":1,"position":{"x":1452.666748046875,"y":-2239.333251953125},"targetType":0,"assetTags":{"_tags":[]},"grantedTags":{"_tags":[]},"applicationRequiredTags":{"_tags":[]},"applicationImmunityTags":{"_tags":[]},"removeGameEffectsWithTags":{"_tags":[]},"durationType":0,"duration":"0","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"_tags":[]},"cancelOnAbilityEnd":true,"damageType":0,"damageSourceType":0,"damageFixedValue":10.0,"damageFormula":"","damageMMCType":0,"damageSetByCallerKey":"","damageMMCCaptureAttribute":200,"damageMMCAttributeSource":0,"damageMMCCoefficient":1.0,"damageMMCUseSnapshot":true,"damageMultiplyByStackCount":false,"damageCalculationType":0,"enableHitKnockback":false,"knockbackDistance":1.0,"knockbackSpeed":12.0}</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
@@ -2851,7 +2851,7 @@
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>{"guid":"a32d1135-94db-4f81-95ba-9d5f105ef8d0","nodeType":1,"position":{"x":308.79998779296875,"y":-1720.0},"targetType":0,"assetTags":{"_tags":[]},"grantedTags":{"_tags":[]},"applicationRequiredTags":{"_tags":[]},"applicationImmunityTags":{"_tags":[]},"removeGameEffectsWithTags":{"_tags":[]},"durationType":0,"duration":"0","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"_tags":[]},"cancelOnAbilityEnd":true,"damageType":0,"damageSourceType":0,"damageFixedValue":1.0,"damageFormula":"","damageMMCType":0,"damageSetByCallerKey":"","damageMMCCaptureAttribute":200,"damageMMCAttributeSource":0,"damageMMCCoefficient":1.0,"damageMMCUseSnapshot":true,"damageMultiplyByStackCount":false,"damageCalculationType":0}</t>
+          <t>{"guid":"a32d1135-94db-4f81-95ba-9d5f105ef8d0","nodeType":1,"position":{"x":308.79998779296875,"y":-1720.0},"targetType":0,"assetTags":{"_tags":[]},"grantedTags":{"_tags":[]},"applicationRequiredTags":{"_tags":[]},"applicationImmunityTags":{"_tags":[]},"removeGameEffectsWithTags":{"_tags":[]},"durationType":0,"duration":"0","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"_tags":[]},"cancelOnAbilityEnd":true,"damageType":0,"damageSourceType":0,"damageFixedValue":1.0,"damageFormula":"","damageMMCType":0,"damageSetByCallerKey":"","damageMMCCaptureAttribute":200,"damageMMCAttributeSource":0,"damageMMCCoefficient":1.0,"damageMMCUseSnapshot":true,"damageMultiplyByStackCount":false,"damageCalculationType":0,"enableHitKnockback":false,"knockbackDistance":1.0,"knockbackSpeed":12.0}</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">

--- a/Design/Excel/ET/Datas/Game/SkillGraph.xlsx
+++ b/Design/Excel/ET/Datas/Game/SkillGraph.xlsx
@@ -1016,7 +1016,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>{"outputNodeGuid":"426755b7-c39a-4524-9cb5-960a31a19c10","outputPortId":3002,"legacyOutputPortName":"每周期执行","inputNodeGuid":"a8c2d6c0-65f1-4bed-8a6a-70197e84bb56","inputPortId":7001,"inputPortName":"输入"}</t>
+          <t>{"outputNodeGuid":"426755b7-c39a-4524-9cb5-960a31a19c10","outputPortId":3002,"inputNodeGuid":"a8c2d6c0-65f1-4bed-8a6a-70197e84bb56","inputPortId":7001}</t>
         </is>
       </c>
       <c r="H5"/>
@@ -1036,7 +1036,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>{"outputNodeGuid":"a8c2d6c0-65f1-4bed-8a6a-70197e84bb56","outputPortId":3004,"legacyOutputPortName":"完成效果","inputNodeGuid":"d086a8c9-8557-4a61-8fd2-64b3c1e543a3","inputPortId":7001,"inputPortName":"输入"}</t>
+          <t>{"outputNodeGuid":"a8c2d6c0-65f1-4bed-8a6a-70197e84bb56","outputPortId":3004,"inputNodeGuid":"d086a8c9-8557-4a61-8fd2-64b3c1e543a3","inputPortId":7001}</t>
         </is>
       </c>
       <c r="H6"/>
@@ -1056,7 +1056,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>{"outputNodeGuid":"d5809887-df6e-4604-bd09-36cef191ce83","outputPortId":1001,"legacyOutputPortName":"激活","inputNodeGuid":"426755b7-c39a-4524-9cb5-960a31a19c10","inputPortId":7001,"inputPortName":"输入"}</t>
+          <t>{"outputNodeGuid":"d5809887-df6e-4604-bd09-36cef191ce83","outputPortId":1001,"inputNodeGuid":"426755b7-c39a-4524-9cb5-960a31a19c10","inputPortId":7001}</t>
         </is>
       </c>
       <c r="H7"/>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>{"outputNodeGuid":"7eefd9ae-c57e-439d-b1b6-e7f4e52f2f6f","outputPortId":3004,"legacyOutputPortName":"完成效果","inputNodeGuid":"426755b7-c39a-4524-9cb5-960a31a19c10","inputPortId":7001,"inputPortName":"输入"}</t>
+          <t>{"outputNodeGuid":"7eefd9ae-c57e-439d-b1b6-e7f4e52f2f6f","outputPortId":3004,"inputNodeGuid":"426755b7-c39a-4524-9cb5-960a31a19c10","inputPortId":7001}</t>
         </is>
       </c>
       <c r="H8"/>
@@ -1118,7 +1118,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>{"outputNodeGuid":"432ff1e3-b18d-476d-af80-d39ddc07402a","outputPortId":2287012,"legacyOutputPortName":"8dea1941-c520-4f9a-aee0-40932c8542ef","inputNodeGuid":"cde57fb8-b693-4da8-a4a8-fd61e56c5dcd","inputPortId":7001,"inputPortName":"输入"}</t>
+          <t>{"outputNodeGuid":"432ff1e3-b18d-476d-af80-d39ddc07402a","outputPortId":2287012,"inputNodeGuid":"cde57fb8-b693-4da8-a4a8-fd61e56c5dcd","inputPortId":7001}</t>
         </is>
       </c>
       <c r="H10"/>
@@ -1138,7 +1138,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>{"outputNodeGuid":"356907e0-1488-4128-bfcc-7ff73cfc3330","outputPortId":1002,"legacyOutputPortName":"动画","inputNodeGuid":"432ff1e3-b18d-476d-af80-d39ddc07402a","inputPortId":7001,"inputPortName":"输入"}</t>
+          <t>{"outputNodeGuid":"356907e0-1488-4128-bfcc-7ff73cfc3330","outputPortId":1002,"inputNodeGuid":"432ff1e3-b18d-476d-af80-d39ddc07402a","inputPortId":7001}</t>
         </is>
       </c>
       <c r="H11"/>
@@ -1158,7 +1158,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>{"outputNodeGuid":"356907e0-1488-4128-bfcc-7ff73cfc3330","outputPortId":1004,"legacyOutputPortName":"冷却","inputNodeGuid":"c28fb88d-51b1-47b2-be59-859e0ac638e3","inputPortId":7001,"inputPortName":"输入"}</t>
+          <t>{"outputNodeGuid":"356907e0-1488-4128-bfcc-7ff73cfc3330","outputPortId":1004,"inputNodeGuid":"c28fb88d-51b1-47b2-be59-859e0ac638e3","inputPortId":7001}</t>
         </is>
       </c>
       <c r="H12"/>
@@ -1178,7 +1178,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>{"outputNodeGuid":"356907e0-1488-4128-bfcc-7ff73cfc3330","outputPortId":1003,"legacyOutputPortName":"消耗","inputNodeGuid":"9d6f459d-b588-4b64-843b-1b71e8f299ae","inputPortId":7001,"inputPortName":"输入"}</t>
+          <t>{"outputNodeGuid":"356907e0-1488-4128-bfcc-7ff73cfc3330","outputPortId":1003,"inputNodeGuid":"9d6f459d-b588-4b64-843b-1b71e8f299ae","inputPortId":7001}</t>
         </is>
       </c>
       <c r="H13"/>
@@ -1198,7 +1198,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>{"outputNodeGuid":"432ff1e3-b18d-476d-af80-d39ddc07402a","outputPortId":2315086,"legacyOutputPortName":"de0ba361-3aba-4ef0-bb07-9b418fcae591","inputNodeGuid":"e33ab94c-1496-4d6a-ba5e-1afd38bb0c30","inputPortId":7001,"inputPortName":"输入"}</t>
+          <t>{"outputNodeGuid":"432ff1e3-b18d-476d-af80-d39ddc07402a","outputPortId":2315086,"inputNodeGuid":"e33ab94c-1496-4d6a-ba5e-1afd38bb0c30","inputPortId":7001}</t>
         </is>
       </c>
       <c r="H14"/>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>{"outputNodeGuid":"f8947676-1084-4228-b991-1509cc7fe851","outputPortId":3004,"legacyOutputPortName":"完成效果","inputNodeGuid":"c353e286-8ef0-460a-b917-887f2aeb390a","inputPortId":7001,"inputPortName":"输入"}</t>
+          <t>{"outputNodeGuid":"f8947676-1084-4228-b991-1509cc7fe851","outputPortId":3004,"inputNodeGuid":"c353e286-8ef0-460a-b917-887f2aeb390a","inputPortId":7001}</t>
         </is>
       </c>
       <c r="H15"/>
@@ -1238,7 +1238,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>{"outputNodeGuid":"e33ab94c-1496-4d6a-ba5e-1afd38bb0c30","outputPortId":4001,"legacyOutputPortName":"对每个目标","inputNodeGuid":"cb1df36f-5729-423e-9d1a-287db5a433f0","inputPortId":7001,"inputPortName":"输入"}</t>
+          <t>{"outputNodeGuid":"e33ab94c-1496-4d6a-ba5e-1afd38bb0c30","outputPortId":4001,"inputNodeGuid":"cb1df36f-5729-423e-9d1a-287db5a433f0","inputPortId":7001}</t>
         </is>
       </c>
       <c r="H16"/>
@@ -1258,7 +1258,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>{"outputNodeGuid":"cb1df36f-5729-423e-9d1a-287db5a433f0","outputPortId":3002,"legacyOutputPortName":"每周期执行","inputNodeGuid":"f8947676-1084-4228-b991-1509cc7fe851","inputPortId":7001,"inputPortName":"输入"}</t>
+          <t>{"outputNodeGuid":"cb1df36f-5729-423e-9d1a-287db5a433f0","outputPortId":3002,"inputNodeGuid":"f8947676-1084-4228-b991-1509cc7fe851","inputPortId":7001}</t>
         </is>
       </c>
       <c r="H17"/>
@@ -1278,7 +1278,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>{"outputNodeGuid":"432ff1e3-b18d-476d-af80-d39ddc07402a","outputPortId":2821173,"legacyOutputPortName":"97dc121c-84b7-4f94-9997-02e0e5b2ea6c","inputNodeGuid":"011aad56-e96c-41eb-9d85-e793d74a40bb","inputPortId":7001,"inputPortName":"输入"}</t>
+          <t>{"outputNodeGuid":"432ff1e3-b18d-476d-af80-d39ddc07402a","outputPortId":2821173,"inputNodeGuid":"011aad56-e96c-41eb-9d85-e793d74a40bb","inputPortId":7001}</t>
         </is>
       </c>
       <c r="H18"/>
@@ -1320,7 +1320,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>{"outputNodeGuid":"356907e0-1488-4128-bfcc-7ff73cfc3330","outputPortId":1002,"legacyOutputPortName":"","inputNodeGuid":"432ff1e3-b18d-476d-af80-d39ddc07402a","inputPortId":7001,"inputPortName":"输入"}</t>
+          <t>{"outputNodeGuid":"356907e0-1488-4128-bfcc-7ff73cfc3330","outputPortId":1002,"inputNodeGuid":"432ff1e3-b18d-476d-af80-d39ddc07402a","inputPortId":7001}</t>
         </is>
       </c>
       <c r="H20"/>
@@ -1340,7 +1340,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>{"outputNodeGuid":"356907e0-1488-4128-bfcc-7ff73cfc3330","outputPortId":1004,"legacyOutputPortName":"","inputNodeGuid":"c28fb88d-51b1-47b2-be59-859e0ac638e3","inputPortId":7001,"inputPortName":"输入"}</t>
+          <t>{"outputNodeGuid":"356907e0-1488-4128-bfcc-7ff73cfc3330","outputPortId":1004,"inputNodeGuid":"c28fb88d-51b1-47b2-be59-859e0ac638e3","inputPortId":7001}</t>
         </is>
       </c>
       <c r="H21"/>
@@ -1360,7 +1360,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>{"outputNodeGuid":"356907e0-1488-4128-bfcc-7ff73cfc3330","outputPortId":1003,"legacyOutputPortName":"","inputNodeGuid":"9d6f459d-b588-4b64-843b-1b71e8f299ae","inputPortId":7001,"inputPortName":"输入"}</t>
+          <t>{"outputNodeGuid":"356907e0-1488-4128-bfcc-7ff73cfc3330","outputPortId":1003,"inputNodeGuid":"9d6f459d-b588-4b64-843b-1b71e8f299ae","inputPortId":7001}</t>
         </is>
       </c>
       <c r="H22"/>
@@ -1380,7 +1380,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>{"outputNodeGuid":"432ff1e3-b18d-476d-af80-d39ddc07402a","outputPortId":2315086,"legacyOutputPortName":"","inputNodeGuid":"90bacd9f-d882-4bba-aaa8-41ed993ac3ff","inputPortId":7001,"inputPortName":"输入"}</t>
+          <t>{"outputNodeGuid":"432ff1e3-b18d-476d-af80-d39ddc07402a","outputPortId":2315086,"inputNodeGuid":"90bacd9f-d882-4bba-aaa8-41ed993ac3ff","inputPortId":7001}</t>
         </is>
       </c>
       <c r="H23"/>
@@ -1400,7 +1400,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>{"outputNodeGuid":"90bacd9f-d882-4bba-aaa8-41ed993ac3ff","outputPortId":5001,"legacyOutputPortName":"","inputNodeGuid":"eae41233-d297-46fe-a6c8-0b5c876fbb2a","inputPortId":7001,"inputPortName":"输入"}</t>
+          <t>{"outputNodeGuid":"90bacd9f-d882-4bba-aaa8-41ed993ac3ff","outputPortId":5001,"inputNodeGuid":"eae41233-d297-46fe-a6c8-0b5c876fbb2a","inputPortId":7001}</t>
         </is>
       </c>
       <c r="H24"/>
@@ -1420,7 +1420,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>{"outputNodeGuid":"eae41233-d297-46fe-a6c8-0b5c876fbb2a","outputPortId":3004,"legacyOutputPortName":"","inputNodeGuid":"2d7e41c4-8e90-4b61-879c-4b2e5b9486db","inputPortId":7001,"inputPortName":"输入"}</t>
+          <t>{"outputNodeGuid":"eae41233-d297-46fe-a6c8-0b5c876fbb2a","outputPortId":3004,"inputNodeGuid":"2d7e41c4-8e90-4b61-879c-4b2e5b9486db","inputPortId":7001}</t>
         </is>
       </c>
       <c r="H25"/>
@@ -1440,7 +1440,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>{"outputNodeGuid":"432ff1e3-b18d-476d-af80-d39ddc07402a","outputPortId":2715463,"legacyOutputPortName":"","inputNodeGuid":"3aafa9a5-4766-4204-91ab-d797aeb3c0e1","inputPortId":7001,"inputPortName":"输入"}</t>
+          <t>{"outputNodeGuid":"432ff1e3-b18d-476d-af80-d39ddc07402a","outputPortId":2715463,"inputNodeGuid":"3aafa9a5-4766-4204-91ab-d797aeb3c0e1","inputPortId":7001}</t>
         </is>
       </c>
       <c r="H26"/>
@@ -1482,7 +1482,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>{"outputNodeGuid":"356907e0-1488-4128-bfcc-7ff73cfc3330","outputPortId":1002,"legacyOutputPortName":"动画","inputNodeGuid":"432ff1e3-b18d-476d-af80-d39ddc07402a","inputPortId":7001,"inputPortName":"输入"}</t>
+          <t>{"outputNodeGuid":"356907e0-1488-4128-bfcc-7ff73cfc3330","outputPortId":1002,"inputNodeGuid":"432ff1e3-b18d-476d-af80-d39ddc07402a","inputPortId":7001}</t>
         </is>
       </c>
       <c r="H28"/>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>{"outputNodeGuid":"356907e0-1488-4128-bfcc-7ff73cfc3330","outputPortId":1004,"legacyOutputPortName":"冷却","inputNodeGuid":"c28fb88d-51b1-47b2-be59-859e0ac638e3","inputPortId":7001,"inputPortName":"输入"}</t>
+          <t>{"outputNodeGuid":"356907e0-1488-4128-bfcc-7ff73cfc3330","outputPortId":1004,"inputNodeGuid":"c28fb88d-51b1-47b2-be59-859e0ac638e3","inputPortId":7001}</t>
         </is>
       </c>
       <c r="H29"/>
@@ -1522,7 +1522,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>{"outputNodeGuid":"356907e0-1488-4128-bfcc-7ff73cfc3330","outputPortId":1003,"legacyOutputPortName":"消耗","inputNodeGuid":"9d6f459d-b588-4b64-843b-1b71e8f299ae","inputPortId":7001,"inputPortName":"输入"}</t>
+          <t>{"outputNodeGuid":"356907e0-1488-4128-bfcc-7ff73cfc3330","outputPortId":1003,"inputNodeGuid":"9d6f459d-b588-4b64-843b-1b71e8f299ae","inputPortId":7001}</t>
         </is>
       </c>
       <c r="H30"/>
@@ -1542,7 +1542,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>{"outputNodeGuid":"432ff1e3-b18d-476d-af80-d39ddc07402a","outputPortId":2315086,"legacyOutputPortName":"de0ba361-3aba-4ef0-bb07-9b418fcae591","inputNodeGuid":"90bacd9f-d882-4bba-aaa8-41ed993ac3ff","inputPortId":7001,"inputPortName":"输入"}</t>
+          <t>{"outputNodeGuid":"432ff1e3-b18d-476d-af80-d39ddc07402a","outputPortId":2315086,"inputNodeGuid":"90bacd9f-d882-4bba-aaa8-41ed993ac3ff","inputPortId":7001}</t>
         </is>
       </c>
       <c r="H31"/>
@@ -1562,7 +1562,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>{"outputNodeGuid":"90bacd9f-d882-4bba-aaa8-41ed993ac3ff","outputPortId":5001,"legacyOutputPortName":"碰撞时","inputNodeGuid":"eae41233-d297-46fe-a6c8-0b5c876fbb2a","inputPortId":7001,"inputPortName":"输入"}</t>
+          <t>{"outputNodeGuid":"90bacd9f-d882-4bba-aaa8-41ed993ac3ff","outputPortId":5001,"inputNodeGuid":"eae41233-d297-46fe-a6c8-0b5c876fbb2a","inputPortId":7001}</t>
         </is>
       </c>
       <c r="H32"/>
@@ -1582,7 +1582,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>{"outputNodeGuid":"eae41233-d297-46fe-a6c8-0b5c876fbb2a","outputPortId":3004,"legacyOutputPortName":"完成效果","inputNodeGuid":"2d7e41c4-8e90-4b61-879c-4b2e5b9486db","inputPortId":7001,"inputPortName":"输入"}</t>
+          <t>{"outputNodeGuid":"eae41233-d297-46fe-a6c8-0b5c876fbb2a","outputPortId":3004,"inputNodeGuid":"2d7e41c4-8e90-4b61-879c-4b2e5b9486db","inputPortId":7001}</t>
         </is>
       </c>
       <c r="H33"/>
@@ -1602,7 +1602,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>{"outputNodeGuid":"432ff1e3-b18d-476d-af80-d39ddc07402a","outputPortId":2715463,"legacyOutputPortName":"7ecf9fe6-7c5e-46ae-bade-7922214225e2","inputNodeGuid":"3aafa9a5-4766-4204-91ab-d797aeb3c0e1","inputPortId":7001,"inputPortName":"输入"}</t>
+          <t>{"outputNodeGuid":"432ff1e3-b18d-476d-af80-d39ddc07402a","outputPortId":2715463,"inputNodeGuid":"3aafa9a5-4766-4204-91ab-d797aeb3c0e1","inputPortId":7001}</t>
         </is>
       </c>
       <c r="H34"/>
@@ -1644,7 +1644,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>{"outputNodeGuid":"356907e0-1488-4128-bfcc-7ff73cfc3330","outputPortId":1002,"legacyOutputPortName":"动画","inputNodeGuid":"432ff1e3-b18d-476d-af80-d39ddc07402a","inputPortId":7001,"inputPortName":"输入"}</t>
+          <t>{"outputNodeGuid":"356907e0-1488-4128-bfcc-7ff73cfc3330","outputPortId":1002,"inputNodeGuid":"432ff1e3-b18d-476d-af80-d39ddc07402a","inputPortId":7001}</t>
         </is>
       </c>
       <c r="H36"/>
@@ -1664,7 +1664,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>{"outputNodeGuid":"356907e0-1488-4128-bfcc-7ff73cfc3330","outputPortId":1004,"legacyOutputPortName":"冷却","inputNodeGuid":"c28fb88d-51b1-47b2-be59-859e0ac638e3","inputPortId":7001,"inputPortName":"输入"}</t>
+          <t>{"outputNodeGuid":"356907e0-1488-4128-bfcc-7ff73cfc3330","outputPortId":1004,"inputNodeGuid":"c28fb88d-51b1-47b2-be59-859e0ac638e3","inputPortId":7001}</t>
         </is>
       </c>
       <c r="H37"/>
@@ -1684,7 +1684,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>{"outputNodeGuid":"356907e0-1488-4128-bfcc-7ff73cfc3330","outputPortId":1003,"legacyOutputPortName":"消耗","inputNodeGuid":"9d6f459d-b588-4b64-843b-1b71e8f299ae","inputPortId":7001,"inputPortName":"输入"}</t>
+          <t>{"outputNodeGuid":"356907e0-1488-4128-bfcc-7ff73cfc3330","outputPortId":1003,"inputNodeGuid":"9d6f459d-b588-4b64-843b-1b71e8f299ae","inputPortId":7001}</t>
         </is>
       </c>
       <c r="H38"/>
@@ -1704,7 +1704,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>{"outputNodeGuid":"432ff1e3-b18d-476d-af80-d39ddc07402a","outputPortId":2000539,"legacyOutputPortName":"f41c85e0-7f26-494e-9ffc-4a06c980f811","inputNodeGuid":"f73ba91e-a76b-456c-b19c-a5176809d5f5","inputPortId":7001,"inputPortName":"输入"}</t>
+          <t>{"outputNodeGuid":"432ff1e3-b18d-476d-af80-d39ddc07402a","outputPortId":2000539,"inputNodeGuid":"f73ba91e-a76b-456c-b19c-a5176809d5f5","inputPortId":7001}</t>
         </is>
       </c>
       <c r="H39"/>
@@ -1724,7 +1724,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>{"outputNodeGuid":"432ff1e3-b18d-476d-af80-d39ddc07402a","outputPortId":2315086,"legacyOutputPortName":"de0ba361-3aba-4ef0-bb07-9b418fcae591","inputNodeGuid":"e33ab94c-1496-4d6a-ba5e-1afd38bb0c30","inputPortId":7001,"inputPortName":"输入"}</t>
+          <t>{"outputNodeGuid":"432ff1e3-b18d-476d-af80-d39ddc07402a","outputPortId":2315086,"inputNodeGuid":"e33ab94c-1496-4d6a-ba5e-1afd38bb0c30","inputPortId":7001}</t>
         </is>
       </c>
       <c r="H40"/>
@@ -1744,7 +1744,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>{"outputNodeGuid":"432ff1e3-b18d-476d-af80-d39ddc07402a","outputPortId":2287012,"legacyOutputPortName":"8dea1941-c520-4f9a-aee0-40932c8542ef","inputNodeGuid":"cde57fb8-b693-4da8-a4a8-fd61e56c5dcd","inputPortId":7001,"inputPortName":"输入"}</t>
+          <t>{"outputNodeGuid":"432ff1e3-b18d-476d-af80-d39ddc07402a","outputPortId":2287012,"inputNodeGuid":"cde57fb8-b693-4da8-a4a8-fd61e56c5dcd","inputPortId":7001}</t>
         </is>
       </c>
       <c r="H41"/>
@@ -1764,7 +1764,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>{"outputNodeGuid":"e33ab94c-1496-4d6a-ba5e-1afd38bb0c30","outputPortId":4001,"legacyOutputPortName":"对每个目标","inputNodeGuid":"091ecddb-f80b-4c00-aa06-f9bc718618d2","inputPortId":7001,"inputPortName":"输入"}</t>
+          <t>{"outputNodeGuid":"e33ab94c-1496-4d6a-ba5e-1afd38bb0c30","outputPortId":4001,"inputNodeGuid":"091ecddb-f80b-4c00-aa06-f9bc718618d2","inputPortId":7001}</t>
         </is>
       </c>
       <c r="H42"/>
@@ -1806,7 +1806,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>{"outputNodeGuid":"356907e0-1488-4128-bfcc-7ff73cfc3330","outputPortId":1004,"legacyOutputPortName":"冷却","inputNodeGuid":"c28fb88d-51b1-47b2-be59-859e0ac638e3","inputPortId":7001,"inputPortName":"输入"}</t>
+          <t>{"outputNodeGuid":"356907e0-1488-4128-bfcc-7ff73cfc3330","outputPortId":1004,"inputNodeGuid":"c28fb88d-51b1-47b2-be59-859e0ac638e3","inputPortId":7001}</t>
         </is>
       </c>
       <c r="H44"/>
@@ -1826,7 +1826,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>{"outputNodeGuid":"356907e0-1488-4128-bfcc-7ff73cfc3330","outputPortId":1003,"legacyOutputPortName":"消耗","inputNodeGuid":"9d6f459d-b588-4b64-843b-1b71e8f299ae","inputPortId":7001,"inputPortName":"输入"}</t>
+          <t>{"outputNodeGuid":"356907e0-1488-4128-bfcc-7ff73cfc3330","outputPortId":1003,"inputNodeGuid":"9d6f459d-b588-4b64-843b-1b71e8f299ae","inputPortId":7001}</t>
         </is>
       </c>
       <c r="H45"/>
@@ -1846,7 +1846,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>{"outputNodeGuid":"356907e0-1488-4128-bfcc-7ff73cfc3330","outputPortId":1001,"legacyOutputPortName":"激活","inputNodeGuid":"5fb21a71-2fff-4477-b79b-4c1a8bc10f9a","inputPortId":7001,"inputPortName":"输入"}</t>
+          <t>{"outputNodeGuid":"356907e0-1488-4128-bfcc-7ff73cfc3330","outputPortId":1001,"inputNodeGuid":"5fb21a71-2fff-4477-b79b-4c1a8bc10f9a","inputPortId":7001}</t>
         </is>
       </c>
       <c r="H46"/>
@@ -1866,7 +1866,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>{"outputNodeGuid":"5fb21a71-2fff-4477-b79b-4c1a8bc10f9a","outputPortId":3001,"legacyOutputPortName":"初始效果","inputNodeGuid":"cde57fb8-b693-4da8-a4a8-fd61e56c5dcd","inputPortId":7001,"inputPortName":"输入"}</t>
+          <t>{"outputNodeGuid":"5fb21a71-2fff-4477-b79b-4c1a8bc10f9a","outputPortId":3001,"inputNodeGuid":"cde57fb8-b693-4da8-a4a8-fd61e56c5dcd","inputPortId":7001}</t>
         </is>
       </c>
       <c r="H47"/>
@@ -1886,7 +1886,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>{"outputNodeGuid":"5fb21a71-2fff-4477-b79b-4c1a8bc10f9a","outputPortId":3004,"legacyOutputPortName":"完成效果","inputNodeGuid":"011aad56-e96c-41eb-9d85-e793d74a40bb","inputPortId":7001,"inputPortName":"输入"}</t>
+          <t>{"outputNodeGuid":"5fb21a71-2fff-4477-b79b-4c1a8bc10f9a","outputPortId":3004,"inputNodeGuid":"011aad56-e96c-41eb-9d85-e793d74a40bb","inputPortId":7001}</t>
         </is>
       </c>
       <c r="H48"/>
@@ -1906,7 +1906,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>{"outputNodeGuid":"5fb21a71-2fff-4477-b79b-4c1a8bc10f9a","outputPortId":3004,"legacyOutputPortName":"完成效果","inputNodeGuid":"becb4d53-8a9e-4dc0-95a3-618d1e79ecc7","inputPortId":7001,"inputPortName":"输入"}</t>
+          <t>{"outputNodeGuid":"5fb21a71-2fff-4477-b79b-4c1a8bc10f9a","outputPortId":3004,"inputNodeGuid":"becb4d53-8a9e-4dc0-95a3-618d1e79ecc7","inputPortId":7001}</t>
         </is>
       </c>
       <c r="H49"/>
@@ -1948,7 +1948,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>{"outputNodeGuid":"356907e0-1488-4128-bfcc-7ff73cfc3330","outputPortId":1002,"legacyOutputPortName":"动画","inputNodeGuid":"432ff1e3-b18d-476d-af80-d39ddc07402a","inputPortId":7001,"inputPortName":"输入"}</t>
+          <t>{"outputNodeGuid":"356907e0-1488-4128-bfcc-7ff73cfc3330","outputPortId":1002,"inputNodeGuid":"432ff1e3-b18d-476d-af80-d39ddc07402a","inputPortId":7001}</t>
         </is>
       </c>
       <c r="H51"/>
@@ -1968,7 +1968,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>{"outputNodeGuid":"356907e0-1488-4128-bfcc-7ff73cfc3330","outputPortId":1004,"legacyOutputPortName":"冷却","inputNodeGuid":"c28fb88d-51b1-47b2-be59-859e0ac638e3","inputPortId":7001,"inputPortName":"输入"}</t>
+          <t>{"outputNodeGuid":"356907e0-1488-4128-bfcc-7ff73cfc3330","outputPortId":1004,"inputNodeGuid":"c28fb88d-51b1-47b2-be59-859e0ac638e3","inputPortId":7001}</t>
         </is>
       </c>
       <c r="H52"/>
@@ -1988,7 +1988,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>{"outputNodeGuid":"356907e0-1488-4128-bfcc-7ff73cfc3330","outputPortId":1003,"legacyOutputPortName":"消耗","inputNodeGuid":"9d6f459d-b588-4b64-843b-1b71e8f299ae","inputPortId":7001,"inputPortName":"输入"}</t>
+          <t>{"outputNodeGuid":"356907e0-1488-4128-bfcc-7ff73cfc3330","outputPortId":1003,"inputNodeGuid":"9d6f459d-b588-4b64-843b-1b71e8f299ae","inputPortId":7001}</t>
         </is>
       </c>
       <c r="H53"/>
@@ -2008,7 +2008,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>{"outputNodeGuid":"e33ab94c-1496-4d6a-ba5e-1afd38bb0c30","outputPortId":4001,"legacyOutputPortName":"对每个目标","inputNodeGuid":"cb1df36f-5729-423e-9d1a-287db5a433f0","inputPortId":7001,"inputPortName":"输入"}</t>
+          <t>{"outputNodeGuid":"e33ab94c-1496-4d6a-ba5e-1afd38bb0c30","outputPortId":4001,"inputNodeGuid":"cb1df36f-5729-423e-9d1a-287db5a433f0","inputPortId":7001}</t>
         </is>
       </c>
       <c r="H54"/>
@@ -2028,7 +2028,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>{"outputNodeGuid":"cb1df36f-5729-423e-9d1a-287db5a433f0","outputPortId":3001,"legacyOutputPortName":"初始效果","inputNodeGuid":"93ec5a43-cc34-4e4a-acb3-39da2f2c3010","inputPortId":7001,"inputPortName":"输入"}</t>
+          <t>{"outputNodeGuid":"cb1df36f-5729-423e-9d1a-287db5a433f0","outputPortId":3001,"inputNodeGuid":"93ec5a43-cc34-4e4a-acb3-39da2f2c3010","inputPortId":7001}</t>
         </is>
       </c>
       <c r="H55"/>
@@ -2048,7 +2048,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>{"outputNodeGuid":"432ff1e3-b18d-476d-af80-d39ddc07402a","outputPortId":2000539,"legacyOutputPortName":"f41c85e0-7f26-494e-9ffc-4a06c980f811","inputNodeGuid":"f73ba91e-a76b-456c-b19c-a5176809d5f5","inputPortId":7001,"inputPortName":"输入"}</t>
+          <t>{"outputNodeGuid":"432ff1e3-b18d-476d-af80-d39ddc07402a","outputPortId":2000539,"inputNodeGuid":"f73ba91e-a76b-456c-b19c-a5176809d5f5","inputPortId":7001}</t>
         </is>
       </c>
       <c r="H56"/>
@@ -2068,7 +2068,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>{"outputNodeGuid":"432ff1e3-b18d-476d-af80-d39ddc07402a","outputPortId":2315086,"legacyOutputPortName":"de0ba361-3aba-4ef0-bb07-9b418fcae591","inputNodeGuid":"e33ab94c-1496-4d6a-ba5e-1afd38bb0c30","inputPortId":7001,"inputPortName":"输入"}</t>
+          <t>{"outputNodeGuid":"432ff1e3-b18d-476d-af80-d39ddc07402a","outputPortId":2315086,"inputNodeGuid":"e33ab94c-1496-4d6a-ba5e-1afd38bb0c30","inputPortId":7001}</t>
         </is>
       </c>
       <c r="H57"/>
@@ -2088,7 +2088,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>{"outputNodeGuid":"432ff1e3-b18d-476d-af80-d39ddc07402a","outputPortId":2287012,"legacyOutputPortName":"8dea1941-c520-4f9a-aee0-40932c8542ef","inputNodeGuid":"cde57fb8-b693-4da8-a4a8-fd61e56c5dcd","inputPortId":7001,"inputPortName":"输入"}</t>
+          <t>{"outputNodeGuid":"432ff1e3-b18d-476d-af80-d39ddc07402a","outputPortId":2287012,"inputNodeGuid":"cde57fb8-b693-4da8-a4a8-fd61e56c5dcd","inputPortId":7001}</t>
         </is>
       </c>
       <c r="H58"/>
@@ -2130,7 +2130,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>{"outputNodeGuid":"356907e0-1488-4128-bfcc-7ff73cfc3330","outputPortId":1002,"legacyOutputPortName":"动画","inputNodeGuid":"432ff1e3-b18d-476d-af80-d39ddc07402a","inputPortId":7001,"inputPortName":"输入"}</t>
+          <t>{"outputNodeGuid":"356907e0-1488-4128-bfcc-7ff73cfc3330","outputPortId":1002,"inputNodeGuid":"432ff1e3-b18d-476d-af80-d39ddc07402a","inputPortId":7001}</t>
         </is>
       </c>
       <c r="H60"/>
@@ -2150,7 +2150,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>{"outputNodeGuid":"356907e0-1488-4128-bfcc-7ff73cfc3330","outputPortId":1004,"legacyOutputPortName":"冷却","inputNodeGuid":"c28fb88d-51b1-47b2-be59-859e0ac638e3","inputPortId":7001,"inputPortName":"输入"}</t>
+          <t>{"outputNodeGuid":"356907e0-1488-4128-bfcc-7ff73cfc3330","outputPortId":1004,"inputNodeGuid":"c28fb88d-51b1-47b2-be59-859e0ac638e3","inputPortId":7001}</t>
         </is>
       </c>
       <c r="H61"/>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>{"outputNodeGuid":"356907e0-1488-4128-bfcc-7ff73cfc3330","outputPortId":1003,"legacyOutputPortName":"消耗","inputNodeGuid":"9d6f459d-b588-4b64-843b-1b71e8f299ae","inputPortId":7001,"inputPortName":"输入"}</t>
+          <t>{"outputNodeGuid":"356907e0-1488-4128-bfcc-7ff73cfc3330","outputPortId":1003,"inputNodeGuid":"9d6f459d-b588-4b64-843b-1b71e8f299ae","inputPortId":7001}</t>
         </is>
       </c>
       <c r="H62"/>
@@ -2190,7 +2190,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>{"outputNodeGuid":"432ff1e3-b18d-476d-af80-d39ddc07402a","outputPortId":2000539,"legacyOutputPortName":"f41c85e0-7f26-494e-9ffc-4a06c980f811","inputNodeGuid":"f73ba91e-a76b-456c-b19c-a5176809d5f5","inputPortId":7001,"inputPortName":"输入"}</t>
+          <t>{"outputNodeGuid":"432ff1e3-b18d-476d-af80-d39ddc07402a","outputPortId":2000539,"inputNodeGuid":"f73ba91e-a76b-456c-b19c-a5176809d5f5","inputPortId":7001}</t>
         </is>
       </c>
       <c r="H63"/>
@@ -2210,7 +2210,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>{"outputNodeGuid":"356907e0-1488-4128-bfcc-7ff73cfc3330","outputPortId":1001,"legacyOutputPortName":"激活","inputNodeGuid":"632c75e2-152b-4376-8e9e-62c0e74f92d0","inputPortId":7001,"inputPortName":"输入"}</t>
+          <t>{"outputNodeGuid":"356907e0-1488-4128-bfcc-7ff73cfc3330","outputPortId":1001,"inputNodeGuid":"632c75e2-152b-4376-8e9e-62c0e74f92d0","inputPortId":7001}</t>
         </is>
       </c>
       <c r="H64"/>
@@ -2252,7 +2252,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>{"outputNodeGuid":"432ff1e3-b18d-476d-af80-d39ddc07402a","outputPortId":2287012,"legacyOutputPortName":"","inputNodeGuid":"cde57fb8-b693-4da8-a4a8-fd61e56c5dcd","inputPortId":7001,"inputPortName":"输入"}</t>
+          <t>{"outputNodeGuid":"432ff1e3-b18d-476d-af80-d39ddc07402a","outputPortId":2287012,"inputNodeGuid":"cde57fb8-b693-4da8-a4a8-fd61e56c5dcd","inputPortId":7001}</t>
         </is>
       </c>
       <c r="H66"/>
@@ -2272,7 +2272,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>{"outputNodeGuid":"356907e0-1488-4128-bfcc-7ff73cfc3330","outputPortId":1002,"legacyOutputPortName":"","inputNodeGuid":"432ff1e3-b18d-476d-af80-d39ddc07402a","inputPortId":7001,"inputPortName":"输入"}</t>
+          <t>{"outputNodeGuid":"356907e0-1488-4128-bfcc-7ff73cfc3330","outputPortId":1002,"inputNodeGuid":"432ff1e3-b18d-476d-af80-d39ddc07402a","inputPortId":7001}</t>
         </is>
       </c>
       <c r="H67"/>
@@ -2292,7 +2292,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>{"outputNodeGuid":"356907e0-1488-4128-bfcc-7ff73cfc3330","outputPortId":1004,"legacyOutputPortName":"","inputNodeGuid":"c28fb88d-51b1-47b2-be59-859e0ac638e3","inputPortId":7001,"inputPortName":"输入"}</t>
+          <t>{"outputNodeGuid":"356907e0-1488-4128-bfcc-7ff73cfc3330","outputPortId":1004,"inputNodeGuid":"c28fb88d-51b1-47b2-be59-859e0ac638e3","inputPortId":7001}</t>
         </is>
       </c>
       <c r="H68"/>
@@ -2312,7 +2312,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>{"outputNodeGuid":"356907e0-1488-4128-bfcc-7ff73cfc3330","outputPortId":1003,"legacyOutputPortName":"","inputNodeGuid":"9d6f459d-b588-4b64-843b-1b71e8f299ae","inputPortId":7001,"inputPortName":"输入"}</t>
+          <t>{"outputNodeGuid":"356907e0-1488-4128-bfcc-7ff73cfc3330","outputPortId":1003,"inputNodeGuid":"9d6f459d-b588-4b64-843b-1b71e8f299ae","inputPortId":7001}</t>
         </is>
       </c>
       <c r="H69"/>
@@ -2332,7 +2332,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>{"outputNodeGuid":"432ff1e3-b18d-476d-af80-d39ddc07402a","outputPortId":2315086,"legacyOutputPortName":"","inputNodeGuid":"e33ab94c-1496-4d6a-ba5e-1afd38bb0c30","inputPortId":7001,"inputPortName":"输入"}</t>
+          <t>{"outputNodeGuid":"432ff1e3-b18d-476d-af80-d39ddc07402a","outputPortId":2315086,"inputNodeGuid":"e33ab94c-1496-4d6a-ba5e-1afd38bb0c30","inputPortId":7001}</t>
         </is>
       </c>
       <c r="H70"/>
@@ -2352,7 +2352,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>{"outputNodeGuid":"e33ab94c-1496-4d6a-ba5e-1afd38bb0c30","outputPortId":4001,"legacyOutputPortName":"","inputNodeGuid":"f8947676-1084-4228-b991-1509cc7fe851","inputPortId":7001,"inputPortName":"输入"}</t>
+          <t>{"outputNodeGuid":"e33ab94c-1496-4d6a-ba5e-1afd38bb0c30","outputPortId":4001,"inputNodeGuid":"f8947676-1084-4228-b991-1509cc7fe851","inputPortId":7001}</t>
         </is>
       </c>
       <c r="H71"/>
@@ -2372,7 +2372,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>{"outputNodeGuid":"f8947676-1084-4228-b991-1509cc7fe851","outputPortId":3004,"legacyOutputPortName":"","inputNodeGuid":"c353e286-8ef0-460a-b917-887f2aeb390a","inputPortId":7001,"inputPortName":"输入"}</t>
+          <t>{"outputNodeGuid":"f8947676-1084-4228-b991-1509cc7fe851","outputPortId":3004,"inputNodeGuid":"c353e286-8ef0-460a-b917-887f2aeb390a","inputPortId":7001}</t>
         </is>
       </c>
       <c r="H72"/>
@@ -2392,7 +2392,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>{"outputNodeGuid":"432ff1e3-b18d-476d-af80-d39ddc07402a","outputPortId":2649436,"legacyOutputPortName":"","inputNodeGuid":"2cfdacd2-0186-49dd-b177-4eb8c0ad87bd","inputPortId":7001,"inputPortName":"输入"}</t>
+          <t>{"outputNodeGuid":"432ff1e3-b18d-476d-af80-d39ddc07402a","outputPortId":2649436,"inputNodeGuid":"2cfdacd2-0186-49dd-b177-4eb8c0ad87bd","inputPortId":7001}</t>
         </is>
       </c>
       <c r="H73"/>
@@ -2434,7 +2434,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>{"outputNodeGuid":"356907e0-1488-4128-bfcc-7ff73cfc3330","outputPortId":1002,"legacyOutputPortName":"动画","inputNodeGuid":"432ff1e3-b18d-476d-af80-d39ddc07402a","inputPortId":7001,"inputPortName":"输入"}</t>
+          <t>{"outputNodeGuid":"356907e0-1488-4128-bfcc-7ff73cfc3330","outputPortId":1002,"inputNodeGuid":"432ff1e3-b18d-476d-af80-d39ddc07402a","inputPortId":7001}</t>
         </is>
       </c>
       <c r="H75"/>
@@ -2454,7 +2454,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>{"outputNodeGuid":"356907e0-1488-4128-bfcc-7ff73cfc3330","outputPortId":1004,"legacyOutputPortName":"冷却","inputNodeGuid":"c28fb88d-51b1-47b2-be59-859e0ac638e3","inputPortId":7001,"inputPortName":"输入"}</t>
+          <t>{"outputNodeGuid":"356907e0-1488-4128-bfcc-7ff73cfc3330","outputPortId":1004,"inputNodeGuid":"c28fb88d-51b1-47b2-be59-859e0ac638e3","inputPortId":7001}</t>
         </is>
       </c>
       <c r="H76"/>
@@ -2474,7 +2474,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>{"outputNodeGuid":"356907e0-1488-4128-bfcc-7ff73cfc3330","outputPortId":1003,"legacyOutputPortName":"消耗","inputNodeGuid":"9d6f459d-b588-4b64-843b-1b71e8f299ae","inputPortId":7001,"inputPortName":"输入"}</t>
+          <t>{"outputNodeGuid":"356907e0-1488-4128-bfcc-7ff73cfc3330","outputPortId":1003,"inputNodeGuid":"9d6f459d-b588-4b64-843b-1b71e8f299ae","inputPortId":7001}</t>
         </is>
       </c>
       <c r="H77"/>
@@ -2494,7 +2494,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>{"outputNodeGuid":"f8947676-1084-4228-b991-1509cc7fe851","outputPortId":3004,"legacyOutputPortName":"完成效果","inputNodeGuid":"c353e286-8ef0-460a-b917-887f2aeb390a","inputPortId":7001,"inputPortName":"输入"}</t>
+          <t>{"outputNodeGuid":"f8947676-1084-4228-b991-1509cc7fe851","outputPortId":3004,"inputNodeGuid":"c353e286-8ef0-460a-b917-887f2aeb390a","inputPortId":7001}</t>
         </is>
       </c>
       <c r="H78"/>
@@ -2514,7 +2514,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>{"outputNodeGuid":"ce857360-de7e-4457-b348-9c124ce98879","outputPortId":5001,"legacyOutputPortName":"碰撞时","inputNodeGuid":"f8947676-1084-4228-b991-1509cc7fe851","inputPortId":7001,"inputPortName":"输入"}</t>
+          <t>{"outputNodeGuid":"ce857360-de7e-4457-b348-9c124ce98879","outputPortId":5001,"inputNodeGuid":"f8947676-1084-4228-b991-1509cc7fe851","inputPortId":7001}</t>
         </is>
       </c>
       <c r="H79"/>
@@ -2534,7 +2534,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>{"outputNodeGuid":"9a695e91-e218-425e-82ed-1e157bf1b014","outputPortId":5001,"legacyOutputPortName":"碰撞时","inputNodeGuid":"f8947676-1084-4228-b991-1509cc7fe851","inputPortId":7001,"inputPortName":"输入"}</t>
+          <t>{"outputNodeGuid":"9a695e91-e218-425e-82ed-1e157bf1b014","outputPortId":5001,"inputNodeGuid":"f8947676-1084-4228-b991-1509cc7fe851","inputPortId":7001}</t>
         </is>
       </c>
       <c r="H80"/>
@@ -2554,7 +2554,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>{"outputNodeGuid":"d897a922-5756-42cf-ac65-90a48c1e5a17","outputPortId":5001,"legacyOutputPortName":"碰撞时","inputNodeGuid":"f8947676-1084-4228-b991-1509cc7fe851","inputPortId":7001,"inputPortName":"输入"}</t>
+          <t>{"outputNodeGuid":"d897a922-5756-42cf-ac65-90a48c1e5a17","outputPortId":5001,"inputNodeGuid":"f8947676-1084-4228-b991-1509cc7fe851","inputPortId":7001}</t>
         </is>
       </c>
       <c r="H81"/>
@@ -2574,7 +2574,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>{"outputNodeGuid":"432ff1e3-b18d-476d-af80-d39ddc07402a","outputPortId":2649436,"legacyOutputPortName":"84e238a8-5baf-470e-829f-186695064945","inputNodeGuid":"2cfdacd2-0186-49dd-b177-4eb8c0ad87bd","inputPortId":7001,"inputPortName":"输入"}</t>
+          <t>{"outputNodeGuid":"432ff1e3-b18d-476d-af80-d39ddc07402a","outputPortId":2649436,"inputNodeGuid":"2cfdacd2-0186-49dd-b177-4eb8c0ad87bd","inputPortId":7001}</t>
         </is>
       </c>
       <c r="H82"/>
@@ -2594,7 +2594,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>{"outputNodeGuid":"432ff1e3-b18d-476d-af80-d39ddc07402a","outputPortId":2315086,"legacyOutputPortName":"de0ba361-3aba-4ef0-bb07-9b418fcae591","inputNodeGuid":"ce857360-de7e-4457-b348-9c124ce98879","inputPortId":7001,"inputPortName":"输入"}</t>
+          <t>{"outputNodeGuid":"432ff1e3-b18d-476d-af80-d39ddc07402a","outputPortId":2315086,"inputNodeGuid":"ce857360-de7e-4457-b348-9c124ce98879","inputPortId":7001}</t>
         </is>
       </c>
       <c r="H83"/>
@@ -2614,7 +2614,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>{"outputNodeGuid":"432ff1e3-b18d-476d-af80-d39ddc07402a","outputPortId":2315086,"legacyOutputPortName":"de0ba361-3aba-4ef0-bb07-9b418fcae591","inputNodeGuid":"9a695e91-e218-425e-82ed-1e157bf1b014","inputPortId":7001,"inputPortName":"输入"}</t>
+          <t>{"outputNodeGuid":"432ff1e3-b18d-476d-af80-d39ddc07402a","outputPortId":2315086,"inputNodeGuid":"9a695e91-e218-425e-82ed-1e157bf1b014","inputPortId":7001}</t>
         </is>
       </c>
       <c r="H84"/>
@@ -2628,7 +2628,7 @@
       <c r="F85"/>
       <c r="G85" t="inlineStr">
         <is>
-          <t>{"outputNodeGuid":"432ff1e3-b18d-476d-af80-d39ddc07402a","outputPortId":2315086,"legacyOutputPortName":"de0ba361-3aba-4ef0-bb07-9b418fcae591","inputNodeGuid":"d897a922-5756-42cf-ac65-90a48c1e5a17","inputPortId":7001,"inputPortName":"输入"}</t>
+          <t>{"outputNodeGuid":"432ff1e3-b18d-476d-af80-d39ddc07402a","outputPortId":2315086,"inputNodeGuid":"d897a922-5756-42cf-ac65-90a48c1e5a17","inputPortId":7001}</t>
         </is>
       </c>
       <c r="H85"/>
@@ -2654,7 +2654,7 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>{"outputNodeGuid":"356907e0-1488-4128-bfcc-7ff73cfc3330","outputPortId":1002,"legacyOutputPortName":"动画","inputNodeGuid":"432ff1e3-b18d-476d-af80-d39ddc07402a","inputPortId":7001,"inputPortName":"输入"}</t>
+          <t>{"outputNodeGuid":"356907e0-1488-4128-bfcc-7ff73cfc3330","outputPortId":1002,"inputNodeGuid":"432ff1e3-b18d-476d-af80-d39ddc07402a","inputPortId":7001}</t>
         </is>
       </c>
       <c r="H86"/>
@@ -2674,7 +2674,7 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>{"outputNodeGuid":"356907e0-1488-4128-bfcc-7ff73cfc3330","outputPortId":1004,"legacyOutputPortName":"冷却","inputNodeGuid":"c28fb88d-51b1-47b2-be59-859e0ac638e3","inputPortId":7001,"inputPortName":"输入"}</t>
+          <t>{"outputNodeGuid":"356907e0-1488-4128-bfcc-7ff73cfc3330","outputPortId":1004,"inputNodeGuid":"c28fb88d-51b1-47b2-be59-859e0ac638e3","inputPortId":7001}</t>
         </is>
       </c>
       <c r="H87"/>
@@ -2694,7 +2694,7 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>{"outputNodeGuid":"356907e0-1488-4128-bfcc-7ff73cfc3330","outputPortId":1003,"legacyOutputPortName":"消耗","inputNodeGuid":"9d6f459d-b588-4b64-843b-1b71e8f299ae","inputPortId":7001,"inputPortName":"输入"}</t>
+          <t>{"outputNodeGuid":"356907e0-1488-4128-bfcc-7ff73cfc3330","outputPortId":1003,"inputNodeGuid":"9d6f459d-b588-4b64-843b-1b71e8f299ae","inputPortId":7001}</t>
         </is>
       </c>
       <c r="H88"/>
@@ -2714,7 +2714,7 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>{"outputNodeGuid":"432ff1e3-b18d-476d-af80-d39ddc07402a","outputPortId":2000539,"legacyOutputPortName":"f41c85e0-7f26-494e-9ffc-4a06c980f811","inputNodeGuid":"f73ba91e-a76b-456c-b19c-a5176809d5f5","inputPortId":7001,"inputPortName":"输入"}</t>
+          <t>{"outputNodeGuid":"432ff1e3-b18d-476d-af80-d39ddc07402a","outputPortId":2000539,"inputNodeGuid":"f73ba91e-a76b-456c-b19c-a5176809d5f5","inputPortId":7001}</t>
         </is>
       </c>
       <c r="H89"/>
@@ -2734,7 +2734,7 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>{"outputNodeGuid":"432ff1e3-b18d-476d-af80-d39ddc07402a","outputPortId":2315086,"legacyOutputPortName":"de0ba361-3aba-4ef0-bb07-9b418fcae591","inputNodeGuid":"e33ab94c-1496-4d6a-ba5e-1afd38bb0c30","inputPortId":7001,"inputPortName":"输入"}</t>
+          <t>{"outputNodeGuid":"432ff1e3-b18d-476d-af80-d39ddc07402a","outputPortId":2315086,"inputNodeGuid":"e33ab94c-1496-4d6a-ba5e-1afd38bb0c30","inputPortId":7001}</t>
         </is>
       </c>
       <c r="H90"/>
@@ -2754,7 +2754,7 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>{"outputNodeGuid":"432ff1e3-b18d-476d-af80-d39ddc07402a","outputPortId":2287012,"legacyOutputPortName":"8dea1941-c520-4f9a-aee0-40932c8542ef","inputNodeGuid":"cde57fb8-b693-4da8-a4a8-fd61e56c5dcd","inputPortId":7001,"inputPortName":"输入"}</t>
+          <t>{"outputNodeGuid":"432ff1e3-b18d-476d-af80-d39ddc07402a","outputPortId":2287012,"inputNodeGuid":"cde57fb8-b693-4da8-a4a8-fd61e56c5dcd","inputPortId":7001}</t>
         </is>
       </c>
       <c r="H91"/>
@@ -2774,7 +2774,7 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>{"outputNodeGuid":"e33ab94c-1496-4d6a-ba5e-1afd38bb0c30","outputPortId":4001,"legacyOutputPortName":"对每个目标","inputNodeGuid":"091ecddb-f80b-4c00-aa06-f9bc718618d2","inputPortId":7001,"inputPortName":"输入"}</t>
+          <t>{"outputNodeGuid":"e33ab94c-1496-4d6a-ba5e-1afd38bb0c30","outputPortId":4001,"inputNodeGuid":"091ecddb-f80b-4c00-aa06-f9bc718618d2","inputPortId":7001}</t>
         </is>
       </c>
       <c r="H92"/>
@@ -2816,7 +2816,7 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>{"outputNodeGuid":"356907e0-1488-4128-bfcc-7ff73cfc3330","outputPortId":1002,"legacyOutputPortName":"动画","inputNodeGuid":"432ff1e3-b18d-476d-af80-d39ddc07402a","inputPortId":7001,"inputPortName":"输入"}</t>
+          <t>{"outputNodeGuid":"356907e0-1488-4128-bfcc-7ff73cfc3330","outputPortId":1002,"inputNodeGuid":"432ff1e3-b18d-476d-af80-d39ddc07402a","inputPortId":7001}</t>
         </is>
       </c>
       <c r="H94"/>
@@ -2836,7 +2836,7 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>{"outputNodeGuid":"356907e0-1488-4128-bfcc-7ff73cfc3330","outputPortId":1004,"legacyOutputPortName":"冷却","inputNodeGuid":"c28fb88d-51b1-47b2-be59-859e0ac638e3","inputPortId":7001,"inputPortName":"输入"}</t>
+          <t>{"outputNodeGuid":"356907e0-1488-4128-bfcc-7ff73cfc3330","outputPortId":1004,"inputNodeGuid":"c28fb88d-51b1-47b2-be59-859e0ac638e3","inputPortId":7001}</t>
         </is>
       </c>
       <c r="H95"/>
@@ -2856,7 +2856,7 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>{"outputNodeGuid":"356907e0-1488-4128-bfcc-7ff73cfc3330","outputPortId":1003,"legacyOutputPortName":"消耗","inputNodeGuid":"9d6f459d-b588-4b64-843b-1b71e8f299ae","inputPortId":7001,"inputPortName":"输入"}</t>
+          <t>{"outputNodeGuid":"356907e0-1488-4128-bfcc-7ff73cfc3330","outputPortId":1003,"inputNodeGuid":"9d6f459d-b588-4b64-843b-1b71e8f299ae","inputPortId":7001}</t>
         </is>
       </c>
       <c r="H96"/>
@@ -2876,7 +2876,7 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>{"outputNodeGuid":"356907e0-1488-4128-bfcc-7ff73cfc3330","outputPortId":1001,"legacyOutputPortName":"激活","inputNodeGuid":"d8847c3e-459e-4589-a96b-37ebb5ec458b","inputPortId":7001,"inputPortName":"输入"}</t>
+          <t>{"outputNodeGuid":"356907e0-1488-4128-bfcc-7ff73cfc3330","outputPortId":1001,"inputNodeGuid":"d8847c3e-459e-4589-a96b-37ebb5ec458b","inputPortId":7001}</t>
         </is>
       </c>
       <c r="H97"/>
@@ -2896,7 +2896,7 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>{"outputNodeGuid":"d8847c3e-459e-4589-a96b-37ebb5ec458b","outputPortId":3002,"legacyOutputPortName":"每周期执行","inputNodeGuid":"e33ab94c-1496-4d6a-ba5e-1afd38bb0c30","inputPortId":7001,"inputPortName":"输入"}</t>
+          <t>{"outputNodeGuid":"d8847c3e-459e-4589-a96b-37ebb5ec458b","outputPortId":3002,"inputNodeGuid":"e33ab94c-1496-4d6a-ba5e-1afd38bb0c30","inputPortId":7001}</t>
         </is>
       </c>
       <c r="H98"/>
@@ -2916,7 +2916,7 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>{"outputNodeGuid":"e33ab94c-1496-4d6a-ba5e-1afd38bb0c30","outputPortId":4001,"legacyOutputPortName":"对每个目标","inputNodeGuid":"a32d1135-94db-4f81-95ba-9d5f105ef8d0","inputPortId":7001,"inputPortName":"输入"}</t>
+          <t>{"outputNodeGuid":"e33ab94c-1496-4d6a-ba5e-1afd38bb0c30","outputPortId":4001,"inputNodeGuid":"a32d1135-94db-4f81-95ba-9d5f105ef8d0","inputPortId":7001}</t>
         </is>
       </c>
       <c r="H99"/>
@@ -2936,7 +2936,7 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>{"outputNodeGuid":"a32d1135-94db-4f81-95ba-9d5f105ef8d0","outputPortId":3004,"legacyOutputPortName":"完成效果","inputNodeGuid":"764289ea-065e-4f48-afc0-0f6963d18d57","inputPortId":7001,"inputPortName":"输入"}</t>
+          <t>{"outputNodeGuid":"a32d1135-94db-4f81-95ba-9d5f105ef8d0","outputPortId":3004,"inputNodeGuid":"764289ea-065e-4f48-afc0-0f6963d18d57","inputPortId":7001}</t>
         </is>
       </c>
       <c r="H100"/>
@@ -2956,7 +2956,7 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>{"outputNodeGuid":"432ff1e3-b18d-476d-af80-d39ddc07402a","outputPortId":2287012,"legacyOutputPortName":"8dea1941-c520-4f9a-aee0-40932c8542ef","inputNodeGuid":"cde57fb8-b693-4da8-a4a8-fd61e56c5dcd","inputPortId":7001,"inputPortName":"输入"}</t>
+          <t>{"outputNodeGuid":"432ff1e3-b18d-476d-af80-d39ddc07402a","outputPortId":2287012,"inputNodeGuid":"cde57fb8-b693-4da8-a4a8-fd61e56c5dcd","inputPortId":7001}</t>
         </is>
       </c>
       <c r="H101"/>
@@ -2976,7 +2976,7 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>{"outputNodeGuid":"432ff1e3-b18d-476d-af80-d39ddc07402a","outputPortId":2000539,"legacyOutputPortName":"f41c85e0-7f26-494e-9ffc-4a06c980f811","inputNodeGuid":"f73ba91e-a76b-456c-b19c-a5176809d5f5","inputPortId":7001,"inputPortName":"输入"}</t>
+          <t>{"outputNodeGuid":"432ff1e3-b18d-476d-af80-d39ddc07402a","outputPortId":2000539,"inputNodeGuid":"f73ba91e-a76b-456c-b19c-a5176809d5f5","inputPortId":7001}</t>
         </is>
       </c>
       <c r="H102"/>

--- a/Design/Excel/ET/Datas/Game/SkillGraph.xlsx
+++ b/Design/Excel/ET/Datas/Game/SkillGraph.xlsx
@@ -1391,11 +1391,11 @@
       <c r="C24"/>
       <c r="D24"/>
       <c r="E24">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>{"guid":"90bacd9f-d882-4bba-aaa8-41ed993ac3ff","nodeType":8,"position":{"x":-401.33331298828125,"y":-1826.666748046875},"targetType":2,"assetTags":{"_tags":[]},"grantedTags":{"_tags":[]},"applicationRequiredTags":{"_tags":[]},"applicationImmunityTags":{"_tags":[]},"removeGameEffectsWithTags":{"_tags":[]},"durationType":2,"duration":"0","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"_tags":[]},"cancelOnAbilityEnd":false,"launchPositionSource":0,"launchBindingName":"center","targetPositionSource":1,"targetBindingName":"center","projectileTargetType":0,"flyOver":false,"offsetAngle":0.0,"curveHeight":0.0,"projectilePrefab":null,"projectilePrefabPath":"Assets/Res/Prefab/Effect/ef_fashi_gandian_buff.prefab","speed":3.0,"maxDistance":10.0,"collisionRadius":0.5,"isPiercing":false,"maxPierceCount":1,"collisionTargetTags":{"_tags":[]},"collisionExcludeTags":{"_tags":[]},"isBouncing":false,"bounceTargetMode":0,"maxBounceCount":3,"bounceSearchRadius":10.0,"canBounceToSameTarget":false,"bounceAngleOffset":0.0}</t>
+          <t>{"guid":"356907e0-1488-4128-bfcc-7ff73cfc3330","nodeType":0,"position":{"x":-880.6666259765625,"y":-1851.3333740234375},"targetType":1,"skillId":7001,"assetTags":{"_tags":[]},"cancelAbilitiesWithTags":{"_tags":[]},"blockAbilitiesWithTags":{"_tags":[]},"activationOwnedTags":{"_tags":[]},"activationRequiredTags":{"_tags":[]},"activationBlockedTags":{"_tags":[{"_name":"CD.Wind","_hashCode":1982736573,"_shortName":"Wind","_ancestorHashCodes":[-1137859925],"_ancestorNames":["CD"]}]},"ongoingBlockedTags":{"_tags":[{"_name":"Buff.DeBuff.Stun","_hashCode":1791562953,"_shortName":"Stun","_ancestorHashCodes":[937056111,321157895],"_ancestorNames":["Buff","Buff.DeBuff"]}]},"eventOutputPorts":[]}</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -1411,11 +1411,11 @@
       <c r="C25"/>
       <c r="D25"/>
       <c r="E25">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>{"guid":"c28fb88d-51b1-47b2-be59-859e0ac638e3","nodeType":10,"position":{"x":-1220.6666259765625,"y":-1747.3333740234375},"targetType":1,"assetTags":{"_tags":[]},"grantedTags":{"_tags":[{"_name":"CD.FireCircle","_hashCode":522143731,"_shortName":"FireCircle","_ancestorHashCodes":[-1137859925],"_ancestorNames":["CD"]}]},"applicationRequiredTags":{"_tags":[]},"applicationImmunityTags":{"_tags":[]},"removeGameEffectsWithTags":{"_tags":[]},"durationType":1,"duration":"1","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"_tags":[]},"cancelOnAbilityEnd":false,"cooldownType":0,"maxCharges":2,"chargeTime":"10"}</t>
+          <t>{"guid":"eae41233-d297-46fe-a6c8-0b5c876fbb2a","nodeType":1,"position":{"x":46.66668701171875,"y":-1808.666748046875},"targetType":0,"assetTags":{"_tags":[]},"grantedTags":{"_tags":[]},"applicationRequiredTags":{"_tags":[]},"applicationImmunityTags":{"_tags":[]},"removeGameEffectsWithTags":{"_tags":[]},"durationType":0,"duration":"0","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"_tags":[]},"cancelOnAbilityEnd":true,"damageType":0,"damageSourceType":0,"damageFixedValue":10.0,"damageFormula":"","damageMMCType":0,"damageSetByCallerKey":"","damageMMCCaptureAttribute":200,"damageMMCAttributeSource":0,"damageMMCCoefficient":1.0,"damageMMCUseSnapshot":true,"damageMultiplyByStackCount":false,"damageCalculationType":0,"enableHitKnockback":true,"knockbackDistance":1.0,"knockbackSpeed":12.0}</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -1431,11 +1431,11 @@
       <c r="C26"/>
       <c r="D26"/>
       <c r="E26">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>{"guid":"356907e0-1488-4128-bfcc-7ff73cfc3330","nodeType":0,"position":{"x":-880.6666259765625,"y":-1851.3333740234375},"targetType":1,"skillId":7001,"assetTags":{"_tags":[]},"cancelAbilitiesWithTags":{"_tags":[]},"blockAbilitiesWithTags":{"_tags":[]},"activationOwnedTags":{"_tags":[]},"activationRequiredTags":{"_tags":[]},"activationBlockedTags":{"_tags":[{"_name":"CD.Wind","_hashCode":1982736573,"_shortName":"Wind","_ancestorHashCodes":[-1137859925],"_ancestorNames":["CD"]}]},"ongoingBlockedTags":{"_tags":[{"_name":"Buff.DeBuff.Stun","_hashCode":1791562953,"_shortName":"Stun","_ancestorHashCodes":[937056111,321157895],"_ancestorNames":["Buff","Buff.DeBuff"]}]},"eventOutputPorts":[]}</t>
+          <t>{"guid":"90bacd9f-d882-4bba-aaa8-41ed993ac3ff","nodeType":8,"position":{"x":-401.33331298828125,"y":-1826.666748046875},"targetType":2,"assetTags":{"_tags":[]},"grantedTags":{"_tags":[]},"applicationRequiredTags":{"_tags":[]},"applicationImmunityTags":{"_tags":[]},"removeGameEffectsWithTags":{"_tags":[]},"durationType":2,"duration":"0","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"_tags":[]},"cancelOnAbilityEnd":false,"launchPositionSource":0,"launchBindingName":"center","targetPositionSource":1,"targetBindingName":"center","projectileTargetType":0,"flyOver":false,"offsetAngle":0.0,"curveHeight":0.0,"projectilePrefab":null,"projectilePrefabPath":"Assets/Res/Prefab/Effect/ef_fashi_gandian_buff.prefab","speed":3.0,"maxDistance":10.0,"collisionRadius":0.5,"isPiercing":false,"maxPierceCount":1,"collisionTargetTags":{"_tags":[]},"collisionExcludeTags":{"_tags":[]},"isBouncing":true,"bounceTargetMode":1,"maxBounceCount":3,"bounceSearchRadius":10.0,"canBounceToSameTarget":false,"excludeSourceCamp":true,"bounceAngleOffset":0.0}</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -1451,11 +1451,11 @@
       <c r="C27"/>
       <c r="D27"/>
       <c r="E27">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>{"guid":"eae41233-d297-46fe-a6c8-0b5c876fbb2a","nodeType":1,"position":{"x":46.66668701171875,"y":-1808.666748046875},"targetType":0,"assetTags":{"_tags":[]},"grantedTags":{"_tags":[]},"applicationRequiredTags":{"_tags":[]},"applicationImmunityTags":{"_tags":[]},"removeGameEffectsWithTags":{"_tags":[]},"durationType":0,"duration":"0","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"_tags":[]},"cancelOnAbilityEnd":true,"damageType":0,"damageSourceType":0,"damageFixedValue":10.0,"damageFormula":"","damageMMCType":0,"damageSetByCallerKey":"","damageMMCCaptureAttribute":200,"damageMMCAttributeSource":0,"damageMMCCoefficient":1.0,"damageMMCUseSnapshot":true,"damageMultiplyByStackCount":false,"damageCalculationType":0,"enableHitKnockback":true,"knockbackDistance":1.0,"knockbackSpeed":12.0}</t>
+          <t>{"guid":"c28fb88d-51b1-47b2-be59-859e0ac638e3","nodeType":10,"position":{"x":-1220.6666259765625,"y":-1747.3333740234375},"targetType":1,"assetTags":{"_tags":[]},"grantedTags":{"_tags":[{"_name":"CD.FireCircle","_hashCode":522143731,"_shortName":"FireCircle","_ancestorHashCodes":[-1137859925],"_ancestorNames":["CD"]}]},"applicationRequiredTags":{"_tags":[]},"applicationImmunityTags":{"_tags":[]},"removeGameEffectsWithTags":{"_tags":[]},"durationType":1,"duration":"3","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"_tags":[]},"cancelOnAbilityEnd":false,"cooldownType":0,"maxCharges":2,"chargeTime":"10"}</t>
         </is>
       </c>
       <c r="G27"/>
@@ -1617,7 +1617,7 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>{"guid":"90bacd9f-d882-4bba-aaa8-41ed993ac3ff","nodeType":8,"position":{"x":-400.66665649414063,"y":-1836.666748046875},"targetType":2,"assetTags":{"_tags":[]},"grantedTags":{"_tags":[]},"applicationRequiredTags":{"_tags":[]},"applicationImmunityTags":{"_tags":[]},"removeGameEffectsWithTags":{"_tags":[]},"durationType":2,"duration":"0","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"_tags":[]},"cancelOnAbilityEnd":false,"launchPositionSource":0,"launchBindingName":"center","targetPositionSource":1,"targetBindingName":"center","projectileTargetType":0,"flyOver":false,"offsetAngle":0.0,"curveHeight":0.0,"projectilePrefab":null,"projectilePrefabPath":"Assets/Res/Prefab/Effect/ef_fashi_gandian_buff.prefab","speed":3.0,"maxDistance":10.0,"collisionRadius":0.5,"isPiercing":false,"maxPierceCount":1,"collisionTargetTags":{"_tags":[]},"collisionExcludeTags":{"_tags":[]},"isBouncing":true,"bounceTargetMode":0,"maxBounceCount":2,"bounceSearchRadius":10.0,"canBounceToSameTarget":false,"bounceAngleOffset":50.0}</t>
+          <t>{"guid":"90bacd9f-d882-4bba-aaa8-41ed993ac3ff","nodeType":8,"position":{"x":-400.66665649414063,"y":-1836.666748046875},"targetType":2,"assetTags":{"_tags":[]},"grantedTags":{"_tags":[]},"applicationRequiredTags":{"_tags":[]},"applicationImmunityTags":{"_tags":[]},"removeGameEffectsWithTags":{"_tags":[]},"durationType":2,"duration":"0","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"_tags":[]},"cancelOnAbilityEnd":false,"launchPositionSource":0,"launchBindingName":"center","targetPositionSource":1,"targetBindingName":"center","projectileTargetType":0,"flyOver":false,"offsetAngle":0.0,"curveHeight":0.0,"projectilePrefab":null,"projectilePrefabPath":"Assets/Res/Prefab/Effect/ef_fashi_gandian_buff.prefab","speed":3.0,"maxDistance":10.0,"collisionRadius":0.5,"isPiercing":false,"maxPierceCount":1,"collisionTargetTags":{"_tags":[]},"collisionExcludeTags":{"_tags":[]},"isBouncing":true,"bounceTargetMode":0,"maxBounceCount":2,"bounceSearchRadius":10.0,"canBounceToSameTarget":false,"excludeSourceCamp":true,"bounceAngleOffset":50.0}</t>
         </is>
       </c>
       <c r="G35"/>
@@ -2569,7 +2569,7 @@
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>{"guid":"ce857360-de7e-4457-b348-9c124ce98879","nodeType":8,"position":{"x":1040.666748046875,"y":-2305.333251953125},"targetType":2,"assetTags":{"_tags":[]},"grantedTags":{"_tags":[]},"applicationRequiredTags":{"_tags":[]},"applicationImmunityTags":{"_tags":[]},"removeGameEffectsWithTags":{"_tags":[]},"durationType":2,"duration":"0","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"_tags":[]},"cancelOnAbilityEnd":false,"launchPositionSource":0,"launchBindingName":"center","targetPositionSource":1,"targetBindingName":"center","projectileTargetType":0,"flyOver":true,"offsetAngle":30.0,"curveHeight":0.0,"projectilePrefab":null,"projectilePrefabPath":"Assets/Res/Prefab/Effect/ef_fashi_huoyandan01.prefab","speed":10.0,"maxDistance":10.0,"collisionRadius":0.5,"isPiercing":false,"maxPierceCount":1,"collisionTargetTags":{"_tags":[]},"collisionExcludeTags":{"_tags":[]},"isBouncing":false,"bounceTargetMode":0,"maxBounceCount":3,"bounceSearchRadius":10.0,"canBounceToSameTarget":false,"bounceAngleOffset":0.0}</t>
+          <t>{"guid":"ce857360-de7e-4457-b348-9c124ce98879","nodeType":8,"position":{"x":1040.666748046875,"y":-2305.333251953125},"targetType":2,"assetTags":{"_tags":[]},"grantedTags":{"_tags":[]},"applicationRequiredTags":{"_tags":[]},"applicationImmunityTags":{"_tags":[]},"removeGameEffectsWithTags":{"_tags":[]},"durationType":2,"duration":"0","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"_tags":[]},"cancelOnAbilityEnd":false,"launchPositionSource":0,"launchBindingName":"center","targetPositionSource":1,"targetBindingName":"center","projectileTargetType":0,"flyOver":true,"offsetAngle":30.0,"curveHeight":0.0,"projectilePrefab":null,"projectilePrefabPath":"Assets/Res/Prefab/Effect/ef_fashi_huoyandan01.prefab","speed":10.0,"maxDistance":10.0,"collisionRadius":0.5,"isPiercing":false,"maxPierceCount":1,"collisionTargetTags":{"_tags":[]},"collisionExcludeTags":{"_tags":[]},"isBouncing":false,"bounceTargetMode":0,"maxBounceCount":3,"bounceSearchRadius":10.0,"canBounceToSameTarget":false,"excludeSourceCamp":true,"bounceAngleOffset":0.0}</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
@@ -2589,7 +2589,7 @@
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>{"guid":"9a695e91-e218-425e-82ed-1e157bf1b014","nodeType":8,"position":{"x":1022.666748046875,"y":-2131.333251953125},"targetType":2,"assetTags":{"_tags":[]},"grantedTags":{"_tags":[]},"applicationRequiredTags":{"_tags":[]},"applicationImmunityTags":{"_tags":[]},"removeGameEffectsWithTags":{"_tags":[]},"durationType":2,"duration":"0","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"_tags":[]},"cancelOnAbilityEnd":false,"launchPositionSource":0,"launchBindingName":"center","targetPositionSource":1,"targetBindingName":"center","projectileTargetType":0,"flyOver":true,"offsetAngle":0.0,"curveHeight":0.0,"projectilePrefab":null,"projectilePrefabPath":"Assets/Res/Prefab/Effect/ef_fashi_huoyandan01.prefab","speed":10.0,"maxDistance":10.0,"collisionRadius":0.5,"isPiercing":false,"maxPierceCount":1,"collisionTargetTags":{"_tags":[]},"collisionExcludeTags":{"_tags":[]},"isBouncing":false,"bounceTargetMode":0,"maxBounceCount":3,"bounceSearchRadius":10.0,"canBounceToSameTarget":false,"bounceAngleOffset":0.0}</t>
+          <t>{"guid":"9a695e91-e218-425e-82ed-1e157bf1b014","nodeType":8,"position":{"x":1022.666748046875,"y":-2131.333251953125},"targetType":2,"assetTags":{"_tags":[]},"grantedTags":{"_tags":[]},"applicationRequiredTags":{"_tags":[]},"applicationImmunityTags":{"_tags":[]},"removeGameEffectsWithTags":{"_tags":[]},"durationType":2,"duration":"0","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"_tags":[]},"cancelOnAbilityEnd":false,"launchPositionSource":0,"launchBindingName":"center","targetPositionSource":1,"targetBindingName":"center","projectileTargetType":0,"flyOver":true,"offsetAngle":0.0,"curveHeight":0.0,"projectilePrefab":null,"projectilePrefabPath":"Assets/Res/Prefab/Effect/ef_fashi_huoyandan01.prefab","speed":10.0,"maxDistance":10.0,"collisionRadius":0.5,"isPiercing":false,"maxPierceCount":1,"collisionTargetTags":{"_tags":[]},"collisionExcludeTags":{"_tags":[]},"isBouncing":false,"bounceTargetMode":0,"maxBounceCount":3,"bounceSearchRadius":10.0,"canBounceToSameTarget":false,"excludeSourceCamp":true,"bounceAngleOffset":0.0}</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
@@ -2609,7 +2609,7 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>{"guid":"d897a922-5756-42cf-ac65-90a48c1e5a17","nodeType":8,"position":{"x":1022.666748046875,"y":-1978.0},"targetType":2,"assetTags":{"_tags":[]},"grantedTags":{"_tags":[]},"applicationRequiredTags":{"_tags":[]},"applicationImmunityTags":{"_tags":[]},"removeGameEffectsWithTags":{"_tags":[]},"durationType":2,"duration":"0","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"_tags":[]},"cancelOnAbilityEnd":false,"launchPositionSource":0,"launchBindingName":"center","targetPositionSource":1,"targetBindingName":"center","projectileTargetType":0,"flyOver":true,"offsetAngle":-30.0,"curveHeight":0.0,"projectilePrefab":null,"projectilePrefabPath":"Assets/Res/Prefab/Effect/ef_fashi_huoyandan01.prefab","speed":10.0,"maxDistance":10.0,"collisionRadius":0.5,"isPiercing":false,"maxPierceCount":1,"collisionTargetTags":{"_tags":[]},"collisionExcludeTags":{"_tags":[]},"isBouncing":false,"bounceTargetMode":0,"maxBounceCount":3,"bounceSearchRadius":10.0,"canBounceToSameTarget":false,"bounceAngleOffset":0.0}</t>
+          <t>{"guid":"d897a922-5756-42cf-ac65-90a48c1e5a17","nodeType":8,"position":{"x":1022.666748046875,"y":-1978.0},"targetType":2,"assetTags":{"_tags":[]},"grantedTags":{"_tags":[]},"applicationRequiredTags":{"_tags":[]},"applicationImmunityTags":{"_tags":[]},"removeGameEffectsWithTags":{"_tags":[]},"durationType":2,"duration":"0","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"_tags":[]},"cancelOnAbilityEnd":false,"launchPositionSource":0,"launchBindingName":"center","targetPositionSource":1,"targetBindingName":"center","projectileTargetType":0,"flyOver":true,"offsetAngle":-30.0,"curveHeight":0.0,"projectilePrefab":null,"projectilePrefabPath":"Assets/Res/Prefab/Effect/ef_fashi_huoyandan01.prefab","speed":10.0,"maxDistance":10.0,"collisionRadius":0.5,"isPiercing":false,"maxPierceCount":1,"collisionTargetTags":{"_tags":[]},"collisionExcludeTags":{"_tags":[]},"isBouncing":false,"bounceTargetMode":0,"maxBounceCount":3,"bounceSearchRadius":10.0,"canBounceToSameTarget":false,"excludeSourceCamp":true,"bounceAngleOffset":0.0}</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">

--- a/Design/Excel/ET/Datas/Game/SkillGraph.xlsx
+++ b/Design/Excel/ET/Datas/Game/SkillGraph.xlsx
@@ -1091,7 +1091,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>{"guid":"d5809887-df6e-4604-bd09-36cef191ce83","nodeType":0,"position":{"x":210.66668701171875,"y":114.66667175292969},"targetType":1,"skillId":2001,"assetTags":{"_tags":[]},"cancelAbilitiesWithTags":{"_tags":[]},"blockAbilitiesWithTags":{"_tags":[]},"activationOwnedTags":{"_tags":[]},"activationRequiredTags":{"_tags":[]},"activationBlockedTags":{"_tags":[]},"ongoingBlockedTags":{"_tags":[]},"eventOutputPorts":[{"eventType":2,"portIdValue":1103,"legacyPortId":"","customEventTag":""}]}</t>
+          <t>{"guid":"d5809887-df6e-4604-bd09-36cef191ce83","nodeType":0,"position":{"x":210.66668701171875,"y":114.66667175292969},"targetType":1,"skillId":2001,"assetTags":{"_tags":[]},"cancelAbilitiesWithTags":{"_tags":[]},"blockAbilitiesWithTags":{"_tags":[]},"activationOwnedTags":{"_tags":[]},"activationRequiredTags":{"_tags":[]},"activationBlockedTags":{"_tags":[]},"ongoingBlockedTags":{"_tags":[]},"eventOutputPorts":[{"eventType":2,"customEventTag":"","PortId":1103}]}</t>
         </is>
       </c>
       <c r="G9"/>
@@ -1395,7 +1395,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>{"guid":"356907e0-1488-4128-bfcc-7ff73cfc3330","nodeType":0,"position":{"x":-880.6666259765625,"y":-1851.3333740234375},"targetType":1,"skillId":7001,"assetTags":{"_tags":[]},"cancelAbilitiesWithTags":{"_tags":[]},"blockAbilitiesWithTags":{"_tags":[]},"activationOwnedTags":{"_tags":[]},"activationRequiredTags":{"_tags":[]},"activationBlockedTags":{"_tags":[{"_name":"CD.Wind","_hashCode":1982736573,"_shortName":"Wind","_ancestorHashCodes":[-1137859925],"_ancestorNames":["CD"]}]},"ongoingBlockedTags":{"_tags":[{"_name":"Buff.DeBuff.Stun","_hashCode":1791562953,"_shortName":"Stun","_ancestorHashCodes":[937056111,321157895],"_ancestorNames":["Buff","Buff.DeBuff"]}]},"eventOutputPorts":[]}</t>
+          <t>{"guid":"356907e0-1488-4128-bfcc-7ff73cfc3330","nodeType":0,"position":{"x":-880.6666259765625,"y":-1851.3333740234375},"targetType":1,"skillId":7001,"assetTags":{"_tags":[]},"cancelAbilitiesWithTags":{"_tags":[]},"blockAbilitiesWithTags":{"_tags":[]},"activationOwnedTags":{"_tags":[]},"activationRequiredTags":{"_tags":[]},"activationBlockedTags":{"_tags":[{"_name":"CD.FireCircle","_hashCode":522143731,"_shortName":"FireCircle","_ancestorHashCodes":[-1137859925],"_ancestorNames":["CD"]}]},"ongoingBlockedTags":{"_tags":[{"_name":"Buff.DeBuff.Stun","_hashCode":1791562953,"_shortName":"Stun","_ancestorHashCodes":[937056111,321157895],"_ancestorNames":["Buff","Buff.DeBuff"]}]},"eventOutputPorts":[]}</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -1801,7 +1801,7 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>{"guid":"9d6f459d-b588-4b64-843b-1b71e8f299ae","nodeType":3,"position":{"x":-1186.4000244140625,"y":-2019.199951171875},"targetType":1,"assetTags":{"_tags":[]},"grantedTags":{"_tags":[]},"applicationRequiredTags":{"_tags":[]},"applicationImmunityTags":{"_tags":[]},"removeGameEffectsWithTags":{"_tags":[]},"durationType":0,"duration":"0","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[{"attrType":100,"operation":0,"magnitudeSourceType":0,"fixedValue":10.0,"formula":"","mmcType":0,"setByCallerKey":"","mmcCaptureAttribute":200,"mmcAttributeSource":0,"mmcCoefficient":1.0,"mmcUseSnapshot":true}],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"_tags":[]},"cancelOnAbilityEnd":true}</t>
+          <t>{"guid":"9d6f459d-b588-4b64-843b-1b71e8f299ae","nodeType":3,"position":{"x":-1186.6666259765625,"y":-2019.3333740234375},"targetType":1,"assetTags":{"_tags":[]},"grantedTags":{"_tags":[]},"applicationRequiredTags":{"_tags":[]},"applicationImmunityTags":{"_tags":[]},"removeGameEffectsWithTags":{"_tags":[]},"durationType":0,"duration":"0","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[{"attrType":100,"operation":0,"magnitudeSourceType":0,"fixedValue":10.0,"formula":"","mmcType":0,"setByCallerKey":"","mmcCaptureAttribute":200,"mmcAttributeSource":0,"mmcCoefficient":1.0,"mmcUseSnapshot":true}],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"_tags":[]},"cancelOnAbilityEnd":true}</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -1821,7 +1821,7 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>{"guid":"5fb21a71-2fff-4477-b79b-4c1a8bc10f9a","nodeType":2,"position":{"x":-571.20001220703125,"y":-1987.199951171875},"targetType":1,"assetTags":{"_tags":[]},"grantedTags":{"_tags":[]},"applicationRequiredTags":{"_tags":[]},"applicationImmunityTags":{"_tags":[]},"removeGameEffectsWithTags":{"_tags":[]},"durationType":0,"duration":"0","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"_tags":[]},"cancelOnAbilityEnd":false,"healSourceType":0,"healFixedValue":10.0,"healFormula":"","healMMCType":0,"healSetByCallerKey":"","healMMCCaptureAttribute":202,"healMMCAttributeSource":0,"healMMCCoefficient":1.0,"healMMCUseSnapshot":true,"healMultiplyByStackCount":false,"healCalculationType":0}</t>
+          <t>{"guid":"5fb21a71-2fff-4477-b79b-4c1a8bc10f9a","nodeType":2,"position":{"x":-571.33331298828125,"y":-1987.3333740234375},"targetType":1,"assetTags":{"_tags":[]},"grantedTags":{"_tags":[]},"applicationRequiredTags":{"_tags":[]},"applicationImmunityTags":{"_tags":[]},"removeGameEffectsWithTags":{"_tags":[]},"durationType":0,"duration":"0","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"_tags":[]},"cancelOnAbilityEnd":false,"healSourceType":0,"healFixedValue":10.0,"healFormula":"","healMMCType":0,"healSetByCallerKey":"","healMMCCaptureAttribute":202,"healMMCAttributeSource":0,"healMMCCoefficient":1.0,"healMMCUseSnapshot":true,"healMultiplyByStackCount":false,"healCalculationType":0}</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -1841,7 +1841,7 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>{"guid":"011aad56-e96c-41eb-9d85-e793d74a40bb","nodeType":7,"position":{"x":-333.60000610351563,"y":-1780.0},"targetType":1,"endType":0}</t>
+          <t>{"guid":"011aad56-e96c-41eb-9d85-e793d74a40bb","nodeType":7,"position":{"x":-333.33331298828125,"y":-1780.0},"targetType":1,"endType":0}</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -1861,7 +1861,7 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>{"guid":"c28fb88d-51b1-47b2-be59-859e0ac638e3","nodeType":10,"position":{"x":-1223.199951171875,"y":-1826.4000244140625},"targetType":1,"assetTags":{"_tags":[]},"grantedTags":{"_tags":[{"_name":"CD.RecBlood","_hashCode":1163914435,"_shortName":"回血","_ancestorHashCodes":[-1137859925],"_ancestorNames":["CD"]}]},"applicationRequiredTags":{"_tags":[]},"applicationImmunityTags":{"_tags":[]},"removeGameEffectsWithTags":{"_tags":[]},"durationType":1,"duration":"3","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"_tags":[]},"cancelOnAbilityEnd":false,"cooldownType":0,"maxCharges":2,"chargeTime":"10"}</t>
+          <t>{"guid":"c28fb88d-51b1-47b2-be59-859e0ac638e3","nodeType":10,"position":{"x":-1223.3333740234375,"y":-1826.666748046875},"targetType":1,"assetTags":{"_tags":[]},"grantedTags":{"_tags":[{"_name":"CD.RecBlood","_hashCode":1163914435,"_shortName":"回血","_ancestorHashCodes":[-1137859925],"_ancestorNames":["CD"]}]},"applicationRequiredTags":{"_tags":[]},"applicationImmunityTags":{"_tags":[]},"removeGameEffectsWithTags":{"_tags":[]},"durationType":1,"duration":"3","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"_tags":[]},"cancelOnAbilityEnd":false,"cooldownType":0,"maxCharges":2,"chargeTime":"10"}</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -1881,7 +1881,7 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>{"guid":"356907e0-1488-4128-bfcc-7ff73cfc3330","nodeType":0,"position":{"x":-902.4000244140625,"y":-1844.0},"targetType":1,"skillId":1007,"assetTags":{"_tags":[]},"cancelAbilitiesWithTags":{"_tags":[]},"blockAbilitiesWithTags":{"_tags":[]},"activationOwnedTags":{"_tags":[]},"activationRequiredTags":{"_tags":[]},"activationBlockedTags":{"_tags":[{"_name":"CD.RecBlood","_hashCode":1163914435,"_shortName":"回血","_ancestorHashCodes":[-1137859925],"_ancestorNames":["CD"]}]},"ongoingBlockedTags":{"_tags":[]},"eventOutputPorts":[]}</t>
+          <t>{"guid":"356907e0-1488-4128-bfcc-7ff73cfc3330","nodeType":0,"position":{"x":-902.6666259765625,"y":-1844.0},"targetType":1,"skillId":1007,"assetTags":{"_tags":[]},"cancelAbilitiesWithTags":{"_tags":[]},"blockAbilitiesWithTags":{"_tags":[]},"activationOwnedTags":{"_tags":[]},"activationRequiredTags":{"_tags":[]},"activationBlockedTags":{"_tags":[{"_name":"CD.RecBlood","_hashCode":1163914435,"_shortName":"回血","_ancestorHashCodes":[-1137859925],"_ancestorNames":["CD"]}]},"ongoingBlockedTags":{"_tags":[]},"eventOutputPorts":[]}</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>{"guid":"becb4d53-8a9e-4dc0-95a3-618d1e79ecc7","nodeType":14,"position":{"x":-313.60000610351563,"y":-1951.199951171875},"targetType":1,"requiredTags":{"_tags":[]},"immunityTags":{"_tags":[]},"destroyWithNode":false,"positionSource":2,"positionBindingName":"head","textType":1,"fixedText":"","contextDataKey":"Heal","textColor":{"r":0.0,"g":1.0,"b":0.10971927642822266,"a":1.0},"criticalColor":{"r":1.0,"g":0.5,"b":0.0,"a":1.0},"missColor":{"r":0.5,"g":0.5,"b":0.5,"a":1.0},"fontSize":45.0,"criticalFontSize":60.0,"duration":1.5,"offset":{"x":0.0,"y":0.0},"moveDirection":{"x":0.0,"y":1.0}}</t>
+          <t>{"guid":"becb4d53-8a9e-4dc0-95a3-618d1e79ecc7","nodeType":14,"position":{"x":-313.33331298828125,"y":-1951.3333740234375},"targetType":1,"requiredTags":{"_tags":[]},"immunityTags":{"_tags":[]},"destroyWithNode":false,"positionSource":2,"positionBindingName":"head","textType":1,"fixedText":"","contextDataKey":"Heal","textColor":{"r":0.0,"g":1.0,"b":0.10971927642822266,"a":1.0},"criticalColor":{"r":1.0,"g":0.5,"b":0.0,"a":1.0},"missColor":{"r":0.5,"g":0.5,"b":0.5,"a":1.0},"fontSize":45.0,"criticalFontSize":60.0,"duration":1.5,"offset":{"x":0.0,"y":0.0},"moveDirection":{"x":0.0,"y":1.0}}</t>
         </is>
       </c>
       <c r="G50"/>
@@ -2243,11 +2243,11 @@
       </c>
       <c r="D66"/>
       <c r="E66">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>{"guid":"2cfdacd2-0186-49dd-b177-4eb8c0ad87bd","nodeType":7,"position":{"x":731.3333740234375,"y":-2080.0},"targetType":1,"endType":0}</t>
+          <t>{"guid":"c28fb88d-51b1-47b2-be59-859e0ac638e3","nodeType":10,"position":{"x":-1130.6666259765625,"y":-2232.0},"targetType":1,"assetTags":{"_tags":[]},"grantedTags":{"_tags":[{"_name":"CD.Sweep","_hashCode":-303359587,"_shortName":"Sweep","_ancestorHashCodes":[-1137859925],"_ancestorNames":["CD"]}]},"applicationRequiredTags":{"_tags":[]},"applicationImmunityTags":{"_tags":[]},"removeGameEffectsWithTags":{"_tags":[]},"durationType":1,"duration":"1","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"_tags":[]},"cancelOnAbilityEnd":false,"cooldownType":0,"maxCharges":2,"chargeTime":"10"}</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
@@ -2263,11 +2263,11 @@
       <c r="C67"/>
       <c r="D67"/>
       <c r="E67">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>{"guid":"e33ab94c-1496-4d6a-ba5e-1afd38bb0c30","nodeType":4,"position":{"x":731.3333740234375,"y":-2344.0},"targetType":1,"searchShapeType":1,"searchLineType":0,"positionSource":0,"positionBindingName":"center","searchCircleRadius":5.0,"searchSectorRadius":2.0,"searchSectorAngle":180.0,"searchLineDirectionOffsetAngle":0.0,"searchLineDirectionWidth":1.0,"searchLineDirectionLength":10.0,"lineStartPositionSource":0,"lineStartBindingName":"","lineEndPositionSource":1,"lineEndBindingName":"","searchLineBetweenWidth":1.0,"searchLineAbsoluteAngle":0.0,"searchLineAbsoluteWidth":1.0,"searchLineAbsoluteLength":10.0,"maxTargets":999,"searchTargetTags":{"_tags":[{"_name":"unitType.monster","_hashCode":-2021655864,"_shortName":"monster","_ancestorHashCodes":[1600484460],"_ancestorNames":["unitType"]}]},"searchExcludeTags":{"_tags":[]}}</t>
+          <t>{"guid":"cde57fb8-b693-4da8-a4a8-fd61e56c5dcd","nodeType":12,"position":{"x":731.3333740234375,"y":-2488.66650390625},"targetType":1,"requiredTags":{"_tags":[]},"immunityTags":{"_tags":[]},"destroyWithNode":false,"positionSource":0,"particlePrefab":null,"particlePrefabPath":"Assets/Res/Prefab/Effect/ef_Zhanshi_attack_02.prefab","particleBindingName":"down","particleOffset":{"x":0.0,"y":0.0,"z":0.0},"particleScale":{"x":1.0,"y":1.0,"z":1.0},"attachToTarget":false,"particleLoop":false}</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
@@ -2283,11 +2283,11 @@
       <c r="C68"/>
       <c r="D68"/>
       <c r="E68">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>{"guid":"cde57fb8-b693-4da8-a4a8-fd61e56c5dcd","nodeType":12,"position":{"x":731.3333740234375,"y":-2488.66650390625},"targetType":1,"requiredTags":{"_tags":[]},"immunityTags":{"_tags":[]},"destroyWithNode":false,"positionSource":0,"particlePrefab":null,"particlePrefabPath":"Assets/Res/Prefab/Effect/ef_Zhanshi_attack_02.prefab","particleBindingName":"down","particleOffset":{"x":0.0,"y":0.0,"z":0.0},"particleScale":{"x":1.0,"y":1.0,"z":1.0},"attachToTarget":false,"particleLoop":false}</t>
+          <t>{"guid":"e33ab94c-1496-4d6a-ba5e-1afd38bb0c30","nodeType":4,"position":{"x":731.3333740234375,"y":-2344.0},"targetType":1,"searchShapeType":1,"searchLineType":0,"positionSource":0,"positionBindingName":"center","searchCircleRadius":5.0,"searchSectorRadius":2.0,"searchSectorAngle":180.0,"searchLineDirectionOffsetAngle":0.0,"searchLineDirectionWidth":1.0,"searchLineDirectionLength":10.0,"lineStartPositionSource":0,"lineStartBindingName":"","lineEndPositionSource":1,"lineEndBindingName":"","searchLineBetweenWidth":1.0,"searchLineAbsoluteAngle":0.0,"searchLineAbsoluteWidth":1.0,"searchLineAbsoluteLength":10.0,"maxTargets":999,"searchTargetTags":{"_tags":[{"_name":"unitType.monster","_hashCode":-2021655864,"_shortName":"monster","_ancestorHashCodes":[1600484460],"_ancestorNames":["unitType"]}]},"searchExcludeTags":{"_tags":[]}}</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
@@ -2307,7 +2307,7 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>{"guid":"c353e286-8ef0-460a-b917-887f2aeb390a","nodeType":14,"position":{"x":1190.0,"y":-2344.0},"targetType":1,"requiredTags":{"_tags":[]},"immunityTags":{"_tags":[]},"destroyWithNode":false,"positionSource":2,"positionBindingName":"head","textType":0,"fixedText":"","contextDataKey":"DamageResult","textColor":{"r":1.0,"g":0.0,"b":0.0,"a":1.0},"criticalColor":{"r":1.0,"g":0.5,"b":0.0,"a":1.0},"missColor":{"r":0.5,"g":0.5,"b":0.5,"a":1.0},"fontSize":45.0,"criticalFontSize":60.0,"duration":1.5,"offset":{"x":0.0,"y":0.0},"moveDirection":{"x":0.0,"y":1.0}}</t>
+          <t>{"guid":"c353e286-8ef0-460a-b917-887f2aeb390a","nodeType":14,"position":{"x":1213.3333740234375,"y":-2354.0},"targetType":1,"requiredTags":{"_tags":[]},"immunityTags":{"_tags":[]},"destroyWithNode":false,"positionSource":2,"positionBindingName":"head","textType":0,"fixedText":"","contextDataKey":"DamageResult","textColor":{"r":1.0,"g":0.0,"b":0.0,"a":1.0},"criticalColor":{"r":1.0,"g":0.5,"b":0.0,"a":1.0},"missColor":{"r":0.5,"g":0.5,"b":0.5,"a":1.0},"fontSize":45.0,"criticalFontSize":60.0,"duration":1.5,"offset":{"x":0.0,"y":0.0},"moveDirection":{"x":0.0,"y":1.0}}</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
@@ -2327,7 +2327,7 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>{"guid":"9d6f459d-b588-4b64-843b-1b71e8f299ae","nodeType":3,"position":{"x":-1130.6666259765625,"y":-2479.333251953125},"targetType":1,"assetTags":{"_tags":[]},"grantedTags":{"_tags":[]},"applicationRequiredTags":{"_tags":[]},"applicationImmunityTags":{"_tags":[]},"removeGameEffectsWithTags":{"_tags":[]},"durationType":0,"duration":"0","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[{"attrType":100,"operation":0,"magnitudeSourceType":0,"fixedValue":-10.0,"formula":"","mmcType":0,"setByCallerKey":"","mmcCaptureAttribute":200,"mmcAttributeSource":0,"mmcCoefficient":1.0,"mmcUseSnapshot":true}],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"_tags":[]},"cancelOnAbilityEnd":true}</t>
+          <t>{"guid":"9d6f459d-b588-4b64-843b-1b71e8f299ae","nodeType":3,"position":{"x":-1130.6666259765625,"y":-2479.333251953125},"targetType":1,"assetTags":{"_tags":[]},"grantedTags":{"_tags":[]},"applicationRequiredTags":{"_tags":[]},"applicationImmunityTags":{"_tags":[]},"removeGameEffectsWithTags":{"_tags":[]},"durationType":0,"duration":"0","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[{"attrType":1003,"operation":0,"magnitudeSourceType":0,"fixedValue":-10.0,"formula":"","mmcType":0,"setByCallerKey":"","mmcCaptureAttribute":200,"mmcAttributeSource":0,"mmcCoefficient":1.0,"mmcUseSnapshot":true}],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"_tags":[]},"cancelOnAbilityEnd":true}</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
@@ -2343,11 +2343,11 @@
       <c r="C71"/>
       <c r="D71"/>
       <c r="E71">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>{"guid":"c28fb88d-51b1-47b2-be59-859e0ac638e3","nodeType":10,"position":{"x":-1130.6666259765625,"y":-2232.0},"targetType":1,"assetTags":{"_tags":[]},"grantedTags":{"_tags":[{"_name":"CD.Sweep","_hashCode":-303359587,"_shortName":"Sweep","_ancestorHashCodes":[-1137859925],"_ancestorNames":["CD"]}]},"applicationRequiredTags":{"_tags":[]},"applicationImmunityTags":{"_tags":[]},"removeGameEffectsWithTags":{"_tags":[]},"durationType":1,"duration":"1","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"_tags":[]},"cancelOnAbilityEnd":false,"cooldownType":0,"maxCharges":2,"chargeTime":"10"}</t>
+          <t>{"guid":"f8947676-1084-4228-b991-1509cc7fe851","nodeType":1,"position":{"x":974.666748046875,"y":-2340.66650390625},"targetType":0,"assetTags":{"_tags":[]},"grantedTags":{"_tags":[]},"applicationRequiredTags":{"_tags":[]},"applicationImmunityTags":{"_tags":[]},"removeGameEffectsWithTags":{"_tags":[]},"durationType":0,"duration":"0","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"_tags":[]},"cancelOnAbilityEnd":true,"damageType":0,"damageSourceType":2,"damageFixedValue":10.0,"damageFormula":"","damageMMCType":0,"damageSetByCallerKey":"","damageMMCCaptureAttribute":1006,"damageMMCAttributeSource":0,"damageMMCCoefficient":1.0,"damageMMCUseSnapshot":true,"damageMultiplyByStackCount":false,"damageCalculationType":0,"enableHitKnockback":true,"knockbackDistance":1.0,"knockbackSpeed":12.0}</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
@@ -2363,11 +2363,11 @@
       <c r="C72"/>
       <c r="D72"/>
       <c r="E72">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>{"guid":"356907e0-1488-4128-bfcc-7ff73cfc3330","nodeType":0,"position":{"x":-797.3333740234375,"y":-2479.333251953125},"targetType":1,"skillId":1001,"assetTags":{"_tags":[]},"cancelAbilitiesWithTags":{"_tags":[]},"blockAbilitiesWithTags":{"_tags":[]},"activationOwnedTags":{"_tags":[]},"activationRequiredTags":{"_tags":[]},"activationBlockedTags":{"_tags":[{"_name":"CD.Sweep","_hashCode":-303359587,"_shortName":"Sweep","_ancestorHashCodes":[-1137859925],"_ancestorNames":["CD"]}]},"ongoingBlockedTags":{"_tags":[]},"eventOutputPorts":[]}</t>
+          <t>{"guid":"2cfdacd2-0186-49dd-b177-4eb8c0ad87bd","nodeType":7,"position":{"x":731.3333740234375,"y":-2082.0},"targetType":1,"endType":0}</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
@@ -2383,11 +2383,11 @@
       <c r="C73"/>
       <c r="D73"/>
       <c r="E73">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>{"guid":"432ff1e3-b18d-476d-af80-d39ddc07402a","nodeType":20,"position":{"x":-414.0,"y":-2826.0},"targetType":1,"skeletonDataAsset":null,"skeletonDataAssetPath":"Assets/Res/Spine/SP_Zhanshi/SP_Zhanshi_SkeletonData.asset","animationName":"Skill_attack_1001","animationDuration":"18","isAnimationLooping":true,"timeEffects":[{"triggerTime":7,"portIdValue":2315086,"legacyPortId":"de0ba361-3aba-4ef0-bb07-9b418fcae591"},{"triggerTime":18,"portIdValue":2649436,"legacyPortId":"84e238a8-5baf-470e-829f-186695064945"}],"timeCues":[{"startTime":7,"endTime":48,"portIdValue":2287012,"legacyPortId":"8dea1941-c520-4f9a-aee0-40932c8542ef"}]}</t>
+          <t>{"guid":"356907e0-1488-4128-bfcc-7ff73cfc3330","nodeType":0,"position":{"x":-850.0,"y":-2490.0},"targetType":1,"skillId":1001,"assetTags":{"_tags":[]},"cancelAbilitiesWithTags":{"_tags":[]},"blockAbilitiesWithTags":{"_tags":[]},"activationOwnedTags":{"_tags":[]},"activationRequiredTags":{"_tags":[]},"activationBlockedTags":{"_tags":[{"_name":"CD.Sweep","_hashCode":-303359587,"_shortName":"Sweep","_ancestorHashCodes":[-1137859925],"_ancestorNames":["CD"]}]},"ongoingBlockedTags":{"_tags":[]},"eventOutputPorts":[]}</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
@@ -2403,11 +2403,11 @@
       <c r="C74"/>
       <c r="D74"/>
       <c r="E74">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>{"guid":"f8947676-1084-4228-b991-1509cc7fe851","nodeType":1,"position":{"x":994.666748046875,"y":-2344.0},"targetType":0,"assetTags":{"_tags":[]},"grantedTags":{"_tags":[]},"applicationRequiredTags":{"_tags":[]},"applicationImmunityTags":{"_tags":[]},"removeGameEffectsWithTags":{"_tags":[]},"durationType":0,"duration":"0","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"_tags":[]},"cancelOnAbilityEnd":true,"damageType":0,"damageSourceType":0,"damageFixedValue":10.0,"damageFormula":"","damageMMCType":0,"damageSetByCallerKey":"","damageMMCCaptureAttribute":200,"damageMMCAttributeSource":0,"damageMMCCoefficient":1.0,"damageMMCUseSnapshot":true,"damageMultiplyByStackCount":false,"damageCalculationType":0,"enableHitKnockback":true,"knockbackDistance":1.0,"knockbackSpeed":12.0}</t>
+          <t>{"guid":"432ff1e3-b18d-476d-af80-d39ddc07402a","nodeType":20,"position":{"x":-414.0,"y":-2826.0},"targetType":1,"skeletonDataAsset":null,"skeletonDataAssetPath":"Assets/Res/Spine/SP_Zhanshi/SP_Zhanshi_SkeletonData.asset","animationName":"Skill_attack_1001","animationDuration":"18","isAnimationLooping":true,"timeEffects":[{"triggerTime":7,"portIdValue":2315086,"legacyPortId":"de0ba361-3aba-4ef0-bb07-9b418fcae591"},{"triggerTime":18,"portIdValue":2649436,"legacyPortId":"84e238a8-5baf-470e-829f-186695064945"}],"timeCues":[{"startTime":7,"endTime":48,"portIdValue":2287012,"legacyPortId":"8dea1941-c520-4f9a-aee0-40932c8542ef"}]}</t>
         </is>
       </c>
       <c r="G74"/>
@@ -2649,7 +2649,7 @@
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>{"guid":"9d6f459d-b588-4b64-843b-1b71e8f299ae","nodeType":3,"position":{"x":-1186.4000244140625,"y":-2011.199951171875},"targetType":1,"assetTags":{"_tags":[]},"grantedTags":{"_tags":[]},"applicationRequiredTags":{"_tags":[]},"applicationImmunityTags":{"_tags":[]},"removeGameEffectsWithTags":{"_tags":[]},"durationType":0,"duration":"0","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[{"attrType":100,"operation":0,"magnitudeSourceType":0,"fixedValue":10.0,"formula":"","mmcType":0,"setByCallerKey":"","mmcCaptureAttribute":200,"mmcAttributeSource":0,"mmcCoefficient":1.0,"mmcUseSnapshot":true}],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"_tags":[]},"cancelOnAbilityEnd":true}</t>
+          <t>{"guid":"9d6f459d-b588-4b64-843b-1b71e8f299ae","nodeType":3,"position":{"x":-1186.6666259765625,"y":-2011.3333740234375},"targetType":1,"assetTags":{"_tags":[]},"grantedTags":{"_tags":[]},"applicationRequiredTags":{"_tags":[]},"applicationImmunityTags":{"_tags":[]},"removeGameEffectsWithTags":{"_tags":[]},"durationType":0,"duration":"0","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[{"attrType":100,"operation":0,"magnitudeSourceType":0,"fixedValue":10.0,"formula":"","mmcType":0,"setByCallerKey":"","mmcCaptureAttribute":200,"mmcAttributeSource":0,"mmcCoefficient":1.0,"mmcUseSnapshot":true}],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"_tags":[]},"cancelOnAbilityEnd":true}</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
@@ -2669,7 +2669,7 @@
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>{"guid":"f73ba91e-a76b-456c-b19c-a5176809d5f5","nodeType":7,"position":{"x":700.0,"y":-1856.800048828125},"targetType":1,"endType":0}</t>
+          <t>{"guid":"f73ba91e-a76b-456c-b19c-a5176809d5f5","nodeType":7,"position":{"x":700.0,"y":-1856.666748046875},"targetType":1,"endType":0}</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
@@ -2689,7 +2689,7 @@
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>{"guid":"091ecddb-f80b-4c00-aa06-f9bc718618d2","nodeType":22,"position":{"x":-93.600006103515625,"y":-1708.800048828125},"targetType":0,"assetTags":{"_tags":[]},"grantedTags":{"_tags":[]},"applicationRequiredTags":{"_tags":[]},"applicationImmunityTags":{"_tags":[]},"removeGameEffectsWithTags":{"_tags":[]},"durationType":1,"duration":"0.5","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"_tags":[]},"cancelOnAbilityEnd":false,"displaceType":0,"speed":10.0,"distance":3.0,"minDistance":0.5,"pointSource":0,"pointBindingName":""}</t>
+          <t>{"guid":"091ecddb-f80b-4c00-aa06-f9bc718618d2","nodeType":22,"position":{"x":-93.333328247070313,"y":-1708.666748046875},"targetType":0,"assetTags":{"_tags":[]},"grantedTags":{"_tags":[]},"applicationRequiredTags":{"_tags":[]},"applicationImmunityTags":{"_tags":[]},"removeGameEffectsWithTags":{"_tags":[]},"durationType":1,"duration":"0.5","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"_tags":[]},"cancelOnAbilityEnd":false,"displaceType":0,"speed":10.0,"distance":3.0,"minDistance":0.5,"pointSource":0,"pointBindingName":""}</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
@@ -2709,7 +2709,7 @@
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>{"guid":"c28fb88d-51b1-47b2-be59-859e0ac638e3","nodeType":10,"position":{"x":-1186.4000244140625,"y":-1747.199951171875},"targetType":1,"assetTags":{"_tags":[]},"grantedTags":{"_tags":[{"_name":"CD.Wan","_hashCode":87403585,"_shortName":"Wan","_ancestorHashCodes":[-1137859925],"_ancestorNames":["CD"]}]},"applicationRequiredTags":{"_tags":[]},"applicationImmunityTags":{"_tags":[]},"removeGameEffectsWithTags":{"_tags":[]},"durationType":1,"duration":"5","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"_tags":[]},"cancelOnAbilityEnd":false,"cooldownType":0,"maxCharges":2,"chargeTime":"10"}</t>
+          <t>{"guid":"c28fb88d-51b1-47b2-be59-859e0ac638e3","nodeType":10,"position":{"x":-1186.6666259765625,"y":-1747.3333740234375},"targetType":1,"assetTags":{"_tags":[]},"grantedTags":{"_tags":[{"_name":"CD.Wan","_hashCode":87403585,"_shortName":"Wan","_ancestorHashCodes":[-1137859925],"_ancestorNames":["CD"]}]},"applicationRequiredTags":{"_tags":[]},"applicationImmunityTags":{"_tags":[]},"removeGameEffectsWithTags":{"_tags":[]},"durationType":1,"duration":"5","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"_tags":[]},"cancelOnAbilityEnd":false,"cooldownType":0,"maxCharges":2,"chargeTime":"10"}</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
@@ -2729,7 +2729,7 @@
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>{"guid":"cde57fb8-b693-4da8-a4a8-fd61e56c5dcd","nodeType":12,"position":{"x":677.5999755859375,"y":-1998.4000244140625},"targetType":1,"requiredTags":{"_tags":[]},"immunityTags":{"_tags":[]},"destroyWithNode":false,"positionSource":0,"particlePrefab":null,"particlePrefabPath":"Assets/Res/Prefab/Effect/ef_Zhanshi_zhentianpaoxiao_01.prefab","particleBindingName":"down","particleOffset":{"x":0.0,"y":0.0,"z":0.0},"particleScale":{"x":1.0,"y":1.0,"z":1.0},"attachToTarget":false,"particleLoop":false}</t>
+          <t>{"guid":"cde57fb8-b693-4da8-a4a8-fd61e56c5dcd","nodeType":12,"position":{"x":677.3333740234375,"y":-1998.666748046875},"targetType":1,"requiredTags":{"_tags":[]},"immunityTags":{"_tags":[]},"destroyWithNode":false,"positionSource":0,"particlePrefab":null,"particlePrefabPath":"Assets/Res/Prefab/Effect/ef_Zhanshi_zhentianpaoxiao_01.prefab","particleBindingName":"down","particleOffset":{"x":0.0,"y":0.0,"z":0.0},"particleScale":{"x":1.0,"y":1.0,"z":1.0},"attachToTarget":false,"particleLoop":false}</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
@@ -2749,7 +2749,7 @@
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>{"guid":"e33ab94c-1496-4d6a-ba5e-1afd38bb0c30","nodeType":4,"position":{"x":-452.0,"y":-1786.4000244140625},"targetType":1,"searchShapeType":0,"searchLineType":0,"positionSource":0,"positionBindingName":"center","searchCircleRadius":4.0,"searchSectorRadius":2.0,"searchSectorAngle":180.0,"searchLineDirectionOffsetAngle":0.0,"searchLineDirectionWidth":1.0,"searchLineDirectionLength":10.0,"lineStartPositionSource":0,"lineStartBindingName":"","lineEndPositionSource":1,"lineEndBindingName":"","searchLineBetweenWidth":1.0,"searchLineAbsoluteAngle":0.0,"searchLineAbsoluteWidth":1.0,"searchLineAbsoluteLength":10.0,"maxTargets":999,"searchTargetTags":{"_tags":[{"_name":"unitType.monster","_hashCode":-2021655864,"_shortName":"monster","_ancestorHashCodes":[1600484460],"_ancestorNames":["unitType"]}]},"searchExcludeTags":{"_tags":[]}}</t>
+          <t>{"guid":"e33ab94c-1496-4d6a-ba5e-1afd38bb0c30","nodeType":4,"position":{"x":-452.0,"y":-1786.666748046875},"targetType":1,"searchShapeType":0,"searchLineType":0,"positionSource":0,"positionBindingName":"center","searchCircleRadius":4.0,"searchSectorRadius":2.0,"searchSectorAngle":180.0,"searchLineDirectionOffsetAngle":0.0,"searchLineDirectionWidth":1.0,"searchLineDirectionLength":10.0,"lineStartPositionSource":0,"lineStartBindingName":"","lineEndPositionSource":1,"lineEndBindingName":"","searchLineBetweenWidth":1.0,"searchLineAbsoluteAngle":0.0,"searchLineAbsoluteWidth":1.0,"searchLineAbsoluteLength":10.0,"maxTargets":999,"searchTargetTags":{"_tags":[{"_name":"unitType.monster","_hashCode":-2021655864,"_shortName":"monster","_ancestorHashCodes":[1600484460],"_ancestorNames":["unitType"]}]},"searchExcludeTags":{"_tags":[]}}</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
@@ -2769,7 +2769,7 @@
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>{"guid":"432ff1e3-b18d-476d-af80-d39ddc07402a","nodeType":20,"position":{"x":-502.39999389648438,"y":-2384.0},"targetType":1,"skeletonDataAsset":null,"skeletonDataAssetPath":"Assets/Res/Spine/SP_Zhanshi/SP_Zhanshi_SkeletonData.asset","animationName":"Skill_attack_1009","animationDuration":"25","isAnimationLooping":false,"timeEffects":[{"triggerTime":4,"portIdValue":2315086,"legacyPortId":"de0ba361-3aba-4ef0-bb07-9b418fcae591"},{"triggerTime":25,"portIdValue":2000539,"legacyPortId":"f41c85e0-7f26-494e-9ffc-4a06c980f811"}],"timeCues":[{"startTime":0,"endTime":75,"portIdValue":2287012,"legacyPortId":"8dea1941-c520-4f9a-aee0-40932c8542ef"}]}</t>
+          <t>{"guid":"432ff1e3-b18d-476d-af80-d39ddc07402a","nodeType":20,"position":{"x":-502.66665649414063,"y":-2384.0},"targetType":1,"skeletonDataAsset":null,"skeletonDataAssetPath":"Assets/Res/Spine/SP_Zhanshi/SP_Zhanshi_SkeletonData.asset","animationName":"Skill_attack_1009","animationDuration":"25","isAnimationLooping":false,"timeEffects":[{"triggerTime":4,"portIdValue":2315086,"legacyPortId":"de0ba361-3aba-4ef0-bb07-9b418fcae591"},{"triggerTime":25,"portIdValue":2000539,"legacyPortId":"f41c85e0-7f26-494e-9ffc-4a06c980f811"}],"timeCues":[{"startTime":0,"endTime":75,"portIdValue":2287012,"legacyPortId":"8dea1941-c520-4f9a-aee0-40932c8542ef"}]}</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
@@ -2789,7 +2789,7 @@
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>{"guid":"356907e0-1488-4128-bfcc-7ff73cfc3330","nodeType":0,"position":{"x":-878.4000244140625,"y":-1853.5999755859375},"targetType":1,"skillId":1006,"assetTags":{"_tags":[]},"cancelAbilitiesWithTags":{"_tags":[]},"blockAbilitiesWithTags":{"_tags":[]},"activationOwnedTags":{"_tags":[{"_name":"Skill.Running","_hashCode":-51601538,"_shortName":"Running","_ancestorHashCodes":[1312877309],"_ancestorNames":["Skill"]}]},"activationRequiredTags":{"_tags":[]},"activationBlockedTags":{"_tags":[{"_name":"CD.Wan","_hashCode":87403585,"_shortName":"Wan","_ancestorHashCodes":[-1137859925],"_ancestorNames":["CD"]},{"_name":"Skill.Running","_hashCode":-51601538,"_shortName":"Running","_ancestorHashCodes":[1312877309],"_ancestorNames":["Skill"]}]},"ongoingBlockedTags":{"_tags":[]},"eventOutputPorts":[]}</t>
+          <t>{"guid":"356907e0-1488-4128-bfcc-7ff73cfc3330","nodeType":0,"position":{"x":-878.6666259765625,"y":-1853.3333740234375},"targetType":1,"skillId":1006,"assetTags":{"_tags":[]},"cancelAbilitiesWithTags":{"_tags":[]},"blockAbilitiesWithTags":{"_tags":[]},"activationOwnedTags":{"_tags":[{"_name":"Skill.Running","_hashCode":-51601538,"_shortName":"Running","_ancestorHashCodes":[1312877309],"_ancestorNames":["Skill"]}]},"activationRequiredTags":{"_tags":[]},"activationBlockedTags":{"_tags":[{"_name":"CD.Wan","_hashCode":87403585,"_shortName":"Wan","_ancestorHashCodes":[-1137859925],"_ancestorNames":["CD"]},{"_name":"Skill.Running","_hashCode":-51601538,"_shortName":"Running","_ancestorHashCodes":[1312877309],"_ancestorNames":["Skill"]}]},"ongoingBlockedTags":{"_tags":[]},"eventOutputPorts":[]}</t>
         </is>
       </c>
       <c r="G93"/>
@@ -2811,7 +2811,7 @@
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>{"guid":"9d6f459d-b588-4b64-843b-1b71e8f299ae","nodeType":3,"position":{"x":-1186.4000244140625,"y":-2011.199951171875},"targetType":1,"assetTags":{"_tags":[]},"grantedTags":{"_tags":[]},"applicationRequiredTags":{"_tags":[]},"applicationImmunityTags":{"_tags":[]},"removeGameEffectsWithTags":{"_tags":[]},"durationType":0,"duration":"0","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[{"attrType":100,"operation":0,"magnitudeSourceType":0,"fixedValue":10.0,"formula":"","mmcType":0,"setByCallerKey":"","mmcCaptureAttribute":200,"mmcAttributeSource":0,"mmcCoefficient":1.0,"mmcUseSnapshot":true}],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"_tags":[]},"cancelOnAbilityEnd":true}</t>
+          <t>{"guid":"9d6f459d-b588-4b64-843b-1b71e8f299ae","nodeType":3,"position":{"x":-1186.6666259765625,"y":-2011.3333740234375},"targetType":1,"assetTags":{"_tags":[]},"grantedTags":{"_tags":[]},"applicationRequiredTags":{"_tags":[]},"applicationImmunityTags":{"_tags":[]},"removeGameEffectsWithTags":{"_tags":[]},"durationType":0,"duration":"0","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[{"attrType":100,"operation":0,"magnitudeSourceType":0,"fixedValue":10.0,"formula":"","mmcType":0,"setByCallerKey":"","mmcCaptureAttribute":200,"mmcAttributeSource":0,"mmcCoefficient":1.0,"mmcUseSnapshot":true}],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"_tags":[]},"cancelOnAbilityEnd":true}</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>{"guid":"764289ea-065e-4f48-afc0-0f6963d18d57","nodeType":14,"position":{"x":492.0,"y":-1539.199951171875},"targetType":1,"requiredTags":{"_tags":[]},"immunityTags":{"_tags":[]},"destroyWithNode":false,"positionSource":2,"positionBindingName":"head","textType":0,"fixedText":"","contextDataKey":"DamageResult","textColor":{"r":1.0,"g":0.0,"b":0.0,"a":1.0},"criticalColor":{"r":1.0,"g":0.5,"b":0.0,"a":1.0},"missColor":{"r":0.5,"g":0.5,"b":0.5,"a":1.0},"fontSize":45.0,"criticalFontSize":60.0,"duration":1.5,"offset":{"x":0.0,"y":0.0},"moveDirection":{"x":0.0,"y":1.0}}</t>
+          <t>{"guid":"764289ea-065e-4f48-afc0-0f6963d18d57","nodeType":14,"position":{"x":492.00003051757813,"y":-1539.3333740234375},"targetType":1,"requiredTags":{"_tags":[]},"immunityTags":{"_tags":[]},"destroyWithNode":false,"positionSource":2,"positionBindingName":"head","textType":0,"fixedText":"","contextDataKey":"DamageResult","textColor":{"r":1.0,"g":0.0,"b":0.0,"a":1.0},"criticalColor":{"r":1.0,"g":0.5,"b":0.0,"a":1.0},"missColor":{"r":0.5,"g":0.5,"b":0.5,"a":1.0},"fontSize":45.0,"criticalFontSize":60.0,"duration":1.5,"offset":{"x":0.0,"y":0.0},"moveDirection":{"x":0.0,"y":1.0}}</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
@@ -2851,7 +2851,7 @@
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>{"guid":"a32d1135-94db-4f81-95ba-9d5f105ef8d0","nodeType":1,"position":{"x":308.79998779296875,"y":-1720.0},"targetType":0,"assetTags":{"_tags":[]},"grantedTags":{"_tags":[]},"applicationRequiredTags":{"_tags":[]},"applicationImmunityTags":{"_tags":[]},"removeGameEffectsWithTags":{"_tags":[]},"durationType":0,"duration":"0","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"_tags":[]},"cancelOnAbilityEnd":true,"damageType":0,"damageSourceType":0,"damageFixedValue":1.0,"damageFormula":"","damageMMCType":0,"damageSetByCallerKey":"","damageMMCCaptureAttribute":200,"damageMMCAttributeSource":0,"damageMMCCoefficient":1.0,"damageMMCUseSnapshot":true,"damageMultiplyByStackCount":false,"damageCalculationType":0,"enableHitKnockback":false,"knockbackDistance":1.0,"knockbackSpeed":12.0}</t>
+          <t>{"guid":"a32d1135-94db-4f81-95ba-9d5f105ef8d0","nodeType":1,"position":{"x":308.66665649414063,"y":-1720.0},"targetType":0,"assetTags":{"_tags":[]},"grantedTags":{"_tags":[]},"applicationRequiredTags":{"_tags":[]},"applicationImmunityTags":{"_tags":[]},"removeGameEffectsWithTags":{"_tags":[]},"durationType":0,"duration":"0","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"_tags":[]},"cancelOnAbilityEnd":true,"damageType":0,"damageSourceType":0,"damageFixedValue":1.0,"damageFormula":"","damageMMCType":0,"damageSetByCallerKey":"","damageMMCCaptureAttribute":200,"damageMMCAttributeSource":0,"damageMMCCoefficient":1.0,"damageMMCUseSnapshot":true,"damageMultiplyByStackCount":false,"damageCalculationType":0,"enableHitKnockback":false,"knockbackDistance":1.0,"knockbackSpeed":12.0}</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
@@ -2871,7 +2871,7 @@
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>{"guid":"cde57fb8-b693-4da8-a4a8-fd61e56c5dcd","nodeType":12,"position":{"x":677.5999755859375,"y":-1998.4000244140625},"targetType":1,"requiredTags":{"_tags":[]},"immunityTags":{"_tags":[]},"destroyWithNode":true,"positionSource":0,"particlePrefab":null,"particlePrefabPath":"Assets/Res/Prefab/Effect/ef_zhanshi_xfz_01.prefab","particleBindingName":"down","particleOffset":{"x":0.0,"y":0.0,"z":0.0},"particleScale":{"x":1.0,"y":1.0,"z":1.0},"attachToTarget":true,"particleLoop":true}</t>
+          <t>{"guid":"cde57fb8-b693-4da8-a4a8-fd61e56c5dcd","nodeType":12,"position":{"x":677.3333740234375,"y":-1998.666748046875},"targetType":1,"requiredTags":{"_tags":[]},"immunityTags":{"_tags":[]},"destroyWithNode":true,"positionSource":0,"particlePrefab":null,"particlePrefabPath":"Assets/Res/Prefab/Effect/ef_zhanshi_xfz_01.prefab","particleBindingName":"down","particleOffset":{"x":0.0,"y":0.0,"z":0.0},"particleScale":{"x":1.0,"y":1.0,"z":1.0},"attachToTarget":true,"particleLoop":true}</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
@@ -2891,7 +2891,7 @@
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>{"guid":"c28fb88d-51b1-47b2-be59-859e0ac638e3","nodeType":10,"position":{"x":-1186.4000244140625,"y":-1747.199951171875},"targetType":1,"assetTags":{"_tags":[]},"grantedTags":{"_tags":[{"_name":"CD.Wind","_hashCode":1982736573,"_shortName":"Wind","_ancestorHashCodes":[-1137859925],"_ancestorNames":["CD"]}]},"applicationRequiredTags":{"_tags":[]},"applicationImmunityTags":{"_tags":[]},"removeGameEffectsWithTags":{"_tags":[]},"durationType":1,"duration":"15","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"_tags":[]},"cancelOnAbilityEnd":false,"cooldownType":0,"maxCharges":2,"chargeTime":"10"}</t>
+          <t>{"guid":"c28fb88d-51b1-47b2-be59-859e0ac638e3","nodeType":10,"position":{"x":-1186.6666259765625,"y":-1747.3333740234375},"targetType":1,"assetTags":{"_tags":[]},"grantedTags":{"_tags":[{"_name":"CD.Wind","_hashCode":1982736573,"_shortName":"Wind","_ancestorHashCodes":[-1137859925],"_ancestorNames":["CD"]}]},"applicationRequiredTags":{"_tags":[]},"applicationImmunityTags":{"_tags":[]},"removeGameEffectsWithTags":{"_tags":[]},"durationType":1,"duration":"15","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"_tags":[]},"cancelOnAbilityEnd":false,"cooldownType":0,"maxCharges":2,"chargeTime":"10"}</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
@@ -2911,7 +2911,7 @@
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>{"guid":"f73ba91e-a76b-456c-b19c-a5176809d5f5","nodeType":7,"position":{"x":700.0,"y":-1856.800048828125},"targetType":1,"endType":0}</t>
+          <t>{"guid":"f73ba91e-a76b-456c-b19c-a5176809d5f5","nodeType":7,"position":{"x":700.0,"y":-1856.666748046875},"targetType":1,"endType":0}</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>{"guid":"d8847c3e-459e-4589-a96b-37ebb5ec458b","nodeType":21,"position":{"x":-308.79998779296875,"y":-1769.5999755859375},"targetType":1,"assetTags":{"_tags":[]},"grantedTags":{"_tags":[]},"applicationRequiredTags":{"_tags":[]},"applicationImmunityTags":{"_tags":[]},"removeGameEffectsWithTags":{"_tags":[]},"durationType":2,"duration":"0","isPeriodic":true,"period":"0.3","executeOnApplication":false,"attributeModifiers":[],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"_tags":[]},"cancelOnAbilityEnd":true}</t>
+          <t>{"guid":"d8847c3e-459e-4589-a96b-37ebb5ec458b","nodeType":21,"position":{"x":-308.66665649414063,"y":-1769.3333740234375},"targetType":1,"assetTags":{"_tags":[]},"grantedTags":{"_tags":[]},"applicationRequiredTags":{"_tags":[]},"applicationImmunityTags":{"_tags":[]},"removeGameEffectsWithTags":{"_tags":[]},"durationType":2,"duration":"0","isPeriodic":true,"period":"0.3","executeOnApplication":false,"attributeModifiers":[],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"_tags":[]},"cancelOnAbilityEnd":true}</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
@@ -2951,7 +2951,7 @@
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>{"guid":"e33ab94c-1496-4d6a-ba5e-1afd38bb0c30","nodeType":4,"position":{"x":27.20001220703125,"y":-1769.5999755859375},"targetType":1,"searchShapeType":0,"searchLineType":0,"positionSource":0,"positionBindingName":"center","searchCircleRadius":2.5,"searchSectorRadius":2.0,"searchSectorAngle":180.0,"searchLineDirectionOffsetAngle":0.0,"searchLineDirectionWidth":1.0,"searchLineDirectionLength":10.0,"lineStartPositionSource":0,"lineStartBindingName":"","lineEndPositionSource":1,"lineEndBindingName":"","searchLineBetweenWidth":1.0,"searchLineAbsoluteAngle":0.0,"searchLineAbsoluteWidth":1.0,"searchLineAbsoluteLength":10.0,"maxTargets":999,"searchTargetTags":{"_tags":[{"_name":"unitType.monster","_hashCode":-2021655864,"_shortName":"monster","_ancestorHashCodes":[1600484460],"_ancestorNames":["unitType"]}]},"searchExcludeTags":{"_tags":[]}}</t>
+          <t>{"guid":"e33ab94c-1496-4d6a-ba5e-1afd38bb0c30","nodeType":4,"position":{"x":27.333343505859375,"y":-1769.3333740234375},"targetType":1,"searchShapeType":0,"searchLineType":0,"positionSource":0,"positionBindingName":"center","searchCircleRadius":2.5,"searchSectorRadius":2.0,"searchSectorAngle":180.0,"searchLineDirectionOffsetAngle":0.0,"searchLineDirectionWidth":1.0,"searchLineDirectionLength":10.0,"lineStartPositionSource":0,"lineStartBindingName":"","lineEndPositionSource":1,"lineEndBindingName":"","searchLineBetweenWidth":1.0,"searchLineAbsoluteAngle":0.0,"searchLineAbsoluteWidth":1.0,"searchLineAbsoluteLength":10.0,"maxTargets":999,"searchTargetTags":{"_tags":[{"_name":"unitType.monster","_hashCode":-2021655864,"_shortName":"monster","_ancestorHashCodes":[1600484460],"_ancestorNames":["unitType"]}]},"searchExcludeTags":{"_tags":[]}}</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>{"guid":"432ff1e3-b18d-476d-af80-d39ddc07402a","nodeType":20,"position":{"x":-452.0,"y":-2375.199951171875},"targetType":1,"skeletonDataAsset":null,"skeletonDataAssetPath":"Assets/Res/Spine/SP_Zhanshi/SP_Zhanshi_SkeletonData.asset","animationName":"Skill_attack_1011","animationDuration":"12","isAnimationLooping":true,"timeEffects":[{"triggerTime":250,"portIdValue":2000539,"legacyPortId":"f41c85e0-7f26-494e-9ffc-4a06c980f811"}],"timeCues":[{"startTime":0,"endTime":255,"portIdValue":2287012,"legacyPortId":"8dea1941-c520-4f9a-aee0-40932c8542ef"}]}</t>
+          <t>{"guid":"432ff1e3-b18d-476d-af80-d39ddc07402a","nodeType":20,"position":{"x":-452.0,"y":-2375.333251953125},"targetType":1,"skeletonDataAsset":null,"skeletonDataAssetPath":"Assets/Res/Spine/SP_Zhanshi/SP_Zhanshi_SkeletonData.asset","animationName":"Skill_attack_1011","animationDuration":"12","isAnimationLooping":true,"timeEffects":[{"triggerTime":250,"portIdValue":2000539,"legacyPortId":"f41c85e0-7f26-494e-9ffc-4a06c980f811"}],"timeCues":[{"startTime":0,"endTime":255,"portIdValue":2287012,"legacyPortId":"8dea1941-c520-4f9a-aee0-40932c8542ef"}]}</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
@@ -2991,7 +2991,7 @@
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>{"guid":"356907e0-1488-4128-bfcc-7ff73cfc3330","nodeType":0,"position":{"x":-878.4000244140625,"y":-1853.5999755859375},"targetType":1,"skillId":1004,"assetTags":{"_tags":[]},"cancelAbilitiesWithTags":{"_tags":[]},"blockAbilitiesWithTags":{"_tags":[]},"activationOwnedTags":{"_tags":[{"_name":"Skill.Running","_hashCode":-51601538,"_shortName":"Running","_ancestorHashCodes":[1312877309],"_ancestorNames":["Skill"]}]},"activationRequiredTags":{"_tags":[]},"activationBlockedTags":{"_tags":[{"_name":"CD.Wind","_hashCode":1982736573,"_shortName":"Wind","_ancestorHashCodes":[-1137859925],"_ancestorNames":["CD"]},{"_name":"Skill.Running","_hashCode":-51601538,"_shortName":"Running","_ancestorHashCodes":[1312877309],"_ancestorNames":["Skill"]}]},"ongoingBlockedTags":{"_tags":[]},"eventOutputPorts":[]}</t>
+          <t>{"guid":"356907e0-1488-4128-bfcc-7ff73cfc3330","nodeType":0,"position":{"x":-878.6666259765625,"y":-1853.3333740234375},"targetType":1,"skillId":1004,"assetTags":{"_tags":[]},"cancelAbilitiesWithTags":{"_tags":[]},"blockAbilitiesWithTags":{"_tags":[]},"activationOwnedTags":{"_tags":[{"_name":"Skill.Running","_hashCode":-51601538,"_shortName":"Running","_ancestorHashCodes":[1312877309],"_ancestorNames":["Skill"]}]},"activationRequiredTags":{"_tags":[]},"activationBlockedTags":{"_tags":[{"_name":"CD.Wind","_hashCode":1982736573,"_shortName":"Wind","_ancestorHashCodes":[-1137859925],"_ancestorNames":["CD"]},{"_name":"Skill.Running","_hashCode":-51601538,"_shortName":"Running","_ancestorHashCodes":[1312877309],"_ancestorNames":["Skill"]}]},"ongoingBlockedTags":{"_tags":[]},"eventOutputPorts":[]}</t>
         </is>
       </c>
       <c r="G103"/>

--- a/Design/Excel/ET/Datas/Game/SkillGraph.xlsx
+++ b/Design/Excel/ET/Datas/Game/SkillGraph.xlsx
@@ -1311,11 +1311,11 @@
       </c>
       <c r="D20"/>
       <c r="E20">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>{"guid":"9d6f459d-b588-4b64-843b-1b71e8f299ae","nodeType":3,"position":{"x":-1186.6666259765625,"y":-2011.3333740234375},"targetType":1,"assetTags":{"_tags":[]},"grantedTags":{"_tags":[]},"applicationRequiredTags":{"_tags":[]},"applicationImmunityTags":{"_tags":[]},"removeGameEffectsWithTags":{"_tags":[]},"durationType":0,"duration":"0","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[{"attrType":100,"operation":0,"magnitudeSourceType":0,"fixedValue":10.0,"formula":"","mmcType":0,"setByCallerKey":"","mmcCaptureAttribute":200,"mmcAttributeSource":0,"mmcCoefficient":1.0,"mmcUseSnapshot":true}],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"_tags":[]},"cancelOnAbilityEnd":true}</t>
+          <t>{"guid":"2d7e41c4-8e90-4b61-879c-4b2e5b9486db","nodeType":14,"position":{"x":408.66665649414063,"y":-1747.3333740234375},"targetType":1,"requiredTags":{"_tags":[]},"immunityTags":{"_tags":[]},"destroyWithNode":false,"positionSource":2,"positionBindingName":"head","textType":0,"fixedText":"","contextDataKey":"DamageResult","textColor":{"r":0.0,"g":0.323091983795166,"b":1.0,"a":1.0},"criticalColor":{"r":1.0,"g":0.5,"b":0.0,"a":1.0},"missColor":{"r":0.5,"g":0.5,"b":0.5,"a":1.0},"fontSize":45.0,"criticalFontSize":60.0,"duration":1.5,"offset":{"x":0.0,"y":0.0},"moveDirection":{"x":0.0,"y":1.0}}</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -1331,11 +1331,11 @@
       <c r="C21"/>
       <c r="D21"/>
       <c r="E21">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>{"guid":"2d7e41c4-8e90-4b61-879c-4b2e5b9486db","nodeType":14,"position":{"x":408.66665649414063,"y":-1747.3333740234375},"targetType":1,"requiredTags":{"_tags":[]},"immunityTags":{"_tags":[]},"destroyWithNode":false,"positionSource":2,"positionBindingName":"head","textType":0,"fixedText":"","contextDataKey":"DamageResult","textColor":{"r":0.0,"g":0.323091983795166,"b":1.0,"a":1.0},"criticalColor":{"r":1.0,"g":0.5,"b":0.0,"a":1.0},"missColor":{"r":0.5,"g":0.5,"b":0.5,"a":1.0},"fontSize":45.0,"criticalFontSize":60.0,"duration":1.5,"offset":{"x":0.0,"y":0.0},"moveDirection":{"x":0.0,"y":1.0}}</t>
+          <t>{"guid":"3aafa9a5-4766-4204-91ab-d797aeb3c0e1","nodeType":7,"position":{"x":580.6666259765625,"y":-1987.3333740234375},"targetType":1,"endType":0}</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -1351,11 +1351,11 @@
       <c r="C22"/>
       <c r="D22"/>
       <c r="E22">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>{"guid":"3aafa9a5-4766-4204-91ab-d797aeb3c0e1","nodeType":7,"position":{"x":580.6666259765625,"y":-1987.3333740234375},"targetType":1,"endType":0}</t>
+          <t>{"guid":"432ff1e3-b18d-476d-af80-d39ddc07402a","nodeType":20,"position":{"x":-491.33331298828125,"y":-2478.66650390625},"targetType":1,"skeletonDataAsset":null,"skeletonDataAssetPath":"Assets/Res/Spine/SP_Xiyiguai/SP_Xiyiguai_SkeletonData.asset","animationName":"Attack","animationDuration":"24","isAnimationLooping":false,"timeEffects":[{"triggerTime":11,"portIdValue":2315086,"legacyPortId":"de0ba361-3aba-4ef0-bb07-9b418fcae591"},{"triggerTime":24,"portIdValue":2715463,"legacyPortId":"7ecf9fe6-7c5e-46ae-bade-7922214225e2"}],"timeCues":[]}</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -1371,11 +1371,11 @@
       <c r="C23"/>
       <c r="D23"/>
       <c r="E23">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>{"guid":"432ff1e3-b18d-476d-af80-d39ddc07402a","nodeType":20,"position":{"x":-491.33331298828125,"y":-2478.66650390625},"targetType":1,"skeletonDataAsset":null,"skeletonDataAssetPath":"Assets/Res/Spine/SP_Xiyiguai/SP_Xiyiguai_SkeletonData.asset","animationName":"Attack","animationDuration":"24","isAnimationLooping":false,"timeEffects":[{"triggerTime":11,"portIdValue":2315086,"legacyPortId":"de0ba361-3aba-4ef0-bb07-9b418fcae591"},{"triggerTime":24,"portIdValue":2715463,"legacyPortId":"7ecf9fe6-7c5e-46ae-bade-7922214225e2"}],"timeCues":[]}</t>
+          <t>{"guid":"356907e0-1488-4128-bfcc-7ff73cfc3330","nodeType":0,"position":{"x":-880.6666259765625,"y":-1851.3333740234375},"targetType":1,"skillId":7001,"assetTags":{"_tags":[]},"cancelAbilitiesWithTags":{"_tags":[]},"blockAbilitiesWithTags":{"_tags":[]},"activationOwnedTags":{"_tags":[]},"activationRequiredTags":{"_tags":[]},"activationBlockedTags":{"_tags":[{"_name":"CD.FireCircle","_hashCode":522143731,"_shortName":"FireCircle","_ancestorHashCodes":[-1137859925],"_ancestorNames":["CD"]}]},"ongoingBlockedTags":{"_tags":[{"_name":"Buff.DeBuff.Stun","_hashCode":1791562953,"_shortName":"Stun","_ancestorHashCodes":[937056111,321157895],"_ancestorNames":["Buff","Buff.DeBuff"]}]},"eventOutputPorts":[]}</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -1391,11 +1391,11 @@
       <c r="C24"/>
       <c r="D24"/>
       <c r="E24">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>{"guid":"356907e0-1488-4128-bfcc-7ff73cfc3330","nodeType":0,"position":{"x":-880.6666259765625,"y":-1851.3333740234375},"targetType":1,"skillId":7001,"assetTags":{"_tags":[]},"cancelAbilitiesWithTags":{"_tags":[]},"blockAbilitiesWithTags":{"_tags":[]},"activationOwnedTags":{"_tags":[]},"activationRequiredTags":{"_tags":[]},"activationBlockedTags":{"_tags":[{"_name":"CD.FireCircle","_hashCode":522143731,"_shortName":"FireCircle","_ancestorHashCodes":[-1137859925],"_ancestorNames":["CD"]}]},"ongoingBlockedTags":{"_tags":[{"_name":"Buff.DeBuff.Stun","_hashCode":1791562953,"_shortName":"Stun","_ancestorHashCodes":[937056111,321157895],"_ancestorNames":["Buff","Buff.DeBuff"]}]},"eventOutputPorts":[]}</t>
+          <t>{"guid":"eae41233-d297-46fe-a6c8-0b5c876fbb2a","nodeType":1,"position":{"x":46.66668701171875,"y":-1808.666748046875},"targetType":0,"assetTags":{"_tags":[]},"grantedTags":{"_tags":[]},"applicationRequiredTags":{"_tags":[]},"applicationImmunityTags":{"_tags":[]},"removeGameEffectsWithTags":{"_tags":[]},"durationType":0,"duration":"0","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"_tags":[]},"cancelOnAbilityEnd":true,"damageType":0,"damageSourceType":0,"damageFixedValue":10.0,"damageFormula":"","damageMMCType":0,"damageSetByCallerKey":"","damageMMCCaptureAttribute":200,"damageMMCAttributeSource":0,"damageMMCCoefficient":1.0,"damageMMCUseSnapshot":true,"damageMultiplyByStackCount":false,"damageCalculationType":0,"enableHitKnockback":true,"knockbackDistance":1.0,"knockbackSpeed":12.0}</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -1411,11 +1411,11 @@
       <c r="C25"/>
       <c r="D25"/>
       <c r="E25">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>{"guid":"eae41233-d297-46fe-a6c8-0b5c876fbb2a","nodeType":1,"position":{"x":46.66668701171875,"y":-1808.666748046875},"targetType":0,"assetTags":{"_tags":[]},"grantedTags":{"_tags":[]},"applicationRequiredTags":{"_tags":[]},"applicationImmunityTags":{"_tags":[]},"removeGameEffectsWithTags":{"_tags":[]},"durationType":0,"duration":"0","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"_tags":[]},"cancelOnAbilityEnd":true,"damageType":0,"damageSourceType":0,"damageFixedValue":10.0,"damageFormula":"","damageMMCType":0,"damageSetByCallerKey":"","damageMMCCaptureAttribute":200,"damageMMCAttributeSource":0,"damageMMCCoefficient":1.0,"damageMMCUseSnapshot":true,"damageMultiplyByStackCount":false,"damageCalculationType":0,"enableHitKnockback":true,"knockbackDistance":1.0,"knockbackSpeed":12.0}</t>
+          <t>{"guid":"90bacd9f-d882-4bba-aaa8-41ed993ac3ff","nodeType":8,"position":{"x":-401.33331298828125,"y":-1826.666748046875},"targetType":2,"assetTags":{"_tags":[]},"grantedTags":{"_tags":[]},"applicationRequiredTags":{"_tags":[]},"applicationImmunityTags":{"_tags":[]},"removeGameEffectsWithTags":{"_tags":[]},"durationType":2,"duration":"0","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"_tags":[]},"cancelOnAbilityEnd":false,"launchPositionSource":0,"launchBindingName":"center","targetPositionSource":1,"targetBindingName":"center","projectileTargetType":0,"flyOver":false,"offsetAngle":0.0,"curveHeight":0.0,"projectilePrefab":null,"projectilePrefabPath":"Assets/Res/Prefab/Effect/ef_fashi_gandian_buff.prefab","speed":3.0,"maxDistance":10.0,"collisionRadius":0.5,"isPiercing":false,"maxPierceCount":1,"collisionTargetTags":{"_tags":[]},"collisionExcludeTags":{"_tags":[]},"isBouncing":true,"bounceTargetMode":1,"maxBounceCount":3,"bounceSearchRadius":10.0,"canBounceToSameTarget":false,"excludeSourceCamp":true,"bounceAngleOffset":0.0}</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -1431,11 +1431,11 @@
       <c r="C26"/>
       <c r="D26"/>
       <c r="E26">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>{"guid":"90bacd9f-d882-4bba-aaa8-41ed993ac3ff","nodeType":8,"position":{"x":-401.33331298828125,"y":-1826.666748046875},"targetType":2,"assetTags":{"_tags":[]},"grantedTags":{"_tags":[]},"applicationRequiredTags":{"_tags":[]},"applicationImmunityTags":{"_tags":[]},"removeGameEffectsWithTags":{"_tags":[]},"durationType":2,"duration":"0","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"_tags":[]},"cancelOnAbilityEnd":false,"launchPositionSource":0,"launchBindingName":"center","targetPositionSource":1,"targetBindingName":"center","projectileTargetType":0,"flyOver":false,"offsetAngle":0.0,"curveHeight":0.0,"projectilePrefab":null,"projectilePrefabPath":"Assets/Res/Prefab/Effect/ef_fashi_gandian_buff.prefab","speed":3.0,"maxDistance":10.0,"collisionRadius":0.5,"isPiercing":false,"maxPierceCount":1,"collisionTargetTags":{"_tags":[]},"collisionExcludeTags":{"_tags":[]},"isBouncing":true,"bounceTargetMode":1,"maxBounceCount":3,"bounceSearchRadius":10.0,"canBounceToSameTarget":false,"excludeSourceCamp":true,"bounceAngleOffset":0.0}</t>
+          <t>{"guid":"c28fb88d-51b1-47b2-be59-859e0ac638e3","nodeType":10,"position":{"x":-1220.6666259765625,"y":-1747.3333740234375},"targetType":1,"assetTags":{"_tags":[]},"grantedTags":{"_tags":[{"_name":"CD.FireCircle","_hashCode":522143731,"_shortName":"FireCircle","_ancestorHashCodes":[-1137859925],"_ancestorNames":["CD"]}]},"applicationRequiredTags":{"_tags":[]},"applicationImmunityTags":{"_tags":[]},"removeGameEffectsWithTags":{"_tags":[]},"durationType":1,"duration":"3","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"_tags":[]},"cancelOnAbilityEnd":false,"cooldownType":0,"maxCharges":2,"chargeTime":"10"}</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -1451,11 +1451,11 @@
       <c r="C27"/>
       <c r="D27"/>
       <c r="E27">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>{"guid":"c28fb88d-51b1-47b2-be59-859e0ac638e3","nodeType":10,"position":{"x":-1220.6666259765625,"y":-1747.3333740234375},"targetType":1,"assetTags":{"_tags":[]},"grantedTags":{"_tags":[{"_name":"CD.FireCircle","_hashCode":522143731,"_shortName":"FireCircle","_ancestorHashCodes":[-1137859925],"_ancestorNames":["CD"]}]},"applicationRequiredTags":{"_tags":[]},"applicationImmunityTags":{"_tags":[]},"removeGameEffectsWithTags":{"_tags":[]},"durationType":1,"duration":"3","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"_tags":[]},"cancelOnAbilityEnd":false,"cooldownType":0,"maxCharges":2,"chargeTime":"10"}</t>
+          <t>{"guid":"9d6f459d-b588-4b64-843b-1b71e8f299ae","nodeType":3,"position":{"x":-1195.3333740234375,"y":-2003.3333740234375},"targetType":1,"assetTags":{"_tags":[]},"grantedTags":{"_tags":[]},"applicationRequiredTags":{"_tags":[]},"applicationImmunityTags":{"_tags":[]},"removeGameEffectsWithTags":{"_tags":[]},"durationType":0,"duration":"0","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[{"attrType":1003,"operation":0,"magnitudeSourceType":0,"fixedValue":-100.0,"formula":"","mmcType":0,"setByCallerKey":"","mmcCaptureAttribute":200,"mmcAttributeSource":0,"mmcCoefficient":1.0,"mmcUseSnapshot":true}],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"_tags":[]},"cancelOnAbilityEnd":true}</t>
         </is>
       </c>
       <c r="G27"/>
@@ -1473,11 +1473,11 @@
       </c>
       <c r="D28"/>
       <c r="E28">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>{"guid":"9d6f459d-b588-4b64-843b-1b71e8f299ae","nodeType":3,"position":{"x":-1186.6666259765625,"y":-2011.3333740234375},"targetType":1,"assetTags":{"_tags":[]},"grantedTags":{"_tags":[]},"applicationRequiredTags":{"_tags":[]},"applicationImmunityTags":{"_tags":[]},"removeGameEffectsWithTags":{"_tags":[]},"durationType":0,"duration":"0","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[{"attrType":100,"operation":0,"magnitudeSourceType":0,"fixedValue":-10.0,"formula":"","mmcType":0,"setByCallerKey":"","mmcCaptureAttribute":200,"mmcAttributeSource":0,"mmcCoefficient":1.0,"mmcUseSnapshot":true}],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"_tags":[]},"cancelOnAbilityEnd":true}</t>
+          <t>{"guid":"eae41233-d297-46fe-a6c8-0b5c876fbb2a","nodeType":1,"position":{"x":46.66668701171875,"y":-1808.666748046875},"targetType":0,"assetTags":{"_tags":[]},"grantedTags":{"_tags":[]},"applicationRequiredTags":{"_tags":[]},"applicationImmunityTags":{"_tags":[]},"removeGameEffectsWithTags":{"_tags":[]},"durationType":0,"duration":"0","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"_tags":[]},"cancelOnAbilityEnd":true,"damageType":0,"damageSourceType":0,"damageFixedValue":10.0,"damageFormula":"","damageMMCType":0,"damageSetByCallerKey":"","damageMMCCaptureAttribute":200,"damageMMCAttributeSource":0,"damageMMCCoefficient":1.0,"damageMMCUseSnapshot":true,"damageMultiplyByStackCount":false,"damageCalculationType":0,"enableHitKnockback":false,"knockbackDistance":1.0,"knockbackSpeed":12.0}</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -1493,11 +1493,11 @@
       <c r="C29"/>
       <c r="D29"/>
       <c r="E29">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>{"guid":"eae41233-d297-46fe-a6c8-0b5c876fbb2a","nodeType":1,"position":{"x":46.66668701171875,"y":-1808.666748046875},"targetType":0,"assetTags":{"_tags":[]},"grantedTags":{"_tags":[]},"applicationRequiredTags":{"_tags":[]},"applicationImmunityTags":{"_tags":[]},"removeGameEffectsWithTags":{"_tags":[]},"durationType":0,"duration":"0","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"_tags":[]},"cancelOnAbilityEnd":true,"damageType":0,"damageSourceType":0,"damageFixedValue":10.0,"damageFormula":"","damageMMCType":0,"damageSetByCallerKey":"","damageMMCCaptureAttribute":200,"damageMMCAttributeSource":0,"damageMMCCoefficient":1.0,"damageMMCUseSnapshot":true,"damageMultiplyByStackCount":false,"damageCalculationType":0,"enableHitKnockback":false,"knockbackDistance":1.0,"knockbackSpeed":12.0}</t>
+          <t>{"guid":"2d7e41c4-8e90-4b61-879c-4b2e5b9486db","nodeType":14,"position":{"x":408.66665649414063,"y":-1747.3333740234375},"targetType":1,"requiredTags":{"_tags":[]},"immunityTags":{"_tags":[]},"destroyWithNode":false,"positionSource":2,"positionBindingName":"head","textType":0,"fixedText":"","contextDataKey":"DamageResult","textColor":{"r":0.0,"g":0.323091983795166,"b":1.0,"a":1.0},"criticalColor":{"r":1.0,"g":0.5,"b":0.0,"a":1.0},"missColor":{"r":0.5,"g":0.5,"b":0.5,"a":1.0},"fontSize":45.0,"criticalFontSize":60.0,"duration":1.5,"offset":{"x":0.0,"y":0.0},"moveDirection":{"x":0.0,"y":1.0}}</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -1513,11 +1513,11 @@
       <c r="C30"/>
       <c r="D30"/>
       <c r="E30">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>{"guid":"2d7e41c4-8e90-4b61-879c-4b2e5b9486db","nodeType":14,"position":{"x":408.66665649414063,"y":-1747.3333740234375},"targetType":1,"requiredTags":{"_tags":[]},"immunityTags":{"_tags":[]},"destroyWithNode":false,"positionSource":2,"positionBindingName":"head","textType":0,"fixedText":"","contextDataKey":"DamageResult","textColor":{"r":0.0,"g":0.323091983795166,"b":1.0,"a":1.0},"criticalColor":{"r":1.0,"g":0.5,"b":0.0,"a":1.0},"missColor":{"r":0.5,"g":0.5,"b":0.5,"a":1.0},"fontSize":45.0,"criticalFontSize":60.0,"duration":1.5,"offset":{"x":0.0,"y":0.0},"moveDirection":{"x":0.0,"y":1.0}}</t>
+          <t>{"guid":"3aafa9a5-4766-4204-91ab-d797aeb3c0e1","nodeType":7,"position":{"x":580.6666259765625,"y":-1987.3333740234375},"targetType":1,"endType":0}</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -1533,11 +1533,11 @@
       <c r="C31"/>
       <c r="D31"/>
       <c r="E31">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>{"guid":"3aafa9a5-4766-4204-91ab-d797aeb3c0e1","nodeType":7,"position":{"x":580.6666259765625,"y":-1987.3333740234375},"targetType":1,"endType":0}</t>
+          <t>{"guid":"432ff1e3-b18d-476d-af80-d39ddc07402a","nodeType":20,"position":{"x":-491.33331298828125,"y":-2478.66650390625},"targetType":1,"skeletonDataAsset":null,"skeletonDataAssetPath":"Assets/Res/Spine/SP_Zhanshi/SP_Zhanshi_SkeletonData.asset","animationName":"Attack_01","animationDuration":"18","isAnimationLooping":false,"timeEffects":[{"triggerTime":11,"portIdValue":2315086,"legacyPortId":"de0ba361-3aba-4ef0-bb07-9b418fcae591"},{"triggerTime":24,"portIdValue":2715463,"legacyPortId":"7ecf9fe6-7c5e-46ae-bade-7922214225e2"}],"timeCues":[]}</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -1553,11 +1553,11 @@
       <c r="C32"/>
       <c r="D32"/>
       <c r="E32">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>{"guid":"432ff1e3-b18d-476d-af80-d39ddc07402a","nodeType":20,"position":{"x":-491.33331298828125,"y":-2478.66650390625},"targetType":1,"skeletonDataAsset":null,"skeletonDataAssetPath":"Assets/Res/Spine/SP_Zhanshi/SP_Zhanshi_SkeletonData.asset","animationName":"Attack_01","animationDuration":"18","isAnimationLooping":false,"timeEffects":[{"triggerTime":11,"portIdValue":2315086,"legacyPortId":"de0ba361-3aba-4ef0-bb07-9b418fcae591"},{"triggerTime":24,"portIdValue":2715463,"legacyPortId":"7ecf9fe6-7c5e-46ae-bade-7922214225e2"}],"timeCues":[]}</t>
+          <t>{"guid":"c28fb88d-51b1-47b2-be59-859e0ac638e3","nodeType":10,"position":{"x":-1220.6666259765625,"y":-1747.3333740234375},"targetType":1,"assetTags":{"_tags":[]},"grantedTags":{"_tags":[{"_name":"CD.FireCircle","_hashCode":522143731,"_shortName":"FireCircle","_ancestorHashCodes":[-1137859925],"_ancestorNames":["CD"]}]},"applicationRequiredTags":{"_tags":[]},"applicationImmunityTags":{"_tags":[]},"removeGameEffectsWithTags":{"_tags":[]},"durationType":1,"duration":"1","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"_tags":[]},"cancelOnAbilityEnd":false,"cooldownType":0,"maxCharges":2,"chargeTime":"10"}</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -1573,11 +1573,11 @@
       <c r="C33"/>
       <c r="D33"/>
       <c r="E33">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>{"guid":"c28fb88d-51b1-47b2-be59-859e0ac638e3","nodeType":10,"position":{"x":-1220.6666259765625,"y":-1747.3333740234375},"targetType":1,"assetTags":{"_tags":[]},"grantedTags":{"_tags":[{"_name":"CD.FireCircle","_hashCode":522143731,"_shortName":"FireCircle","_ancestorHashCodes":[-1137859925],"_ancestorNames":["CD"]}]},"applicationRequiredTags":{"_tags":[]},"applicationImmunityTags":{"_tags":[]},"removeGameEffectsWithTags":{"_tags":[]},"durationType":1,"duration":"1","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"_tags":[]},"cancelOnAbilityEnd":false,"cooldownType":0,"maxCharges":2,"chargeTime":"10"}</t>
+          <t>{"guid":"356907e0-1488-4128-bfcc-7ff73cfc3330","nodeType":0,"position":{"x":-878.6666259765625,"y":-1851.3333740234375},"targetType":1,"skillId":1010,"assetTags":{"_tags":[]},"cancelAbilitiesWithTags":{"_tags":[]},"blockAbilitiesWithTags":{"_tags":[]},"activationOwnedTags":{"_tags":[]},"activationRequiredTags":{"_tags":[]},"activationBlockedTags":{"_tags":[{"_name":"CD.FireCircle","_hashCode":522143731,"_shortName":"FireCircle","_ancestorHashCodes":[-1137859925],"_ancestorNames":["CD"]}]},"ongoingBlockedTags":{"_tags":[]},"eventOutputPorts":[]}</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -1593,11 +1593,11 @@
       <c r="C34"/>
       <c r="D34"/>
       <c r="E34">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>{"guid":"356907e0-1488-4128-bfcc-7ff73cfc3330","nodeType":0,"position":{"x":-878.6666259765625,"y":-1851.3333740234375},"targetType":1,"skillId":1010,"assetTags":{"_tags":[]},"cancelAbilitiesWithTags":{"_tags":[]},"blockAbilitiesWithTags":{"_tags":[]},"activationOwnedTags":{"_tags":[]},"activationRequiredTags":{"_tags":[]},"activationBlockedTags":{"_tags":[{"_name":"CD.FireCircle","_hashCode":522143731,"_shortName":"FireCircle","_ancestorHashCodes":[-1137859925],"_ancestorNames":["CD"]}]},"ongoingBlockedTags":{"_tags":[]},"eventOutputPorts":[]}</t>
+          <t>{"guid":"90bacd9f-d882-4bba-aaa8-41ed993ac3ff","nodeType":8,"position":{"x":-400.66665649414063,"y":-1836.666748046875},"targetType":2,"assetTags":{"_tags":[]},"grantedTags":{"_tags":[]},"applicationRequiredTags":{"_tags":[]},"applicationImmunityTags":{"_tags":[]},"removeGameEffectsWithTags":{"_tags":[]},"durationType":2,"duration":"0","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"_tags":[]},"cancelOnAbilityEnd":false,"launchPositionSource":0,"launchBindingName":"center","targetPositionSource":1,"targetBindingName":"center","projectileTargetType":0,"flyOver":false,"offsetAngle":0.0,"curveHeight":0.0,"projectilePrefab":null,"projectilePrefabPath":"Assets/Res/Prefab/Effect/ef_fashi_gandian_buff.prefab","speed":3.0,"maxDistance":10.0,"collisionRadius":0.5,"isPiercing":false,"maxPierceCount":1,"collisionTargetTags":{"_tags":[]},"collisionExcludeTags":{"_tags":[]},"isBouncing":true,"bounceTargetMode":0,"maxBounceCount":2,"bounceSearchRadius":10.0,"canBounceToSameTarget":false,"excludeSourceCamp":true,"bounceAngleOffset":50.0}</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -1613,11 +1613,11 @@
       <c r="C35"/>
       <c r="D35"/>
       <c r="E35">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>{"guid":"90bacd9f-d882-4bba-aaa8-41ed993ac3ff","nodeType":8,"position":{"x":-400.66665649414063,"y":-1836.666748046875},"targetType":2,"assetTags":{"_tags":[]},"grantedTags":{"_tags":[]},"applicationRequiredTags":{"_tags":[]},"applicationImmunityTags":{"_tags":[]},"removeGameEffectsWithTags":{"_tags":[]},"durationType":2,"duration":"0","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"_tags":[]},"cancelOnAbilityEnd":false,"launchPositionSource":0,"launchBindingName":"center","targetPositionSource":1,"targetBindingName":"center","projectileTargetType":0,"flyOver":false,"offsetAngle":0.0,"curveHeight":0.0,"projectilePrefab":null,"projectilePrefabPath":"Assets/Res/Prefab/Effect/ef_fashi_gandian_buff.prefab","speed":3.0,"maxDistance":10.0,"collisionRadius":0.5,"isPiercing":false,"maxPierceCount":1,"collisionTargetTags":{"_tags":[]},"collisionExcludeTags":{"_tags":[]},"isBouncing":true,"bounceTargetMode":0,"maxBounceCount":2,"bounceSearchRadius":10.0,"canBounceToSameTarget":false,"excludeSourceCamp":true,"bounceAngleOffset":50.0}</t>
+          <t>{"guid":"9d6f459d-b588-4b64-843b-1b71e8f299ae","nodeType":3,"position":{"x":-1195.3333740234375,"y":-2013.3333740234375},"targetType":1,"assetTags":{"_tags":[]},"grantedTags":{"_tags":[]},"applicationRequiredTags":{"_tags":[]},"applicationImmunityTags":{"_tags":[]},"removeGameEffectsWithTags":{"_tags":[]},"durationType":0,"duration":"0","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[{"attrType":1003,"operation":0,"magnitudeSourceType":0,"fixedValue":-100.0,"formula":"","mmcType":0,"setByCallerKey":"","mmcCaptureAttribute":200,"mmcAttributeSource":0,"mmcCoefficient":1.0,"mmcUseSnapshot":true}],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"_tags":[]},"cancelOnAbilityEnd":true}</t>
         </is>
       </c>
       <c r="G35"/>
@@ -2252,7 +2252,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>{"outputNodeGuid":"432ff1e3-b18d-476d-af80-d39ddc07402a","outputPortId":2287012,"inputNodeGuid":"cde57fb8-b693-4da8-a4a8-fd61e56c5dcd","inputPortId":7001}</t>
+          <t>{"outputNodeGuid":"356907e0-1488-4128-bfcc-7ff73cfc3330","outputPortId":1002,"inputNodeGuid":"432ff1e3-b18d-476d-af80-d39ddc07402a","inputPortId":7001}</t>
         </is>
       </c>
       <c r="H66"/>
@@ -2263,16 +2263,16 @@
       <c r="C67"/>
       <c r="D67"/>
       <c r="E67">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>{"guid":"cde57fb8-b693-4da8-a4a8-fd61e56c5dcd","nodeType":12,"position":{"x":731.3333740234375,"y":-2488.66650390625},"targetType":1,"requiredTags":{"_tags":[]},"immunityTags":{"_tags":[]},"destroyWithNode":false,"positionSource":0,"particlePrefab":null,"particlePrefabPath":"Assets/Res/Prefab/Effect/ef_Zhanshi_attack_02.prefab","particleBindingName":"down","particleOffset":{"x":0.0,"y":0.0,"z":0.0},"particleScale":{"x":1.0,"y":1.0,"z":1.0},"attachToTarget":false,"particleLoop":false}</t>
+          <t>{"guid":"e33ab94c-1496-4d6a-ba5e-1afd38bb0c30","nodeType":4,"position":{"x":731.3333740234375,"y":-2344.0},"targetType":1,"searchShapeType":1,"searchLineType":0,"positionSource":0,"positionBindingName":"center","searchCircleRadius":5.0,"searchSectorRadius":2.0,"searchSectorAngle":180.0,"searchLineDirectionOffsetAngle":0.0,"searchLineDirectionWidth":1.0,"searchLineDirectionLength":10.0,"lineStartPositionSource":0,"lineStartBindingName":"","lineEndPositionSource":1,"lineEndBindingName":"","searchLineBetweenWidth":1.0,"searchLineAbsoluteAngle":0.0,"searchLineAbsoluteWidth":1.0,"searchLineAbsoluteLength":10.0,"maxTargets":999,"searchTargetTags":{"_tags":[{"_name":"unitType.monster","_hashCode":-2021655864,"_shortName":"monster","_ancestorHashCodes":[1600484460],"_ancestorNames":["unitType"]}]},"searchExcludeTags":{"_tags":[]}}</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>{"outputNodeGuid":"356907e0-1488-4128-bfcc-7ff73cfc3330","outputPortId":1002,"inputNodeGuid":"432ff1e3-b18d-476d-af80-d39ddc07402a","inputPortId":7001}</t>
+          <t>{"outputNodeGuid":"356907e0-1488-4128-bfcc-7ff73cfc3330","outputPortId":1004,"inputNodeGuid":"c28fb88d-51b1-47b2-be59-859e0ac638e3","inputPortId":7001}</t>
         </is>
       </c>
       <c r="H67"/>
@@ -2283,16 +2283,16 @@
       <c r="C68"/>
       <c r="D68"/>
       <c r="E68">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>{"guid":"e33ab94c-1496-4d6a-ba5e-1afd38bb0c30","nodeType":4,"position":{"x":731.3333740234375,"y":-2344.0},"targetType":1,"searchShapeType":1,"searchLineType":0,"positionSource":0,"positionBindingName":"center","searchCircleRadius":5.0,"searchSectorRadius":2.0,"searchSectorAngle":180.0,"searchLineDirectionOffsetAngle":0.0,"searchLineDirectionWidth":1.0,"searchLineDirectionLength":10.0,"lineStartPositionSource":0,"lineStartBindingName":"","lineEndPositionSource":1,"lineEndBindingName":"","searchLineBetweenWidth":1.0,"searchLineAbsoluteAngle":0.0,"searchLineAbsoluteWidth":1.0,"searchLineAbsoluteLength":10.0,"maxTargets":999,"searchTargetTags":{"_tags":[{"_name":"unitType.monster","_hashCode":-2021655864,"_shortName":"monster","_ancestorHashCodes":[1600484460],"_ancestorNames":["unitType"]}]},"searchExcludeTags":{"_tags":[]}}</t>
+          <t>{"guid":"f8947676-1084-4228-b991-1509cc7fe851","nodeType":1,"position":{"x":974.666748046875,"y":-2340.66650390625},"targetType":0,"assetTags":{"_tags":[]},"grantedTags":{"_tags":[]},"applicationRequiredTags":{"_tags":[]},"applicationImmunityTags":{"_tags":[]},"removeGameEffectsWithTags":{"_tags":[]},"durationType":0,"duration":"0","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"_tags":[]},"cancelOnAbilityEnd":true,"damageType":0,"damageSourceType":2,"damageFixedValue":10.0,"damageFormula":"","damageMMCType":0,"damageSetByCallerKey":"","damageMMCCaptureAttribute":1006,"damageMMCAttributeSource":0,"damageMMCCoefficient":1.0,"damageMMCUseSnapshot":true,"damageMultiplyByStackCount":false,"damageCalculationType":0,"enableHitKnockback":true,"knockbackDistance":1.0,"knockbackSpeed":12.0}</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>{"outputNodeGuid":"356907e0-1488-4128-bfcc-7ff73cfc3330","outputPortId":1004,"inputNodeGuid":"c28fb88d-51b1-47b2-be59-859e0ac638e3","inputPortId":7001}</t>
+          <t>{"outputNodeGuid":"356907e0-1488-4128-bfcc-7ff73cfc3330","outputPortId":1003,"inputNodeGuid":"9d6f459d-b588-4b64-843b-1b71e8f299ae","inputPortId":7001}</t>
         </is>
       </c>
       <c r="H68"/>
@@ -2303,16 +2303,16 @@
       <c r="C69"/>
       <c r="D69"/>
       <c r="E69">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>{"guid":"c353e286-8ef0-460a-b917-887f2aeb390a","nodeType":14,"position":{"x":1213.3333740234375,"y":-2354.0},"targetType":1,"requiredTags":{"_tags":[]},"immunityTags":{"_tags":[]},"destroyWithNode":false,"positionSource":2,"positionBindingName":"head","textType":0,"fixedText":"","contextDataKey":"DamageResult","textColor":{"r":1.0,"g":0.0,"b":0.0,"a":1.0},"criticalColor":{"r":1.0,"g":0.5,"b":0.0,"a":1.0},"missColor":{"r":0.5,"g":0.5,"b":0.5,"a":1.0},"fontSize":45.0,"criticalFontSize":60.0,"duration":1.5,"offset":{"x":0.0,"y":0.0},"moveDirection":{"x":0.0,"y":1.0}}</t>
+          <t>{"guid":"356907e0-1488-4128-bfcc-7ff73cfc3330","nodeType":0,"position":{"x":-843.3333740234375,"y":-2479.333251953125},"targetType":1,"skillId":1001,"assetTags":{"_tags":[]},"cancelAbilitiesWithTags":{"_tags":[]},"blockAbilitiesWithTags":{"_tags":[]},"activationOwnedTags":{"_tags":[]},"activationRequiredTags":{"_tags":[]},"activationBlockedTags":{"_tags":[{"_name":"CD.Sweep","_hashCode":-303359587,"_shortName":"Sweep","_ancestorHashCodes":[-1137859925],"_ancestorNames":["CD"]}]},"ongoingBlockedTags":{"_tags":[]},"eventOutputPorts":[]}</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>{"outputNodeGuid":"356907e0-1488-4128-bfcc-7ff73cfc3330","outputPortId":1003,"inputNodeGuid":"9d6f459d-b588-4b64-843b-1b71e8f299ae","inputPortId":7001}</t>
+          <t>{"outputNodeGuid":"e33ab94c-1496-4d6a-ba5e-1afd38bb0c30","outputPortId":4001,"inputNodeGuid":"f8947676-1084-4228-b991-1509cc7fe851","inputPortId":7001}</t>
         </is>
       </c>
       <c r="H69"/>
@@ -2323,16 +2323,16 @@
       <c r="C70"/>
       <c r="D70"/>
       <c r="E70">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>{"guid":"9d6f459d-b588-4b64-843b-1b71e8f299ae","nodeType":3,"position":{"x":-1130.6666259765625,"y":-2479.333251953125},"targetType":1,"assetTags":{"_tags":[]},"grantedTags":{"_tags":[]},"applicationRequiredTags":{"_tags":[]},"applicationImmunityTags":{"_tags":[]},"removeGameEffectsWithTags":{"_tags":[]},"durationType":0,"duration":"0","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[{"attrType":1003,"operation":0,"magnitudeSourceType":0,"fixedValue":-10.0,"formula":"","mmcType":0,"setByCallerKey":"","mmcCaptureAttribute":200,"mmcAttributeSource":0,"mmcCoefficient":1.0,"mmcUseSnapshot":true}],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"_tags":[]},"cancelOnAbilityEnd":true}</t>
+          <t>{"guid":"432ff1e3-b18d-476d-af80-d39ddc07402a","nodeType":20,"position":{"x":-414.0,"y":-2826.0},"targetType":1,"skeletonDataAsset":null,"skeletonDataAssetPath":"Assets/Res/Spine/SP_Zhanshi/SP_Zhanshi_SkeletonData.asset","animationName":"Skill_attack_1001","animationDuration":"18","isAnimationLooping":false,"timeEffects":[{"triggerTime":7,"portIdValue":2315086,"legacyPortId":"de0ba361-3aba-4ef0-bb07-9b418fcae591"},{"triggerTime":18,"portIdValue":2649436,"legacyPortId":"84e238a8-5baf-470e-829f-186695064945"}],"timeCues":[{"startTime":7,"endTime":48,"portIdValue":2287012,"legacyPortId":"8dea1941-c520-4f9a-aee0-40932c8542ef"}]}</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>{"outputNodeGuid":"432ff1e3-b18d-476d-af80-d39ddc07402a","outputPortId":2315086,"inputNodeGuid":"e33ab94c-1496-4d6a-ba5e-1afd38bb0c30","inputPortId":7001}</t>
+          <t>{"outputNodeGuid":"f8947676-1084-4228-b991-1509cc7fe851","outputPortId":3004,"inputNodeGuid":"c353e286-8ef0-460a-b917-887f2aeb390a","inputPortId":7001}</t>
         </is>
       </c>
       <c r="H70"/>
@@ -2343,16 +2343,16 @@
       <c r="C71"/>
       <c r="D71"/>
       <c r="E71">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>{"guid":"f8947676-1084-4228-b991-1509cc7fe851","nodeType":1,"position":{"x":974.666748046875,"y":-2340.66650390625},"targetType":0,"assetTags":{"_tags":[]},"grantedTags":{"_tags":[]},"applicationRequiredTags":{"_tags":[]},"applicationImmunityTags":{"_tags":[]},"removeGameEffectsWithTags":{"_tags":[]},"durationType":0,"duration":"0","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"_tags":[]},"cancelOnAbilityEnd":true,"damageType":0,"damageSourceType":2,"damageFixedValue":10.0,"damageFormula":"","damageMMCType":0,"damageSetByCallerKey":"","damageMMCCaptureAttribute":1006,"damageMMCAttributeSource":0,"damageMMCCoefficient":1.0,"damageMMCUseSnapshot":true,"damageMultiplyByStackCount":false,"damageCalculationType":0,"enableHitKnockback":true,"knockbackDistance":1.0,"knockbackSpeed":12.0}</t>
+          <t>{"guid":"c353e286-8ef0-460a-b917-887f2aeb390a","nodeType":14,"position":{"x":1213.3333740234375,"y":-2354.0},"targetType":1,"requiredTags":{"_tags":[]},"immunityTags":{"_tags":[]},"destroyWithNode":false,"positionSource":2,"positionBindingName":"head","textType":0,"fixedText":"","contextDataKey":"DamageResult","textColor":{"r":1.0,"g":0.0,"b":0.0,"a":1.0},"criticalColor":{"r":1.0,"g":0.5,"b":0.0,"a":1.0},"missColor":{"r":0.5,"g":0.5,"b":0.5,"a":1.0},"fontSize":45.0,"criticalFontSize":60.0,"duration":1.5,"offset":{"x":0.0,"y":0.0},"moveDirection":{"x":0.0,"y":1.0}}</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>{"outputNodeGuid":"e33ab94c-1496-4d6a-ba5e-1afd38bb0c30","outputPortId":4001,"inputNodeGuid":"f8947676-1084-4228-b991-1509cc7fe851","inputPortId":7001}</t>
+          <t>{"outputNodeGuid":"432ff1e3-b18d-476d-af80-d39ddc07402a","outputPortId":2287012,"inputNodeGuid":"cde57fb8-b693-4da8-a4a8-fd61e56c5dcd","inputPortId":7001}</t>
         </is>
       </c>
       <c r="H71"/>
@@ -2367,12 +2367,12 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>{"guid":"2cfdacd2-0186-49dd-b177-4eb8c0ad87bd","nodeType":7,"position":{"x":731.3333740234375,"y":-2082.0},"targetType":1,"endType":0}</t>
+          <t>{"guid":"2cfdacd2-0186-49dd-b177-4eb8c0ad87bd","nodeType":7,"position":{"x":731.3333740234375,"y":-2142.66650390625},"targetType":1,"endType":0}</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>{"outputNodeGuid":"f8947676-1084-4228-b991-1509cc7fe851","outputPortId":3004,"inputNodeGuid":"c353e286-8ef0-460a-b917-887f2aeb390a","inputPortId":7001}</t>
+          <t>{"outputNodeGuid":"432ff1e3-b18d-476d-af80-d39ddc07402a","outputPortId":2315086,"inputNodeGuid":"e33ab94c-1496-4d6a-ba5e-1afd38bb0c30","inputPortId":7001}</t>
         </is>
       </c>
       <c r="H72"/>
@@ -2383,11 +2383,11 @@
       <c r="C73"/>
       <c r="D73"/>
       <c r="E73">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>{"guid":"356907e0-1488-4128-bfcc-7ff73cfc3330","nodeType":0,"position":{"x":-850.0,"y":-2490.0},"targetType":1,"skillId":1001,"assetTags":{"_tags":[]},"cancelAbilitiesWithTags":{"_tags":[]},"blockAbilitiesWithTags":{"_tags":[]},"activationOwnedTags":{"_tags":[]},"activationRequiredTags":{"_tags":[]},"activationBlockedTags":{"_tags":[{"_name":"CD.Sweep","_hashCode":-303359587,"_shortName":"Sweep","_ancestorHashCodes":[-1137859925],"_ancestorNames":["CD"]}]},"ongoingBlockedTags":{"_tags":[]},"eventOutputPorts":[]}</t>
+          <t>{"guid":"cde57fb8-b693-4da8-a4a8-fd61e56c5dcd","nodeType":12,"position":{"x":731.3333740234375,"y":-2489.333251953125},"targetType":1,"requiredTags":{"_tags":[]},"immunityTags":{"_tags":[]},"destroyWithNode":false,"positionSource":0,"particlePrefab":null,"particlePrefabPath":"Assets/Res/Prefab/Effect/ef_Zhanshi_attack_02.prefab","particleBindingName":"down","particleOffset":{"x":5.0,"y":0.0,"z":0.0},"particleScale":{"x":1.0,"y":1.0,"z":1.0},"attachToTarget":false,"particleLoop":false}</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
@@ -2403,11 +2403,11 @@
       <c r="C74"/>
       <c r="D74"/>
       <c r="E74">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>{"guid":"432ff1e3-b18d-476d-af80-d39ddc07402a","nodeType":20,"position":{"x":-414.0,"y":-2826.0},"targetType":1,"skeletonDataAsset":null,"skeletonDataAssetPath":"Assets/Res/Spine/SP_Zhanshi/SP_Zhanshi_SkeletonData.asset","animationName":"Skill_attack_1001","animationDuration":"18","isAnimationLooping":true,"timeEffects":[{"triggerTime":7,"portIdValue":2315086,"legacyPortId":"de0ba361-3aba-4ef0-bb07-9b418fcae591"},{"triggerTime":18,"portIdValue":2649436,"legacyPortId":"84e238a8-5baf-470e-829f-186695064945"}],"timeCues":[{"startTime":7,"endTime":48,"portIdValue":2287012,"legacyPortId":"8dea1941-c520-4f9a-aee0-40932c8542ef"}]}</t>
+          <t>{"guid":"9d6f459d-b588-4b64-843b-1b71e8f299ae","nodeType":3,"position":{"x":-1130.6666259765625,"y":-2479.333251953125},"targetType":1,"assetTags":{"_tags":[]},"grantedTags":{"_tags":[]},"applicationRequiredTags":{"_tags":[]},"applicationImmunityTags":{"_tags":[]},"removeGameEffectsWithTags":{"_tags":[]},"durationType":0,"duration":"0","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[{"attrType":1003,"operation":0,"magnitudeSourceType":0,"fixedValue":-100.0,"formula":"","mmcType":0,"setByCallerKey":"","mmcCaptureAttribute":200,"mmcAttributeSource":0,"mmcCoefficient":1.0,"mmcUseSnapshot":true}],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"_tags":[]},"cancelOnAbilityEnd":true}</t>
         </is>
       </c>
       <c r="G74"/>

--- a/Design/Excel/ET/Datas/Game/SkillGraph.xlsx
+++ b/Design/Excel/ET/Datas/Game/SkillGraph.xlsx
@@ -1091,7 +1091,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>{"guid":"d5809887-df6e-4604-bd09-36cef191ce83","nodeType":0,"position":{"x":210.66668701171875,"y":114.66667175292969},"targetType":1,"skillId":2001,"assetTags":{"_tags":[]},"cancelAbilitiesWithTags":{"_tags":[]},"blockAbilitiesWithTags":{"_tags":[]},"activationOwnedTags":{"_tags":[]},"activationRequiredTags":{"_tags":[]},"activationBlockedTags":{"_tags":[]},"ongoingBlockedTags":{"_tags":[]},"eventOutputPorts":[{"eventType":2,"customEventTag":"","PortId":1103}]}</t>
+          <t>{"guid":"d5809887-df6e-4604-bd09-36cef191ce83","nodeType":0,"position":{"x":146.0,"y":124.66667175292969},"targetType":1,"skillId":2001,"assetTags":{"_tags":[]},"cancelAbilitiesWithTags":{"_tags":[]},"blockAbilitiesWithTags":{"_tags":[]},"activationOwnedTags":{"_tags":[]},"activationRequiredTags":{"_tags":[]},"activationBlockedTags":{"_tags":[]},"ongoingBlockedTags":{"_tags":[]},"eventOutputPorts":[{"eventType":2,"customEventTag":"","PortId":1103}]}</t>
         </is>
       </c>
       <c r="G9"/>
@@ -1797,16 +1797,16 @@
       </c>
       <c r="D44"/>
       <c r="E44">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>{"guid":"9d6f459d-b588-4b64-843b-1b71e8f299ae","nodeType":3,"position":{"x":-1186.6666259765625,"y":-2019.3333740234375},"targetType":1,"assetTags":{"_tags":[]},"grantedTags":{"_tags":[]},"applicationRequiredTags":{"_tags":[]},"applicationImmunityTags":{"_tags":[]},"removeGameEffectsWithTags":{"_tags":[]},"durationType":0,"duration":"0","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[{"attrType":100,"operation":0,"magnitudeSourceType":0,"fixedValue":10.0,"formula":"","mmcType":0,"setByCallerKey":"","mmcCaptureAttribute":200,"mmcAttributeSource":0,"mmcCoefficient":1.0,"mmcUseSnapshot":true}],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"_tags":[]},"cancelOnAbilityEnd":true}</t>
+          <t>{"guid":"011aad56-e96c-41eb-9d85-e793d74a40bb","nodeType":7,"position":{"x":-333.33331298828125,"y":-1780.0},"targetType":1,"endType":0}</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>{"outputNodeGuid":"356907e0-1488-4128-bfcc-7ff73cfc3330","outputPortId":1004,"inputNodeGuid":"c28fb88d-51b1-47b2-be59-859e0ac638e3","inputPortId":7001}</t>
+          <t>{"outputNodeGuid":"356907e0-1488-4128-bfcc-7ff73cfc3330","outputPortId":1003,"inputNodeGuid":"9d6f459d-b588-4b64-843b-1b71e8f299ae","inputPortId":7001}</t>
         </is>
       </c>
       <c r="H44"/>
@@ -1817,16 +1817,16 @@
       <c r="C45"/>
       <c r="D45"/>
       <c r="E45">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>{"guid":"5fb21a71-2fff-4477-b79b-4c1a8bc10f9a","nodeType":2,"position":{"x":-571.33331298828125,"y":-1987.3333740234375},"targetType":1,"assetTags":{"_tags":[]},"grantedTags":{"_tags":[]},"applicationRequiredTags":{"_tags":[]},"applicationImmunityTags":{"_tags":[]},"removeGameEffectsWithTags":{"_tags":[]},"durationType":0,"duration":"0","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"_tags":[]},"cancelOnAbilityEnd":false,"healSourceType":0,"healFixedValue":10.0,"healFormula":"","healMMCType":0,"healSetByCallerKey":"","healMMCCaptureAttribute":202,"healMMCAttributeSource":0,"healMMCCoefficient":1.0,"healMMCUseSnapshot":true,"healMultiplyByStackCount":false,"healCalculationType":0}</t>
+          <t>{"guid":"cde57fb8-b693-4da8-a4a8-fd61e56c5dcd","nodeType":12,"position":{"x":-304.0,"y":-2072.0},"targetType":1,"requiredTags":{"_tags":[]},"immunityTags":{"_tags":[]},"destroyWithNode":false,"positionSource":0,"particlePrefab":null,"particlePrefabPath":"Assets/Res/Prefab/Effect/ef_skill_zhanshi_huifunengliang.prefab","particleBindingName":"down","particleOffset":{"x":0.0,"y":0.0,"z":0.0},"particleScale":{"x":1.0,"y":1.0,"z":1.0},"attachToTarget":false,"particleLoop":false}</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>{"outputNodeGuid":"356907e0-1488-4128-bfcc-7ff73cfc3330","outputPortId":1003,"inputNodeGuid":"9d6f459d-b588-4b64-843b-1b71e8f299ae","inputPortId":7001}</t>
+          <t>{"outputNodeGuid":"6d127270-5aeb-4542-9183-8d2d028d6786","outputPortId":3001,"inputNodeGuid":"cde57fb8-b693-4da8-a4a8-fd61e56c5dcd","inputPortId":7001}</t>
         </is>
       </c>
       <c r="H45"/>
@@ -1837,16 +1837,16 @@
       <c r="C46"/>
       <c r="D46"/>
       <c r="E46">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>{"guid":"011aad56-e96c-41eb-9d85-e793d74a40bb","nodeType":7,"position":{"x":-333.33331298828125,"y":-1780.0},"targetType":1,"endType":0}</t>
+          <t>{"guid":"becb4d53-8a9e-4dc0-95a3-618d1e79ecc7","nodeType":14,"position":{"x":-313.33331298828125,"y":-1951.3333740234375},"targetType":1,"requiredTags":{"_tags":[]},"immunityTags":{"_tags":[]},"destroyWithNode":false,"positionSource":2,"positionBindingName":"head","textType":1,"fixedText":"","contextDataKey":"Heal","textColor":{"r":0.0,"g":1.0,"b":0.10971927642822266,"a":1.0},"criticalColor":{"r":1.0,"g":0.5,"b":0.0,"a":1.0},"missColor":{"r":0.5,"g":0.5,"b":0.5,"a":1.0},"fontSize":45.0,"criticalFontSize":60.0,"duration":1.5,"offset":{"x":0.0,"y":0.0},"moveDirection":{"x":0.0,"y":1.0}}</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>{"outputNodeGuid":"356907e0-1488-4128-bfcc-7ff73cfc3330","outputPortId":1001,"inputNodeGuid":"5fb21a71-2fff-4477-b79b-4c1a8bc10f9a","inputPortId":7001}</t>
+          <t>{"outputNodeGuid":"6d127270-5aeb-4542-9183-8d2d028d6786","outputPortId":3004,"inputNodeGuid":"becb4d53-8a9e-4dc0-95a3-618d1e79ecc7","inputPortId":7001}</t>
         </is>
       </c>
       <c r="H46"/>
@@ -1857,16 +1857,16 @@
       <c r="C47"/>
       <c r="D47"/>
       <c r="E47">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>{"guid":"c28fb88d-51b1-47b2-be59-859e0ac638e3","nodeType":10,"position":{"x":-1223.3333740234375,"y":-1826.666748046875},"targetType":1,"assetTags":{"_tags":[]},"grantedTags":{"_tags":[{"_name":"CD.RecBlood","_hashCode":1163914435,"_shortName":"回血","_ancestorHashCodes":[-1137859925],"_ancestorNames":["CD"]}]},"applicationRequiredTags":{"_tags":[]},"applicationImmunityTags":{"_tags":[]},"removeGameEffectsWithTags":{"_tags":[]},"durationType":1,"duration":"3","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"_tags":[]},"cancelOnAbilityEnd":false,"cooldownType":0,"maxCharges":2,"chargeTime":"10"}</t>
+          <t>{"guid":"356907e0-1488-4128-bfcc-7ff73cfc3330","nodeType":0,"position":{"x":-924.6666259765625,"y":-1886.666748046875},"targetType":1,"skillId":1007,"assetTags":{"_tags":[]},"cancelAbilitiesWithTags":{"_tags":[]},"blockAbilitiesWithTags":{"_tags":[]},"activationOwnedTags":{"_tags":[]},"activationRequiredTags":{"_tags":[]},"activationBlockedTags":{"_tags":[{"_name":"CD.RecBlood","_hashCode":1163914435,"_shortName":"回血","_ancestorHashCodes":[-1137859925],"_ancestorNames":["CD"]}]},"ongoingBlockedTags":{"_tags":[]},"eventOutputPorts":[]}</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>{"outputNodeGuid":"5fb21a71-2fff-4477-b79b-4c1a8bc10f9a","outputPortId":3001,"inputNodeGuid":"cde57fb8-b693-4da8-a4a8-fd61e56c5dcd","inputPortId":7001}</t>
+          <t>{"outputNodeGuid":"356907e0-1488-4128-bfcc-7ff73cfc3330","outputPortId":1001,"inputNodeGuid":"6d127270-5aeb-4542-9183-8d2d028d6786","inputPortId":7001}</t>
         </is>
       </c>
       <c r="H47"/>
@@ -1877,16 +1877,16 @@
       <c r="C48"/>
       <c r="D48"/>
       <c r="E48">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>{"guid":"356907e0-1488-4128-bfcc-7ff73cfc3330","nodeType":0,"position":{"x":-902.6666259765625,"y":-1844.0},"targetType":1,"skillId":1007,"assetTags":{"_tags":[]},"cancelAbilitiesWithTags":{"_tags":[]},"blockAbilitiesWithTags":{"_tags":[]},"activationOwnedTags":{"_tags":[]},"activationRequiredTags":{"_tags":[]},"activationBlockedTags":{"_tags":[{"_name":"CD.RecBlood","_hashCode":1163914435,"_shortName":"回血","_ancestorHashCodes":[-1137859925],"_ancestorNames":["CD"]}]},"ongoingBlockedTags":{"_tags":[]},"eventOutputPorts":[]}</t>
+          <t>{"guid":"c28fb88d-51b1-47b2-be59-859e0ac638e3","nodeType":10,"position":{"x":-1156.0,"y":-1801.3333740234375},"targetType":1,"assetTags":{"_tags":[]},"grantedTags":{"_tags":[{"_name":"CD.RecBlood","_hashCode":1163914435,"_shortName":"回血","_ancestorHashCodes":[-1137859925],"_ancestorNames":["CD"]}]},"applicationRequiredTags":{"_tags":[]},"applicationImmunityTags":{"_tags":[]},"removeGameEffectsWithTags":{"_tags":[]},"durationType":1,"duration":"3","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"_tags":[]},"cancelOnAbilityEnd":false,"cooldownType":0,"maxCharges":2,"chargeTime":"10"}</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>{"outputNodeGuid":"5fb21a71-2fff-4477-b79b-4c1a8bc10f9a","outputPortId":3004,"inputNodeGuid":"011aad56-e96c-41eb-9d85-e793d74a40bb","inputPortId":7001}</t>
+          <t>{"outputNodeGuid":"356907e0-1488-4128-bfcc-7ff73cfc3330","outputPortId":1004,"inputNodeGuid":"c28fb88d-51b1-47b2-be59-859e0ac638e3","inputPortId":7001}</t>
         </is>
       </c>
       <c r="H48"/>
@@ -1897,16 +1897,16 @@
       <c r="C49"/>
       <c r="D49"/>
       <c r="E49">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>{"guid":"cde57fb8-b693-4da8-a4a8-fd61e56c5dcd","nodeType":12,"position":{"x":-304.0,"y":-2072.0},"targetType":1,"requiredTags":{"_tags":[]},"immunityTags":{"_tags":[]},"destroyWithNode":false,"positionSource":0,"particlePrefab":null,"particlePrefabPath":"Assets/Res/Prefab/Effect/ef_skill_zhanshi_huifunengliang.prefab","particleBindingName":"down","particleOffset":{"x":0.0,"y":0.0,"z":0.0},"particleScale":{"x":1.0,"y":1.0,"z":1.0},"attachToTarget":false,"particleLoop":false}</t>
+          <t>{"guid":"6d127270-5aeb-4542-9183-8d2d028d6786","nodeType":2,"position":{"x":-551.33331298828125,"y":-2050.0},"targetType":1,"assetTags":{"_tags":[]},"grantedTags":{"_tags":[]},"applicationRequiredTags":{"_tags":[]},"applicationImmunityTags":{"_tags":[]},"removeGameEffectsWithTags":{"_tags":[]},"durationType":0,"duration":"0","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"_tags":[]},"cancelOnAbilityEnd":false,"healSourceType":0,"healFixedValue":10.0,"healFormula":"","healMMCType":0,"healSetByCallerKey":"","healMMCCaptureAttribute":1007,"healMMCAttributeSource":0,"healMMCCoefficient":1.0,"healMMCUseSnapshot":true,"healMultiplyByStackCount":false,"healCalculationType":0}</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>{"outputNodeGuid":"5fb21a71-2fff-4477-b79b-4c1a8bc10f9a","outputPortId":3004,"inputNodeGuid":"becb4d53-8a9e-4dc0-95a3-618d1e79ecc7","inputPortId":7001}</t>
+          <t>{"outputNodeGuid":"6d127270-5aeb-4542-9183-8d2d028d6786","outputPortId":3004,"inputNodeGuid":"011aad56-e96c-41eb-9d85-e793d74a40bb","inputPortId":7001}</t>
         </is>
       </c>
       <c r="H49"/>
@@ -1917,11 +1917,11 @@
       <c r="C50"/>
       <c r="D50"/>
       <c r="E50">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>{"guid":"becb4d53-8a9e-4dc0-95a3-618d1e79ecc7","nodeType":14,"position":{"x":-313.33331298828125,"y":-1951.3333740234375},"targetType":1,"requiredTags":{"_tags":[]},"immunityTags":{"_tags":[]},"destroyWithNode":false,"positionSource":2,"positionBindingName":"head","textType":1,"fixedText":"","contextDataKey":"Heal","textColor":{"r":0.0,"g":1.0,"b":0.10971927642822266,"a":1.0},"criticalColor":{"r":1.0,"g":0.5,"b":0.0,"a":1.0},"missColor":{"r":0.5,"g":0.5,"b":0.5,"a":1.0},"fontSize":45.0,"criticalFontSize":60.0,"duration":1.5,"offset":{"x":0.0,"y":0.0},"moveDirection":{"x":0.0,"y":1.0}}</t>
+          <t>{"guid":"9d6f459d-b588-4b64-843b-1b71e8f299ae","nodeType":3,"position":{"x":-1223.3333740234375,"y":-2020.666748046875},"targetType":1,"assetTags":{"_tags":[]},"grantedTags":{"_tags":[]},"applicationRequiredTags":{"_tags":[]},"applicationImmunityTags":{"_tags":[]},"removeGameEffectsWithTags":{"_tags":[]},"durationType":0,"duration":"0","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[{"attrType":1003,"operation":0,"magnitudeSourceType":0,"fixedValue":100.0,"formula":"","mmcType":0,"setByCallerKey":"","mmcCaptureAttribute":200,"mmcAttributeSource":0,"mmcCoefficient":1.0,"mmcUseSnapshot":true}],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"_tags":[]},"cancelOnAbilityEnd":true}</t>
         </is>
       </c>
       <c r="G50"/>
@@ -2243,11 +2243,11 @@
       </c>
       <c r="D66"/>
       <c r="E66">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>{"guid":"c28fb88d-51b1-47b2-be59-859e0ac638e3","nodeType":10,"position":{"x":-1130.6666259765625,"y":-2232.0},"targetType":1,"assetTags":{"_tags":[]},"grantedTags":{"_tags":[{"_name":"CD.Sweep","_hashCode":-303359587,"_shortName":"Sweep","_ancestorHashCodes":[-1137859925],"_ancestorNames":["CD"]}]},"applicationRequiredTags":{"_tags":[]},"applicationImmunityTags":{"_tags":[]},"removeGameEffectsWithTags":{"_tags":[]},"durationType":1,"duration":"1","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"_tags":[]},"cancelOnAbilityEnd":false,"cooldownType":0,"maxCharges":2,"chargeTime":"10"}</t>
+          <t>{"guid":"e33ab94c-1496-4d6a-ba5e-1afd38bb0c30","nodeType":4,"position":{"x":731.3333740234375,"y":-2344.0},"targetType":1,"searchShapeType":1,"searchLineType":0,"positionSource":0,"positionBindingName":"center","searchCircleRadius":5.0,"searchSectorRadius":2.0,"searchSectorAngle":180.0,"searchLineDirectionOffsetAngle":0.0,"searchLineDirectionWidth":1.0,"searchLineDirectionLength":10.0,"lineStartPositionSource":0,"lineStartBindingName":"","lineEndPositionSource":1,"lineEndBindingName":"","searchLineBetweenWidth":1.0,"searchLineAbsoluteAngle":0.0,"searchLineAbsoluteWidth":1.0,"searchLineAbsoluteLength":10.0,"maxTargets":999,"searchTargetTags":{"_tags":[{"_name":"unitType.monster","_hashCode":-2021655864,"_shortName":"monster","_ancestorHashCodes":[1600484460],"_ancestorNames":["unitType"]}]},"searchExcludeTags":{"_tags":[]}}</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
@@ -2263,11 +2263,11 @@
       <c r="C67"/>
       <c r="D67"/>
       <c r="E67">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>{"guid":"e33ab94c-1496-4d6a-ba5e-1afd38bb0c30","nodeType":4,"position":{"x":731.3333740234375,"y":-2344.0},"targetType":1,"searchShapeType":1,"searchLineType":0,"positionSource":0,"positionBindingName":"center","searchCircleRadius":5.0,"searchSectorRadius":2.0,"searchSectorAngle":180.0,"searchLineDirectionOffsetAngle":0.0,"searchLineDirectionWidth":1.0,"searchLineDirectionLength":10.0,"lineStartPositionSource":0,"lineStartBindingName":"","lineEndPositionSource":1,"lineEndBindingName":"","searchLineBetweenWidth":1.0,"searchLineAbsoluteAngle":0.0,"searchLineAbsoluteWidth":1.0,"searchLineAbsoluteLength":10.0,"maxTargets":999,"searchTargetTags":{"_tags":[{"_name":"unitType.monster","_hashCode":-2021655864,"_shortName":"monster","_ancestorHashCodes":[1600484460],"_ancestorNames":["unitType"]}]},"searchExcludeTags":{"_tags":[]}}</t>
+          <t>{"guid":"f8947676-1084-4228-b991-1509cc7fe851","nodeType":1,"position":{"x":974.666748046875,"y":-2340.66650390625},"targetType":0,"assetTags":{"_tags":[]},"grantedTags":{"_tags":[]},"applicationRequiredTags":{"_tags":[]},"applicationImmunityTags":{"_tags":[]},"removeGameEffectsWithTags":{"_tags":[]},"durationType":0,"duration":"0","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"_tags":[]},"cancelOnAbilityEnd":true,"damageType":0,"damageSourceType":2,"damageFixedValue":10.0,"damageFormula":"","damageMMCType":0,"damageSetByCallerKey":"","damageMMCCaptureAttribute":1006,"damageMMCAttributeSource":0,"damageMMCCoefficient":1.0,"damageMMCUseSnapshot":true,"damageMultiplyByStackCount":false,"damageCalculationType":0,"enableHitKnockback":true,"knockbackDistance":1.0,"knockbackSpeed":12.0}</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
@@ -2283,11 +2283,11 @@
       <c r="C68"/>
       <c r="D68"/>
       <c r="E68">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>{"guid":"f8947676-1084-4228-b991-1509cc7fe851","nodeType":1,"position":{"x":974.666748046875,"y":-2340.66650390625},"targetType":0,"assetTags":{"_tags":[]},"grantedTags":{"_tags":[]},"applicationRequiredTags":{"_tags":[]},"applicationImmunityTags":{"_tags":[]},"removeGameEffectsWithTags":{"_tags":[]},"durationType":0,"duration":"0","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"_tags":[]},"cancelOnAbilityEnd":true,"damageType":0,"damageSourceType":2,"damageFixedValue":10.0,"damageFormula":"","damageMMCType":0,"damageSetByCallerKey":"","damageMMCCaptureAttribute":1006,"damageMMCAttributeSource":0,"damageMMCCoefficient":1.0,"damageMMCUseSnapshot":true,"damageMultiplyByStackCount":false,"damageCalculationType":0,"enableHitKnockback":true,"knockbackDistance":1.0,"knockbackSpeed":12.0}</t>
+          <t>{"guid":"c353e286-8ef0-460a-b917-887f2aeb390a","nodeType":14,"position":{"x":1213.3333740234375,"y":-2354.0},"targetType":1,"requiredTags":{"_tags":[]},"immunityTags":{"_tags":[]},"destroyWithNode":false,"positionSource":2,"positionBindingName":"head","textType":0,"fixedText":"","contextDataKey":"DamageResult","textColor":{"r":1.0,"g":0.0,"b":0.0,"a":1.0},"criticalColor":{"r":1.0,"g":0.5,"b":0.0,"a":1.0},"missColor":{"r":0.5,"g":0.5,"b":0.5,"a":1.0},"fontSize":45.0,"criticalFontSize":60.0,"duration":1.5,"offset":{"x":0.0,"y":0.0},"moveDirection":{"x":0.0,"y":1.0}}</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
@@ -2303,11 +2303,11 @@
       <c r="C69"/>
       <c r="D69"/>
       <c r="E69">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>{"guid":"356907e0-1488-4128-bfcc-7ff73cfc3330","nodeType":0,"position":{"x":-843.3333740234375,"y":-2479.333251953125},"targetType":1,"skillId":1001,"assetTags":{"_tags":[]},"cancelAbilitiesWithTags":{"_tags":[]},"blockAbilitiesWithTags":{"_tags":[]},"activationOwnedTags":{"_tags":[]},"activationRequiredTags":{"_tags":[]},"activationBlockedTags":{"_tags":[{"_name":"CD.Sweep","_hashCode":-303359587,"_shortName":"Sweep","_ancestorHashCodes":[-1137859925],"_ancestorNames":["CD"]}]},"ongoingBlockedTags":{"_tags":[]},"eventOutputPorts":[]}</t>
+          <t>{"guid":"2cfdacd2-0186-49dd-b177-4eb8c0ad87bd","nodeType":7,"position":{"x":731.3333740234375,"y":-2142.66650390625},"targetType":1,"endType":0}</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
@@ -2323,11 +2323,11 @@
       <c r="C70"/>
       <c r="D70"/>
       <c r="E70">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>{"guid":"432ff1e3-b18d-476d-af80-d39ddc07402a","nodeType":20,"position":{"x":-414.0,"y":-2826.0},"targetType":1,"skeletonDataAsset":null,"skeletonDataAssetPath":"Assets/Res/Spine/SP_Zhanshi/SP_Zhanshi_SkeletonData.asset","animationName":"Skill_attack_1001","animationDuration":"18","isAnimationLooping":false,"timeEffects":[{"triggerTime":7,"portIdValue":2315086,"legacyPortId":"de0ba361-3aba-4ef0-bb07-9b418fcae591"},{"triggerTime":18,"portIdValue":2649436,"legacyPortId":"84e238a8-5baf-470e-829f-186695064945"}],"timeCues":[{"startTime":7,"endTime":48,"portIdValue":2287012,"legacyPortId":"8dea1941-c520-4f9a-aee0-40932c8542ef"}]}</t>
+          <t>{"guid":"c28fb88d-51b1-47b2-be59-859e0ac638e3","nodeType":10,"position":{"x":-1130.6666259765625,"y":-2232.0},"targetType":1,"assetTags":{"_tags":[]},"grantedTags":{"_tags":[{"_name":"CD.Sweep","_hashCode":-303359587,"_shortName":"Sweep","_ancestorHashCodes":[-1137859925],"_ancestorNames":["CD"]}]},"applicationRequiredTags":{"_tags":[]},"applicationImmunityTags":{"_tags":[]},"removeGameEffectsWithTags":{"_tags":[]},"durationType":1,"duration":"1","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"_tags":[]},"cancelOnAbilityEnd":false,"cooldownType":0,"maxCharges":2,"chargeTime":"10"}</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
@@ -2343,11 +2343,11 @@
       <c r="C71"/>
       <c r="D71"/>
       <c r="E71">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>{"guid":"c353e286-8ef0-460a-b917-887f2aeb390a","nodeType":14,"position":{"x":1213.3333740234375,"y":-2354.0},"targetType":1,"requiredTags":{"_tags":[]},"immunityTags":{"_tags":[]},"destroyWithNode":false,"positionSource":2,"positionBindingName":"head","textType":0,"fixedText":"","contextDataKey":"DamageResult","textColor":{"r":1.0,"g":0.0,"b":0.0,"a":1.0},"criticalColor":{"r":1.0,"g":0.5,"b":0.0,"a":1.0},"missColor":{"r":0.5,"g":0.5,"b":0.5,"a":1.0},"fontSize":45.0,"criticalFontSize":60.0,"duration":1.5,"offset":{"x":0.0,"y":0.0},"moveDirection":{"x":0.0,"y":1.0}}</t>
+          <t>{"guid":"356907e0-1488-4128-bfcc-7ff73cfc3330","nodeType":0,"position":{"x":-843.3333740234375,"y":-2479.333251953125},"targetType":1,"skillId":1001,"assetTags":{"_tags":[]},"cancelAbilitiesWithTags":{"_tags":[]},"blockAbilitiesWithTags":{"_tags":[]},"activationOwnedTags":{"_tags":[]},"activationRequiredTags":{"_tags":[]},"activationBlockedTags":{"_tags":[{"_name":"CD.Sweep","_hashCode":-303359587,"_shortName":"Sweep","_ancestorHashCodes":[-1137859925],"_ancestorNames":["CD"]}]},"ongoingBlockedTags":{"_tags":[]},"eventOutputPorts":[]}</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
@@ -2363,11 +2363,11 @@
       <c r="C72"/>
       <c r="D72"/>
       <c r="E72">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>{"guid":"2cfdacd2-0186-49dd-b177-4eb8c0ad87bd","nodeType":7,"position":{"x":731.3333740234375,"y":-2142.66650390625},"targetType":1,"endType":0}</t>
+          <t>{"guid":"432ff1e3-b18d-476d-af80-d39ddc07402a","nodeType":20,"position":{"x":-415.33331298828125,"y":-2827.333251953125},"targetType":1,"skeletonDataAsset":null,"skeletonDataAssetPath":"Assets/Res/Spine/SP_Zhanshi/SP_Zhanshi_SkeletonData.asset","animationName":"Skill_attack_1001","animationDuration":"18","isAnimationLooping":false,"timeEffects":[{"triggerTime":7,"portIdValue":2315086,"legacyPortId":"de0ba361-3aba-4ef0-bb07-9b418fcae591"},{"triggerTime":18,"portIdValue":2649436,"legacyPortId":"84e238a8-5baf-470e-829f-186695064945"}],"timeCues":[{"startTime":7,"endTime":48,"portIdValue":2287012,"legacyPortId":"8dea1941-c520-4f9a-aee0-40932c8542ef"}]}</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
@@ -2387,7 +2387,7 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>{"guid":"cde57fb8-b693-4da8-a4a8-fd61e56c5dcd","nodeType":12,"position":{"x":731.3333740234375,"y":-2489.333251953125},"targetType":1,"requiredTags":{"_tags":[]},"immunityTags":{"_tags":[]},"destroyWithNode":false,"positionSource":0,"particlePrefab":null,"particlePrefabPath":"Assets/Res/Prefab/Effect/ef_Zhanshi_attack_02.prefab","particleBindingName":"down","particleOffset":{"x":5.0,"y":0.0,"z":0.0},"particleScale":{"x":1.0,"y":1.0,"z":1.0},"attachToTarget":false,"particleLoop":false}</t>
+          <t>{"guid":"cde57fb8-b693-4da8-a4a8-fd61e56c5dcd","nodeType":12,"position":{"x":731.3333740234375,"y":-2490.66650390625},"targetType":1,"requiredTags":{"_tags":[]},"immunityTags":{"_tags":[]},"destroyWithNode":false,"positionSource":0,"particlePrefab":null,"particlePrefabPath":"Assets/Res/Prefab/Effect/ef_Zhanshi_attack_02.prefab","particleBindingName":"down","particleOffset":{"x":5.0,"y":0.0,"z":0.0},"particleScale":{"x":1.0,"y":1.0,"z":1.0},"attachToTarget":false,"particleLoop":false}</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
@@ -2407,7 +2407,7 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>{"guid":"9d6f459d-b588-4b64-843b-1b71e8f299ae","nodeType":3,"position":{"x":-1130.6666259765625,"y":-2479.333251953125},"targetType":1,"assetTags":{"_tags":[]},"grantedTags":{"_tags":[]},"applicationRequiredTags":{"_tags":[]},"applicationImmunityTags":{"_tags":[]},"removeGameEffectsWithTags":{"_tags":[]},"durationType":0,"duration":"0","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[{"attrType":1003,"operation":0,"magnitudeSourceType":0,"fixedValue":-100.0,"formula":"","mmcType":0,"setByCallerKey":"","mmcCaptureAttribute":200,"mmcAttributeSource":0,"mmcCoefficient":1.0,"mmcUseSnapshot":true}],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"_tags":[]},"cancelOnAbilityEnd":true}</t>
+          <t>{"guid":"9d6f459d-b588-4b64-843b-1b71e8f299ae","nodeType":3,"position":{"x":-1130.6666259765625,"y":-2479.333251953125},"targetType":1,"assetTags":{"_tags":[]},"grantedTags":{"_tags":[]},"applicationRequiredTags":{"_tags":[]},"applicationImmunityTags":{"_tags":[]},"removeGameEffectsWithTags":{"_tags":[]},"durationType":0,"duration":"0","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[{"attrType":1003,"operation":0,"magnitudeSourceType":0,"fixedValue":-10.0,"formula":"","mmcType":0,"setByCallerKey":"","mmcCaptureAttribute":200,"mmcAttributeSource":0,"mmcCoefficient":1.0,"mmcUseSnapshot":true}],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"_tags":[]},"cancelOnAbilityEnd":true}</t>
         </is>
       </c>
       <c r="G74"/>

--- a/Design/Excel/ET/Datas/Game/SkillGraph.xlsx
+++ b/Design/Excel/ET/Datas/Game/SkillGraph.xlsx
@@ -789,11 +789,11 @@
       </c>
       <c r="D10"/>
       <c r="E10">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>{"guid":"cde57fb8-b693-4da8-a4a8-fd61e56c5dcd","nodeType":12,"position":{"x":677.3333740234375,"y":-1998.666748046875},"targetType":1,"requiredTags":{"_tags":[]},"immunityTags":{"_tags":[]},"destroyWithNode":false,"positionSource":0,"particlePrefab":null,"particlePrefabPath":"Assets/Res/Prefab/Effect/ef_Zhanshi_attack_02.prefab","particleBindingName":"down","particleOffset":{"x":0.0,"y":0.0,"z":0.0},"particleScale":{"x":1.0,"y":1.0,"z":1.0},"attachToTarget":false,"particleLoop":false}</t>
+          <t>{"guid":"9d6f459d-b588-4b64-843b-1b71e8f299ae","nodeType":3,"position":{"x":-1186.6666259765625,"y":-2019.3333740234375},"targetType":1,"assetTags":{"_tags":[]},"grantedTags":{"_tags":[]},"applicationRequiredTags":{"_tags":[]},"applicationImmunityTags":{"_tags":[]},"removeGameEffectsWithTags":{"_tags":[]},"durationType":0,"duration":"0","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[{"attrType":100,"operation":0,"magnitudeSourceType":0,"fixedValue":10.0,"formula":"","mmcType":0,"setByCallerKey":"","mmcCaptureAttribute":200,"mmcAttributeSource":0,"mmcCoefficient":1.0,"mmcUseSnapshot":true}],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"_tags":[]},"cancelOnAbilityEnd":true}</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -809,11 +809,11 @@
       <c r="C11"/>
       <c r="D11"/>
       <c r="E11">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>{"guid":"9d6f459d-b588-4b64-843b-1b71e8f299ae","nodeType":3,"position":{"x":-1186.6666259765625,"y":-2019.3333740234375},"targetType":1,"assetTags":{"_tags":[]},"grantedTags":{"_tags":[]},"applicationRequiredTags":{"_tags":[]},"applicationImmunityTags":{"_tags":[]},"removeGameEffectsWithTags":{"_tags":[]},"durationType":0,"duration":"0","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[{"attrType":100,"operation":0,"magnitudeSourceType":0,"fixedValue":10.0,"formula":"","mmcType":0,"setByCallerKey":"","mmcCaptureAttribute":200,"mmcAttributeSource":0,"mmcCoefficient":1.0,"mmcUseSnapshot":true}],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"_tags":[]},"cancelOnAbilityEnd":true}</t>
+          <t>{"guid":"c28fb88d-51b1-47b2-be59-859e0ac638e3","nodeType":10,"position":{"x":-1186.6666259765625,"y":-1825.3333740234375},"targetType":1,"assetTags":{"_tags":[]},"grantedTags":{"_tags":[{"_name":"CD.Blood","_hashCode":274000851,"_shortName":"Blood","_ancestorHashCodes":[-1137859925],"_ancestorNames":["CD"]}]},"applicationRequiredTags":{"_tags":[]},"applicationImmunityTags":{"_tags":[]},"removeGameEffectsWithTags":{"_tags":[]},"durationType":1,"duration":"3","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"_tags":[]},"cancelOnAbilityEnd":false,"cooldownType":0,"maxCharges":2,"chargeTime":"10"}</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -829,11 +829,11 @@
       <c r="C12"/>
       <c r="D12"/>
       <c r="E12">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>{"guid":"c28fb88d-51b1-47b2-be59-859e0ac638e3","nodeType":10,"position":{"x":-1186.6666259765625,"y":-1825.3333740234375},"targetType":1,"assetTags":{"_tags":[]},"grantedTags":{"_tags":[{"_name":"CD.Blood","_hashCode":274000851,"_shortName":"Blood","_ancestorHashCodes":[-1137859925],"_ancestorNames":["CD"]}]},"applicationRequiredTags":{"_tags":[]},"applicationImmunityTags":{"_tags":[]},"removeGameEffectsWithTags":{"_tags":[]},"durationType":1,"duration":"3","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"_tags":[]},"cancelOnAbilityEnd":false,"cooldownType":0,"maxCharges":2,"chargeTime":"10"}</t>
+          <t>{"guid":"c353e286-8ef0-460a-b917-887f2aeb390a","nodeType":14,"position":{"x":383.33334350585938,"y":-1531.3333740234375},"targetType":1,"requiredTags":{"_tags":[]},"immunityTags":{"_tags":[]},"destroyWithNode":false,"positionSource":2,"positionBindingName":"head","textType":0,"fixedText":"","contextDataKey":"DamageResult","textColor":{"r":1.0,"g":0.0,"b":0.0,"a":1.0},"criticalColor":{"r":1.0,"g":0.5,"b":0.0,"a":1.0},"missColor":{"r":0.5,"g":0.5,"b":0.5,"a":1.0},"fontSize":45.0,"criticalFontSize":60.0,"duration":1.5,"offset":{"x":0.0,"y":0.0},"moveDirection":{"x":0.0,"y":1.0}}</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -849,11 +849,11 @@
       <c r="C13"/>
       <c r="D13"/>
       <c r="E13">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>{"guid":"c353e286-8ef0-460a-b917-887f2aeb390a","nodeType":14,"position":{"x":383.33334350585938,"y":-1531.3333740234375},"targetType":1,"requiredTags":{"_tags":[]},"immunityTags":{"_tags":[]},"destroyWithNode":false,"positionSource":2,"positionBindingName":"head","textType":0,"fixedText":"","contextDataKey":"DamageResult","textColor":{"r":1.0,"g":0.0,"b":0.0,"a":1.0},"criticalColor":{"r":1.0,"g":0.5,"b":0.0,"a":1.0},"missColor":{"r":0.5,"g":0.5,"b":0.5,"a":1.0},"fontSize":45.0,"criticalFontSize":60.0,"duration":1.5,"offset":{"x":0.0,"y":0.0},"moveDirection":{"x":0.0,"y":1.0}}</t>
+          <t>{"guid":"011aad56-e96c-41eb-9d85-e793d74a40bb","nodeType":7,"position":{"x":677.3333740234375,"y":-1879.3333740234375},"targetType":1,"endType":0}</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -869,11 +869,11 @@
       <c r="C14"/>
       <c r="D14"/>
       <c r="E14">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>{"guid":"011aad56-e96c-41eb-9d85-e793d74a40bb","nodeType":7,"position":{"x":677.3333740234375,"y":-1879.3333740234375},"targetType":1,"endType":0}</t>
+          <t>{"guid":"432ff1e3-b18d-476d-af80-d39ddc07402a","nodeType":20,"position":{"x":-472.0,"y":-2380.66650390625},"targetType":1,"skeletonDataAsset":null,"skeletonDataAssetPath":"Assets/Res/Spine/SP_Zhanshi/SP_Zhanshi_SkeletonData.asset","animationName":"Attack_02","animationDuration":"22","isAnimationLooping":false,"timeEffects":[{"triggerTime":7,"portIdValue":2315086,"legacyPortId":"de0ba361-3aba-4ef0-bb07-9b418fcae591"},{"triggerTime":22,"portIdValue":2821173,"legacyPortId":"97dc121c-84b7-4f94-9997-02e0e5b2ea6c"}],"timeCues":[{"startTime":7,"endTime":48,"portIdValue":2287012,"legacyPortId":"8dea1941-c520-4f9a-aee0-40932c8542ef"}]}</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -889,11 +889,11 @@
       <c r="C15"/>
       <c r="D15"/>
       <c r="E15">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>{"guid":"f8947676-1084-4228-b991-1509cc7fe851","nodeType":1,"position":{"x":195.33334350585938,"y":-1761.3333740234375},"targetType":0,"assetTags":{"_tags":[]},"grantedTags":{"_tags":[]},"applicationRequiredTags":{"_tags":[]},"applicationImmunityTags":{"_tags":[]},"removeGameEffectsWithTags":{"_tags":[]},"durationType":0,"duration":"0","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"_tags":[]},"cancelOnAbilityEnd":true,"damageType":0,"damageSourceType":0,"damageFixedValue":3.0,"damageFormula":"","damageMMCType":0,"damageSetByCallerKey":"","damageMMCCaptureAttribute":200,"damageMMCAttributeSource":0,"damageMMCCoefficient":1.0,"damageMMCUseSnapshot":true,"damageMultiplyByStackCount":true,"damageCalculationType":0,"enableHitKnockback":false,"knockbackDistance":1.0,"knockbackSpeed":12.0}</t>
+          <t>{"guid":"356907e0-1488-4128-bfcc-7ff73cfc3330","nodeType":0,"position":{"x":-878.6666259765625,"y":-1853.3333740234375},"targetType":1,"skillId":1002,"assetTags":{"_tags":[]},"cancelAbilitiesWithTags":{"_tags":[]},"blockAbilitiesWithTags":{"_tags":[]},"activationOwnedTags":{"_tags":[{"_name":"Skill.Running","_hashCode":-51601538,"_shortName":"Running","_ancestorHashCodes":[1312877309],"_ancestorNames":["Skill"]}]},"activationRequiredTags":{"_tags":[]},"activationBlockedTags":{"_tags":[{"_name":"CD.Blood","_hashCode":274000851,"_shortName":"Blood","_ancestorHashCodes":[-1137859925],"_ancestorNames":["CD"]},{"_name":"Skill.Running","_hashCode":-51601538,"_shortName":"Running","_ancestorHashCodes":[1312877309],"_ancestorNames":["Skill"]}]},"ongoingBlockedTags":{"_tags":[]},"eventOutputPorts":[]}</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -933,7 +933,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>{"guid":"e33ab94c-1496-4d6a-ba5e-1afd38bb0c30","nodeType":4,"position":{"x":-452.0,"y":-1786.666748046875},"targetType":1,"searchShapeType":1,"searchLineType":0,"positionSource":0,"positionBindingName":"center","searchCircleRadius":5.0,"searchSectorRadius":2.0,"searchSectorAngle":180.0,"searchLineDirectionOffsetAngle":0.0,"searchLineDirectionWidth":1.0,"searchLineDirectionLength":10.0,"lineStartPositionSource":0,"lineStartBindingName":"","lineEndPositionSource":1,"lineEndBindingName":"","searchLineBetweenWidth":1.0,"searchLineAbsoluteAngle":0.0,"searchLineAbsoluteWidth":1.0,"searchLineAbsoluteLength":10.0,"maxTargets":999,"searchTargetTags":{"_tags":[{"_name":"unitType.monster","_hashCode":-2021655864,"_shortName":"monster","_ancestorHashCodes":[1600484460],"_ancestorNames":["unitType"]}]},"searchExcludeTags":{"_tags":[]}}</t>
+          <t>{"guid":"e33ab94c-1496-4d6a-ba5e-1afd38bb0c30","nodeType":4,"position":{"x":-452.66665649414063,"y":-1786.666748046875},"targetType":1,"searchShapeType":1,"searchLineType":0,"positionSource":0,"positionBindingName":"center","searchCircleRadius":5.0,"searchSectorRadius":5.0,"searchSectorAngle":180.0,"searchLineDirectionOffsetAngle":0.0,"searchLineDirectionWidth":1.0,"searchLineDirectionLength":10.0,"lineStartPositionSource":0,"lineStartBindingName":"","lineEndPositionSource":1,"lineEndBindingName":"","searchLineBetweenWidth":1.0,"searchLineAbsoluteAngle":0.0,"searchLineAbsoluteWidth":1.0,"searchLineAbsoluteLength":10.0,"maxTargets":999,"searchTargetTags":{"_tags":[{"_name":"unitType.monster","_hashCode":-2021655864,"_shortName":"monster","_ancestorHashCodes":[1600484460],"_ancestorNames":["unitType"]}]},"searchExcludeTags":{"_tags":[]}}</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -949,11 +949,11 @@
       <c r="C18"/>
       <c r="D18"/>
       <c r="E18">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>{"guid":"432ff1e3-b18d-476d-af80-d39ddc07402a","nodeType":20,"position":{"x":-472.0,"y":-2380.66650390625},"targetType":1,"skeletonDataAsset":null,"skeletonDataAssetPath":"Assets/Res/Spine/SP_Zhanshi/SP_Zhanshi_SkeletonData.asset","animationName":"Attack_02","animationDuration":"22","isAnimationLooping":false,"timeEffects":[{"triggerTime":7,"portIdValue":2315086,"legacyPortId":"de0ba361-3aba-4ef0-bb07-9b418fcae591"},{"triggerTime":22,"portIdValue":2821173,"legacyPortId":"97dc121c-84b7-4f94-9997-02e0e5b2ea6c"}],"timeCues":[{"startTime":7,"endTime":48,"portIdValue":2287012,"legacyPortId":"8dea1941-c520-4f9a-aee0-40932c8542ef"}]}</t>
+          <t>{"guid":"cde57fb8-b693-4da8-a4a8-fd61e56c5dcd","nodeType":12,"position":{"x":677.3333740234375,"y":-1998.666748046875},"targetType":1,"requiredTags":{"_tags":[]},"immunityTags":{"_tags":[]},"destroyWithNode":false,"positionSource":0,"particlePrefab":null,"particlePrefabPath":"Assets/Res/Prefab/Effect/ef_Zhanshi_attack_02.prefab","particleBindingName":"down","particleOffset":{"x":5.0,"y":0.0,"z":0.0},"particleScale":{"x":1.0,"y":1.0,"z":1.0},"attachToTarget":false,"particleLoop":false}</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -969,11 +969,11 @@
       <c r="C19"/>
       <c r="D19"/>
       <c r="E19">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>{"guid":"356907e0-1488-4128-bfcc-7ff73cfc3330","nodeType":0,"position":{"x":-878.6666259765625,"y":-1853.3333740234375},"targetType":1,"skillId":1002,"assetTags":{"_tags":[]},"cancelAbilitiesWithTags":{"_tags":[]},"blockAbilitiesWithTags":{"_tags":[]},"activationOwnedTags":{"_tags":[{"_name":"Skill.Running","_hashCode":-51601538,"_shortName":"Running","_ancestorHashCodes":[1312877309],"_ancestorNames":["Skill"]}]},"activationRequiredTags":{"_tags":[]},"activationBlockedTags":{"_tags":[{"_name":"CD.Blood","_hashCode":274000851,"_shortName":"Blood","_ancestorHashCodes":[-1137859925],"_ancestorNames":["CD"]},{"_name":"Skill.Running","_hashCode":-51601538,"_shortName":"Running","_ancestorHashCodes":[1312877309],"_ancestorNames":["Skill"]}]},"ongoingBlockedTags":{"_tags":[]},"eventOutputPorts":[]}</t>
+          <t>{"guid":"f8947676-1084-4228-b991-1509cc7fe851","nodeType":1,"position":{"x":195.33334350585938,"y":-1761.3333740234375},"targetType":0,"assetTags":{"_tags":[]},"grantedTags":{"_tags":[]},"applicationRequiredTags":{"_tags":[]},"applicationImmunityTags":{"_tags":[]},"removeGameEffectsWithTags":{"_tags":[]},"durationType":0,"duration":"0","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"_tags":[]},"cancelOnAbilityEnd":true,"damageType":0,"damageSourceType":0,"damageFixedValue":20.0,"damageFormula":"","damageMMCType":0,"damageSetByCallerKey":"","damageMMCCaptureAttribute":200,"damageMMCAttributeSource":0,"damageMMCCoefficient":1.0,"damageMMCUseSnapshot":true,"damageMultiplyByStackCount":true,"damageCalculationType":0,"enableHitKnockback":false,"knockbackDistance":1.0,"knockbackSpeed":12.0}</t>
         </is>
       </c>
       <c r="G19"/>
@@ -1923,11 +1923,11 @@
       </c>
       <c r="D66"/>
       <c r="E66">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>{"guid":"e33ab94c-1496-4d6a-ba5e-1afd38bb0c30","nodeType":4,"position":{"x":731.3333740234375,"y":-2344.0},"targetType":1,"searchShapeType":1,"searchLineType":0,"positionSource":0,"positionBindingName":"center","searchCircleRadius":5.0,"searchSectorRadius":2.0,"searchSectorAngle":180.0,"searchLineDirectionOffsetAngle":0.0,"searchLineDirectionWidth":1.0,"searchLineDirectionLength":10.0,"lineStartPositionSource":0,"lineStartBindingName":"","lineEndPositionSource":1,"lineEndBindingName":"","searchLineBetweenWidth":1.0,"searchLineAbsoluteAngle":0.0,"searchLineAbsoluteWidth":1.0,"searchLineAbsoluteLength":10.0,"maxTargets":999,"searchTargetTags":{"_tags":[{"_name":"unitType.monster","_hashCode":-2021655864,"_shortName":"monster","_ancestorHashCodes":[1600484460],"_ancestorNames":["unitType"]}]},"searchExcludeTags":{"_tags":[]}}</t>
+          <t>{"guid":"c353e286-8ef0-460a-b917-887f2aeb390a","nodeType":14,"position":{"x":1213.3333740234375,"y":-2354.0},"targetType":1,"requiredTags":{"_tags":[]},"immunityTags":{"_tags":[]},"destroyWithNode":false,"positionSource":2,"positionBindingName":"head","textType":0,"fixedText":"","contextDataKey":"DamageResult","textColor":{"r":1.0,"g":0.0,"b":0.0,"a":1.0},"criticalColor":{"r":1.0,"g":0.5,"b":0.0,"a":1.0},"missColor":{"r":0.5,"g":0.5,"b":0.5,"a":1.0},"fontSize":45.0,"criticalFontSize":60.0,"duration":1.5,"offset":{"x":0.0,"y":0.0},"moveDirection":{"x":0.0,"y":1.0}}</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
@@ -1943,11 +1943,11 @@
       <c r="C67"/>
       <c r="D67"/>
       <c r="E67">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>{"guid":"f8947676-1084-4228-b991-1509cc7fe851","nodeType":1,"position":{"x":974.666748046875,"y":-2340.66650390625},"targetType":0,"assetTags":{"_tags":[]},"grantedTags":{"_tags":[]},"applicationRequiredTags":{"_tags":[]},"applicationImmunityTags":{"_tags":[]},"removeGameEffectsWithTags":{"_tags":[]},"durationType":0,"duration":"0","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"_tags":[]},"cancelOnAbilityEnd":true,"damageType":0,"damageSourceType":2,"damageFixedValue":10.0,"damageFormula":"","damageMMCType":0,"damageSetByCallerKey":"","damageMMCCaptureAttribute":1006,"damageMMCAttributeSource":0,"damageMMCCoefficient":1.0,"damageMMCUseSnapshot":true,"damageMultiplyByStackCount":false,"damageCalculationType":0,"enableHitKnockback":true,"knockbackDistance":1.0,"knockbackSpeed":12.0}</t>
+          <t>{"guid":"2cfdacd2-0186-49dd-b177-4eb8c0ad87bd","nodeType":7,"position":{"x":731.3333740234375,"y":-2142.66650390625},"targetType":1,"endType":0}</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
@@ -1963,11 +1963,11 @@
       <c r="C68"/>
       <c r="D68"/>
       <c r="E68">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>{"guid":"c353e286-8ef0-460a-b917-887f2aeb390a","nodeType":14,"position":{"x":1213.3333740234375,"y":-2354.0},"targetType":1,"requiredTags":{"_tags":[]},"immunityTags":{"_tags":[]},"destroyWithNode":false,"positionSource":2,"positionBindingName":"head","textType":0,"fixedText":"","contextDataKey":"DamageResult","textColor":{"r":1.0,"g":0.0,"b":0.0,"a":1.0},"criticalColor":{"r":1.0,"g":0.5,"b":0.0,"a":1.0},"missColor":{"r":0.5,"g":0.5,"b":0.5,"a":1.0},"fontSize":45.0,"criticalFontSize":60.0,"duration":1.5,"offset":{"x":0.0,"y":0.0},"moveDirection":{"x":0.0,"y":1.0}}</t>
+          <t>{"guid":"c28fb88d-51b1-47b2-be59-859e0ac638e3","nodeType":10,"position":{"x":-1130.6666259765625,"y":-2232.0},"targetType":1,"assetTags":{"_tags":[]},"grantedTags":{"_tags":[{"_name":"CD.Sweep","_hashCode":-303359587,"_shortName":"Sweep","_ancestorHashCodes":[-1137859925],"_ancestorNames":["CD"]}]},"applicationRequiredTags":{"_tags":[]},"applicationImmunityTags":{"_tags":[]},"removeGameEffectsWithTags":{"_tags":[]},"durationType":1,"duration":"1","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"_tags":[]},"cancelOnAbilityEnd":false,"cooldownType":0,"maxCharges":2,"chargeTime":"10"}</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
@@ -1983,11 +1983,11 @@
       <c r="C69"/>
       <c r="D69"/>
       <c r="E69">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>{"guid":"2cfdacd2-0186-49dd-b177-4eb8c0ad87bd","nodeType":7,"position":{"x":731.3333740234375,"y":-2142.66650390625},"targetType":1,"endType":0}</t>
+          <t>{"guid":"432ff1e3-b18d-476d-af80-d39ddc07402a","nodeType":20,"position":{"x":-415.33331298828125,"y":-2827.333251953125},"targetType":1,"skeletonDataAsset":null,"skeletonDataAssetPath":"Assets/Res/Spine/SP_Zhanshi/SP_Zhanshi_SkeletonData.asset","animationName":"Skill_attack_1001","animationDuration":"18","isAnimationLooping":false,"timeEffects":[{"triggerTime":7,"portIdValue":2315086,"legacyPortId":"de0ba361-3aba-4ef0-bb07-9b418fcae591"},{"triggerTime":18,"portIdValue":2649436,"legacyPortId":"84e238a8-5baf-470e-829f-186695064945"}],"timeCues":[{"startTime":7,"endTime":48,"portIdValue":2287012,"legacyPortId":"8dea1941-c520-4f9a-aee0-40932c8542ef"}]}</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
@@ -2003,11 +2003,11 @@
       <c r="C70"/>
       <c r="D70"/>
       <c r="E70">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>{"guid":"c28fb88d-51b1-47b2-be59-859e0ac638e3","nodeType":10,"position":{"x":-1130.6666259765625,"y":-2232.0},"targetType":1,"assetTags":{"_tags":[]},"grantedTags":{"_tags":[{"_name":"CD.Sweep","_hashCode":-303359587,"_shortName":"Sweep","_ancestorHashCodes":[-1137859925],"_ancestorNames":["CD"]}]},"applicationRequiredTags":{"_tags":[]},"applicationImmunityTags":{"_tags":[]},"removeGameEffectsWithTags":{"_tags":[]},"durationType":1,"duration":"1","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"_tags":[]},"cancelOnAbilityEnd":false,"cooldownType":0,"maxCharges":2,"chargeTime":"10"}</t>
+          <t>{"guid":"9d6f459d-b588-4b64-843b-1b71e8f299ae","nodeType":3,"position":{"x":-1130.6666259765625,"y":-2479.333251953125},"targetType":1,"assetTags":{"_tags":[]},"grantedTags":{"_tags":[]},"applicationRequiredTags":{"_tags":[]},"applicationImmunityTags":{"_tags":[]},"removeGameEffectsWithTags":{"_tags":[]},"durationType":0,"duration":"0","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[{"attrType":1003,"operation":0,"magnitudeSourceType":0,"fixedValue":-10.0,"formula":"","mmcType":0,"setByCallerKey":"","mmcCaptureAttribute":200,"mmcAttributeSource":0,"mmcCoefficient":1.0,"mmcUseSnapshot":true}],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"_tags":[]},"cancelOnAbilityEnd":true}</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
@@ -2023,11 +2023,11 @@
       <c r="C71"/>
       <c r="D71"/>
       <c r="E71">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>{"guid":"432ff1e3-b18d-476d-af80-d39ddc07402a","nodeType":20,"position":{"x":-415.33331298828125,"y":-2827.333251953125},"targetType":1,"skeletonDataAsset":null,"skeletonDataAssetPath":"Assets/Res/Spine/SP_Zhanshi/SP_Zhanshi_SkeletonData.asset","animationName":"Skill_attack_1001","animationDuration":"18","isAnimationLooping":false,"timeEffects":[{"triggerTime":7,"portIdValue":2315086,"legacyPortId":"de0ba361-3aba-4ef0-bb07-9b418fcae591"},{"triggerTime":18,"portIdValue":2649436,"legacyPortId":"84e238a8-5baf-470e-829f-186695064945"}],"timeCues":[{"startTime":7,"endTime":48,"portIdValue":2287012,"legacyPortId":"8dea1941-c520-4f9a-aee0-40932c8542ef"}]}</t>
+          <t>{"guid":"356907e0-1488-4128-bfcc-7ff73cfc3330","nodeType":0,"position":{"x":-843.3333740234375,"y":-2480.0},"targetType":1,"skillId":1001,"assetTags":{"_tags":[]},"cancelAbilitiesWithTags":{"_tags":[]},"blockAbilitiesWithTags":{"_tags":[]},"activationOwnedTags":{"_tags":[]},"activationRequiredTags":{"_tags":[]},"activationBlockedTags":{"_tags":[{"_name":"CD.Sweep","_hashCode":-303359587,"_shortName":"Sweep","_ancestorHashCodes":[-1137859925],"_ancestorNames":["CD"]}]},"ongoingBlockedTags":{"_tags":[]},"eventOutputPorts":[]}</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
@@ -2043,11 +2043,11 @@
       <c r="C72"/>
       <c r="D72"/>
       <c r="E72">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>{"guid":"cde57fb8-b693-4da8-a4a8-fd61e56c5dcd","nodeType":12,"position":{"x":731.3333740234375,"y":-2490.66650390625},"targetType":1,"requiredTags":{"_tags":[]},"immunityTags":{"_tags":[]},"destroyWithNode":false,"positionSource":0,"particlePrefab":null,"particlePrefabPath":"Assets/Res/Prefab/Effect/ef_Zhanshi_attack_02.prefab","particleBindingName":"down","particleOffset":{"x":5.0,"y":0.0,"z":0.0},"particleScale":{"x":1.0,"y":1.0,"z":1.0},"attachToTarget":false,"particleLoop":false}</t>
+          <t>{"guid":"f8947676-1084-4228-b991-1509cc7fe851","nodeType":1,"position":{"x":974.666748046875,"y":-2340.66650390625},"targetType":0,"assetTags":{"_tags":[]},"grantedTags":{"_tags":[]},"applicationRequiredTags":{"_tags":[]},"applicationImmunityTags":{"_tags":[]},"removeGameEffectsWithTags":{"_tags":[]},"durationType":0,"duration":"0","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"_tags":[]},"cancelOnAbilityEnd":true,"damageType":0,"damageSourceType":2,"damageFixedValue":10.0,"damageFormula":"","damageMMCType":0,"damageSetByCallerKey":"","damageMMCCaptureAttribute":1006,"damageMMCAttributeSource":0,"damageMMCCoefficient":1.0,"damageMMCUseSnapshot":true,"damageMultiplyByStackCount":false,"damageCalculationType":0,"enableHitKnockback":true,"knockbackDistance":1.0,"knockbackSpeed":12.0}</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
@@ -2063,11 +2063,11 @@
       <c r="C73"/>
       <c r="D73"/>
       <c r="E73">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>{"guid":"9d6f459d-b588-4b64-843b-1b71e8f299ae","nodeType":3,"position":{"x":-1130.6666259765625,"y":-2479.333251953125},"targetType":1,"assetTags":{"_tags":[]},"grantedTags":{"_tags":[]},"applicationRequiredTags":{"_tags":[]},"applicationImmunityTags":{"_tags":[]},"removeGameEffectsWithTags":{"_tags":[]},"durationType":0,"duration":"0","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[{"attrType":1003,"operation":0,"magnitudeSourceType":0,"fixedValue":-10.0,"formula":"","mmcType":0,"setByCallerKey":"","mmcCaptureAttribute":200,"mmcAttributeSource":0,"mmcCoefficient":1.0,"mmcUseSnapshot":true}],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"_tags":[]},"cancelOnAbilityEnd":true}</t>
+          <t>{"guid":"cde57fb8-b693-4da8-a4a8-fd61e56c5dcd","nodeType":12,"position":{"x":731.3333740234375,"y":-2490.66650390625},"targetType":1,"requiredTags":{"_tags":[]},"immunityTags":{"_tags":[]},"destroyWithNode":false,"positionSource":0,"particlePrefab":null,"particlePrefabPath":"Assets/Res/Prefab/Effect/ef_Zhanshi_attack_02.prefab","particleBindingName":"down","particleOffset":{"x":5.0,"y":0.0,"z":0.0},"particleScale":{"x":1.0,"y":1.0,"z":1.0},"attachToTarget":false,"particleLoop":false}</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
@@ -2083,11 +2083,11 @@
       <c r="C74"/>
       <c r="D74"/>
       <c r="E74">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>{"guid":"356907e0-1488-4128-bfcc-7ff73cfc3330","nodeType":0,"position":{"x":-843.3333740234375,"y":-2480.0},"targetType":1,"skillId":1001,"assetTags":{"_tags":[]},"cancelAbilitiesWithTags":{"_tags":[]},"blockAbilitiesWithTags":{"_tags":[]},"activationOwnedTags":{"_tags":[]},"activationRequiredTags":{"_tags":[]},"activationBlockedTags":{"_tags":[{"_name":"CD.Sweep","_hashCode":-303359587,"_shortName":"Sweep","_ancestorHashCodes":[-1137859925],"_ancestorNames":["CD"]}]},"ongoingBlockedTags":{"_tags":[]},"eventOutputPorts":[]}</t>
+          <t>{"guid":"e33ab94c-1496-4d6a-ba5e-1afd38bb0c30","nodeType":4,"position":{"x":731.3333740234375,"y":-2344.0},"targetType":1,"searchShapeType":1,"searchLineType":0,"positionSource":0,"positionBindingName":"center","searchCircleRadius":5.0,"searchSectorRadius":5.0,"searchSectorAngle":180.0,"searchLineDirectionOffsetAngle":0.0,"searchLineDirectionWidth":1.0,"searchLineDirectionLength":10.0,"lineStartPositionSource":0,"lineStartBindingName":"","lineEndPositionSource":1,"lineEndBindingName":"","searchLineBetweenWidth":1.0,"searchLineAbsoluteAngle":0.0,"searchLineAbsoluteWidth":1.0,"searchLineAbsoluteLength":10.0,"maxTargets":999,"searchTargetTags":{"_tags":[{"_name":"unitType.monster","_hashCode":-2021655864,"_shortName":"monster","_ancestorHashCodes":[1600484460],"_ancestorNames":["unitType"]}]},"searchExcludeTags":{"_tags":[]}}</t>
         </is>
       </c>
       <c r="G74"/>

--- a/Design/Excel/ET/Datas/Game/SkillGraph.xlsx
+++ b/Design/Excel/ET/Datas/Game/SkillGraph.xlsx
@@ -953,7 +953,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>{"guid":"cde57fb8-b693-4da8-a4a8-fd61e56c5dcd","nodeType":12,"position":{"x":677.3333740234375,"y":-1998.666748046875},"targetType":1,"requiredTags":{"_tags":[]},"immunityTags":{"_tags":[]},"destroyWithNode":false,"positionSource":0,"particlePrefab":null,"particlePrefabPath":"Assets/Res/Prefab/Effect/ef_Zhanshi_attack_02.prefab","particleBindingName":"down","particleOffset":{"x":5.0,"y":0.0,"z":0.0},"particleScale":{"x":1.0,"y":1.0,"z":1.0},"attachToTarget":false,"particleLoop":false}</t>
+          <t>{"guid":"cde57fb8-b693-4da8-a4a8-fd61e56c5dcd","nodeType":12,"position":{"x":677.3333740234375,"y":-1998.666748046875},"targetType":1,"requiredTags":{"_tags":[]},"immunityTags":{"_tags":[]},"destroyWithNode":false,"positionSource":0,"particlePrefab":null,"particlePrefabPath":"Assets/Res/Entity/Effect/ef_Zhanshi_attack_02.prefab","particleBindingName":"down","particleOffset":{"x":5.0,"y":0.0,"z":0.0},"particleScale":{"x":1.0,"y":1.0,"z":1.0},"attachToTarget":false,"particleLoop":false}</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -1031,11 +1031,11 @@
       <c r="C22"/>
       <c r="D22"/>
       <c r="E22">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>{"guid":"356907e0-1488-4128-bfcc-7ff73cfc3330","nodeType":0,"position":{"x":-880.6666259765625,"y":-1851.3333740234375},"targetType":1,"skillId":7001,"assetTags":{"_tags":[]},"cancelAbilitiesWithTags":{"_tags":[]},"blockAbilitiesWithTags":{"_tags":[]},"activationOwnedTags":{"_tags":[]},"activationRequiredTags":{"_tags":[]},"activationBlockedTags":{"_tags":[{"_name":"CD.FireCircle","_hashCode":522143731,"_shortName":"FireCircle","_ancestorHashCodes":[-1137859925],"_ancestorNames":["CD"]}]},"ongoingBlockedTags":{"_tags":[{"_name":"Buff.DeBuff.Stun","_hashCode":1791562953,"_shortName":"Stun","_ancestorHashCodes":[937056111,321157895],"_ancestorNames":["Buff","Buff.DeBuff"]}]},"eventOutputPorts":[]}</t>
+          <t>{"guid":"c28fb88d-51b1-47b2-be59-859e0ac638e3","nodeType":10,"position":{"x":-1220.6666259765625,"y":-1747.3333740234375},"targetType":1,"assetTags":{"_tags":[]},"grantedTags":{"_tags":[{"_name":"CD.FireCircle","_hashCode":522143731,"_shortName":"FireCircle","_ancestorHashCodes":[-1137859925],"_ancestorNames":["CD"]}]},"applicationRequiredTags":{"_tags":[]},"applicationImmunityTags":{"_tags":[]},"removeGameEffectsWithTags":{"_tags":[]},"durationType":1,"duration":"3","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"_tags":[]},"cancelOnAbilityEnd":false,"cooldownType":0,"maxCharges":2,"chargeTime":"10"}</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -1051,11 +1051,11 @@
       <c r="C23"/>
       <c r="D23"/>
       <c r="E23">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>{"guid":"c28fb88d-51b1-47b2-be59-859e0ac638e3","nodeType":10,"position":{"x":-1220.6666259765625,"y":-1747.3333740234375},"targetType":1,"assetTags":{"_tags":[]},"grantedTags":{"_tags":[{"_name":"CD.FireCircle","_hashCode":522143731,"_shortName":"FireCircle","_ancestorHashCodes":[-1137859925],"_ancestorNames":["CD"]}]},"applicationRequiredTags":{"_tags":[]},"applicationImmunityTags":{"_tags":[]},"removeGameEffectsWithTags":{"_tags":[]},"durationType":1,"duration":"3","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"_tags":[]},"cancelOnAbilityEnd":false,"cooldownType":0,"maxCharges":2,"chargeTime":"10"}</t>
+          <t>{"guid":"9d6f459d-b588-4b64-843b-1b71e8f299ae","nodeType":3,"position":{"x":-1195.3333740234375,"y":-2003.3333740234375},"targetType":1,"assetTags":{"_tags":[]},"grantedTags":{"_tags":[]},"applicationRequiredTags":{"_tags":[]},"applicationImmunityTags":{"_tags":[]},"removeGameEffectsWithTags":{"_tags":[]},"durationType":0,"duration":"0","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[{"attrType":1003,"operation":0,"magnitudeSourceType":0,"fixedValue":-100.0,"formula":"","mmcType":0,"setByCallerKey":"","mmcCaptureAttribute":200,"mmcAttributeSource":0,"mmcCoefficient":1.0,"mmcUseSnapshot":true}],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"_tags":[]},"cancelOnAbilityEnd":true}</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -1071,11 +1071,11 @@
       <c r="C24"/>
       <c r="D24"/>
       <c r="E24">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>{"guid":"9d6f459d-b588-4b64-843b-1b71e8f299ae","nodeType":3,"position":{"x":-1195.3333740234375,"y":-2003.3333740234375},"targetType":1,"assetTags":{"_tags":[]},"grantedTags":{"_tags":[]},"applicationRequiredTags":{"_tags":[]},"applicationImmunityTags":{"_tags":[]},"removeGameEffectsWithTags":{"_tags":[]},"durationType":0,"duration":"0","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[{"attrType":1003,"operation":0,"magnitudeSourceType":0,"fixedValue":-100.0,"formula":"","mmcType":0,"setByCallerKey":"","mmcCaptureAttribute":200,"mmcAttributeSource":0,"mmcCoefficient":1.0,"mmcUseSnapshot":true}],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"_tags":[]},"cancelOnAbilityEnd":true}</t>
+          <t>{"guid":"2d7e41c4-8e90-4b61-879c-4b2e5b9486db","nodeType":14,"position":{"x":180.0,"y":-1810.0},"targetType":1,"requiredTags":{"_tags":[]},"immunityTags":{"_tags":[]},"destroyWithNode":false,"positionSource":2,"positionBindingName":"head","textType":0,"fixedText":"","contextDataKey":"DamageResult","textColor":{"r":0.0,"g":0.323091983795166,"b":1.0,"a":1.0},"criticalColor":{"r":1.0,"g":0.5,"b":0.0,"a":1.0},"missColor":{"r":0.5,"g":0.5,"b":0.5,"a":1.0},"fontSize":45.0,"criticalFontSize":60.0,"duration":1.5,"offset":{"x":0.0,"y":0.0},"moveDirection":{"x":0.0,"y":1.0}}</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -1091,11 +1091,11 @@
       <c r="C25"/>
       <c r="D25"/>
       <c r="E25">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>{"guid":"2d7e41c4-8e90-4b61-879c-4b2e5b9486db","nodeType":14,"position":{"x":180.0,"y":-1810.0},"targetType":1,"requiredTags":{"_tags":[]},"immunityTags":{"_tags":[]},"destroyWithNode":false,"positionSource":2,"positionBindingName":"head","textType":0,"fixedText":"","contextDataKey":"DamageResult","textColor":{"r":0.0,"g":0.323091983795166,"b":1.0,"a":1.0},"criticalColor":{"r":1.0,"g":0.5,"b":0.0,"a":1.0},"missColor":{"r":0.5,"g":0.5,"b":0.5,"a":1.0},"fontSize":45.0,"criticalFontSize":60.0,"duration":1.5,"offset":{"x":0.0,"y":0.0},"moveDirection":{"x":0.0,"y":1.0}}</t>
+          <t>{"guid":"eae41233-d297-46fe-a6c8-0b5c876fbb2a","nodeType":1,"position":{"x":-97.333328247070313,"y":-1810.0},"targetType":0,"assetTags":{"_tags":[]},"grantedTags":{"_tags":[]},"applicationRequiredTags":{"_tags":[]},"applicationImmunityTags":{"_tags":[]},"removeGameEffectsWithTags":{"_tags":[]},"durationType":0,"duration":"0","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"_tags":[]},"cancelOnAbilityEnd":true,"damageType":0,"damageSourceType":0,"damageFixedValue":10.0,"damageFormula":"","damageMMCType":0,"damageSetByCallerKey":"","damageMMCCaptureAttribute":200,"damageMMCAttributeSource":0,"damageMMCCoefficient":1.0,"damageMMCUseSnapshot":true,"damageMultiplyByStackCount":false,"damageCalculationType":0,"enableHitKnockback":true,"knockbackDistance":1.0,"knockbackSpeed":12.0}</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -1111,11 +1111,11 @@
       <c r="C26"/>
       <c r="D26"/>
       <c r="E26">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>{"guid":"90bacd9f-d882-4bba-aaa8-41ed993ac3ff","nodeType":8,"position":{"x":-419.33331298828125,"y":-1840.0},"targetType":2,"assetTags":{"_tags":[]},"grantedTags":{"_tags":[]},"applicationRequiredTags":{"_tags":[]},"applicationImmunityTags":{"_tags":[]},"removeGameEffectsWithTags":{"_tags":[]},"durationType":2,"duration":"0","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"_tags":[]},"cancelOnAbilityEnd":false,"launchPositionSource":0,"launchBindingName":"center","targetPositionSource":1,"targetBindingName":"center","projectileTargetType":0,"flyOver":false,"offsetAngle":0.0,"curveHeight":0.0,"projectilePrefab":null,"projectilePrefabPath":"Assets/Res/Prefab/Effect/ef_fashi_gandian_buff.prefab","speed":3.0,"maxDistance":10.0,"collisionRadius":0.5,"isPiercing":false,"maxPierceCount":1,"collisionTargetTags":{"_tags":[]},"collisionExcludeTags":{"_tags":[]},"isBouncing":true,"bounceTargetMode":0,"maxBounceCount":3,"bounceSearchRadius":10.0,"canBounceToSameTarget":false,"excludeSourceCamp":true,"bounceAngleOffset":0.0}</t>
+          <t>{"guid":"356907e0-1488-4128-bfcc-7ff73cfc3330","nodeType":0,"position":{"x":-881.3333740234375,"y":-1854.666748046875},"targetType":1,"skillId":7001,"assetTags":{"_tags":[]},"cancelAbilitiesWithTags":{"_tags":[]},"blockAbilitiesWithTags":{"_tags":[]},"activationOwnedTags":{"_tags":[]},"activationRequiredTags":{"_tags":[]},"activationBlockedTags":{"_tags":[{"_name":"CD.FireCircle","_hashCode":522143731,"_shortName":"FireCircle","_ancestorHashCodes":[-1137859925],"_ancestorNames":["CD"]}]},"ongoingBlockedTags":{"_tags":[{"_name":"Buff.DeBuff.Stun","_hashCode":1791562953,"_shortName":"Stun","_ancestorHashCodes":[937056111,321157895],"_ancestorNames":["Buff","Buff.DeBuff"]}]},"eventOutputPorts":[]}</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -1131,11 +1131,11 @@
       <c r="C27"/>
       <c r="D27"/>
       <c r="E27">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>{"guid":"eae41233-d297-46fe-a6c8-0b5c876fbb2a","nodeType":1,"position":{"x":-97.333328247070313,"y":-1810.0},"targetType":0,"assetTags":{"_tags":[]},"grantedTags":{"_tags":[]},"applicationRequiredTags":{"_tags":[]},"applicationImmunityTags":{"_tags":[]},"removeGameEffectsWithTags":{"_tags":[]},"durationType":0,"duration":"0","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"_tags":[]},"cancelOnAbilityEnd":true,"damageType":0,"damageSourceType":0,"damageFixedValue":10.0,"damageFormula":"","damageMMCType":0,"damageSetByCallerKey":"","damageMMCCaptureAttribute":200,"damageMMCAttributeSource":0,"damageMMCCoefficient":1.0,"damageMMCUseSnapshot":true,"damageMultiplyByStackCount":false,"damageCalculationType":0,"enableHitKnockback":true,"knockbackDistance":1.0,"knockbackSpeed":12.0}</t>
+          <t>{"guid":"90bacd9f-d882-4bba-aaa8-41ed993ac3ff","nodeType":8,"position":{"x":-419.33331298828125,"y":-1840.0},"targetType":2,"assetTags":{"_tags":[]},"grantedTags":{"_tags":[]},"applicationRequiredTags":{"_tags":[]},"applicationImmunityTags":{"_tags":[]},"removeGameEffectsWithTags":{"_tags":[]},"durationType":2,"duration":"0","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"_tags":[]},"cancelOnAbilityEnd":false,"launchPositionSource":0,"launchBindingName":"center","targetPositionSource":1,"targetBindingName":"center","projectileTargetType":0,"flyOver":false,"offsetAngle":0.0,"curveHeight":0.0,"projectileEntityId":50001,"projectilePrefab":null,"projectilePrefabPath":"Assets/Res/Entity/Effect/ef_fashi_gandian_buff.prefab","speed":3.0,"maxDistance":10.0,"collisionRadius":0.5,"isPiercing":false,"maxPierceCount":1,"collisionTargetTags":{"_tags":[]},"collisionExcludeTags":{"_tags":[]},"isBouncing":true,"bounceTargetMode":0,"maxBounceCount":3,"bounceSearchRadius":10.0,"canBounceToSameTarget":false,"excludeSourceCamp":true,"bounceAngleOffset":0.0}</t>
         </is>
       </c>
       <c r="G27"/>
@@ -1253,11 +1253,11 @@
       <c r="C33"/>
       <c r="D33"/>
       <c r="E33">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>{"guid":"90bacd9f-d882-4bba-aaa8-41ed993ac3ff","nodeType":8,"position":{"x":-400.66665649414063,"y":-1836.666748046875},"targetType":2,"assetTags":{"_tags":[]},"grantedTags":{"_tags":[]},"applicationRequiredTags":{"_tags":[]},"applicationImmunityTags":{"_tags":[]},"removeGameEffectsWithTags":{"_tags":[]},"durationType":2,"duration":"0","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"_tags":[]},"cancelOnAbilityEnd":false,"launchPositionSource":0,"launchBindingName":"center","targetPositionSource":1,"targetBindingName":"center","projectileTargetType":0,"flyOver":false,"offsetAngle":0.0,"curveHeight":0.0,"projectilePrefab":null,"projectilePrefabPath":"Assets/Res/Prefab/Effect/ef_fashi_gandian_buff.prefab","speed":3.0,"maxDistance":10.0,"collisionRadius":0.5,"isPiercing":false,"maxPierceCount":1,"collisionTargetTags":{"_tags":[]},"collisionExcludeTags":{"_tags":[]},"isBouncing":true,"bounceTargetMode":0,"maxBounceCount":2,"bounceSearchRadius":10.0,"canBounceToSameTarget":false,"excludeSourceCamp":true,"bounceAngleOffset":50.0}</t>
+          <t>{"guid":"9d6f459d-b588-4b64-843b-1b71e8f299ae","nodeType":3,"position":{"x":-1195.3333740234375,"y":-2013.3333740234375},"targetType":1,"assetTags":{"_tags":[]},"grantedTags":{"_tags":[]},"applicationRequiredTags":{"_tags":[]},"applicationImmunityTags":{"_tags":[]},"removeGameEffectsWithTags":{"_tags":[]},"durationType":0,"duration":"0","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[{"attrType":1003,"operation":0,"magnitudeSourceType":0,"fixedValue":-100.0,"formula":"","mmcType":0,"setByCallerKey":"","mmcCaptureAttribute":200,"mmcAttributeSource":0,"mmcCoefficient":1.0,"mmcUseSnapshot":true}],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"_tags":[]},"cancelOnAbilityEnd":true}</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -1273,11 +1273,11 @@
       <c r="C34"/>
       <c r="D34"/>
       <c r="E34">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>{"guid":"9d6f459d-b588-4b64-843b-1b71e8f299ae","nodeType":3,"position":{"x":-1195.3333740234375,"y":-2013.3333740234375},"targetType":1,"assetTags":{"_tags":[]},"grantedTags":{"_tags":[]},"applicationRequiredTags":{"_tags":[]},"applicationImmunityTags":{"_tags":[]},"removeGameEffectsWithTags":{"_tags":[]},"durationType":0,"duration":"0","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[{"attrType":1003,"operation":0,"magnitudeSourceType":0,"fixedValue":-100.0,"formula":"","mmcType":0,"setByCallerKey":"","mmcCaptureAttribute":200,"mmcAttributeSource":0,"mmcCoefficient":1.0,"mmcUseSnapshot":true}],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"_tags":[]},"cancelOnAbilityEnd":true}</t>
+          <t>{"guid":"eae41233-d297-46fe-a6c8-0b5c876fbb2a","nodeType":1,"position":{"x":45.333343505859375,"y":-1806.666748046875},"targetType":0,"assetTags":{"_tags":[]},"grantedTags":{"_tags":[]},"applicationRequiredTags":{"_tags":[]},"applicationImmunityTags":{"_tags":[]},"removeGameEffectsWithTags":{"_tags":[]},"durationType":0,"duration":"0","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"_tags":[]},"cancelOnAbilityEnd":true,"damageType":0,"damageSourceType":0,"damageFixedValue":10.0,"damageFormula":"","damageMMCType":0,"damageSetByCallerKey":"","damageMMCCaptureAttribute":200,"damageMMCAttributeSource":0,"damageMMCCoefficient":1.0,"damageMMCUseSnapshot":true,"damageMultiplyByStackCount":false,"damageCalculationType":0,"enableHitKnockback":true,"knockbackDistance":1.0,"knockbackSpeed":12.0}</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -1293,11 +1293,11 @@
       <c r="C35"/>
       <c r="D35"/>
       <c r="E35">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>{"guid":"eae41233-d297-46fe-a6c8-0b5c876fbb2a","nodeType":1,"position":{"x":45.333343505859375,"y":-1806.666748046875},"targetType":0,"assetTags":{"_tags":[]},"grantedTags":{"_tags":[]},"applicationRequiredTags":{"_tags":[]},"applicationImmunityTags":{"_tags":[]},"removeGameEffectsWithTags":{"_tags":[]},"durationType":0,"duration":"0","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"_tags":[]},"cancelOnAbilityEnd":true,"damageType":0,"damageSourceType":0,"damageFixedValue":10.0,"damageFormula":"","damageMMCType":0,"damageSetByCallerKey":"","damageMMCCaptureAttribute":200,"damageMMCAttributeSource":0,"damageMMCCoefficient":1.0,"damageMMCUseSnapshot":true,"damageMultiplyByStackCount":false,"damageCalculationType":0,"enableHitKnockback":true,"knockbackDistance":1.0,"knockbackSpeed":12.0}</t>
+          <t>{"guid":"90bacd9f-d882-4bba-aaa8-41ed993ac3ff","nodeType":8,"position":{"x":-400.66665649414063,"y":-1836.666748046875},"targetType":2,"assetTags":{"_tags":[]},"grantedTags":{"_tags":[]},"applicationRequiredTags":{"_tags":[]},"applicationImmunityTags":{"_tags":[]},"removeGameEffectsWithTags":{"_tags":[]},"durationType":2,"duration":"0","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"_tags":[]},"cancelOnAbilityEnd":false,"launchPositionSource":0,"launchBindingName":"center","targetPositionSource":1,"targetBindingName":"center","projectileTargetType":0,"flyOver":false,"offsetAngle":0.0,"curveHeight":0.0,"projectileEntityId":50001,"projectilePrefab":null,"projectilePrefabPath":"Assets/Res/Entity/Effect/ef_fashi_gandian_buff.prefab","speed":3.0,"maxDistance":10.0,"collisionRadius":0.5,"isPiercing":false,"maxPierceCount":1,"collisionTargetTags":{"_tags":[]},"collisionExcludeTags":{"_tags":[]},"isBouncing":true,"bounceTargetMode":0,"maxBounceCount":2,"bounceSearchRadius":10.0,"canBounceToSameTarget":false,"excludeSourceCamp":true,"bounceAngleOffset":50.0}</t>
         </is>
       </c>
       <c r="G35"/>
@@ -1359,7 +1359,7 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>{"guid":"cde57fb8-b693-4da8-a4a8-fd61e56c5dcd","nodeType":12,"position":{"x":677.3333740234375,"y":-1998.666748046875},"targetType":1,"requiredTags":{"_tags":[]},"immunityTags":{"_tags":[]},"destroyWithNode":false,"positionSource":0,"particlePrefab":null,"particlePrefabPath":"Assets/Res/Prefab/Effect/ef_Zhanshi_zhandounuhou_01.prefab","particleBindingName":"down","particleOffset":{"x":0.0,"y":0.0,"z":0.0},"particleScale":{"x":1.0,"y":1.0,"z":1.0},"attachToTarget":false,"particleLoop":false}</t>
+          <t>{"guid":"cde57fb8-b693-4da8-a4a8-fd61e56c5dcd","nodeType":12,"position":{"x":677.3333740234375,"y":-1998.666748046875},"targetType":1,"requiredTags":{"_tags":[]},"immunityTags":{"_tags":[]},"destroyWithNode":false,"positionSource":0,"particlePrefab":null,"particlePrefabPath":"Assets/Res/Entity/Effect/ef_Zhanshi_zhandounuhou_01.prefab","particleBindingName":"down","particleOffset":{"x":0.0,"y":0.0,"z":0.0},"particleScale":{"x":1.0,"y":1.0,"z":1.0},"attachToTarget":false,"particleLoop":false}</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -1481,7 +1481,7 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>{"guid":"cde57fb8-b693-4da8-a4a8-fd61e56c5dcd","nodeType":12,"position":{"x":-304.0,"y":-2072.0},"targetType":1,"requiredTags":{"_tags":[]},"immunityTags":{"_tags":[]},"destroyWithNode":false,"positionSource":0,"particlePrefab":null,"particlePrefabPath":"Assets/Res/Prefab/Effect/ef_skill_zhanshi_huifunengliang.prefab","particleBindingName":"down","particleOffset":{"x":0.0,"y":0.0,"z":0.0},"particleScale":{"x":1.0,"y":1.0,"z":1.0},"attachToTarget":false,"particleLoop":false}</t>
+          <t>{"guid":"cde57fb8-b693-4da8-a4a8-fd61e56c5dcd","nodeType":12,"position":{"x":-304.0,"y":-2072.0},"targetType":1,"requiredTags":{"_tags":[]},"immunityTags":{"_tags":[]},"destroyWithNode":false,"positionSource":0,"particlePrefab":null,"particlePrefabPath":"Assets/Res/Entity/Effect/ef_skill_zhanshi_huifunengliang.prefab","particleBindingName":"down","particleOffset":{"x":0.0,"y":0.0,"z":0.0},"particleScale":{"x":1.0,"y":1.0,"z":1.0},"attachToTarget":false,"particleLoop":false}</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -1659,11 +1659,11 @@
       <c r="C53"/>
       <c r="D53"/>
       <c r="E53">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>{"guid":"cde57fb8-b693-4da8-a4a8-fd61e56c5dcd","nodeType":12,"position":{"x":677.3333740234375,"y":-1998.666748046875},"targetType":1,"requiredTags":{"_tags":[]},"immunityTags":{"_tags":[]},"destroyWithNode":false,"positionSource":0,"particlePrefab":null,"particlePrefabPath":"Assets/Res/Prefab/Effect/ef_zhanshi_jcjt_01.prefab","particleBindingName":"down","particleOffset":{"x":0.0,"y":0.0,"z":0.0},"particleScale":{"x":1.0,"y":1.0,"z":1.0},"attachToTarget":false,"particleLoop":false}</t>
+          <t>{"guid":"f73ba91e-a76b-456c-b19c-a5176809d5f5","nodeType":7,"position":{"x":700.0,"y":-1856.666748046875},"targetType":1,"endType":0}</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
@@ -1679,11 +1679,11 @@
       <c r="C54"/>
       <c r="D54"/>
       <c r="E54">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>{"guid":"f73ba91e-a76b-456c-b19c-a5176809d5f5","nodeType":7,"position":{"x":700.0,"y":-1856.666748046875},"targetType":1,"endType":0}</t>
+          <t>{"guid":"93ec5a43-cc34-4e4a-acb3-39da2f2c3010","nodeType":12,"position":{"x":468.66665649414063,"y":-1749.3333740234375},"targetType":1,"requiredTags":{"_tags":[]},"immunityTags":{"_tags":[]},"destroyWithNode":true,"positionSource":2,"particlePrefab":null,"particlePrefabPath":"Assets/Res/Entity/Effect/ef_Xuanyun_01.prefab","particleBindingName":"head","particleOffset":{"x":0.0,"y":0.0,"z":0.0},"particleScale":{"x":1.0,"y":1.0,"z":1.0},"attachToTarget":true,"particleLoop":true}</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
@@ -1699,11 +1699,11 @@
       <c r="C55"/>
       <c r="D55"/>
       <c r="E55">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>{"guid":"93ec5a43-cc34-4e4a-acb3-39da2f2c3010","nodeType":12,"position":{"x":468.66665649414063,"y":-1749.3333740234375},"targetType":1,"requiredTags":{"_tags":[]},"immunityTags":{"_tags":[]},"destroyWithNode":true,"positionSource":2,"particlePrefab":null,"particlePrefabPath":"Assets/Res/Prefab/Effect/ef_Xuanyun_01.prefab","particleBindingName":"head","particleOffset":{"x":0.0,"y":0.0,"z":0.0},"particleScale":{"x":1.0,"y":1.0,"z":1.0},"attachToTarget":true,"particleLoop":true}</t>
+          <t>{"guid":"cb1df36f-5729-423e-9d1a-287db5a433f0","nodeType":11,"position":{"x":18.66668701171875,"y":-1786.666748046875},"targetType":0,"assetTags":{"_tags":[{"_name":"Buff.DeBuff.Stun","_hashCode":1791562953,"_shortName":"Stun","_ancestorHashCodes":[937056111,321157895],"_ancestorNames":["Buff","Buff.DeBuff"]}]},"grantedTags":{"_tags":[{"_name":"Buff.DeBuff.Stun","_hashCode":1791562953,"_shortName":"Stun","_ancestorHashCodes":[937056111,321157895],"_ancestorNames":["Buff","Buff.DeBuff"]}]},"applicationRequiredTags":{"_tags":[]},"applicationImmunityTags":{"_tags":[]},"removeGameEffectsWithTags":{"_tags":[]},"durationType":1,"duration":"4","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[],"stackType":1,"stackLimit":1,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":1,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"_tags":[]},"cancelOnAbilityEnd":false,"buffId":0}</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
@@ -1719,11 +1719,11 @@
       <c r="C56"/>
       <c r="D56"/>
       <c r="E56">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>{"guid":"cb1df36f-5729-423e-9d1a-287db5a433f0","nodeType":11,"position":{"x":18.66668701171875,"y":-1786.666748046875},"targetType":0,"assetTags":{"_tags":[{"_name":"Buff.DeBuff.Stun","_hashCode":1791562953,"_shortName":"Stun","_ancestorHashCodes":[937056111,321157895],"_ancestorNames":["Buff","Buff.DeBuff"]}]},"grantedTags":{"_tags":[{"_name":"Buff.DeBuff.Stun","_hashCode":1791562953,"_shortName":"Stun","_ancestorHashCodes":[937056111,321157895],"_ancestorNames":["Buff","Buff.DeBuff"]}]},"applicationRequiredTags":{"_tags":[]},"applicationImmunityTags":{"_tags":[]},"removeGameEffectsWithTags":{"_tags":[]},"durationType":1,"duration":"4","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[],"stackType":1,"stackLimit":1,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":1,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"_tags":[]},"cancelOnAbilityEnd":false,"buffId":0}</t>
+          <t>{"guid":"e33ab94c-1496-4d6a-ba5e-1afd38bb0c30","nodeType":4,"position":{"x":-452.0,"y":-1786.666748046875},"targetType":1,"searchShapeType":0,"searchLineType":0,"positionSource":0,"positionBindingName":"center","searchCircleRadius":2.5,"searchSectorRadius":2.0,"searchSectorAngle":180.0,"searchLineDirectionOffsetAngle":0.0,"searchLineDirectionWidth":1.0,"searchLineDirectionLength":10.0,"lineStartPositionSource":0,"lineStartBindingName":"","lineEndPositionSource":1,"lineEndBindingName":"","searchLineBetweenWidth":1.0,"searchLineAbsoluteAngle":0.0,"searchLineAbsoluteWidth":1.0,"searchLineAbsoluteLength":10.0,"maxTargets":999,"searchTargetTags":{"_tags":[{"_name":"unitType.monster","_hashCode":-2021655864,"_shortName":"monster","_ancestorHashCodes":[1600484460],"_ancestorNames":["unitType"]}]},"searchExcludeTags":{"_tags":[]}}</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
@@ -1739,11 +1739,11 @@
       <c r="C57"/>
       <c r="D57"/>
       <c r="E57">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>{"guid":"e33ab94c-1496-4d6a-ba5e-1afd38bb0c30","nodeType":4,"position":{"x":-452.0,"y":-1786.666748046875},"targetType":1,"searchShapeType":0,"searchLineType":0,"positionSource":0,"positionBindingName":"center","searchCircleRadius":2.5,"searchSectorRadius":2.0,"searchSectorAngle":180.0,"searchLineDirectionOffsetAngle":0.0,"searchLineDirectionWidth":1.0,"searchLineDirectionLength":10.0,"lineStartPositionSource":0,"lineStartBindingName":"","lineEndPositionSource":1,"lineEndBindingName":"","searchLineBetweenWidth":1.0,"searchLineAbsoluteAngle":0.0,"searchLineAbsoluteWidth":1.0,"searchLineAbsoluteLength":10.0,"maxTargets":999,"searchTargetTags":{"_tags":[{"_name":"unitType.monster","_hashCode":-2021655864,"_shortName":"monster","_ancestorHashCodes":[1600484460],"_ancestorNames":["unitType"]}]},"searchExcludeTags":{"_tags":[]}}</t>
+          <t>{"guid":"432ff1e3-b18d-476d-af80-d39ddc07402a","nodeType":20,"position":{"x":-452.0,"y":-2375.333251953125},"targetType":1,"skeletonDataAsset":null,"skeletonDataAssetPath":"Assets/Res/Spine/SP_Zhanshi/SP_Zhanshi_SkeletonData.asset","animationName":"Skill_attack_1005","animationDuration":"16","isAnimationLooping":false,"timeEffects":[{"triggerTime":7,"portIdValue":2315086,"legacyPortId":"de0ba361-3aba-4ef0-bb07-9b418fcae591"},{"triggerTime":16,"portIdValue":2000539,"legacyPortId":"f41c85e0-7f26-494e-9ffc-4a06c980f811"}],"timeCues":[{"startTime":6,"endTime":55,"portIdValue":2287012,"legacyPortId":"8dea1941-c520-4f9a-aee0-40932c8542ef"}]}</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
@@ -1759,11 +1759,11 @@
       <c r="C58"/>
       <c r="D58"/>
       <c r="E58">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>{"guid":"432ff1e3-b18d-476d-af80-d39ddc07402a","nodeType":20,"position":{"x":-452.0,"y":-2375.333251953125},"targetType":1,"skeletonDataAsset":null,"skeletonDataAssetPath":"Assets/Res/Spine/SP_Zhanshi/SP_Zhanshi_SkeletonData.asset","animationName":"Skill_attack_1005","animationDuration":"16","isAnimationLooping":false,"timeEffects":[{"triggerTime":7,"portIdValue":2315086,"legacyPortId":"de0ba361-3aba-4ef0-bb07-9b418fcae591"},{"triggerTime":16,"portIdValue":2000539,"legacyPortId":"f41c85e0-7f26-494e-9ffc-4a06c980f811"}],"timeCues":[{"startTime":6,"endTime":55,"portIdValue":2287012,"legacyPortId":"8dea1941-c520-4f9a-aee0-40932c8542ef"}]}</t>
+          <t>{"guid":"356907e0-1488-4128-bfcc-7ff73cfc3330","nodeType":0,"position":{"x":-878.6666259765625,"y":-1853.3333740234375},"targetType":1,"skillId":1003,"assetTags":{"_tags":[]},"cancelAbilitiesWithTags":{"_tags":[]},"blockAbilitiesWithTags":{"_tags":[]},"activationOwnedTags":{"_tags":[{"_name":"Skill.Running","_hashCode":-51601538,"_shortName":"Running","_ancestorHashCodes":[1312877309],"_ancestorNames":["Skill"]}]},"activationRequiredTags":{"_tags":[]},"activationBlockedTags":{"_tags":[{"_name":"CD.RuFood","_hashCode":-1045902856,"_shortName":"RuFood","_ancestorHashCodes":[-1137859925],"_ancestorNames":["CD"]},{"_name":"Skill.Running","_hashCode":-51601538,"_shortName":"Running","_ancestorHashCodes":[1312877309],"_ancestorNames":["Skill"]}]},"ongoingBlockedTags":{"_tags":[]},"eventOutputPorts":[]}</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
@@ -1779,11 +1779,11 @@
       <c r="C59"/>
       <c r="D59"/>
       <c r="E59">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>{"guid":"356907e0-1488-4128-bfcc-7ff73cfc3330","nodeType":0,"position":{"x":-878.6666259765625,"y":-1853.3333740234375},"targetType":1,"skillId":1003,"assetTags":{"_tags":[]},"cancelAbilitiesWithTags":{"_tags":[]},"blockAbilitiesWithTags":{"_tags":[]},"activationOwnedTags":{"_tags":[{"_name":"Skill.Running","_hashCode":-51601538,"_shortName":"Running","_ancestorHashCodes":[1312877309],"_ancestorNames":["Skill"]}]},"activationRequiredTags":{"_tags":[]},"activationBlockedTags":{"_tags":[{"_name":"CD.RuFood","_hashCode":-1045902856,"_shortName":"RuFood","_ancestorHashCodes":[-1137859925],"_ancestorNames":["CD"]},{"_name":"Skill.Running","_hashCode":-51601538,"_shortName":"Running","_ancestorHashCodes":[1312877309],"_ancestorNames":["Skill"]}]},"ongoingBlockedTags":{"_tags":[]},"eventOutputPorts":[]}</t>
+          <t>{"guid":"cde57fb8-b693-4da8-a4a8-fd61e56c5dcd","nodeType":12,"position":{"x":676.6666259765625,"y":-1998.0},"targetType":1,"requiredTags":{"_tags":[]},"immunityTags":{"_tags":[]},"destroyWithNode":false,"positionSource":0,"particlePrefab":null,"particlePrefabPath":"Assets/Res/Entity/Effect/ef_zhanshi_jcjt_01.prefab","particleBindingName":"down","particleOffset":{"x":0.0,"y":0.0,"z":0.0},"particleScale":{"x":1.0,"y":1.0,"z":1.0},"attachToTarget":false,"particleLoop":false}</t>
         </is>
       </c>
       <c r="G59"/>
@@ -2067,7 +2067,7 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>{"guid":"cde57fb8-b693-4da8-a4a8-fd61e56c5dcd","nodeType":12,"position":{"x":731.3333740234375,"y":-2490.66650390625},"targetType":1,"requiredTags":{"_tags":[]},"immunityTags":{"_tags":[]},"destroyWithNode":false,"positionSource":0,"particlePrefab":null,"particlePrefabPath":"Assets/Res/Prefab/Effect/ef_Zhanshi_attack_02.prefab","particleBindingName":"down","particleOffset":{"x":5.0,"y":0.0,"z":0.0},"particleScale":{"x":1.0,"y":1.0,"z":1.0},"attachToTarget":false,"particleLoop":false}</t>
+          <t>{"guid":"cde57fb8-b693-4da8-a4a8-fd61e56c5dcd","nodeType":12,"position":{"x":731.3333740234375,"y":-2490.66650390625},"targetType":1,"requiredTags":{"_tags":[]},"immunityTags":{"_tags":[]},"destroyWithNode":false,"positionSource":0,"particlePrefab":null,"particlePrefabPath":"Assets/Res/Entity/Effect/ef_Zhanshi_attack_02.prefab","particleBindingName":"down","particleOffset":{"x":5.0,"y":0.0,"z":0.0},"particleScale":{"x":1.0,"y":1.0,"z":1.0},"attachToTarget":false,"particleLoop":false}</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
@@ -2249,7 +2249,7 @@
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>{"guid":"ce857360-de7e-4457-b348-9c124ce98879","nodeType":8,"position":{"x":1040.666748046875,"y":-2305.333251953125},"targetType":2,"assetTags":{"_tags":[]},"grantedTags":{"_tags":[]},"applicationRequiredTags":{"_tags":[]},"applicationImmunityTags":{"_tags":[]},"removeGameEffectsWithTags":{"_tags":[]},"durationType":2,"duration":"0","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"_tags":[]},"cancelOnAbilityEnd":false,"launchPositionSource":0,"launchBindingName":"center","targetPositionSource":1,"targetBindingName":"center","projectileTargetType":0,"flyOver":true,"offsetAngle":30.0,"curveHeight":0.0,"projectilePrefab":null,"projectilePrefabPath":"Assets/Res/Prefab/Effect/ef_fashi_huoyandan01.prefab","speed":10.0,"maxDistance":10.0,"collisionRadius":0.5,"isPiercing":false,"maxPierceCount":1,"collisionTargetTags":{"_tags":[]},"collisionExcludeTags":{"_tags":[]},"isBouncing":false,"bounceTargetMode":0,"maxBounceCount":3,"bounceSearchRadius":10.0,"canBounceToSameTarget":false,"excludeSourceCamp":true,"bounceAngleOffset":0.0}</t>
+          <t>{"guid":"ce857360-de7e-4457-b348-9c124ce98879","nodeType":8,"position":{"x":1040.666748046875,"y":-2305.333251953125},"targetType":2,"assetTags":{"_tags":[]},"grantedTags":{"_tags":[]},"applicationRequiredTags":{"_tags":[]},"applicationImmunityTags":{"_tags":[]},"removeGameEffectsWithTags":{"_tags":[]},"durationType":2,"duration":"0","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"_tags":[]},"cancelOnAbilityEnd":false,"launchPositionSource":0,"launchBindingName":"center","targetPositionSource":1,"targetBindingName":"center","projectileTargetType":0,"flyOver":true,"offsetAngle":30.0,"curveHeight":0.0,"projectileEntityId":0,"projectilePrefab":null,"projectilePrefabPath":"Assets/Res/Entity/Effect/ef_fashi_huoyandan01.prefab","speed":10.0,"maxDistance":10.0,"collisionRadius":0.5,"isPiercing":false,"maxPierceCount":1,"collisionTargetTags":{"_tags":[]},"collisionExcludeTags":{"_tags":[]},"isBouncing":false,"bounceTargetMode":0,"maxBounceCount":3,"bounceSearchRadius":10.0,"canBounceToSameTarget":false,"excludeSourceCamp":true,"bounceAngleOffset":0.0}</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
@@ -2269,7 +2269,7 @@
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>{"guid":"9a695e91-e218-425e-82ed-1e157bf1b014","nodeType":8,"position":{"x":1022.666748046875,"y":-2131.333251953125},"targetType":2,"assetTags":{"_tags":[]},"grantedTags":{"_tags":[]},"applicationRequiredTags":{"_tags":[]},"applicationImmunityTags":{"_tags":[]},"removeGameEffectsWithTags":{"_tags":[]},"durationType":2,"duration":"0","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"_tags":[]},"cancelOnAbilityEnd":false,"launchPositionSource":0,"launchBindingName":"center","targetPositionSource":1,"targetBindingName":"center","projectileTargetType":0,"flyOver":true,"offsetAngle":0.0,"curveHeight":0.0,"projectilePrefab":null,"projectilePrefabPath":"Assets/Res/Prefab/Effect/ef_fashi_huoyandan01.prefab","speed":10.0,"maxDistance":10.0,"collisionRadius":0.5,"isPiercing":false,"maxPierceCount":1,"collisionTargetTags":{"_tags":[]},"collisionExcludeTags":{"_tags":[]},"isBouncing":false,"bounceTargetMode":0,"maxBounceCount":3,"bounceSearchRadius":10.0,"canBounceToSameTarget":false,"excludeSourceCamp":true,"bounceAngleOffset":0.0}</t>
+          <t>{"guid":"9a695e91-e218-425e-82ed-1e157bf1b014","nodeType":8,"position":{"x":1022.666748046875,"y":-2131.333251953125},"targetType":2,"assetTags":{"_tags":[]},"grantedTags":{"_tags":[]},"applicationRequiredTags":{"_tags":[]},"applicationImmunityTags":{"_tags":[]},"removeGameEffectsWithTags":{"_tags":[]},"durationType":2,"duration":"0","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"_tags":[]},"cancelOnAbilityEnd":false,"launchPositionSource":0,"launchBindingName":"center","targetPositionSource":1,"targetBindingName":"center","projectileTargetType":0,"flyOver":true,"offsetAngle":0.0,"curveHeight":0.0,"projectileEntityId":0,"projectilePrefab":null,"projectilePrefabPath":"Assets/Res/Entity/Effect/ef_fashi_huoyandan01.prefab","speed":10.0,"maxDistance":10.0,"collisionRadius":0.5,"isPiercing":false,"maxPierceCount":1,"collisionTargetTags":{"_tags":[]},"collisionExcludeTags":{"_tags":[]},"isBouncing":false,"bounceTargetMode":0,"maxBounceCount":3,"bounceSearchRadius":10.0,"canBounceToSameTarget":false,"excludeSourceCamp":true,"bounceAngleOffset":0.0}</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
@@ -2289,7 +2289,7 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>{"guid":"d897a922-5756-42cf-ac65-90a48c1e5a17","nodeType":8,"position":{"x":1022.666748046875,"y":-1978.0},"targetType":2,"assetTags":{"_tags":[]},"grantedTags":{"_tags":[]},"applicationRequiredTags":{"_tags":[]},"applicationImmunityTags":{"_tags":[]},"removeGameEffectsWithTags":{"_tags":[]},"durationType":2,"duration":"0","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"_tags":[]},"cancelOnAbilityEnd":false,"launchPositionSource":0,"launchBindingName":"center","targetPositionSource":1,"targetBindingName":"center","projectileTargetType":0,"flyOver":true,"offsetAngle":-30.0,"curveHeight":0.0,"projectilePrefab":null,"projectilePrefabPath":"Assets/Res/Prefab/Effect/ef_fashi_huoyandan01.prefab","speed":10.0,"maxDistance":10.0,"collisionRadius":0.5,"isPiercing":false,"maxPierceCount":1,"collisionTargetTags":{"_tags":[]},"collisionExcludeTags":{"_tags":[]},"isBouncing":false,"bounceTargetMode":0,"maxBounceCount":3,"bounceSearchRadius":10.0,"canBounceToSameTarget":false,"excludeSourceCamp":true,"bounceAngleOffset":0.0}</t>
+          <t>{"guid":"d897a922-5756-42cf-ac65-90a48c1e5a17","nodeType":8,"position":{"x":1022.666748046875,"y":-1978.0},"targetType":2,"assetTags":{"_tags":[]},"grantedTags":{"_tags":[]},"applicationRequiredTags":{"_tags":[]},"applicationImmunityTags":{"_tags":[]},"removeGameEffectsWithTags":{"_tags":[]},"durationType":2,"duration":"0","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"_tags":[]},"cancelOnAbilityEnd":false,"launchPositionSource":0,"launchBindingName":"center","targetPositionSource":1,"targetBindingName":"center","projectileTargetType":0,"flyOver":true,"offsetAngle":-30.0,"curveHeight":0.0,"projectileEntityId":0,"projectilePrefab":null,"projectilePrefabPath":"Assets/Res/Entity/Effect/ef_fashi_huoyandan01.prefab","speed":10.0,"maxDistance":10.0,"collisionRadius":0.5,"isPiercing":false,"maxPierceCount":1,"collisionTargetTags":{"_tags":[]},"collisionExcludeTags":{"_tags":[]},"isBouncing":false,"bounceTargetMode":0,"maxBounceCount":3,"bounceSearchRadius":10.0,"canBounceToSameTarget":false,"excludeSourceCamp":true,"bounceAngleOffset":0.0}</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
@@ -2409,7 +2409,7 @@
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>{"guid":"cde57fb8-b693-4da8-a4a8-fd61e56c5dcd","nodeType":12,"position":{"x":677.3333740234375,"y":-1998.666748046875},"targetType":1,"requiredTags":{"_tags":[]},"immunityTags":{"_tags":[]},"destroyWithNode":false,"positionSource":0,"particlePrefab":null,"particlePrefabPath":"Assets/Res/Prefab/Effect/ef_Zhanshi_zhentianpaoxiao_01.prefab","particleBindingName":"down","particleOffset":{"x":0.0,"y":0.0,"z":0.0},"particleScale":{"x":1.0,"y":1.0,"z":1.0},"attachToTarget":false,"particleLoop":false}</t>
+          <t>{"guid":"cde57fb8-b693-4da8-a4a8-fd61e56c5dcd","nodeType":12,"position":{"x":677.3333740234375,"y":-1998.666748046875},"targetType":1,"requiredTags":{"_tags":[]},"immunityTags":{"_tags":[]},"destroyWithNode":false,"positionSource":0,"particlePrefab":null,"particlePrefabPath":"Assets/Res/Entity/Effect/ef_Zhanshi_zhentianpaoxiao_01.prefab","particleBindingName":"down","particleOffset":{"x":0.0,"y":0.0,"z":0.0},"particleScale":{"x":1.0,"y":1.0,"z":1.0},"attachToTarget":false,"particleLoop":false}</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>{"guid":"cde57fb8-b693-4da8-a4a8-fd61e56c5dcd","nodeType":12,"position":{"x":677.3333740234375,"y":-1998.666748046875},"targetType":1,"requiredTags":{"_tags":[]},"immunityTags":{"_tags":[]},"destroyWithNode":true,"positionSource":0,"particlePrefab":null,"particlePrefabPath":"Assets/Res/Prefab/Effect/ef_zhanshi_xfz_01.prefab","particleBindingName":"down","particleOffset":{"x":0.0,"y":0.0,"z":0.0},"particleScale":{"x":1.0,"y":1.0,"z":1.0},"attachToTarget":true,"particleLoop":true}</t>
+          <t>{"guid":"cde57fb8-b693-4da8-a4a8-fd61e56c5dcd","nodeType":12,"position":{"x":677.3333740234375,"y":-1998.666748046875},"targetType":1,"requiredTags":{"_tags":[]},"immunityTags":{"_tags":[]},"destroyWithNode":true,"positionSource":0,"particlePrefab":null,"particlePrefabPath":"Assets/Res/Entity/Effect/ef_zhanshi_xfz_01.prefab","particleBindingName":"down","particleOffset":{"x":0.0,"y":0.0,"z":0.0},"particleScale":{"x":1.0,"y":1.0,"z":1.0},"attachToTarget":true,"particleLoop":true}</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">

--- a/Design/Excel/ET/Datas/Game/SkillGraph.xlsx
+++ b/Design/Excel/ET/Datas/Game/SkillGraph.xlsx
@@ -687,11 +687,11 @@
       </c>
       <c r="D5"/>
       <c r="E5">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>{"guid":"a8c2d6c0-65f1-4bed-8a6a-70197e84bb56","nodeType":2,"position":{"x":933.3333740234375,"y":226.66667175292969},"targetType":1,"assetTags":{"_tags":[]},"grantedTags":{"_tags":[]},"applicationRequiredTags":{"_tags":[]},"applicationImmunityTags":{"_tags":[]},"removeGameEffectsWithTags":{"_tags":[]},"durationType":0,"duration":"0","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"_tags":[]},"cancelOnAbilityEnd":false,"healSourceType":0,"healFixedValue":2.0,"healFormula":"","healMMCType":0,"healSetByCallerKey":"","healMMCCaptureAttribute":202,"healMMCAttributeSource":0,"healMMCCoefficient":1.0,"healMMCUseSnapshot":true,"healMultiplyByStackCount":false,"healCalculationType":0}</t>
+          <t>{"guid":"7eefd9ae-c57e-439d-b1b6-e7f4e52f2f6f","nodeType":10,"position":{"x":370.66665649414063,"y":484.66665649414063},"targetType":1,"assetTags":{"_tags":[]},"grantedTags":{"_tags":[{"_name":"CD.BeRecBlood","_hashCode":-1099994396,"_shortName":"被动回血","_ancestorHashCodes":[-1137859925],"_ancestorNames":["CD"]}]},"applicationRequiredTags":{"_tags":[]},"applicationImmunityTags":{"_tags":[]},"removeGameEffectsWithTags":{"_tags":[]},"durationType":1,"duration":"3","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"_tags":[]},"cancelOnAbilityEnd":false,"cooldownType":0,"maxCharges":2,"chargeTime":"10"}</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -707,11 +707,11 @@
       <c r="C6"/>
       <c r="D6"/>
       <c r="E6">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>{"guid":"d086a8c9-8557-4a61-8fd2-64b3c1e543a3","nodeType":14,"position":{"x":1148.666748046875,"y":208.00001525878906},"targetType":1,"requiredTags":{"_tags":[]},"immunityTags":{"_tags":[]},"destroyWithNode":false,"positionSource":0,"positionBindingName":"head","textType":1,"fixedText":"","contextDataKey":"Heal","textColor":{"r":0.040635824203491211,"g":1.0,"b":0.0,"a":1.0},"criticalColor":{"r":1.0,"g":0.5,"b":0.0,"a":1.0},"missColor":{"r":0.5,"g":0.5,"b":0.5,"a":1.0},"fontSize":45.0,"criticalFontSize":60.0,"duration":1.5,"offset":{"x":0.0,"y":0.0},"moveDirection":{"x":0.0,"y":1.0}}</t>
+          <t>{"guid":"426755b7-c39a-4524-9cb5-960a31a19c10","nodeType":11,"position":{"x":587.3333740234375,"y":114.66667175292969},"targetType":1,"assetTags":{"_tags":[]},"grantedTags":{"_tags":[]},"applicationRequiredTags":{"_tags":[]},"applicationImmunityTags":{"_tags":[]},"removeGameEffectsWithTags":{"_tags":[]},"durationType":2,"duration":"10","isPeriodic":true,"period":"1","executeOnApplication":false,"attributeModifiers":[],"stackType":1,"stackLimit":1,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"_tags":[{"_name":"CD.BeRecBlood","_hashCode":-1099994396,"_shortName":"被动回血","_ancestorHashCodes":[-1137859925],"_ancestorNames":["CD"]}]},"cancelOnAbilityEnd":true,"buffId":0}</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -727,11 +727,11 @@
       <c r="C7"/>
       <c r="D7"/>
       <c r="E7">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>{"guid":"7eefd9ae-c57e-439d-b1b6-e7f4e52f2f6f","nodeType":10,"position":{"x":370.66665649414063,"y":484.66665649414063},"targetType":1,"assetTags":{"_tags":[]},"grantedTags":{"_tags":[{"_name":"CD.BeRecBlood","_hashCode":-1099994396,"_shortName":"被动回血","_ancestorHashCodes":[-1137859925],"_ancestorNames":["CD"]}]},"applicationRequiredTags":{"_tags":[]},"applicationImmunityTags":{"_tags":[]},"removeGameEffectsWithTags":{"_tags":[]},"durationType":1,"duration":"3","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"_tags":[]},"cancelOnAbilityEnd":false,"cooldownType":0,"maxCharges":2,"chargeTime":"10"}</t>
+          <t>{"guid":"d5809887-df6e-4604-bd09-36cef191ce83","nodeType":0,"position":{"x":113.33334350585938,"y":158.66667175292969},"targetType":1,"skillId":2001,"assetTags":{"_tags":[]},"cancelAbilitiesWithTags":{"_tags":[]},"blockAbilitiesWithTags":{"_tags":[]},"activationOwnedTags":{"_tags":[]},"activationRequiredTags":{"_tags":[]},"activationBlockedTags":{"_tags":[]},"ongoingBlockedTags":{"_tags":[]},"eventOutputPorts":[{"eventType":2,"customEventTag":"","PortId":1103}]}</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -747,11 +747,11 @@
       <c r="C8"/>
       <c r="D8"/>
       <c r="E8">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>{"guid":"426755b7-c39a-4524-9cb5-960a31a19c10","nodeType":11,"position":{"x":587.3333740234375,"y":114.66667175292969},"targetType":1,"assetTags":{"_tags":[]},"grantedTags":{"_tags":[]},"applicationRequiredTags":{"_tags":[]},"applicationImmunityTags":{"_tags":[]},"removeGameEffectsWithTags":{"_tags":[]},"durationType":2,"duration":"10","isPeriodic":true,"period":"1","executeOnApplication":false,"attributeModifiers":[],"stackType":1,"stackLimit":1,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"_tags":[{"_name":"CD.BeRecBlood","_hashCode":-1099994396,"_shortName":"被动回血","_ancestorHashCodes":[-1137859925],"_ancestorNames":["CD"]}]},"cancelOnAbilityEnd":true,"buffId":0}</t>
+          <t>{"guid":"d086a8c9-8557-4a61-8fd2-64b3c1e543a3","nodeType":14,"position":{"x":1148.666748046875,"y":207.33332824707031},"targetType":1,"requiredTags":{"_tags":[]},"immunityTags":{"_tags":[]},"destroyWithNode":false,"positionSource":0,"positionBindingName":"head","textType":1,"fixedText":"","contextDataKey":"Heal","textColor":{"r":0.040635824203491211,"g":1.0,"b":0.0,"a":1.0},"criticalColor":{"r":1.0,"g":0.5,"b":0.0,"a":1.0},"missColor":{"r":0.5,"g":0.5,"b":0.5,"a":1.0},"fontSize":45.0,"criticalFontSize":60.0,"duration":1.5,"offset":{"x":0.0,"y":0.0},"moveDirection":{"x":0.0,"y":1.0}}</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -767,11 +767,11 @@
       <c r="C9"/>
       <c r="D9"/>
       <c r="E9">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>{"guid":"d5809887-df6e-4604-bd09-36cef191ce83","nodeType":0,"position":{"x":146.0,"y":124.66667175292969},"targetType":1,"skillId":2001,"assetTags":{"_tags":[]},"cancelAbilitiesWithTags":{"_tags":[]},"blockAbilitiesWithTags":{"_tags":[]},"activationOwnedTags":{"_tags":[]},"activationRequiredTags":{"_tags":[]},"activationBlockedTags":{"_tags":[]},"ongoingBlockedTags":{"_tags":[]},"eventOutputPorts":[{"eventType":2,"customEventTag":"","PortId":1103}]}</t>
+          <t>{"guid":"a8c2d6c0-65f1-4bed-8a6a-70197e84bb56","nodeType":2,"position":{"x":933.3333740234375,"y":226.66667175292969},"targetType":1,"assetTags":{"_tags":[]},"grantedTags":{"_tags":[]},"applicationRequiredTags":{"_tags":[]},"applicationImmunityTags":{"_tags":[]},"removeGameEffectsWithTags":{"_tags":[]},"durationType":0,"duration":"0","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"_tags":[]},"cancelOnAbilityEnd":false,"healSourceType":0,"healFixedValue":2.0,"healFormula":"","healMMCType":0,"healSetByCallerKey":"","healMMCCaptureAttribute":202,"healMMCAttributeSource":0,"healMMCCoefficient":1.0,"healMMCUseSnapshot":true,"healMultiplyByStackCount":false,"healCalculationType":0}</t>
         </is>
       </c>
       <c r="G9"/>
@@ -949,11 +949,11 @@
       <c r="C18"/>
       <c r="D18"/>
       <c r="E18">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>{"guid":"cde57fb8-b693-4da8-a4a8-fd61e56c5dcd","nodeType":12,"position":{"x":677.3333740234375,"y":-1998.666748046875},"targetType":1,"requiredTags":{"_tags":[]},"immunityTags":{"_tags":[]},"destroyWithNode":false,"positionSource":0,"particlePrefab":null,"particlePrefabPath":"Assets/Res/Entity/Effect/ef_Zhanshi_attack_02.prefab","particleBindingName":"down","particleOffset":{"x":5.0,"y":0.0,"z":0.0},"particleScale":{"x":1.0,"y":1.0,"z":1.0},"attachToTarget":false,"particleLoop":false}</t>
+          <t>{"guid":"f8947676-1084-4228-b991-1509cc7fe851","nodeType":1,"position":{"x":195.33334350585938,"y":-1761.3333740234375},"targetType":0,"assetTags":{"_tags":[]},"grantedTags":{"_tags":[]},"applicationRequiredTags":{"_tags":[]},"applicationImmunityTags":{"_tags":[]},"removeGameEffectsWithTags":{"_tags":[]},"durationType":0,"duration":"0","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"_tags":[]},"cancelOnAbilityEnd":true,"damageType":0,"damageSourceType":0,"damageFixedValue":20.0,"damageFormula":"","damageMMCType":0,"damageSetByCallerKey":"","damageMMCCaptureAttribute":200,"damageMMCAttributeSource":0,"damageMMCCoefficient":1.0,"damageMMCUseSnapshot":true,"damageMultiplyByStackCount":true,"damageCalculationType":0,"enableHitKnockback":false,"knockbackDistance":1.0,"knockbackSpeed":12.0}</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -969,11 +969,11 @@
       <c r="C19"/>
       <c r="D19"/>
       <c r="E19">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>{"guid":"f8947676-1084-4228-b991-1509cc7fe851","nodeType":1,"position":{"x":195.33334350585938,"y":-1761.3333740234375},"targetType":0,"assetTags":{"_tags":[]},"grantedTags":{"_tags":[]},"applicationRequiredTags":{"_tags":[]},"applicationImmunityTags":{"_tags":[]},"removeGameEffectsWithTags":{"_tags":[]},"durationType":0,"duration":"0","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"_tags":[]},"cancelOnAbilityEnd":true,"damageType":0,"damageSourceType":0,"damageFixedValue":20.0,"damageFormula":"","damageMMCType":0,"damageSetByCallerKey":"","damageMMCCaptureAttribute":200,"damageMMCAttributeSource":0,"damageMMCCoefficient":1.0,"damageMMCUseSnapshot":true,"damageMultiplyByStackCount":true,"damageCalculationType":0,"enableHitKnockback":false,"knockbackDistance":1.0,"knockbackSpeed":12.0}</t>
+          <t>{"guid":"cde57fb8-b693-4da8-a4a8-fd61e56c5dcd","nodeType":12,"position":{"x":677.3333740234375,"y":-1998.666748046875},"targetType":1,"requiredTags":{"_tags":[]},"immunityTags":{"_tags":[]},"destroyWithNode":false,"positionSource":0,"particleEntityId":50006,"particlePrefab":null,"particlePrefabPath":"Assets/Res/Entity/Effect/ef_Zhanshi_attack_02.prefab","particleBindingName":"down","particleOffset":{"x":5.0,"y":0.0,"z":0.0},"particleScale":{"x":1.0,"y":1.0,"z":1.0},"attachToTarget":false,"particleLoop":false}</t>
         </is>
       </c>
       <c r="G19"/>
@@ -1355,11 +1355,11 @@
       <c r="C38"/>
       <c r="D38"/>
       <c r="E38">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>{"guid":"cde57fb8-b693-4da8-a4a8-fd61e56c5dcd","nodeType":12,"position":{"x":677.3333740234375,"y":-1998.666748046875},"targetType":1,"requiredTags":{"_tags":[]},"immunityTags":{"_tags":[]},"destroyWithNode":false,"positionSource":0,"particlePrefab":null,"particlePrefabPath":"Assets/Res/Entity/Effect/ef_Zhanshi_zhandounuhou_01.prefab","particleBindingName":"down","particleOffset":{"x":0.0,"y":0.0,"z":0.0},"particleScale":{"x":1.0,"y":1.0,"z":1.0},"attachToTarget":false,"particleLoop":false}</t>
+          <t>{"guid":"c28fb88d-51b1-47b2-be59-859e0ac638e3","nodeType":10,"position":{"x":-1186.6666259765625,"y":-1747.3333740234375},"targetType":1,"assetTags":{"_tags":[]},"grantedTags":{"_tags":[{"_name":"CD.God","_hashCode":1317201809,"_shortName":"God","_ancestorHashCodes":[-1137859925],"_ancestorNames":["CD"]}]},"applicationRequiredTags":{"_tags":[]},"applicationImmunityTags":{"_tags":[]},"removeGameEffectsWithTags":{"_tags":[]},"durationType":1,"duration":"5","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"_tags":[]},"cancelOnAbilityEnd":false,"cooldownType":0,"maxCharges":2,"chargeTime":"10"}</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -1375,11 +1375,11 @@
       <c r="C39"/>
       <c r="D39"/>
       <c r="E39">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>{"guid":"c28fb88d-51b1-47b2-be59-859e0ac638e3","nodeType":10,"position":{"x":-1186.6666259765625,"y":-1747.3333740234375},"targetType":1,"assetTags":{"_tags":[]},"grantedTags":{"_tags":[{"_name":"CD.God","_hashCode":1317201809,"_shortName":"God","_ancestorHashCodes":[-1137859925],"_ancestorNames":["CD"]}]},"applicationRequiredTags":{"_tags":[]},"applicationImmunityTags":{"_tags":[]},"removeGameEffectsWithTags":{"_tags":[]},"durationType":1,"duration":"5","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"_tags":[]},"cancelOnAbilityEnd":false,"cooldownType":0,"maxCharges":2,"chargeTime":"10"}</t>
+          <t>{"guid":"091ecddb-f80b-4c00-aa06-f9bc718618d2","nodeType":22,"position":{"x":-93.333328247070313,"y":-1708.666748046875},"targetType":0,"assetTags":{"_tags":[]},"grantedTags":{"_tags":[]},"applicationRequiredTags":{"_tags":[]},"applicationImmunityTags":{"_tags":[]},"removeGameEffectsWithTags":{"_tags":[]},"durationType":1,"duration":"0.5","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"_tags":[]},"cancelOnAbilityEnd":false,"displaceType":1,"speed":10.0,"distance":3.0,"minDistance":0.5,"pointSource":0,"pointBindingName":""}</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -1395,11 +1395,11 @@
       <c r="C40"/>
       <c r="D40"/>
       <c r="E40">
-        <v>22</v>
+        <v>4</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>{"guid":"091ecddb-f80b-4c00-aa06-f9bc718618d2","nodeType":22,"position":{"x":-93.333328247070313,"y":-1708.666748046875},"targetType":0,"assetTags":{"_tags":[]},"grantedTags":{"_tags":[]},"applicationRequiredTags":{"_tags":[]},"applicationImmunityTags":{"_tags":[]},"removeGameEffectsWithTags":{"_tags":[]},"durationType":1,"duration":"0.5","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"_tags":[]},"cancelOnAbilityEnd":false,"displaceType":1,"speed":10.0,"distance":3.0,"minDistance":0.5,"pointSource":0,"pointBindingName":""}</t>
+          <t>{"guid":"e33ab94c-1496-4d6a-ba5e-1afd38bb0c30","nodeType":4,"position":{"x":-452.0,"y":-1786.666748046875},"targetType":1,"searchShapeType":0,"searchLineType":0,"positionSource":0,"positionBindingName":"center","searchCircleRadius":4.0,"searchSectorRadius":2.0,"searchSectorAngle":180.0,"searchLineDirectionOffsetAngle":0.0,"searchLineDirectionWidth":1.0,"searchLineDirectionLength":10.0,"lineStartPositionSource":0,"lineStartBindingName":"","lineEndPositionSource":1,"lineEndBindingName":"","searchLineBetweenWidth":1.0,"searchLineAbsoluteAngle":0.0,"searchLineAbsoluteWidth":1.0,"searchLineAbsoluteLength":10.0,"maxTargets":999,"searchTargetTags":{"_tags":[{"_name":"unitType.monster","_hashCode":-2021655864,"_shortName":"monster","_ancestorHashCodes":[1600484460],"_ancestorNames":["unitType"]}]},"searchExcludeTags":{"_tags":[]}}</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -1415,11 +1415,11 @@
       <c r="C41"/>
       <c r="D41"/>
       <c r="E41">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>{"guid":"e33ab94c-1496-4d6a-ba5e-1afd38bb0c30","nodeType":4,"position":{"x":-452.0,"y":-1786.666748046875},"targetType":1,"searchShapeType":0,"searchLineType":0,"positionSource":0,"positionBindingName":"center","searchCircleRadius":4.0,"searchSectorRadius":2.0,"searchSectorAngle":180.0,"searchLineDirectionOffsetAngle":0.0,"searchLineDirectionWidth":1.0,"searchLineDirectionLength":10.0,"lineStartPositionSource":0,"lineStartBindingName":"","lineEndPositionSource":1,"lineEndBindingName":"","searchLineBetweenWidth":1.0,"searchLineAbsoluteAngle":0.0,"searchLineAbsoluteWidth":1.0,"searchLineAbsoluteLength":10.0,"maxTargets":999,"searchTargetTags":{"_tags":[{"_name":"unitType.monster","_hashCode":-2021655864,"_shortName":"monster","_ancestorHashCodes":[1600484460],"_ancestorNames":["unitType"]}]},"searchExcludeTags":{"_tags":[]}}</t>
+          <t>{"guid":"432ff1e3-b18d-476d-af80-d39ddc07402a","nodeType":20,"position":{"x":-646.0,"y":-2456.0},"targetType":1,"skeletonDataAsset":null,"skeletonDataAssetPath":"Assets/Res/Spine/SP_Zhanshi/SP_Zhanshi_SkeletonData.asset","animationName":"Skill_attack_1009","animationDuration":"25","isAnimationLooping":false,"timeEffects":[{"triggerTime":4,"portIdValue":2315086,"legacyPortId":"de0ba361-3aba-4ef0-bb07-9b418fcae591"},{"triggerTime":25,"portIdValue":2000539,"legacyPortId":"f41c85e0-7f26-494e-9ffc-4a06c980f811"}],"timeCues":[{"startTime":0,"endTime":75,"portIdValue":2287012,"legacyPortId":"8dea1941-c520-4f9a-aee0-40932c8542ef"}]}</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -1435,11 +1435,11 @@
       <c r="C42"/>
       <c r="D42"/>
       <c r="E42">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>{"guid":"432ff1e3-b18d-476d-af80-d39ddc07402a","nodeType":20,"position":{"x":-646.0,"y":-2456.0},"targetType":1,"skeletonDataAsset":null,"skeletonDataAssetPath":"Assets/Res/Spine/SP_Zhanshi/SP_Zhanshi_SkeletonData.asset","animationName":"Skill_attack_1009","animationDuration":"25","isAnimationLooping":false,"timeEffects":[{"triggerTime":4,"portIdValue":2315086,"legacyPortId":"de0ba361-3aba-4ef0-bb07-9b418fcae591"},{"triggerTime":25,"portIdValue":2000539,"legacyPortId":"f41c85e0-7f26-494e-9ffc-4a06c980f811"}],"timeCues":[{"startTime":0,"endTime":75,"portIdValue":2287012,"legacyPortId":"8dea1941-c520-4f9a-aee0-40932c8542ef"}]}</t>
+          <t>{"guid":"356907e0-1488-4128-bfcc-7ff73cfc3330","nodeType":0,"position":{"x":-878.6666259765625,"y":-1853.3333740234375},"targetType":1,"skillId":1005,"assetTags":{"_tags":[]},"cancelAbilitiesWithTags":{"_tags":[]},"blockAbilitiesWithTags":{"_tags":[]},"activationOwnedTags":{"_tags":[{"_name":"Skill.Running","_hashCode":-51601538,"_shortName":"Running","_ancestorHashCodes":[1312877309],"_ancestorNames":["Skill"]}]},"activationRequiredTags":{"_tags":[]},"activationBlockedTags":{"_tags":[{"_name":"CD.RecBlood","_hashCode":1043024739,"_shortName":"RecBlood","_ancestorHashCodes":[-1137859925],"_ancestorNames":["CD"]},{"_name":"Skill.Running","_hashCode":-51601538,"_shortName":"Running","_ancestorHashCodes":[1312877309],"_ancestorNames":["Skill"]}]},"ongoingBlockedTags":{"_tags":[]},"eventOutputPorts":[]}</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -1455,11 +1455,11 @@
       <c r="C43"/>
       <c r="D43"/>
       <c r="E43">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>{"guid":"356907e0-1488-4128-bfcc-7ff73cfc3330","nodeType":0,"position":{"x":-878.6666259765625,"y":-1853.3333740234375},"targetType":1,"skillId":1005,"assetTags":{"_tags":[]},"cancelAbilitiesWithTags":{"_tags":[]},"blockAbilitiesWithTags":{"_tags":[]},"activationOwnedTags":{"_tags":[{"_name":"Skill.Running","_hashCode":-51601538,"_shortName":"Running","_ancestorHashCodes":[1312877309],"_ancestorNames":["Skill"]}]},"activationRequiredTags":{"_tags":[]},"activationBlockedTags":{"_tags":[{"_name":"CD.RecBlood","_hashCode":1043024739,"_shortName":"RecBlood","_ancestorHashCodes":[-1137859925],"_ancestorNames":["CD"]},{"_name":"Skill.Running","_hashCode":-51601538,"_shortName":"Running","_ancestorHashCodes":[1312877309],"_ancestorNames":["Skill"]}]},"ongoingBlockedTags":{"_tags":[]},"eventOutputPorts":[]}</t>
+          <t>{"guid":"cde57fb8-b693-4da8-a4a8-fd61e56c5dcd","nodeType":12,"position":{"x":677.3333740234375,"y":-1998.666748046875},"targetType":1,"requiredTags":{"_tags":[]},"immunityTags":{"_tags":[]},"destroyWithNode":false,"positionSource":0,"particleEntityId":50009,"particlePrefab":null,"particlePrefabPath":"Assets/Res/Entity/Effect/ef_Zhanshi_zhandounuhou_01.prefab","particleBindingName":"down","particleOffset":{"x":0.0,"y":0.0,"z":0.0},"particleScale":{"x":1.0,"y":1.0,"z":1.0},"attachToTarget":false,"particleLoop":false}</t>
         </is>
       </c>
       <c r="G43"/>
@@ -1477,11 +1477,11 @@
       </c>
       <c r="D44"/>
       <c r="E44">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>{"guid":"cde57fb8-b693-4da8-a4a8-fd61e56c5dcd","nodeType":12,"position":{"x":-304.0,"y":-2072.0},"targetType":1,"requiredTags":{"_tags":[]},"immunityTags":{"_tags":[]},"destroyWithNode":false,"positionSource":0,"particlePrefab":null,"particlePrefabPath":"Assets/Res/Entity/Effect/ef_skill_zhanshi_huifunengliang.prefab","particleBindingName":"down","particleOffset":{"x":0.0,"y":0.0,"z":0.0},"particleScale":{"x":1.0,"y":1.0,"z":1.0},"attachToTarget":false,"particleLoop":false}</t>
+          <t>{"guid":"356907e0-1488-4128-bfcc-7ff73cfc3330","nodeType":0,"position":{"x":-924.6666259765625,"y":-1886.666748046875},"targetType":1,"skillId":1007,"assetTags":{"_tags":[]},"cancelAbilitiesWithTags":{"_tags":[]},"blockAbilitiesWithTags":{"_tags":[]},"activationOwnedTags":{"_tags":[]},"activationRequiredTags":{"_tags":[]},"activationBlockedTags":{"_tags":[{"_name":"CD.RecBlood","_hashCode":1163914435,"_shortName":"回血","_ancestorHashCodes":[-1137859925],"_ancestorNames":["CD"]}]},"ongoingBlockedTags":{"_tags":[]},"eventOutputPorts":[]}</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -1497,11 +1497,11 @@
       <c r="C45"/>
       <c r="D45"/>
       <c r="E45">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>{"guid":"356907e0-1488-4128-bfcc-7ff73cfc3330","nodeType":0,"position":{"x":-924.6666259765625,"y":-1886.666748046875},"targetType":1,"skillId":1007,"assetTags":{"_tags":[]},"cancelAbilitiesWithTags":{"_tags":[]},"blockAbilitiesWithTags":{"_tags":[]},"activationOwnedTags":{"_tags":[]},"activationRequiredTags":{"_tags":[]},"activationBlockedTags":{"_tags":[{"_name":"CD.RecBlood","_hashCode":1163914435,"_shortName":"回血","_ancestorHashCodes":[-1137859925],"_ancestorNames":["CD"]}]},"ongoingBlockedTags":{"_tags":[]},"eventOutputPorts":[]}</t>
+          <t>{"guid":"c28fb88d-51b1-47b2-be59-859e0ac638e3","nodeType":10,"position":{"x":-1156.0,"y":-1801.3333740234375},"targetType":1,"assetTags":{"_tags":[]},"grantedTags":{"_tags":[{"_name":"CD.RecBlood","_hashCode":1163914435,"_shortName":"回血","_ancestorHashCodes":[-1137859925],"_ancestorNames":["CD"]}]},"applicationRequiredTags":{"_tags":[]},"applicationImmunityTags":{"_tags":[]},"removeGameEffectsWithTags":{"_tags":[]},"durationType":1,"duration":"3","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"_tags":[]},"cancelOnAbilityEnd":false,"cooldownType":0,"maxCharges":2,"chargeTime":"10"}</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -1517,11 +1517,11 @@
       <c r="C46"/>
       <c r="D46"/>
       <c r="E46">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>{"guid":"c28fb88d-51b1-47b2-be59-859e0ac638e3","nodeType":10,"position":{"x":-1156.0,"y":-1801.3333740234375},"targetType":1,"assetTags":{"_tags":[]},"grantedTags":{"_tags":[{"_name":"CD.RecBlood","_hashCode":1163914435,"_shortName":"回血","_ancestorHashCodes":[-1137859925],"_ancestorNames":["CD"]}]},"applicationRequiredTags":{"_tags":[]},"applicationImmunityTags":{"_tags":[]},"removeGameEffectsWithTags":{"_tags":[]},"durationType":1,"duration":"3","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"_tags":[]},"cancelOnAbilityEnd":false,"cooldownType":0,"maxCharges":2,"chargeTime":"10"}</t>
+          <t>{"guid":"011aad56-e96c-41eb-9d85-e793d74a40bb","nodeType":7,"position":{"x":-333.33331298828125,"y":-1780.0},"targetType":1,"endType":0}</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -1537,11 +1537,11 @@
       <c r="C47"/>
       <c r="D47"/>
       <c r="E47">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>{"guid":"011aad56-e96c-41eb-9d85-e793d74a40bb","nodeType":7,"position":{"x":-333.33331298828125,"y":-1780.0},"targetType":1,"endType":0}</t>
+          <t>{"guid":"6d127270-5aeb-4542-9183-8d2d028d6786","nodeType":2,"position":{"x":-550.6666259765625,"y":-2050.0},"targetType":1,"assetTags":{"_tags":[]},"grantedTags":{"_tags":[]},"applicationRequiredTags":{"_tags":[]},"applicationImmunityTags":{"_tags":[]},"removeGameEffectsWithTags":{"_tags":[]},"durationType":0,"duration":"0","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"_tags":[]},"cancelOnAbilityEnd":false,"healSourceType":0,"healFixedValue":10.0,"healFormula":"","healMMCType":0,"healSetByCallerKey":"","healMMCCaptureAttribute":1007,"healMMCAttributeSource":0,"healMMCCoefficient":1.0,"healMMCUseSnapshot":true,"healMultiplyByStackCount":false,"healCalculationType":0}</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -1557,11 +1557,11 @@
       <c r="C48"/>
       <c r="D48"/>
       <c r="E48">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>{"guid":"6d127270-5aeb-4542-9183-8d2d028d6786","nodeType":2,"position":{"x":-550.6666259765625,"y":-2050.0},"targetType":1,"assetTags":{"_tags":[]},"grantedTags":{"_tags":[]},"applicationRequiredTags":{"_tags":[]},"applicationImmunityTags":{"_tags":[]},"removeGameEffectsWithTags":{"_tags":[]},"durationType":0,"duration":"0","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"_tags":[]},"cancelOnAbilityEnd":false,"healSourceType":0,"healFixedValue":10.0,"healFormula":"","healMMCType":0,"healSetByCallerKey":"","healMMCCaptureAttribute":1007,"healMMCAttributeSource":0,"healMMCCoefficient":1.0,"healMMCUseSnapshot":true,"healMultiplyByStackCount":false,"healCalculationType":0}</t>
+          <t>{"guid":"becb4d53-8a9e-4dc0-95a3-618d1e79ecc7","nodeType":14,"position":{"x":-303.33331298828125,"y":-1952.666748046875},"targetType":1,"requiredTags":{"_tags":[]},"immunityTags":{"_tags":[]},"destroyWithNode":false,"positionSource":2,"positionBindingName":"head","textType":1,"fixedText":"","contextDataKey":"Heal","textColor":{"r":0.25257891416549683,"g":0.96226418018341064,"b":0.1180134117603302,"a":1.0},"criticalColor":{"r":1.0,"g":0.5,"b":0.0,"a":1.0},"missColor":{"r":0.5,"g":0.5,"b":0.5,"a":1.0},"fontSize":45.0,"criticalFontSize":60.0,"duration":1.5,"offset":{"x":0.0,"y":0.0},"moveDirection":{"x":0.0,"y":1.0}}</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -1577,11 +1577,11 @@
       <c r="C49"/>
       <c r="D49"/>
       <c r="E49">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>{"guid":"becb4d53-8a9e-4dc0-95a3-618d1e79ecc7","nodeType":14,"position":{"x":-303.33331298828125,"y":-1952.666748046875},"targetType":1,"requiredTags":{"_tags":[]},"immunityTags":{"_tags":[]},"destroyWithNode":false,"positionSource":2,"positionBindingName":"head","textType":1,"fixedText":"","contextDataKey":"Heal","textColor":{"r":0.25257891416549683,"g":0.96226418018341064,"b":0.1180134117603302,"a":1.0},"criticalColor":{"r":1.0,"g":0.5,"b":0.0,"a":1.0},"missColor":{"r":0.5,"g":0.5,"b":0.5,"a":1.0},"fontSize":45.0,"criticalFontSize":60.0,"duration":1.5,"offset":{"x":0.0,"y":0.0},"moveDirection":{"x":0.0,"y":1.0}}</t>
+          <t>{"guid":"3cc340e3-1583-428e-ada4-c4e8539725d6","nodeType":3,"position":{"x":-1256.0,"y":-2008.0},"targetType":1,"assetTags":{"_tags":[]},"grantedTags":{"_tags":[]},"applicationRequiredTags":{"_tags":[]},"applicationImmunityTags":{"_tags":[]},"removeGameEffectsWithTags":{"_tags":[]},"durationType":0,"duration":"0","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[{"attrType":1003,"operation":0,"magnitudeSourceType":0,"fixedValue":100.0,"formula":"","mmcType":0,"setByCallerKey":"","mmcCaptureAttribute":1006,"mmcAttributeSource":0,"mmcCoefficient":1.0,"mmcUseSnapshot":true}],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"_tags":[]},"cancelOnAbilityEnd":false}</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -1597,11 +1597,11 @@
       <c r="C50"/>
       <c r="D50"/>
       <c r="E50">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>{"guid":"3cc340e3-1583-428e-ada4-c4e8539725d6","nodeType":3,"position":{"x":-1256.0,"y":-2008.0},"targetType":1,"assetTags":{"_tags":[]},"grantedTags":{"_tags":[]},"applicationRequiredTags":{"_tags":[]},"applicationImmunityTags":{"_tags":[]},"removeGameEffectsWithTags":{"_tags":[]},"durationType":0,"duration":"0","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[{"attrType":1003,"operation":0,"magnitudeSourceType":0,"fixedValue":100.0,"formula":"","mmcType":0,"setByCallerKey":"","mmcCaptureAttribute":1006,"mmcAttributeSource":0,"mmcCoefficient":1.0,"mmcUseSnapshot":true}],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"_tags":[]},"cancelOnAbilityEnd":false}</t>
+          <t>{"guid":"cde57fb8-b693-4da8-a4a8-fd61e56c5dcd","nodeType":12,"position":{"x":-303.33331298828125,"y":-2072.666748046875},"targetType":1,"requiredTags":{"_tags":[]},"immunityTags":{"_tags":[]},"destroyWithNode":false,"positionSource":0,"particleEntityId":50004,"particlePrefab":null,"particlePrefabPath":"Assets/Res/Entity/Effect/ef_skill_zhanshi_huifunengliang.prefab","particleBindingName":"down","particleOffset":{"x":0.0,"y":0.0,"z":0.0},"particleScale":{"x":1.0,"y":1.0,"z":1.0},"attachToTarget":false,"particleLoop":false}</t>
         </is>
       </c>
       <c r="G50"/>
@@ -1683,7 +1683,7 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>{"guid":"93ec5a43-cc34-4e4a-acb3-39da2f2c3010","nodeType":12,"position":{"x":468.66665649414063,"y":-1749.3333740234375},"targetType":1,"requiredTags":{"_tags":[]},"immunityTags":{"_tags":[]},"destroyWithNode":true,"positionSource":2,"particlePrefab":null,"particlePrefabPath":"Assets/Res/Entity/Effect/ef_Xuanyun_01.prefab","particleBindingName":"head","particleOffset":{"x":0.0,"y":0.0,"z":0.0},"particleScale":{"x":1.0,"y":1.0,"z":1.0},"attachToTarget":true,"particleLoop":true}</t>
+          <t>{"guid":"93ec5a43-cc34-4e4a-acb3-39da2f2c3010","nodeType":12,"position":{"x":468.66665649414063,"y":-1749.3333740234375},"targetType":1,"requiredTags":{"_tags":[]},"immunityTags":{"_tags":[]},"destroyWithNode":true,"positionSource":2,"particleEntityId":0,"particlePrefab":null,"particlePrefabPath":"Assets/Res/Entity/Effect/ef_Xuanyun_01.prefab","particleBindingName":"head","particleOffset":{"x":0.0,"y":0.0,"z":0.0},"particleScale":{"x":1.0,"y":1.0,"z":1.0},"attachToTarget":true,"particleLoop":true}</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
@@ -1783,7 +1783,7 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>{"guid":"cde57fb8-b693-4da8-a4a8-fd61e56c5dcd","nodeType":12,"position":{"x":676.6666259765625,"y":-1998.0},"targetType":1,"requiredTags":{"_tags":[]},"immunityTags":{"_tags":[]},"destroyWithNode":false,"positionSource":0,"particlePrefab":null,"particlePrefabPath":"Assets/Res/Entity/Effect/ef_zhanshi_jcjt_01.prefab","particleBindingName":"down","particleOffset":{"x":0.0,"y":0.0,"z":0.0},"particleScale":{"x":1.0,"y":1.0,"z":1.0},"attachToTarget":false,"particleLoop":false}</t>
+          <t>{"guid":"cde57fb8-b693-4da8-a4a8-fd61e56c5dcd","nodeType":12,"position":{"x":676.6666259765625,"y":-1998.0},"targetType":1,"requiredTags":{"_tags":[]},"immunityTags":{"_tags":[]},"destroyWithNode":false,"positionSource":0,"particleEntityId":50007,"particlePrefab":null,"particlePrefabPath":"Assets/Res/Entity/Effect/ef_zhanshi_jcjt_01.prefab","particleBindingName":"down","particleOffset":{"x":0.0,"y":0.0,"z":0.0},"particleScale":{"x":1.0,"y":1.0,"z":1.0},"attachToTarget":false,"particleLoop":false}</t>
         </is>
       </c>
       <c r="G59"/>
@@ -1841,11 +1841,11 @@
       <c r="C62"/>
       <c r="D62"/>
       <c r="E62">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>{"guid":"432ff1e3-b18d-476d-af80-d39ddc07402a","nodeType":20,"position":{"x":-502.66665649414063,"y":-2384.0},"targetType":1,"skeletonDataAsset":null,"skeletonDataAssetPath":"Assets/Res/Spine/SP_Zhanshi/SP_Zhanshi_SkeletonData.asset","animationName":"Stand","animationDuration":"24","isAnimationLooping":false,"timeEffects":[{"triggerTime":25,"portIdValue":2000539,"legacyPortId":"f41c85e0-7f26-494e-9ffc-4a06c980f811"}],"timeCues":[]}</t>
+          <t>{"guid":"c28fb88d-51b1-47b2-be59-859e0ac638e3","nodeType":10,"position":{"x":-1186.6666259765625,"y":-1747.3333740234375},"targetType":1,"assetTags":{"_tags":[]},"grantedTags":{"_tags":[{"_name":"CD.SpeedUp","_hashCode":-605747253,"_shortName":"急速","_ancestorHashCodes":[-1137859925],"_ancestorNames":["CD"]}]},"applicationRequiredTags":{"_tags":[]},"applicationImmunityTags":{"_tags":[]},"removeGameEffectsWithTags":{"_tags":[]},"durationType":1,"duration":"10","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"_tags":[]},"cancelOnAbilityEnd":false,"cooldownType":0,"maxCharges":2,"chargeTime":"10"}</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
@@ -1861,11 +1861,11 @@
       <c r="C63"/>
       <c r="D63"/>
       <c r="E63">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>{"guid":"c28fb88d-51b1-47b2-be59-859e0ac638e3","nodeType":10,"position":{"x":-1186.6666259765625,"y":-1747.3333740234375},"targetType":1,"assetTags":{"_tags":[]},"grantedTags":{"_tags":[{"_name":"CD.SpeedUp","_hashCode":-605747253,"_shortName":"急速","_ancestorHashCodes":[-1137859925],"_ancestorNames":["CD"]}]},"applicationRequiredTags":{"_tags":[]},"applicationImmunityTags":{"_tags":[]},"removeGameEffectsWithTags":{"_tags":[]},"durationType":1,"duration":"10","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"_tags":[]},"cancelOnAbilityEnd":false,"cooldownType":0,"maxCharges":2,"chargeTime":"10"}</t>
+          <t>{"guid":"356907e0-1488-4128-bfcc-7ff73cfc3330","nodeType":0,"position":{"x":-878.6666259765625,"y":-1853.3333740234375},"targetType":1,"skillId":1009,"assetTags":{"_tags":[]},"cancelAbilitiesWithTags":{"_tags":[]},"blockAbilitiesWithTags":{"_tags":[]},"activationOwnedTags":{"_tags":[]},"activationRequiredTags":{"_tags":[]},"activationBlockedTags":{"_tags":[{"_name":"CD.SpeedUp","_hashCode":-605747253,"_shortName":"急速","_ancestorHashCodes":[-1137859925],"_ancestorNames":["CD"]}]},"ongoingBlockedTags":{"_tags":[]},"eventOutputPorts":[]}</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
@@ -1885,7 +1885,7 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>{"guid":"632c75e2-152b-4376-8e9e-62c0e74f92d0","nodeType":11,"position":{"x":-514.6666259765625,"y":-1880.0},"targetType":1,"assetTags":{"_tags":[]},"grantedTags":{"_tags":[]},"applicationRequiredTags":{"_tags":[]},"applicationImmunityTags":{"_tags":[]},"removeGameEffectsWithTags":{"_tags":[]},"durationType":1,"duration":"7","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[{"attrType":300,"operation":0,"magnitudeSourceType":0,"fixedValue":10.0,"formula":"","mmcType":0,"setByCallerKey":"","mmcCaptureAttribute":200,"mmcAttributeSource":0,"mmcCoefficient":1.0,"mmcUseSnapshot":true}],"stackType":2,"stackLimit":1,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"_tags":[]},"cancelOnAbilityEnd":false,"buffId":0}</t>
+          <t>{"guid":"632c75e2-152b-4376-8e9e-62c0e74f92d0","nodeType":11,"position":{"x":-502.66665649414063,"y":-1890.666748046875},"targetType":1,"assetTags":{"_tags":[]},"grantedTags":{"_tags":[]},"applicationRequiredTags":{"_tags":[]},"applicationImmunityTags":{"_tags":[]},"removeGameEffectsWithTags":{"_tags":[]},"durationType":1,"duration":"7","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[{"attrType":300,"operation":0,"magnitudeSourceType":0,"fixedValue":10.0,"formula":"","mmcType":0,"setByCallerKey":"","mmcCaptureAttribute":200,"mmcAttributeSource":0,"mmcCoefficient":1.0,"mmcUseSnapshot":true}],"stackType":2,"stackLimit":1,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"_tags":[]},"cancelOnAbilityEnd":false,"buffId":0}</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
@@ -1901,11 +1901,11 @@
       <c r="C65"/>
       <c r="D65"/>
       <c r="E65">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>{"guid":"356907e0-1488-4128-bfcc-7ff73cfc3330","nodeType":0,"position":{"x":-878.6666259765625,"y":-1853.3333740234375},"targetType":1,"skillId":1009,"assetTags":{"_tags":[]},"cancelAbilitiesWithTags":{"_tags":[]},"blockAbilitiesWithTags":{"_tags":[]},"activationOwnedTags":{"_tags":[]},"activationRequiredTags":{"_tags":[]},"activationBlockedTags":{"_tags":[{"_name":"CD.SpeedUp","_hashCode":-605747253,"_shortName":"急速","_ancestorHashCodes":[-1137859925],"_ancestorNames":["CD"]}]},"ongoingBlockedTags":{"_tags":[]},"eventOutputPorts":[]}</t>
+          <t>{"guid":"432ff1e3-b18d-476d-af80-d39ddc07402a","nodeType":20,"position":{"x":-502.66665649414063,"y":-2384.0},"targetType":1,"skeletonDataAsset":null,"skeletonDataAssetPath":"Assets/Res/Spine/SP_Zhanshi/SP_Zhanshi_SkeletonData.asset","animationName":"Stand","animationDuration":"24","isAnimationLooping":false,"timeEffects":[{"triggerTime":25,"portIdValue":2000539,"legacyPortId":"f41c85e0-7f26-494e-9ffc-4a06c980f811"}],"timeCues":[]}</t>
         </is>
       </c>
       <c r="G65"/>
@@ -1943,11 +1943,11 @@
       <c r="C67"/>
       <c r="D67"/>
       <c r="E67">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>{"guid":"2cfdacd2-0186-49dd-b177-4eb8c0ad87bd","nodeType":7,"position":{"x":731.3333740234375,"y":-2142.66650390625},"targetType":1,"endType":0}</t>
+          <t>{"guid":"c28fb88d-51b1-47b2-be59-859e0ac638e3","nodeType":10,"position":{"x":-1130.6666259765625,"y":-2232.0},"targetType":1,"assetTags":{"_tags":[]},"grantedTags":{"_tags":[{"_name":"CD.Sweep","_hashCode":-303359587,"_shortName":"Sweep","_ancestorHashCodes":[-1137859925],"_ancestorNames":["CD"]}]},"applicationRequiredTags":{"_tags":[]},"applicationImmunityTags":{"_tags":[]},"removeGameEffectsWithTags":{"_tags":[]},"durationType":1,"duration":"1","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"_tags":[]},"cancelOnAbilityEnd":false,"cooldownType":0,"maxCharges":2,"chargeTime":"10"}</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
@@ -1963,11 +1963,11 @@
       <c r="C68"/>
       <c r="D68"/>
       <c r="E68">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>{"guid":"c28fb88d-51b1-47b2-be59-859e0ac638e3","nodeType":10,"position":{"x":-1130.6666259765625,"y":-2232.0},"targetType":1,"assetTags":{"_tags":[]},"grantedTags":{"_tags":[{"_name":"CD.Sweep","_hashCode":-303359587,"_shortName":"Sweep","_ancestorHashCodes":[-1137859925],"_ancestorNames":["CD"]}]},"applicationRequiredTags":{"_tags":[]},"applicationImmunityTags":{"_tags":[]},"removeGameEffectsWithTags":{"_tags":[]},"durationType":1,"duration":"1","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"_tags":[]},"cancelOnAbilityEnd":false,"cooldownType":0,"maxCharges":2,"chargeTime":"10"}</t>
+          <t>{"guid":"432ff1e3-b18d-476d-af80-d39ddc07402a","nodeType":20,"position":{"x":-415.33331298828125,"y":-2827.333251953125},"targetType":1,"skeletonDataAsset":null,"skeletonDataAssetPath":"Assets/Res/Spine/SP_Zhanshi/SP_Zhanshi_SkeletonData.asset","animationName":"Skill_attack_1001","animationDuration":"18","isAnimationLooping":false,"timeEffects":[{"triggerTime":7,"portIdValue":2315086,"legacyPortId":"de0ba361-3aba-4ef0-bb07-9b418fcae591"},{"triggerTime":18,"portIdValue":2649436,"legacyPortId":"84e238a8-5baf-470e-829f-186695064945"}],"timeCues":[{"startTime":7,"endTime":48,"portIdValue":2287012,"legacyPortId":"8dea1941-c520-4f9a-aee0-40932c8542ef"}]}</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
@@ -1983,11 +1983,11 @@
       <c r="C69"/>
       <c r="D69"/>
       <c r="E69">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>{"guid":"432ff1e3-b18d-476d-af80-d39ddc07402a","nodeType":20,"position":{"x":-415.33331298828125,"y":-2827.333251953125},"targetType":1,"skeletonDataAsset":null,"skeletonDataAssetPath":"Assets/Res/Spine/SP_Zhanshi/SP_Zhanshi_SkeletonData.asset","animationName":"Skill_attack_1001","animationDuration":"18","isAnimationLooping":false,"timeEffects":[{"triggerTime":7,"portIdValue":2315086,"legacyPortId":"de0ba361-3aba-4ef0-bb07-9b418fcae591"},{"triggerTime":18,"portIdValue":2649436,"legacyPortId":"84e238a8-5baf-470e-829f-186695064945"}],"timeCues":[{"startTime":7,"endTime":48,"portIdValue":2287012,"legacyPortId":"8dea1941-c520-4f9a-aee0-40932c8542ef"}]}</t>
+          <t>{"guid":"9d6f459d-b588-4b64-843b-1b71e8f299ae","nodeType":3,"position":{"x":-1130.6666259765625,"y":-2479.333251953125},"targetType":1,"assetTags":{"_tags":[]},"grantedTags":{"_tags":[]},"applicationRequiredTags":{"_tags":[]},"applicationImmunityTags":{"_tags":[]},"removeGameEffectsWithTags":{"_tags":[]},"durationType":0,"duration":"0","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[{"attrType":1003,"operation":0,"magnitudeSourceType":0,"fixedValue":-10.0,"formula":"","mmcType":0,"setByCallerKey":"","mmcCaptureAttribute":200,"mmcAttributeSource":0,"mmcCoefficient":1.0,"mmcUseSnapshot":true}],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"_tags":[]},"cancelOnAbilityEnd":true}</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
@@ -2003,11 +2003,11 @@
       <c r="C70"/>
       <c r="D70"/>
       <c r="E70">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>{"guid":"9d6f459d-b588-4b64-843b-1b71e8f299ae","nodeType":3,"position":{"x":-1130.6666259765625,"y":-2479.333251953125},"targetType":1,"assetTags":{"_tags":[]},"grantedTags":{"_tags":[]},"applicationRequiredTags":{"_tags":[]},"applicationImmunityTags":{"_tags":[]},"removeGameEffectsWithTags":{"_tags":[]},"durationType":0,"duration":"0","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[{"attrType":1003,"operation":0,"magnitudeSourceType":0,"fixedValue":-10.0,"formula":"","mmcType":0,"setByCallerKey":"","mmcCaptureAttribute":200,"mmcAttributeSource":0,"mmcCoefficient":1.0,"mmcUseSnapshot":true}],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"_tags":[]},"cancelOnAbilityEnd":true}</t>
+          <t>{"guid":"356907e0-1488-4128-bfcc-7ff73cfc3330","nodeType":0,"position":{"x":-843.3333740234375,"y":-2480.0},"targetType":1,"skillId":1001,"assetTags":{"_tags":[]},"cancelAbilitiesWithTags":{"_tags":[]},"blockAbilitiesWithTags":{"_tags":[]},"activationOwnedTags":{"_tags":[]},"activationRequiredTags":{"_tags":[]},"activationBlockedTags":{"_tags":[{"_name":"CD.Sweep","_hashCode":-303359587,"_shortName":"Sweep","_ancestorHashCodes":[-1137859925],"_ancestorNames":["CD"]}]},"ongoingBlockedTags":{"_tags":[]},"eventOutputPorts":[]}</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
@@ -2023,11 +2023,11 @@
       <c r="C71"/>
       <c r="D71"/>
       <c r="E71">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>{"guid":"356907e0-1488-4128-bfcc-7ff73cfc3330","nodeType":0,"position":{"x":-843.3333740234375,"y":-2480.0},"targetType":1,"skillId":1001,"assetTags":{"_tags":[]},"cancelAbilitiesWithTags":{"_tags":[]},"blockAbilitiesWithTags":{"_tags":[]},"activationOwnedTags":{"_tags":[]},"activationRequiredTags":{"_tags":[]},"activationBlockedTags":{"_tags":[{"_name":"CD.Sweep","_hashCode":-303359587,"_shortName":"Sweep","_ancestorHashCodes":[-1137859925],"_ancestorNames":["CD"]}]},"ongoingBlockedTags":{"_tags":[]},"eventOutputPorts":[]}</t>
+          <t>{"guid":"f8947676-1084-4228-b991-1509cc7fe851","nodeType":1,"position":{"x":974.666748046875,"y":-2340.66650390625},"targetType":0,"assetTags":{"_tags":[]},"grantedTags":{"_tags":[]},"applicationRequiredTags":{"_tags":[]},"applicationImmunityTags":{"_tags":[]},"removeGameEffectsWithTags":{"_tags":[]},"durationType":0,"duration":"0","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"_tags":[]},"cancelOnAbilityEnd":true,"damageType":0,"damageSourceType":2,"damageFixedValue":10.0,"damageFormula":"","damageMMCType":0,"damageSetByCallerKey":"","damageMMCCaptureAttribute":1006,"damageMMCAttributeSource":0,"damageMMCCoefficient":1.0,"damageMMCUseSnapshot":true,"damageMultiplyByStackCount":false,"damageCalculationType":0,"enableHitKnockback":true,"knockbackDistance":1.0,"knockbackSpeed":12.0}</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
@@ -2043,11 +2043,11 @@
       <c r="C72"/>
       <c r="D72"/>
       <c r="E72">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>{"guid":"f8947676-1084-4228-b991-1509cc7fe851","nodeType":1,"position":{"x":974.666748046875,"y":-2340.66650390625},"targetType":0,"assetTags":{"_tags":[]},"grantedTags":{"_tags":[]},"applicationRequiredTags":{"_tags":[]},"applicationImmunityTags":{"_tags":[]},"removeGameEffectsWithTags":{"_tags":[]},"durationType":0,"duration":"0","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"_tags":[]},"cancelOnAbilityEnd":true,"damageType":0,"damageSourceType":2,"damageFixedValue":10.0,"damageFormula":"","damageMMCType":0,"damageSetByCallerKey":"","damageMMCCaptureAttribute":1006,"damageMMCAttributeSource":0,"damageMMCCoefficient":1.0,"damageMMCUseSnapshot":true,"damageMultiplyByStackCount":false,"damageCalculationType":0,"enableHitKnockback":true,"knockbackDistance":1.0,"knockbackSpeed":12.0}</t>
+          <t>{"guid":"e33ab94c-1496-4d6a-ba5e-1afd38bb0c30","nodeType":4,"position":{"x":731.3333740234375,"y":-2344.0},"targetType":1,"searchShapeType":1,"searchLineType":0,"positionSource":0,"positionBindingName":"center","searchCircleRadius":5.0,"searchSectorRadius":5.0,"searchSectorAngle":180.0,"searchLineDirectionOffsetAngle":0.0,"searchLineDirectionWidth":1.0,"searchLineDirectionLength":10.0,"lineStartPositionSource":0,"lineStartBindingName":"","lineEndPositionSource":1,"lineEndBindingName":"","searchLineBetweenWidth":1.0,"searchLineAbsoluteAngle":0.0,"searchLineAbsoluteWidth":1.0,"searchLineAbsoluteLength":10.0,"maxTargets":999,"searchTargetTags":{"_tags":[{"_name":"unitType.monster","_hashCode":-2021655864,"_shortName":"monster","_ancestorHashCodes":[1600484460],"_ancestorNames":["unitType"]}]},"searchExcludeTags":{"_tags":[]}}</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
@@ -2063,11 +2063,11 @@
       <c r="C73"/>
       <c r="D73"/>
       <c r="E73">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>{"guid":"cde57fb8-b693-4da8-a4a8-fd61e56c5dcd","nodeType":12,"position":{"x":731.3333740234375,"y":-2490.66650390625},"targetType":1,"requiredTags":{"_tags":[]},"immunityTags":{"_tags":[]},"destroyWithNode":false,"positionSource":0,"particlePrefab":null,"particlePrefabPath":"Assets/Res/Entity/Effect/ef_Zhanshi_attack_02.prefab","particleBindingName":"down","particleOffset":{"x":5.0,"y":0.0,"z":0.0},"particleScale":{"x":1.0,"y":1.0,"z":1.0},"attachToTarget":false,"particleLoop":false}</t>
+          <t>{"guid":"2cfdacd2-0186-49dd-b177-4eb8c0ad87bd","nodeType":7,"position":{"x":731.3333740234375,"y":-2142.66650390625},"targetType":1,"endType":0}</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
@@ -2083,11 +2083,11 @@
       <c r="C74"/>
       <c r="D74"/>
       <c r="E74">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>{"guid":"e33ab94c-1496-4d6a-ba5e-1afd38bb0c30","nodeType":4,"position":{"x":731.3333740234375,"y":-2344.0},"targetType":1,"searchShapeType":1,"searchLineType":0,"positionSource":0,"positionBindingName":"center","searchCircleRadius":5.0,"searchSectorRadius":5.0,"searchSectorAngle":180.0,"searchLineDirectionOffsetAngle":0.0,"searchLineDirectionWidth":1.0,"searchLineDirectionLength":10.0,"lineStartPositionSource":0,"lineStartBindingName":"","lineEndPositionSource":1,"lineEndBindingName":"","searchLineBetweenWidth":1.0,"searchLineAbsoluteAngle":0.0,"searchLineAbsoluteWidth":1.0,"searchLineAbsoluteLength":10.0,"maxTargets":999,"searchTargetTags":{"_tags":[{"_name":"unitType.monster","_hashCode":-2021655864,"_shortName":"monster","_ancestorHashCodes":[1600484460],"_ancestorNames":["unitType"]}]},"searchExcludeTags":{"_tags":[]}}</t>
+          <t>{"guid":"cde57fb8-b693-4da8-a4a8-fd61e56c5dcd","nodeType":12,"position":{"x":731.3333740234375,"y":-2491.333251953125},"targetType":1,"requiredTags":{"_tags":[]},"immunityTags":{"_tags":[]},"destroyWithNode":false,"positionSource":0,"particleEntityId":50006,"particlePrefab":null,"particlePrefabPath":"Assets/Res/Entity/Effect/ef_Zhanshi_attack_02.prefab","particleBindingName":"down","particleOffset":{"x":5.0,"y":0.0,"z":0.0},"particleScale":{"x":1.0,"y":1.0,"z":1.0},"attachToTarget":false,"particleLoop":false}</t>
         </is>
       </c>
       <c r="G74"/>
@@ -2249,7 +2249,7 @@
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>{"guid":"ce857360-de7e-4457-b348-9c124ce98879","nodeType":8,"position":{"x":1040.666748046875,"y":-2305.333251953125},"targetType":2,"assetTags":{"_tags":[]},"grantedTags":{"_tags":[]},"applicationRequiredTags":{"_tags":[]},"applicationImmunityTags":{"_tags":[]},"removeGameEffectsWithTags":{"_tags":[]},"durationType":2,"duration":"0","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"_tags":[]},"cancelOnAbilityEnd":false,"launchPositionSource":0,"launchBindingName":"center","targetPositionSource":1,"targetBindingName":"center","projectileTargetType":0,"flyOver":true,"offsetAngle":30.0,"curveHeight":0.0,"projectileEntityId":0,"projectilePrefab":null,"projectilePrefabPath":"Assets/Res/Entity/Effect/ef_fashi_huoyandan01.prefab","speed":10.0,"maxDistance":10.0,"collisionRadius":0.5,"isPiercing":false,"maxPierceCount":1,"collisionTargetTags":{"_tags":[]},"collisionExcludeTags":{"_tags":[]},"isBouncing":false,"bounceTargetMode":0,"maxBounceCount":3,"bounceSearchRadius":10.0,"canBounceToSameTarget":false,"excludeSourceCamp":true,"bounceAngleOffset":0.0}</t>
+          <t>{"guid":"ce857360-de7e-4457-b348-9c124ce98879","nodeType":8,"position":{"x":1040.666748046875,"y":-2305.333251953125},"targetType":2,"assetTags":{"_tags":[]},"grantedTags":{"_tags":[]},"applicationRequiredTags":{"_tags":[]},"applicationImmunityTags":{"_tags":[]},"removeGameEffectsWithTags":{"_tags":[]},"durationType":2,"duration":"0","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"_tags":[]},"cancelOnAbilityEnd":false,"launchPositionSource":0,"launchBindingName":"center","targetPositionSource":1,"targetBindingName":"center","projectileTargetType":0,"flyOver":true,"offsetAngle":30.0,"curveHeight":0.0,"projectileEntityId":50002,"projectilePrefab":null,"projectilePrefabPath":"Assets/Res/Entity/Effect/ef_fashi_huoyandan01.prefab","speed":10.0,"maxDistance":10.0,"collisionRadius":0.5,"isPiercing":false,"maxPierceCount":1,"collisionTargetTags":{"_tags":[]},"collisionExcludeTags":{"_tags":[]},"isBouncing":false,"bounceTargetMode":0,"maxBounceCount":3,"bounceSearchRadius":10.0,"canBounceToSameTarget":false,"excludeSourceCamp":true,"bounceAngleOffset":0.0}</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
@@ -2269,7 +2269,7 @@
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>{"guid":"9a695e91-e218-425e-82ed-1e157bf1b014","nodeType":8,"position":{"x":1022.666748046875,"y":-2131.333251953125},"targetType":2,"assetTags":{"_tags":[]},"grantedTags":{"_tags":[]},"applicationRequiredTags":{"_tags":[]},"applicationImmunityTags":{"_tags":[]},"removeGameEffectsWithTags":{"_tags":[]},"durationType":2,"duration":"0","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"_tags":[]},"cancelOnAbilityEnd":false,"launchPositionSource":0,"launchBindingName":"center","targetPositionSource":1,"targetBindingName":"center","projectileTargetType":0,"flyOver":true,"offsetAngle":0.0,"curveHeight":0.0,"projectileEntityId":0,"projectilePrefab":null,"projectilePrefabPath":"Assets/Res/Entity/Effect/ef_fashi_huoyandan01.prefab","speed":10.0,"maxDistance":10.0,"collisionRadius":0.5,"isPiercing":false,"maxPierceCount":1,"collisionTargetTags":{"_tags":[]},"collisionExcludeTags":{"_tags":[]},"isBouncing":false,"bounceTargetMode":0,"maxBounceCount":3,"bounceSearchRadius":10.0,"canBounceToSameTarget":false,"excludeSourceCamp":true,"bounceAngleOffset":0.0}</t>
+          <t>{"guid":"9a695e91-e218-425e-82ed-1e157bf1b014","nodeType":8,"position":{"x":1022.666748046875,"y":-2131.333251953125},"targetType":2,"assetTags":{"_tags":[]},"grantedTags":{"_tags":[]},"applicationRequiredTags":{"_tags":[]},"applicationImmunityTags":{"_tags":[]},"removeGameEffectsWithTags":{"_tags":[]},"durationType":2,"duration":"0","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"_tags":[]},"cancelOnAbilityEnd":false,"launchPositionSource":0,"launchBindingName":"center","targetPositionSource":1,"targetBindingName":"center","projectileTargetType":0,"flyOver":true,"offsetAngle":0.0,"curveHeight":0.0,"projectileEntityId":50002,"projectilePrefab":null,"projectilePrefabPath":"Assets/Res/Entity/Effect/ef_fashi_huoyandan01.prefab","speed":10.0,"maxDistance":10.0,"collisionRadius":0.5,"isPiercing":false,"maxPierceCount":1,"collisionTargetTags":{"_tags":[]},"collisionExcludeTags":{"_tags":[]},"isBouncing":false,"bounceTargetMode":0,"maxBounceCount":3,"bounceSearchRadius":10.0,"canBounceToSameTarget":false,"excludeSourceCamp":true,"bounceAngleOffset":0.0}</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
@@ -2289,7 +2289,7 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>{"guid":"d897a922-5756-42cf-ac65-90a48c1e5a17","nodeType":8,"position":{"x":1022.666748046875,"y":-1978.0},"targetType":2,"assetTags":{"_tags":[]},"grantedTags":{"_tags":[]},"applicationRequiredTags":{"_tags":[]},"applicationImmunityTags":{"_tags":[]},"removeGameEffectsWithTags":{"_tags":[]},"durationType":2,"duration":"0","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"_tags":[]},"cancelOnAbilityEnd":false,"launchPositionSource":0,"launchBindingName":"center","targetPositionSource":1,"targetBindingName":"center","projectileTargetType":0,"flyOver":true,"offsetAngle":-30.0,"curveHeight":0.0,"projectileEntityId":0,"projectilePrefab":null,"projectilePrefabPath":"Assets/Res/Entity/Effect/ef_fashi_huoyandan01.prefab","speed":10.0,"maxDistance":10.0,"collisionRadius":0.5,"isPiercing":false,"maxPierceCount":1,"collisionTargetTags":{"_tags":[]},"collisionExcludeTags":{"_tags":[]},"isBouncing":false,"bounceTargetMode":0,"maxBounceCount":3,"bounceSearchRadius":10.0,"canBounceToSameTarget":false,"excludeSourceCamp":true,"bounceAngleOffset":0.0}</t>
+          <t>{"guid":"d897a922-5756-42cf-ac65-90a48c1e5a17","nodeType":8,"position":{"x":1022.666748046875,"y":-1951.3333740234375},"targetType":2,"assetTags":{"_tags":[]},"grantedTags":{"_tags":[]},"applicationRequiredTags":{"_tags":[]},"applicationImmunityTags":{"_tags":[]},"removeGameEffectsWithTags":{"_tags":[]},"durationType":2,"duration":"0","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"_tags":[]},"cancelOnAbilityEnd":false,"launchPositionSource":0,"launchBindingName":"center","targetPositionSource":1,"targetBindingName":"center","projectileTargetType":0,"flyOver":true,"offsetAngle":-30.0,"curveHeight":0.0,"projectileEntityId":50002,"projectilePrefab":null,"projectilePrefabPath":"Assets/Res/Entity/Effect/ef_fashi_huoyandan01.prefab","speed":10.0,"maxDistance":10.0,"collisionRadius":0.5,"isPiercing":false,"maxPierceCount":1,"collisionTargetTags":{"_tags":[]},"collisionExcludeTags":{"_tags":[]},"isBouncing":false,"bounceTargetMode":0,"maxBounceCount":3,"bounceSearchRadius":10.0,"canBounceToSameTarget":false,"excludeSourceCamp":true,"bounceAngleOffset":0.0}</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
@@ -2405,11 +2405,11 @@
       <c r="C90"/>
       <c r="D90"/>
       <c r="E90">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>{"guid":"cde57fb8-b693-4da8-a4a8-fd61e56c5dcd","nodeType":12,"position":{"x":677.3333740234375,"y":-1998.666748046875},"targetType":1,"requiredTags":{"_tags":[]},"immunityTags":{"_tags":[]},"destroyWithNode":false,"positionSource":0,"particlePrefab":null,"particlePrefabPath":"Assets/Res/Entity/Effect/ef_Zhanshi_zhentianpaoxiao_01.prefab","particleBindingName":"down","particleOffset":{"x":0.0,"y":0.0,"z":0.0},"particleScale":{"x":1.0,"y":1.0,"z":1.0},"attachToTarget":false,"particleLoop":false}</t>
+          <t>{"guid":"e33ab94c-1496-4d6a-ba5e-1afd38bb0c30","nodeType":4,"position":{"x":-452.0,"y":-1786.666748046875},"targetType":1,"searchShapeType":0,"searchLineType":0,"positionSource":0,"positionBindingName":"center","searchCircleRadius":4.0,"searchSectorRadius":2.0,"searchSectorAngle":180.0,"searchLineDirectionOffsetAngle":0.0,"searchLineDirectionWidth":1.0,"searchLineDirectionLength":10.0,"lineStartPositionSource":0,"lineStartBindingName":"","lineEndPositionSource":1,"lineEndBindingName":"","searchLineBetweenWidth":1.0,"searchLineAbsoluteAngle":0.0,"searchLineAbsoluteWidth":1.0,"searchLineAbsoluteLength":10.0,"maxTargets":999,"searchTargetTags":{"_tags":[{"_name":"unitType.monster","_hashCode":-2021655864,"_shortName":"monster","_ancestorHashCodes":[1600484460],"_ancestorNames":["unitType"]}]},"searchExcludeTags":{"_tags":[]}}</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
@@ -2425,11 +2425,11 @@
       <c r="C91"/>
       <c r="D91"/>
       <c r="E91">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>{"guid":"e33ab94c-1496-4d6a-ba5e-1afd38bb0c30","nodeType":4,"position":{"x":-452.0,"y":-1786.666748046875},"targetType":1,"searchShapeType":0,"searchLineType":0,"positionSource":0,"positionBindingName":"center","searchCircleRadius":4.0,"searchSectorRadius":2.0,"searchSectorAngle":180.0,"searchLineDirectionOffsetAngle":0.0,"searchLineDirectionWidth":1.0,"searchLineDirectionLength":10.0,"lineStartPositionSource":0,"lineStartBindingName":"","lineEndPositionSource":1,"lineEndBindingName":"","searchLineBetweenWidth":1.0,"searchLineAbsoluteAngle":0.0,"searchLineAbsoluteWidth":1.0,"searchLineAbsoluteLength":10.0,"maxTargets":999,"searchTargetTags":{"_tags":[{"_name":"unitType.monster","_hashCode":-2021655864,"_shortName":"monster","_ancestorHashCodes":[1600484460],"_ancestorNames":["unitType"]}]},"searchExcludeTags":{"_tags":[]}}</t>
+          <t>{"guid":"432ff1e3-b18d-476d-af80-d39ddc07402a","nodeType":20,"position":{"x":-502.66665649414063,"y":-2384.0},"targetType":1,"skeletonDataAsset":null,"skeletonDataAssetPath":"Assets/Res/Spine/SP_Zhanshi/SP_Zhanshi_SkeletonData.asset","animationName":"Skill_attack_1009","animationDuration":"25","isAnimationLooping":false,"timeEffects":[{"triggerTime":4,"portIdValue":2315086,"legacyPortId":"de0ba361-3aba-4ef0-bb07-9b418fcae591"},{"triggerTime":25,"portIdValue":2000539,"legacyPortId":"f41c85e0-7f26-494e-9ffc-4a06c980f811"}],"timeCues":[{"startTime":0,"endTime":75,"portIdValue":2287012,"legacyPortId":"8dea1941-c520-4f9a-aee0-40932c8542ef"}]}</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
@@ -2445,11 +2445,11 @@
       <c r="C92"/>
       <c r="D92"/>
       <c r="E92">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>{"guid":"432ff1e3-b18d-476d-af80-d39ddc07402a","nodeType":20,"position":{"x":-502.66665649414063,"y":-2384.0},"targetType":1,"skeletonDataAsset":null,"skeletonDataAssetPath":"Assets/Res/Spine/SP_Zhanshi/SP_Zhanshi_SkeletonData.asset","animationName":"Skill_attack_1009","animationDuration":"25","isAnimationLooping":false,"timeEffects":[{"triggerTime":4,"portIdValue":2315086,"legacyPortId":"de0ba361-3aba-4ef0-bb07-9b418fcae591"},{"triggerTime":25,"portIdValue":2000539,"legacyPortId":"f41c85e0-7f26-494e-9ffc-4a06c980f811"}],"timeCues":[{"startTime":0,"endTime":75,"portIdValue":2287012,"legacyPortId":"8dea1941-c520-4f9a-aee0-40932c8542ef"}]}</t>
+          <t>{"guid":"356907e0-1488-4128-bfcc-7ff73cfc3330","nodeType":0,"position":{"x":-878.6666259765625,"y":-1853.3333740234375},"targetType":1,"skillId":1006,"assetTags":{"_tags":[]},"cancelAbilitiesWithTags":{"_tags":[]},"blockAbilitiesWithTags":{"_tags":[]},"activationOwnedTags":{"_tags":[{"_name":"Skill.Running","_hashCode":-51601538,"_shortName":"Running","_ancestorHashCodes":[1312877309],"_ancestorNames":["Skill"]}]},"activationRequiredTags":{"_tags":[]},"activationBlockedTags":{"_tags":[{"_name":"CD.Wan","_hashCode":87403585,"_shortName":"Wan","_ancestorHashCodes":[-1137859925],"_ancestorNames":["CD"]},{"_name":"Skill.Running","_hashCode":-51601538,"_shortName":"Running","_ancestorHashCodes":[1312877309],"_ancestorNames":["Skill"]}]},"ongoingBlockedTags":{"_tags":[]},"eventOutputPorts":[]}</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
@@ -2465,11 +2465,11 @@
       <c r="C93"/>
       <c r="D93"/>
       <c r="E93">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>{"guid":"356907e0-1488-4128-bfcc-7ff73cfc3330","nodeType":0,"position":{"x":-878.6666259765625,"y":-1853.3333740234375},"targetType":1,"skillId":1006,"assetTags":{"_tags":[]},"cancelAbilitiesWithTags":{"_tags":[]},"blockAbilitiesWithTags":{"_tags":[]},"activationOwnedTags":{"_tags":[{"_name":"Skill.Running","_hashCode":-51601538,"_shortName":"Running","_ancestorHashCodes":[1312877309],"_ancestorNames":["Skill"]}]},"activationRequiredTags":{"_tags":[]},"activationBlockedTags":{"_tags":[{"_name":"CD.Wan","_hashCode":87403585,"_shortName":"Wan","_ancestorHashCodes":[-1137859925],"_ancestorNames":["CD"]},{"_name":"Skill.Running","_hashCode":-51601538,"_shortName":"Running","_ancestorHashCodes":[1312877309],"_ancestorNames":["Skill"]}]},"ongoingBlockedTags":{"_tags":[]},"eventOutputPorts":[]}</t>
+          <t>{"guid":"cde57fb8-b693-4da8-a4a8-fd61e56c5dcd","nodeType":12,"position":{"x":677.3333740234375,"y":-1998.666748046875},"targetType":1,"requiredTags":{"_tags":[]},"immunityTags":{"_tags":[]},"destroyWithNode":false,"positionSource":0,"particleEntityId":50010,"particlePrefab":null,"particlePrefabPath":"Assets/Res/Entity/Effect/ef_Zhanshi_zhentianpaoxiao_01.prefab","particleBindingName":"down","particleOffset":{"x":0.0,"y":0.0,"z":0.0},"particleScale":{"x":1.0,"y":1.0,"z":1.0},"attachToTarget":false,"particleLoop":false}</t>
         </is>
       </c>
       <c r="G93"/>
@@ -2547,11 +2547,11 @@
       <c r="C97"/>
       <c r="D97"/>
       <c r="E97">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>{"guid":"cde57fb8-b693-4da8-a4a8-fd61e56c5dcd","nodeType":12,"position":{"x":677.3333740234375,"y":-1998.666748046875},"targetType":1,"requiredTags":{"_tags":[]},"immunityTags":{"_tags":[]},"destroyWithNode":true,"positionSource":0,"particlePrefab":null,"particlePrefabPath":"Assets/Res/Entity/Effect/ef_zhanshi_xfz_01.prefab","particleBindingName":"down","particleOffset":{"x":0.0,"y":0.0,"z":0.0},"particleScale":{"x":1.0,"y":1.0,"z":1.0},"attachToTarget":true,"particleLoop":true}</t>
+          <t>{"guid":"c28fb88d-51b1-47b2-be59-859e0ac638e3","nodeType":10,"position":{"x":-1186.6666259765625,"y":-1747.3333740234375},"targetType":1,"assetTags":{"_tags":[]},"grantedTags":{"_tags":[{"_name":"CD.Wind","_hashCode":1982736573,"_shortName":"Wind","_ancestorHashCodes":[-1137859925],"_ancestorNames":["CD"]}]},"applicationRequiredTags":{"_tags":[]},"applicationImmunityTags":{"_tags":[]},"removeGameEffectsWithTags":{"_tags":[]},"durationType":1,"duration":"15","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"_tags":[]},"cancelOnAbilityEnd":false,"cooldownType":0,"maxCharges":2,"chargeTime":"10"}</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
@@ -2567,11 +2567,11 @@
       <c r="C98"/>
       <c r="D98"/>
       <c r="E98">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>{"guid":"c28fb88d-51b1-47b2-be59-859e0ac638e3","nodeType":10,"position":{"x":-1186.6666259765625,"y":-1747.3333740234375},"targetType":1,"assetTags":{"_tags":[]},"grantedTags":{"_tags":[{"_name":"CD.Wind","_hashCode":1982736573,"_shortName":"Wind","_ancestorHashCodes":[-1137859925],"_ancestorNames":["CD"]}]},"applicationRequiredTags":{"_tags":[]},"applicationImmunityTags":{"_tags":[]},"removeGameEffectsWithTags":{"_tags":[]},"durationType":1,"duration":"15","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"_tags":[]},"cancelOnAbilityEnd":false,"cooldownType":0,"maxCharges":2,"chargeTime":"10"}</t>
+          <t>{"guid":"f73ba91e-a76b-456c-b19c-a5176809d5f5","nodeType":7,"position":{"x":700.0,"y":-1856.666748046875},"targetType":1,"endType":0}</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
@@ -2587,11 +2587,11 @@
       <c r="C99"/>
       <c r="D99"/>
       <c r="E99">
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>{"guid":"f73ba91e-a76b-456c-b19c-a5176809d5f5","nodeType":7,"position":{"x":700.0,"y":-1856.666748046875},"targetType":1,"endType":0}</t>
+          <t>{"guid":"d8847c3e-459e-4589-a96b-37ebb5ec458b","nodeType":21,"position":{"x":-308.66665649414063,"y":-1769.3333740234375},"targetType":1,"assetTags":{"_tags":[]},"grantedTags":{"_tags":[]},"applicationRequiredTags":{"_tags":[]},"applicationImmunityTags":{"_tags":[]},"removeGameEffectsWithTags":{"_tags":[]},"durationType":2,"duration":"0","isPeriodic":true,"period":"0.3","executeOnApplication":false,"attributeModifiers":[],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"_tags":[]},"cancelOnAbilityEnd":true}</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
@@ -2607,11 +2607,11 @@
       <c r="C100"/>
       <c r="D100"/>
       <c r="E100">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>{"guid":"d8847c3e-459e-4589-a96b-37ebb5ec458b","nodeType":21,"position":{"x":-308.66665649414063,"y":-1769.3333740234375},"targetType":1,"assetTags":{"_tags":[]},"grantedTags":{"_tags":[]},"applicationRequiredTags":{"_tags":[]},"applicationImmunityTags":{"_tags":[]},"removeGameEffectsWithTags":{"_tags":[]},"durationType":2,"duration":"0","isPeriodic":true,"period":"0.3","executeOnApplication":false,"attributeModifiers":[],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"_tags":[]},"cancelOnAbilityEnd":true}</t>
+          <t>{"guid":"e33ab94c-1496-4d6a-ba5e-1afd38bb0c30","nodeType":4,"position":{"x":27.333343505859375,"y":-1769.3333740234375},"targetType":1,"searchShapeType":0,"searchLineType":0,"positionSource":0,"positionBindingName":"center","searchCircleRadius":2.5,"searchSectorRadius":2.0,"searchSectorAngle":180.0,"searchLineDirectionOffsetAngle":0.0,"searchLineDirectionWidth":1.0,"searchLineDirectionLength":10.0,"lineStartPositionSource":0,"lineStartBindingName":"","lineEndPositionSource":1,"lineEndBindingName":"","searchLineBetweenWidth":1.0,"searchLineAbsoluteAngle":0.0,"searchLineAbsoluteWidth":1.0,"searchLineAbsoluteLength":10.0,"maxTargets":999,"searchTargetTags":{"_tags":[{"_name":"unitType.monster","_hashCode":-2021655864,"_shortName":"monster","_ancestorHashCodes":[1600484460],"_ancestorNames":["unitType"]}]},"searchExcludeTags":{"_tags":[]}}</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
@@ -2627,11 +2627,11 @@
       <c r="C101"/>
       <c r="D101"/>
       <c r="E101">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>{"guid":"e33ab94c-1496-4d6a-ba5e-1afd38bb0c30","nodeType":4,"position":{"x":27.333343505859375,"y":-1769.3333740234375},"targetType":1,"searchShapeType":0,"searchLineType":0,"positionSource":0,"positionBindingName":"center","searchCircleRadius":2.5,"searchSectorRadius":2.0,"searchSectorAngle":180.0,"searchLineDirectionOffsetAngle":0.0,"searchLineDirectionWidth":1.0,"searchLineDirectionLength":10.0,"lineStartPositionSource":0,"lineStartBindingName":"","lineEndPositionSource":1,"lineEndBindingName":"","searchLineBetweenWidth":1.0,"searchLineAbsoluteAngle":0.0,"searchLineAbsoluteWidth":1.0,"searchLineAbsoluteLength":10.0,"maxTargets":999,"searchTargetTags":{"_tags":[{"_name":"unitType.monster","_hashCode":-2021655864,"_shortName":"monster","_ancestorHashCodes":[1600484460],"_ancestorNames":["unitType"]}]},"searchExcludeTags":{"_tags":[]}}</t>
+          <t>{"guid":"432ff1e3-b18d-476d-af80-d39ddc07402a","nodeType":20,"position":{"x":-452.0,"y":-2375.333251953125},"targetType":1,"skeletonDataAsset":null,"skeletonDataAssetPath":"Assets/Res/Spine/SP_Zhanshi/SP_Zhanshi_SkeletonData.asset","animationName":"Skill_attack_1011","animationDuration":"12","isAnimationLooping":true,"timeEffects":[{"triggerTime":250,"portIdValue":2000539,"legacyPortId":"f41c85e0-7f26-494e-9ffc-4a06c980f811"}],"timeCues":[{"startTime":0,"endTime":255,"portIdValue":2287012,"legacyPortId":"8dea1941-c520-4f9a-aee0-40932c8542ef"}]}</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
@@ -2647,11 +2647,11 @@
       <c r="C102"/>
       <c r="D102"/>
       <c r="E102">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>{"guid":"432ff1e3-b18d-476d-af80-d39ddc07402a","nodeType":20,"position":{"x":-452.0,"y":-2375.333251953125},"targetType":1,"skeletonDataAsset":null,"skeletonDataAssetPath":"Assets/Res/Spine/SP_Zhanshi/SP_Zhanshi_SkeletonData.asset","animationName":"Skill_attack_1011","animationDuration":"12","isAnimationLooping":true,"timeEffects":[{"triggerTime":250,"portIdValue":2000539,"legacyPortId":"f41c85e0-7f26-494e-9ffc-4a06c980f811"}],"timeCues":[{"startTime":0,"endTime":255,"portIdValue":2287012,"legacyPortId":"8dea1941-c520-4f9a-aee0-40932c8542ef"}]}</t>
+          <t>{"guid":"356907e0-1488-4128-bfcc-7ff73cfc3330","nodeType":0,"position":{"x":-878.6666259765625,"y":-1853.3333740234375},"targetType":1,"skillId":1004,"assetTags":{"_tags":[]},"cancelAbilitiesWithTags":{"_tags":[]},"blockAbilitiesWithTags":{"_tags":[]},"activationOwnedTags":{"_tags":[{"_name":"Skill.Running","_hashCode":-51601538,"_shortName":"Running","_ancestorHashCodes":[1312877309],"_ancestorNames":["Skill"]}]},"activationRequiredTags":{"_tags":[]},"activationBlockedTags":{"_tags":[{"_name":"CD.Wind","_hashCode":1982736573,"_shortName":"Wind","_ancestorHashCodes":[-1137859925],"_ancestorNames":["CD"]},{"_name":"Skill.Running","_hashCode":-51601538,"_shortName":"Running","_ancestorHashCodes":[1312877309],"_ancestorNames":["Skill"]}]},"ongoingBlockedTags":{"_tags":[]},"eventOutputPorts":[]}</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
@@ -2667,11 +2667,11 @@
       <c r="C103"/>
       <c r="D103"/>
       <c r="E103">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>{"guid":"356907e0-1488-4128-bfcc-7ff73cfc3330","nodeType":0,"position":{"x":-878.6666259765625,"y":-1853.3333740234375},"targetType":1,"skillId":1004,"assetTags":{"_tags":[]},"cancelAbilitiesWithTags":{"_tags":[]},"blockAbilitiesWithTags":{"_tags":[]},"activationOwnedTags":{"_tags":[{"_name":"Skill.Running","_hashCode":-51601538,"_shortName":"Running","_ancestorHashCodes":[1312877309],"_ancestorNames":["Skill"]}]},"activationRequiredTags":{"_tags":[]},"activationBlockedTags":{"_tags":[{"_name":"CD.Wind","_hashCode":1982736573,"_shortName":"Wind","_ancestorHashCodes":[-1137859925],"_ancestorNames":["CD"]},{"_name":"Skill.Running","_hashCode":-51601538,"_shortName":"Running","_ancestorHashCodes":[1312877309],"_ancestorNames":["Skill"]}]},"ongoingBlockedTags":{"_tags":[]},"eventOutputPorts":[]}</t>
+          <t>{"guid":"cde57fb8-b693-4da8-a4a8-fd61e56c5dcd","nodeType":12,"position":{"x":677.3333740234375,"y":-1998.666748046875},"targetType":1,"requiredTags":{"_tags":[]},"immunityTags":{"_tags":[]},"destroyWithNode":true,"positionSource":0,"particleEntityId":50008,"particlePrefab":null,"particlePrefabPath":"Assets/Res/Entity/Effect/ef_zhanshi_xfz_01.prefab","particleBindingName":"down","particleOffset":{"x":0.0,"y":0.0,"z":0.0},"particleScale":{"x":1.0,"y":1.0,"z":1.0},"attachToTarget":true,"particleLoop":true}</t>
         </is>
       </c>
       <c r="G103"/>

--- a/Design/Excel/ET/Datas/Game/SkillGraph.xlsx
+++ b/Design/Excel/ET/Datas/Game/SkillGraph.xlsx
@@ -1679,11 +1679,11 @@
       <c r="C54"/>
       <c r="D54"/>
       <c r="E54">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>{"guid":"93ec5a43-cc34-4e4a-acb3-39da2f2c3010","nodeType":12,"position":{"x":468.66665649414063,"y":-1749.3333740234375},"targetType":1,"requiredTags":{"_tags":[]},"immunityTags":{"_tags":[]},"destroyWithNode":true,"positionSource":2,"particleEntityId":0,"particlePrefab":null,"particlePrefabPath":"Assets/Res/Entity/Effect/ef_Xuanyun_01.prefab","particleBindingName":"head","particleOffset":{"x":0.0,"y":0.0,"z":0.0},"particleScale":{"x":1.0,"y":1.0,"z":1.0},"attachToTarget":true,"particleLoop":true}</t>
+          <t>{"guid":"e33ab94c-1496-4d6a-ba5e-1afd38bb0c30","nodeType":4,"position":{"x":-452.0,"y":-1786.666748046875},"targetType":1,"searchShapeType":0,"searchLineType":0,"positionSource":0,"positionBindingName":"center","searchCircleRadius":2.5,"searchSectorRadius":2.0,"searchSectorAngle":180.0,"searchLineDirectionOffsetAngle":0.0,"searchLineDirectionWidth":1.0,"searchLineDirectionLength":10.0,"lineStartPositionSource":0,"lineStartBindingName":"","lineEndPositionSource":1,"lineEndBindingName":"","searchLineBetweenWidth":1.0,"searchLineAbsoluteAngle":0.0,"searchLineAbsoluteWidth":1.0,"searchLineAbsoluteLength":10.0,"maxTargets":999,"searchTargetTags":{"_tags":[{"_name":"unitType.monster","_hashCode":-2021655864,"_shortName":"monster","_ancestorHashCodes":[1600484460],"_ancestorNames":["unitType"]}]},"searchExcludeTags":{"_tags":[]}}</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
@@ -1699,11 +1699,11 @@
       <c r="C55"/>
       <c r="D55"/>
       <c r="E55">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>{"guid":"cb1df36f-5729-423e-9d1a-287db5a433f0","nodeType":11,"position":{"x":18.66668701171875,"y":-1786.666748046875},"targetType":0,"assetTags":{"_tags":[{"_name":"Buff.DeBuff.Stun","_hashCode":1791562953,"_shortName":"Stun","_ancestorHashCodes":[937056111,321157895],"_ancestorNames":["Buff","Buff.DeBuff"]}]},"grantedTags":{"_tags":[{"_name":"Buff.DeBuff.Stun","_hashCode":1791562953,"_shortName":"Stun","_ancestorHashCodes":[937056111,321157895],"_ancestorNames":["Buff","Buff.DeBuff"]}]},"applicationRequiredTags":{"_tags":[]},"applicationImmunityTags":{"_tags":[]},"removeGameEffectsWithTags":{"_tags":[]},"durationType":1,"duration":"4","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[],"stackType":1,"stackLimit":1,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":1,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"_tags":[]},"cancelOnAbilityEnd":false,"buffId":0}</t>
+          <t>{"guid":"432ff1e3-b18d-476d-af80-d39ddc07402a","nodeType":20,"position":{"x":-452.0,"y":-2375.333251953125},"targetType":1,"skeletonDataAsset":null,"skeletonDataAssetPath":"Assets/Res/Spine/SP_Zhanshi/SP_Zhanshi_SkeletonData.asset","animationName":"Skill_attack_1005","animationDuration":"16","isAnimationLooping":false,"timeEffects":[{"triggerTime":7,"portIdValue":2315086,"legacyPortId":"de0ba361-3aba-4ef0-bb07-9b418fcae591"},{"triggerTime":16,"portIdValue":2000539,"legacyPortId":"f41c85e0-7f26-494e-9ffc-4a06c980f811"}],"timeCues":[{"startTime":6,"endTime":55,"portIdValue":2287012,"legacyPortId":"8dea1941-c520-4f9a-aee0-40932c8542ef"}]}</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
@@ -1719,11 +1719,11 @@
       <c r="C56"/>
       <c r="D56"/>
       <c r="E56">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>{"guid":"e33ab94c-1496-4d6a-ba5e-1afd38bb0c30","nodeType":4,"position":{"x":-452.0,"y":-1786.666748046875},"targetType":1,"searchShapeType":0,"searchLineType":0,"positionSource":0,"positionBindingName":"center","searchCircleRadius":2.5,"searchSectorRadius":2.0,"searchSectorAngle":180.0,"searchLineDirectionOffsetAngle":0.0,"searchLineDirectionWidth":1.0,"searchLineDirectionLength":10.0,"lineStartPositionSource":0,"lineStartBindingName":"","lineEndPositionSource":1,"lineEndBindingName":"","searchLineBetweenWidth":1.0,"searchLineAbsoluteAngle":0.0,"searchLineAbsoluteWidth":1.0,"searchLineAbsoluteLength":10.0,"maxTargets":999,"searchTargetTags":{"_tags":[{"_name":"unitType.monster","_hashCode":-2021655864,"_shortName":"monster","_ancestorHashCodes":[1600484460],"_ancestorNames":["unitType"]}]},"searchExcludeTags":{"_tags":[]}}</t>
+          <t>{"guid":"356907e0-1488-4128-bfcc-7ff73cfc3330","nodeType":0,"position":{"x":-878.6666259765625,"y":-1853.3333740234375},"targetType":1,"skillId":1003,"assetTags":{"_tags":[]},"cancelAbilitiesWithTags":{"_tags":[]},"blockAbilitiesWithTags":{"_tags":[]},"activationOwnedTags":{"_tags":[{"_name":"Skill.Running","_hashCode":-51601538,"_shortName":"Running","_ancestorHashCodes":[1312877309],"_ancestorNames":["Skill"]}]},"activationRequiredTags":{"_tags":[]},"activationBlockedTags":{"_tags":[{"_name":"CD.RuFood","_hashCode":-1045902856,"_shortName":"RuFood","_ancestorHashCodes":[-1137859925],"_ancestorNames":["CD"]},{"_name":"Skill.Running","_hashCode":-51601538,"_shortName":"Running","_ancestorHashCodes":[1312877309],"_ancestorNames":["Skill"]}]},"ongoingBlockedTags":{"_tags":[]},"eventOutputPorts":[]}</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
@@ -1739,11 +1739,11 @@
       <c r="C57"/>
       <c r="D57"/>
       <c r="E57">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>{"guid":"432ff1e3-b18d-476d-af80-d39ddc07402a","nodeType":20,"position":{"x":-452.0,"y":-2375.333251953125},"targetType":1,"skeletonDataAsset":null,"skeletonDataAssetPath":"Assets/Res/Spine/SP_Zhanshi/SP_Zhanshi_SkeletonData.asset","animationName":"Skill_attack_1005","animationDuration":"16","isAnimationLooping":false,"timeEffects":[{"triggerTime":7,"portIdValue":2315086,"legacyPortId":"de0ba361-3aba-4ef0-bb07-9b418fcae591"},{"triggerTime":16,"portIdValue":2000539,"legacyPortId":"f41c85e0-7f26-494e-9ffc-4a06c980f811"}],"timeCues":[{"startTime":6,"endTime":55,"portIdValue":2287012,"legacyPortId":"8dea1941-c520-4f9a-aee0-40932c8542ef"}]}</t>
+          <t>{"guid":"cde57fb8-b693-4da8-a4a8-fd61e56c5dcd","nodeType":12,"position":{"x":676.6666259765625,"y":-1998.0},"targetType":1,"requiredTags":{"_tags":[]},"immunityTags":{"_tags":[]},"destroyWithNode":false,"positionSource":0,"particleEntityId":50007,"particlePrefab":null,"particlePrefabPath":"Assets/Res/Entity/Effect/ef_zhanshi_jcjt_01.prefab","particleBindingName":"down","particleOffset":{"x":0.0,"y":0.0,"z":0.0},"particleScale":{"x":1.0,"y":1.0,"z":1.0},"attachToTarget":false,"particleLoop":false}</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
@@ -1759,11 +1759,11 @@
       <c r="C58"/>
       <c r="D58"/>
       <c r="E58">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>{"guid":"356907e0-1488-4128-bfcc-7ff73cfc3330","nodeType":0,"position":{"x":-878.6666259765625,"y":-1853.3333740234375},"targetType":1,"skillId":1003,"assetTags":{"_tags":[]},"cancelAbilitiesWithTags":{"_tags":[]},"blockAbilitiesWithTags":{"_tags":[]},"activationOwnedTags":{"_tags":[{"_name":"Skill.Running","_hashCode":-51601538,"_shortName":"Running","_ancestorHashCodes":[1312877309],"_ancestorNames":["Skill"]}]},"activationRequiredTags":{"_tags":[]},"activationBlockedTags":{"_tags":[{"_name":"CD.RuFood","_hashCode":-1045902856,"_shortName":"RuFood","_ancestorHashCodes":[-1137859925],"_ancestorNames":["CD"]},{"_name":"Skill.Running","_hashCode":-51601538,"_shortName":"Running","_ancestorHashCodes":[1312877309],"_ancestorNames":["Skill"]}]},"ongoingBlockedTags":{"_tags":[]},"eventOutputPorts":[]}</t>
+          <t>{"guid":"cb1df36f-5729-423e-9d1a-287db5a433f0","nodeType":11,"position":{"x":18.66668701171875,"y":-1786.666748046875},"targetType":0,"assetTags":{"_tags":[{"_name":"Buff.DeBuff.Stun","_hashCode":1791562953,"_shortName":"Stun","_ancestorHashCodes":[937056111,321157895],"_ancestorNames":["Buff","Buff.DeBuff"]}]},"grantedTags":{"_tags":[{"_name":"Buff.DeBuff.Stun","_hashCode":1791562953,"_shortName":"Stun","_ancestorHashCodes":[937056111,321157895],"_ancestorNames":["Buff","Buff.DeBuff"]}]},"applicationRequiredTags":{"_tags":[]},"applicationImmunityTags":{"_tags":[]},"removeGameEffectsWithTags":{"_tags":[]},"durationType":1,"duration":"4","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[],"stackType":1,"stackLimit":1,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":1,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"_tags":[]},"cancelOnAbilityEnd":false,"buffId":0}</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
@@ -1783,7 +1783,7 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>{"guid":"cde57fb8-b693-4da8-a4a8-fd61e56c5dcd","nodeType":12,"position":{"x":676.6666259765625,"y":-1998.0},"targetType":1,"requiredTags":{"_tags":[]},"immunityTags":{"_tags":[]},"destroyWithNode":false,"positionSource":0,"particleEntityId":50007,"particlePrefab":null,"particlePrefabPath":"Assets/Res/Entity/Effect/ef_zhanshi_jcjt_01.prefab","particleBindingName":"down","particleOffset":{"x":0.0,"y":0.0,"z":0.0},"particleScale":{"x":1.0,"y":1.0,"z":1.0},"attachToTarget":false,"particleLoop":false}</t>
+          <t>{"guid":"93ec5a43-cc34-4e4a-acb3-39da2f2c3010","nodeType":12,"position":{"x":468.66665649414063,"y":-1749.3333740234375},"targetType":1,"requiredTags":{"_tags":[]},"immunityTags":{"_tags":[]},"destroyWithNode":true,"positionSource":2,"particleEntityId":50005,"particlePrefab":null,"particlePrefabPath":"Assets/Res/Entity/Effect/ef_Xuanyun_01.prefab","particleBindingName":"head","particleOffset":{"x":0.0,"y":0.0,"z":0.0},"particleScale":{"x":1.0,"y":1.0,"z":1.0},"attachToTarget":true,"particleLoop":true}</t>
         </is>
       </c>
       <c r="G59"/>

--- a/Design/Excel/ET/Datas/Game/SkillGraph.xlsx
+++ b/Design/Excel/ET/Datas/Game/SkillGraph.xlsx
@@ -687,11 +687,11 @@
       </c>
       <c r="D5"/>
       <c r="E5">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>{"guid":"7eefd9ae-c57e-439d-b1b6-e7f4e52f2f6f","nodeType":10,"position":{"x":370.66665649414063,"y":484.66665649414063},"targetType":1,"assetTags":{"_tags":[]},"grantedTags":{"_tags":[{"_name":"CD.BeRecBlood","_hashCode":-1099994396,"_shortName":"被动回血","_ancestorHashCodes":[-1137859925],"_ancestorNames":["CD"]}]},"applicationRequiredTags":{"_tags":[]},"applicationImmunityTags":{"_tags":[]},"removeGameEffectsWithTags":{"_tags":[]},"durationType":1,"duration":"3","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"_tags":[]},"cancelOnAbilityEnd":false,"cooldownType":0,"maxCharges":2,"chargeTime":"10"}</t>
+          <t>{"guid":"426755b7-c39a-4524-9cb5-960a31a19c10","nodeType":11,"position":{"x":587.3333740234375,"y":114.66667175292969},"targetType":1,"assetTags":{"_tags":[]},"grantedTags":{"_tags":[]},"applicationRequiredTags":{"_tags":[]},"applicationImmunityTags":{"_tags":[]},"removeGameEffectsWithTags":{"_tags":[]},"durationType":2,"duration":"10","isPeriodic":true,"period":"1","executeOnApplication":false,"attributeModifiers":[],"stackType":1,"stackLimit":1,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"_tags":[{"_name":"CD.BeRecBlood","_hashCode":-1099994396,"_shortName":"被动回血","_ancestorHashCodes":[-1137859925],"_ancestorNames":["CD"]}]},"cancelOnAbilityEnd":true,"buffId":0}</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -707,11 +707,11 @@
       <c r="C6"/>
       <c r="D6"/>
       <c r="E6">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>{"guid":"426755b7-c39a-4524-9cb5-960a31a19c10","nodeType":11,"position":{"x":587.3333740234375,"y":114.66667175292969},"targetType":1,"assetTags":{"_tags":[]},"grantedTags":{"_tags":[]},"applicationRequiredTags":{"_tags":[]},"applicationImmunityTags":{"_tags":[]},"removeGameEffectsWithTags":{"_tags":[]},"durationType":2,"duration":"10","isPeriodic":true,"period":"1","executeOnApplication":false,"attributeModifiers":[],"stackType":1,"stackLimit":1,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"_tags":[{"_name":"CD.BeRecBlood","_hashCode":-1099994396,"_shortName":"被动回血","_ancestorHashCodes":[-1137859925],"_ancestorNames":["CD"]}]},"cancelOnAbilityEnd":true,"buffId":0}</t>
+          <t>{"guid":"d5809887-df6e-4604-bd09-36cef191ce83","nodeType":0,"position":{"x":113.33334350585938,"y":158.66667175292969},"targetType":1,"skillId":2001,"assetTags":{"_tags":[]},"cancelAbilitiesWithTags":{"_tags":[]},"blockAbilitiesWithTags":{"_tags":[]},"activationOwnedTags":{"_tags":[]},"activationRequiredTags":{"_tags":[]},"activationBlockedTags":{"_tags":[]},"ongoingBlockedTags":{"_tags":[]},"eventOutputPorts":[{"eventType":2,"customEventTag":"","PortId":1103}]}</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -727,11 +727,11 @@
       <c r="C7"/>
       <c r="D7"/>
       <c r="E7">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>{"guid":"d5809887-df6e-4604-bd09-36cef191ce83","nodeType":0,"position":{"x":113.33334350585938,"y":158.66667175292969},"targetType":1,"skillId":2001,"assetTags":{"_tags":[]},"cancelAbilitiesWithTags":{"_tags":[]},"blockAbilitiesWithTags":{"_tags":[]},"activationOwnedTags":{"_tags":[]},"activationRequiredTags":{"_tags":[]},"activationBlockedTags":{"_tags":[]},"ongoingBlockedTags":{"_tags":[]},"eventOutputPorts":[{"eventType":2,"customEventTag":"","PortId":1103}]}</t>
+          <t>{"guid":"7eefd9ae-c57e-439d-b1b6-e7f4e52f2f6f","nodeType":10,"position":{"x":370.66665649414063,"y":484.66665649414063},"targetType":1,"assetTags":{"_tags":[]},"grantedTags":{"_tags":[{"_name":"CD.BeRecBlood","_hashCode":-1099994396,"_shortName":"被动回血","_ancestorHashCodes":[-1137859925],"_ancestorNames":["CD"]}]},"applicationRequiredTags":{"_tags":[]},"applicationImmunityTags":{"_tags":[]},"removeGameEffectsWithTags":{"_tags":[]},"durationType":1,"duration":"3","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"_tags":[]},"cancelOnAbilityEnd":false,"cooldownType":0,"maxCharges":2,"chargeTime":"10"}</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -747,11 +747,11 @@
       <c r="C8"/>
       <c r="D8"/>
       <c r="E8">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>{"guid":"d086a8c9-8557-4a61-8fd2-64b3c1e543a3","nodeType":14,"position":{"x":1148.666748046875,"y":207.33332824707031},"targetType":1,"requiredTags":{"_tags":[]},"immunityTags":{"_tags":[]},"destroyWithNode":false,"positionSource":0,"positionBindingName":"head","textType":1,"fixedText":"","contextDataKey":"Heal","textColor":{"r":0.040635824203491211,"g":1.0,"b":0.0,"a":1.0},"criticalColor":{"r":1.0,"g":0.5,"b":0.0,"a":1.0},"missColor":{"r":0.5,"g":0.5,"b":0.5,"a":1.0},"fontSize":45.0,"criticalFontSize":60.0,"duration":1.5,"offset":{"x":0.0,"y":0.0},"moveDirection":{"x":0.0,"y":1.0}}</t>
+          <t>{"guid":"a8c2d6c0-65f1-4bed-8a6a-70197e84bb56","nodeType":2,"position":{"x":933.3333740234375,"y":226.66667175292969},"targetType":1,"assetTags":{"_tags":[]},"grantedTags":{"_tags":[]},"applicationRequiredTags":{"_tags":[]},"applicationImmunityTags":{"_tags":[]},"removeGameEffectsWithTags":{"_tags":[]},"durationType":0,"duration":"0","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"_tags":[]},"cancelOnAbilityEnd":false,"healSourceType":0,"healFixedValue":2.0,"healFormula":"","healMMCType":0,"healSetByCallerKey":"","healMMCCaptureAttribute":202,"healMMCAttributeSource":0,"healMMCCoefficient":1.0,"healMMCUseSnapshot":true,"healMultiplyByStackCount":false,"healCalculationType":0}</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -767,11 +767,11 @@
       <c r="C9"/>
       <c r="D9"/>
       <c r="E9">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>{"guid":"a8c2d6c0-65f1-4bed-8a6a-70197e84bb56","nodeType":2,"position":{"x":933.3333740234375,"y":226.66667175292969},"targetType":1,"assetTags":{"_tags":[]},"grantedTags":{"_tags":[]},"applicationRequiredTags":{"_tags":[]},"applicationImmunityTags":{"_tags":[]},"removeGameEffectsWithTags":{"_tags":[]},"durationType":0,"duration":"0","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"_tags":[]},"cancelOnAbilityEnd":false,"healSourceType":0,"healFixedValue":2.0,"healFormula":"","healMMCType":0,"healSetByCallerKey":"","healMMCCaptureAttribute":202,"healMMCAttributeSource":0,"healMMCCoefficient":1.0,"healMMCUseSnapshot":true,"healMultiplyByStackCount":false,"healCalculationType":0}</t>
+          <t>{"guid":"d086a8c9-8557-4a61-8fd2-64b3c1e543a3","nodeType":14,"position":{"x":1148.666748046875,"y":206.66667175292969},"targetType":1,"requiredTags":{"_tags":[]},"immunityTags":{"_tags":[]},"destroyWithNode":false,"positionSource":0,"positionBindingName":"head","textType":1,"fixedText":"","contextDataKey":"Heal","textColor":{"r":0.040635824203491211,"g":1.0,"b":0.0,"a":1.0},"criticalColor":{"r":1.0,"g":0.5,"b":0.0,"a":1.0},"missColor":{"r":0.5,"g":0.5,"b":0.5,"a":1.0},"fontSize":5.0,"criticalFontSize":60.0,"duration":1.5,"offset":{"x":0.0,"y":0.0},"moveDirection":{"x":0.0,"y":1.0}}</t>
         </is>
       </c>
       <c r="G9"/>
@@ -833,7 +833,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>{"guid":"c353e286-8ef0-460a-b917-887f2aeb390a","nodeType":14,"position":{"x":383.33334350585938,"y":-1531.3333740234375},"targetType":1,"requiredTags":{"_tags":[]},"immunityTags":{"_tags":[]},"destroyWithNode":false,"positionSource":2,"positionBindingName":"head","textType":0,"fixedText":"","contextDataKey":"DamageResult","textColor":{"r":1.0,"g":0.0,"b":0.0,"a":1.0},"criticalColor":{"r":1.0,"g":0.5,"b":0.0,"a":1.0},"missColor":{"r":0.5,"g":0.5,"b":0.5,"a":1.0},"fontSize":45.0,"criticalFontSize":60.0,"duration":1.5,"offset":{"x":0.0,"y":0.0},"moveDirection":{"x":0.0,"y":1.0}}</t>
+          <t>{"guid":"c353e286-8ef0-460a-b917-887f2aeb390a","nodeType":14,"position":{"x":383.33334350585938,"y":-1531.3333740234375},"targetType":1,"requiredTags":{"_tags":[]},"immunityTags":{"_tags":[]},"destroyWithNode":false,"positionSource":2,"positionBindingName":"head","textType":0,"fixedText":"","contextDataKey":"DamageResult","textColor":{"r":1.0,"g":0.0,"b":0.0,"a":1.0},"criticalColor":{"r":1.0,"g":0.5,"b":0.0,"a":1.0},"missColor":{"r":0.5,"g":0.5,"b":0.5,"a":1.0},"fontSize":5.0,"criticalFontSize":60.0,"duration":1.5,"offset":{"x":0.0,"y":0.0},"moveDirection":{"x":0.0,"y":1.0}}</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -1071,11 +1071,11 @@
       <c r="C24"/>
       <c r="D24"/>
       <c r="E24">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>{"guid":"2d7e41c4-8e90-4b61-879c-4b2e5b9486db","nodeType":14,"position":{"x":180.0,"y":-1810.0},"targetType":1,"requiredTags":{"_tags":[]},"immunityTags":{"_tags":[]},"destroyWithNode":false,"positionSource":2,"positionBindingName":"head","textType":0,"fixedText":"","contextDataKey":"DamageResult","textColor":{"r":0.0,"g":0.323091983795166,"b":1.0,"a":1.0},"criticalColor":{"r":1.0,"g":0.5,"b":0.0,"a":1.0},"missColor":{"r":0.5,"g":0.5,"b":0.5,"a":1.0},"fontSize":45.0,"criticalFontSize":60.0,"duration":1.5,"offset":{"x":0.0,"y":0.0},"moveDirection":{"x":0.0,"y":1.0}}</t>
+          <t>{"guid":"eae41233-d297-46fe-a6c8-0b5c876fbb2a","nodeType":1,"position":{"x":-97.333328247070313,"y":-1810.0},"targetType":0,"assetTags":{"_tags":[]},"grantedTags":{"_tags":[]},"applicationRequiredTags":{"_tags":[]},"applicationImmunityTags":{"_tags":[]},"removeGameEffectsWithTags":{"_tags":[]},"durationType":0,"duration":"0","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"_tags":[]},"cancelOnAbilityEnd":true,"damageType":0,"damageSourceType":0,"damageFixedValue":10.0,"damageFormula":"","damageMMCType":0,"damageSetByCallerKey":"","damageMMCCaptureAttribute":200,"damageMMCAttributeSource":0,"damageMMCCoefficient":1.0,"damageMMCUseSnapshot":true,"damageMultiplyByStackCount":false,"damageCalculationType":0,"enableHitKnockback":true,"knockbackDistance":1.0,"knockbackSpeed":12.0}</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -1091,11 +1091,11 @@
       <c r="C25"/>
       <c r="D25"/>
       <c r="E25">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>{"guid":"eae41233-d297-46fe-a6c8-0b5c876fbb2a","nodeType":1,"position":{"x":-97.333328247070313,"y":-1810.0},"targetType":0,"assetTags":{"_tags":[]},"grantedTags":{"_tags":[]},"applicationRequiredTags":{"_tags":[]},"applicationImmunityTags":{"_tags":[]},"removeGameEffectsWithTags":{"_tags":[]},"durationType":0,"duration":"0","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"_tags":[]},"cancelOnAbilityEnd":true,"damageType":0,"damageSourceType":0,"damageFixedValue":10.0,"damageFormula":"","damageMMCType":0,"damageSetByCallerKey":"","damageMMCCaptureAttribute":200,"damageMMCAttributeSource":0,"damageMMCCoefficient":1.0,"damageMMCUseSnapshot":true,"damageMultiplyByStackCount":false,"damageCalculationType":0,"enableHitKnockback":true,"knockbackDistance":1.0,"knockbackSpeed":12.0}</t>
+          <t>{"guid":"356907e0-1488-4128-bfcc-7ff73cfc3330","nodeType":0,"position":{"x":-881.3333740234375,"y":-1854.666748046875},"targetType":1,"skillId":7001,"assetTags":{"_tags":[]},"cancelAbilitiesWithTags":{"_tags":[]},"blockAbilitiesWithTags":{"_tags":[]},"activationOwnedTags":{"_tags":[]},"activationRequiredTags":{"_tags":[]},"activationBlockedTags":{"_tags":[{"_name":"CD.FireCircle","_hashCode":522143731,"_shortName":"FireCircle","_ancestorHashCodes":[-1137859925],"_ancestorNames":["CD"]}]},"ongoingBlockedTags":{"_tags":[{"_name":"Buff.DeBuff.Stun","_hashCode":1791562953,"_shortName":"Stun","_ancestorHashCodes":[937056111,321157895],"_ancestorNames":["Buff","Buff.DeBuff"]}]},"eventOutputPorts":[]}</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -1111,11 +1111,11 @@
       <c r="C26"/>
       <c r="D26"/>
       <c r="E26">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>{"guid":"356907e0-1488-4128-bfcc-7ff73cfc3330","nodeType":0,"position":{"x":-881.3333740234375,"y":-1854.666748046875},"targetType":1,"skillId":7001,"assetTags":{"_tags":[]},"cancelAbilitiesWithTags":{"_tags":[]},"blockAbilitiesWithTags":{"_tags":[]},"activationOwnedTags":{"_tags":[]},"activationRequiredTags":{"_tags":[]},"activationBlockedTags":{"_tags":[{"_name":"CD.FireCircle","_hashCode":522143731,"_shortName":"FireCircle","_ancestorHashCodes":[-1137859925],"_ancestorNames":["CD"]}]},"ongoingBlockedTags":{"_tags":[{"_name":"Buff.DeBuff.Stun","_hashCode":1791562953,"_shortName":"Stun","_ancestorHashCodes":[937056111,321157895],"_ancestorNames":["Buff","Buff.DeBuff"]}]},"eventOutputPorts":[]}</t>
+          <t>{"guid":"90bacd9f-d882-4bba-aaa8-41ed993ac3ff","nodeType":8,"position":{"x":-419.33331298828125,"y":-1840.0},"targetType":2,"assetTags":{"_tags":[]},"grantedTags":{"_tags":[]},"applicationRequiredTags":{"_tags":[]},"applicationImmunityTags":{"_tags":[]},"removeGameEffectsWithTags":{"_tags":[]},"durationType":2,"duration":"0","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"_tags":[]},"cancelOnAbilityEnd":false,"launchPositionSource":0,"launchBindingName":"center","targetPositionSource":1,"targetBindingName":"center","projectileTargetType":0,"flyOver":false,"offsetAngle":0.0,"curveHeight":0.0,"projectileEntityId":50001,"projectilePrefab":null,"projectilePrefabPath":"Assets/Res/Entity/Effect/ef_fashi_gandian_buff.prefab","speed":3.0,"maxDistance":10.0,"collisionRadius":0.5,"isPiercing":false,"maxPierceCount":1,"collisionTargetTags":{"_tags":[]},"collisionExcludeTags":{"_tags":[]},"isBouncing":true,"bounceTargetMode":0,"maxBounceCount":3,"bounceSearchRadius":10.0,"canBounceToSameTarget":false,"excludeSourceCamp":true,"bounceAngleOffset":0.0}</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -1131,11 +1131,11 @@
       <c r="C27"/>
       <c r="D27"/>
       <c r="E27">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>{"guid":"90bacd9f-d882-4bba-aaa8-41ed993ac3ff","nodeType":8,"position":{"x":-419.33331298828125,"y":-1840.0},"targetType":2,"assetTags":{"_tags":[]},"grantedTags":{"_tags":[]},"applicationRequiredTags":{"_tags":[]},"applicationImmunityTags":{"_tags":[]},"removeGameEffectsWithTags":{"_tags":[]},"durationType":2,"duration":"0","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"_tags":[]},"cancelOnAbilityEnd":false,"launchPositionSource":0,"launchBindingName":"center","targetPositionSource":1,"targetBindingName":"center","projectileTargetType":0,"flyOver":false,"offsetAngle":0.0,"curveHeight":0.0,"projectileEntityId":50001,"projectilePrefab":null,"projectilePrefabPath":"Assets/Res/Entity/Effect/ef_fashi_gandian_buff.prefab","speed":3.0,"maxDistance":10.0,"collisionRadius":0.5,"isPiercing":false,"maxPierceCount":1,"collisionTargetTags":{"_tags":[]},"collisionExcludeTags":{"_tags":[]},"isBouncing":true,"bounceTargetMode":0,"maxBounceCount":3,"bounceSearchRadius":10.0,"canBounceToSameTarget":false,"excludeSourceCamp":true,"bounceAngleOffset":0.0}</t>
+          <t>{"guid":"2d7e41c4-8e90-4b61-879c-4b2e5b9486db","nodeType":14,"position":{"x":180.0,"y":-1810.0},"targetType":1,"requiredTags":{"_tags":[]},"immunityTags":{"_tags":[]},"destroyWithNode":false,"positionSource":2,"positionBindingName":"head","textType":0,"fixedText":"","contextDataKey":"DamageResult","textColor":{"r":1.0,"g":0.16293229162693024,"b":0.0,"a":1.0},"criticalColor":{"r":1.0,"g":0.5,"b":0.0,"a":1.0},"missColor":{"r":0.5,"g":0.5,"b":0.5,"a":1.0},"fontSize":5.0,"criticalFontSize":60.0,"duration":1.5,"offset":{"x":0.0,"y":0.0},"moveDirection":{"x":0.0,"y":1.0}}</t>
         </is>
       </c>
       <c r="G27"/>
@@ -1153,11 +1153,11 @@
       </c>
       <c r="D28"/>
       <c r="E28">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>{"guid":"2d7e41c4-8e90-4b61-879c-4b2e5b9486db","nodeType":14,"position":{"x":408.66665649414063,"y":-1747.3333740234375},"targetType":1,"requiredTags":{"_tags":[]},"immunityTags":{"_tags":[]},"destroyWithNode":false,"positionSource":2,"positionBindingName":"head","textType":0,"fixedText":"","contextDataKey":"DamageResult","textColor":{"r":0.0,"g":0.323091983795166,"b":1.0,"a":1.0},"criticalColor":{"r":1.0,"g":0.5,"b":0.0,"a":1.0},"missColor":{"r":0.5,"g":0.5,"b":0.5,"a":1.0},"fontSize":45.0,"criticalFontSize":60.0,"duration":1.5,"offset":{"x":0.0,"y":0.0},"moveDirection":{"x":0.0,"y":1.0}}</t>
+          <t>{"guid":"3aafa9a5-4766-4204-91ab-d797aeb3c0e1","nodeType":7,"position":{"x":580.6666259765625,"y":-1987.3333740234375},"targetType":1,"endType":0}</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -1173,11 +1173,11 @@
       <c r="C29"/>
       <c r="D29"/>
       <c r="E29">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>{"guid":"3aafa9a5-4766-4204-91ab-d797aeb3c0e1","nodeType":7,"position":{"x":580.6666259765625,"y":-1987.3333740234375},"targetType":1,"endType":0}</t>
+          <t>{"guid":"432ff1e3-b18d-476d-af80-d39ddc07402a","nodeType":20,"position":{"x":-491.33331298828125,"y":-2478.66650390625},"targetType":1,"skeletonDataAsset":null,"skeletonDataAssetPath":"Assets/Res/Spine/SP_Zhanshi/SP_Zhanshi_SkeletonData.asset","animationName":"Attack_01","animationDuration":"18","isAnimationLooping":false,"timeEffects":[{"triggerTime":11,"portIdValue":2315086,"legacyPortId":"de0ba361-3aba-4ef0-bb07-9b418fcae591"},{"triggerTime":24,"portIdValue":2715463,"legacyPortId":"7ecf9fe6-7c5e-46ae-bade-7922214225e2"}],"timeCues":[]}</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -1193,11 +1193,11 @@
       <c r="C30"/>
       <c r="D30"/>
       <c r="E30">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>{"guid":"432ff1e3-b18d-476d-af80-d39ddc07402a","nodeType":20,"position":{"x":-491.33331298828125,"y":-2478.66650390625},"targetType":1,"skeletonDataAsset":null,"skeletonDataAssetPath":"Assets/Res/Spine/SP_Zhanshi/SP_Zhanshi_SkeletonData.asset","animationName":"Attack_01","animationDuration":"18","isAnimationLooping":false,"timeEffects":[{"triggerTime":11,"portIdValue":2315086,"legacyPortId":"de0ba361-3aba-4ef0-bb07-9b418fcae591"},{"triggerTime":24,"portIdValue":2715463,"legacyPortId":"7ecf9fe6-7c5e-46ae-bade-7922214225e2"}],"timeCues":[]}</t>
+          <t>{"guid":"c28fb88d-51b1-47b2-be59-859e0ac638e3","nodeType":10,"position":{"x":-1220.6666259765625,"y":-1747.3333740234375},"targetType":1,"assetTags":{"_tags":[]},"grantedTags":{"_tags":[{"_name":"CD.FireCircle","_hashCode":522143731,"_shortName":"FireCircle","_ancestorHashCodes":[-1137859925],"_ancestorNames":["CD"]}]},"applicationRequiredTags":{"_tags":[]},"applicationImmunityTags":{"_tags":[]},"removeGameEffectsWithTags":{"_tags":[]},"durationType":1,"duration":"1","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"_tags":[]},"cancelOnAbilityEnd":false,"cooldownType":0,"maxCharges":2,"chargeTime":"10"}</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -1213,11 +1213,11 @@
       <c r="C31"/>
       <c r="D31"/>
       <c r="E31">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>{"guid":"c28fb88d-51b1-47b2-be59-859e0ac638e3","nodeType":10,"position":{"x":-1220.6666259765625,"y":-1747.3333740234375},"targetType":1,"assetTags":{"_tags":[]},"grantedTags":{"_tags":[{"_name":"CD.FireCircle","_hashCode":522143731,"_shortName":"FireCircle","_ancestorHashCodes":[-1137859925],"_ancestorNames":["CD"]}]},"applicationRequiredTags":{"_tags":[]},"applicationImmunityTags":{"_tags":[]},"removeGameEffectsWithTags":{"_tags":[]},"durationType":1,"duration":"1","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"_tags":[]},"cancelOnAbilityEnd":false,"cooldownType":0,"maxCharges":2,"chargeTime":"10"}</t>
+          <t>{"guid":"356907e0-1488-4128-bfcc-7ff73cfc3330","nodeType":0,"position":{"x":-878.6666259765625,"y":-1851.3333740234375},"targetType":1,"skillId":1010,"assetTags":{"_tags":[]},"cancelAbilitiesWithTags":{"_tags":[]},"blockAbilitiesWithTags":{"_tags":[]},"activationOwnedTags":{"_tags":[]},"activationRequiredTags":{"_tags":[]},"activationBlockedTags":{"_tags":[{"_name":"CD.FireCircle","_hashCode":522143731,"_shortName":"FireCircle","_ancestorHashCodes":[-1137859925],"_ancestorNames":["CD"]}]},"ongoingBlockedTags":{"_tags":[]},"eventOutputPorts":[]}</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -1233,11 +1233,11 @@
       <c r="C32"/>
       <c r="D32"/>
       <c r="E32">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>{"guid":"356907e0-1488-4128-bfcc-7ff73cfc3330","nodeType":0,"position":{"x":-878.6666259765625,"y":-1851.3333740234375},"targetType":1,"skillId":1010,"assetTags":{"_tags":[]},"cancelAbilitiesWithTags":{"_tags":[]},"blockAbilitiesWithTags":{"_tags":[]},"activationOwnedTags":{"_tags":[]},"activationRequiredTags":{"_tags":[]},"activationBlockedTags":{"_tags":[{"_name":"CD.FireCircle","_hashCode":522143731,"_shortName":"FireCircle","_ancestorHashCodes":[-1137859925],"_ancestorNames":["CD"]}]},"ongoingBlockedTags":{"_tags":[]},"eventOutputPorts":[]}</t>
+          <t>{"guid":"9d6f459d-b588-4b64-843b-1b71e8f299ae","nodeType":3,"position":{"x":-1195.3333740234375,"y":-2013.3333740234375},"targetType":1,"assetTags":{"_tags":[]},"grantedTags":{"_tags":[]},"applicationRequiredTags":{"_tags":[]},"applicationImmunityTags":{"_tags":[]},"removeGameEffectsWithTags":{"_tags":[]},"durationType":0,"duration":"0","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[{"attrType":1003,"operation":0,"magnitudeSourceType":0,"fixedValue":-100.0,"formula":"","mmcType":0,"setByCallerKey":"","mmcCaptureAttribute":200,"mmcAttributeSource":0,"mmcCoefficient":1.0,"mmcUseSnapshot":true}],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"_tags":[]},"cancelOnAbilityEnd":true}</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -1253,11 +1253,11 @@
       <c r="C33"/>
       <c r="D33"/>
       <c r="E33">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>{"guid":"9d6f459d-b588-4b64-843b-1b71e8f299ae","nodeType":3,"position":{"x":-1195.3333740234375,"y":-2013.3333740234375},"targetType":1,"assetTags":{"_tags":[]},"grantedTags":{"_tags":[]},"applicationRequiredTags":{"_tags":[]},"applicationImmunityTags":{"_tags":[]},"removeGameEffectsWithTags":{"_tags":[]},"durationType":0,"duration":"0","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[{"attrType":1003,"operation":0,"magnitudeSourceType":0,"fixedValue":-100.0,"formula":"","mmcType":0,"setByCallerKey":"","mmcCaptureAttribute":200,"mmcAttributeSource":0,"mmcCoefficient":1.0,"mmcUseSnapshot":true}],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"_tags":[]},"cancelOnAbilityEnd":true}</t>
+          <t>{"guid":"eae41233-d297-46fe-a6c8-0b5c876fbb2a","nodeType":1,"position":{"x":45.333343505859375,"y":-1806.666748046875},"targetType":0,"assetTags":{"_tags":[]},"grantedTags":{"_tags":[]},"applicationRequiredTags":{"_tags":[]},"applicationImmunityTags":{"_tags":[]},"removeGameEffectsWithTags":{"_tags":[]},"durationType":0,"duration":"0","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"_tags":[]},"cancelOnAbilityEnd":true,"damageType":0,"damageSourceType":0,"damageFixedValue":10.0,"damageFormula":"","damageMMCType":0,"damageSetByCallerKey":"","damageMMCCaptureAttribute":200,"damageMMCAttributeSource":0,"damageMMCCoefficient":1.0,"damageMMCUseSnapshot":true,"damageMultiplyByStackCount":false,"damageCalculationType":0,"enableHitKnockback":true,"knockbackDistance":1.0,"knockbackSpeed":12.0}</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -1273,11 +1273,11 @@
       <c r="C34"/>
       <c r="D34"/>
       <c r="E34">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>{"guid":"eae41233-d297-46fe-a6c8-0b5c876fbb2a","nodeType":1,"position":{"x":45.333343505859375,"y":-1806.666748046875},"targetType":0,"assetTags":{"_tags":[]},"grantedTags":{"_tags":[]},"applicationRequiredTags":{"_tags":[]},"applicationImmunityTags":{"_tags":[]},"removeGameEffectsWithTags":{"_tags":[]},"durationType":0,"duration":"0","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"_tags":[]},"cancelOnAbilityEnd":true,"damageType":0,"damageSourceType":0,"damageFixedValue":10.0,"damageFormula":"","damageMMCType":0,"damageSetByCallerKey":"","damageMMCCaptureAttribute":200,"damageMMCAttributeSource":0,"damageMMCCoefficient":1.0,"damageMMCUseSnapshot":true,"damageMultiplyByStackCount":false,"damageCalculationType":0,"enableHitKnockback":true,"knockbackDistance":1.0,"knockbackSpeed":12.0}</t>
+          <t>{"guid":"90bacd9f-d882-4bba-aaa8-41ed993ac3ff","nodeType":8,"position":{"x":-400.66665649414063,"y":-1836.666748046875},"targetType":2,"assetTags":{"_tags":[]},"grantedTags":{"_tags":[]},"applicationRequiredTags":{"_tags":[]},"applicationImmunityTags":{"_tags":[]},"removeGameEffectsWithTags":{"_tags":[]},"durationType":2,"duration":"0","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"_tags":[]},"cancelOnAbilityEnd":false,"launchPositionSource":0,"launchBindingName":"center","targetPositionSource":1,"targetBindingName":"center","projectileTargetType":0,"flyOver":false,"offsetAngle":0.0,"curveHeight":0.0,"projectileEntityId":50001,"projectilePrefab":null,"projectilePrefabPath":"Assets/Res/Entity/Effect/ef_fashi_gandian_buff.prefab","speed":3.0,"maxDistance":10.0,"collisionRadius":0.5,"isPiercing":false,"maxPierceCount":1,"collisionTargetTags":{"_tags":[]},"collisionExcludeTags":{"_tags":[]},"isBouncing":true,"bounceTargetMode":0,"maxBounceCount":2,"bounceSearchRadius":10.0,"canBounceToSameTarget":false,"excludeSourceCamp":true,"bounceAngleOffset":50.0}</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -1293,11 +1293,11 @@
       <c r="C35"/>
       <c r="D35"/>
       <c r="E35">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>{"guid":"90bacd9f-d882-4bba-aaa8-41ed993ac3ff","nodeType":8,"position":{"x":-400.66665649414063,"y":-1836.666748046875},"targetType":2,"assetTags":{"_tags":[]},"grantedTags":{"_tags":[]},"applicationRequiredTags":{"_tags":[]},"applicationImmunityTags":{"_tags":[]},"removeGameEffectsWithTags":{"_tags":[]},"durationType":2,"duration":"0","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"_tags":[]},"cancelOnAbilityEnd":false,"launchPositionSource":0,"launchBindingName":"center","targetPositionSource":1,"targetBindingName":"center","projectileTargetType":0,"flyOver":false,"offsetAngle":0.0,"curveHeight":0.0,"projectileEntityId":50001,"projectilePrefab":null,"projectilePrefabPath":"Assets/Res/Entity/Effect/ef_fashi_gandian_buff.prefab","speed":3.0,"maxDistance":10.0,"collisionRadius":0.5,"isPiercing":false,"maxPierceCount":1,"collisionTargetTags":{"_tags":[]},"collisionExcludeTags":{"_tags":[]},"isBouncing":true,"bounceTargetMode":0,"maxBounceCount":2,"bounceSearchRadius":10.0,"canBounceToSameTarget":false,"excludeSourceCamp":true,"bounceAngleOffset":50.0}</t>
+          <t>{"guid":"2d7e41c4-8e90-4b61-879c-4b2e5b9486db","nodeType":14,"position":{"x":408.66665649414063,"y":-1747.3333740234375},"targetType":1,"requiredTags":{"_tags":[]},"immunityTags":{"_tags":[]},"destroyWithNode":false,"positionSource":2,"positionBindingName":"head","textType":0,"fixedText":"","contextDataKey":"DamageResult","textColor":{"r":0.0,"g":0.323091983795166,"b":1.0,"a":1.0},"criticalColor":{"r":1.0,"g":0.5,"b":0.0,"a":1.0},"missColor":{"r":0.5,"g":0.5,"b":0.5,"a":1.0},"fontSize":5.0,"criticalFontSize":60.0,"duration":1.5,"offset":{"x":0.0,"y":0.0},"moveDirection":{"x":0.0,"y":1.0}}</t>
         </is>
       </c>
       <c r="G35"/>
@@ -1561,7 +1561,7 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>{"guid":"becb4d53-8a9e-4dc0-95a3-618d1e79ecc7","nodeType":14,"position":{"x":-303.33331298828125,"y":-1952.666748046875},"targetType":1,"requiredTags":{"_tags":[]},"immunityTags":{"_tags":[]},"destroyWithNode":false,"positionSource":2,"positionBindingName":"head","textType":1,"fixedText":"","contextDataKey":"Heal","textColor":{"r":0.25257891416549683,"g":0.96226418018341064,"b":0.1180134117603302,"a":1.0},"criticalColor":{"r":1.0,"g":0.5,"b":0.0,"a":1.0},"missColor":{"r":0.5,"g":0.5,"b":0.5,"a":1.0},"fontSize":45.0,"criticalFontSize":60.0,"duration":1.5,"offset":{"x":0.0,"y":0.0},"moveDirection":{"x":0.0,"y":1.0}}</t>
+          <t>{"guid":"becb4d53-8a9e-4dc0-95a3-618d1e79ecc7","nodeType":14,"position":{"x":-303.33331298828125,"y":-1952.666748046875},"targetType":1,"requiredTags":{"_tags":[]},"immunityTags":{"_tags":[]},"destroyWithNode":false,"positionSource":2,"positionBindingName":"head","textType":1,"fixedText":"","contextDataKey":"Heal","textColor":{"r":0.25257891416549683,"g":0.96226418018341064,"b":0.1180134117603302,"a":1.0},"criticalColor":{"r":1.0,"g":0.5,"b":0.0,"a":1.0},"missColor":{"r":0.5,"g":0.5,"b":0.5,"a":1.0},"fontSize":5.0,"criticalFontSize":60.0,"duration":1.5,"offset":{"x":0.0,"y":0.0},"moveDirection":{"x":0.0,"y":1.0}}</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -1679,11 +1679,11 @@
       <c r="C54"/>
       <c r="D54"/>
       <c r="E54">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>{"guid":"e33ab94c-1496-4d6a-ba5e-1afd38bb0c30","nodeType":4,"position":{"x":-452.0,"y":-1786.666748046875},"targetType":1,"searchShapeType":0,"searchLineType":0,"positionSource":0,"positionBindingName":"center","searchCircleRadius":2.5,"searchSectorRadius":2.0,"searchSectorAngle":180.0,"searchLineDirectionOffsetAngle":0.0,"searchLineDirectionWidth":1.0,"searchLineDirectionLength":10.0,"lineStartPositionSource":0,"lineStartBindingName":"","lineEndPositionSource":1,"lineEndBindingName":"","searchLineBetweenWidth":1.0,"searchLineAbsoluteAngle":0.0,"searchLineAbsoluteWidth":1.0,"searchLineAbsoluteLength":10.0,"maxTargets":999,"searchTargetTags":{"_tags":[{"_name":"unitType.monster","_hashCode":-2021655864,"_shortName":"monster","_ancestorHashCodes":[1600484460],"_ancestorNames":["unitType"]}]},"searchExcludeTags":{"_tags":[]}}</t>
+          <t>{"guid":"432ff1e3-b18d-476d-af80-d39ddc07402a","nodeType":20,"position":{"x":-452.0,"y":-2375.333251953125},"targetType":1,"skeletonDataAsset":null,"skeletonDataAssetPath":"Assets/Res/Spine/SP_Zhanshi/SP_Zhanshi_SkeletonData.asset","animationName":"Skill_attack_1005","animationDuration":"16","isAnimationLooping":false,"timeEffects":[{"triggerTime":7,"portIdValue":2315086,"legacyPortId":"de0ba361-3aba-4ef0-bb07-9b418fcae591"},{"triggerTime":16,"portIdValue":2000539,"legacyPortId":"f41c85e0-7f26-494e-9ffc-4a06c980f811"}],"timeCues":[{"startTime":6,"endTime":55,"portIdValue":2287012,"legacyPortId":"8dea1941-c520-4f9a-aee0-40932c8542ef"}]}</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
@@ -1699,11 +1699,11 @@
       <c r="C55"/>
       <c r="D55"/>
       <c r="E55">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>{"guid":"432ff1e3-b18d-476d-af80-d39ddc07402a","nodeType":20,"position":{"x":-452.0,"y":-2375.333251953125},"targetType":1,"skeletonDataAsset":null,"skeletonDataAssetPath":"Assets/Res/Spine/SP_Zhanshi/SP_Zhanshi_SkeletonData.asset","animationName":"Skill_attack_1005","animationDuration":"16","isAnimationLooping":false,"timeEffects":[{"triggerTime":7,"portIdValue":2315086,"legacyPortId":"de0ba361-3aba-4ef0-bb07-9b418fcae591"},{"triggerTime":16,"portIdValue":2000539,"legacyPortId":"f41c85e0-7f26-494e-9ffc-4a06c980f811"}],"timeCues":[{"startTime":6,"endTime":55,"portIdValue":2287012,"legacyPortId":"8dea1941-c520-4f9a-aee0-40932c8542ef"}]}</t>
+          <t>{"guid":"356907e0-1488-4128-bfcc-7ff73cfc3330","nodeType":0,"position":{"x":-878.6666259765625,"y":-1853.3333740234375},"targetType":1,"skillId":1003,"assetTags":{"_tags":[]},"cancelAbilitiesWithTags":{"_tags":[]},"blockAbilitiesWithTags":{"_tags":[]},"activationOwnedTags":{"_tags":[{"_name":"Skill.Running","_hashCode":-51601538,"_shortName":"Running","_ancestorHashCodes":[1312877309],"_ancestorNames":["Skill"]}]},"activationRequiredTags":{"_tags":[]},"activationBlockedTags":{"_tags":[{"_name":"CD.RuFood","_hashCode":-1045902856,"_shortName":"RuFood","_ancestorHashCodes":[-1137859925],"_ancestorNames":["CD"]},{"_name":"Skill.Running","_hashCode":-51601538,"_shortName":"Running","_ancestorHashCodes":[1312877309],"_ancestorNames":["Skill"]}]},"ongoingBlockedTags":{"_tags":[]},"eventOutputPorts":[]}</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
@@ -1719,11 +1719,11 @@
       <c r="C56"/>
       <c r="D56"/>
       <c r="E56">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>{"guid":"356907e0-1488-4128-bfcc-7ff73cfc3330","nodeType":0,"position":{"x":-878.6666259765625,"y":-1853.3333740234375},"targetType":1,"skillId":1003,"assetTags":{"_tags":[]},"cancelAbilitiesWithTags":{"_tags":[]},"blockAbilitiesWithTags":{"_tags":[]},"activationOwnedTags":{"_tags":[{"_name":"Skill.Running","_hashCode":-51601538,"_shortName":"Running","_ancestorHashCodes":[1312877309],"_ancestorNames":["Skill"]}]},"activationRequiredTags":{"_tags":[]},"activationBlockedTags":{"_tags":[{"_name":"CD.RuFood","_hashCode":-1045902856,"_shortName":"RuFood","_ancestorHashCodes":[-1137859925],"_ancestorNames":["CD"]},{"_name":"Skill.Running","_hashCode":-51601538,"_shortName":"Running","_ancestorHashCodes":[1312877309],"_ancestorNames":["Skill"]}]},"ongoingBlockedTags":{"_tags":[]},"eventOutputPorts":[]}</t>
+          <t>{"guid":"cde57fb8-b693-4da8-a4a8-fd61e56c5dcd","nodeType":12,"position":{"x":676.6666259765625,"y":-1998.0},"targetType":1,"requiredTags":{"_tags":[]},"immunityTags":{"_tags":[]},"destroyWithNode":false,"positionSource":0,"particleEntityId":50007,"particlePrefab":null,"particlePrefabPath":"Assets/Res/Entity/Effect/ef_zhanshi_jcjt_01.prefab","particleBindingName":"down","particleOffset":{"x":0.0,"y":0.0,"z":0.0},"particleScale":{"x":1.0,"y":1.0,"z":1.0},"attachToTarget":false,"particleLoop":false}</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
@@ -1743,7 +1743,7 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>{"guid":"cde57fb8-b693-4da8-a4a8-fd61e56c5dcd","nodeType":12,"position":{"x":676.6666259765625,"y":-1998.0},"targetType":1,"requiredTags":{"_tags":[]},"immunityTags":{"_tags":[]},"destroyWithNode":false,"positionSource":0,"particleEntityId":50007,"particlePrefab":null,"particlePrefabPath":"Assets/Res/Entity/Effect/ef_zhanshi_jcjt_01.prefab","particleBindingName":"down","particleOffset":{"x":0.0,"y":0.0,"z":0.0},"particleScale":{"x":1.0,"y":1.0,"z":1.0},"attachToTarget":false,"particleLoop":false}</t>
+          <t>{"guid":"93ec5a43-cc34-4e4a-acb3-39da2f2c3010","nodeType":12,"position":{"x":387.33334350585938,"y":-1790.666748046875},"targetType":1,"requiredTags":{"_tags":[]},"immunityTags":{"_tags":[]},"destroyWithNode":true,"positionSource":2,"particleEntityId":50005,"particlePrefab":null,"particlePrefabPath":"Assets/Res/Entity/Effect/ef_Xuanyun_01.prefab","particleBindingName":"head","particleOffset":{"x":0.0,"y":0.0,"z":0.0},"particleScale":{"x":1.0,"y":1.0,"z":1.0},"attachToTarget":true,"particleLoop":true}</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
@@ -1759,11 +1759,11 @@
       <c r="C58"/>
       <c r="D58"/>
       <c r="E58">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>{"guid":"cb1df36f-5729-423e-9d1a-287db5a433f0","nodeType":11,"position":{"x":18.66668701171875,"y":-1786.666748046875},"targetType":0,"assetTags":{"_tags":[{"_name":"Buff.DeBuff.Stun","_hashCode":1791562953,"_shortName":"Stun","_ancestorHashCodes":[937056111,321157895],"_ancestorNames":["Buff","Buff.DeBuff"]}]},"grantedTags":{"_tags":[{"_name":"Buff.DeBuff.Stun","_hashCode":1791562953,"_shortName":"Stun","_ancestorHashCodes":[937056111,321157895],"_ancestorNames":["Buff","Buff.DeBuff"]}]},"applicationRequiredTags":{"_tags":[]},"applicationImmunityTags":{"_tags":[]},"removeGameEffectsWithTags":{"_tags":[]},"durationType":1,"duration":"4","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[],"stackType":1,"stackLimit":1,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":1,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"_tags":[]},"cancelOnAbilityEnd":false,"buffId":0}</t>
+          <t>{"guid":"e33ab94c-1496-4d6a-ba5e-1afd38bb0c30","nodeType":4,"position":{"x":-452.0,"y":-1786.666748046875},"targetType":1,"searchShapeType":0,"searchLineType":0,"positionSource":0,"positionBindingName":"center","searchCircleRadius":5.0,"searchSectorRadius":2.0,"searchSectorAngle":180.0,"searchLineDirectionOffsetAngle":0.0,"searchLineDirectionWidth":1.0,"searchLineDirectionLength":10.0,"lineStartPositionSource":0,"lineStartBindingName":"","lineEndPositionSource":1,"lineEndBindingName":"","searchLineBetweenWidth":1.0,"searchLineAbsoluteAngle":0.0,"searchLineAbsoluteWidth":1.0,"searchLineAbsoluteLength":10.0,"maxTargets":999,"searchTargetTags":{"_tags":[{"_name":"unitType.monster","_hashCode":-2021655864,"_shortName":"monster","_ancestorHashCodes":[1600484460],"_ancestorNames":["unitType"]}]},"searchExcludeTags":{"_tags":[]}}</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
@@ -1779,11 +1779,11 @@
       <c r="C59"/>
       <c r="D59"/>
       <c r="E59">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>{"guid":"93ec5a43-cc34-4e4a-acb3-39da2f2c3010","nodeType":12,"position":{"x":468.66665649414063,"y":-1749.3333740234375},"targetType":1,"requiredTags":{"_tags":[]},"immunityTags":{"_tags":[]},"destroyWithNode":true,"positionSource":2,"particleEntityId":50005,"particlePrefab":null,"particlePrefabPath":"Assets/Res/Entity/Effect/ef_Xuanyun_01.prefab","particleBindingName":"head","particleOffset":{"x":0.0,"y":0.0,"z":0.0},"particleScale":{"x":1.0,"y":1.0,"z":1.0},"attachToTarget":true,"particleLoop":true}</t>
+          <t>{"guid":"cb1df36f-5729-423e-9d1a-287db5a433f0","nodeType":11,"position":{"x":18.66668701171875,"y":-1787.3333740234375},"targetType":0,"assetTags":{"_tags":[{"_name":"Buff.DeBuff.Stun","_hashCode":1791562953,"_shortName":"Stun","_ancestorHashCodes":[937056111,321157895],"_ancestorNames":["Buff","Buff.DeBuff"]}]},"grantedTags":{"_tags":[{"_name":"Buff.DeBuff.Stun","_hashCode":1791562953,"_shortName":"Stun","_ancestorHashCodes":[937056111,321157895],"_ancestorNames":["Buff","Buff.DeBuff"]}]},"applicationRequiredTags":{"_tags":[]},"applicationImmunityTags":{"_tags":[]},"removeGameEffectsWithTags":{"_tags":[]},"durationType":1,"duration":"4","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[],"stackType":1,"stackLimit":1,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":1,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"_tags":[]},"cancelOnAbilityEnd":false,"buffId":0}</t>
         </is>
       </c>
       <c r="G59"/>
@@ -1923,11 +1923,11 @@
       </c>
       <c r="D66"/>
       <c r="E66">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>{"guid":"c353e286-8ef0-460a-b917-887f2aeb390a","nodeType":14,"position":{"x":1213.3333740234375,"y":-2354.0},"targetType":1,"requiredTags":{"_tags":[]},"immunityTags":{"_tags":[]},"destroyWithNode":false,"positionSource":2,"positionBindingName":"head","textType":0,"fixedText":"","contextDataKey":"DamageResult","textColor":{"r":1.0,"g":0.0,"b":0.0,"a":1.0},"criticalColor":{"r":1.0,"g":0.5,"b":0.0,"a":1.0},"missColor":{"r":0.5,"g":0.5,"b":0.5,"a":1.0},"fontSize":45.0,"criticalFontSize":60.0,"duration":1.5,"offset":{"x":0.0,"y":0.0},"moveDirection":{"x":0.0,"y":1.0}}</t>
+          <t>{"guid":"c28fb88d-51b1-47b2-be59-859e0ac638e3","nodeType":10,"position":{"x":-1130.6666259765625,"y":-2232.0},"targetType":1,"assetTags":{"_tags":[]},"grantedTags":{"_tags":[{"_name":"CD.Sweep","_hashCode":-303359587,"_shortName":"Sweep","_ancestorHashCodes":[-1137859925],"_ancestorNames":["CD"]}]},"applicationRequiredTags":{"_tags":[]},"applicationImmunityTags":{"_tags":[]},"removeGameEffectsWithTags":{"_tags":[]},"durationType":1,"duration":"1","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"_tags":[]},"cancelOnAbilityEnd":false,"cooldownType":0,"maxCharges":2,"chargeTime":"10"}</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
@@ -1943,11 +1943,11 @@
       <c r="C67"/>
       <c r="D67"/>
       <c r="E67">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>{"guid":"c28fb88d-51b1-47b2-be59-859e0ac638e3","nodeType":10,"position":{"x":-1130.6666259765625,"y":-2232.0},"targetType":1,"assetTags":{"_tags":[]},"grantedTags":{"_tags":[{"_name":"CD.Sweep","_hashCode":-303359587,"_shortName":"Sweep","_ancestorHashCodes":[-1137859925],"_ancestorNames":["CD"]}]},"applicationRequiredTags":{"_tags":[]},"applicationImmunityTags":{"_tags":[]},"removeGameEffectsWithTags":{"_tags":[]},"durationType":1,"duration":"1","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"_tags":[]},"cancelOnAbilityEnd":false,"cooldownType":0,"maxCharges":2,"chargeTime":"10"}</t>
+          <t>{"guid":"432ff1e3-b18d-476d-af80-d39ddc07402a","nodeType":20,"position":{"x":-415.33331298828125,"y":-2827.333251953125},"targetType":1,"skeletonDataAsset":null,"skeletonDataAssetPath":"Assets/Res/Spine/SP_Zhanshi/SP_Zhanshi_SkeletonData.asset","animationName":"Skill_attack_1001","animationDuration":"18","isAnimationLooping":false,"timeEffects":[{"triggerTime":7,"portIdValue":2315086,"legacyPortId":"de0ba361-3aba-4ef0-bb07-9b418fcae591"},{"triggerTime":18,"portIdValue":2649436,"legacyPortId":"84e238a8-5baf-470e-829f-186695064945"}],"timeCues":[{"startTime":7,"endTime":48,"portIdValue":2287012,"legacyPortId":"8dea1941-c520-4f9a-aee0-40932c8542ef"}]}</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
@@ -1963,11 +1963,11 @@
       <c r="C68"/>
       <c r="D68"/>
       <c r="E68">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>{"guid":"432ff1e3-b18d-476d-af80-d39ddc07402a","nodeType":20,"position":{"x":-415.33331298828125,"y":-2827.333251953125},"targetType":1,"skeletonDataAsset":null,"skeletonDataAssetPath":"Assets/Res/Spine/SP_Zhanshi/SP_Zhanshi_SkeletonData.asset","animationName":"Skill_attack_1001","animationDuration":"18","isAnimationLooping":false,"timeEffects":[{"triggerTime":7,"portIdValue":2315086,"legacyPortId":"de0ba361-3aba-4ef0-bb07-9b418fcae591"},{"triggerTime":18,"portIdValue":2649436,"legacyPortId":"84e238a8-5baf-470e-829f-186695064945"}],"timeCues":[{"startTime":7,"endTime":48,"portIdValue":2287012,"legacyPortId":"8dea1941-c520-4f9a-aee0-40932c8542ef"}]}</t>
+          <t>{"guid":"9d6f459d-b588-4b64-843b-1b71e8f299ae","nodeType":3,"position":{"x":-1130.6666259765625,"y":-2479.333251953125},"targetType":1,"assetTags":{"_tags":[]},"grantedTags":{"_tags":[]},"applicationRequiredTags":{"_tags":[]},"applicationImmunityTags":{"_tags":[]},"removeGameEffectsWithTags":{"_tags":[]},"durationType":0,"duration":"0","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[{"attrType":1003,"operation":0,"magnitudeSourceType":0,"fixedValue":-10.0,"formula":"","mmcType":0,"setByCallerKey":"","mmcCaptureAttribute":200,"mmcAttributeSource":0,"mmcCoefficient":1.0,"mmcUseSnapshot":true}],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"_tags":[]},"cancelOnAbilityEnd":true}</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
@@ -1983,11 +1983,11 @@
       <c r="C69"/>
       <c r="D69"/>
       <c r="E69">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>{"guid":"9d6f459d-b588-4b64-843b-1b71e8f299ae","nodeType":3,"position":{"x":-1130.6666259765625,"y":-2479.333251953125},"targetType":1,"assetTags":{"_tags":[]},"grantedTags":{"_tags":[]},"applicationRequiredTags":{"_tags":[]},"applicationImmunityTags":{"_tags":[]},"removeGameEffectsWithTags":{"_tags":[]},"durationType":0,"duration":"0","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[{"attrType":1003,"operation":0,"magnitudeSourceType":0,"fixedValue":-10.0,"formula":"","mmcType":0,"setByCallerKey":"","mmcCaptureAttribute":200,"mmcAttributeSource":0,"mmcCoefficient":1.0,"mmcUseSnapshot":true}],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"_tags":[]},"cancelOnAbilityEnd":true}</t>
+          <t>{"guid":"356907e0-1488-4128-bfcc-7ff73cfc3330","nodeType":0,"position":{"x":-843.3333740234375,"y":-2480.0},"targetType":1,"skillId":1001,"assetTags":{"_tags":[]},"cancelAbilitiesWithTags":{"_tags":[]},"blockAbilitiesWithTags":{"_tags":[]},"activationOwnedTags":{"_tags":[]},"activationRequiredTags":{"_tags":[]},"activationBlockedTags":{"_tags":[{"_name":"CD.Sweep","_hashCode":-303359587,"_shortName":"Sweep","_ancestorHashCodes":[-1137859925],"_ancestorNames":["CD"]}]},"ongoingBlockedTags":{"_tags":[]},"eventOutputPorts":[]}</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
@@ -2003,11 +2003,11 @@
       <c r="C70"/>
       <c r="D70"/>
       <c r="E70">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>{"guid":"356907e0-1488-4128-bfcc-7ff73cfc3330","nodeType":0,"position":{"x":-843.3333740234375,"y":-2480.0},"targetType":1,"skillId":1001,"assetTags":{"_tags":[]},"cancelAbilitiesWithTags":{"_tags":[]},"blockAbilitiesWithTags":{"_tags":[]},"activationOwnedTags":{"_tags":[]},"activationRequiredTags":{"_tags":[]},"activationBlockedTags":{"_tags":[{"_name":"CD.Sweep","_hashCode":-303359587,"_shortName":"Sweep","_ancestorHashCodes":[-1137859925],"_ancestorNames":["CD"]}]},"ongoingBlockedTags":{"_tags":[]},"eventOutputPorts":[]}</t>
+          <t>{"guid":"f8947676-1084-4228-b991-1509cc7fe851","nodeType":1,"position":{"x":974.666748046875,"y":-2340.66650390625},"targetType":0,"assetTags":{"_tags":[]},"grantedTags":{"_tags":[]},"applicationRequiredTags":{"_tags":[]},"applicationImmunityTags":{"_tags":[]},"removeGameEffectsWithTags":{"_tags":[]},"durationType":0,"duration":"0","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"_tags":[]},"cancelOnAbilityEnd":true,"damageType":0,"damageSourceType":2,"damageFixedValue":10.0,"damageFormula":"","damageMMCType":0,"damageSetByCallerKey":"","damageMMCCaptureAttribute":1006,"damageMMCAttributeSource":0,"damageMMCCoefficient":1.0,"damageMMCUseSnapshot":true,"damageMultiplyByStackCount":false,"damageCalculationType":0,"enableHitKnockback":true,"knockbackDistance":1.0,"knockbackSpeed":12.0}</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
@@ -2023,11 +2023,11 @@
       <c r="C71"/>
       <c r="D71"/>
       <c r="E71">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>{"guid":"f8947676-1084-4228-b991-1509cc7fe851","nodeType":1,"position":{"x":974.666748046875,"y":-2340.66650390625},"targetType":0,"assetTags":{"_tags":[]},"grantedTags":{"_tags":[]},"applicationRequiredTags":{"_tags":[]},"applicationImmunityTags":{"_tags":[]},"removeGameEffectsWithTags":{"_tags":[]},"durationType":0,"duration":"0","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"_tags":[]},"cancelOnAbilityEnd":true,"damageType":0,"damageSourceType":2,"damageFixedValue":10.0,"damageFormula":"","damageMMCType":0,"damageSetByCallerKey":"","damageMMCCaptureAttribute":1006,"damageMMCAttributeSource":0,"damageMMCCoefficient":1.0,"damageMMCUseSnapshot":true,"damageMultiplyByStackCount":false,"damageCalculationType":0,"enableHitKnockback":true,"knockbackDistance":1.0,"knockbackSpeed":12.0}</t>
+          <t>{"guid":"e33ab94c-1496-4d6a-ba5e-1afd38bb0c30","nodeType":4,"position":{"x":731.3333740234375,"y":-2344.0},"targetType":1,"searchShapeType":1,"searchLineType":0,"positionSource":0,"positionBindingName":"center","searchCircleRadius":5.0,"searchSectorRadius":5.0,"searchSectorAngle":180.0,"searchLineDirectionOffsetAngle":0.0,"searchLineDirectionWidth":1.0,"searchLineDirectionLength":10.0,"lineStartPositionSource":0,"lineStartBindingName":"","lineEndPositionSource":1,"lineEndBindingName":"","searchLineBetweenWidth":1.0,"searchLineAbsoluteAngle":0.0,"searchLineAbsoluteWidth":1.0,"searchLineAbsoluteLength":10.0,"maxTargets":999,"searchTargetTags":{"_tags":[{"_name":"unitType.monster","_hashCode":-2021655864,"_shortName":"monster","_ancestorHashCodes":[1600484460],"_ancestorNames":["unitType"]}]},"searchExcludeTags":{"_tags":[]}}</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
@@ -2043,11 +2043,11 @@
       <c r="C72"/>
       <c r="D72"/>
       <c r="E72">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>{"guid":"e33ab94c-1496-4d6a-ba5e-1afd38bb0c30","nodeType":4,"position":{"x":731.3333740234375,"y":-2344.0},"targetType":1,"searchShapeType":1,"searchLineType":0,"positionSource":0,"positionBindingName":"center","searchCircleRadius":5.0,"searchSectorRadius":5.0,"searchSectorAngle":180.0,"searchLineDirectionOffsetAngle":0.0,"searchLineDirectionWidth":1.0,"searchLineDirectionLength":10.0,"lineStartPositionSource":0,"lineStartBindingName":"","lineEndPositionSource":1,"lineEndBindingName":"","searchLineBetweenWidth":1.0,"searchLineAbsoluteAngle":0.0,"searchLineAbsoluteWidth":1.0,"searchLineAbsoluteLength":10.0,"maxTargets":999,"searchTargetTags":{"_tags":[{"_name":"unitType.monster","_hashCode":-2021655864,"_shortName":"monster","_ancestorHashCodes":[1600484460],"_ancestorNames":["unitType"]}]},"searchExcludeTags":{"_tags":[]}}</t>
+          <t>{"guid":"2cfdacd2-0186-49dd-b177-4eb8c0ad87bd","nodeType":7,"position":{"x":731.3333740234375,"y":-2142.66650390625},"targetType":1,"endType":0}</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
@@ -2063,11 +2063,11 @@
       <c r="C73"/>
       <c r="D73"/>
       <c r="E73">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>{"guid":"2cfdacd2-0186-49dd-b177-4eb8c0ad87bd","nodeType":7,"position":{"x":731.3333740234375,"y":-2142.66650390625},"targetType":1,"endType":0}</t>
+          <t>{"guid":"cde57fb8-b693-4da8-a4a8-fd61e56c5dcd","nodeType":12,"position":{"x":731.3333740234375,"y":-2491.333251953125},"targetType":1,"requiredTags":{"_tags":[]},"immunityTags":{"_tags":[]},"destroyWithNode":false,"positionSource":0,"particleEntityId":50006,"particlePrefab":null,"particlePrefabPath":"Assets/Res/Entity/Effect/ef_Zhanshi_attack_02.prefab","particleBindingName":"down","particleOffset":{"x":5.0,"y":0.0,"z":0.0},"particleScale":{"x":1.0,"y":1.0,"z":1.0},"attachToTarget":false,"particleLoop":false}</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
@@ -2083,11 +2083,11 @@
       <c r="C74"/>
       <c r="D74"/>
       <c r="E74">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>{"guid":"cde57fb8-b693-4da8-a4a8-fd61e56c5dcd","nodeType":12,"position":{"x":731.3333740234375,"y":-2491.333251953125},"targetType":1,"requiredTags":{"_tags":[]},"immunityTags":{"_tags":[]},"destroyWithNode":false,"positionSource":0,"particleEntityId":50006,"particlePrefab":null,"particlePrefabPath":"Assets/Res/Entity/Effect/ef_Zhanshi_attack_02.prefab","particleBindingName":"down","particleOffset":{"x":5.0,"y":0.0,"z":0.0},"particleScale":{"x":1.0,"y":1.0,"z":1.0},"attachToTarget":false,"particleLoop":false}</t>
+          <t>{"guid":"c353e286-8ef0-460a-b917-887f2aeb390a","nodeType":14,"position":{"x":1213.3333740234375,"y":-2354.66650390625},"targetType":1,"requiredTags":{"_tags":[]},"immunityTags":{"_tags":[]},"destroyWithNode":false,"positionSource":2,"positionBindingName":"head","textType":0,"fixedText":"","contextDataKey":"DamageResult","textColor":{"r":1.0,"g":0.0,"b":0.0,"a":1.0},"criticalColor":{"r":1.0,"g":0.5,"b":0.0,"a":1.0},"missColor":{"r":0.5,"g":0.5,"b":0.5,"a":1.0},"fontSize":5.0,"criticalFontSize":60.0,"duration":1.5,"offset":{"x":0.0,"y":0.0},"moveDirection":{"x":0.0,"y":1.0}}</t>
         </is>
       </c>
       <c r="G74"/>
@@ -2105,11 +2105,11 @@
       </c>
       <c r="D75"/>
       <c r="E75">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>{"guid":"c353e286-8ef0-460a-b917-887f2aeb390a","nodeType":14,"position":{"x":1677.3333740234375,"y":-2239.333251953125},"targetType":1,"requiredTags":{"_tags":[]},"immunityTags":{"_tags":[]},"destroyWithNode":false,"positionSource":2,"positionBindingName":"head","textType":0,"fixedText":"","contextDataKey":"DamageResult","textColor":{"r":1.0,"g":0.0,"b":0.0,"a":1.0},"criticalColor":{"r":1.0,"g":0.5,"b":0.0,"a":1.0},"missColor":{"r":0.5,"g":0.5,"b":0.5,"a":1.0},"fontSize":45.0,"criticalFontSize":60.0,"duration":1.5,"offset":{"x":0.0,"y":0.0},"moveDirection":{"x":0.0,"y":1.0}}</t>
+          <t>{"guid":"f8947676-1084-4228-b991-1509cc7fe851","nodeType":1,"position":{"x":1452.666748046875,"y":-2239.333251953125},"targetType":0,"assetTags":{"_tags":[]},"grantedTags":{"_tags":[]},"applicationRequiredTags":{"_tags":[]},"applicationImmunityTags":{"_tags":[]},"removeGameEffectsWithTags":{"_tags":[]},"durationType":0,"duration":"0","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"_tags":[]},"cancelOnAbilityEnd":true,"damageType":0,"damageSourceType":0,"damageFixedValue":10.0,"damageFormula":"","damageMMCType":0,"damageSetByCallerKey":"","damageMMCCaptureAttribute":200,"damageMMCAttributeSource":0,"damageMMCCoefficient":1.0,"damageMMCUseSnapshot":true,"damageMultiplyByStackCount":false,"damageCalculationType":0,"enableHitKnockback":false,"knockbackDistance":1.0,"knockbackSpeed":12.0}</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
@@ -2125,11 +2125,11 @@
       <c r="C76"/>
       <c r="D76"/>
       <c r="E76">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>{"guid":"f8947676-1084-4228-b991-1509cc7fe851","nodeType":1,"position":{"x":1452.666748046875,"y":-2239.333251953125},"targetType":0,"assetTags":{"_tags":[]},"grantedTags":{"_tags":[]},"applicationRequiredTags":{"_tags":[]},"applicationImmunityTags":{"_tags":[]},"removeGameEffectsWithTags":{"_tags":[]},"durationType":0,"duration":"0","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"_tags":[]},"cancelOnAbilityEnd":true,"damageType":0,"damageSourceType":0,"damageFixedValue":10.0,"damageFormula":"","damageMMCType":0,"damageSetByCallerKey":"","damageMMCCaptureAttribute":200,"damageMMCAttributeSource":0,"damageMMCCoefficient":1.0,"damageMMCUseSnapshot":true,"damageMultiplyByStackCount":false,"damageCalculationType":0,"enableHitKnockback":false,"knockbackDistance":1.0,"knockbackSpeed":12.0}</t>
+          <t>{"guid":"2cfdacd2-0186-49dd-b177-4eb8c0ad87bd","nodeType":7,"position":{"x":1052.666748046875,"y":-2551.333251953125},"targetType":1,"endType":0}</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
@@ -2145,11 +2145,11 @@
       <c r="C77"/>
       <c r="D77"/>
       <c r="E77">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>{"guid":"2cfdacd2-0186-49dd-b177-4eb8c0ad87bd","nodeType":7,"position":{"x":1052.666748046875,"y":-2551.333251953125},"targetType":1,"endType":0}</t>
+          <t>{"guid":"9d6f459d-b588-4b64-843b-1b71e8f299ae","nodeType":3,"position":{"x":-1144.0,"y":-2405.333251953125},"targetType":1,"assetTags":{"_tags":[]},"grantedTags":{"_tags":[]},"applicationRequiredTags":{"_tags":[]},"applicationImmunityTags":{"_tags":[]},"removeGameEffectsWithTags":{"_tags":[]},"durationType":0,"duration":"0","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[{"attrType":100,"operation":0,"magnitudeSourceType":0,"fixedValue":10.0,"formula":"","mmcType":0,"setByCallerKey":"","mmcCaptureAttribute":200,"mmcAttributeSource":0,"mmcCoefficient":1.0,"mmcUseSnapshot":true}],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"_tags":[]},"cancelOnAbilityEnd":true}</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
@@ -2165,11 +2165,11 @@
       <c r="C78"/>
       <c r="D78"/>
       <c r="E78">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>{"guid":"9d6f459d-b588-4b64-843b-1b71e8f299ae","nodeType":3,"position":{"x":-1144.0,"y":-2405.333251953125},"targetType":1,"assetTags":{"_tags":[]},"grantedTags":{"_tags":[]},"applicationRequiredTags":{"_tags":[]},"applicationImmunityTags":{"_tags":[]},"removeGameEffectsWithTags":{"_tags":[]},"durationType":0,"duration":"0","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[{"attrType":100,"operation":0,"magnitudeSourceType":0,"fixedValue":10.0,"formula":"","mmcType":0,"setByCallerKey":"","mmcCaptureAttribute":200,"mmcAttributeSource":0,"mmcCoefficient":1.0,"mmcUseSnapshot":true}],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"_tags":[]},"cancelOnAbilityEnd":true}</t>
+          <t>{"guid":"c28fb88d-51b1-47b2-be59-859e0ac638e3","nodeType":10,"position":{"x":-1067.3333740234375,"y":-2188.66650390625},"targetType":1,"assetTags":{"_tags":[]},"grantedTags":{"_tags":[{"_name":"CD.ThreeFire","_hashCode":960327319,"_shortName":"ThreeFire","_ancestorHashCodes":[-1137859925],"_ancestorNames":["CD"]}]},"applicationRequiredTags":{"_tags":[]},"applicationImmunityTags":{"_tags":[]},"removeGameEffectsWithTags":{"_tags":[]},"durationType":1,"duration":"1","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"_tags":[]},"cancelOnAbilityEnd":false,"cooldownType":0,"maxCharges":2,"chargeTime":"10"}</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
@@ -2185,11 +2185,11 @@
       <c r="C79"/>
       <c r="D79"/>
       <c r="E79">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>{"guid":"c28fb88d-51b1-47b2-be59-859e0ac638e3","nodeType":10,"position":{"x":-1067.3333740234375,"y":-2188.66650390625},"targetType":1,"assetTags":{"_tags":[]},"grantedTags":{"_tags":[{"_name":"CD.ThreeFire","_hashCode":960327319,"_shortName":"ThreeFire","_ancestorHashCodes":[-1137859925],"_ancestorNames":["CD"]}]},"applicationRequiredTags":{"_tags":[]},"applicationImmunityTags":{"_tags":[]},"removeGameEffectsWithTags":{"_tags":[]},"durationType":1,"duration":"1","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"_tags":[]},"cancelOnAbilityEnd":false,"cooldownType":0,"maxCharges":2,"chargeTime":"10"}</t>
+          <t>{"guid":"356907e0-1488-4128-bfcc-7ff73cfc3330","nodeType":0,"position":{"x":-746.6666259765625,"y":-2405.333251953125},"targetType":1,"skillId":1008,"assetTags":{"_tags":[]},"cancelAbilitiesWithTags":{"_tags":[]},"blockAbilitiesWithTags":{"_tags":[]},"activationOwnedTags":{"_tags":[]},"activationRequiredTags":{"_tags":[]},"activationBlockedTags":{"_tags":[{"_name":"CD.ThreeFire","_hashCode":960327319,"_shortName":"ThreeFire","_ancestorHashCodes":[-1137859925],"_ancestorNames":["CD"]}]},"ongoingBlockedTags":{"_tags":[]},"eventOutputPorts":[]}</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
@@ -2205,11 +2205,11 @@
       <c r="C80"/>
       <c r="D80"/>
       <c r="E80">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>{"guid":"356907e0-1488-4128-bfcc-7ff73cfc3330","nodeType":0,"position":{"x":-746.6666259765625,"y":-2405.333251953125},"targetType":1,"skillId":1008,"assetTags":{"_tags":[]},"cancelAbilitiesWithTags":{"_tags":[]},"blockAbilitiesWithTags":{"_tags":[]},"activationOwnedTags":{"_tags":[]},"activationRequiredTags":{"_tags":[]},"activationBlockedTags":{"_tags":[{"_name":"CD.ThreeFire","_hashCode":960327319,"_shortName":"ThreeFire","_ancestorHashCodes":[-1137859925],"_ancestorNames":["CD"]}]},"ongoingBlockedTags":{"_tags":[]},"eventOutputPorts":[]}</t>
+          <t>{"guid":"432ff1e3-b18d-476d-af80-d39ddc07402a","nodeType":20,"position":{"x":-238.66665649414063,"y":-2405.333251953125},"targetType":1,"skeletonDataAsset":null,"skeletonDataAssetPath":"Assets/Res/Spine/SP_Zhanshi/SP_Zhanshi_SkeletonData.asset","animationName":"Attack_01","animationDuration":"18","isAnimationLooping":false,"timeEffects":[{"triggerTime":7,"portIdValue":2315086,"legacyPortId":"de0ba361-3aba-4ef0-bb07-9b418fcae591"},{"triggerTime":18,"portIdValue":2649436,"legacyPortId":"84e238a8-5baf-470e-829f-186695064945"}],"timeCues":[]}</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
@@ -2225,11 +2225,11 @@
       <c r="C81"/>
       <c r="D81"/>
       <c r="E81">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>{"guid":"432ff1e3-b18d-476d-af80-d39ddc07402a","nodeType":20,"position":{"x":-238.66665649414063,"y":-2405.333251953125},"targetType":1,"skeletonDataAsset":null,"skeletonDataAssetPath":"Assets/Res/Spine/SP_Zhanshi/SP_Zhanshi_SkeletonData.asset","animationName":"Attack_01","animationDuration":"18","isAnimationLooping":false,"timeEffects":[{"triggerTime":7,"portIdValue":2315086,"legacyPortId":"de0ba361-3aba-4ef0-bb07-9b418fcae591"},{"triggerTime":18,"portIdValue":2649436,"legacyPortId":"84e238a8-5baf-470e-829f-186695064945"}],"timeCues":[]}</t>
+          <t>{"guid":"ce857360-de7e-4457-b348-9c124ce98879","nodeType":8,"position":{"x":1040.666748046875,"y":-2305.333251953125},"targetType":2,"assetTags":{"_tags":[]},"grantedTags":{"_tags":[]},"applicationRequiredTags":{"_tags":[]},"applicationImmunityTags":{"_tags":[]},"removeGameEffectsWithTags":{"_tags":[]},"durationType":2,"duration":"0","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"_tags":[]},"cancelOnAbilityEnd":false,"launchPositionSource":0,"launchBindingName":"center","targetPositionSource":1,"targetBindingName":"center","projectileTargetType":0,"flyOver":true,"offsetAngle":30.0,"curveHeight":0.0,"projectileEntityId":50002,"projectilePrefab":null,"projectilePrefabPath":"Assets/Res/Entity/Effect/ef_fashi_huoyandan01.prefab","speed":10.0,"maxDistance":10.0,"collisionRadius":0.5,"isPiercing":false,"maxPierceCount":1,"collisionTargetTags":{"_tags":[]},"collisionExcludeTags":{"_tags":[]},"isBouncing":false,"bounceTargetMode":0,"maxBounceCount":3,"bounceSearchRadius":10.0,"canBounceToSameTarget":false,"excludeSourceCamp":true,"bounceAngleOffset":0.0}</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
@@ -2249,7 +2249,7 @@
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>{"guid":"ce857360-de7e-4457-b348-9c124ce98879","nodeType":8,"position":{"x":1040.666748046875,"y":-2305.333251953125},"targetType":2,"assetTags":{"_tags":[]},"grantedTags":{"_tags":[]},"applicationRequiredTags":{"_tags":[]},"applicationImmunityTags":{"_tags":[]},"removeGameEffectsWithTags":{"_tags":[]},"durationType":2,"duration":"0","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"_tags":[]},"cancelOnAbilityEnd":false,"launchPositionSource":0,"launchBindingName":"center","targetPositionSource":1,"targetBindingName":"center","projectileTargetType":0,"flyOver":true,"offsetAngle":30.0,"curveHeight":0.0,"projectileEntityId":50002,"projectilePrefab":null,"projectilePrefabPath":"Assets/Res/Entity/Effect/ef_fashi_huoyandan01.prefab","speed":10.0,"maxDistance":10.0,"collisionRadius":0.5,"isPiercing":false,"maxPierceCount":1,"collisionTargetTags":{"_tags":[]},"collisionExcludeTags":{"_tags":[]},"isBouncing":false,"bounceTargetMode":0,"maxBounceCount":3,"bounceSearchRadius":10.0,"canBounceToSameTarget":false,"excludeSourceCamp":true,"bounceAngleOffset":0.0}</t>
+          <t>{"guid":"9a695e91-e218-425e-82ed-1e157bf1b014","nodeType":8,"position":{"x":1022.666748046875,"y":-2131.333251953125},"targetType":2,"assetTags":{"_tags":[]},"grantedTags":{"_tags":[]},"applicationRequiredTags":{"_tags":[]},"applicationImmunityTags":{"_tags":[]},"removeGameEffectsWithTags":{"_tags":[]},"durationType":2,"duration":"0","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"_tags":[]},"cancelOnAbilityEnd":false,"launchPositionSource":0,"launchBindingName":"center","targetPositionSource":1,"targetBindingName":"center","projectileTargetType":0,"flyOver":true,"offsetAngle":0.0,"curveHeight":0.0,"projectileEntityId":50002,"projectilePrefab":null,"projectilePrefabPath":"Assets/Res/Entity/Effect/ef_fashi_huoyandan01.prefab","speed":10.0,"maxDistance":10.0,"collisionRadius":0.5,"isPiercing":false,"maxPierceCount":1,"collisionTargetTags":{"_tags":[]},"collisionExcludeTags":{"_tags":[]},"isBouncing":false,"bounceTargetMode":0,"maxBounceCount":3,"bounceSearchRadius":10.0,"canBounceToSameTarget":false,"excludeSourceCamp":true,"bounceAngleOffset":0.0}</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
@@ -2269,7 +2269,7 @@
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>{"guid":"9a695e91-e218-425e-82ed-1e157bf1b014","nodeType":8,"position":{"x":1022.666748046875,"y":-2131.333251953125},"targetType":2,"assetTags":{"_tags":[]},"grantedTags":{"_tags":[]},"applicationRequiredTags":{"_tags":[]},"applicationImmunityTags":{"_tags":[]},"removeGameEffectsWithTags":{"_tags":[]},"durationType":2,"duration":"0","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"_tags":[]},"cancelOnAbilityEnd":false,"launchPositionSource":0,"launchBindingName":"center","targetPositionSource":1,"targetBindingName":"center","projectileTargetType":0,"flyOver":true,"offsetAngle":0.0,"curveHeight":0.0,"projectileEntityId":50002,"projectilePrefab":null,"projectilePrefabPath":"Assets/Res/Entity/Effect/ef_fashi_huoyandan01.prefab","speed":10.0,"maxDistance":10.0,"collisionRadius":0.5,"isPiercing":false,"maxPierceCount":1,"collisionTargetTags":{"_tags":[]},"collisionExcludeTags":{"_tags":[]},"isBouncing":false,"bounceTargetMode":0,"maxBounceCount":3,"bounceSearchRadius":10.0,"canBounceToSameTarget":false,"excludeSourceCamp":true,"bounceAngleOffset":0.0}</t>
+          <t>{"guid":"d897a922-5756-42cf-ac65-90a48c1e5a17","nodeType":8,"position":{"x":1022.666748046875,"y":-1951.3333740234375},"targetType":2,"assetTags":{"_tags":[]},"grantedTags":{"_tags":[]},"applicationRequiredTags":{"_tags":[]},"applicationImmunityTags":{"_tags":[]},"removeGameEffectsWithTags":{"_tags":[]},"durationType":2,"duration":"0","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"_tags":[]},"cancelOnAbilityEnd":false,"launchPositionSource":0,"launchBindingName":"center","targetPositionSource":1,"targetBindingName":"center","projectileTargetType":0,"flyOver":true,"offsetAngle":-30.0,"curveHeight":0.0,"projectileEntityId":50002,"projectilePrefab":null,"projectilePrefabPath":"Assets/Res/Entity/Effect/ef_fashi_huoyandan01.prefab","speed":10.0,"maxDistance":10.0,"collisionRadius":0.5,"isPiercing":false,"maxPierceCount":1,"collisionTargetTags":{"_tags":[]},"collisionExcludeTags":{"_tags":[]},"isBouncing":false,"bounceTargetMode":0,"maxBounceCount":3,"bounceSearchRadius":10.0,"canBounceToSameTarget":false,"excludeSourceCamp":true,"bounceAngleOffset":0.0}</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
@@ -2285,11 +2285,11 @@
       <c r="C84"/>
       <c r="D84"/>
       <c r="E84">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>{"guid":"d897a922-5756-42cf-ac65-90a48c1e5a17","nodeType":8,"position":{"x":1022.666748046875,"y":-1951.3333740234375},"targetType":2,"assetTags":{"_tags":[]},"grantedTags":{"_tags":[]},"applicationRequiredTags":{"_tags":[]},"applicationImmunityTags":{"_tags":[]},"removeGameEffectsWithTags":{"_tags":[]},"durationType":2,"duration":"0","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"_tags":[]},"cancelOnAbilityEnd":false,"launchPositionSource":0,"launchBindingName":"center","targetPositionSource":1,"targetBindingName":"center","projectileTargetType":0,"flyOver":true,"offsetAngle":-30.0,"curveHeight":0.0,"projectileEntityId":50002,"projectilePrefab":null,"projectilePrefabPath":"Assets/Res/Entity/Effect/ef_fashi_huoyandan01.prefab","speed":10.0,"maxDistance":10.0,"collisionRadius":0.5,"isPiercing":false,"maxPierceCount":1,"collisionTargetTags":{"_tags":[]},"collisionExcludeTags":{"_tags":[]},"isBouncing":false,"bounceTargetMode":0,"maxBounceCount":3,"bounceSearchRadius":10.0,"canBounceToSameTarget":false,"excludeSourceCamp":true,"bounceAngleOffset":0.0}</t>
+          <t>{"guid":"c353e286-8ef0-460a-b917-887f2aeb390a","nodeType":14,"position":{"x":1677.3333740234375,"y":-2239.333251953125},"targetType":1,"requiredTags":{"_tags":[]},"immunityTags":{"_tags":[]},"destroyWithNode":false,"positionSource":2,"positionBindingName":"head","textType":0,"fixedText":"","contextDataKey":"DamageResult","textColor":{"r":1.0,"g":0.0,"b":0.0,"a":1.0},"criticalColor":{"r":1.0,"g":0.5,"b":0.0,"a":1.0},"missColor":{"r":0.5,"g":0.5,"b":0.5,"a":1.0},"fontSize":5.0,"criticalFontSize":60.0,"duration":1.5,"offset":{"x":0.0,"y":0.0},"moveDirection":{"x":0.0,"y":1.0}}</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
@@ -2511,7 +2511,7 @@
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>{"guid":"764289ea-065e-4f48-afc0-0f6963d18d57","nodeType":14,"position":{"x":492.00003051757813,"y":-1539.3333740234375},"targetType":1,"requiredTags":{"_tags":[]},"immunityTags":{"_tags":[]},"destroyWithNode":false,"positionSource":2,"positionBindingName":"head","textType":0,"fixedText":"","contextDataKey":"DamageResult","textColor":{"r":1.0,"g":0.0,"b":0.0,"a":1.0},"criticalColor":{"r":1.0,"g":0.5,"b":0.0,"a":1.0},"missColor":{"r":0.5,"g":0.5,"b":0.5,"a":1.0},"fontSize":45.0,"criticalFontSize":60.0,"duration":1.5,"offset":{"x":0.0,"y":0.0},"moveDirection":{"x":0.0,"y":1.0}}</t>
+          <t>{"guid":"764289ea-065e-4f48-afc0-0f6963d18d57","nodeType":14,"position":{"x":492.00003051757813,"y":-1539.3333740234375},"targetType":1,"requiredTags":{"_tags":[]},"immunityTags":{"_tags":[]},"destroyWithNode":false,"positionSource":2,"positionBindingName":"head","textType":0,"fixedText":"","contextDataKey":"DamageResult","textColor":{"r":1.0,"g":0.0,"b":0.0,"a":1.0},"criticalColor":{"r":1.0,"g":0.5,"b":0.0,"a":1.0},"missColor":{"r":0.5,"g":0.5,"b":0.5,"a":1.0},"fontSize":5.0,"criticalFontSize":60.0,"duration":1.5,"offset":{"x":0.0,"y":0.0},"moveDirection":{"x":0.0,"y":1.0}}</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">

--- a/Design/Excel/ET/Datas/Game/SkillGraph.xlsx
+++ b/Design/Excel/ET/Datas/Game/SkillGraph.xlsx
@@ -691,7 +691,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>{"guid":"426755b7-c39a-4524-9cb5-960a31a19c10","nodeType":11,"position":{"x":587.3333740234375,"y":114.66667175292969},"targetType":1,"assetTags":{"_tags":[]},"grantedTags":{"_tags":[]},"applicationRequiredTags":{"_tags":[]},"applicationImmunityTags":{"_tags":[]},"removeGameEffectsWithTags":{"_tags":[]},"durationType":2,"duration":"10","isPeriodic":true,"period":"1","executeOnApplication":false,"attributeModifiers":[],"stackType":1,"stackLimit":1,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"_tags":[{"_name":"CD.BeRecBlood","_hashCode":-1099994396,"_shortName":"被动回血","_ancestorHashCodes":[-1137859925],"_ancestorNames":["CD"]}]},"cancelOnAbilityEnd":true,"buffId":0}</t>
+          <t>{"guid":"426755b7-c39a-4524-9cb5-960a31a19c10","nodeType":11,"position":{"x":587.3333740234375,"y":114.66667175292969},"targetType":1,"assetTags":{"Tags":[]},"grantedTags":{"Tags":[]},"applicationRequiredTags":{"Tags":[]},"applicationImmunityTags":{"Tags":[]},"removeGameEffectsWithTags":{"Tags":[]},"durationType":2,"duration":"10","isPeriodic":true,"period":"1","executeOnApplication":false,"attributeModifiers":[],"stackType":1,"stackLimit":1,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"Tags":[{"Name":"CD.BeRecBlood","HashCode":-1099994396,"ShortName":"被动回血","AncestorHashCodes":[-1137859925],"AncestorNames":["CD"]}]},"cancelOnAbilityEnd":true,"buffId":0}</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -711,7 +711,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>{"guid":"d5809887-df6e-4604-bd09-36cef191ce83","nodeType":0,"position":{"x":113.33334350585938,"y":158.66667175292969},"targetType":1,"skillId":2001,"assetTags":{"_tags":[]},"cancelAbilitiesWithTags":{"_tags":[]},"blockAbilitiesWithTags":{"_tags":[]},"activationOwnedTags":{"_tags":[]},"activationRequiredTags":{"_tags":[]},"activationBlockedTags":{"_tags":[]},"ongoingBlockedTags":{"_tags":[]},"eventOutputPorts":[{"eventType":2,"customEventTag":"","PortId":1103}]}</t>
+          <t>{"guid":"d5809887-df6e-4604-bd09-36cef191ce83","nodeType":0,"position":{"x":113.33334350585938,"y":158.66667175292969},"targetType":1,"skillId":2001,"assetTags":{"Tags":[]},"cancelAbilitiesWithTags":{"Tags":[]},"blockAbilitiesWithTags":{"Tags":[]},"activationOwnedTags":{"Tags":[]},"activationRequiredTags":{"Tags":[]},"activationBlockedTags":{"Tags":[]},"ongoingBlockedTags":{"Tags":[]},"eventOutputPorts":[{"eventType":2,"customEventTag":"","PortId":1103}]}</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -731,7 +731,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>{"guid":"7eefd9ae-c57e-439d-b1b6-e7f4e52f2f6f","nodeType":10,"position":{"x":370.66665649414063,"y":484.66665649414063},"targetType":1,"assetTags":{"_tags":[]},"grantedTags":{"_tags":[{"_name":"CD.BeRecBlood","_hashCode":-1099994396,"_shortName":"被动回血","_ancestorHashCodes":[-1137859925],"_ancestorNames":["CD"]}]},"applicationRequiredTags":{"_tags":[]},"applicationImmunityTags":{"_tags":[]},"removeGameEffectsWithTags":{"_tags":[]},"durationType":1,"duration":"3","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"_tags":[]},"cancelOnAbilityEnd":false,"cooldownType":0,"maxCharges":2,"chargeTime":"10"}</t>
+          <t>{"guid":"7eefd9ae-c57e-439d-b1b6-e7f4e52f2f6f","nodeType":10,"position":{"x":370.66665649414063,"y":484.66665649414063},"targetType":1,"assetTags":{"Tags":[]},"grantedTags":{"Tags":[{"Name":"CD.BeRecBlood","HashCode":-1099994396,"ShortName":"被动回血","AncestorHashCodes":[-1137859925],"AncestorNames":["CD"]}]},"applicationRequiredTags":{"Tags":[]},"applicationImmunityTags":{"Tags":[]},"removeGameEffectsWithTags":{"Tags":[]},"durationType":1,"duration":"3","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"Tags":[]},"cancelOnAbilityEnd":false,"cooldownType":0,"maxCharges":2,"chargeTime":"10"}</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -751,7 +751,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>{"guid":"a8c2d6c0-65f1-4bed-8a6a-70197e84bb56","nodeType":2,"position":{"x":933.3333740234375,"y":226.66667175292969},"targetType":1,"assetTags":{"_tags":[]},"grantedTags":{"_tags":[]},"applicationRequiredTags":{"_tags":[]},"applicationImmunityTags":{"_tags":[]},"removeGameEffectsWithTags":{"_tags":[]},"durationType":0,"duration":"0","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"_tags":[]},"cancelOnAbilityEnd":false,"healSourceType":0,"healFixedValue":2.0,"healFormula":"","healMMCType":0,"healSetByCallerKey":"","healMMCCaptureAttribute":202,"healMMCAttributeSource":0,"healMMCCoefficient":1.0,"healMMCUseSnapshot":true,"healMultiplyByStackCount":false,"healCalculationType":0}</t>
+          <t>{"guid":"a8c2d6c0-65f1-4bed-8a6a-70197e84bb56","nodeType":2,"position":{"x":933.3333740234375,"y":226.66667175292969},"targetType":1,"assetTags":{"Tags":[]},"grantedTags":{"Tags":[]},"applicationRequiredTags":{"Tags":[]},"applicationImmunityTags":{"Tags":[]},"removeGameEffectsWithTags":{"Tags":[]},"durationType":0,"duration":"0","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"Tags":[]},"cancelOnAbilityEnd":false,"healSourceType":0,"healFixedValue":2.0,"healFormula":"","healMMCType":0,"healSetByCallerKey":"","healMMCCaptureAttribute":202,"healMMCAttributeSource":0,"healMMCCoefficient":1.0,"healMMCUseSnapshot":true,"healMultiplyByStackCount":false,"healCalculationType":0}</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -771,7 +771,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>{"guid":"d086a8c9-8557-4a61-8fd2-64b3c1e543a3","nodeType":14,"position":{"x":1148.666748046875,"y":206.66667175292969},"targetType":1,"requiredTags":{"_tags":[]},"immunityTags":{"_tags":[]},"destroyWithNode":false,"positionSource":0,"positionBindingName":"head","textType":1,"fixedText":"","contextDataKey":"Heal","textColor":{"r":0.040635824203491211,"g":1.0,"b":0.0,"a":1.0},"criticalColor":{"r":1.0,"g":0.5,"b":0.0,"a":1.0},"missColor":{"r":0.5,"g":0.5,"b":0.5,"a":1.0},"fontSize":5.0,"criticalFontSize":60.0,"duration":1.5,"offset":{"x":0.0,"y":0.0},"moveDirection":{"x":0.0,"y":1.0}}</t>
+          <t>{"guid":"d086a8c9-8557-4a61-8fd2-64b3c1e543a3","nodeType":14,"position":{"x":1148.666748046875,"y":206.66667175292969},"targetType":1,"requiredTags":{"Tags":[]},"immunityTags":{"Tags":[]},"destroyWithNode":false,"positionSource":0,"positionBindingName":"head","textType":1,"fixedText":"","contextDataKey":"Heal","textColor":{"r":0.040635824203491211,"g":1.0,"b":0.0,"a":1.0},"criticalColor":{"r":1.0,"g":0.5,"b":0.0,"a":1.0},"missColor":{"r":0.5,"g":0.5,"b":0.5,"a":1.0},"fontSize":5.0,"criticalFontSize":60.0,"duration":1.5,"offset":{"x":0.0,"y":0.0},"moveDirection":{"x":0.0,"y":1.0}}</t>
         </is>
       </c>
       <c r="G9"/>
@@ -793,7 +793,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>{"guid":"9d6f459d-b588-4b64-843b-1b71e8f299ae","nodeType":3,"position":{"x":-1186.6666259765625,"y":-2019.3333740234375},"targetType":1,"assetTags":{"_tags":[]},"grantedTags":{"_tags":[]},"applicationRequiredTags":{"_tags":[]},"applicationImmunityTags":{"_tags":[]},"removeGameEffectsWithTags":{"_tags":[]},"durationType":0,"duration":"0","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[{"attrType":100,"operation":0,"magnitudeSourceType":0,"fixedValue":10.0,"formula":"","mmcType":0,"setByCallerKey":"","mmcCaptureAttribute":200,"mmcAttributeSource":0,"mmcCoefficient":1.0,"mmcUseSnapshot":true}],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"_tags":[]},"cancelOnAbilityEnd":true}</t>
+          <t>{"guid":"9d6f459d-b588-4b64-843b-1b71e8f299ae","nodeType":3,"position":{"x":-1186.6666259765625,"y":-2019.3333740234375},"targetType":1,"assetTags":{"Tags":[]},"grantedTags":{"Tags":[]},"applicationRequiredTags":{"Tags":[]},"applicationImmunityTags":{"Tags":[]},"removeGameEffectsWithTags":{"Tags":[]},"durationType":0,"duration":"0","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[{"attrType":100,"operation":0,"magnitudeSourceType":0,"fixedValue":10.0,"formula":"","mmcType":0,"setByCallerKey":"","mmcCaptureAttribute":200,"mmcAttributeSource":0,"mmcCoefficient":1.0,"mmcUseSnapshot":true}],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"Tags":[]},"cancelOnAbilityEnd":true}</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -813,7 +813,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>{"guid":"c28fb88d-51b1-47b2-be59-859e0ac638e3","nodeType":10,"position":{"x":-1186.6666259765625,"y":-1825.3333740234375},"targetType":1,"assetTags":{"_tags":[]},"grantedTags":{"_tags":[{"_name":"CD.Blood","_hashCode":274000851,"_shortName":"Blood","_ancestorHashCodes":[-1137859925],"_ancestorNames":["CD"]}]},"applicationRequiredTags":{"_tags":[]},"applicationImmunityTags":{"_tags":[]},"removeGameEffectsWithTags":{"_tags":[]},"durationType":1,"duration":"3","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"_tags":[]},"cancelOnAbilityEnd":false,"cooldownType":0,"maxCharges":2,"chargeTime":"10"}</t>
+          <t>{"guid":"c28fb88d-51b1-47b2-be59-859e0ac638e3","nodeType":10,"position":{"x":-1186.6666259765625,"y":-1825.3333740234375},"targetType":1,"assetTags":{"Tags":[]},"grantedTags":{"Tags":[{"Name":"CD.Blood","HashCode":274000851,"ShortName":"Blood","AncestorHashCodes":[-1137859925],"AncestorNames":["CD"]}]},"applicationRequiredTags":{"Tags":[]},"applicationImmunityTags":{"Tags":[]},"removeGameEffectsWithTags":{"Tags":[]},"durationType":1,"duration":"3","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"Tags":[]},"cancelOnAbilityEnd":false,"cooldownType":0,"maxCharges":2,"chargeTime":"10"}</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -833,7 +833,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>{"guid":"c353e286-8ef0-460a-b917-887f2aeb390a","nodeType":14,"position":{"x":383.33334350585938,"y":-1531.3333740234375},"targetType":1,"requiredTags":{"_tags":[]},"immunityTags":{"_tags":[]},"destroyWithNode":false,"positionSource":2,"positionBindingName":"head","textType":0,"fixedText":"","contextDataKey":"DamageResult","textColor":{"r":1.0,"g":0.0,"b":0.0,"a":1.0},"criticalColor":{"r":1.0,"g":0.5,"b":0.0,"a":1.0},"missColor":{"r":0.5,"g":0.5,"b":0.5,"a":1.0},"fontSize":5.0,"criticalFontSize":60.0,"duration":1.5,"offset":{"x":0.0,"y":0.0},"moveDirection":{"x":0.0,"y":1.0}}</t>
+          <t>{"guid":"c353e286-8ef0-460a-b917-887f2aeb390a","nodeType":14,"position":{"x":383.33334350585938,"y":-1531.3333740234375},"targetType":1,"requiredTags":{"Tags":[]},"immunityTags":{"Tags":[]},"destroyWithNode":false,"positionSource":2,"positionBindingName":"head","textType":0,"fixedText":"","contextDataKey":"DamageResult","textColor":{"r":1.0,"g":0.0,"b":0.0,"a":1.0},"criticalColor":{"r":1.0,"g":0.5,"b":0.0,"a":1.0},"missColor":{"r":0.5,"g":0.5,"b":0.5,"a":1.0},"fontSize":5.0,"criticalFontSize":60.0,"duration":1.5,"offset":{"x":0.0,"y":0.0},"moveDirection":{"x":0.0,"y":1.0}}</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -893,7 +893,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>{"guid":"356907e0-1488-4128-bfcc-7ff73cfc3330","nodeType":0,"position":{"x":-878.6666259765625,"y":-1853.3333740234375},"targetType":1,"skillId":1002,"assetTags":{"_tags":[]},"cancelAbilitiesWithTags":{"_tags":[]},"blockAbilitiesWithTags":{"_tags":[]},"activationOwnedTags":{"_tags":[{"_name":"Skill.Running","_hashCode":-51601538,"_shortName":"Running","_ancestorHashCodes":[1312877309],"_ancestorNames":["Skill"]}]},"activationRequiredTags":{"_tags":[]},"activationBlockedTags":{"_tags":[{"_name":"CD.Blood","_hashCode":274000851,"_shortName":"Blood","_ancestorHashCodes":[-1137859925],"_ancestorNames":["CD"]},{"_name":"Skill.Running","_hashCode":-51601538,"_shortName":"Running","_ancestorHashCodes":[1312877309],"_ancestorNames":["Skill"]}]},"ongoingBlockedTags":{"_tags":[]},"eventOutputPorts":[]}</t>
+          <t>{"guid":"356907e0-1488-4128-bfcc-7ff73cfc3330","nodeType":0,"position":{"x":-878.6666259765625,"y":-1853.3333740234375},"targetType":1,"skillId":1002,"assetTags":{"Tags":[]},"cancelAbilitiesWithTags":{"Tags":[]},"blockAbilitiesWithTags":{"Tags":[]},"activationOwnedTags":{"Tags":[{"Name":"Skill.Running","HashCode":-51601538,"ShortName":"Running","AncestorHashCodes":[1312877309],"AncestorNames":["Skill"]}]},"activationRequiredTags":{"Tags":[]},"activationBlockedTags":{"Tags":[{"Name":"CD.Blood","HashCode":274000851,"ShortName":"Blood","AncestorHashCodes":[-1137859925],"AncestorNames":["CD"]},{"Name":"Skill.Running","HashCode":-51601538,"ShortName":"Running","AncestorHashCodes":[1312877309],"AncestorNames":["Skill"]}]},"ongoingBlockedTags":{"Tags":[]},"eventOutputPorts":[]}</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -913,7 +913,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>{"guid":"cb1df36f-5729-423e-9d1a-287db5a433f0","nodeType":11,"position":{"x":-160.66665649414063,"y":-1761.3333740234375},"targetType":0,"assetTags":{"_tags":[{"_name":"Buff.DeBuff.Dot","_hashCode":-637848644,"_shortName":"Dot","_ancestorHashCodes":[937056111,321157895],"_ancestorNames":["Buff","Buff.DeBuff"]}]},"grantedTags":{"_tags":[]},"applicationRequiredTags":{"_tags":[]},"applicationImmunityTags":{"_tags":[]},"removeGameEffectsWithTags":{"_tags":[]},"durationType":1,"duration":"10","isPeriodic":true,"period":"1","executeOnApplication":false,"attributeModifiers":[],"stackType":1,"stackLimit":3,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":1,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"_tags":[]},"cancelOnAbilityEnd":false,"buffId":0}</t>
+          <t>{"guid":"cb1df36f-5729-423e-9d1a-287db5a433f0","nodeType":11,"position":{"x":-160.66665649414063,"y":-1761.3333740234375},"targetType":0,"assetTags":{"Tags":[{"Name":"Buff.DeBuff.Dot","HashCode":-637848644,"ShortName":"Dot","AncestorHashCodes":[937056111,321157895],"AncestorNames":["Buff","Buff.DeBuff"]}]},"grantedTags":{"Tags":[]},"applicationRequiredTags":{"Tags":[]},"applicationImmunityTags":{"Tags":[]},"removeGameEffectsWithTags":{"Tags":[]},"durationType":1,"duration":"10","isPeriodic":true,"period":"1","executeOnApplication":false,"attributeModifiers":[],"stackType":1,"stackLimit":3,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":1,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"Tags":[]},"cancelOnAbilityEnd":false,"buffId":0}</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -933,7 +933,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>{"guid":"e33ab94c-1496-4d6a-ba5e-1afd38bb0c30","nodeType":4,"position":{"x":-452.66665649414063,"y":-1786.666748046875},"targetType":1,"searchShapeType":1,"searchLineType":0,"positionSource":0,"positionBindingName":"center","searchCircleRadius":5.0,"searchSectorRadius":5.0,"searchSectorAngle":180.0,"searchLineDirectionOffsetAngle":0.0,"searchLineDirectionWidth":1.0,"searchLineDirectionLength":10.0,"lineStartPositionSource":0,"lineStartBindingName":"","lineEndPositionSource":1,"lineEndBindingName":"","searchLineBetweenWidth":1.0,"searchLineAbsoluteAngle":0.0,"searchLineAbsoluteWidth":1.0,"searchLineAbsoluteLength":10.0,"maxTargets":999,"searchTargetTags":{"_tags":[{"_name":"unitType.monster","_hashCode":-2021655864,"_shortName":"monster","_ancestorHashCodes":[1600484460],"_ancestorNames":["unitType"]}]},"searchExcludeTags":{"_tags":[]}}</t>
+          <t>{"guid":"e33ab94c-1496-4d6a-ba5e-1afd38bb0c30","nodeType":4,"position":{"x":-452.66665649414063,"y":-1786.666748046875},"targetType":1,"searchShapeType":1,"searchLineType":0,"positionSource":0,"positionBindingName":"center","searchCircleRadius":5.0,"searchSectorRadius":5.0,"searchSectorAngle":180.0,"searchLineDirectionOffsetAngle":0.0,"searchLineDirectionWidth":1.0,"searchLineDirectionLength":10.0,"lineStartPositionSource":0,"lineStartBindingName":"","lineEndPositionSource":1,"lineEndBindingName":"","searchLineBetweenWidth":1.0,"searchLineAbsoluteAngle":0.0,"searchLineAbsoluteWidth":1.0,"searchLineAbsoluteLength":10.0,"maxTargets":999,"searchTargetTags":{"Tags":[{"Name":"unitType.monster","HashCode":-2021655864,"ShortName":"monster","AncestorHashCodes":[1600484460],"AncestorNames":["unitType"]}]},"searchExcludeTags":{"Tags":[]}}</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -953,7 +953,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>{"guid":"f8947676-1084-4228-b991-1509cc7fe851","nodeType":1,"position":{"x":195.33334350585938,"y":-1761.3333740234375},"targetType":0,"assetTags":{"_tags":[]},"grantedTags":{"_tags":[]},"applicationRequiredTags":{"_tags":[]},"applicationImmunityTags":{"_tags":[]},"removeGameEffectsWithTags":{"_tags":[]},"durationType":0,"duration":"0","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"_tags":[]},"cancelOnAbilityEnd":true,"damageType":0,"damageSourceType":0,"damageFixedValue":20.0,"damageFormula":"","damageMMCType":0,"damageSetByCallerKey":"","damageMMCCaptureAttribute":200,"damageMMCAttributeSource":0,"damageMMCCoefficient":1.0,"damageMMCUseSnapshot":true,"damageMultiplyByStackCount":true,"damageCalculationType":0,"enableHitKnockback":false,"knockbackDistance":1.0,"knockbackSpeed":12.0}</t>
+          <t>{"guid":"f8947676-1084-4228-b991-1509cc7fe851","nodeType":1,"position":{"x":195.33334350585938,"y":-1761.3333740234375},"targetType":0,"assetTags":{"Tags":[]},"grantedTags":{"Tags":[]},"applicationRequiredTags":{"Tags":[]},"applicationImmunityTags":{"Tags":[]},"removeGameEffectsWithTags":{"Tags":[]},"durationType":0,"duration":"0","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"Tags":[]},"cancelOnAbilityEnd":true,"damageType":0,"damageSourceType":0,"damageFixedValue":20.0,"damageFormula":"","damageMMCType":0,"damageSetByCallerKey":"","damageMMCCaptureAttribute":200,"damageMMCAttributeSource":0,"damageMMCCoefficient":1.0,"damageMMCUseSnapshot":true,"damageMultiplyByStackCount":true,"damageCalculationType":0,"enableHitKnockback":false,"knockbackDistance":1.0,"knockbackSpeed":12.0}</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -973,7 +973,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>{"guid":"cde57fb8-b693-4da8-a4a8-fd61e56c5dcd","nodeType":12,"position":{"x":677.3333740234375,"y":-1998.666748046875},"targetType":1,"requiredTags":{"_tags":[]},"immunityTags":{"_tags":[]},"destroyWithNode":false,"positionSource":0,"particleEntityId":50006,"particlePrefab":null,"particlePrefabPath":"Assets/Res/Entity/Effect/ef_Zhanshi_attack_02.prefab","particleBindingName":"down","particleOffset":{"x":5.0,"y":0.0,"z":0.0},"particleScale":{"x":1.0,"y":1.0,"z":1.0},"attachToTarget":false,"particleLoop":false}</t>
+          <t>{"guid":"cde57fb8-b693-4da8-a4a8-fd61e56c5dcd","nodeType":12,"position":{"x":677.3333740234375,"y":-1998.666748046875},"targetType":1,"requiredTags":{"Tags":[]},"immunityTags":{"Tags":[]},"destroyWithNode":false,"positionSource":0,"particleEntityId":50006,"particlePrefab":null,"particlePrefabPath":"Assets/Res/Entity/Effect/ef_Zhanshi_attack_02.prefab","particleBindingName":"down","particleOffset":{"x":5.0,"y":0.0,"z":0.0},"particleScale":{"x":1.0,"y":1.0,"z":1.0},"attachToTarget":false,"particleLoop":false}</t>
         </is>
       </c>
       <c r="G19"/>
@@ -1035,7 +1035,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>{"guid":"c28fb88d-51b1-47b2-be59-859e0ac638e3","nodeType":10,"position":{"x":-1220.6666259765625,"y":-1747.3333740234375},"targetType":1,"assetTags":{"_tags":[]},"grantedTags":{"_tags":[{"_name":"CD.FireCircle","_hashCode":522143731,"_shortName":"FireCircle","_ancestorHashCodes":[-1137859925],"_ancestorNames":["CD"]}]},"applicationRequiredTags":{"_tags":[]},"applicationImmunityTags":{"_tags":[]},"removeGameEffectsWithTags":{"_tags":[]},"durationType":1,"duration":"3","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"_tags":[]},"cancelOnAbilityEnd":false,"cooldownType":0,"maxCharges":2,"chargeTime":"10"}</t>
+          <t>{"guid":"c28fb88d-51b1-47b2-be59-859e0ac638e3","nodeType":10,"position":{"x":-1220.6666259765625,"y":-1747.3333740234375},"targetType":1,"assetTags":{"Tags":[]},"grantedTags":{"Tags":[{"Name":"CD.FireCircle","HashCode":522143731,"ShortName":"FireCircle","AncestorHashCodes":[-1137859925],"AncestorNames":["CD"]}]},"applicationRequiredTags":{"Tags":[]},"applicationImmunityTags":{"Tags":[]},"removeGameEffectsWithTags":{"Tags":[]},"durationType":1,"duration":"3","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"Tags":[]},"cancelOnAbilityEnd":false,"cooldownType":0,"maxCharges":2,"chargeTime":"10"}</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -1055,7 +1055,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>{"guid":"9d6f459d-b588-4b64-843b-1b71e8f299ae","nodeType":3,"position":{"x":-1195.3333740234375,"y":-2003.3333740234375},"targetType":1,"assetTags":{"_tags":[]},"grantedTags":{"_tags":[]},"applicationRequiredTags":{"_tags":[]},"applicationImmunityTags":{"_tags":[]},"removeGameEffectsWithTags":{"_tags":[]},"durationType":0,"duration":"0","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[{"attrType":1003,"operation":0,"magnitudeSourceType":0,"fixedValue":-100.0,"formula":"","mmcType":0,"setByCallerKey":"","mmcCaptureAttribute":200,"mmcAttributeSource":0,"mmcCoefficient":1.0,"mmcUseSnapshot":true}],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"_tags":[]},"cancelOnAbilityEnd":true}</t>
+          <t>{"guid":"9d6f459d-b588-4b64-843b-1b71e8f299ae","nodeType":3,"position":{"x":-1195.3333740234375,"y":-2003.3333740234375},"targetType":1,"assetTags":{"Tags":[]},"grantedTags":{"Tags":[]},"applicationRequiredTags":{"Tags":[]},"applicationImmunityTags":{"Tags":[]},"removeGameEffectsWithTags":{"Tags":[]},"durationType":0,"duration":"0","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[{"attrType":1003,"operation":0,"magnitudeSourceType":0,"fixedValue":-100.0,"formula":"","mmcType":0,"setByCallerKey":"","mmcCaptureAttribute":200,"mmcAttributeSource":0,"mmcCoefficient":1.0,"mmcUseSnapshot":true}],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"Tags":[]},"cancelOnAbilityEnd":true}</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -1075,7 +1075,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>{"guid":"eae41233-d297-46fe-a6c8-0b5c876fbb2a","nodeType":1,"position":{"x":-97.333328247070313,"y":-1810.0},"targetType":0,"assetTags":{"_tags":[]},"grantedTags":{"_tags":[]},"applicationRequiredTags":{"_tags":[]},"applicationImmunityTags":{"_tags":[]},"removeGameEffectsWithTags":{"_tags":[]},"durationType":0,"duration":"0","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"_tags":[]},"cancelOnAbilityEnd":true,"damageType":0,"damageSourceType":0,"damageFixedValue":10.0,"damageFormula":"","damageMMCType":0,"damageSetByCallerKey":"","damageMMCCaptureAttribute":200,"damageMMCAttributeSource":0,"damageMMCCoefficient":1.0,"damageMMCUseSnapshot":true,"damageMultiplyByStackCount":false,"damageCalculationType":0,"enableHitKnockback":true,"knockbackDistance":1.0,"knockbackSpeed":12.0}</t>
+          <t>{"guid":"eae41233-d297-46fe-a6c8-0b5c876fbb2a","nodeType":1,"position":{"x":-97.333328247070313,"y":-1810.0},"targetType":0,"assetTags":{"Tags":[]},"grantedTags":{"Tags":[]},"applicationRequiredTags":{"Tags":[]},"applicationImmunityTags":{"Tags":[]},"removeGameEffectsWithTags":{"Tags":[]},"durationType":0,"duration":"0","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"Tags":[]},"cancelOnAbilityEnd":true,"damageType":0,"damageSourceType":0,"damageFixedValue":10.0,"damageFormula":"","damageMMCType":0,"damageSetByCallerKey":"","damageMMCCaptureAttribute":200,"damageMMCAttributeSource":0,"damageMMCCoefficient":1.0,"damageMMCUseSnapshot":true,"damageMultiplyByStackCount":false,"damageCalculationType":0,"enableHitKnockback":true,"knockbackDistance":1.0,"knockbackSpeed":12.0}</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -1095,7 +1095,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>{"guid":"356907e0-1488-4128-bfcc-7ff73cfc3330","nodeType":0,"position":{"x":-881.3333740234375,"y":-1854.666748046875},"targetType":1,"skillId":7001,"assetTags":{"_tags":[]},"cancelAbilitiesWithTags":{"_tags":[]},"blockAbilitiesWithTags":{"_tags":[]},"activationOwnedTags":{"_tags":[]},"activationRequiredTags":{"_tags":[]},"activationBlockedTags":{"_tags":[{"_name":"CD.FireCircle","_hashCode":522143731,"_shortName":"FireCircle","_ancestorHashCodes":[-1137859925],"_ancestorNames":["CD"]}]},"ongoingBlockedTags":{"_tags":[{"_name":"Buff.DeBuff.Stun","_hashCode":1791562953,"_shortName":"Stun","_ancestorHashCodes":[937056111,321157895],"_ancestorNames":["Buff","Buff.DeBuff"]}]},"eventOutputPorts":[]}</t>
+          <t>{"guid":"356907e0-1488-4128-bfcc-7ff73cfc3330","nodeType":0,"position":{"x":-881.3333740234375,"y":-1854.666748046875},"targetType":1,"skillId":7001,"assetTags":{"Tags":[]},"cancelAbilitiesWithTags":{"Tags":[]},"blockAbilitiesWithTags":{"Tags":[]},"activationOwnedTags":{"Tags":[]},"activationRequiredTags":{"Tags":[]},"activationBlockedTags":{"Tags":[{"Name":"CD.FireCircle","HashCode":522143731,"ShortName":"FireCircle","AncestorHashCodes":[-1137859925],"AncestorNames":["CD"]}]},"ongoingBlockedTags":{"Tags":[{"Name":"Buff.DeBuff.Stun","HashCode":1791562953,"ShortName":"Stun","AncestorHashCodes":[937056111,321157895],"AncestorNames":["Buff","Buff.DeBuff"]}]},"eventOutputPorts":[]}</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -1115,7 +1115,7 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>{"guid":"90bacd9f-d882-4bba-aaa8-41ed993ac3ff","nodeType":8,"position":{"x":-419.33331298828125,"y":-1840.0},"targetType":2,"assetTags":{"_tags":[]},"grantedTags":{"_tags":[]},"applicationRequiredTags":{"_tags":[]},"applicationImmunityTags":{"_tags":[]},"removeGameEffectsWithTags":{"_tags":[]},"durationType":2,"duration":"0","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"_tags":[]},"cancelOnAbilityEnd":false,"launchPositionSource":0,"launchBindingName":"center","targetPositionSource":1,"targetBindingName":"center","projectileTargetType":0,"flyOver":false,"offsetAngle":0.0,"curveHeight":0.0,"projectileEntityId":50001,"projectilePrefab":null,"projectilePrefabPath":"Assets/Res/Entity/Effect/ef_fashi_gandian_buff.prefab","speed":3.0,"maxDistance":10.0,"collisionRadius":0.5,"isPiercing":false,"maxPierceCount":1,"collisionTargetTags":{"_tags":[]},"collisionExcludeTags":{"_tags":[]},"isBouncing":true,"bounceTargetMode":0,"maxBounceCount":3,"bounceSearchRadius":10.0,"canBounceToSameTarget":false,"excludeSourceCamp":true,"bounceAngleOffset":0.0}</t>
+          <t>{"guid":"90bacd9f-d882-4bba-aaa8-41ed993ac3ff","nodeType":8,"position":{"x":-419.33331298828125,"y":-1840.0},"targetType":2,"assetTags":{"Tags":[]},"grantedTags":{"Tags":[]},"applicationRequiredTags":{"Tags":[]},"applicationImmunityTags":{"Tags":[]},"removeGameEffectsWithTags":{"Tags":[]},"durationType":2,"duration":"0","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"Tags":[]},"cancelOnAbilityEnd":false,"launchPositionSource":0,"launchBindingName":"center","targetPositionSource":1,"targetBindingName":"center","projectileTargetType":0,"flyOver":false,"offsetAngle":0.0,"curveHeight":0.0,"projectileEntityId":50001,"projectilePrefab":null,"projectilePrefabPath":"Assets/Res/Entity/Effect/ef_fashi_gandian_buff.prefab","speed":3.0,"maxDistance":10.0,"collisionRadius":0.5,"isPiercing":false,"maxPierceCount":1,"collisionTargetTags":{"Tags":[]},"collisionExcludeTags":{"Tags":[]},"isBouncing":true,"bounceTargetMode":0,"maxBounceCount":3,"bounceSearchRadius":10.0,"canBounceToSameTarget":false,"excludeSourceCamp":true,"bounceAngleOffset":0.0}</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -1135,7 +1135,7 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>{"guid":"2d7e41c4-8e90-4b61-879c-4b2e5b9486db","nodeType":14,"position":{"x":180.0,"y":-1810.0},"targetType":1,"requiredTags":{"_tags":[]},"immunityTags":{"_tags":[]},"destroyWithNode":false,"positionSource":2,"positionBindingName":"head","textType":0,"fixedText":"","contextDataKey":"DamageResult","textColor":{"r":1.0,"g":0.16293229162693024,"b":0.0,"a":1.0},"criticalColor":{"r":1.0,"g":0.5,"b":0.0,"a":1.0},"missColor":{"r":0.5,"g":0.5,"b":0.5,"a":1.0},"fontSize":5.0,"criticalFontSize":60.0,"duration":1.5,"offset":{"x":0.0,"y":0.0},"moveDirection":{"x":0.0,"y":1.0}}</t>
+          <t>{"guid":"2d7e41c4-8e90-4b61-879c-4b2e5b9486db","nodeType":14,"position":{"x":180.0,"y":-1810.0},"targetType":1,"requiredTags":{"Tags":[]},"immunityTags":{"Tags":[]},"destroyWithNode":false,"positionSource":2,"positionBindingName":"head","textType":0,"fixedText":"","contextDataKey":"DamageResult","textColor":{"r":1.0,"g":0.16293229162693024,"b":0.0,"a":1.0},"criticalColor":{"r":1.0,"g":0.5,"b":0.0,"a":1.0},"missColor":{"r":0.5,"g":0.5,"b":0.5,"a":1.0},"fontSize":5.0,"criticalFontSize":60.0,"duration":1.5,"offset":{"x":0.0,"y":0.0},"moveDirection":{"x":0.0,"y":1.0}}</t>
         </is>
       </c>
       <c r="G27"/>
@@ -1197,7 +1197,7 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>{"guid":"c28fb88d-51b1-47b2-be59-859e0ac638e3","nodeType":10,"position":{"x":-1220.6666259765625,"y":-1747.3333740234375},"targetType":1,"assetTags":{"_tags":[]},"grantedTags":{"_tags":[{"_name":"CD.FireCircle","_hashCode":522143731,"_shortName":"FireCircle","_ancestorHashCodes":[-1137859925],"_ancestorNames":["CD"]}]},"applicationRequiredTags":{"_tags":[]},"applicationImmunityTags":{"_tags":[]},"removeGameEffectsWithTags":{"_tags":[]},"durationType":1,"duration":"1","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"_tags":[]},"cancelOnAbilityEnd":false,"cooldownType":0,"maxCharges":2,"chargeTime":"10"}</t>
+          <t>{"guid":"c28fb88d-51b1-47b2-be59-859e0ac638e3","nodeType":10,"position":{"x":-1220.6666259765625,"y":-1747.3333740234375},"targetType":1,"assetTags":{"Tags":[]},"grantedTags":{"Tags":[{"Name":"CD.FireCircle","HashCode":522143731,"ShortName":"FireCircle","AncestorHashCodes":[-1137859925],"AncestorNames":["CD"]}]},"applicationRequiredTags":{"Tags":[]},"applicationImmunityTags":{"Tags":[]},"removeGameEffectsWithTags":{"Tags":[]},"durationType":1,"duration":"1","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"Tags":[]},"cancelOnAbilityEnd":false,"cooldownType":0,"maxCharges":2,"chargeTime":"10"}</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -1217,7 +1217,7 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>{"guid":"356907e0-1488-4128-bfcc-7ff73cfc3330","nodeType":0,"position":{"x":-878.6666259765625,"y":-1851.3333740234375},"targetType":1,"skillId":1010,"assetTags":{"_tags":[]},"cancelAbilitiesWithTags":{"_tags":[]},"blockAbilitiesWithTags":{"_tags":[]},"activationOwnedTags":{"_tags":[]},"activationRequiredTags":{"_tags":[]},"activationBlockedTags":{"_tags":[{"_name":"CD.FireCircle","_hashCode":522143731,"_shortName":"FireCircle","_ancestorHashCodes":[-1137859925],"_ancestorNames":["CD"]}]},"ongoingBlockedTags":{"_tags":[]},"eventOutputPorts":[]}</t>
+          <t>{"guid":"356907e0-1488-4128-bfcc-7ff73cfc3330","nodeType":0,"position":{"x":-878.6666259765625,"y":-1851.3333740234375},"targetType":1,"skillId":1010,"assetTags":{"Tags":[]},"cancelAbilitiesWithTags":{"Tags":[]},"blockAbilitiesWithTags":{"Tags":[]},"activationOwnedTags":{"Tags":[]},"activationRequiredTags":{"Tags":[]},"activationBlockedTags":{"Tags":[{"Name":"CD.FireCircle","HashCode":522143731,"ShortName":"FireCircle","AncestorHashCodes":[-1137859925],"AncestorNames":["CD"]}]},"ongoingBlockedTags":{"Tags":[]},"eventOutputPorts":[]}</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -1237,7 +1237,7 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>{"guid":"9d6f459d-b588-4b64-843b-1b71e8f299ae","nodeType":3,"position":{"x":-1195.3333740234375,"y":-2013.3333740234375},"targetType":1,"assetTags":{"_tags":[]},"grantedTags":{"_tags":[]},"applicationRequiredTags":{"_tags":[]},"applicationImmunityTags":{"_tags":[]},"removeGameEffectsWithTags":{"_tags":[]},"durationType":0,"duration":"0","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[{"attrType":1003,"operation":0,"magnitudeSourceType":0,"fixedValue":-100.0,"formula":"","mmcType":0,"setByCallerKey":"","mmcCaptureAttribute":200,"mmcAttributeSource":0,"mmcCoefficient":1.0,"mmcUseSnapshot":true}],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"_tags":[]},"cancelOnAbilityEnd":true}</t>
+          <t>{"guid":"9d6f459d-b588-4b64-843b-1b71e8f299ae","nodeType":3,"position":{"x":-1195.3333740234375,"y":-2013.3333740234375},"targetType":1,"assetTags":{"Tags":[]},"grantedTags":{"Tags":[]},"applicationRequiredTags":{"Tags":[]},"applicationImmunityTags":{"Tags":[]},"removeGameEffectsWithTags":{"Tags":[]},"durationType":0,"duration":"0","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[{"attrType":1003,"operation":0,"magnitudeSourceType":0,"fixedValue":-100.0,"formula":"","mmcType":0,"setByCallerKey":"","mmcCaptureAttribute":200,"mmcAttributeSource":0,"mmcCoefficient":1.0,"mmcUseSnapshot":true}],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"Tags":[]},"cancelOnAbilityEnd":true}</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -1257,7 +1257,7 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>{"guid":"eae41233-d297-46fe-a6c8-0b5c876fbb2a","nodeType":1,"position":{"x":45.333343505859375,"y":-1806.666748046875},"targetType":0,"assetTags":{"_tags":[]},"grantedTags":{"_tags":[]},"applicationRequiredTags":{"_tags":[]},"applicationImmunityTags":{"_tags":[]},"removeGameEffectsWithTags":{"_tags":[]},"durationType":0,"duration":"0","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"_tags":[]},"cancelOnAbilityEnd":true,"damageType":0,"damageSourceType":0,"damageFixedValue":10.0,"damageFormula":"","damageMMCType":0,"damageSetByCallerKey":"","damageMMCCaptureAttribute":200,"damageMMCAttributeSource":0,"damageMMCCoefficient":1.0,"damageMMCUseSnapshot":true,"damageMultiplyByStackCount":false,"damageCalculationType":0,"enableHitKnockback":true,"knockbackDistance":1.0,"knockbackSpeed":12.0}</t>
+          <t>{"guid":"eae41233-d297-46fe-a6c8-0b5c876fbb2a","nodeType":1,"position":{"x":45.333343505859375,"y":-1806.666748046875},"targetType":0,"assetTags":{"Tags":[]},"grantedTags":{"Tags":[]},"applicationRequiredTags":{"Tags":[]},"applicationImmunityTags":{"Tags":[]},"removeGameEffectsWithTags":{"Tags":[]},"durationType":0,"duration":"0","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"Tags":[]},"cancelOnAbilityEnd":true,"damageType":0,"damageSourceType":0,"damageFixedValue":10.0,"damageFormula":"","damageMMCType":0,"damageSetByCallerKey":"","damageMMCCaptureAttribute":200,"damageMMCAttributeSource":0,"damageMMCCoefficient":1.0,"damageMMCUseSnapshot":true,"damageMultiplyByStackCount":false,"damageCalculationType":0,"enableHitKnockback":true,"knockbackDistance":1.0,"knockbackSpeed":12.0}</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -1277,7 +1277,7 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>{"guid":"90bacd9f-d882-4bba-aaa8-41ed993ac3ff","nodeType":8,"position":{"x":-400.66665649414063,"y":-1836.666748046875},"targetType":2,"assetTags":{"_tags":[]},"grantedTags":{"_tags":[]},"applicationRequiredTags":{"_tags":[]},"applicationImmunityTags":{"_tags":[]},"removeGameEffectsWithTags":{"_tags":[]},"durationType":2,"duration":"0","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"_tags":[]},"cancelOnAbilityEnd":false,"launchPositionSource":0,"launchBindingName":"center","targetPositionSource":1,"targetBindingName":"center","projectileTargetType":0,"flyOver":false,"offsetAngle":0.0,"curveHeight":0.0,"projectileEntityId":50001,"projectilePrefab":null,"projectilePrefabPath":"Assets/Res/Entity/Effect/ef_fashi_gandian_buff.prefab","speed":3.0,"maxDistance":10.0,"collisionRadius":0.5,"isPiercing":false,"maxPierceCount":1,"collisionTargetTags":{"_tags":[]},"collisionExcludeTags":{"_tags":[]},"isBouncing":true,"bounceTargetMode":0,"maxBounceCount":2,"bounceSearchRadius":10.0,"canBounceToSameTarget":false,"excludeSourceCamp":true,"bounceAngleOffset":50.0}</t>
+          <t>{"guid":"90bacd9f-d882-4bba-aaa8-41ed993ac3ff","nodeType":8,"position":{"x":-400.66665649414063,"y":-1836.666748046875},"targetType":2,"assetTags":{"Tags":[]},"grantedTags":{"Tags":[]},"applicationRequiredTags":{"Tags":[]},"applicationImmunityTags":{"Tags":[]},"removeGameEffectsWithTags":{"Tags":[]},"durationType":2,"duration":"0","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"Tags":[]},"cancelOnAbilityEnd":false,"launchPositionSource":0,"launchBindingName":"center","targetPositionSource":1,"targetBindingName":"center","projectileTargetType":0,"flyOver":false,"offsetAngle":0.0,"curveHeight":0.0,"projectileEntityId":50001,"projectilePrefab":null,"projectilePrefabPath":"Assets/Res/Entity/Effect/ef_fashi_gandian_buff.prefab","speed":3.0,"maxDistance":10.0,"collisionRadius":0.5,"isPiercing":false,"maxPierceCount":1,"collisionTargetTags":{"Tags":[]},"collisionExcludeTags":{"Tags":[]},"isBouncing":true,"bounceTargetMode":0,"maxBounceCount":2,"bounceSearchRadius":10.0,"canBounceToSameTarget":false,"excludeSourceCamp":true,"bounceAngleOffset":50.0}</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>{"guid":"2d7e41c4-8e90-4b61-879c-4b2e5b9486db","nodeType":14,"position":{"x":408.66665649414063,"y":-1747.3333740234375},"targetType":1,"requiredTags":{"_tags":[]},"immunityTags":{"_tags":[]},"destroyWithNode":false,"positionSource":2,"positionBindingName":"head","textType":0,"fixedText":"","contextDataKey":"DamageResult","textColor":{"r":0.0,"g":0.323091983795166,"b":1.0,"a":1.0},"criticalColor":{"r":1.0,"g":0.5,"b":0.0,"a":1.0},"missColor":{"r":0.5,"g":0.5,"b":0.5,"a":1.0},"fontSize":5.0,"criticalFontSize":60.0,"duration":1.5,"offset":{"x":0.0,"y":0.0},"moveDirection":{"x":0.0,"y":1.0}}</t>
+          <t>{"guid":"2d7e41c4-8e90-4b61-879c-4b2e5b9486db","nodeType":14,"position":{"x":408.66665649414063,"y":-1747.3333740234375},"targetType":1,"requiredTags":{"Tags":[]},"immunityTags":{"Tags":[]},"destroyWithNode":false,"positionSource":2,"positionBindingName":"head","textType":0,"fixedText":"","contextDataKey":"DamageResult","textColor":{"r":0.0,"g":0.323091983795166,"b":1.0,"a":1.0},"criticalColor":{"r":1.0,"g":0.5,"b":0.0,"a":1.0},"missColor":{"r":0.5,"g":0.5,"b":0.5,"a":1.0},"fontSize":5.0,"criticalFontSize":60.0,"duration":1.5,"offset":{"x":0.0,"y":0.0},"moveDirection":{"x":0.0,"y":1.0}}</t>
         </is>
       </c>
       <c r="G35"/>
@@ -1319,7 +1319,7 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>{"guid":"9d6f459d-b588-4b64-843b-1b71e8f299ae","nodeType":3,"position":{"x":-1186.6666259765625,"y":-2011.3333740234375},"targetType":1,"assetTags":{"_tags":[]},"grantedTags":{"_tags":[]},"applicationRequiredTags":{"_tags":[]},"applicationImmunityTags":{"_tags":[]},"removeGameEffectsWithTags":{"_tags":[]},"durationType":0,"duration":"0","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[{"attrType":100,"operation":0,"magnitudeSourceType":0,"fixedValue":10.0,"formula":"","mmcType":0,"setByCallerKey":"","mmcCaptureAttribute":200,"mmcAttributeSource":0,"mmcCoefficient":1.0,"mmcUseSnapshot":true}],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"_tags":[]},"cancelOnAbilityEnd":true}</t>
+          <t>{"guid":"9d6f459d-b588-4b64-843b-1b71e8f299ae","nodeType":3,"position":{"x":-1186.6666259765625,"y":-2011.3333740234375},"targetType":1,"assetTags":{"Tags":[]},"grantedTags":{"Tags":[]},"applicationRequiredTags":{"Tags":[]},"applicationImmunityTags":{"Tags":[]},"removeGameEffectsWithTags":{"Tags":[]},"durationType":0,"duration":"0","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[{"attrType":100,"operation":0,"magnitudeSourceType":0,"fixedValue":10.0,"formula":"","mmcType":0,"setByCallerKey":"","mmcCaptureAttribute":200,"mmcAttributeSource":0,"mmcCoefficient":1.0,"mmcUseSnapshot":true}],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"Tags":[]},"cancelOnAbilityEnd":true}</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -1359,7 +1359,7 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>{"guid":"c28fb88d-51b1-47b2-be59-859e0ac638e3","nodeType":10,"position":{"x":-1186.6666259765625,"y":-1747.3333740234375},"targetType":1,"assetTags":{"_tags":[]},"grantedTags":{"_tags":[{"_name":"CD.God","_hashCode":1317201809,"_shortName":"God","_ancestorHashCodes":[-1137859925],"_ancestorNames":["CD"]}]},"applicationRequiredTags":{"_tags":[]},"applicationImmunityTags":{"_tags":[]},"removeGameEffectsWithTags":{"_tags":[]},"durationType":1,"duration":"5","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"_tags":[]},"cancelOnAbilityEnd":false,"cooldownType":0,"maxCharges":2,"chargeTime":"10"}</t>
+          <t>{"guid":"c28fb88d-51b1-47b2-be59-859e0ac638e3","nodeType":10,"position":{"x":-1186.6666259765625,"y":-1747.3333740234375},"targetType":1,"assetTags":{"Tags":[]},"grantedTags":{"Tags":[{"Name":"CD.God","HashCode":1317201809,"ShortName":"God","AncestorHashCodes":[-1137859925],"AncestorNames":["CD"]}]},"applicationRequiredTags":{"Tags":[]},"applicationImmunityTags":{"Tags":[]},"removeGameEffectsWithTags":{"Tags":[]},"durationType":1,"duration":"5","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"Tags":[]},"cancelOnAbilityEnd":false,"cooldownType":0,"maxCharges":2,"chargeTime":"10"}</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -1379,7 +1379,7 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>{"guid":"091ecddb-f80b-4c00-aa06-f9bc718618d2","nodeType":22,"position":{"x":-93.333328247070313,"y":-1708.666748046875},"targetType":0,"assetTags":{"_tags":[]},"grantedTags":{"_tags":[]},"applicationRequiredTags":{"_tags":[]},"applicationImmunityTags":{"_tags":[]},"removeGameEffectsWithTags":{"_tags":[]},"durationType":1,"duration":"0.5","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"_tags":[]},"cancelOnAbilityEnd":false,"displaceType":1,"speed":10.0,"distance":3.0,"minDistance":0.5,"pointSource":0,"pointBindingName":""}</t>
+          <t>{"guid":"091ecddb-f80b-4c00-aa06-f9bc718618d2","nodeType":22,"position":{"x":-93.333328247070313,"y":-1708.666748046875},"targetType":0,"assetTags":{"Tags":[]},"grantedTags":{"Tags":[]},"applicationRequiredTags":{"Tags":[]},"applicationImmunityTags":{"Tags":[]},"removeGameEffectsWithTags":{"Tags":[]},"durationType":1,"duration":"0.5","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"Tags":[]},"cancelOnAbilityEnd":false,"displaceType":1,"speed":10.0,"distance":3.0,"minDistance":0.5,"pointSource":0,"pointBindingName":""}</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -1399,7 +1399,7 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>{"guid":"e33ab94c-1496-4d6a-ba5e-1afd38bb0c30","nodeType":4,"position":{"x":-452.0,"y":-1786.666748046875},"targetType":1,"searchShapeType":0,"searchLineType":0,"positionSource":0,"positionBindingName":"center","searchCircleRadius":4.0,"searchSectorRadius":2.0,"searchSectorAngle":180.0,"searchLineDirectionOffsetAngle":0.0,"searchLineDirectionWidth":1.0,"searchLineDirectionLength":10.0,"lineStartPositionSource":0,"lineStartBindingName":"","lineEndPositionSource":1,"lineEndBindingName":"","searchLineBetweenWidth":1.0,"searchLineAbsoluteAngle":0.0,"searchLineAbsoluteWidth":1.0,"searchLineAbsoluteLength":10.0,"maxTargets":999,"searchTargetTags":{"_tags":[{"_name":"unitType.monster","_hashCode":-2021655864,"_shortName":"monster","_ancestorHashCodes":[1600484460],"_ancestorNames":["unitType"]}]},"searchExcludeTags":{"_tags":[]}}</t>
+          <t>{"guid":"e33ab94c-1496-4d6a-ba5e-1afd38bb0c30","nodeType":4,"position":{"x":-452.0,"y":-1786.666748046875},"targetType":1,"searchShapeType":0,"searchLineType":0,"positionSource":0,"positionBindingName":"center","searchCircleRadius":4.0,"searchSectorRadius":2.0,"searchSectorAngle":180.0,"searchLineDirectionOffsetAngle":0.0,"searchLineDirectionWidth":1.0,"searchLineDirectionLength":10.0,"lineStartPositionSource":0,"lineStartBindingName":"","lineEndPositionSource":1,"lineEndBindingName":"","searchLineBetweenWidth":1.0,"searchLineAbsoluteAngle":0.0,"searchLineAbsoluteWidth":1.0,"searchLineAbsoluteLength":10.0,"maxTargets":999,"searchTargetTags":{"Tags":[{"Name":"unitType.monster","HashCode":-2021655864,"ShortName":"monster","AncestorHashCodes":[1600484460],"AncestorNames":["unitType"]}]},"searchExcludeTags":{"Tags":[]}}</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -1439,7 +1439,7 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>{"guid":"356907e0-1488-4128-bfcc-7ff73cfc3330","nodeType":0,"position":{"x":-878.6666259765625,"y":-1853.3333740234375},"targetType":1,"skillId":1005,"assetTags":{"_tags":[]},"cancelAbilitiesWithTags":{"_tags":[]},"blockAbilitiesWithTags":{"_tags":[]},"activationOwnedTags":{"_tags":[{"_name":"Skill.Running","_hashCode":-51601538,"_shortName":"Running","_ancestorHashCodes":[1312877309],"_ancestorNames":["Skill"]}]},"activationRequiredTags":{"_tags":[]},"activationBlockedTags":{"_tags":[{"_name":"CD.RecBlood","_hashCode":1043024739,"_shortName":"RecBlood","_ancestorHashCodes":[-1137859925],"_ancestorNames":["CD"]},{"_name":"Skill.Running","_hashCode":-51601538,"_shortName":"Running","_ancestorHashCodes":[1312877309],"_ancestorNames":["Skill"]}]},"ongoingBlockedTags":{"_tags":[]},"eventOutputPorts":[]}</t>
+          <t>{"guid":"356907e0-1488-4128-bfcc-7ff73cfc3330","nodeType":0,"position":{"x":-878.6666259765625,"y":-1853.3333740234375},"targetType":1,"skillId":1005,"assetTags":{"Tags":[]},"cancelAbilitiesWithTags":{"Tags":[]},"blockAbilitiesWithTags":{"Tags":[]},"activationOwnedTags":{"Tags":[{"Name":"Skill.Running","HashCode":-51601538,"ShortName":"Running","AncestorHashCodes":[1312877309],"AncestorNames":["Skill"]}]},"activationRequiredTags":{"Tags":[]},"activationBlockedTags":{"Tags":[{"Name":"CD.RecBlood","HashCode":1043024739,"ShortName":"RecBlood","AncestorHashCodes":[-1137859925],"AncestorNames":["CD"]},{"Name":"Skill.Running","HashCode":-51601538,"ShortName":"Running","AncestorHashCodes":[1312877309],"AncestorNames":["Skill"]}]},"ongoingBlockedTags":{"Tags":[]},"eventOutputPorts":[]}</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -1459,7 +1459,7 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>{"guid":"cde57fb8-b693-4da8-a4a8-fd61e56c5dcd","nodeType":12,"position":{"x":677.3333740234375,"y":-1998.666748046875},"targetType":1,"requiredTags":{"_tags":[]},"immunityTags":{"_tags":[]},"destroyWithNode":false,"positionSource":0,"particleEntityId":50009,"particlePrefab":null,"particlePrefabPath":"Assets/Res/Entity/Effect/ef_Zhanshi_zhandounuhou_01.prefab","particleBindingName":"down","particleOffset":{"x":0.0,"y":0.0,"z":0.0},"particleScale":{"x":1.0,"y":1.0,"z":1.0},"attachToTarget":false,"particleLoop":false}</t>
+          <t>{"guid":"cde57fb8-b693-4da8-a4a8-fd61e56c5dcd","nodeType":12,"position":{"x":677.3333740234375,"y":-1998.666748046875},"targetType":1,"requiredTags":{"Tags":[]},"immunityTags":{"Tags":[]},"destroyWithNode":false,"positionSource":0,"particleEntityId":50009,"particlePrefab":null,"particlePrefabPath":"Assets/Res/Entity/Effect/ef_Zhanshi_zhandounuhou_01.prefab","particleBindingName":"down","particleOffset":{"x":0.0,"y":0.0,"z":0.0},"particleScale":{"x":1.0,"y":1.0,"z":1.0},"attachToTarget":false,"particleLoop":false}</t>
         </is>
       </c>
       <c r="G43"/>
@@ -1481,7 +1481,7 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>{"guid":"356907e0-1488-4128-bfcc-7ff73cfc3330","nodeType":0,"position":{"x":-924.6666259765625,"y":-1886.666748046875},"targetType":1,"skillId":1007,"assetTags":{"_tags":[]},"cancelAbilitiesWithTags":{"_tags":[]},"blockAbilitiesWithTags":{"_tags":[]},"activationOwnedTags":{"_tags":[]},"activationRequiredTags":{"_tags":[]},"activationBlockedTags":{"_tags":[{"_name":"CD.RecBlood","_hashCode":1163914435,"_shortName":"回血","_ancestorHashCodes":[-1137859925],"_ancestorNames":["CD"]}]},"ongoingBlockedTags":{"_tags":[]},"eventOutputPorts":[]}</t>
+          <t>{"guid":"356907e0-1488-4128-bfcc-7ff73cfc3330","nodeType":0,"position":{"x":-924.6666259765625,"y":-1886.666748046875},"targetType":1,"skillId":1007,"assetTags":{"Tags":[]},"cancelAbilitiesWithTags":{"Tags":[]},"blockAbilitiesWithTags":{"Tags":[]},"activationOwnedTags":{"Tags":[]},"activationRequiredTags":{"Tags":[]},"activationBlockedTags":{"Tags":[{"Name":"CD.RecBlood","HashCode":1163914435,"ShortName":"回血","AncestorHashCodes":[-1137859925],"AncestorNames":["CD"]}]},"ongoingBlockedTags":{"Tags":[]},"eventOutputPorts":[]}</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>{"guid":"c28fb88d-51b1-47b2-be59-859e0ac638e3","nodeType":10,"position":{"x":-1156.0,"y":-1801.3333740234375},"targetType":1,"assetTags":{"_tags":[]},"grantedTags":{"_tags":[{"_name":"CD.RecBlood","_hashCode":1163914435,"_shortName":"回血","_ancestorHashCodes":[-1137859925],"_ancestorNames":["CD"]}]},"applicationRequiredTags":{"_tags":[]},"applicationImmunityTags":{"_tags":[]},"removeGameEffectsWithTags":{"_tags":[]},"durationType":1,"duration":"3","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"_tags":[]},"cancelOnAbilityEnd":false,"cooldownType":0,"maxCharges":2,"chargeTime":"10"}</t>
+          <t>{"guid":"c28fb88d-51b1-47b2-be59-859e0ac638e3","nodeType":10,"position":{"x":-1156.0,"y":-1801.3333740234375},"targetType":1,"assetTags":{"Tags":[]},"grantedTags":{"Tags":[{"Name":"CD.RecBlood","HashCode":1163914435,"ShortName":"回血","AncestorHashCodes":[-1137859925],"AncestorNames":["CD"]}]},"applicationRequiredTags":{"Tags":[]},"applicationImmunityTags":{"Tags":[]},"removeGameEffectsWithTags":{"Tags":[]},"durationType":1,"duration":"3","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"Tags":[]},"cancelOnAbilityEnd":false,"cooldownType":0,"maxCharges":2,"chargeTime":"10"}</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -1541,7 +1541,7 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>{"guid":"6d127270-5aeb-4542-9183-8d2d028d6786","nodeType":2,"position":{"x":-550.6666259765625,"y":-2050.0},"targetType":1,"assetTags":{"_tags":[]},"grantedTags":{"_tags":[]},"applicationRequiredTags":{"_tags":[]},"applicationImmunityTags":{"_tags":[]},"removeGameEffectsWithTags":{"_tags":[]},"durationType":0,"duration":"0","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"_tags":[]},"cancelOnAbilityEnd":false,"healSourceType":0,"healFixedValue":10.0,"healFormula":"","healMMCType":0,"healSetByCallerKey":"","healMMCCaptureAttribute":1007,"healMMCAttributeSource":0,"healMMCCoefficient":1.0,"healMMCUseSnapshot":true,"healMultiplyByStackCount":false,"healCalculationType":0}</t>
+          <t>{"guid":"6d127270-5aeb-4542-9183-8d2d028d6786","nodeType":2,"position":{"x":-550.6666259765625,"y":-2050.0},"targetType":1,"assetTags":{"Tags":[]},"grantedTags":{"Tags":[]},"applicationRequiredTags":{"Tags":[]},"applicationImmunityTags":{"Tags":[]},"removeGameEffectsWithTags":{"Tags":[]},"durationType":0,"duration":"0","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"Tags":[]},"cancelOnAbilityEnd":false,"healSourceType":0,"healFixedValue":10.0,"healFormula":"","healMMCType":0,"healSetByCallerKey":"","healMMCCaptureAttribute":1007,"healMMCAttributeSource":0,"healMMCCoefficient":1.0,"healMMCUseSnapshot":true,"healMultiplyByStackCount":false,"healCalculationType":0}</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -1561,7 +1561,7 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>{"guid":"becb4d53-8a9e-4dc0-95a3-618d1e79ecc7","nodeType":14,"position":{"x":-303.33331298828125,"y":-1952.666748046875},"targetType":1,"requiredTags":{"_tags":[]},"immunityTags":{"_tags":[]},"destroyWithNode":false,"positionSource":2,"positionBindingName":"head","textType":1,"fixedText":"","contextDataKey":"Heal","textColor":{"r":0.25257891416549683,"g":0.96226418018341064,"b":0.1180134117603302,"a":1.0},"criticalColor":{"r":1.0,"g":0.5,"b":0.0,"a":1.0},"missColor":{"r":0.5,"g":0.5,"b":0.5,"a":1.0},"fontSize":5.0,"criticalFontSize":60.0,"duration":1.5,"offset":{"x":0.0,"y":0.0},"moveDirection":{"x":0.0,"y":1.0}}</t>
+          <t>{"guid":"becb4d53-8a9e-4dc0-95a3-618d1e79ecc7","nodeType":14,"position":{"x":-303.33331298828125,"y":-1952.666748046875},"targetType":1,"requiredTags":{"Tags":[]},"immunityTags":{"Tags":[]},"destroyWithNode":false,"positionSource":2,"positionBindingName":"head","textType":1,"fixedText":"","contextDataKey":"Heal","textColor":{"r":0.25257891416549683,"g":0.96226418018341064,"b":0.1180134117603302,"a":1.0},"criticalColor":{"r":1.0,"g":0.5,"b":0.0,"a":1.0},"missColor":{"r":0.5,"g":0.5,"b":0.5,"a":1.0},"fontSize":5.0,"criticalFontSize":60.0,"duration":1.5,"offset":{"x":0.0,"y":0.0},"moveDirection":{"x":0.0,"y":1.0}}</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>{"guid":"3cc340e3-1583-428e-ada4-c4e8539725d6","nodeType":3,"position":{"x":-1256.0,"y":-2008.0},"targetType":1,"assetTags":{"_tags":[]},"grantedTags":{"_tags":[]},"applicationRequiredTags":{"_tags":[]},"applicationImmunityTags":{"_tags":[]},"removeGameEffectsWithTags":{"_tags":[]},"durationType":0,"duration":"0","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[{"attrType":1003,"operation":0,"magnitudeSourceType":0,"fixedValue":100.0,"formula":"","mmcType":0,"setByCallerKey":"","mmcCaptureAttribute":1006,"mmcAttributeSource":0,"mmcCoefficient":1.0,"mmcUseSnapshot":true}],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"_tags":[]},"cancelOnAbilityEnd":false}</t>
+          <t>{"guid":"3cc340e3-1583-428e-ada4-c4e8539725d6","nodeType":3,"position":{"x":-1256.0,"y":-2008.0},"targetType":1,"assetTags":{"Tags":[]},"grantedTags":{"Tags":[]},"applicationRequiredTags":{"Tags":[]},"applicationImmunityTags":{"Tags":[]},"removeGameEffectsWithTags":{"Tags":[]},"durationType":0,"duration":"0","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[{"attrType":1003,"operation":0,"magnitudeSourceType":0,"fixedValue":100.0,"formula":"","mmcType":0,"setByCallerKey":"","mmcCaptureAttribute":1006,"mmcAttributeSource":0,"mmcCoefficient":1.0,"mmcUseSnapshot":true}],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"Tags":[]},"cancelOnAbilityEnd":false}</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -1601,7 +1601,7 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>{"guid":"cde57fb8-b693-4da8-a4a8-fd61e56c5dcd","nodeType":12,"position":{"x":-303.33331298828125,"y":-2072.666748046875},"targetType":1,"requiredTags":{"_tags":[]},"immunityTags":{"_tags":[]},"destroyWithNode":false,"positionSource":0,"particleEntityId":50004,"particlePrefab":null,"particlePrefabPath":"Assets/Res/Entity/Effect/ef_skill_zhanshi_huifunengliang.prefab","particleBindingName":"down","particleOffset":{"x":0.0,"y":0.0,"z":0.0},"particleScale":{"x":1.0,"y":1.0,"z":1.0},"attachToTarget":false,"particleLoop":false}</t>
+          <t>{"guid":"cde57fb8-b693-4da8-a4a8-fd61e56c5dcd","nodeType":12,"position":{"x":-303.33331298828125,"y":-2072.666748046875},"targetType":1,"requiredTags":{"Tags":[]},"immunityTags":{"Tags":[]},"destroyWithNode":false,"positionSource":0,"particleEntityId":50004,"particlePrefab":null,"particlePrefabPath":"Assets/Res/Entity/Effect/ef_skill_zhanshi_huifunengliang.prefab","particleBindingName":"down","particleOffset":{"x":0.0,"y":0.0,"z":0.0},"particleScale":{"x":1.0,"y":1.0,"z":1.0},"attachToTarget":false,"particleLoop":false}</t>
         </is>
       </c>
       <c r="G50"/>
@@ -1623,7 +1623,7 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>{"guid":"9d6f459d-b588-4b64-843b-1b71e8f299ae","nodeType":3,"position":{"x":-1186.6666259765625,"y":-2011.3333740234375},"targetType":1,"assetTags":{"_tags":[]},"grantedTags":{"_tags":[]},"applicationRequiredTags":{"_tags":[]},"applicationImmunityTags":{"_tags":[]},"removeGameEffectsWithTags":{"_tags":[]},"durationType":0,"duration":"0","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[{"attrType":100,"operation":0,"magnitudeSourceType":0,"fixedValue":10.0,"formula":"","mmcType":0,"setByCallerKey":"","mmcCaptureAttribute":200,"mmcAttributeSource":0,"mmcCoefficient":1.0,"mmcUseSnapshot":true}],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"_tags":[]},"cancelOnAbilityEnd":true}</t>
+          <t>{"guid":"9d6f459d-b588-4b64-843b-1b71e8f299ae","nodeType":3,"position":{"x":-1186.6666259765625,"y":-2011.3333740234375},"targetType":1,"assetTags":{"Tags":[]},"grantedTags":{"Tags":[]},"applicationRequiredTags":{"Tags":[]},"applicationImmunityTags":{"Tags":[]},"removeGameEffectsWithTags":{"Tags":[]},"durationType":0,"duration":"0","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[{"attrType":100,"operation":0,"magnitudeSourceType":0,"fixedValue":10.0,"formula":"","mmcType":0,"setByCallerKey":"","mmcCaptureAttribute":200,"mmcAttributeSource":0,"mmcCoefficient":1.0,"mmcUseSnapshot":true}],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"Tags":[]},"cancelOnAbilityEnd":true}</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -1643,7 +1643,7 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>{"guid":"c28fb88d-51b1-47b2-be59-859e0ac638e3","nodeType":10,"position":{"x":-1186.6666259765625,"y":-1747.3333740234375},"targetType":1,"assetTags":{"_tags":[]},"grantedTags":{"_tags":[{"_name":"CD.RuFood","_hashCode":-1045902856,"_shortName":"RuFood","_ancestorHashCodes":[-1137859925],"_ancestorNames":["CD"]}]},"applicationRequiredTags":{"_tags":[]},"applicationImmunityTags":{"_tags":[]},"removeGameEffectsWithTags":{"_tags":[]},"durationType":1,"duration":"5","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"_tags":[]},"cancelOnAbilityEnd":false,"cooldownType":0,"maxCharges":2,"chargeTime":"10"}</t>
+          <t>{"guid":"c28fb88d-51b1-47b2-be59-859e0ac638e3","nodeType":10,"position":{"x":-1186.6666259765625,"y":-1747.3333740234375},"targetType":1,"assetTags":{"Tags":[]},"grantedTags":{"Tags":[{"Name":"CD.RuFood","HashCode":-1045902856,"ShortName":"RuFood","AncestorHashCodes":[-1137859925],"AncestorNames":["CD"]}]},"applicationRequiredTags":{"Tags":[]},"applicationImmunityTags":{"Tags":[]},"removeGameEffectsWithTags":{"Tags":[]},"durationType":1,"duration":"5","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"Tags":[]},"cancelOnAbilityEnd":false,"cooldownType":0,"maxCharges":2,"chargeTime":"10"}</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -1703,12 +1703,12 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>{"guid":"356907e0-1488-4128-bfcc-7ff73cfc3330","nodeType":0,"position":{"x":-878.6666259765625,"y":-1853.3333740234375},"targetType":1,"skillId":1003,"assetTags":{"_tags":[]},"cancelAbilitiesWithTags":{"_tags":[]},"blockAbilitiesWithTags":{"_tags":[]},"activationOwnedTags":{"_tags":[{"_name":"Skill.Running","_hashCode":-51601538,"_shortName":"Running","_ancestorHashCodes":[1312877309],"_ancestorNames":["Skill"]}]},"activationRequiredTags":{"_tags":[]},"activationBlockedTags":{"_tags":[{"_name":"CD.RuFood","_hashCode":-1045902856,"_shortName":"RuFood","_ancestorHashCodes":[-1137859925],"_ancestorNames":["CD"]},{"_name":"Skill.Running","_hashCode":-51601538,"_shortName":"Running","_ancestorHashCodes":[1312877309],"_ancestorNames":["Skill"]}]},"ongoingBlockedTags":{"_tags":[]},"eventOutputPorts":[]}</t>
+          <t>{"guid":"356907e0-1488-4128-bfcc-7ff73cfc3330","nodeType":0,"position":{"x":-878.6666259765625,"y":-1853.3333740234375},"targetType":1,"skillId":1003,"assetTags":{"Tags":[]},"cancelAbilitiesWithTags":{"Tags":[]},"blockAbilitiesWithTags":{"Tags":[]},"activationOwnedTags":{"Tags":[{"Name":"Skill.Running","HashCode":-51601538,"ShortName":"Running","AncestorHashCodes":[1312877309],"AncestorNames":["Skill"]}]},"activationRequiredTags":{"Tags":[]},"activationBlockedTags":{"Tags":[{"Name":"CD.RuFood","HashCode":-1045902856,"ShortName":"RuFood","AncestorHashCodes":[-1137859925],"AncestorNames":["CD"]},{"Name":"Skill.Running","HashCode":-51601538,"ShortName":"Running","AncestorHashCodes":[1312877309],"AncestorNames":["Skill"]}]},"ongoingBlockedTags":{"Tags":[]},"eventOutputPorts":[]}</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>{"outputNodeGuid":"cb1df36f-5729-423e-9d1a-287db5a433f0","outputPortId":3001,"inputNodeGuid":"93ec5a43-cc34-4e4a-acb3-39da2f2c3010","inputPortId":7001}</t>
+          <t>{"outputNodeGuid":"432ff1e3-b18d-476d-af80-d39ddc07402a","outputPortId":2000539,"inputNodeGuid":"f73ba91e-a76b-456c-b19c-a5176809d5f5","inputPortId":7001}</t>
         </is>
       </c>
       <c r="H55"/>
@@ -1723,12 +1723,12 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>{"guid":"cde57fb8-b693-4da8-a4a8-fd61e56c5dcd","nodeType":12,"position":{"x":676.6666259765625,"y":-1998.0},"targetType":1,"requiredTags":{"_tags":[]},"immunityTags":{"_tags":[]},"destroyWithNode":false,"positionSource":0,"particleEntityId":50007,"particlePrefab":null,"particlePrefabPath":"Assets/Res/Entity/Effect/ef_zhanshi_jcjt_01.prefab","particleBindingName":"down","particleOffset":{"x":0.0,"y":0.0,"z":0.0},"particleScale":{"x":1.0,"y":1.0,"z":1.0},"attachToTarget":false,"particleLoop":false}</t>
+          <t>{"guid":"cde57fb8-b693-4da8-a4a8-fd61e56c5dcd","nodeType":12,"position":{"x":676.6666259765625,"y":-1998.0},"targetType":1,"requiredTags":{"Tags":[]},"immunityTags":{"Tags":[]},"destroyWithNode":false,"positionSource":0,"particleEntityId":50007,"particlePrefab":null,"particlePrefabPath":"Assets/Res/Entity/Effect/ef_zhanshi_jcjt_01.prefab","particleBindingName":"down","particleOffset":{"x":0.0,"y":0.0,"z":0.0},"particleScale":{"x":1.0,"y":1.0,"z":1.0},"attachToTarget":false,"particleLoop":false}</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>{"outputNodeGuid":"432ff1e3-b18d-476d-af80-d39ddc07402a","outputPortId":2000539,"inputNodeGuid":"f73ba91e-a76b-456c-b19c-a5176809d5f5","inputPortId":7001}</t>
+          <t>{"outputNodeGuid":"432ff1e3-b18d-476d-af80-d39ddc07402a","outputPortId":2315086,"inputNodeGuid":"e33ab94c-1496-4d6a-ba5e-1afd38bb0c30","inputPortId":7001}</t>
         </is>
       </c>
       <c r="H56"/>
@@ -1739,16 +1739,16 @@
       <c r="C57"/>
       <c r="D57"/>
       <c r="E57">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>{"guid":"93ec5a43-cc34-4e4a-acb3-39da2f2c3010","nodeType":12,"position":{"x":387.33334350585938,"y":-1790.666748046875},"targetType":1,"requiredTags":{"_tags":[]},"immunityTags":{"_tags":[]},"destroyWithNode":true,"positionSource":2,"particleEntityId":50005,"particlePrefab":null,"particlePrefabPath":"Assets/Res/Entity/Effect/ef_Xuanyun_01.prefab","particleBindingName":"head","particleOffset":{"x":0.0,"y":0.0,"z":0.0},"particleScale":{"x":1.0,"y":1.0,"z":1.0},"attachToTarget":true,"particleLoop":true}</t>
+          <t>{"guid":"e33ab94c-1496-4d6a-ba5e-1afd38bb0c30","nodeType":4,"position":{"x":-452.0,"y":-1786.666748046875},"targetType":1,"searchShapeType":0,"searchLineType":0,"positionSource":0,"positionBindingName":"center","searchCircleRadius":5.0,"searchSectorRadius":2.0,"searchSectorAngle":180.0,"searchLineDirectionOffsetAngle":0.0,"searchLineDirectionWidth":1.0,"searchLineDirectionLength":10.0,"lineStartPositionSource":0,"lineStartBindingName":"","lineEndPositionSource":1,"lineEndBindingName":"","searchLineBetweenWidth":1.0,"searchLineAbsoluteAngle":0.0,"searchLineAbsoluteWidth":1.0,"searchLineAbsoluteLength":10.0,"maxTargets":999,"searchTargetTags":{"Tags":[{"Name":"unitType.monster","HashCode":-2021655864,"ShortName":"monster","AncestorHashCodes":[1600484460],"AncestorNames":["unitType"]}]},"searchExcludeTags":{"Tags":[]}}</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>{"outputNodeGuid":"432ff1e3-b18d-476d-af80-d39ddc07402a","outputPortId":2315086,"inputNodeGuid":"e33ab94c-1496-4d6a-ba5e-1afd38bb0c30","inputPortId":7001}</t>
+          <t>{"outputNodeGuid":"432ff1e3-b18d-476d-af80-d39ddc07402a","outputPortId":2287012,"inputNodeGuid":"cde57fb8-b693-4da8-a4a8-fd61e56c5dcd","inputPortId":7001}</t>
         </is>
       </c>
       <c r="H57"/>
@@ -1759,16 +1759,16 @@
       <c r="C58"/>
       <c r="D58"/>
       <c r="E58">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>{"guid":"e33ab94c-1496-4d6a-ba5e-1afd38bb0c30","nodeType":4,"position":{"x":-452.0,"y":-1786.666748046875},"targetType":1,"searchShapeType":0,"searchLineType":0,"positionSource":0,"positionBindingName":"center","searchCircleRadius":5.0,"searchSectorRadius":2.0,"searchSectorAngle":180.0,"searchLineDirectionOffsetAngle":0.0,"searchLineDirectionWidth":1.0,"searchLineDirectionLength":10.0,"lineStartPositionSource":0,"lineStartBindingName":"","lineEndPositionSource":1,"lineEndBindingName":"","searchLineBetweenWidth":1.0,"searchLineAbsoluteAngle":0.0,"searchLineAbsoluteWidth":1.0,"searchLineAbsoluteLength":10.0,"maxTargets":999,"searchTargetTags":{"_tags":[{"_name":"unitType.monster","_hashCode":-2021655864,"_shortName":"monster","_ancestorHashCodes":[1600484460],"_ancestorNames":["unitType"]}]},"searchExcludeTags":{"_tags":[]}}</t>
+          <t>{"guid":"cb1df36f-5729-423e-9d1a-287db5a433f0","nodeType":11,"position":{"x":18.66668701171875,"y":-1819.3333740234375},"targetType":0,"assetTags":{"Tags":[{"Name":"Buff.DeBuff.Stun","HashCode":1791562953,"ShortName":"Stun","AncestorHashCodes":[937056111,321157895],"AncestorNames":["Buff","Buff.DeBuff"]}]},"grantedTags":{"Tags":[{"Name":"Buff.DeBuff.Stun","HashCode":1791562953,"ShortName":"Stun","AncestorHashCodes":[937056111,321157895],"AncestorNames":["Buff","Buff.DeBuff"]}]},"applicationRequiredTags":{"Tags":[]},"applicationImmunityTags":{"Tags":[]},"removeGameEffectsWithTags":{"Tags":[]},"durationType":1,"duration":"4","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[],"stackType":1,"stackLimit":1,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":1,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"Tags":[]},"cancelOnAbilityEnd":false,"buffId":0}</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>{"outputNodeGuid":"432ff1e3-b18d-476d-af80-d39ddc07402a","outputPortId":2287012,"inputNodeGuid":"cde57fb8-b693-4da8-a4a8-fd61e56c5dcd","inputPortId":7001}</t>
+          <t>{"outputNodeGuid":"cb1df36f-5729-423e-9d1a-287db5a433f0","outputPortId":3001,"inputNodeGuid":"93ec5a43-cc34-4e4a-acb3-39da2f2c3010","inputPortId":7001}</t>
         </is>
       </c>
       <c r="H58"/>
@@ -1779,11 +1779,11 @@
       <c r="C59"/>
       <c r="D59"/>
       <c r="E59">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>{"guid":"cb1df36f-5729-423e-9d1a-287db5a433f0","nodeType":11,"position":{"x":18.66668701171875,"y":-1787.3333740234375},"targetType":0,"assetTags":{"_tags":[{"_name":"Buff.DeBuff.Stun","_hashCode":1791562953,"_shortName":"Stun","_ancestorHashCodes":[937056111,321157895],"_ancestorNames":["Buff","Buff.DeBuff"]}]},"grantedTags":{"_tags":[{"_name":"Buff.DeBuff.Stun","_hashCode":1791562953,"_shortName":"Stun","_ancestorHashCodes":[937056111,321157895],"_ancestorNames":["Buff","Buff.DeBuff"]}]},"applicationRequiredTags":{"_tags":[]},"applicationImmunityTags":{"_tags":[]},"removeGameEffectsWithTags":{"_tags":[]},"durationType":1,"duration":"4","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[],"stackType":1,"stackLimit":1,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":1,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"_tags":[]},"cancelOnAbilityEnd":false,"buffId":0}</t>
+          <t>{"guid":"93ec5a43-cc34-4e4a-acb3-39da2f2c3010","nodeType":12,"position":{"x":408.66665649414063,"y":-1790.666748046875},"targetType":1,"requiredTags":{"Tags":[]},"immunityTags":{"Tags":[]},"destroyWithNode":true,"positionSource":2,"particleEntityId":50005,"particlePrefab":null,"particlePrefabPath":"Assets/Res/Entity/Effect/ef_Xuanyun_01.prefab","particleBindingName":"head","particleOffset":{"x":0.0,"y":0.0,"z":0.0},"particleScale":{"x":1.0,"y":1.0,"z":1.0},"attachToTarget":true,"particleLoop":true}</t>
         </is>
       </c>
       <c r="G59"/>
@@ -1805,7 +1805,7 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>{"guid":"9d6f459d-b588-4b64-843b-1b71e8f299ae","nodeType":3,"position":{"x":-1186.6666259765625,"y":-2011.3333740234375},"targetType":1,"assetTags":{"_tags":[]},"grantedTags":{"_tags":[]},"applicationRequiredTags":{"_tags":[]},"applicationImmunityTags":{"_tags":[]},"removeGameEffectsWithTags":{"_tags":[]},"durationType":0,"duration":"0","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[{"attrType":100,"operation":0,"magnitudeSourceType":0,"fixedValue":10.0,"formula":"","mmcType":0,"setByCallerKey":"","mmcCaptureAttribute":200,"mmcAttributeSource":0,"mmcCoefficient":1.0,"mmcUseSnapshot":true}],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"_tags":[]},"cancelOnAbilityEnd":true}</t>
+          <t>{"guid":"9d6f459d-b588-4b64-843b-1b71e8f299ae","nodeType":3,"position":{"x":-1186.6666259765625,"y":-2011.3333740234375},"targetType":1,"assetTags":{"Tags":[]},"grantedTags":{"Tags":[]},"applicationRequiredTags":{"Tags":[]},"applicationImmunityTags":{"Tags":[]},"removeGameEffectsWithTags":{"Tags":[]},"durationType":0,"duration":"0","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[{"attrType":100,"operation":0,"magnitudeSourceType":0,"fixedValue":10.0,"formula":"","mmcType":0,"setByCallerKey":"","mmcCaptureAttribute":200,"mmcAttributeSource":0,"mmcCoefficient":1.0,"mmcUseSnapshot":true}],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"Tags":[]},"cancelOnAbilityEnd":true}</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
@@ -1845,7 +1845,7 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>{"guid":"c28fb88d-51b1-47b2-be59-859e0ac638e3","nodeType":10,"position":{"x":-1186.6666259765625,"y":-1747.3333740234375},"targetType":1,"assetTags":{"_tags":[]},"grantedTags":{"_tags":[{"_name":"CD.SpeedUp","_hashCode":-605747253,"_shortName":"急速","_ancestorHashCodes":[-1137859925],"_ancestorNames":["CD"]}]},"applicationRequiredTags":{"_tags":[]},"applicationImmunityTags":{"_tags":[]},"removeGameEffectsWithTags":{"_tags":[]},"durationType":1,"duration":"10","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"_tags":[]},"cancelOnAbilityEnd":false,"cooldownType":0,"maxCharges":2,"chargeTime":"10"}</t>
+          <t>{"guid":"c28fb88d-51b1-47b2-be59-859e0ac638e3","nodeType":10,"position":{"x":-1186.6666259765625,"y":-1747.3333740234375},"targetType":1,"assetTags":{"Tags":[]},"grantedTags":{"Tags":[{"Name":"CD.SpeedUp","HashCode":-605747253,"ShortName":"急速","AncestorHashCodes":[-1137859925],"AncestorNames":["CD"]}]},"applicationRequiredTags":{"Tags":[]},"applicationImmunityTags":{"Tags":[]},"removeGameEffectsWithTags":{"Tags":[]},"durationType":1,"duration":"10","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"Tags":[]},"cancelOnAbilityEnd":false,"cooldownType":0,"maxCharges":2,"chargeTime":"10"}</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
@@ -1865,7 +1865,7 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>{"guid":"356907e0-1488-4128-bfcc-7ff73cfc3330","nodeType":0,"position":{"x":-878.6666259765625,"y":-1853.3333740234375},"targetType":1,"skillId":1009,"assetTags":{"_tags":[]},"cancelAbilitiesWithTags":{"_tags":[]},"blockAbilitiesWithTags":{"_tags":[]},"activationOwnedTags":{"_tags":[]},"activationRequiredTags":{"_tags":[]},"activationBlockedTags":{"_tags":[{"_name":"CD.SpeedUp","_hashCode":-605747253,"_shortName":"急速","_ancestorHashCodes":[-1137859925],"_ancestorNames":["CD"]}]},"ongoingBlockedTags":{"_tags":[]},"eventOutputPorts":[]}</t>
+          <t>{"guid":"356907e0-1488-4128-bfcc-7ff73cfc3330","nodeType":0,"position":{"x":-878.6666259765625,"y":-1853.3333740234375},"targetType":1,"skillId":1009,"assetTags":{"Tags":[]},"cancelAbilitiesWithTags":{"Tags":[]},"blockAbilitiesWithTags":{"Tags":[]},"activationOwnedTags":{"Tags":[]},"activationRequiredTags":{"Tags":[]},"activationBlockedTags":{"Tags":[{"Name":"CD.SpeedUp","HashCode":-605747253,"ShortName":"急速","AncestorHashCodes":[-1137859925],"AncestorNames":["CD"]}]},"ongoingBlockedTags":{"Tags":[]},"eventOutputPorts":[]}</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
@@ -1885,7 +1885,7 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>{"guid":"632c75e2-152b-4376-8e9e-62c0e74f92d0","nodeType":11,"position":{"x":-502.66665649414063,"y":-1890.666748046875},"targetType":1,"assetTags":{"_tags":[]},"grantedTags":{"_tags":[]},"applicationRequiredTags":{"_tags":[]},"applicationImmunityTags":{"_tags":[]},"removeGameEffectsWithTags":{"_tags":[]},"durationType":1,"duration":"7","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[{"attrType":300,"operation":0,"magnitudeSourceType":0,"fixedValue":10.0,"formula":"","mmcType":0,"setByCallerKey":"","mmcCaptureAttribute":200,"mmcAttributeSource":0,"mmcCoefficient":1.0,"mmcUseSnapshot":true}],"stackType":2,"stackLimit":1,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"_tags":[]},"cancelOnAbilityEnd":false,"buffId":0}</t>
+          <t>{"guid":"632c75e2-152b-4376-8e9e-62c0e74f92d0","nodeType":11,"position":{"x":-502.66665649414063,"y":-1890.666748046875},"targetType":1,"assetTags":{"Tags":[]},"grantedTags":{"Tags":[]},"applicationRequiredTags":{"Tags":[]},"applicationImmunityTags":{"Tags":[]},"removeGameEffectsWithTags":{"Tags":[]},"durationType":1,"duration":"7","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[{"attrType":300,"operation":0,"magnitudeSourceType":0,"fixedValue":10.0,"formula":"","mmcType":0,"setByCallerKey":"","mmcCaptureAttribute":200,"mmcAttributeSource":0,"mmcCoefficient":1.0,"mmcUseSnapshot":true}],"stackType":2,"stackLimit":1,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"Tags":[]},"cancelOnAbilityEnd":false,"buffId":0}</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
@@ -1927,7 +1927,7 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>{"guid":"c28fb88d-51b1-47b2-be59-859e0ac638e3","nodeType":10,"position":{"x":-1130.6666259765625,"y":-2232.0},"targetType":1,"assetTags":{"_tags":[]},"grantedTags":{"_tags":[{"_name":"CD.Sweep","_hashCode":-303359587,"_shortName":"Sweep","_ancestorHashCodes":[-1137859925],"_ancestorNames":["CD"]}]},"applicationRequiredTags":{"_tags":[]},"applicationImmunityTags":{"_tags":[]},"removeGameEffectsWithTags":{"_tags":[]},"durationType":1,"duration":"1","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"_tags":[]},"cancelOnAbilityEnd":false,"cooldownType":0,"maxCharges":2,"chargeTime":"10"}</t>
+          <t>{"guid":"c28fb88d-51b1-47b2-be59-859e0ac638e3","nodeType":10,"position":{"x":-1130.6666259765625,"y":-2232.0},"targetType":1,"assetTags":{"Tags":[]},"grantedTags":{"Tags":[{"Name":"CD.Sweep","HashCode":-303359587,"ShortName":"Sweep","AncestorHashCodes":[-1137859925],"AncestorNames":["CD"]}]},"applicationRequiredTags":{"Tags":[]},"applicationImmunityTags":{"Tags":[]},"removeGameEffectsWithTags":{"Tags":[]},"durationType":1,"duration":"1","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"Tags":[]},"cancelOnAbilityEnd":false,"cooldownType":0,"maxCharges":2,"chargeTime":"10"}</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
@@ -1967,7 +1967,7 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>{"guid":"9d6f459d-b588-4b64-843b-1b71e8f299ae","nodeType":3,"position":{"x":-1130.6666259765625,"y":-2479.333251953125},"targetType":1,"assetTags":{"_tags":[]},"grantedTags":{"_tags":[]},"applicationRequiredTags":{"_tags":[]},"applicationImmunityTags":{"_tags":[]},"removeGameEffectsWithTags":{"_tags":[]},"durationType":0,"duration":"0","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[{"attrType":1003,"operation":0,"magnitudeSourceType":0,"fixedValue":-10.0,"formula":"","mmcType":0,"setByCallerKey":"","mmcCaptureAttribute":200,"mmcAttributeSource":0,"mmcCoefficient":1.0,"mmcUseSnapshot":true}],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"_tags":[]},"cancelOnAbilityEnd":true}</t>
+          <t>{"guid":"9d6f459d-b588-4b64-843b-1b71e8f299ae","nodeType":3,"position":{"x":-1130.6666259765625,"y":-2479.333251953125},"targetType":1,"assetTags":{"Tags":[]},"grantedTags":{"Tags":[]},"applicationRequiredTags":{"Tags":[]},"applicationImmunityTags":{"Tags":[]},"removeGameEffectsWithTags":{"Tags":[]},"durationType":0,"duration":"0","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[{"attrType":1003,"operation":0,"magnitudeSourceType":0,"fixedValue":-10.0,"formula":"","mmcType":0,"setByCallerKey":"","mmcCaptureAttribute":200,"mmcAttributeSource":0,"mmcCoefficient":1.0,"mmcUseSnapshot":true}],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"Tags":[]},"cancelOnAbilityEnd":true}</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
@@ -1987,7 +1987,7 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>{"guid":"356907e0-1488-4128-bfcc-7ff73cfc3330","nodeType":0,"position":{"x":-843.3333740234375,"y":-2480.0},"targetType":1,"skillId":1001,"assetTags":{"_tags":[]},"cancelAbilitiesWithTags":{"_tags":[]},"blockAbilitiesWithTags":{"_tags":[]},"activationOwnedTags":{"_tags":[]},"activationRequiredTags":{"_tags":[]},"activationBlockedTags":{"_tags":[{"_name":"CD.Sweep","_hashCode":-303359587,"_shortName":"Sweep","_ancestorHashCodes":[-1137859925],"_ancestorNames":["CD"]}]},"ongoingBlockedTags":{"_tags":[]},"eventOutputPorts":[]}</t>
+          <t>{"guid":"356907e0-1488-4128-bfcc-7ff73cfc3330","nodeType":0,"position":{"x":-843.3333740234375,"y":-2480.0},"targetType":1,"skillId":1001,"assetTags":{"Tags":[]},"cancelAbilitiesWithTags":{"Tags":[]},"blockAbilitiesWithTags":{"Tags":[]},"activationOwnedTags":{"Tags":[]},"activationRequiredTags":{"Tags":[]},"activationBlockedTags":{"Tags":[{"Name":"CD.Sweep","HashCode":-303359587,"ShortName":"Sweep","AncestorHashCodes":[-1137859925],"AncestorNames":["CD"]}]},"ongoingBlockedTags":{"Tags":[]},"eventOutputPorts":[]}</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
@@ -2007,7 +2007,7 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>{"guid":"f8947676-1084-4228-b991-1509cc7fe851","nodeType":1,"position":{"x":974.666748046875,"y":-2340.66650390625},"targetType":0,"assetTags":{"_tags":[]},"grantedTags":{"_tags":[]},"applicationRequiredTags":{"_tags":[]},"applicationImmunityTags":{"_tags":[]},"removeGameEffectsWithTags":{"_tags":[]},"durationType":0,"duration":"0","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"_tags":[]},"cancelOnAbilityEnd":true,"damageType":0,"damageSourceType":2,"damageFixedValue":10.0,"damageFormula":"","damageMMCType":0,"damageSetByCallerKey":"","damageMMCCaptureAttribute":1006,"damageMMCAttributeSource":0,"damageMMCCoefficient":1.0,"damageMMCUseSnapshot":true,"damageMultiplyByStackCount":false,"damageCalculationType":0,"enableHitKnockback":true,"knockbackDistance":1.0,"knockbackSpeed":12.0}</t>
+          <t>{"guid":"f8947676-1084-4228-b991-1509cc7fe851","nodeType":1,"position":{"x":974.666748046875,"y":-2340.66650390625},"targetType":0,"assetTags":{"Tags":[]},"grantedTags":{"Tags":[]},"applicationRequiredTags":{"Tags":[]},"applicationImmunityTags":{"Tags":[]},"removeGameEffectsWithTags":{"Tags":[]},"durationType":0,"duration":"0","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"Tags":[]},"cancelOnAbilityEnd":true,"damageType":0,"damageSourceType":2,"damageFixedValue":10.0,"damageFormula":"","damageMMCType":0,"damageSetByCallerKey":"","damageMMCCaptureAttribute":1006,"damageMMCAttributeSource":0,"damageMMCCoefficient":1.0,"damageMMCUseSnapshot":true,"damageMultiplyByStackCount":false,"damageCalculationType":0,"enableHitKnockback":true,"knockbackDistance":1.0,"knockbackSpeed":12.0}</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
@@ -2027,7 +2027,7 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>{"guid":"e33ab94c-1496-4d6a-ba5e-1afd38bb0c30","nodeType":4,"position":{"x":731.3333740234375,"y":-2344.0},"targetType":1,"searchShapeType":1,"searchLineType":0,"positionSource":0,"positionBindingName":"center","searchCircleRadius":5.0,"searchSectorRadius":5.0,"searchSectorAngle":180.0,"searchLineDirectionOffsetAngle":0.0,"searchLineDirectionWidth":1.0,"searchLineDirectionLength":10.0,"lineStartPositionSource":0,"lineStartBindingName":"","lineEndPositionSource":1,"lineEndBindingName":"","searchLineBetweenWidth":1.0,"searchLineAbsoluteAngle":0.0,"searchLineAbsoluteWidth":1.0,"searchLineAbsoluteLength":10.0,"maxTargets":999,"searchTargetTags":{"_tags":[{"_name":"unitType.monster","_hashCode":-2021655864,"_shortName":"monster","_ancestorHashCodes":[1600484460],"_ancestorNames":["unitType"]}]},"searchExcludeTags":{"_tags":[]}}</t>
+          <t>{"guid":"e33ab94c-1496-4d6a-ba5e-1afd38bb0c30","nodeType":4,"position":{"x":731.3333740234375,"y":-2344.0},"targetType":1,"searchShapeType":1,"searchLineType":0,"positionSource":0,"positionBindingName":"center","searchCircleRadius":5.0,"searchSectorRadius":5.0,"searchSectorAngle":180.0,"searchLineDirectionOffsetAngle":0.0,"searchLineDirectionWidth":1.0,"searchLineDirectionLength":10.0,"lineStartPositionSource":0,"lineStartBindingName":"","lineEndPositionSource":1,"lineEndBindingName":"","searchLineBetweenWidth":1.0,"searchLineAbsoluteAngle":0.0,"searchLineAbsoluteWidth":1.0,"searchLineAbsoluteLength":10.0,"maxTargets":999,"searchTargetTags":{"Tags":[{"Name":"unitType.monster","HashCode":-2021655864,"ShortName":"monster","AncestorHashCodes":[1600484460],"AncestorNames":["unitType"]}]},"searchExcludeTags":{"Tags":[]}}</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
@@ -2067,7 +2067,7 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>{"guid":"cde57fb8-b693-4da8-a4a8-fd61e56c5dcd","nodeType":12,"position":{"x":731.3333740234375,"y":-2491.333251953125},"targetType":1,"requiredTags":{"_tags":[]},"immunityTags":{"_tags":[]},"destroyWithNode":false,"positionSource":0,"particleEntityId":50006,"particlePrefab":null,"particlePrefabPath":"Assets/Res/Entity/Effect/ef_Zhanshi_attack_02.prefab","particleBindingName":"down","particleOffset":{"x":5.0,"y":0.0,"z":0.0},"particleScale":{"x":1.0,"y":1.0,"z":1.0},"attachToTarget":false,"particleLoop":false}</t>
+          <t>{"guid":"cde57fb8-b693-4da8-a4a8-fd61e56c5dcd","nodeType":12,"position":{"x":731.3333740234375,"y":-2491.333251953125},"targetType":1,"requiredTags":{"Tags":[]},"immunityTags":{"Tags":[]},"destroyWithNode":false,"positionSource":0,"particleEntityId":50006,"particlePrefab":null,"particlePrefabPath":"Assets/Res/Entity/Effect/ef_Zhanshi_attack_02.prefab","particleBindingName":"down","particleOffset":{"x":5.0,"y":0.0,"z":0.0},"particleScale":{"x":1.0,"y":1.0,"z":1.0},"attachToTarget":false,"particleLoop":false}</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
@@ -2087,7 +2087,7 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>{"guid":"c353e286-8ef0-460a-b917-887f2aeb390a","nodeType":14,"position":{"x":1213.3333740234375,"y":-2354.66650390625},"targetType":1,"requiredTags":{"_tags":[]},"immunityTags":{"_tags":[]},"destroyWithNode":false,"positionSource":2,"positionBindingName":"head","textType":0,"fixedText":"","contextDataKey":"DamageResult","textColor":{"r":1.0,"g":0.0,"b":0.0,"a":1.0},"criticalColor":{"r":1.0,"g":0.5,"b":0.0,"a":1.0},"missColor":{"r":0.5,"g":0.5,"b":0.5,"a":1.0},"fontSize":5.0,"criticalFontSize":60.0,"duration":1.5,"offset":{"x":0.0,"y":0.0},"moveDirection":{"x":0.0,"y":1.0}}</t>
+          <t>{"guid":"c353e286-8ef0-460a-b917-887f2aeb390a","nodeType":14,"position":{"x":1213.3333740234375,"y":-2354.66650390625},"targetType":1,"requiredTags":{"Tags":[]},"immunityTags":{"Tags":[]},"destroyWithNode":false,"positionSource":2,"positionBindingName":"head","textType":0,"fixedText":"","contextDataKey":"DamageResult","textColor":{"r":1.0,"g":0.0,"b":0.0,"a":1.0},"criticalColor":{"r":1.0,"g":0.5,"b":0.0,"a":1.0},"missColor":{"r":0.5,"g":0.5,"b":0.5,"a":1.0},"fontSize":5.0,"criticalFontSize":60.0,"duration":1.5,"offset":{"x":0.0,"y":0.0},"moveDirection":{"x":0.0,"y":1.0}}</t>
         </is>
       </c>
       <c r="G74"/>
@@ -2109,7 +2109,7 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>{"guid":"f8947676-1084-4228-b991-1509cc7fe851","nodeType":1,"position":{"x":1452.666748046875,"y":-2239.333251953125},"targetType":0,"assetTags":{"_tags":[]},"grantedTags":{"_tags":[]},"applicationRequiredTags":{"_tags":[]},"applicationImmunityTags":{"_tags":[]},"removeGameEffectsWithTags":{"_tags":[]},"durationType":0,"duration":"0","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"_tags":[]},"cancelOnAbilityEnd":true,"damageType":0,"damageSourceType":0,"damageFixedValue":10.0,"damageFormula":"","damageMMCType":0,"damageSetByCallerKey":"","damageMMCCaptureAttribute":200,"damageMMCAttributeSource":0,"damageMMCCoefficient":1.0,"damageMMCUseSnapshot":true,"damageMultiplyByStackCount":false,"damageCalculationType":0,"enableHitKnockback":false,"knockbackDistance":1.0,"knockbackSpeed":12.0}</t>
+          <t>{"guid":"f8947676-1084-4228-b991-1509cc7fe851","nodeType":1,"position":{"x":1452.666748046875,"y":-2239.333251953125},"targetType":0,"assetTags":{"Tags":[]},"grantedTags":{"Tags":[]},"applicationRequiredTags":{"Tags":[]},"applicationImmunityTags":{"Tags":[]},"removeGameEffectsWithTags":{"Tags":[]},"durationType":0,"duration":"0","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"Tags":[]},"cancelOnAbilityEnd":true,"damageType":0,"damageSourceType":0,"damageFixedValue":10.0,"damageFormula":"","damageMMCType":0,"damageSetByCallerKey":"","damageMMCCaptureAttribute":200,"damageMMCAttributeSource":0,"damageMMCCoefficient":1.0,"damageMMCUseSnapshot":true,"damageMultiplyByStackCount":false,"damageCalculationType":0,"enableHitKnockback":false,"knockbackDistance":1.0,"knockbackSpeed":12.0}</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
@@ -2149,7 +2149,7 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>{"guid":"9d6f459d-b588-4b64-843b-1b71e8f299ae","nodeType":3,"position":{"x":-1144.0,"y":-2405.333251953125},"targetType":1,"assetTags":{"_tags":[]},"grantedTags":{"_tags":[]},"applicationRequiredTags":{"_tags":[]},"applicationImmunityTags":{"_tags":[]},"removeGameEffectsWithTags":{"_tags":[]},"durationType":0,"duration":"0","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[{"attrType":100,"operation":0,"magnitudeSourceType":0,"fixedValue":10.0,"formula":"","mmcType":0,"setByCallerKey":"","mmcCaptureAttribute":200,"mmcAttributeSource":0,"mmcCoefficient":1.0,"mmcUseSnapshot":true}],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"_tags":[]},"cancelOnAbilityEnd":true}</t>
+          <t>{"guid":"9d6f459d-b588-4b64-843b-1b71e8f299ae","nodeType":3,"position":{"x":-1144.0,"y":-2405.333251953125},"targetType":1,"assetTags":{"Tags":[]},"grantedTags":{"Tags":[]},"applicationRequiredTags":{"Tags":[]},"applicationImmunityTags":{"Tags":[]},"removeGameEffectsWithTags":{"Tags":[]},"durationType":0,"duration":"0","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[{"attrType":100,"operation":0,"magnitudeSourceType":0,"fixedValue":10.0,"formula":"","mmcType":0,"setByCallerKey":"","mmcCaptureAttribute":200,"mmcAttributeSource":0,"mmcCoefficient":1.0,"mmcUseSnapshot":true}],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"Tags":[]},"cancelOnAbilityEnd":true}</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
@@ -2169,7 +2169,7 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>{"guid":"c28fb88d-51b1-47b2-be59-859e0ac638e3","nodeType":10,"position":{"x":-1067.3333740234375,"y":-2188.66650390625},"targetType":1,"assetTags":{"_tags":[]},"grantedTags":{"_tags":[{"_name":"CD.ThreeFire","_hashCode":960327319,"_shortName":"ThreeFire","_ancestorHashCodes":[-1137859925],"_ancestorNames":["CD"]}]},"applicationRequiredTags":{"_tags":[]},"applicationImmunityTags":{"_tags":[]},"removeGameEffectsWithTags":{"_tags":[]},"durationType":1,"duration":"1","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"_tags":[]},"cancelOnAbilityEnd":false,"cooldownType":0,"maxCharges":2,"chargeTime":"10"}</t>
+          <t>{"guid":"c28fb88d-51b1-47b2-be59-859e0ac638e3","nodeType":10,"position":{"x":-1067.3333740234375,"y":-2188.66650390625},"targetType":1,"assetTags":{"Tags":[]},"grantedTags":{"Tags":[{"Name":"CD.ThreeFire","HashCode":960327319,"ShortName":"ThreeFire","AncestorHashCodes":[-1137859925],"AncestorNames":["CD"]}]},"applicationRequiredTags":{"Tags":[]},"applicationImmunityTags":{"Tags":[]},"removeGameEffectsWithTags":{"Tags":[]},"durationType":1,"duration":"1","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"Tags":[]},"cancelOnAbilityEnd":false,"cooldownType":0,"maxCharges":2,"chargeTime":"10"}</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
@@ -2189,7 +2189,7 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>{"guid":"356907e0-1488-4128-bfcc-7ff73cfc3330","nodeType":0,"position":{"x":-746.6666259765625,"y":-2405.333251953125},"targetType":1,"skillId":1008,"assetTags":{"_tags":[]},"cancelAbilitiesWithTags":{"_tags":[]},"blockAbilitiesWithTags":{"_tags":[]},"activationOwnedTags":{"_tags":[]},"activationRequiredTags":{"_tags":[]},"activationBlockedTags":{"_tags":[{"_name":"CD.ThreeFire","_hashCode":960327319,"_shortName":"ThreeFire","_ancestorHashCodes":[-1137859925],"_ancestorNames":["CD"]}]},"ongoingBlockedTags":{"_tags":[]},"eventOutputPorts":[]}</t>
+          <t>{"guid":"356907e0-1488-4128-bfcc-7ff73cfc3330","nodeType":0,"position":{"x":-746.6666259765625,"y":-2405.333251953125},"targetType":1,"skillId":1008,"assetTags":{"Tags":[]},"cancelAbilitiesWithTags":{"Tags":[]},"blockAbilitiesWithTags":{"Tags":[]},"activationOwnedTags":{"Tags":[]},"activationRequiredTags":{"Tags":[]},"activationBlockedTags":{"Tags":[{"Name":"CD.ThreeFire","HashCode":960327319,"ShortName":"ThreeFire","AncestorHashCodes":[-1137859925],"AncestorNames":["CD"]}]},"ongoingBlockedTags":{"Tags":[]},"eventOutputPorts":[]}</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
@@ -2229,7 +2229,7 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>{"guid":"ce857360-de7e-4457-b348-9c124ce98879","nodeType":8,"position":{"x":1040.666748046875,"y":-2305.333251953125},"targetType":2,"assetTags":{"_tags":[]},"grantedTags":{"_tags":[]},"applicationRequiredTags":{"_tags":[]},"applicationImmunityTags":{"_tags":[]},"removeGameEffectsWithTags":{"_tags":[]},"durationType":2,"duration":"0","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"_tags":[]},"cancelOnAbilityEnd":false,"launchPositionSource":0,"launchBindingName":"center","targetPositionSource":1,"targetBindingName":"center","projectileTargetType":0,"flyOver":true,"offsetAngle":30.0,"curveHeight":0.0,"projectileEntityId":50002,"projectilePrefab":null,"projectilePrefabPath":"Assets/Res/Entity/Effect/ef_fashi_huoyandan01.prefab","speed":10.0,"maxDistance":10.0,"collisionRadius":0.5,"isPiercing":false,"maxPierceCount":1,"collisionTargetTags":{"_tags":[]},"collisionExcludeTags":{"_tags":[]},"isBouncing":false,"bounceTargetMode":0,"maxBounceCount":3,"bounceSearchRadius":10.0,"canBounceToSameTarget":false,"excludeSourceCamp":true,"bounceAngleOffset":0.0}</t>
+          <t>{"guid":"ce857360-de7e-4457-b348-9c124ce98879","nodeType":8,"position":{"x":1040.666748046875,"y":-2305.333251953125},"targetType":2,"assetTags":{"Tags":[]},"grantedTags":{"Tags":[]},"applicationRequiredTags":{"Tags":[]},"applicationImmunityTags":{"Tags":[]},"removeGameEffectsWithTags":{"Tags":[]},"durationType":2,"duration":"0","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"Tags":[]},"cancelOnAbilityEnd":false,"launchPositionSource":0,"launchBindingName":"center","targetPositionSource":1,"targetBindingName":"center","projectileTargetType":0,"flyOver":true,"offsetAngle":30.0,"curveHeight":0.0,"projectileEntityId":50002,"projectilePrefab":null,"projectilePrefabPath":"Assets/Res/Entity/Effect/ef_fashi_huoyandan01.prefab","speed":10.0,"maxDistance":10.0,"collisionRadius":0.5,"isPiercing":false,"maxPierceCount":1,"collisionTargetTags":{"Tags":[]},"collisionExcludeTags":{"Tags":[]},"isBouncing":false,"bounceTargetMode":0,"maxBounceCount":3,"bounceSearchRadius":10.0,"canBounceToSameTarget":false,"excludeSourceCamp":true,"bounceAngleOffset":0.0}</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
@@ -2249,7 +2249,7 @@
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>{"guid":"9a695e91-e218-425e-82ed-1e157bf1b014","nodeType":8,"position":{"x":1022.666748046875,"y":-2131.333251953125},"targetType":2,"assetTags":{"_tags":[]},"grantedTags":{"_tags":[]},"applicationRequiredTags":{"_tags":[]},"applicationImmunityTags":{"_tags":[]},"removeGameEffectsWithTags":{"_tags":[]},"durationType":2,"duration":"0","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"_tags":[]},"cancelOnAbilityEnd":false,"launchPositionSource":0,"launchBindingName":"center","targetPositionSource":1,"targetBindingName":"center","projectileTargetType":0,"flyOver":true,"offsetAngle":0.0,"curveHeight":0.0,"projectileEntityId":50002,"projectilePrefab":null,"projectilePrefabPath":"Assets/Res/Entity/Effect/ef_fashi_huoyandan01.prefab","speed":10.0,"maxDistance":10.0,"collisionRadius":0.5,"isPiercing":false,"maxPierceCount":1,"collisionTargetTags":{"_tags":[]},"collisionExcludeTags":{"_tags":[]},"isBouncing":false,"bounceTargetMode":0,"maxBounceCount":3,"bounceSearchRadius":10.0,"canBounceToSameTarget":false,"excludeSourceCamp":true,"bounceAngleOffset":0.0}</t>
+          <t>{"guid":"9a695e91-e218-425e-82ed-1e157bf1b014","nodeType":8,"position":{"x":1022.666748046875,"y":-2131.333251953125},"targetType":2,"assetTags":{"Tags":[]},"grantedTags":{"Tags":[]},"applicationRequiredTags":{"Tags":[]},"applicationImmunityTags":{"Tags":[]},"removeGameEffectsWithTags":{"Tags":[]},"durationType":2,"duration":"0","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"Tags":[]},"cancelOnAbilityEnd":false,"launchPositionSource":0,"launchBindingName":"center","targetPositionSource":1,"targetBindingName":"center","projectileTargetType":0,"flyOver":true,"offsetAngle":0.0,"curveHeight":0.0,"projectileEntityId":50002,"projectilePrefab":null,"projectilePrefabPath":"Assets/Res/Entity/Effect/ef_fashi_huoyandan01.prefab","speed":10.0,"maxDistance":10.0,"collisionRadius":0.5,"isPiercing":false,"maxPierceCount":1,"collisionTargetTags":{"Tags":[]},"collisionExcludeTags":{"Tags":[]},"isBouncing":false,"bounceTargetMode":0,"maxBounceCount":3,"bounceSearchRadius":10.0,"canBounceToSameTarget":false,"excludeSourceCamp":true,"bounceAngleOffset":0.0}</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
@@ -2269,7 +2269,7 @@
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>{"guid":"d897a922-5756-42cf-ac65-90a48c1e5a17","nodeType":8,"position":{"x":1022.666748046875,"y":-1951.3333740234375},"targetType":2,"assetTags":{"_tags":[]},"grantedTags":{"_tags":[]},"applicationRequiredTags":{"_tags":[]},"applicationImmunityTags":{"_tags":[]},"removeGameEffectsWithTags":{"_tags":[]},"durationType":2,"duration":"0","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"_tags":[]},"cancelOnAbilityEnd":false,"launchPositionSource":0,"launchBindingName":"center","targetPositionSource":1,"targetBindingName":"center","projectileTargetType":0,"flyOver":true,"offsetAngle":-30.0,"curveHeight":0.0,"projectileEntityId":50002,"projectilePrefab":null,"projectilePrefabPath":"Assets/Res/Entity/Effect/ef_fashi_huoyandan01.prefab","speed":10.0,"maxDistance":10.0,"collisionRadius":0.5,"isPiercing":false,"maxPierceCount":1,"collisionTargetTags":{"_tags":[]},"collisionExcludeTags":{"_tags":[]},"isBouncing":false,"bounceTargetMode":0,"maxBounceCount":3,"bounceSearchRadius":10.0,"canBounceToSameTarget":false,"excludeSourceCamp":true,"bounceAngleOffset":0.0}</t>
+          <t>{"guid":"d897a922-5756-42cf-ac65-90a48c1e5a17","nodeType":8,"position":{"x":1022.666748046875,"y":-1951.3333740234375},"targetType":2,"assetTags":{"Tags":[]},"grantedTags":{"Tags":[]},"applicationRequiredTags":{"Tags":[]},"applicationImmunityTags":{"Tags":[]},"removeGameEffectsWithTags":{"Tags":[]},"durationType":2,"duration":"0","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"Tags":[]},"cancelOnAbilityEnd":false,"launchPositionSource":0,"launchBindingName":"center","targetPositionSource":1,"targetBindingName":"center","projectileTargetType":0,"flyOver":true,"offsetAngle":-30.0,"curveHeight":0.0,"projectileEntityId":50002,"projectilePrefab":null,"projectilePrefabPath":"Assets/Res/Entity/Effect/ef_fashi_huoyandan01.prefab","speed":10.0,"maxDistance":10.0,"collisionRadius":0.5,"isPiercing":false,"maxPierceCount":1,"collisionTargetTags":{"Tags":[]},"collisionExcludeTags":{"Tags":[]},"isBouncing":false,"bounceTargetMode":0,"maxBounceCount":3,"bounceSearchRadius":10.0,"canBounceToSameTarget":false,"excludeSourceCamp":true,"bounceAngleOffset":0.0}</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
@@ -2289,7 +2289,7 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>{"guid":"c353e286-8ef0-460a-b917-887f2aeb390a","nodeType":14,"position":{"x":1677.3333740234375,"y":-2239.333251953125},"targetType":1,"requiredTags":{"_tags":[]},"immunityTags":{"_tags":[]},"destroyWithNode":false,"positionSource":2,"positionBindingName":"head","textType":0,"fixedText":"","contextDataKey":"DamageResult","textColor":{"r":1.0,"g":0.0,"b":0.0,"a":1.0},"criticalColor":{"r":1.0,"g":0.5,"b":0.0,"a":1.0},"missColor":{"r":0.5,"g":0.5,"b":0.5,"a":1.0},"fontSize":5.0,"criticalFontSize":60.0,"duration":1.5,"offset":{"x":0.0,"y":0.0},"moveDirection":{"x":0.0,"y":1.0}}</t>
+          <t>{"guid":"c353e286-8ef0-460a-b917-887f2aeb390a","nodeType":14,"position":{"x":1677.3333740234375,"y":-2239.333251953125},"targetType":1,"requiredTags":{"Tags":[]},"immunityTags":{"Tags":[]},"destroyWithNode":false,"positionSource":2,"positionBindingName":"head","textType":0,"fixedText":"","contextDataKey":"DamageResult","textColor":{"r":1.0,"g":0.0,"b":0.0,"a":1.0},"criticalColor":{"r":1.0,"g":0.5,"b":0.0,"a":1.0},"missColor":{"r":0.5,"g":0.5,"b":0.5,"a":1.0},"fontSize":5.0,"criticalFontSize":60.0,"duration":1.5,"offset":{"x":0.0,"y":0.0},"moveDirection":{"x":0.0,"y":1.0}}</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
@@ -2329,7 +2329,7 @@
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>{"guid":"9d6f459d-b588-4b64-843b-1b71e8f299ae","nodeType":3,"position":{"x":-1186.6666259765625,"y":-2011.3333740234375},"targetType":1,"assetTags":{"_tags":[]},"grantedTags":{"_tags":[]},"applicationRequiredTags":{"_tags":[]},"applicationImmunityTags":{"_tags":[]},"removeGameEffectsWithTags":{"_tags":[]},"durationType":0,"duration":"0","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[{"attrType":100,"operation":0,"magnitudeSourceType":0,"fixedValue":10.0,"formula":"","mmcType":0,"setByCallerKey":"","mmcCaptureAttribute":200,"mmcAttributeSource":0,"mmcCoefficient":1.0,"mmcUseSnapshot":true}],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"_tags":[]},"cancelOnAbilityEnd":true}</t>
+          <t>{"guid":"9d6f459d-b588-4b64-843b-1b71e8f299ae","nodeType":3,"position":{"x":-1186.6666259765625,"y":-2011.3333740234375},"targetType":1,"assetTags":{"Tags":[]},"grantedTags":{"Tags":[]},"applicationRequiredTags":{"Tags":[]},"applicationImmunityTags":{"Tags":[]},"removeGameEffectsWithTags":{"Tags":[]},"durationType":0,"duration":"0","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[{"attrType":100,"operation":0,"magnitudeSourceType":0,"fixedValue":10.0,"formula":"","mmcType":0,"setByCallerKey":"","mmcCaptureAttribute":200,"mmcAttributeSource":0,"mmcCoefficient":1.0,"mmcUseSnapshot":true}],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"Tags":[]},"cancelOnAbilityEnd":true}</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
@@ -2369,7 +2369,7 @@
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>{"guid":"091ecddb-f80b-4c00-aa06-f9bc718618d2","nodeType":22,"position":{"x":-93.333328247070313,"y":-1708.666748046875},"targetType":0,"assetTags":{"_tags":[]},"grantedTags":{"_tags":[]},"applicationRequiredTags":{"_tags":[]},"applicationImmunityTags":{"_tags":[]},"removeGameEffectsWithTags":{"_tags":[]},"durationType":1,"duration":"0.5","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"_tags":[]},"cancelOnAbilityEnd":false,"displaceType":0,"speed":10.0,"distance":3.0,"minDistance":0.5,"pointSource":0,"pointBindingName":""}</t>
+          <t>{"guid":"091ecddb-f80b-4c00-aa06-f9bc718618d2","nodeType":22,"position":{"x":-93.333328247070313,"y":-1708.666748046875},"targetType":0,"assetTags":{"Tags":[]},"grantedTags":{"Tags":[]},"applicationRequiredTags":{"Tags":[]},"applicationImmunityTags":{"Tags":[]},"removeGameEffectsWithTags":{"Tags":[]},"durationType":1,"duration":"0.5","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"Tags":[]},"cancelOnAbilityEnd":false,"displaceType":0,"speed":10.0,"distance":3.0,"minDistance":0.5,"pointSource":0,"pointBindingName":""}</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
@@ -2389,7 +2389,7 @@
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>{"guid":"c28fb88d-51b1-47b2-be59-859e0ac638e3","nodeType":10,"position":{"x":-1186.6666259765625,"y":-1747.3333740234375},"targetType":1,"assetTags":{"_tags":[]},"grantedTags":{"_tags":[{"_name":"CD.Wan","_hashCode":87403585,"_shortName":"Wan","_ancestorHashCodes":[-1137859925],"_ancestorNames":["CD"]}]},"applicationRequiredTags":{"_tags":[]},"applicationImmunityTags":{"_tags":[]},"removeGameEffectsWithTags":{"_tags":[]},"durationType":1,"duration":"5","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"_tags":[]},"cancelOnAbilityEnd":false,"cooldownType":0,"maxCharges":2,"chargeTime":"10"}</t>
+          <t>{"guid":"c28fb88d-51b1-47b2-be59-859e0ac638e3","nodeType":10,"position":{"x":-1186.6666259765625,"y":-1747.3333740234375},"targetType":1,"assetTags":{"Tags":[]},"grantedTags":{"Tags":[{"Name":"CD.Wan","HashCode":87403585,"ShortName":"Wan","AncestorHashCodes":[-1137859925],"AncestorNames":["CD"]}]},"applicationRequiredTags":{"Tags":[]},"applicationImmunityTags":{"Tags":[]},"removeGameEffectsWithTags":{"Tags":[]},"durationType":1,"duration":"5","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"Tags":[]},"cancelOnAbilityEnd":false,"cooldownType":0,"maxCharges":2,"chargeTime":"10"}</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
@@ -2409,7 +2409,7 @@
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>{"guid":"e33ab94c-1496-4d6a-ba5e-1afd38bb0c30","nodeType":4,"position":{"x":-452.0,"y":-1786.666748046875},"targetType":1,"searchShapeType":0,"searchLineType":0,"positionSource":0,"positionBindingName":"center","searchCircleRadius":4.0,"searchSectorRadius":2.0,"searchSectorAngle":180.0,"searchLineDirectionOffsetAngle":0.0,"searchLineDirectionWidth":1.0,"searchLineDirectionLength":10.0,"lineStartPositionSource":0,"lineStartBindingName":"","lineEndPositionSource":1,"lineEndBindingName":"","searchLineBetweenWidth":1.0,"searchLineAbsoluteAngle":0.0,"searchLineAbsoluteWidth":1.0,"searchLineAbsoluteLength":10.0,"maxTargets":999,"searchTargetTags":{"_tags":[{"_name":"unitType.monster","_hashCode":-2021655864,"_shortName":"monster","_ancestorHashCodes":[1600484460],"_ancestorNames":["unitType"]}]},"searchExcludeTags":{"_tags":[]}}</t>
+          <t>{"guid":"e33ab94c-1496-4d6a-ba5e-1afd38bb0c30","nodeType":4,"position":{"x":-452.0,"y":-1786.666748046875},"targetType":1,"searchShapeType":0,"searchLineType":0,"positionSource":0,"positionBindingName":"center","searchCircleRadius":4.0,"searchSectorRadius":2.0,"searchSectorAngle":180.0,"searchLineDirectionOffsetAngle":0.0,"searchLineDirectionWidth":1.0,"searchLineDirectionLength":10.0,"lineStartPositionSource":0,"lineStartBindingName":"","lineEndPositionSource":1,"lineEndBindingName":"","searchLineBetweenWidth":1.0,"searchLineAbsoluteAngle":0.0,"searchLineAbsoluteWidth":1.0,"searchLineAbsoluteLength":10.0,"maxTargets":999,"searchTargetTags":{"Tags":[{"Name":"unitType.monster","HashCode":-2021655864,"ShortName":"monster","AncestorHashCodes":[1600484460],"AncestorNames":["unitType"]}]},"searchExcludeTags":{"Tags":[]}}</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
@@ -2449,7 +2449,7 @@
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>{"guid":"356907e0-1488-4128-bfcc-7ff73cfc3330","nodeType":0,"position":{"x":-878.6666259765625,"y":-1853.3333740234375},"targetType":1,"skillId":1006,"assetTags":{"_tags":[]},"cancelAbilitiesWithTags":{"_tags":[]},"blockAbilitiesWithTags":{"_tags":[]},"activationOwnedTags":{"_tags":[{"_name":"Skill.Running","_hashCode":-51601538,"_shortName":"Running","_ancestorHashCodes":[1312877309],"_ancestorNames":["Skill"]}]},"activationRequiredTags":{"_tags":[]},"activationBlockedTags":{"_tags":[{"_name":"CD.Wan","_hashCode":87403585,"_shortName":"Wan","_ancestorHashCodes":[-1137859925],"_ancestorNames":["CD"]},{"_name":"Skill.Running","_hashCode":-51601538,"_shortName":"Running","_ancestorHashCodes":[1312877309],"_ancestorNames":["Skill"]}]},"ongoingBlockedTags":{"_tags":[]},"eventOutputPorts":[]}</t>
+          <t>{"guid":"356907e0-1488-4128-bfcc-7ff73cfc3330","nodeType":0,"position":{"x":-878.6666259765625,"y":-1853.3333740234375},"targetType":1,"skillId":1006,"assetTags":{"Tags":[]},"cancelAbilitiesWithTags":{"Tags":[]},"blockAbilitiesWithTags":{"Tags":[]},"activationOwnedTags":{"Tags":[{"Name":"Skill.Running","HashCode":-51601538,"ShortName":"Running","AncestorHashCodes":[1312877309],"AncestorNames":["Skill"]}]},"activationRequiredTags":{"Tags":[]},"activationBlockedTags":{"Tags":[{"Name":"CD.Wan","HashCode":87403585,"ShortName":"Wan","AncestorHashCodes":[-1137859925],"AncestorNames":["CD"]},{"Name":"Skill.Running","HashCode":-51601538,"ShortName":"Running","AncestorHashCodes":[1312877309],"AncestorNames":["Skill"]}]},"ongoingBlockedTags":{"Tags":[]},"eventOutputPorts":[]}</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
@@ -2469,7 +2469,7 @@
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>{"guid":"cde57fb8-b693-4da8-a4a8-fd61e56c5dcd","nodeType":12,"position":{"x":677.3333740234375,"y":-1998.666748046875},"targetType":1,"requiredTags":{"_tags":[]},"immunityTags":{"_tags":[]},"destroyWithNode":false,"positionSource":0,"particleEntityId":50010,"particlePrefab":null,"particlePrefabPath":"Assets/Res/Entity/Effect/ef_Zhanshi_zhentianpaoxiao_01.prefab","particleBindingName":"down","particleOffset":{"x":0.0,"y":0.0,"z":0.0},"particleScale":{"x":1.0,"y":1.0,"z":1.0},"attachToTarget":false,"particleLoop":false}</t>
+          <t>{"guid":"cde57fb8-b693-4da8-a4a8-fd61e56c5dcd","nodeType":12,"position":{"x":677.3333740234375,"y":-1998.666748046875},"targetType":1,"requiredTags":{"Tags":[]},"immunityTags":{"Tags":[]},"destroyWithNode":false,"positionSource":0,"particleEntityId":50010,"particlePrefab":null,"particlePrefabPath":"Assets/Res/Entity/Effect/ef_Zhanshi_zhentianpaoxiao_01.prefab","particleBindingName":"down","particleOffset":{"x":0.0,"y":0.0,"z":0.0},"particleScale":{"x":1.0,"y":1.0,"z":1.0},"attachToTarget":false,"particleLoop":false}</t>
         </is>
       </c>
       <c r="G93"/>
@@ -2491,7 +2491,7 @@
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>{"guid":"9d6f459d-b588-4b64-843b-1b71e8f299ae","nodeType":3,"position":{"x":-1186.6666259765625,"y":-2011.3333740234375},"targetType":1,"assetTags":{"_tags":[]},"grantedTags":{"_tags":[]},"applicationRequiredTags":{"_tags":[]},"applicationImmunityTags":{"_tags":[]},"removeGameEffectsWithTags":{"_tags":[]},"durationType":0,"duration":"0","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[{"attrType":100,"operation":0,"magnitudeSourceType":0,"fixedValue":10.0,"formula":"","mmcType":0,"setByCallerKey":"","mmcCaptureAttribute":200,"mmcAttributeSource":0,"mmcCoefficient":1.0,"mmcUseSnapshot":true}],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"_tags":[]},"cancelOnAbilityEnd":true}</t>
+          <t>{"guid":"9d6f459d-b588-4b64-843b-1b71e8f299ae","nodeType":3,"position":{"x":-1186.6666259765625,"y":-2011.3333740234375},"targetType":1,"assetTags":{"Tags":[]},"grantedTags":{"Tags":[]},"applicationRequiredTags":{"Tags":[]},"applicationImmunityTags":{"Tags":[]},"removeGameEffectsWithTags":{"Tags":[]},"durationType":0,"duration":"0","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[{"attrType":100,"operation":0,"magnitudeSourceType":0,"fixedValue":10.0,"formula":"","mmcType":0,"setByCallerKey":"","mmcCaptureAttribute":200,"mmcAttributeSource":0,"mmcCoefficient":1.0,"mmcUseSnapshot":true}],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"Tags":[]},"cancelOnAbilityEnd":true}</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
@@ -2511,7 +2511,7 @@
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>{"guid":"764289ea-065e-4f48-afc0-0f6963d18d57","nodeType":14,"position":{"x":492.00003051757813,"y":-1539.3333740234375},"targetType":1,"requiredTags":{"_tags":[]},"immunityTags":{"_tags":[]},"destroyWithNode":false,"positionSource":2,"positionBindingName":"head","textType":0,"fixedText":"","contextDataKey":"DamageResult","textColor":{"r":1.0,"g":0.0,"b":0.0,"a":1.0},"criticalColor":{"r":1.0,"g":0.5,"b":0.0,"a":1.0},"missColor":{"r":0.5,"g":0.5,"b":0.5,"a":1.0},"fontSize":5.0,"criticalFontSize":60.0,"duration":1.5,"offset":{"x":0.0,"y":0.0},"moveDirection":{"x":0.0,"y":1.0}}</t>
+          <t>{"guid":"764289ea-065e-4f48-afc0-0f6963d18d57","nodeType":14,"position":{"x":492.00003051757813,"y":-1539.3333740234375},"targetType":1,"requiredTags":{"Tags":[]},"immunityTags":{"Tags":[]},"destroyWithNode":false,"positionSource":2,"positionBindingName":"head","textType":0,"fixedText":"","contextDataKey":"DamageResult","textColor":{"r":1.0,"g":0.0,"b":0.0,"a":1.0},"criticalColor":{"r":1.0,"g":0.5,"b":0.0,"a":1.0},"missColor":{"r":0.5,"g":0.5,"b":0.5,"a":1.0},"fontSize":5.0,"criticalFontSize":60.0,"duration":1.5,"offset":{"x":0.0,"y":0.0},"moveDirection":{"x":0.0,"y":1.0}}</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
@@ -2531,7 +2531,7 @@
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>{"guid":"a32d1135-94db-4f81-95ba-9d5f105ef8d0","nodeType":1,"position":{"x":308.66665649414063,"y":-1720.0},"targetType":0,"assetTags":{"_tags":[]},"grantedTags":{"_tags":[]},"applicationRequiredTags":{"_tags":[]},"applicationImmunityTags":{"_tags":[]},"removeGameEffectsWithTags":{"_tags":[]},"durationType":0,"duration":"0","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"_tags":[]},"cancelOnAbilityEnd":true,"damageType":0,"damageSourceType":0,"damageFixedValue":1.0,"damageFormula":"","damageMMCType":0,"damageSetByCallerKey":"","damageMMCCaptureAttribute":200,"damageMMCAttributeSource":0,"damageMMCCoefficient":1.0,"damageMMCUseSnapshot":true,"damageMultiplyByStackCount":false,"damageCalculationType":0,"enableHitKnockback":false,"knockbackDistance":1.0,"knockbackSpeed":12.0}</t>
+          <t>{"guid":"a32d1135-94db-4f81-95ba-9d5f105ef8d0","nodeType":1,"position":{"x":308.66665649414063,"y":-1720.0},"targetType":0,"assetTags":{"Tags":[]},"grantedTags":{"Tags":[]},"applicationRequiredTags":{"Tags":[]},"applicationImmunityTags":{"Tags":[]},"removeGameEffectsWithTags":{"Tags":[]},"durationType":0,"duration":"0","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"Tags":[]},"cancelOnAbilityEnd":true,"damageType":0,"damageSourceType":0,"damageFixedValue":1.0,"damageFormula":"","damageMMCType":0,"damageSetByCallerKey":"","damageMMCCaptureAttribute":200,"damageMMCAttributeSource":0,"damageMMCCoefficient":1.0,"damageMMCUseSnapshot":true,"damageMultiplyByStackCount":false,"damageCalculationType":0,"enableHitKnockback":false,"knockbackDistance":1.0,"knockbackSpeed":12.0}</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>{"guid":"c28fb88d-51b1-47b2-be59-859e0ac638e3","nodeType":10,"position":{"x":-1186.6666259765625,"y":-1747.3333740234375},"targetType":1,"assetTags":{"_tags":[]},"grantedTags":{"_tags":[{"_name":"CD.Wind","_hashCode":1982736573,"_shortName":"Wind","_ancestorHashCodes":[-1137859925],"_ancestorNames":["CD"]}]},"applicationRequiredTags":{"_tags":[]},"applicationImmunityTags":{"_tags":[]},"removeGameEffectsWithTags":{"_tags":[]},"durationType":1,"duration":"15","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"_tags":[]},"cancelOnAbilityEnd":false,"cooldownType":0,"maxCharges":2,"chargeTime":"10"}</t>
+          <t>{"guid":"c28fb88d-51b1-47b2-be59-859e0ac638e3","nodeType":10,"position":{"x":-1186.6666259765625,"y":-1747.3333740234375},"targetType":1,"assetTags":{"Tags":[]},"grantedTags":{"Tags":[{"Name":"CD.Wind","HashCode":1982736573,"ShortName":"Wind","AncestorHashCodes":[-1137859925],"AncestorNames":["CD"]}]},"applicationRequiredTags":{"Tags":[]},"applicationImmunityTags":{"Tags":[]},"removeGameEffectsWithTags":{"Tags":[]},"durationType":1,"duration":"15","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"Tags":[]},"cancelOnAbilityEnd":false,"cooldownType":0,"maxCharges":2,"chargeTime":"10"}</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
@@ -2591,7 +2591,7 @@
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>{"guid":"d8847c3e-459e-4589-a96b-37ebb5ec458b","nodeType":21,"position":{"x":-308.66665649414063,"y":-1769.3333740234375},"targetType":1,"assetTags":{"_tags":[]},"grantedTags":{"_tags":[]},"applicationRequiredTags":{"_tags":[]},"applicationImmunityTags":{"_tags":[]},"removeGameEffectsWithTags":{"_tags":[]},"durationType":2,"duration":"0","isPeriodic":true,"period":"0.3","executeOnApplication":false,"attributeModifiers":[],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"_tags":[]},"cancelOnAbilityEnd":true}</t>
+          <t>{"guid":"d8847c3e-459e-4589-a96b-37ebb5ec458b","nodeType":21,"position":{"x":-308.66665649414063,"y":-1769.3333740234375},"targetType":1,"assetTags":{"Tags":[]},"grantedTags":{"Tags":[]},"applicationRequiredTags":{"Tags":[]},"applicationImmunityTags":{"Tags":[]},"removeGameEffectsWithTags":{"Tags":[]},"durationType":2,"duration":"0","isPeriodic":true,"period":"0.3","executeOnApplication":false,"attributeModifiers":[],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"Tags":[]},"cancelOnAbilityEnd":true}</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
@@ -2611,7 +2611,7 @@
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>{"guid":"e33ab94c-1496-4d6a-ba5e-1afd38bb0c30","nodeType":4,"position":{"x":27.333343505859375,"y":-1769.3333740234375},"targetType":1,"searchShapeType":0,"searchLineType":0,"positionSource":0,"positionBindingName":"center","searchCircleRadius":2.5,"searchSectorRadius":2.0,"searchSectorAngle":180.0,"searchLineDirectionOffsetAngle":0.0,"searchLineDirectionWidth":1.0,"searchLineDirectionLength":10.0,"lineStartPositionSource":0,"lineStartBindingName":"","lineEndPositionSource":1,"lineEndBindingName":"","searchLineBetweenWidth":1.0,"searchLineAbsoluteAngle":0.0,"searchLineAbsoluteWidth":1.0,"searchLineAbsoluteLength":10.0,"maxTargets":999,"searchTargetTags":{"_tags":[{"_name":"unitType.monster","_hashCode":-2021655864,"_shortName":"monster","_ancestorHashCodes":[1600484460],"_ancestorNames":["unitType"]}]},"searchExcludeTags":{"_tags":[]}}</t>
+          <t>{"guid":"e33ab94c-1496-4d6a-ba5e-1afd38bb0c30","nodeType":4,"position":{"x":27.333343505859375,"y":-1769.3333740234375},"targetType":1,"searchShapeType":0,"searchLineType":0,"positionSource":0,"positionBindingName":"center","searchCircleRadius":2.5,"searchSectorRadius":2.0,"searchSectorAngle":180.0,"searchLineDirectionOffsetAngle":0.0,"searchLineDirectionWidth":1.0,"searchLineDirectionLength":10.0,"lineStartPositionSource":0,"lineStartBindingName":"","lineEndPositionSource":1,"lineEndBindingName":"","searchLineBetweenWidth":1.0,"searchLineAbsoluteAngle":0.0,"searchLineAbsoluteWidth":1.0,"searchLineAbsoluteLength":10.0,"maxTargets":999,"searchTargetTags":{"Tags":[{"Name":"unitType.monster","HashCode":-2021655864,"ShortName":"monster","AncestorHashCodes":[1600484460],"AncestorNames":["unitType"]}]},"searchExcludeTags":{"Tags":[]}}</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
@@ -2651,7 +2651,7 @@
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>{"guid":"356907e0-1488-4128-bfcc-7ff73cfc3330","nodeType":0,"position":{"x":-878.6666259765625,"y":-1853.3333740234375},"targetType":1,"skillId":1004,"assetTags":{"_tags":[]},"cancelAbilitiesWithTags":{"_tags":[]},"blockAbilitiesWithTags":{"_tags":[]},"activationOwnedTags":{"_tags":[{"_name":"Skill.Running","_hashCode":-51601538,"_shortName":"Running","_ancestorHashCodes":[1312877309],"_ancestorNames":["Skill"]}]},"activationRequiredTags":{"_tags":[]},"activationBlockedTags":{"_tags":[{"_name":"CD.Wind","_hashCode":1982736573,"_shortName":"Wind","_ancestorHashCodes":[-1137859925],"_ancestorNames":["CD"]},{"_name":"Skill.Running","_hashCode":-51601538,"_shortName":"Running","_ancestorHashCodes":[1312877309],"_ancestorNames":["Skill"]}]},"ongoingBlockedTags":{"_tags":[]},"eventOutputPorts":[]}</t>
+          <t>{"guid":"356907e0-1488-4128-bfcc-7ff73cfc3330","nodeType":0,"position":{"x":-878.6666259765625,"y":-1853.3333740234375},"targetType":1,"skillId":1004,"assetTags":{"Tags":[]},"cancelAbilitiesWithTags":{"Tags":[]},"blockAbilitiesWithTags":{"Tags":[]},"activationOwnedTags":{"Tags":[{"Name":"Skill.Running","HashCode":-51601538,"ShortName":"Running","AncestorHashCodes":[1312877309],"AncestorNames":["Skill"]}]},"activationRequiredTags":{"Tags":[]},"activationBlockedTags":{"Tags":[{"Name":"CD.Wind","HashCode":1982736573,"ShortName":"Wind","AncestorHashCodes":[-1137859925],"AncestorNames":["CD"]},{"Name":"Skill.Running","HashCode":-51601538,"ShortName":"Running","AncestorHashCodes":[1312877309],"AncestorNames":["Skill"]}]},"ongoingBlockedTags":{"Tags":[]},"eventOutputPorts":[]}</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
@@ -2671,7 +2671,7 @@
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>{"guid":"cde57fb8-b693-4da8-a4a8-fd61e56c5dcd","nodeType":12,"position":{"x":677.3333740234375,"y":-1998.666748046875},"targetType":1,"requiredTags":{"_tags":[]},"immunityTags":{"_tags":[]},"destroyWithNode":true,"positionSource":0,"particleEntityId":50008,"particlePrefab":null,"particlePrefabPath":"Assets/Res/Entity/Effect/ef_zhanshi_xfz_01.prefab","particleBindingName":"down","particleOffset":{"x":0.0,"y":0.0,"z":0.0},"particleScale":{"x":1.0,"y":1.0,"z":1.0},"attachToTarget":true,"particleLoop":true}</t>
+          <t>{"guid":"cde57fb8-b693-4da8-a4a8-fd61e56c5dcd","nodeType":12,"position":{"x":677.3333740234375,"y":-1998.666748046875},"targetType":1,"requiredTags":{"Tags":[]},"immunityTags":{"Tags":[]},"destroyWithNode":true,"positionSource":0,"particleEntityId":50008,"particlePrefab":null,"particlePrefabPath":"Assets/Res/Entity/Effect/ef_zhanshi_xfz_01.prefab","particleBindingName":"down","particleOffset":{"x":0.0,"y":0.0,"z":0.0},"particleScale":{"x":1.0,"y":1.0,"z":1.0},"attachToTarget":true,"particleLoop":true}</t>
         </is>
       </c>
       <c r="G103"/>

--- a/Design/Excel/ET/Datas/Game/SkillGraph.xlsx
+++ b/Design/Excel/ET/Datas/Game/SkillGraph.xlsx
@@ -1923,16 +1923,16 @@
       </c>
       <c r="D66"/>
       <c r="E66">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>{"guid":"c28fb88d-51b1-47b2-be59-859e0ac638e3","nodeType":10,"position":{"x":-1130.6666259765625,"y":-2232.0},"targetType":1,"assetTags":{"Tags":[]},"grantedTags":{"Tags":[{"Name":"CD.Sweep","HashCode":-303359587,"ShortName":"Sweep","AncestorHashCodes":[-1137859925],"AncestorNames":["CD"]}]},"applicationRequiredTags":{"Tags":[]},"applicationImmunityTags":{"Tags":[]},"removeGameEffectsWithTags":{"Tags":[]},"durationType":1,"duration":"1","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"Tags":[]},"cancelOnAbilityEnd":false,"cooldownType":0,"maxCharges":2,"chargeTime":"10"}</t>
+          <t>{"guid":"356907e0-1488-4128-bfcc-7ff73cfc3330","nodeType":0,"position":{"x":-843.3333740234375,"y":-2480.0},"targetType":1,"skillId":1001,"assetTags":{"Tags":[]},"cancelAbilitiesWithTags":{"Tags":[]},"blockAbilitiesWithTags":{"Tags":[]},"activationOwnedTags":{"Tags":[]},"activationRequiredTags":{"Tags":[]},"activationBlockedTags":{"Tags":[{"Name":"CD.Sweep","HashCode":-303359587,"ShortName":"Sweep","AncestorHashCodes":[-1137859925],"AncestorNames":["CD"]}]},"ongoingBlockedTags":{"Tags":[]},"eventOutputPorts":[]}</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>{"outputNodeGuid":"356907e0-1488-4128-bfcc-7ff73cfc3330","outputPortId":1002,"inputNodeGuid":"432ff1e3-b18d-476d-af80-d39ddc07402a","inputPortId":7001}</t>
+          <t>{"outputNodeGuid":"356907e0-1488-4128-bfcc-7ff73cfc3330","outputPortId":1004,"inputNodeGuid":"c28fb88d-51b1-47b2-be59-859e0ac638e3","inputPortId":7001}</t>
         </is>
       </c>
       <c r="H66"/>
@@ -1943,16 +1943,16 @@
       <c r="C67"/>
       <c r="D67"/>
       <c r="E67">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>{"guid":"432ff1e3-b18d-476d-af80-d39ddc07402a","nodeType":20,"position":{"x":-415.33331298828125,"y":-2827.333251953125},"targetType":1,"skeletonDataAsset":null,"skeletonDataAssetPath":"Assets/Res/Spine/SP_Zhanshi/SP_Zhanshi_SkeletonData.asset","animationName":"Skill_attack_1001","animationDuration":"18","isAnimationLooping":false,"timeEffects":[{"triggerTime":7,"portIdValue":2315086,"legacyPortId":"de0ba361-3aba-4ef0-bb07-9b418fcae591"},{"triggerTime":18,"portIdValue":2649436,"legacyPortId":"84e238a8-5baf-470e-829f-186695064945"}],"timeCues":[{"startTime":7,"endTime":48,"portIdValue":2287012,"legacyPortId":"8dea1941-c520-4f9a-aee0-40932c8542ef"}]}</t>
+          <t>{"guid":"2cfdacd2-0186-49dd-b177-4eb8c0ad87bd","nodeType":7,"position":{"x":731.3333740234375,"y":-2142.66650390625},"targetType":1,"endType":0}</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>{"outputNodeGuid":"356907e0-1488-4128-bfcc-7ff73cfc3330","outputPortId":1004,"inputNodeGuid":"c28fb88d-51b1-47b2-be59-859e0ac638e3","inputPortId":7001}</t>
+          <t>{"outputNodeGuid":"356907e0-1488-4128-bfcc-7ff73cfc3330","outputPortId":1003,"inputNodeGuid":"9d6f459d-b588-4b64-843b-1b71e8f299ae","inputPortId":7001}</t>
         </is>
       </c>
       <c r="H67"/>
@@ -1963,16 +1963,16 @@
       <c r="C68"/>
       <c r="D68"/>
       <c r="E68">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>{"guid":"9d6f459d-b588-4b64-843b-1b71e8f299ae","nodeType":3,"position":{"x":-1130.6666259765625,"y":-2479.333251953125},"targetType":1,"assetTags":{"Tags":[]},"grantedTags":{"Tags":[]},"applicationRequiredTags":{"Tags":[]},"applicationImmunityTags":{"Tags":[]},"removeGameEffectsWithTags":{"Tags":[]},"durationType":0,"duration":"0","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[{"attrType":1003,"operation":0,"magnitudeSourceType":0,"fixedValue":-10.0,"formula":"","mmcType":0,"setByCallerKey":"","mmcCaptureAttribute":200,"mmcAttributeSource":0,"mmcCoefficient":1.0,"mmcUseSnapshot":true}],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"Tags":[]},"cancelOnAbilityEnd":true}</t>
+          <t>{"guid":"c353e286-8ef0-460a-b917-887f2aeb390a","nodeType":14,"position":{"x":1213.3333740234375,"y":-2354.66650390625},"targetType":1,"requiredTags":{"Tags":[]},"immunityTags":{"Tags":[]},"destroyWithNode":false,"positionSource":2,"positionBindingName":"head","textType":0,"fixedText":"","contextDataKey":"DamageResult","textColor":{"r":1.0,"g":0.0,"b":0.0,"a":1.0},"criticalColor":{"r":1.0,"g":0.5,"b":0.0,"a":1.0},"missColor":{"r":0.5,"g":0.5,"b":0.5,"a":1.0},"fontSize":5.0,"criticalFontSize":60.0,"duration":1.5,"offset":{"x":0.0,"y":0.0},"moveDirection":{"x":0.0,"y":1.0}}</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>{"outputNodeGuid":"356907e0-1488-4128-bfcc-7ff73cfc3330","outputPortId":1003,"inputNodeGuid":"9d6f459d-b588-4b64-843b-1b71e8f299ae","inputPortId":7001}</t>
+          <t>{"outputNodeGuid":"e33ab94c-1496-4d6a-ba5e-1afd38bb0c30","outputPortId":4001,"inputNodeGuid":"f8947676-1084-4228-b991-1509cc7fe851","inputPortId":7001}</t>
         </is>
       </c>
       <c r="H68"/>
@@ -1983,16 +1983,16 @@
       <c r="C69"/>
       <c r="D69"/>
       <c r="E69">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>{"guid":"356907e0-1488-4128-bfcc-7ff73cfc3330","nodeType":0,"position":{"x":-843.3333740234375,"y":-2480.0},"targetType":1,"skillId":1001,"assetTags":{"Tags":[]},"cancelAbilitiesWithTags":{"Tags":[]},"blockAbilitiesWithTags":{"Tags":[]},"activationOwnedTags":{"Tags":[]},"activationRequiredTags":{"Tags":[]},"activationBlockedTags":{"Tags":[{"Name":"CD.Sweep","HashCode":-303359587,"ShortName":"Sweep","AncestorHashCodes":[-1137859925],"AncestorNames":["CD"]}]},"ongoingBlockedTags":{"Tags":[]},"eventOutputPorts":[]}</t>
+          <t>{"guid":"f8947676-1084-4228-b991-1509cc7fe851","nodeType":1,"position":{"x":975.3333740234375,"y":-2344.0},"targetType":0,"assetTags":{"Tags":[]},"grantedTags":{"Tags":[]},"applicationRequiredTags":{"Tags":[]},"applicationImmunityTags":{"Tags":[]},"removeGameEffectsWithTags":{"Tags":[]},"durationType":0,"duration":"0","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"Tags":[]},"cancelOnAbilityEnd":true,"damageType":1,"damageSourceType":0,"damageFixedValue":10.0,"damageFormula":"","damageMMCType":0,"damageSetByCallerKey":"","damageMMCCaptureAttribute":1006,"damageMMCAttributeSource":0,"damageMMCCoefficient":1.0,"damageMMCUseSnapshot":true,"damageMultiplyByStackCount":false,"damageCalculationType":0,"enableHitKnockback":false,"knockbackDistance":1.0,"knockbackSpeed":12.0}</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>{"outputNodeGuid":"e33ab94c-1496-4d6a-ba5e-1afd38bb0c30","outputPortId":4001,"inputNodeGuid":"f8947676-1084-4228-b991-1509cc7fe851","inputPortId":7001}</t>
+          <t>{"outputNodeGuid":"f8947676-1084-4228-b991-1509cc7fe851","outputPortId":3004,"inputNodeGuid":"c353e286-8ef0-460a-b917-887f2aeb390a","inputPortId":7001}</t>
         </is>
       </c>
       <c r="H69"/>
@@ -2003,16 +2003,16 @@
       <c r="C70"/>
       <c r="D70"/>
       <c r="E70">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>{"guid":"f8947676-1084-4228-b991-1509cc7fe851","nodeType":1,"position":{"x":974.666748046875,"y":-2340.66650390625},"targetType":0,"assetTags":{"Tags":[]},"grantedTags":{"Tags":[]},"applicationRequiredTags":{"Tags":[]},"applicationImmunityTags":{"Tags":[]},"removeGameEffectsWithTags":{"Tags":[]},"durationType":0,"duration":"0","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"Tags":[]},"cancelOnAbilityEnd":true,"damageType":0,"damageSourceType":2,"damageFixedValue":10.0,"damageFormula":"","damageMMCType":0,"damageSetByCallerKey":"","damageMMCCaptureAttribute":1006,"damageMMCAttributeSource":0,"damageMMCCoefficient":1.0,"damageMMCUseSnapshot":true,"damageMultiplyByStackCount":false,"damageCalculationType":0,"enableHitKnockback":true,"knockbackDistance":1.0,"knockbackSpeed":12.0}</t>
+          <t>{"guid":"e33ab94c-1496-4d6a-ba5e-1afd38bb0c30","nodeType":4,"position":{"x":731.3333740234375,"y":-2344.0},"targetType":1,"searchShapeType":0,"searchLineType":0,"positionSource":0,"positionBindingName":"center","searchCircleRadius":5.0,"searchSectorRadius":5.0,"searchSectorAngle":180.0,"searchLineDirectionOffsetAngle":0.0,"searchLineDirectionWidth":1.0,"searchLineDirectionLength":10.0,"lineStartPositionSource":0,"lineStartBindingName":"","lineEndPositionSource":1,"lineEndBindingName":"","searchLineBetweenWidth":1.0,"searchLineAbsoluteAngle":0.0,"searchLineAbsoluteWidth":1.0,"searchLineAbsoluteLength":10.0,"maxTargets":1,"searchTargetTags":{"Tags":[{"Name":"unitType.monster","HashCode":-2021655864,"ShortName":"monster","AncestorHashCodes":[1600484460],"AncestorNames":["unitType"]}]},"searchExcludeTags":{"Tags":[]}}</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>{"outputNodeGuid":"f8947676-1084-4228-b991-1509cc7fe851","outputPortId":3004,"inputNodeGuid":"c353e286-8ef0-460a-b917-887f2aeb390a","inputPortId":7001}</t>
+          <t>{"outputNodeGuid":"79dea24a-eaf5-45f2-b5a0-cbb8c4ad6df2","outputPortId":2867116,"inputNodeGuid":"e33ab94c-1496-4d6a-ba5e-1afd38bb0c30","inputPortId":7001}</t>
         </is>
       </c>
       <c r="H70"/>
@@ -2023,16 +2023,16 @@
       <c r="C71"/>
       <c r="D71"/>
       <c r="E71">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>{"guid":"e33ab94c-1496-4d6a-ba5e-1afd38bb0c30","nodeType":4,"position":{"x":731.3333740234375,"y":-2344.0},"targetType":1,"searchShapeType":1,"searchLineType":0,"positionSource":0,"positionBindingName":"center","searchCircleRadius":5.0,"searchSectorRadius":5.0,"searchSectorAngle":180.0,"searchLineDirectionOffsetAngle":0.0,"searchLineDirectionWidth":1.0,"searchLineDirectionLength":10.0,"lineStartPositionSource":0,"lineStartBindingName":"","lineEndPositionSource":1,"lineEndBindingName":"","searchLineBetweenWidth":1.0,"searchLineAbsoluteAngle":0.0,"searchLineAbsoluteWidth":1.0,"searchLineAbsoluteLength":10.0,"maxTargets":999,"searchTargetTags":{"Tags":[{"Name":"unitType.monster","HashCode":-2021655864,"ShortName":"monster","AncestorHashCodes":[1600484460],"AncestorNames":["unitType"]}]},"searchExcludeTags":{"Tags":[]}}</t>
+          <t>{"guid":"c28fb88d-51b1-47b2-be59-859e0ac638e3","nodeType":10,"position":{"x":-843.3333740234375,"y":-2243.333251953125},"targetType":1,"assetTags":{"Tags":[]},"grantedTags":{"Tags":[{"Name":"CD.Sweep","HashCode":-303359587,"ShortName":"Sweep","AncestorHashCodes":[-1137859925],"AncestorNames":["CD"]}]},"applicationRequiredTags":{"Tags":[]},"applicationImmunityTags":{"Tags":[]},"removeGameEffectsWithTags":{"Tags":[]},"durationType":1,"duration":"1","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"Tags":[]},"cancelOnAbilityEnd":false,"cooldownType":0,"maxCharges":2,"chargeTime":"10"}</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>{"outputNodeGuid":"432ff1e3-b18d-476d-af80-d39ddc07402a","outputPortId":2287012,"inputNodeGuid":"cde57fb8-b693-4da8-a4a8-fd61e56c5dcd","inputPortId":7001}</t>
+          <t>{"outputNodeGuid":"79dea24a-eaf5-45f2-b5a0-cbb8c4ad6df2","outputPortId":2095095,"inputNodeGuid":"2cfdacd2-0186-49dd-b177-4eb8c0ad87bd","inputPortId":7001}</t>
         </is>
       </c>
       <c r="H71"/>
@@ -2043,16 +2043,16 @@
       <c r="C72"/>
       <c r="D72"/>
       <c r="E72">
-        <v>7</v>
+        <v>23</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>{"guid":"2cfdacd2-0186-49dd-b177-4eb8c0ad87bd","nodeType":7,"position":{"x":731.3333740234375,"y":-2142.66650390625},"targetType":1,"endType":0}</t>
+          <t>{"guid":"79dea24a-eaf5-45f2-b5a0-cbb8c4ad6df2","nodeType":23,"position":{"x":-460.66665649414063,"y":-2684.0},"targetType":1,"animationPrefab":null,"animationPrefabPath":"Assets/Res/UI/UIEntity/UIHeadItem.prefab","animationComponentPath":"UIHeadItem(Clone)/Root_Animation","animationName":"Attack","animationDuration":"10","isAnimationLooping":false,"timeEffects":[{"triggerTime":3,"portIdValue":2867116,"legacyPortId":""},{"triggerTime":10,"portIdValue":2095095,"legacyPortId":""}],"timeCues":[{"startTime":0,"endTime":41,"portIdValue":2893914,"legacyPortId":""}]}</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>{"outputNodeGuid":"432ff1e3-b18d-476d-af80-d39ddc07402a","outputPortId":2315086,"inputNodeGuid":"e33ab94c-1496-4d6a-ba5e-1afd38bb0c30","inputPortId":7001}</t>
+          <t>{"outputNodeGuid":"79dea24a-eaf5-45f2-b5a0-cbb8c4ad6df2","outputPortId":2893914,"inputNodeGuid":"cde57fb8-b693-4da8-a4a8-fd61e56c5dcd","inputPortId":7001}</t>
         </is>
       </c>
       <c r="H72"/>
@@ -2067,12 +2067,12 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>{"guid":"cde57fb8-b693-4da8-a4a8-fd61e56c5dcd","nodeType":12,"position":{"x":731.3333740234375,"y":-2491.333251953125},"targetType":1,"requiredTags":{"Tags":[]},"immunityTags":{"Tags":[]},"destroyWithNode":false,"positionSource":0,"particleEntityId":50006,"particlePrefab":null,"particlePrefabPath":"Assets/Res/Entity/Effect/ef_Zhanshi_attack_02.prefab","particleBindingName":"down","particleOffset":{"x":5.0,"y":0.0,"z":0.0},"particleScale":{"x":1.0,"y":1.0,"z":1.0},"attachToTarget":false,"particleLoop":false}</t>
+          <t>{"guid":"cde57fb8-b693-4da8-a4a8-fd61e56c5dcd","nodeType":12,"position":{"x":821.3333740234375,"y":-2600.66650390625},"targetType":1,"requiredTags":{"Tags":[]},"immunityTags":{"Tags":[]},"destroyWithNode":false,"positionSource":0,"particleEntityId":50006,"particlePrefab":null,"particlePrefabPath":"Assets/Res/Entity/Effect/ef_Zhanshi_attack_02.prefab","particleBindingName":"down","particleOffset":{"x":5.0,"y":0.0,"z":0.0},"particleScale":{"x":1.0,"y":1.0,"z":1.0},"attachToTarget":false,"particleLoop":false}</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>{"outputNodeGuid":"432ff1e3-b18d-476d-af80-d39ddc07402a","outputPortId":2649436,"inputNodeGuid":"2cfdacd2-0186-49dd-b177-4eb8c0ad87bd","inputPortId":7001}</t>
+          <t>{"outputNodeGuid":"356907e0-1488-4128-bfcc-7ff73cfc3330","outputPortId":1002,"inputNodeGuid":"79dea24a-eaf5-45f2-b5a0-cbb8c4ad6df2","inputPortId":7001}</t>
         </is>
       </c>
       <c r="H73"/>
@@ -2083,11 +2083,11 @@
       <c r="C74"/>
       <c r="D74"/>
       <c r="E74">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>{"guid":"c353e286-8ef0-460a-b917-887f2aeb390a","nodeType":14,"position":{"x":1213.3333740234375,"y":-2354.66650390625},"targetType":1,"requiredTags":{"Tags":[]},"immunityTags":{"Tags":[]},"destroyWithNode":false,"positionSource":2,"positionBindingName":"head","textType":0,"fixedText":"","contextDataKey":"DamageResult","textColor":{"r":1.0,"g":0.0,"b":0.0,"a":1.0},"criticalColor":{"r":1.0,"g":0.5,"b":0.0,"a":1.0},"missColor":{"r":0.5,"g":0.5,"b":0.5,"a":1.0},"fontSize":5.0,"criticalFontSize":60.0,"duration":1.5,"offset":{"x":0.0,"y":0.0},"moveDirection":{"x":0.0,"y":1.0}}</t>
+          <t>{"guid":"9d6f459d-b588-4b64-843b-1b71e8f299ae","nodeType":3,"position":{"x":-1130.6666259765625,"y":-2479.333251953125},"targetType":1,"assetTags":{"Tags":[]},"grantedTags":{"Tags":[]},"applicationRequiredTags":{"Tags":[]},"applicationImmunityTags":{"Tags":[]},"removeGameEffectsWithTags":{"Tags":[]},"durationType":0,"duration":"0","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[{"attrType":1003,"operation":0,"magnitudeSourceType":0,"fixedValue":-10.0,"formula":"","mmcType":0,"setByCallerKey":"","mmcCaptureAttribute":200,"mmcAttributeSource":0,"mmcCoefficient":1.0,"mmcUseSnapshot":true}],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"Tags":[]},"cancelOnAbilityEnd":true}</t>
         </is>
       </c>
       <c r="G74"/>
@@ -2507,11 +2507,11 @@
       <c r="C95"/>
       <c r="D95"/>
       <c r="E95">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>{"guid":"764289ea-065e-4f48-afc0-0f6963d18d57","nodeType":14,"position":{"x":492.00003051757813,"y":-1539.3333740234375},"targetType":1,"requiredTags":{"Tags":[]},"immunityTags":{"Tags":[]},"destroyWithNode":false,"positionSource":2,"positionBindingName":"head","textType":0,"fixedText":"","contextDataKey":"DamageResult","textColor":{"r":1.0,"g":0.0,"b":0.0,"a":1.0},"criticalColor":{"r":1.0,"g":0.5,"b":0.0,"a":1.0},"missColor":{"r":0.5,"g":0.5,"b":0.5,"a":1.0},"fontSize":5.0,"criticalFontSize":60.0,"duration":1.5,"offset":{"x":0.0,"y":0.0},"moveDirection":{"x":0.0,"y":1.0}}</t>
+          <t>{"guid":"c28fb88d-51b1-47b2-be59-859e0ac638e3","nodeType":10,"position":{"x":-1186.6666259765625,"y":-1747.3333740234375},"targetType":1,"assetTags":{"Tags":[]},"grantedTags":{"Tags":[{"Name":"CD.Wind","HashCode":1982736573,"ShortName":"Wind","AncestorHashCodes":[-1137859925],"AncestorNames":["CD"]}]},"applicationRequiredTags":{"Tags":[]},"applicationImmunityTags":{"Tags":[]},"removeGameEffectsWithTags":{"Tags":[]},"durationType":1,"duration":"15","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"Tags":[]},"cancelOnAbilityEnd":false,"cooldownType":0,"maxCharges":2,"chargeTime":"10"}</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
@@ -2527,11 +2527,11 @@
       <c r="C96"/>
       <c r="D96"/>
       <c r="E96">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>{"guid":"a32d1135-94db-4f81-95ba-9d5f105ef8d0","nodeType":1,"position":{"x":308.66665649414063,"y":-1720.0},"targetType":0,"assetTags":{"Tags":[]},"grantedTags":{"Tags":[]},"applicationRequiredTags":{"Tags":[]},"applicationImmunityTags":{"Tags":[]},"removeGameEffectsWithTags":{"Tags":[]},"durationType":0,"duration":"0","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"Tags":[]},"cancelOnAbilityEnd":true,"damageType":0,"damageSourceType":0,"damageFixedValue":1.0,"damageFormula":"","damageMMCType":0,"damageSetByCallerKey":"","damageMMCCaptureAttribute":200,"damageMMCAttributeSource":0,"damageMMCCoefficient":1.0,"damageMMCUseSnapshot":true,"damageMultiplyByStackCount":false,"damageCalculationType":0,"enableHitKnockback":false,"knockbackDistance":1.0,"knockbackSpeed":12.0}</t>
+          <t>{"guid":"e33ab94c-1496-4d6a-ba5e-1afd38bb0c30","nodeType":4,"position":{"x":-182.0,"y":-1784.0},"targetType":1,"searchShapeType":0,"searchLineType":0,"positionSource":0,"positionBindingName":"center","searchCircleRadius":2.5,"searchSectorRadius":2.0,"searchSectorAngle":180.0,"searchLineDirectionOffsetAngle":0.0,"searchLineDirectionWidth":1.0,"searchLineDirectionLength":10.0,"lineStartPositionSource":0,"lineStartBindingName":"","lineEndPositionSource":1,"lineEndBindingName":"","searchLineBetweenWidth":1.0,"searchLineAbsoluteAngle":0.0,"searchLineAbsoluteWidth":1.0,"searchLineAbsoluteLength":10.0,"maxTargets":999,"searchTargetTags":{"Tags":[{"Name":"unitType.monster","HashCode":-2021655864,"ShortName":"monster","AncestorHashCodes":[1600484460],"AncestorNames":["unitType"]}]},"searchExcludeTags":{"Tags":[]}}</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
@@ -2547,11 +2547,11 @@
       <c r="C97"/>
       <c r="D97"/>
       <c r="E97">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>{"guid":"c28fb88d-51b1-47b2-be59-859e0ac638e3","nodeType":10,"position":{"x":-1186.6666259765625,"y":-1747.3333740234375},"targetType":1,"assetTags":{"Tags":[]},"grantedTags":{"Tags":[{"Name":"CD.Wind","HashCode":1982736573,"ShortName":"Wind","AncestorHashCodes":[-1137859925],"AncestorNames":["CD"]}]},"applicationRequiredTags":{"Tags":[]},"applicationImmunityTags":{"Tags":[]},"removeGameEffectsWithTags":{"Tags":[]},"durationType":1,"duration":"15","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"Tags":[]},"cancelOnAbilityEnd":false,"cooldownType":0,"maxCharges":2,"chargeTime":"10"}</t>
+          <t>{"guid":"a32d1135-94db-4f81-95ba-9d5f105ef8d0","nodeType":1,"position":{"x":93.333343505859375,"y":-1784.0},"targetType":0,"assetTags":{"Tags":[]},"grantedTags":{"Tags":[]},"applicationRequiredTags":{"Tags":[]},"applicationImmunityTags":{"Tags":[]},"removeGameEffectsWithTags":{"Tags":[]},"durationType":0,"duration":"0","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"Tags":[]},"cancelOnAbilityEnd":true,"damageType":0,"damageSourceType":0,"damageFixedValue":1.0,"damageFormula":"","damageMMCType":0,"damageSetByCallerKey":"","damageMMCCaptureAttribute":200,"damageMMCAttributeSource":0,"damageMMCCoefficient":1.0,"damageMMCUseSnapshot":true,"damageMultiplyByStackCount":false,"damageCalculationType":0,"enableHitKnockback":false,"knockbackDistance":1.0,"knockbackSpeed":12.0}</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
@@ -2567,11 +2567,11 @@
       <c r="C98"/>
       <c r="D98"/>
       <c r="E98">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>{"guid":"f73ba91e-a76b-456c-b19c-a5176809d5f5","nodeType":7,"position":{"x":700.0,"y":-1856.666748046875},"targetType":1,"endType":0}</t>
+          <t>{"guid":"764289ea-065e-4f48-afc0-0f6963d18d57","nodeType":14,"position":{"x":306.66665649414063,"y":-1784.0},"targetType":1,"requiredTags":{"Tags":[]},"immunityTags":{"Tags":[]},"destroyWithNode":false,"positionSource":2,"positionBindingName":"head","textType":0,"fixedText":"","contextDataKey":"DamageResult","textColor":{"r":1.0,"g":0.0,"b":0.0,"a":1.0},"criticalColor":{"r":1.0,"g":0.5,"b":0.0,"a":1.0},"missColor":{"r":0.5,"g":0.5,"b":0.5,"a":1.0},"fontSize":5.0,"criticalFontSize":60.0,"duration":1.5,"offset":{"x":0.0,"y":0.0},"moveDirection":{"x":0.0,"y":1.0}}</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
@@ -2591,7 +2591,7 @@
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>{"guid":"d8847c3e-459e-4589-a96b-37ebb5ec458b","nodeType":21,"position":{"x":-308.66665649414063,"y":-1769.3333740234375},"targetType":1,"assetTags":{"Tags":[]},"grantedTags":{"Tags":[]},"applicationRequiredTags":{"Tags":[]},"applicationImmunityTags":{"Tags":[]},"removeGameEffectsWithTags":{"Tags":[]},"durationType":2,"duration":"0","isPeriodic":true,"period":"0.3","executeOnApplication":false,"attributeModifiers":[],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"Tags":[]},"cancelOnAbilityEnd":true}</t>
+          <t>{"guid":"d8847c3e-459e-4589-a96b-37ebb5ec458b","nodeType":21,"position":{"x":-572.0,"y":-1804.0},"targetType":1,"assetTags":{"Tags":[]},"grantedTags":{"Tags":[]},"applicationRequiredTags":{"Tags":[]},"applicationImmunityTags":{"Tags":[]},"removeGameEffectsWithTags":{"Tags":[]},"durationType":2,"duration":"0","isPeriodic":true,"period":"0.3","executeOnApplication":false,"attributeModifiers":[],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"Tags":[]},"cancelOnAbilityEnd":true}</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
@@ -2607,11 +2607,11 @@
       <c r="C100"/>
       <c r="D100"/>
       <c r="E100">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>{"guid":"e33ab94c-1496-4d6a-ba5e-1afd38bb0c30","nodeType":4,"position":{"x":27.333343505859375,"y":-1769.3333740234375},"targetType":1,"searchShapeType":0,"searchLineType":0,"positionSource":0,"positionBindingName":"center","searchCircleRadius":2.5,"searchSectorRadius":2.0,"searchSectorAngle":180.0,"searchLineDirectionOffsetAngle":0.0,"searchLineDirectionWidth":1.0,"searchLineDirectionLength":10.0,"lineStartPositionSource":0,"lineStartBindingName":"","lineEndPositionSource":1,"lineEndBindingName":"","searchLineBetweenWidth":1.0,"searchLineAbsoluteAngle":0.0,"searchLineAbsoluteWidth":1.0,"searchLineAbsoluteLength":10.0,"maxTargets":999,"searchTargetTags":{"Tags":[{"Name":"unitType.monster","HashCode":-2021655864,"ShortName":"monster","AncestorHashCodes":[1600484460],"AncestorNames":["unitType"]}]},"searchExcludeTags":{"Tags":[]}}</t>
+          <t>{"guid":"356907e0-1488-4128-bfcc-7ff73cfc3330","nodeType":0,"position":{"x":-911.3333740234375,"y":-2121.333251953125},"targetType":1,"skillId":1004,"assetTags":{"Tags":[]},"cancelAbilitiesWithTags":{"Tags":[]},"blockAbilitiesWithTags":{"Tags":[]},"activationOwnedTags":{"Tags":[{"Name":"Skill.Running","HashCode":-51601538,"ShortName":"Running","AncestorHashCodes":[1312877309],"AncestorNames":["Skill"]}]},"activationRequiredTags":{"Tags":[]},"activationBlockedTags":{"Tags":[{"Name":"CD.Wind","HashCode":1982736573,"ShortName":"Wind","AncestorHashCodes":[-1137859925],"AncestorNames":["CD"]},{"Name":"Skill.Running","HashCode":-51601538,"ShortName":"Running","AncestorHashCodes":[1312877309],"AncestorNames":["Skill"]}]},"ongoingBlockedTags":{"Tags":[]},"eventOutputPorts":[]}</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
@@ -2627,11 +2627,11 @@
       <c r="C101"/>
       <c r="D101"/>
       <c r="E101">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>{"guid":"432ff1e3-b18d-476d-af80-d39ddc07402a","nodeType":20,"position":{"x":-452.0,"y":-2375.333251953125},"targetType":1,"skeletonDataAsset":null,"skeletonDataAssetPath":"Assets/Res/Spine/SP_Zhanshi/SP_Zhanshi_SkeletonData.asset","animationName":"Skill_attack_1011","animationDuration":"12","isAnimationLooping":true,"timeEffects":[{"triggerTime":250,"portIdValue":2000539,"legacyPortId":"f41c85e0-7f26-494e-9ffc-4a06c980f811"}],"timeCues":[{"startTime":0,"endTime":255,"portIdValue":2287012,"legacyPortId":"8dea1941-c520-4f9a-aee0-40932c8542ef"}]}</t>
+          <t>{"guid":"f73ba91e-a76b-456c-b19c-a5176809d5f5","nodeType":7,"position":{"x":522.0,"y":-1858.666748046875},"targetType":1,"endType":0}</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
@@ -2647,11 +2647,11 @@
       <c r="C102"/>
       <c r="D102"/>
       <c r="E102">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>{"guid":"356907e0-1488-4128-bfcc-7ff73cfc3330","nodeType":0,"position":{"x":-878.6666259765625,"y":-1853.3333740234375},"targetType":1,"skillId":1004,"assetTags":{"Tags":[]},"cancelAbilitiesWithTags":{"Tags":[]},"blockAbilitiesWithTags":{"Tags":[]},"activationOwnedTags":{"Tags":[{"Name":"Skill.Running","HashCode":-51601538,"ShortName":"Running","AncestorHashCodes":[1312877309],"AncestorNames":["Skill"]}]},"activationRequiredTags":{"Tags":[]},"activationBlockedTags":{"Tags":[{"Name":"CD.Wind","HashCode":1982736573,"ShortName":"Wind","AncestorHashCodes":[-1137859925],"AncestorNames":["CD"]},{"Name":"Skill.Running","HashCode":-51601538,"ShortName":"Running","AncestorHashCodes":[1312877309],"AncestorNames":["Skill"]}]},"ongoingBlockedTags":{"Tags":[]},"eventOutputPorts":[]}</t>
+          <t>{"guid":"cde57fb8-b693-4da8-a4a8-fd61e56c5dcd","nodeType":12,"position":{"x":522.0,"y":-2026.666748046875},"targetType":1,"requiredTags":{"Tags":[]},"immunityTags":{"Tags":[]},"destroyWithNode":true,"positionSource":0,"particleEntityId":50008,"particlePrefab":null,"particlePrefabPath":"Assets/Res/Entity/Effect/ef_zhanshi_xfz_01.prefab","particleBindingName":"down","particleOffset":{"x":0.0,"y":0.0,"z":0.0},"particleScale":{"x":1.0,"y":1.0,"z":1.0},"attachToTarget":true,"particleLoop":true}</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
@@ -2667,11 +2667,11 @@
       <c r="C103"/>
       <c r="D103"/>
       <c r="E103">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>{"guid":"cde57fb8-b693-4da8-a4a8-fd61e56c5dcd","nodeType":12,"position":{"x":677.3333740234375,"y":-1998.666748046875},"targetType":1,"requiredTags":{"Tags":[]},"immunityTags":{"Tags":[]},"destroyWithNode":true,"positionSource":0,"particleEntityId":50008,"particlePrefab":null,"particlePrefabPath":"Assets/Res/Entity/Effect/ef_zhanshi_xfz_01.prefab","particleBindingName":"down","particleOffset":{"x":0.0,"y":0.0,"z":0.0},"particleScale":{"x":1.0,"y":1.0,"z":1.0},"attachToTarget":true,"particleLoop":true}</t>
+          <t>{"guid":"432ff1e3-b18d-476d-af80-d39ddc07402a","nodeType":20,"position":{"x":-434.0,"y":-2553.333251953125},"targetType":1,"skeletonDataAsset":null,"skeletonDataAssetPath":"Assets/Res/Spine/SP_Zhanshi/SP_Zhanshi_SkeletonData.asset","animationName":"Skill_attack_1011","animationDuration":"12","isAnimationLooping":true,"timeEffects":[{"triggerTime":250,"portIdValue":2000539,"legacyPortId":"f41c85e0-7f26-494e-9ffc-4a06c980f811"}],"timeCues":[{"startTime":0,"endTime":255,"portIdValue":2287012,"legacyPortId":"8dea1941-c520-4f9a-aee0-40932c8542ef"}]}</t>
         </is>
       </c>
       <c r="G103"/>

--- a/Design/Excel/ET/Datas/Game/SkillGraph.xlsx
+++ b/Design/Excel/ET/Datas/Game/SkillGraph.xlsx
@@ -1000,7 +1000,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>{"outputNodeGuid":"356907e0-1488-4128-bfcc-7ff73cfc3330","outputPortId":1002,"inputNodeGuid":"432ff1e3-b18d-476d-af80-d39ddc07402a","inputPortId":7001}</t>
+          <t>{"outputNodeGuid":"356907e0-1488-4128-bfcc-7ff73cfc3330","outputPortId":1004,"inputNodeGuid":"c28fb88d-51b1-47b2-be59-859e0ac638e3","inputPortId":7001}</t>
         </is>
       </c>
       <c r="H20"/>
@@ -1011,16 +1011,16 @@
       <c r="C21"/>
       <c r="D21"/>
       <c r="E21">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>{"guid":"432ff1e3-b18d-476d-af80-d39ddc07402a","nodeType":20,"position":{"x":-491.33331298828125,"y":-2478.66650390625},"targetType":1,"skeletonDataAsset":null,"skeletonDataAssetPath":"Assets/Res/Spine/SP_Xiyiguai/SP_Xiyiguai_SkeletonData.asset","animationName":"Attack","animationDuration":"24","isAnimationLooping":false,"timeEffects":[{"triggerTime":11,"portIdValue":2315086,"legacyPortId":"de0ba361-3aba-4ef0-bb07-9b418fcae591"},{"triggerTime":24,"portIdValue":2715463,"legacyPortId":"7ecf9fe6-7c5e-46ae-bade-7922214225e2"}],"timeCues":[]}</t>
+          <t>{"guid":"c28fb88d-51b1-47b2-be59-859e0ac638e3","nodeType":10,"position":{"x":-1220.6666259765625,"y":-1747.3333740234375},"targetType":1,"assetTags":{"Tags":[]},"grantedTags":{"Tags":[{"Name":"CD.FireCircle","HashCode":522143731,"ShortName":"FireCircle","AncestorHashCodes":[-1137859925],"AncestorNames":["CD"]}]},"applicationRequiredTags":{"Tags":[]},"applicationImmunityTags":{"Tags":[]},"removeGameEffectsWithTags":{"Tags":[]},"durationType":1,"duration":"3","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"Tags":[]},"cancelOnAbilityEnd":false,"cooldownType":0,"maxCharges":2,"chargeTime":"10"}</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>{"outputNodeGuid":"356907e0-1488-4128-bfcc-7ff73cfc3330","outputPortId":1004,"inputNodeGuid":"c28fb88d-51b1-47b2-be59-859e0ac638e3","inputPortId":7001}</t>
+          <t>{"outputNodeGuid":"356907e0-1488-4128-bfcc-7ff73cfc3330","outputPortId":1003,"inputNodeGuid":"9d6f459d-b588-4b64-843b-1b71e8f299ae","inputPortId":7001}</t>
         </is>
       </c>
       <c r="H21"/>
@@ -1031,16 +1031,16 @@
       <c r="C22"/>
       <c r="D22"/>
       <c r="E22">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>{"guid":"c28fb88d-51b1-47b2-be59-859e0ac638e3","nodeType":10,"position":{"x":-1220.6666259765625,"y":-1747.3333740234375},"targetType":1,"assetTags":{"Tags":[]},"grantedTags":{"Tags":[{"Name":"CD.FireCircle","HashCode":522143731,"ShortName":"FireCircle","AncestorHashCodes":[-1137859925],"AncestorNames":["CD"]}]},"applicationRequiredTags":{"Tags":[]},"applicationImmunityTags":{"Tags":[]},"removeGameEffectsWithTags":{"Tags":[]},"durationType":1,"duration":"3","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"Tags":[]},"cancelOnAbilityEnd":false,"cooldownType":0,"maxCharges":2,"chargeTime":"10"}</t>
+          <t>{"guid":"9d6f459d-b588-4b64-843b-1b71e8f299ae","nodeType":3,"position":{"x":-1195.3333740234375,"y":-2003.3333740234375},"targetType":1,"assetTags":{"Tags":[]},"grantedTags":{"Tags":[]},"applicationRequiredTags":{"Tags":[]},"applicationImmunityTags":{"Tags":[]},"removeGameEffectsWithTags":{"Tags":[]},"durationType":0,"duration":"0","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[{"attrType":1003,"operation":0,"magnitudeSourceType":0,"fixedValue":-100.0,"formula":"","mmcType":0,"setByCallerKey":"","mmcCaptureAttribute":200,"mmcAttributeSource":0,"mmcCoefficient":1.0,"mmcUseSnapshot":true}],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"Tags":[]},"cancelOnAbilityEnd":true}</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>{"outputNodeGuid":"356907e0-1488-4128-bfcc-7ff73cfc3330","outputPortId":1003,"inputNodeGuid":"9d6f459d-b588-4b64-843b-1b71e8f299ae","inputPortId":7001}</t>
+          <t>{"outputNodeGuid":"90bacd9f-d882-4bba-aaa8-41ed993ac3ff","outputPortId":5001,"inputNodeGuid":"eae41233-d297-46fe-a6c8-0b5c876fbb2a","inputPortId":7001}</t>
         </is>
       </c>
       <c r="H22"/>
@@ -1051,16 +1051,16 @@
       <c r="C23"/>
       <c r="D23"/>
       <c r="E23">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>{"guid":"9d6f459d-b588-4b64-843b-1b71e8f299ae","nodeType":3,"position":{"x":-1195.3333740234375,"y":-2003.3333740234375},"targetType":1,"assetTags":{"Tags":[]},"grantedTags":{"Tags":[]},"applicationRequiredTags":{"Tags":[]},"applicationImmunityTags":{"Tags":[]},"removeGameEffectsWithTags":{"Tags":[]},"durationType":0,"duration":"0","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[{"attrType":1003,"operation":0,"magnitudeSourceType":0,"fixedValue":-100.0,"formula":"","mmcType":0,"setByCallerKey":"","mmcCaptureAttribute":200,"mmcAttributeSource":0,"mmcCoefficient":1.0,"mmcUseSnapshot":true}],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"Tags":[]},"cancelOnAbilityEnd":true}</t>
+          <t>{"guid":"eae41233-d297-46fe-a6c8-0b5c876fbb2a","nodeType":1,"position":{"x":-97.333328247070313,"y":-1810.0},"targetType":0,"assetTags":{"Tags":[]},"grantedTags":{"Tags":[]},"applicationRequiredTags":{"Tags":[]},"applicationImmunityTags":{"Tags":[]},"removeGameEffectsWithTags":{"Tags":[]},"durationType":0,"duration":"0","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"Tags":[]},"cancelOnAbilityEnd":true,"damageType":0,"damageSourceType":0,"damageFixedValue":10.0,"damageFormula":"","damageMMCType":0,"damageSetByCallerKey":"","damageMMCCaptureAttribute":200,"damageMMCAttributeSource":0,"damageMMCCoefficient":1.0,"damageMMCUseSnapshot":true,"damageMultiplyByStackCount":false,"damageCalculationType":0,"enableHitKnockback":true,"knockbackDistance":1.0,"knockbackSpeed":12.0}</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>{"outputNodeGuid":"432ff1e3-b18d-476d-af80-d39ddc07402a","outputPortId":2315086,"inputNodeGuid":"90bacd9f-d882-4bba-aaa8-41ed993ac3ff","inputPortId":7001}</t>
+          <t>{"outputNodeGuid":"eae41233-d297-46fe-a6c8-0b5c876fbb2a","outputPortId":3004,"inputNodeGuid":"2d7e41c4-8e90-4b61-879c-4b2e5b9486db","inputPortId":7001}</t>
         </is>
       </c>
       <c r="H23"/>
@@ -1071,16 +1071,16 @@
       <c r="C24"/>
       <c r="D24"/>
       <c r="E24">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>{"guid":"eae41233-d297-46fe-a6c8-0b5c876fbb2a","nodeType":1,"position":{"x":-97.333328247070313,"y":-1810.0},"targetType":0,"assetTags":{"Tags":[]},"grantedTags":{"Tags":[]},"applicationRequiredTags":{"Tags":[]},"applicationImmunityTags":{"Tags":[]},"removeGameEffectsWithTags":{"Tags":[]},"durationType":0,"duration":"0","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"Tags":[]},"cancelOnAbilityEnd":true,"damageType":0,"damageSourceType":0,"damageFixedValue":10.0,"damageFormula":"","damageMMCType":0,"damageSetByCallerKey":"","damageMMCCaptureAttribute":200,"damageMMCAttributeSource":0,"damageMMCCoefficient":1.0,"damageMMCUseSnapshot":true,"damageMultiplyByStackCount":false,"damageCalculationType":0,"enableHitKnockback":true,"knockbackDistance":1.0,"knockbackSpeed":12.0}</t>
+          <t>{"guid":"356907e0-1488-4128-bfcc-7ff73cfc3330","nodeType":0,"position":{"x":-881.3333740234375,"y":-1854.666748046875},"targetType":1,"skillId":7001,"assetTags":{"Tags":[]},"cancelAbilitiesWithTags":{"Tags":[]},"blockAbilitiesWithTags":{"Tags":[]},"activationOwnedTags":{"Tags":[]},"activationRequiredTags":{"Tags":[]},"activationBlockedTags":{"Tags":[{"Name":"CD.FireCircle","HashCode":522143731,"ShortName":"FireCircle","AncestorHashCodes":[-1137859925],"AncestorNames":["CD"]}]},"ongoingBlockedTags":{"Tags":[{"Name":"Buff.DeBuff.Stun","HashCode":1791562953,"ShortName":"Stun","AncestorHashCodes":[937056111,321157895],"AncestorNames":["Buff","Buff.DeBuff"]}]},"eventOutputPorts":[]}</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>{"outputNodeGuid":"90bacd9f-d882-4bba-aaa8-41ed993ac3ff","outputPortId":5001,"inputNodeGuid":"eae41233-d297-46fe-a6c8-0b5c876fbb2a","inputPortId":7001}</t>
+          <t>{"outputNodeGuid":"08bcef27-5270-4668-be7d-bb9e9fc01e6a","outputPortId":2131464,"inputNodeGuid":"90bacd9f-d882-4bba-aaa8-41ed993ac3ff","inputPortId":7001}</t>
         </is>
       </c>
       <c r="H24"/>
@@ -1091,16 +1091,16 @@
       <c r="C25"/>
       <c r="D25"/>
       <c r="E25">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>{"guid":"356907e0-1488-4128-bfcc-7ff73cfc3330","nodeType":0,"position":{"x":-881.3333740234375,"y":-1854.666748046875},"targetType":1,"skillId":7001,"assetTags":{"Tags":[]},"cancelAbilitiesWithTags":{"Tags":[]},"blockAbilitiesWithTags":{"Tags":[]},"activationOwnedTags":{"Tags":[]},"activationRequiredTags":{"Tags":[]},"activationBlockedTags":{"Tags":[{"Name":"CD.FireCircle","HashCode":522143731,"ShortName":"FireCircle","AncestorHashCodes":[-1137859925],"AncestorNames":["CD"]}]},"ongoingBlockedTags":{"Tags":[{"Name":"Buff.DeBuff.Stun","HashCode":1791562953,"ShortName":"Stun","AncestorHashCodes":[937056111,321157895],"AncestorNames":["Buff","Buff.DeBuff"]}]},"eventOutputPorts":[]}</t>
+          <t>{"guid":"90bacd9f-d882-4bba-aaa8-41ed993ac3ff","nodeType":8,"position":{"x":-419.33331298828125,"y":-1840.0},"targetType":2,"assetTags":{"Tags":[]},"grantedTags":{"Tags":[]},"applicationRequiredTags":{"Tags":[]},"applicationImmunityTags":{"Tags":[]},"removeGameEffectsWithTags":{"Tags":[]},"durationType":2,"duration":"0","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"Tags":[]},"cancelOnAbilityEnd":false,"launchPositionSource":0,"launchBindingName":"center","targetPositionSource":1,"targetBindingName":"center","projectileTargetType":0,"flyOver":false,"offsetAngle":0.0,"curveHeight":0.0,"projectileEntityId":50001,"projectilePrefab":null,"projectilePrefabPath":"Assets/Res/Entity/Effect/ef_fashi_gandian_buff.prefab","speed":3.0,"maxDistance":10.0,"collisionRadius":0.5,"isPiercing":false,"maxPierceCount":1,"collisionTargetTags":{"Tags":[]},"collisionExcludeTags":{"Tags":[]},"isBouncing":true,"bounceTargetMode":0,"maxBounceCount":3,"bounceSearchRadius":10.0,"canBounceToSameTarget":false,"excludeSourceCamp":true,"bounceAngleOffset":0.0}</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>{"outputNodeGuid":"432ff1e3-b18d-476d-af80-d39ddc07402a","outputPortId":2715463,"inputNodeGuid":"3aafa9a5-4766-4204-91ab-d797aeb3c0e1","inputPortId":7001}</t>
+          <t>{"outputNodeGuid":"08bcef27-5270-4668-be7d-bb9e9fc01e6a","outputPortId":2547623,"inputNodeGuid":"3aafa9a5-4766-4204-91ab-d797aeb3c0e1","inputPortId":7001}</t>
         </is>
       </c>
       <c r="H25"/>
@@ -1111,18 +1111,14 @@
       <c r="C26"/>
       <c r="D26"/>
       <c r="E26">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>{"guid":"90bacd9f-d882-4bba-aaa8-41ed993ac3ff","nodeType":8,"position":{"x":-419.33331298828125,"y":-1840.0},"targetType":2,"assetTags":{"Tags":[]},"grantedTags":{"Tags":[]},"applicationRequiredTags":{"Tags":[]},"applicationImmunityTags":{"Tags":[]},"removeGameEffectsWithTags":{"Tags":[]},"durationType":2,"duration":"0","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"Tags":[]},"cancelOnAbilityEnd":false,"launchPositionSource":0,"launchBindingName":"center","targetPositionSource":1,"targetBindingName":"center","projectileTargetType":0,"flyOver":false,"offsetAngle":0.0,"curveHeight":0.0,"projectileEntityId":50001,"projectilePrefab":null,"projectilePrefabPath":"Assets/Res/Entity/Effect/ef_fashi_gandian_buff.prefab","speed":3.0,"maxDistance":10.0,"collisionRadius":0.5,"isPiercing":false,"maxPierceCount":1,"collisionTargetTags":{"Tags":[]},"collisionExcludeTags":{"Tags":[]},"isBouncing":true,"bounceTargetMode":0,"maxBounceCount":3,"bounceSearchRadius":10.0,"canBounceToSameTarget":false,"excludeSourceCamp":true,"bounceAngleOffset":0.0}</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>{"outputNodeGuid":"eae41233-d297-46fe-a6c8-0b5c876fbb2a","outputPortId":3004,"inputNodeGuid":"2d7e41c4-8e90-4b61-879c-4b2e5b9486db","inputPortId":7001}</t>
-        </is>
-      </c>
+          <t>{"guid":"2d7e41c4-8e90-4b61-879c-4b2e5b9486db","nodeType":14,"position":{"x":180.0,"y":-1810.0},"targetType":1,"requiredTags":{"Tags":[]},"immunityTags":{"Tags":[]},"destroyWithNode":false,"positionSource":2,"positionBindingName":"head","textType":0,"fixedText":"","contextDataKey":"DamageResult","textColor":{"r":1.0,"g":0.16293229162693024,"b":0.0,"a":1.0},"criticalColor":{"r":1.0,"g":0.5,"b":0.0,"a":1.0},"missColor":{"r":0.5,"g":0.5,"b":0.5,"a":1.0},"fontSize":5.0,"criticalFontSize":60.0,"duration":1.5,"offset":{"x":0.0,"y":0.0},"moveDirection":{"x":0.0,"y":1.0}}</t>
+        </is>
+      </c>
+      <c r="G26"/>
       <c r="H26"/>
     </row>
     <row r="27">
@@ -1131,11 +1127,11 @@
       <c r="C27"/>
       <c r="D27"/>
       <c r="E27">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>{"guid":"2d7e41c4-8e90-4b61-879c-4b2e5b9486db","nodeType":14,"position":{"x":180.0,"y":-1810.0},"targetType":1,"requiredTags":{"Tags":[]},"immunityTags":{"Tags":[]},"destroyWithNode":false,"positionSource":2,"positionBindingName":"head","textType":0,"fixedText":"","contextDataKey":"DamageResult","textColor":{"r":1.0,"g":0.16293229162693024,"b":0.0,"a":1.0},"criticalColor":{"r":1.0,"g":0.5,"b":0.0,"a":1.0},"missColor":{"r":0.5,"g":0.5,"b":0.5,"a":1.0},"fontSize":5.0,"criticalFontSize":60.0,"duration":1.5,"offset":{"x":0.0,"y":0.0},"moveDirection":{"x":0.0,"y":1.0}}</t>
+          <t>{"guid":"08bcef27-5270-4668-be7d-bb9e9fc01e6a","nodeType":23,"position":{"x":-634.6666259765625,"y":-2399.333251953125},"targetType":1,"animationPrefab":null,"animationPrefabPath":"Assets/Res/UI/UIEntity/UIHeadItem.prefab","animationComponentPath":"UIHeadItem(Clone)/Root_Animation","animationName":"Attack","animationDuration":"10","isAnimationLooping":false,"timeEffects":[{"triggerTime":10,"portIdValue":2131464,"legacyPortId":""},{"triggerTime":10,"portIdValue":2547623,"legacyPortId":""}],"timeCues":[{"startTime":0,"endTime":8,"portIdValue":2247261,"legacyPortId":""}]}</t>
         </is>
       </c>
       <c r="G27"/>
@@ -1983,11 +1979,11 @@
       <c r="C69"/>
       <c r="D69"/>
       <c r="E69">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>{"guid":"f8947676-1084-4228-b991-1509cc7fe851","nodeType":1,"position":{"x":975.3333740234375,"y":-2344.0},"targetType":0,"assetTags":{"Tags":[]},"grantedTags":{"Tags":[]},"applicationRequiredTags":{"Tags":[]},"applicationImmunityTags":{"Tags":[]},"removeGameEffectsWithTags":{"Tags":[]},"durationType":0,"duration":"0","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"Tags":[]},"cancelOnAbilityEnd":true,"damageType":1,"damageSourceType":0,"damageFixedValue":10.0,"damageFormula":"","damageMMCType":0,"damageSetByCallerKey":"","damageMMCCaptureAttribute":1006,"damageMMCAttributeSource":0,"damageMMCCoefficient":1.0,"damageMMCUseSnapshot":true,"damageMultiplyByStackCount":false,"damageCalculationType":0,"enableHitKnockback":false,"knockbackDistance":1.0,"knockbackSpeed":12.0}</t>
+          <t>{"guid":"c28fb88d-51b1-47b2-be59-859e0ac638e3","nodeType":10,"position":{"x":-843.3333740234375,"y":-2243.333251953125},"targetType":1,"assetTags":{"Tags":[]},"grantedTags":{"Tags":[{"Name":"CD.Sweep","HashCode":-303359587,"ShortName":"Sweep","AncestorHashCodes":[-1137859925],"AncestorNames":["CD"]}]},"applicationRequiredTags":{"Tags":[]},"applicationImmunityTags":{"Tags":[]},"removeGameEffectsWithTags":{"Tags":[]},"durationType":1,"duration":"1","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"Tags":[]},"cancelOnAbilityEnd":false,"cooldownType":0,"maxCharges":2,"chargeTime":"10"}</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
@@ -2003,11 +1999,11 @@
       <c r="C70"/>
       <c r="D70"/>
       <c r="E70">
-        <v>4</v>
+        <v>23</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>{"guid":"e33ab94c-1496-4d6a-ba5e-1afd38bb0c30","nodeType":4,"position":{"x":731.3333740234375,"y":-2344.0},"targetType":1,"searchShapeType":0,"searchLineType":0,"positionSource":0,"positionBindingName":"center","searchCircleRadius":5.0,"searchSectorRadius":5.0,"searchSectorAngle":180.0,"searchLineDirectionOffsetAngle":0.0,"searchLineDirectionWidth":1.0,"searchLineDirectionLength":10.0,"lineStartPositionSource":0,"lineStartBindingName":"","lineEndPositionSource":1,"lineEndBindingName":"","searchLineBetweenWidth":1.0,"searchLineAbsoluteAngle":0.0,"searchLineAbsoluteWidth":1.0,"searchLineAbsoluteLength":10.0,"maxTargets":1,"searchTargetTags":{"Tags":[{"Name":"unitType.monster","HashCode":-2021655864,"ShortName":"monster","AncestorHashCodes":[1600484460],"AncestorNames":["unitType"]}]},"searchExcludeTags":{"Tags":[]}}</t>
+          <t>{"guid":"79dea24a-eaf5-45f2-b5a0-cbb8c4ad6df2","nodeType":23,"position":{"x":-460.66665649414063,"y":-2684.0},"targetType":1,"animationPrefab":null,"animationPrefabPath":"Assets/Res/UI/UIEntity/UIHeadItem.prefab","animationComponentPath":"UIHeadItem(Clone)/Root_Animation","animationName":"Attack","animationDuration":"10","isAnimationLooping":false,"timeEffects":[{"triggerTime":3,"portIdValue":2867116,"legacyPortId":""},{"triggerTime":10,"portIdValue":2095095,"legacyPortId":""}],"timeCues":[{"startTime":0,"endTime":41,"portIdValue":2893914,"legacyPortId":""}]}</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
@@ -2023,11 +2019,11 @@
       <c r="C71"/>
       <c r="D71"/>
       <c r="E71">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>{"guid":"c28fb88d-51b1-47b2-be59-859e0ac638e3","nodeType":10,"position":{"x":-843.3333740234375,"y":-2243.333251953125},"targetType":1,"assetTags":{"Tags":[]},"grantedTags":{"Tags":[{"Name":"CD.Sweep","HashCode":-303359587,"ShortName":"Sweep","AncestorHashCodes":[-1137859925],"AncestorNames":["CD"]}]},"applicationRequiredTags":{"Tags":[]},"applicationImmunityTags":{"Tags":[]},"removeGameEffectsWithTags":{"Tags":[]},"durationType":1,"duration":"1","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"Tags":[]},"cancelOnAbilityEnd":false,"cooldownType":0,"maxCharges":2,"chargeTime":"10"}</t>
+          <t>{"guid":"cde57fb8-b693-4da8-a4a8-fd61e56c5dcd","nodeType":12,"position":{"x":821.3333740234375,"y":-2600.66650390625},"targetType":1,"requiredTags":{"Tags":[]},"immunityTags":{"Tags":[]},"destroyWithNode":false,"positionSource":0,"particleEntityId":50006,"particlePrefab":null,"particlePrefabPath":"Assets/Res/Entity/Effect/ef_Zhanshi_attack_02.prefab","particleBindingName":"down","particleOffset":{"x":5.0,"y":0.0,"z":0.0},"particleScale":{"x":1.0,"y":1.0,"z":1.0},"attachToTarget":false,"particleLoop":false}</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
@@ -2043,11 +2039,11 @@
       <c r="C72"/>
       <c r="D72"/>
       <c r="E72">
-        <v>23</v>
+        <v>3</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>{"guid":"79dea24a-eaf5-45f2-b5a0-cbb8c4ad6df2","nodeType":23,"position":{"x":-460.66665649414063,"y":-2684.0},"targetType":1,"animationPrefab":null,"animationPrefabPath":"Assets/Res/UI/UIEntity/UIHeadItem.prefab","animationComponentPath":"UIHeadItem(Clone)/Root_Animation","animationName":"Attack","animationDuration":"10","isAnimationLooping":false,"timeEffects":[{"triggerTime":3,"portIdValue":2867116,"legacyPortId":""},{"triggerTime":10,"portIdValue":2095095,"legacyPortId":""}],"timeCues":[{"startTime":0,"endTime":41,"portIdValue":2893914,"legacyPortId":""}]}</t>
+          <t>{"guid":"9d6f459d-b588-4b64-843b-1b71e8f299ae","nodeType":3,"position":{"x":-1130.6666259765625,"y":-2479.333251953125},"targetType":1,"assetTags":{"Tags":[]},"grantedTags":{"Tags":[]},"applicationRequiredTags":{"Tags":[]},"applicationImmunityTags":{"Tags":[]},"removeGameEffectsWithTags":{"Tags":[]},"durationType":0,"duration":"0","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[{"attrType":1003,"operation":0,"magnitudeSourceType":0,"fixedValue":-10.0,"formula":"","mmcType":0,"setByCallerKey":"","mmcCaptureAttribute":200,"mmcAttributeSource":0,"mmcCoefficient":1.0,"mmcUseSnapshot":true}],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"Tags":[]},"cancelOnAbilityEnd":true}</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
@@ -2063,11 +2059,11 @@
       <c r="C73"/>
       <c r="D73"/>
       <c r="E73">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>{"guid":"cde57fb8-b693-4da8-a4a8-fd61e56c5dcd","nodeType":12,"position":{"x":821.3333740234375,"y":-2600.66650390625},"targetType":1,"requiredTags":{"Tags":[]},"immunityTags":{"Tags":[]},"destroyWithNode":false,"positionSource":0,"particleEntityId":50006,"particlePrefab":null,"particlePrefabPath":"Assets/Res/Entity/Effect/ef_Zhanshi_attack_02.prefab","particleBindingName":"down","particleOffset":{"x":5.0,"y":0.0,"z":0.0},"particleScale":{"x":1.0,"y":1.0,"z":1.0},"attachToTarget":false,"particleLoop":false}</t>
+          <t>{"guid":"f8947676-1084-4228-b991-1509cc7fe851","nodeType":1,"position":{"x":975.3333740234375,"y":-2344.0},"targetType":0,"assetTags":{"Tags":[]},"grantedTags":{"Tags":[]},"applicationRequiredTags":{"Tags":[]},"applicationImmunityTags":{"Tags":[]},"removeGameEffectsWithTags":{"Tags":[]},"durationType":0,"duration":"0","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"Tags":[]},"cancelOnAbilityEnd":true,"damageType":1,"damageSourceType":0,"damageFixedValue":10.0,"damageFormula":"","damageMMCType":0,"damageSetByCallerKey":"","damageMMCCaptureAttribute":1006,"damageMMCAttributeSource":0,"damageMMCCoefficient":1.0,"damageMMCUseSnapshot":true,"damageMultiplyByStackCount":false,"damageCalculationType":0,"enableHitKnockback":false,"knockbackDistance":1.0,"knockbackSpeed":12.0}</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
@@ -2083,11 +2079,11 @@
       <c r="C74"/>
       <c r="D74"/>
       <c r="E74">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>{"guid":"9d6f459d-b588-4b64-843b-1b71e8f299ae","nodeType":3,"position":{"x":-1130.6666259765625,"y":-2479.333251953125},"targetType":1,"assetTags":{"Tags":[]},"grantedTags":{"Tags":[]},"applicationRequiredTags":{"Tags":[]},"applicationImmunityTags":{"Tags":[]},"removeGameEffectsWithTags":{"Tags":[]},"durationType":0,"duration":"0","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[{"attrType":1003,"operation":0,"magnitudeSourceType":0,"fixedValue":-10.0,"formula":"","mmcType":0,"setByCallerKey":"","mmcCaptureAttribute":200,"mmcAttributeSource":0,"mmcCoefficient":1.0,"mmcUseSnapshot":true}],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"Tags":[]},"cancelOnAbilityEnd":true}</t>
+          <t>{"guid":"e33ab94c-1496-4d6a-ba5e-1afd38bb0c30","nodeType":4,"position":{"x":731.3333740234375,"y":-2344.0},"targetType":1,"searchShapeType":0,"searchLineType":0,"positionSource":0,"positionBindingName":"center","searchCircleRadius":5.0,"searchSectorRadius":5.0,"searchSectorAngle":180.0,"searchLineDirectionOffsetAngle":0.0,"searchLineDirectionWidth":1.0,"searchLineDirectionLength":10.0,"lineStartPositionSource":0,"lineStartBindingName":"","lineEndPositionSource":1,"lineEndBindingName":"","searchLineBetweenWidth":1.0,"searchLineAbsoluteAngle":0.0,"searchLineAbsoluteWidth":1.0,"searchLineAbsoluteLength":10.0,"maxTargets":1,"searchTargetTags":{"Tags":[{"Name":"unitType.monster","HashCode":-2021655864,"ShortName":"monster","AncestorHashCodes":[1600484460],"AncestorNames":["unitType"]}]},"searchExcludeTags":{"Tags":[]}}</t>
         </is>
       </c>
       <c r="G74"/>

--- a/Design/Excel/ET/Datas/Game/SkillGraph.xlsx
+++ b/Design/Excel/ET/Datas/Game/SkillGraph.xlsx
@@ -1131,7 +1131,7 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>{"guid":"08bcef27-5270-4668-be7d-bb9e9fc01e6a","nodeType":23,"position":{"x":-634.6666259765625,"y":-2399.333251953125},"targetType":1,"animationPrefab":null,"animationPrefabPath":"Assets/Res/UI/UIEntity/UIHeadItem.prefab","animationComponentPath":"UIHeadItem(Clone)/Root_Animation","animationName":"Attack","animationDuration":"10","isAnimationLooping":false,"timeEffects":[{"triggerTime":10,"portIdValue":2131464,"legacyPortId":""},{"triggerTime":10,"portIdValue":2547623,"legacyPortId":""}],"timeCues":[{"startTime":0,"endTime":8,"portIdValue":2247261,"legacyPortId":""}]}</t>
+          <t>{"guid":"08bcef27-5270-4668-be7d-bb9e9fc01e6a","nodeType":23,"position":{"x":-634.6666259765625,"y":-2399.333251953125},"targetType":1,"animationPrefab":null,"animationPrefabPath":"Assets/Res/Entity/Head/HeadItem.prefab","animationComponentPath":"UIHeadItem(Clone)/Root_Animation","animationName":"Attack","animationDuration":"10","isAnimationLooping":false,"timeEffects":[{"triggerTime":10,"portIdValue":2131464,"legacyPortId":""},{"triggerTime":10,"portIdValue":2547623,"legacyPortId":""}],"timeCues":[{"startTime":0,"endTime":8,"portIdValue":2247261,"legacyPortId":""}]}</t>
         </is>
       </c>
       <c r="G27"/>
@@ -1959,11 +1959,11 @@
       <c r="C68"/>
       <c r="D68"/>
       <c r="E68">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>{"guid":"c353e286-8ef0-460a-b917-887f2aeb390a","nodeType":14,"position":{"x":1213.3333740234375,"y":-2354.66650390625},"targetType":1,"requiredTags":{"Tags":[]},"immunityTags":{"Tags":[]},"destroyWithNode":false,"positionSource":2,"positionBindingName":"head","textType":0,"fixedText":"","contextDataKey":"DamageResult","textColor":{"r":1.0,"g":0.0,"b":0.0,"a":1.0},"criticalColor":{"r":1.0,"g":0.5,"b":0.0,"a":1.0},"missColor":{"r":0.5,"g":0.5,"b":0.5,"a":1.0},"fontSize":5.0,"criticalFontSize":60.0,"duration":1.5,"offset":{"x":0.0,"y":0.0},"moveDirection":{"x":0.0,"y":1.0}}</t>
+          <t>{"guid":"c28fb88d-51b1-47b2-be59-859e0ac638e3","nodeType":10,"position":{"x":-843.3333740234375,"y":-2243.333251953125},"targetType":1,"assetTags":{"Tags":[]},"grantedTags":{"Tags":[{"Name":"CD.Sweep","HashCode":-303359587,"ShortName":"Sweep","AncestorHashCodes":[-1137859925],"AncestorNames":["CD"]}]},"applicationRequiredTags":{"Tags":[]},"applicationImmunityTags":{"Tags":[]},"removeGameEffectsWithTags":{"Tags":[]},"durationType":1,"duration":"1","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"Tags":[]},"cancelOnAbilityEnd":false,"cooldownType":0,"maxCharges":2,"chargeTime":"10"}</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
@@ -1979,11 +1979,11 @@
       <c r="C69"/>
       <c r="D69"/>
       <c r="E69">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>{"guid":"c28fb88d-51b1-47b2-be59-859e0ac638e3","nodeType":10,"position":{"x":-843.3333740234375,"y":-2243.333251953125},"targetType":1,"assetTags":{"Tags":[]},"grantedTags":{"Tags":[{"Name":"CD.Sweep","HashCode":-303359587,"ShortName":"Sweep","AncestorHashCodes":[-1137859925],"AncestorNames":["CD"]}]},"applicationRequiredTags":{"Tags":[]},"applicationImmunityTags":{"Tags":[]},"removeGameEffectsWithTags":{"Tags":[]},"durationType":1,"duration":"1","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"Tags":[]},"cancelOnAbilityEnd":false,"cooldownType":0,"maxCharges":2,"chargeTime":"10"}</t>
+          <t>{"guid":"79dea24a-eaf5-45f2-b5a0-cbb8c4ad6df2","nodeType":23,"position":{"x":-460.66665649414063,"y":-2684.0},"targetType":1,"animationPrefab":null,"animationPrefabPath":"Assets/Res/Entity/Head/HeadItem.prefab","animationComponentPath":"HeadItem(Clone)/Root_Animation","animationName":"Attack","animationDuration":"15","isAnimationLooping":false,"timeEffects":[{"triggerTime":3,"portIdValue":2867116,"legacyPortId":""},{"triggerTime":10,"portIdValue":2095095,"legacyPortId":""}],"timeCues":[{"startTime":0,"endTime":41,"portIdValue":2893914,"legacyPortId":""}]}</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
@@ -1999,11 +1999,11 @@
       <c r="C70"/>
       <c r="D70"/>
       <c r="E70">
-        <v>23</v>
+        <v>3</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>{"guid":"79dea24a-eaf5-45f2-b5a0-cbb8c4ad6df2","nodeType":23,"position":{"x":-460.66665649414063,"y":-2684.0},"targetType":1,"animationPrefab":null,"animationPrefabPath":"Assets/Res/UI/UIEntity/UIHeadItem.prefab","animationComponentPath":"UIHeadItem(Clone)/Root_Animation","animationName":"Attack","animationDuration":"10","isAnimationLooping":false,"timeEffects":[{"triggerTime":3,"portIdValue":2867116,"legacyPortId":""},{"triggerTime":10,"portIdValue":2095095,"legacyPortId":""}],"timeCues":[{"startTime":0,"endTime":41,"portIdValue":2893914,"legacyPortId":""}]}</t>
+          <t>{"guid":"9d6f459d-b588-4b64-843b-1b71e8f299ae","nodeType":3,"position":{"x":-1130.6666259765625,"y":-2479.333251953125},"targetType":1,"assetTags":{"Tags":[]},"grantedTags":{"Tags":[]},"applicationRequiredTags":{"Tags":[]},"applicationImmunityTags":{"Tags":[]},"removeGameEffectsWithTags":{"Tags":[]},"durationType":0,"duration":"0","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[{"attrType":1003,"operation":0,"magnitudeSourceType":0,"fixedValue":-10.0,"formula":"","mmcType":0,"setByCallerKey":"","mmcCaptureAttribute":200,"mmcAttributeSource":0,"mmcCoefficient":1.0,"mmcUseSnapshot":true}],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"Tags":[]},"cancelOnAbilityEnd":true}</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
@@ -2019,11 +2019,11 @@
       <c r="C71"/>
       <c r="D71"/>
       <c r="E71">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>{"guid":"cde57fb8-b693-4da8-a4a8-fd61e56c5dcd","nodeType":12,"position":{"x":821.3333740234375,"y":-2600.66650390625},"targetType":1,"requiredTags":{"Tags":[]},"immunityTags":{"Tags":[]},"destroyWithNode":false,"positionSource":0,"particleEntityId":50006,"particlePrefab":null,"particlePrefabPath":"Assets/Res/Entity/Effect/ef_Zhanshi_attack_02.prefab","particleBindingName":"down","particleOffset":{"x":5.0,"y":0.0,"z":0.0},"particleScale":{"x":1.0,"y":1.0,"z":1.0},"attachToTarget":false,"particleLoop":false}</t>
+          <t>{"guid":"f8947676-1084-4228-b991-1509cc7fe851","nodeType":1,"position":{"x":975.3333740234375,"y":-2344.0},"targetType":0,"assetTags":{"Tags":[]},"grantedTags":{"Tags":[]},"applicationRequiredTags":{"Tags":[]},"applicationImmunityTags":{"Tags":[]},"removeGameEffectsWithTags":{"Tags":[]},"durationType":0,"duration":"0","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"Tags":[]},"cancelOnAbilityEnd":true,"damageType":1,"damageSourceType":0,"damageFixedValue":10.0,"damageFormula":"","damageMMCType":0,"damageSetByCallerKey":"","damageMMCCaptureAttribute":1006,"damageMMCAttributeSource":0,"damageMMCCoefficient":1.0,"damageMMCUseSnapshot":true,"damageMultiplyByStackCount":false,"damageCalculationType":0,"enableHitKnockback":false,"knockbackDistance":1.0,"knockbackSpeed":12.0}</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
@@ -2039,16 +2039,16 @@
       <c r="C72"/>
       <c r="D72"/>
       <c r="E72">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>{"guid":"9d6f459d-b588-4b64-843b-1b71e8f299ae","nodeType":3,"position":{"x":-1130.6666259765625,"y":-2479.333251953125},"targetType":1,"assetTags":{"Tags":[]},"grantedTags":{"Tags":[]},"applicationRequiredTags":{"Tags":[]},"applicationImmunityTags":{"Tags":[]},"removeGameEffectsWithTags":{"Tags":[]},"durationType":0,"duration":"0","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[{"attrType":1003,"operation":0,"magnitudeSourceType":0,"fixedValue":-10.0,"formula":"","mmcType":0,"setByCallerKey":"","mmcCaptureAttribute":200,"mmcAttributeSource":0,"mmcCoefficient":1.0,"mmcUseSnapshot":true}],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"Tags":[]},"cancelOnAbilityEnd":true}</t>
+          <t>{"guid":"c353e286-8ef0-460a-b917-887f2aeb390a","nodeType":14,"position":{"x":1218.666748046875,"y":-2347.333251953125},"targetType":1,"requiredTags":{"Tags":[]},"immunityTags":{"Tags":[]},"destroyWithNode":false,"positionSource":2,"positionBindingName":"head","textType":0,"fixedText":"","contextDataKey":"DamageResult","textColor":{"r":1.0,"g":0.0,"b":0.0,"a":1.0},"criticalColor":{"r":1.0,"g":0.5,"b":0.0,"a":1.0},"missColor":{"r":0.5,"g":0.5,"b":0.5,"a":1.0},"fontSize":5.0,"criticalFontSize":60.0,"duration":1.5,"offset":{"x":0.0,"y":0.0},"moveDirection":{"x":0.0,"y":1.0}}</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>{"outputNodeGuid":"79dea24a-eaf5-45f2-b5a0-cbb8c4ad6df2","outputPortId":2893914,"inputNodeGuid":"cde57fb8-b693-4da8-a4a8-fd61e56c5dcd","inputPortId":7001}</t>
+          <t>{"outputNodeGuid":"356907e0-1488-4128-bfcc-7ff73cfc3330","outputPortId":1002,"inputNodeGuid":"79dea24a-eaf5-45f2-b5a0-cbb8c4ad6df2","inputPortId":7001}</t>
         </is>
       </c>
       <c r="H72"/>
@@ -2059,16 +2059,16 @@
       <c r="C73"/>
       <c r="D73"/>
       <c r="E73">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>{"guid":"f8947676-1084-4228-b991-1509cc7fe851","nodeType":1,"position":{"x":975.3333740234375,"y":-2344.0},"targetType":0,"assetTags":{"Tags":[]},"grantedTags":{"Tags":[]},"applicationRequiredTags":{"Tags":[]},"applicationImmunityTags":{"Tags":[]},"removeGameEffectsWithTags":{"Tags":[]},"durationType":0,"duration":"0","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"Tags":[]},"cancelOnAbilityEnd":true,"damageType":1,"damageSourceType":0,"damageFixedValue":10.0,"damageFormula":"","damageMMCType":0,"damageSetByCallerKey":"","damageMMCCaptureAttribute":1006,"damageMMCAttributeSource":0,"damageMMCCoefficient":1.0,"damageMMCUseSnapshot":true,"damageMultiplyByStackCount":false,"damageCalculationType":0,"enableHitKnockback":false,"knockbackDistance":1.0,"knockbackSpeed":12.0}</t>
+          <t>{"guid":"cde57fb8-b693-4da8-a4a8-fd61e56c5dcd","nodeType":12,"position":{"x":1005.3333740234375,"y":-2186.0},"targetType":1,"requiredTags":{"Tags":[]},"immunityTags":{"Tags":[]},"destroyWithNode":false,"positionSource":2,"particleEntityId":50006,"particlePrefab":null,"particlePrefabPath":"Assets/Res/Entity/Effect/ef_Zhanshi_attack_02.prefab","particleBindingName":"head","particleOffset":{"x":0.0,"y":0.0,"z":0.0},"particleScale":{"x":1.0,"y":1.0,"z":1.0},"attachToTarget":false,"particleLoop":false}</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>{"outputNodeGuid":"356907e0-1488-4128-bfcc-7ff73cfc3330","outputPortId":1002,"inputNodeGuid":"79dea24a-eaf5-45f2-b5a0-cbb8c4ad6df2","inputPortId":7001}</t>
+          <t>{"outputNodeGuid":"e33ab94c-1496-4d6a-ba5e-1afd38bb0c30","outputPortId":4001,"inputNodeGuid":"cde57fb8-b693-4da8-a4a8-fd61e56c5dcd","inputPortId":7001}</t>
         </is>
       </c>
       <c r="H73"/>

--- a/Design/Excel/ET/Datas/Game/SkillGraph.xlsx
+++ b/Design/Excel/ET/Datas/Game/SkillGraph.xlsx
@@ -1091,11 +1091,11 @@
       <c r="C25"/>
       <c r="D25"/>
       <c r="E25">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>{"guid":"90bacd9f-d882-4bba-aaa8-41ed993ac3ff","nodeType":8,"position":{"x":-419.33331298828125,"y":-1840.0},"targetType":2,"assetTags":{"Tags":[]},"grantedTags":{"Tags":[]},"applicationRequiredTags":{"Tags":[]},"applicationImmunityTags":{"Tags":[]},"removeGameEffectsWithTags":{"Tags":[]},"durationType":2,"duration":"0","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"Tags":[]},"cancelOnAbilityEnd":false,"launchPositionSource":0,"launchBindingName":"center","targetPositionSource":1,"targetBindingName":"center","projectileTargetType":0,"flyOver":false,"offsetAngle":0.0,"curveHeight":0.0,"projectileEntityId":50001,"projectilePrefab":null,"projectilePrefabPath":"Assets/Res/Entity/Effect/ef_fashi_gandian_buff.prefab","speed":3.0,"maxDistance":10.0,"collisionRadius":0.5,"isPiercing":false,"maxPierceCount":1,"collisionTargetTags":{"Tags":[]},"collisionExcludeTags":{"Tags":[]},"isBouncing":true,"bounceTargetMode":0,"maxBounceCount":3,"bounceSearchRadius":10.0,"canBounceToSameTarget":false,"excludeSourceCamp":true,"bounceAngleOffset":0.0}</t>
+          <t>{"guid":"2d7e41c4-8e90-4b61-879c-4b2e5b9486db","nodeType":14,"position":{"x":180.0,"y":-1810.0},"targetType":1,"requiredTags":{"Tags":[]},"immunityTags":{"Tags":[]},"destroyWithNode":false,"positionSource":2,"positionBindingName":"head","textType":0,"fixedText":"","contextDataKey":"DamageResult","textColor":{"r":1.0,"g":0.16293229162693024,"b":0.0,"a":1.0},"criticalColor":{"r":1.0,"g":0.5,"b":0.0,"a":1.0},"missColor":{"r":0.5,"g":0.5,"b":0.5,"a":1.0},"fontSize":5.0,"criticalFontSize":60.0,"duration":1.5,"offset":{"x":0.0,"y":0.0},"moveDirection":{"x":0.0,"y":1.0}}</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -1111,11 +1111,11 @@
       <c r="C26"/>
       <c r="D26"/>
       <c r="E26">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>{"guid":"2d7e41c4-8e90-4b61-879c-4b2e5b9486db","nodeType":14,"position":{"x":180.0,"y":-1810.0},"targetType":1,"requiredTags":{"Tags":[]},"immunityTags":{"Tags":[]},"destroyWithNode":false,"positionSource":2,"positionBindingName":"head","textType":0,"fixedText":"","contextDataKey":"DamageResult","textColor":{"r":1.0,"g":0.16293229162693024,"b":0.0,"a":1.0},"criticalColor":{"r":1.0,"g":0.5,"b":0.0,"a":1.0},"missColor":{"r":0.5,"g":0.5,"b":0.5,"a":1.0},"fontSize":5.0,"criticalFontSize":60.0,"duration":1.5,"offset":{"x":0.0,"y":0.0},"moveDirection":{"x":0.0,"y":1.0}}</t>
+          <t>{"guid":"08bcef27-5270-4668-be7d-bb9e9fc01e6a","nodeType":23,"position":{"x":-677.33331298828125,"y":-2446.66650390625},"targetType":1,"animationPrefab":null,"animationPrefabPath":"Assets/Res/Entity/Head/HeadItem.prefab","animationComponentPath":"HeadItem(Clone)/Root_Animation","animationName":"Attack","animationDuration":"15","isAnimationLooping":false,"timeEffects":[{"triggerTime":10,"portIdValue":2131464,"legacyPortId":""},{"triggerTime":10,"portIdValue":2547623,"legacyPortId":""}],"timeCues":[{"startTime":0,"endTime":8,"portIdValue":2247261,"legacyPortId":""}]}</t>
         </is>
       </c>
       <c r="G26"/>
@@ -1127,11 +1127,11 @@
       <c r="C27"/>
       <c r="D27"/>
       <c r="E27">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>{"guid":"08bcef27-5270-4668-be7d-bb9e9fc01e6a","nodeType":23,"position":{"x":-634.6666259765625,"y":-2399.333251953125},"targetType":1,"animationPrefab":null,"animationPrefabPath":"Assets/Res/Entity/Head/HeadItem.prefab","animationComponentPath":"UIHeadItem(Clone)/Root_Animation","animationName":"Attack","animationDuration":"10","isAnimationLooping":false,"timeEffects":[{"triggerTime":10,"portIdValue":2131464,"legacyPortId":""},{"triggerTime":10,"portIdValue":2547623,"legacyPortId":""}],"timeCues":[{"startTime":0,"endTime":8,"portIdValue":2247261,"legacyPortId":""}]}</t>
+          <t>{"guid":"90bacd9f-d882-4bba-aaa8-41ed993ac3ff","nodeType":8,"position":{"x":-419.33331298828125,"y":-1840.0},"targetType":2,"assetTags":{"Tags":[]},"grantedTags":{"Tags":[]},"applicationRequiredTags":{"Tags":[]},"applicationImmunityTags":{"Tags":[]},"removeGameEffectsWithTags":{"Tags":[]},"durationType":2,"duration":"0","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"Tags":[]},"cancelOnAbilityEnd":false,"launchPositionSource":0,"launchBindingName":"center","targetPositionSource":1,"targetBindingName":"center","projectileTargetType":0,"flyOver":false,"offsetAngle":0.0,"curveHeight":0.0,"projectileEntityId":50001,"projectilePrefab":null,"projectilePrefabPath":"Assets/Res/Entity/Effect/ef_fashi_gandian_buff.prefab","speed":3.0,"maxDistance":10.0,"collisionRadius":0.5,"isPiercing":false,"maxPierceCount":1,"collisionTargetTags":{"Tags":[]},"collisionExcludeTags":{"Tags":[]},"isBouncing":true,"bounceTargetMode":0,"maxBounceCount":3,"bounceSearchRadius":10.0,"canBounceToSameTarget":false,"excludeSourceCamp":true,"bounceAngleOffset":0.0}</t>
         </is>
       </c>
       <c r="G27"/>
@@ -2083,7 +2083,7 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>{"guid":"e33ab94c-1496-4d6a-ba5e-1afd38bb0c30","nodeType":4,"position":{"x":731.3333740234375,"y":-2344.0},"targetType":1,"searchShapeType":0,"searchLineType":0,"positionSource":0,"positionBindingName":"center","searchCircleRadius":5.0,"searchSectorRadius":5.0,"searchSectorAngle":180.0,"searchLineDirectionOffsetAngle":0.0,"searchLineDirectionWidth":1.0,"searchLineDirectionLength":10.0,"lineStartPositionSource":0,"lineStartBindingName":"","lineEndPositionSource":1,"lineEndBindingName":"","searchLineBetweenWidth":1.0,"searchLineAbsoluteAngle":0.0,"searchLineAbsoluteWidth":1.0,"searchLineAbsoluteLength":10.0,"maxTargets":1,"searchTargetTags":{"Tags":[{"Name":"unitType.monster","HashCode":-2021655864,"ShortName":"monster","AncestorHashCodes":[1600484460],"AncestorNames":["unitType"]}]},"searchExcludeTags":{"Tags":[]}}</t>
+          <t>{"guid":"e33ab94c-1496-4d6a-ba5e-1afd38bb0c30","nodeType":4,"position":{"x":731.3333740234375,"y":-2344.0},"targetType":1,"searchShapeType":0,"searchLineType":0,"positionSource":0,"positionBindingName":"center","searchCircleRadius":1.0,"searchSectorRadius":5.0,"searchSectorAngle":180.0,"searchLineDirectionOffsetAngle":0.0,"searchLineDirectionWidth":1.0,"searchLineDirectionLength":10.0,"lineStartPositionSource":0,"lineStartBindingName":"","lineEndPositionSource":1,"lineEndBindingName":"","searchLineBetweenWidth":1.0,"searchLineAbsoluteAngle":0.0,"searchLineAbsoluteWidth":1.0,"searchLineAbsoluteLength":10.0,"maxTargets":1,"searchTargetTags":{"Tags":[{"Name":"unitType.monster","HashCode":-2021655864,"ShortName":"monster","AncestorHashCodes":[1600484460],"AncestorNames":["unitType"]}]},"searchExcludeTags":{"Tags":[]}}</t>
         </is>
       </c>
       <c r="G74"/>

--- a/Design/Excel/ET/Datas/Game/SkillGraph.xlsx
+++ b/Design/Excel/ET/Datas/Game/SkillGraph.xlsx
@@ -2083,7 +2083,7 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>{"guid":"e33ab94c-1496-4d6a-ba5e-1afd38bb0c30","nodeType":4,"position":{"x":731.3333740234375,"y":-2344.0},"targetType":1,"searchShapeType":0,"searchLineType":0,"positionSource":0,"positionBindingName":"center","searchCircleRadius":1.0,"searchSectorRadius":5.0,"searchSectorAngle":180.0,"searchLineDirectionOffsetAngle":0.0,"searchLineDirectionWidth":1.0,"searchLineDirectionLength":10.0,"lineStartPositionSource":0,"lineStartBindingName":"","lineEndPositionSource":1,"lineEndBindingName":"","searchLineBetweenWidth":1.0,"searchLineAbsoluteAngle":0.0,"searchLineAbsoluteWidth":1.0,"searchLineAbsoluteLength":10.0,"maxTargets":1,"searchTargetTags":{"Tags":[{"Name":"unitType.monster","HashCode":-2021655864,"ShortName":"monster","AncestorHashCodes":[1600484460],"AncestorNames":["unitType"]}]},"searchExcludeTags":{"Tags":[]}}</t>
+          <t>{"guid":"e33ab94c-1496-4d6a-ba5e-1afd38bb0c30","nodeType":4,"position":{"x":731.3333740234375,"y":-2344.0},"targetType":1,"searchShapeType":3,"searchLineType":0,"positionSource":0,"positionBindingName":"center","searchCircleRadius":1.0,"searchSectorRadius":5.0,"searchSectorAngle":180.0,"searchLineDirectionOffsetAngle":0.0,"searchLineDirectionWidth":1.0,"searchLineDirectionLength":10.0,"lineStartPositionSource":0,"lineStartBindingName":"","lineEndPositionSource":1,"lineEndBindingName":"","searchLineBetweenWidth":1.0,"searchLineAbsoluteAngle":0.0,"searchLineAbsoluteWidth":1.0,"searchLineAbsoluteLength":10.0,"maxTargets":1,"searchTargetTags":{"Tags":[{"Name":"unitType.monster","HashCode":-2021655864,"ShortName":"monster","AncestorHashCodes":[1600484460],"AncestorNames":["unitType"]}]},"searchExcludeTags":{"Tags":[]}}</t>
         </is>
       </c>
       <c r="G74"/>

--- a/Design/Excel/ET/Datas/Game/SkillGraph.xlsx
+++ b/Design/Excel/ET/Datas/Game/SkillGraph.xlsx
@@ -991,11 +991,11 @@
       </c>
       <c r="D20"/>
       <c r="E20">
-        <v>7</v>
+        <v>23</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>{"guid":"3aafa9a5-4766-4204-91ab-d797aeb3c0e1","nodeType":7,"position":{"x":580.6666259765625,"y":-1987.3333740234375},"targetType":1,"endType":0}</t>
+          <t>{"guid":"08bcef27-5270-4668-be7d-bb9e9fc01e6a","nodeType":23,"position":{"x":-649.33331298828125,"y":-2446.66650390625},"targetType":1,"animationPrefab":null,"animationPrefabPath":"Assets/Res/Entity/Head/HeadItem.prefab","animationComponentPath":"HeadItem(Clone)/Root_Animation","animationName":"Attack","animationDuration":"15","isAnimationLooping":false,"timeEffects":[{"triggerTime":1,"portIdValue":2131464,"legacyPortId":""},{"triggerTime":15,"portIdValue":2547623,"legacyPortId":""}],"timeCues":[{"startTime":0,"endTime":15,"portIdValue":2247261,"legacyPortId":""}]}</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -1011,11 +1011,11 @@
       <c r="C21"/>
       <c r="D21"/>
       <c r="E21">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>{"guid":"c28fb88d-51b1-47b2-be59-859e0ac638e3","nodeType":10,"position":{"x":-1220.6666259765625,"y":-1747.3333740234375},"targetType":1,"assetTags":{"Tags":[]},"grantedTags":{"Tags":[{"Name":"CD.FireCircle","HashCode":522143731,"ShortName":"FireCircle","AncestorHashCodes":[-1137859925],"AncestorNames":["CD"]}]},"applicationRequiredTags":{"Tags":[]},"applicationImmunityTags":{"Tags":[]},"removeGameEffectsWithTags":{"Tags":[]},"durationType":1,"duration":"3","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"Tags":[]},"cancelOnAbilityEnd":false,"cooldownType":0,"maxCharges":2,"chargeTime":"10"}</t>
+          <t>{"guid":"3aafa9a5-4766-4204-91ab-d797aeb3c0e1","nodeType":7,"position":{"x":301.33334350585938,"y":-1866.666748046875},"targetType":1,"endType":0}</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -1031,16 +1031,16 @@
       <c r="C22"/>
       <c r="D22"/>
       <c r="E22">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>{"guid":"9d6f459d-b588-4b64-843b-1b71e8f299ae","nodeType":3,"position":{"x":-1195.3333740234375,"y":-2003.3333740234375},"targetType":1,"assetTags":{"Tags":[]},"grantedTags":{"Tags":[]},"applicationRequiredTags":{"Tags":[]},"applicationImmunityTags":{"Tags":[]},"removeGameEffectsWithTags":{"Tags":[]},"durationType":0,"duration":"0","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[{"attrType":1003,"operation":0,"magnitudeSourceType":0,"fixedValue":-100.0,"formula":"","mmcType":0,"setByCallerKey":"","mmcCaptureAttribute":200,"mmcAttributeSource":0,"mmcCoefficient":1.0,"mmcUseSnapshot":true}],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"Tags":[]},"cancelOnAbilityEnd":true}</t>
+          <t>{"guid":"93b489d8-3d60-4ded-9f04-789fe2990ece","nodeType":4,"position":{"x":492.66665649414063,"y":-1903.3333740234375},"targetType":1,"searchShapeType":3,"searchLineType":0,"positionSource":1,"positionBindingName":"","searchCircleRadius":5.0,"searchSectorRadius":5.0,"searchSectorAngle":90.0,"searchLineDirectionOffsetAngle":0.0,"searchLineDirectionWidth":1.0,"searchLineDirectionLength":10.0,"lineStartPositionSource":0,"lineStartBindingName":"","lineEndPositionSource":1,"lineEndBindingName":"","searchLineBetweenWidth":1.0,"searchLineAbsoluteAngle":0.0,"searchLineAbsoluteWidth":1.0,"searchLineAbsoluteLength":10.0,"maxTargets":1,"searchTargetTags":{"Tags":[{"Name":"unitType.monster","HashCode":-2021655864,"ShortName":"monster","AncestorHashCodes":[1600484460],"AncestorNames":["unitType"]}]},"searchExcludeTags":{"Tags":[]}}</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>{"outputNodeGuid":"90bacd9f-d882-4bba-aaa8-41ed993ac3ff","outputPortId":5001,"inputNodeGuid":"eae41233-d297-46fe-a6c8-0b5c876fbb2a","inputPortId":7001}</t>
+          <t>{"outputNodeGuid":"eae41233-d297-46fe-a6c8-0b5c876fbb2a","outputPortId":3004,"inputNodeGuid":"2d7e41c4-8e90-4b61-879c-4b2e5b9486db","inputPortId":7001}</t>
         </is>
       </c>
       <c r="H22"/>
@@ -1051,16 +1051,16 @@
       <c r="C23"/>
       <c r="D23"/>
       <c r="E23">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>{"guid":"eae41233-d297-46fe-a6c8-0b5c876fbb2a","nodeType":1,"position":{"x":-97.333328247070313,"y":-1810.0},"targetType":0,"assetTags":{"Tags":[]},"grantedTags":{"Tags":[]},"applicationRequiredTags":{"Tags":[]},"applicationImmunityTags":{"Tags":[]},"removeGameEffectsWithTags":{"Tags":[]},"durationType":0,"duration":"0","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"Tags":[]},"cancelOnAbilityEnd":true,"damageType":0,"damageSourceType":0,"damageFixedValue":10.0,"damageFormula":"","damageMMCType":0,"damageSetByCallerKey":"","damageMMCCaptureAttribute":200,"damageMMCAttributeSource":0,"damageMMCCoefficient":1.0,"damageMMCUseSnapshot":true,"damageMultiplyByStackCount":false,"damageCalculationType":0,"enableHitKnockback":true,"knockbackDistance":1.0,"knockbackSpeed":12.0}</t>
+          <t>{"guid":"2d7e41c4-8e90-4b61-879c-4b2e5b9486db","nodeType":14,"position":{"x":1200.0,"y":-2044.666748046875},"targetType":1,"requiredTags":{"Tags":[]},"immunityTags":{"Tags":[]},"destroyWithNode":false,"positionSource":2,"positionBindingName":"head","textType":0,"fixedText":"","contextDataKey":"DamageResult","textColor":{"r":1.0,"g":0.16293229162693024,"b":0.0,"a":1.0},"criticalColor":{"r":1.0,"g":0.5,"b":0.0,"a":1.0},"missColor":{"r":0.5,"g":0.5,"b":0.5,"a":1.0},"fontSize":5.0,"criticalFontSize":60.0,"duration":1.5,"offset":{"x":0.0,"y":0.0},"moveDirection":{"x":0.0,"y":1.0}}</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>{"outputNodeGuid":"eae41233-d297-46fe-a6c8-0b5c876fbb2a","outputPortId":3004,"inputNodeGuid":"2d7e41c4-8e90-4b61-879c-4b2e5b9486db","inputPortId":7001}</t>
+          <t>{"outputNodeGuid":"08bcef27-5270-4668-be7d-bb9e9fc01e6a","outputPortId":2547623,"inputNodeGuid":"3aafa9a5-4766-4204-91ab-d797aeb3c0e1","inputPortId":7001}</t>
         </is>
       </c>
       <c r="H23"/>
@@ -1075,12 +1075,12 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>{"guid":"356907e0-1488-4128-bfcc-7ff73cfc3330","nodeType":0,"position":{"x":-881.3333740234375,"y":-1854.666748046875},"targetType":1,"skillId":7001,"assetTags":{"Tags":[]},"cancelAbilitiesWithTags":{"Tags":[]},"blockAbilitiesWithTags":{"Tags":[]},"activationOwnedTags":{"Tags":[]},"activationRequiredTags":{"Tags":[]},"activationBlockedTags":{"Tags":[{"Name":"CD.FireCircle","HashCode":522143731,"ShortName":"FireCircle","AncestorHashCodes":[-1137859925],"AncestorNames":["CD"]}]},"ongoingBlockedTags":{"Tags":[{"Name":"Buff.DeBuff.Stun","HashCode":1791562953,"ShortName":"Stun","AncestorHashCodes":[937056111,321157895],"AncestorNames":["Buff","Buff.DeBuff"]}]},"eventOutputPorts":[]}</t>
+          <t>{"guid":"356907e0-1488-4128-bfcc-7ff73cfc3330","nodeType":0,"position":{"x":-1100.0,"y":-2288.66650390625},"targetType":1,"skillId":7001,"assetTags":{"Tags":[]},"cancelAbilitiesWithTags":{"Tags":[]},"blockAbilitiesWithTags":{"Tags":[]},"activationOwnedTags":{"Tags":[]},"activationRequiredTags":{"Tags":[]},"activationBlockedTags":{"Tags":[{"Name":"CD.FireCircle","HashCode":522143731,"ShortName":"FireCircle","AncestorHashCodes":[-1137859925],"AncestorNames":["CD"]}]},"ongoingBlockedTags":{"Tags":[{"Name":"Buff.DeBuff.Stun","HashCode":1791562953,"ShortName":"Stun","AncestorHashCodes":[937056111,321157895],"AncestorNames":["Buff","Buff.DeBuff"]}]},"eventOutputPorts":[]}</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>{"outputNodeGuid":"08bcef27-5270-4668-be7d-bb9e9fc01e6a","outputPortId":2131464,"inputNodeGuid":"90bacd9f-d882-4bba-aaa8-41ed993ac3ff","inputPortId":7001}</t>
+          <t>{"outputNodeGuid":"356907e0-1488-4128-bfcc-7ff73cfc3330","outputPortId":1002,"inputNodeGuid":"08bcef27-5270-4668-be7d-bb9e9fc01e6a","inputPortId":7001}</t>
         </is>
       </c>
       <c r="H24"/>
@@ -1091,16 +1091,16 @@
       <c r="C25"/>
       <c r="D25"/>
       <c r="E25">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>{"guid":"2d7e41c4-8e90-4b61-879c-4b2e5b9486db","nodeType":14,"position":{"x":180.0,"y":-1810.0},"targetType":1,"requiredTags":{"Tags":[]},"immunityTags":{"Tags":[]},"destroyWithNode":false,"positionSource":2,"positionBindingName":"head","textType":0,"fixedText":"","contextDataKey":"DamageResult","textColor":{"r":1.0,"g":0.16293229162693024,"b":0.0,"a":1.0},"criticalColor":{"r":1.0,"g":0.5,"b":0.0,"a":1.0},"missColor":{"r":0.5,"g":0.5,"b":0.5,"a":1.0},"fontSize":5.0,"criticalFontSize":60.0,"duration":1.5,"offset":{"x":0.0,"y":0.0},"moveDirection":{"x":0.0,"y":1.0}}</t>
+          <t>{"guid":"9d6f459d-b588-4b64-843b-1b71e8f299ae","nodeType":3,"position":{"x":-1423.333251953125,"y":-2391.333251953125},"targetType":1,"assetTags":{"Tags":[]},"grantedTags":{"Tags":[]},"applicationRequiredTags":{"Tags":[]},"applicationImmunityTags":{"Tags":[]},"removeGameEffectsWithTags":{"Tags":[]},"durationType":0,"duration":"0","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[{"attrType":1003,"operation":0,"magnitudeSourceType":0,"fixedValue":-100.0,"formula":"","mmcType":0,"setByCallerKey":"","mmcCaptureAttribute":200,"mmcAttributeSource":0,"mmcCoefficient":1.0,"mmcUseSnapshot":true}],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"Tags":[]},"cancelOnAbilityEnd":true}</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>{"outputNodeGuid":"08bcef27-5270-4668-be7d-bb9e9fc01e6a","outputPortId":2547623,"inputNodeGuid":"3aafa9a5-4766-4204-91ab-d797aeb3c0e1","inputPortId":7001}</t>
+          <t>{"outputNodeGuid":"93b489d8-3d60-4ded-9f04-789fe2990ece","outputPortId":4001,"inputNodeGuid":"90bacd9f-d882-4bba-aaa8-41ed993ac3ff","inputPortId":7001}</t>
         </is>
       </c>
       <c r="H25"/>
@@ -1111,14 +1111,18 @@
       <c r="C26"/>
       <c r="D26"/>
       <c r="E26">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>{"guid":"08bcef27-5270-4668-be7d-bb9e9fc01e6a","nodeType":23,"position":{"x":-677.33331298828125,"y":-2446.66650390625},"targetType":1,"animationPrefab":null,"animationPrefabPath":"Assets/Res/Entity/Head/HeadItem.prefab","animationComponentPath":"HeadItem(Clone)/Root_Animation","animationName":"Attack","animationDuration":"15","isAnimationLooping":false,"timeEffects":[{"triggerTime":10,"portIdValue":2131464,"legacyPortId":""},{"triggerTime":10,"portIdValue":2547623,"legacyPortId":""}],"timeCues":[{"startTime":0,"endTime":8,"portIdValue":2247261,"legacyPortId":""}]}</t>
-        </is>
-      </c>
-      <c r="G26"/>
+          <t>{"guid":"c28fb88d-51b1-47b2-be59-859e0ac638e3","nodeType":10,"position":{"x":-1363.333251953125,"y":-2166.0},"targetType":1,"assetTags":{"Tags":[]},"grantedTags":{"Tags":[{"Name":"CD.FireCircle","HashCode":522143731,"ShortName":"FireCircle","AncestorHashCodes":[-1137859925],"AncestorNames":["CD"]}]},"applicationRequiredTags":{"Tags":[]},"applicationImmunityTags":{"Tags":[]},"removeGameEffectsWithTags":{"Tags":[]},"durationType":1,"duration":"3","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"Tags":[]},"cancelOnAbilityEnd":false,"cooldownType":0,"maxCharges":2,"chargeTime":"10"}</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>{"outputNodeGuid":"08bcef27-5270-4668-be7d-bb9e9fc01e6a","outputPortId":2131464,"inputNodeGuid":"93b489d8-3d60-4ded-9f04-789fe2990ece","inputPortId":7001}</t>
+        </is>
+      </c>
       <c r="H26"/>
     </row>
     <row r="27">
@@ -1127,58 +1131,58 @@
       <c r="C27"/>
       <c r="D27"/>
       <c r="E27">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>{"guid":"90bacd9f-d882-4bba-aaa8-41ed993ac3ff","nodeType":8,"position":{"x":-419.33331298828125,"y":-1840.0},"targetType":2,"assetTags":{"Tags":[]},"grantedTags":{"Tags":[]},"applicationRequiredTags":{"Tags":[]},"applicationImmunityTags":{"Tags":[]},"removeGameEffectsWithTags":{"Tags":[]},"durationType":2,"duration":"0","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"Tags":[]},"cancelOnAbilityEnd":false,"launchPositionSource":0,"launchBindingName":"center","targetPositionSource":1,"targetBindingName":"center","projectileTargetType":0,"flyOver":false,"offsetAngle":0.0,"curveHeight":0.0,"projectileEntityId":50001,"projectilePrefab":null,"projectilePrefabPath":"Assets/Res/Entity/Effect/ef_fashi_gandian_buff.prefab","speed":3.0,"maxDistance":10.0,"collisionRadius":0.5,"isPiercing":false,"maxPierceCount":1,"collisionTargetTags":{"Tags":[]},"collisionExcludeTags":{"Tags":[]},"isBouncing":true,"bounceTargetMode":0,"maxBounceCount":3,"bounceSearchRadius":10.0,"canBounceToSameTarget":false,"excludeSourceCamp":true,"bounceAngleOffset":0.0}</t>
-        </is>
-      </c>
-      <c r="G27"/>
+          <t>{"guid":"eae41233-d297-46fe-a6c8-0b5c876fbb2a","nodeType":1,"position":{"x":942.0,"y":-2072.666748046875},"targetType":0,"assetTags":{"Tags":[]},"grantedTags":{"Tags":[]},"applicationRequiredTags":{"Tags":[]},"applicationImmunityTags":{"Tags":[]},"removeGameEffectsWithTags":{"Tags":[]},"durationType":0,"duration":"0","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"Tags":[]},"cancelOnAbilityEnd":true,"damageType":1,"damageSourceType":0,"damageFixedValue":10.0,"damageFormula":"","damageMMCType":0,"damageSetByCallerKey":"","damageMMCCaptureAttribute":200,"damageMMCAttributeSource":0,"damageMMCCoefficient":1.0,"damageMMCUseSnapshot":true,"damageMultiplyByStackCount":false,"damageCalculationType":0,"enableHitKnockback":false,"knockbackDistance":1.0,"knockbackSpeed":12.0}</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>{"outputNodeGuid":"90bacd9f-d882-4bba-aaa8-41ed993ac3ff","outputPortId":5002,"inputNodeGuid":"eae41233-d297-46fe-a6c8-0b5c876fbb2a","inputPortId":7001}</t>
+        </is>
+      </c>
       <c r="H27"/>
     </row>
     <row r="28">
       <c r="A28"/>
-      <c r="B28">
-        <v>1010</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>FireCircle2</t>
-        </is>
-      </c>
+      <c r="B28"/>
+      <c r="C28"/>
       <c r="D28"/>
       <c r="E28">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>{"guid":"3aafa9a5-4766-4204-91ab-d797aeb3c0e1","nodeType":7,"position":{"x":580.6666259765625,"y":-1987.3333740234375},"targetType":1,"endType":0}</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>{"outputNodeGuid":"356907e0-1488-4128-bfcc-7ff73cfc3330","outputPortId":1002,"inputNodeGuid":"432ff1e3-b18d-476d-af80-d39ddc07402a","inputPortId":7001}</t>
-        </is>
-      </c>
+          <t>{"guid":"90bacd9f-d882-4bba-aaa8-41ed993ac3ff","nodeType":8,"position":{"x":602.6666259765625,"y":-2102.666748046875},"targetType":1,"assetTags":{"Tags":[]},"grantedTags":{"Tags":[]},"applicationRequiredTags":{"Tags":[]},"applicationImmunityTags":{"Tags":[]},"removeGameEffectsWithTags":{"Tags":[]},"durationType":2,"duration":"0","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"Tags":[]},"cancelOnAbilityEnd":false,"launchPositionSource":0,"launchBindingName":"center","targetPositionSource":2,"targetBindingName":"center","projectileTargetType":1,"flyOver":false,"offsetAngle":0.0,"curveHeight":0.0,"projectileEntityId":50001,"projectilePrefab":null,"projectilePrefabPath":"Assets/Res/Entity/Effect/ef_fashi_gandian_buff.prefab","speed":3.0,"maxDistance":10.0,"collisionRadius":0.10000000149011612,"isPiercing":false,"maxPierceCount":1,"collisionTargetTags":{"Tags":[{"Name":"unitType.monster","HashCode":-2021655864,"ShortName":"monster","AncestorHashCodes":[1600484460],"AncestorNames":["unitType"]}]},"collisionExcludeTags":{"Tags":[]},"isBouncing":false,"bounceTargetMode":0,"maxBounceCount":3,"bounceSearchRadius":10.0,"canBounceToSameTarget":false,"excludeSourceCamp":true,"bounceAngleOffset":0.0}</t>
+        </is>
+      </c>
+      <c r="G28"/>
       <c r="H28"/>
     </row>
     <row r="29">
       <c r="A29"/>
-      <c r="B29"/>
-      <c r="C29"/>
+      <c r="B29">
+        <v>1010</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>FireCircle2</t>
+        </is>
+      </c>
       <c r="D29"/>
       <c r="E29">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>{"guid":"432ff1e3-b18d-476d-af80-d39ddc07402a","nodeType":20,"position":{"x":-491.33331298828125,"y":-2478.66650390625},"targetType":1,"skeletonDataAsset":null,"skeletonDataAssetPath":"Assets/Res/Spine/SP_Zhanshi/SP_Zhanshi_SkeletonData.asset","animationName":"Attack_01","animationDuration":"18","isAnimationLooping":false,"timeEffects":[{"triggerTime":11,"portIdValue":2315086,"legacyPortId":"de0ba361-3aba-4ef0-bb07-9b418fcae591"},{"triggerTime":24,"portIdValue":2715463,"legacyPortId":"7ecf9fe6-7c5e-46ae-bade-7922214225e2"}],"timeCues":[]}</t>
+          <t>{"guid":"3aafa9a5-4766-4204-91ab-d797aeb3c0e1","nodeType":7,"position":{"x":580.6666259765625,"y":-1987.3333740234375},"targetType":1,"endType":0}</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>{"outputNodeGuid":"356907e0-1488-4128-bfcc-7ff73cfc3330","outputPortId":1004,"inputNodeGuid":"c28fb88d-51b1-47b2-be59-859e0ac638e3","inputPortId":7001}</t>
+          <t>{"outputNodeGuid":"356907e0-1488-4128-bfcc-7ff73cfc3330","outputPortId":1002,"inputNodeGuid":"432ff1e3-b18d-476d-af80-d39ddc07402a","inputPortId":7001}</t>
         </is>
       </c>
       <c r="H29"/>
@@ -1189,16 +1193,16 @@
       <c r="C30"/>
       <c r="D30"/>
       <c r="E30">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>{"guid":"c28fb88d-51b1-47b2-be59-859e0ac638e3","nodeType":10,"position":{"x":-1220.6666259765625,"y":-1747.3333740234375},"targetType":1,"assetTags":{"Tags":[]},"grantedTags":{"Tags":[{"Name":"CD.FireCircle","HashCode":522143731,"ShortName":"FireCircle","AncestorHashCodes":[-1137859925],"AncestorNames":["CD"]}]},"applicationRequiredTags":{"Tags":[]},"applicationImmunityTags":{"Tags":[]},"removeGameEffectsWithTags":{"Tags":[]},"durationType":1,"duration":"1","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"Tags":[]},"cancelOnAbilityEnd":false,"cooldownType":0,"maxCharges":2,"chargeTime":"10"}</t>
+          <t>{"guid":"432ff1e3-b18d-476d-af80-d39ddc07402a","nodeType":20,"position":{"x":-491.33331298828125,"y":-2478.66650390625},"targetType":1,"skeletonDataAsset":null,"skeletonDataAssetPath":"Assets/Res/Spine/SP_Zhanshi/SP_Zhanshi_SkeletonData.asset","animationName":"Attack_01","animationDuration":"18","isAnimationLooping":false,"timeEffects":[{"triggerTime":11,"portIdValue":2315086,"legacyPortId":"de0ba361-3aba-4ef0-bb07-9b418fcae591"},{"triggerTime":24,"portIdValue":2715463,"legacyPortId":"7ecf9fe6-7c5e-46ae-bade-7922214225e2"}],"timeCues":[]}</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>{"outputNodeGuid":"356907e0-1488-4128-bfcc-7ff73cfc3330","outputPortId":1003,"inputNodeGuid":"9d6f459d-b588-4b64-843b-1b71e8f299ae","inputPortId":7001}</t>
+          <t>{"outputNodeGuid":"356907e0-1488-4128-bfcc-7ff73cfc3330","outputPortId":1004,"inputNodeGuid":"c28fb88d-51b1-47b2-be59-859e0ac638e3","inputPortId":7001}</t>
         </is>
       </c>
       <c r="H30"/>
@@ -1209,16 +1213,16 @@
       <c r="C31"/>
       <c r="D31"/>
       <c r="E31">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>{"guid":"356907e0-1488-4128-bfcc-7ff73cfc3330","nodeType":0,"position":{"x":-878.6666259765625,"y":-1851.3333740234375},"targetType":1,"skillId":1010,"assetTags":{"Tags":[]},"cancelAbilitiesWithTags":{"Tags":[]},"blockAbilitiesWithTags":{"Tags":[]},"activationOwnedTags":{"Tags":[]},"activationRequiredTags":{"Tags":[]},"activationBlockedTags":{"Tags":[{"Name":"CD.FireCircle","HashCode":522143731,"ShortName":"FireCircle","AncestorHashCodes":[-1137859925],"AncestorNames":["CD"]}]},"ongoingBlockedTags":{"Tags":[]},"eventOutputPorts":[]}</t>
+          <t>{"guid":"c28fb88d-51b1-47b2-be59-859e0ac638e3","nodeType":10,"position":{"x":-1220.6666259765625,"y":-1747.3333740234375},"targetType":1,"assetTags":{"Tags":[]},"grantedTags":{"Tags":[{"Name":"CD.FireCircle","HashCode":522143731,"ShortName":"FireCircle","AncestorHashCodes":[-1137859925],"AncestorNames":["CD"]}]},"applicationRequiredTags":{"Tags":[]},"applicationImmunityTags":{"Tags":[]},"removeGameEffectsWithTags":{"Tags":[]},"durationType":1,"duration":"1","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"Tags":[]},"cancelOnAbilityEnd":false,"cooldownType":0,"maxCharges":2,"chargeTime":"10"}</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>{"outputNodeGuid":"432ff1e3-b18d-476d-af80-d39ddc07402a","outputPortId":2315086,"inputNodeGuid":"90bacd9f-d882-4bba-aaa8-41ed993ac3ff","inputPortId":7001}</t>
+          <t>{"outputNodeGuid":"356907e0-1488-4128-bfcc-7ff73cfc3330","outputPortId":1003,"inputNodeGuid":"9d6f459d-b588-4b64-843b-1b71e8f299ae","inputPortId":7001}</t>
         </is>
       </c>
       <c r="H31"/>
@@ -1229,16 +1233,16 @@
       <c r="C32"/>
       <c r="D32"/>
       <c r="E32">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>{"guid":"9d6f459d-b588-4b64-843b-1b71e8f299ae","nodeType":3,"position":{"x":-1195.3333740234375,"y":-2013.3333740234375},"targetType":1,"assetTags":{"Tags":[]},"grantedTags":{"Tags":[]},"applicationRequiredTags":{"Tags":[]},"applicationImmunityTags":{"Tags":[]},"removeGameEffectsWithTags":{"Tags":[]},"durationType":0,"duration":"0","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[{"attrType":1003,"operation":0,"magnitudeSourceType":0,"fixedValue":-100.0,"formula":"","mmcType":0,"setByCallerKey":"","mmcCaptureAttribute":200,"mmcAttributeSource":0,"mmcCoefficient":1.0,"mmcUseSnapshot":true}],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"Tags":[]},"cancelOnAbilityEnd":true}</t>
+          <t>{"guid":"356907e0-1488-4128-bfcc-7ff73cfc3330","nodeType":0,"position":{"x":-878.6666259765625,"y":-1851.3333740234375},"targetType":1,"skillId":1010,"assetTags":{"Tags":[]},"cancelAbilitiesWithTags":{"Tags":[]},"blockAbilitiesWithTags":{"Tags":[]},"activationOwnedTags":{"Tags":[]},"activationRequiredTags":{"Tags":[]},"activationBlockedTags":{"Tags":[{"Name":"CD.FireCircle","HashCode":522143731,"ShortName":"FireCircle","AncestorHashCodes":[-1137859925],"AncestorNames":["CD"]}]},"ongoingBlockedTags":{"Tags":[]},"eventOutputPorts":[]}</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>{"outputNodeGuid":"90bacd9f-d882-4bba-aaa8-41ed993ac3ff","outputPortId":5001,"inputNodeGuid":"eae41233-d297-46fe-a6c8-0b5c876fbb2a","inputPortId":7001}</t>
+          <t>{"outputNodeGuid":"432ff1e3-b18d-476d-af80-d39ddc07402a","outputPortId":2315086,"inputNodeGuid":"90bacd9f-d882-4bba-aaa8-41ed993ac3ff","inputPortId":7001}</t>
         </is>
       </c>
       <c r="H32"/>
@@ -1249,16 +1253,16 @@
       <c r="C33"/>
       <c r="D33"/>
       <c r="E33">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>{"guid":"eae41233-d297-46fe-a6c8-0b5c876fbb2a","nodeType":1,"position":{"x":45.333343505859375,"y":-1806.666748046875},"targetType":0,"assetTags":{"Tags":[]},"grantedTags":{"Tags":[]},"applicationRequiredTags":{"Tags":[]},"applicationImmunityTags":{"Tags":[]},"removeGameEffectsWithTags":{"Tags":[]},"durationType":0,"duration":"0","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"Tags":[]},"cancelOnAbilityEnd":true,"damageType":0,"damageSourceType":0,"damageFixedValue":10.0,"damageFormula":"","damageMMCType":0,"damageSetByCallerKey":"","damageMMCCaptureAttribute":200,"damageMMCAttributeSource":0,"damageMMCCoefficient":1.0,"damageMMCUseSnapshot":true,"damageMultiplyByStackCount":false,"damageCalculationType":0,"enableHitKnockback":true,"knockbackDistance":1.0,"knockbackSpeed":12.0}</t>
+          <t>{"guid":"9d6f459d-b588-4b64-843b-1b71e8f299ae","nodeType":3,"position":{"x":-1195.3333740234375,"y":-2013.3333740234375},"targetType":1,"assetTags":{"Tags":[]},"grantedTags":{"Tags":[]},"applicationRequiredTags":{"Tags":[]},"applicationImmunityTags":{"Tags":[]},"removeGameEffectsWithTags":{"Tags":[]},"durationType":0,"duration":"0","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[{"attrType":1003,"operation":0,"magnitudeSourceType":0,"fixedValue":-100.0,"formula":"","mmcType":0,"setByCallerKey":"","mmcCaptureAttribute":200,"mmcAttributeSource":0,"mmcCoefficient":1.0,"mmcUseSnapshot":true}],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"Tags":[]},"cancelOnAbilityEnd":true}</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>{"outputNodeGuid":"eae41233-d297-46fe-a6c8-0b5c876fbb2a","outputPortId":3004,"inputNodeGuid":"2d7e41c4-8e90-4b61-879c-4b2e5b9486db","inputPortId":7001}</t>
+          <t>{"outputNodeGuid":"90bacd9f-d882-4bba-aaa8-41ed993ac3ff","outputPortId":5001,"inputNodeGuid":"eae41233-d297-46fe-a6c8-0b5c876fbb2a","inputPortId":7001}</t>
         </is>
       </c>
       <c r="H33"/>
@@ -1269,16 +1273,16 @@
       <c r="C34"/>
       <c r="D34"/>
       <c r="E34">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>{"guid":"90bacd9f-d882-4bba-aaa8-41ed993ac3ff","nodeType":8,"position":{"x":-400.66665649414063,"y":-1836.666748046875},"targetType":2,"assetTags":{"Tags":[]},"grantedTags":{"Tags":[]},"applicationRequiredTags":{"Tags":[]},"applicationImmunityTags":{"Tags":[]},"removeGameEffectsWithTags":{"Tags":[]},"durationType":2,"duration":"0","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"Tags":[]},"cancelOnAbilityEnd":false,"launchPositionSource":0,"launchBindingName":"center","targetPositionSource":1,"targetBindingName":"center","projectileTargetType":0,"flyOver":false,"offsetAngle":0.0,"curveHeight":0.0,"projectileEntityId":50001,"projectilePrefab":null,"projectilePrefabPath":"Assets/Res/Entity/Effect/ef_fashi_gandian_buff.prefab","speed":3.0,"maxDistance":10.0,"collisionRadius":0.5,"isPiercing":false,"maxPierceCount":1,"collisionTargetTags":{"Tags":[]},"collisionExcludeTags":{"Tags":[]},"isBouncing":true,"bounceTargetMode":0,"maxBounceCount":2,"bounceSearchRadius":10.0,"canBounceToSameTarget":false,"excludeSourceCamp":true,"bounceAngleOffset":50.0}</t>
+          <t>{"guid":"eae41233-d297-46fe-a6c8-0b5c876fbb2a","nodeType":1,"position":{"x":45.333343505859375,"y":-1806.666748046875},"targetType":0,"assetTags":{"Tags":[]},"grantedTags":{"Tags":[]},"applicationRequiredTags":{"Tags":[]},"applicationImmunityTags":{"Tags":[]},"removeGameEffectsWithTags":{"Tags":[]},"durationType":0,"duration":"0","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"Tags":[]},"cancelOnAbilityEnd":true,"damageType":0,"damageSourceType":0,"damageFixedValue":10.0,"damageFormula":"","damageMMCType":0,"damageSetByCallerKey":"","damageMMCCaptureAttribute":200,"damageMMCAttributeSource":0,"damageMMCCoefficient":1.0,"damageMMCUseSnapshot":true,"damageMultiplyByStackCount":false,"damageCalculationType":0,"enableHitKnockback":true,"knockbackDistance":1.0,"knockbackSpeed":12.0}</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>{"outputNodeGuid":"432ff1e3-b18d-476d-af80-d39ddc07402a","outputPortId":2715463,"inputNodeGuid":"3aafa9a5-4766-4204-91ab-d797aeb3c0e1","inputPortId":7001}</t>
+          <t>{"outputNodeGuid":"eae41233-d297-46fe-a6c8-0b5c876fbb2a","outputPortId":3004,"inputNodeGuid":"2d7e41c4-8e90-4b61-879c-4b2e5b9486db","inputPortId":7001}</t>
         </is>
       </c>
       <c r="H34"/>
@@ -1289,58 +1293,58 @@
       <c r="C35"/>
       <c r="D35"/>
       <c r="E35">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>{"guid":"2d7e41c4-8e90-4b61-879c-4b2e5b9486db","nodeType":14,"position":{"x":408.66665649414063,"y":-1747.3333740234375},"targetType":1,"requiredTags":{"Tags":[]},"immunityTags":{"Tags":[]},"destroyWithNode":false,"positionSource":2,"positionBindingName":"head","textType":0,"fixedText":"","contextDataKey":"DamageResult","textColor":{"r":0.0,"g":0.323091983795166,"b":1.0,"a":1.0},"criticalColor":{"r":1.0,"g":0.5,"b":0.0,"a":1.0},"missColor":{"r":0.5,"g":0.5,"b":0.5,"a":1.0},"fontSize":5.0,"criticalFontSize":60.0,"duration":1.5,"offset":{"x":0.0,"y":0.0},"moveDirection":{"x":0.0,"y":1.0}}</t>
-        </is>
-      </c>
-      <c r="G35"/>
+          <t>{"guid":"90bacd9f-d882-4bba-aaa8-41ed993ac3ff","nodeType":8,"position":{"x":-400.66665649414063,"y":-1836.666748046875},"targetType":2,"assetTags":{"Tags":[]},"grantedTags":{"Tags":[]},"applicationRequiredTags":{"Tags":[]},"applicationImmunityTags":{"Tags":[]},"removeGameEffectsWithTags":{"Tags":[]},"durationType":2,"duration":"0","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"Tags":[]},"cancelOnAbilityEnd":false,"launchPositionSource":0,"launchBindingName":"center","targetPositionSource":1,"targetBindingName":"center","projectileTargetType":0,"flyOver":false,"offsetAngle":0.0,"curveHeight":0.0,"projectileEntityId":50001,"projectilePrefab":null,"projectilePrefabPath":"Assets/Res/Entity/Effect/ef_fashi_gandian_buff.prefab","speed":3.0,"maxDistance":10.0,"collisionRadius":0.5,"isPiercing":false,"maxPierceCount":1,"collisionTargetTags":{"Tags":[]},"collisionExcludeTags":{"Tags":[]},"isBouncing":true,"bounceTargetMode":0,"maxBounceCount":2,"bounceSearchRadius":10.0,"canBounceToSameTarget":false,"excludeSourceCamp":true,"bounceAngleOffset":50.0}</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>{"outputNodeGuid":"432ff1e3-b18d-476d-af80-d39ddc07402a","outputPortId":2715463,"inputNodeGuid":"3aafa9a5-4766-4204-91ab-d797aeb3c0e1","inputPortId":7001}</t>
+        </is>
+      </c>
       <c r="H35"/>
     </row>
     <row r="36">
       <c r="A36"/>
-      <c r="B36">
-        <v>1005</v>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>God</t>
-        </is>
-      </c>
+      <c r="B36"/>
+      <c r="C36"/>
       <c r="D36"/>
       <c r="E36">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>{"guid":"9d6f459d-b588-4b64-843b-1b71e8f299ae","nodeType":3,"position":{"x":-1186.6666259765625,"y":-2011.3333740234375},"targetType":1,"assetTags":{"Tags":[]},"grantedTags":{"Tags":[]},"applicationRequiredTags":{"Tags":[]},"applicationImmunityTags":{"Tags":[]},"removeGameEffectsWithTags":{"Tags":[]},"durationType":0,"duration":"0","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[{"attrType":100,"operation":0,"magnitudeSourceType":0,"fixedValue":10.0,"formula":"","mmcType":0,"setByCallerKey":"","mmcCaptureAttribute":200,"mmcAttributeSource":0,"mmcCoefficient":1.0,"mmcUseSnapshot":true}],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"Tags":[]},"cancelOnAbilityEnd":true}</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>{"outputNodeGuid":"356907e0-1488-4128-bfcc-7ff73cfc3330","outputPortId":1002,"inputNodeGuid":"432ff1e3-b18d-476d-af80-d39ddc07402a","inputPortId":7001}</t>
-        </is>
-      </c>
+          <t>{"guid":"2d7e41c4-8e90-4b61-879c-4b2e5b9486db","nodeType":14,"position":{"x":408.66665649414063,"y":-1747.3333740234375},"targetType":1,"requiredTags":{"Tags":[]},"immunityTags":{"Tags":[]},"destroyWithNode":false,"positionSource":2,"positionBindingName":"head","textType":0,"fixedText":"","contextDataKey":"DamageResult","textColor":{"r":0.0,"g":0.323091983795166,"b":1.0,"a":1.0},"criticalColor":{"r":1.0,"g":0.5,"b":0.0,"a":1.0},"missColor":{"r":0.5,"g":0.5,"b":0.5,"a":1.0},"fontSize":5.0,"criticalFontSize":60.0,"duration":1.5,"offset":{"x":0.0,"y":0.0},"moveDirection":{"x":0.0,"y":1.0}}</t>
+        </is>
+      </c>
+      <c r="G36"/>
       <c r="H36"/>
     </row>
     <row r="37">
       <c r="A37"/>
-      <c r="B37"/>
-      <c r="C37"/>
+      <c r="B37">
+        <v>1005</v>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>God</t>
+        </is>
+      </c>
       <c r="D37"/>
       <c r="E37">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>{"guid":"f73ba91e-a76b-456c-b19c-a5176809d5f5","nodeType":7,"position":{"x":700.0,"y":-1856.666748046875},"targetType":1,"endType":0}</t>
+          <t>{"guid":"9d6f459d-b588-4b64-843b-1b71e8f299ae","nodeType":3,"position":{"x":-1186.6666259765625,"y":-2011.3333740234375},"targetType":1,"assetTags":{"Tags":[]},"grantedTags":{"Tags":[]},"applicationRequiredTags":{"Tags":[]},"applicationImmunityTags":{"Tags":[]},"removeGameEffectsWithTags":{"Tags":[]},"durationType":0,"duration":"0","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[{"attrType":100,"operation":0,"magnitudeSourceType":0,"fixedValue":10.0,"formula":"","mmcType":0,"setByCallerKey":"","mmcCaptureAttribute":200,"mmcAttributeSource":0,"mmcCoefficient":1.0,"mmcUseSnapshot":true}],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"Tags":[]},"cancelOnAbilityEnd":true}</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>{"outputNodeGuid":"356907e0-1488-4128-bfcc-7ff73cfc3330","outputPortId":1004,"inputNodeGuid":"c28fb88d-51b1-47b2-be59-859e0ac638e3","inputPortId":7001}</t>
+          <t>{"outputNodeGuid":"356907e0-1488-4128-bfcc-7ff73cfc3330","outputPortId":1002,"inputNodeGuid":"432ff1e3-b18d-476d-af80-d39ddc07402a","inputPortId":7001}</t>
         </is>
       </c>
       <c r="H37"/>
@@ -1351,16 +1355,16 @@
       <c r="C38"/>
       <c r="D38"/>
       <c r="E38">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>{"guid":"c28fb88d-51b1-47b2-be59-859e0ac638e3","nodeType":10,"position":{"x":-1186.6666259765625,"y":-1747.3333740234375},"targetType":1,"assetTags":{"Tags":[]},"grantedTags":{"Tags":[{"Name":"CD.God","HashCode":1317201809,"ShortName":"God","AncestorHashCodes":[-1137859925],"AncestorNames":["CD"]}]},"applicationRequiredTags":{"Tags":[]},"applicationImmunityTags":{"Tags":[]},"removeGameEffectsWithTags":{"Tags":[]},"durationType":1,"duration":"5","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"Tags":[]},"cancelOnAbilityEnd":false,"cooldownType":0,"maxCharges":2,"chargeTime":"10"}</t>
+          <t>{"guid":"f73ba91e-a76b-456c-b19c-a5176809d5f5","nodeType":7,"position":{"x":700.0,"y":-1856.666748046875},"targetType":1,"endType":0}</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>{"outputNodeGuid":"356907e0-1488-4128-bfcc-7ff73cfc3330","outputPortId":1003,"inputNodeGuid":"9d6f459d-b588-4b64-843b-1b71e8f299ae","inputPortId":7001}</t>
+          <t>{"outputNodeGuid":"356907e0-1488-4128-bfcc-7ff73cfc3330","outputPortId":1004,"inputNodeGuid":"c28fb88d-51b1-47b2-be59-859e0ac638e3","inputPortId":7001}</t>
         </is>
       </c>
       <c r="H38"/>
@@ -1371,16 +1375,16 @@
       <c r="C39"/>
       <c r="D39"/>
       <c r="E39">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>{"guid":"091ecddb-f80b-4c00-aa06-f9bc718618d2","nodeType":22,"position":{"x":-93.333328247070313,"y":-1708.666748046875},"targetType":0,"assetTags":{"Tags":[]},"grantedTags":{"Tags":[]},"applicationRequiredTags":{"Tags":[]},"applicationImmunityTags":{"Tags":[]},"removeGameEffectsWithTags":{"Tags":[]},"durationType":1,"duration":"0.5","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"Tags":[]},"cancelOnAbilityEnd":false,"displaceType":1,"speed":10.0,"distance":3.0,"minDistance":0.5,"pointSource":0,"pointBindingName":""}</t>
+          <t>{"guid":"c28fb88d-51b1-47b2-be59-859e0ac638e3","nodeType":10,"position":{"x":-1186.6666259765625,"y":-1747.3333740234375},"targetType":1,"assetTags":{"Tags":[]},"grantedTags":{"Tags":[{"Name":"CD.God","HashCode":1317201809,"ShortName":"God","AncestorHashCodes":[-1137859925],"AncestorNames":["CD"]}]},"applicationRequiredTags":{"Tags":[]},"applicationImmunityTags":{"Tags":[]},"removeGameEffectsWithTags":{"Tags":[]},"durationType":1,"duration":"5","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"Tags":[]},"cancelOnAbilityEnd":false,"cooldownType":0,"maxCharges":2,"chargeTime":"10"}</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>{"outputNodeGuid":"432ff1e3-b18d-476d-af80-d39ddc07402a","outputPortId":2000539,"inputNodeGuid":"f73ba91e-a76b-456c-b19c-a5176809d5f5","inputPortId":7001}</t>
+          <t>{"outputNodeGuid":"356907e0-1488-4128-bfcc-7ff73cfc3330","outputPortId":1003,"inputNodeGuid":"9d6f459d-b588-4b64-843b-1b71e8f299ae","inputPortId":7001}</t>
         </is>
       </c>
       <c r="H39"/>
@@ -1391,16 +1395,16 @@
       <c r="C40"/>
       <c r="D40"/>
       <c r="E40">
-        <v>4</v>
+        <v>22</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>{"guid":"e33ab94c-1496-4d6a-ba5e-1afd38bb0c30","nodeType":4,"position":{"x":-452.0,"y":-1786.666748046875},"targetType":1,"searchShapeType":0,"searchLineType":0,"positionSource":0,"positionBindingName":"center","searchCircleRadius":4.0,"searchSectorRadius":2.0,"searchSectorAngle":180.0,"searchLineDirectionOffsetAngle":0.0,"searchLineDirectionWidth":1.0,"searchLineDirectionLength":10.0,"lineStartPositionSource":0,"lineStartBindingName":"","lineEndPositionSource":1,"lineEndBindingName":"","searchLineBetweenWidth":1.0,"searchLineAbsoluteAngle":0.0,"searchLineAbsoluteWidth":1.0,"searchLineAbsoluteLength":10.0,"maxTargets":999,"searchTargetTags":{"Tags":[{"Name":"unitType.monster","HashCode":-2021655864,"ShortName":"monster","AncestorHashCodes":[1600484460],"AncestorNames":["unitType"]}]},"searchExcludeTags":{"Tags":[]}}</t>
+          <t>{"guid":"091ecddb-f80b-4c00-aa06-f9bc718618d2","nodeType":22,"position":{"x":-93.333328247070313,"y":-1708.666748046875},"targetType":0,"assetTags":{"Tags":[]},"grantedTags":{"Tags":[]},"applicationRequiredTags":{"Tags":[]},"applicationImmunityTags":{"Tags":[]},"removeGameEffectsWithTags":{"Tags":[]},"durationType":1,"duration":"0.5","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"Tags":[]},"cancelOnAbilityEnd":false,"displaceType":1,"speed":10.0,"distance":3.0,"minDistance":0.5,"pointSource":0,"pointBindingName":""}</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>{"outputNodeGuid":"432ff1e3-b18d-476d-af80-d39ddc07402a","outputPortId":2315086,"inputNodeGuid":"e33ab94c-1496-4d6a-ba5e-1afd38bb0c30","inputPortId":7001}</t>
+          <t>{"outputNodeGuid":"432ff1e3-b18d-476d-af80-d39ddc07402a","outputPortId":2000539,"inputNodeGuid":"f73ba91e-a76b-456c-b19c-a5176809d5f5","inputPortId":7001}</t>
         </is>
       </c>
       <c r="H40"/>
@@ -1411,16 +1415,16 @@
       <c r="C41"/>
       <c r="D41"/>
       <c r="E41">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>{"guid":"432ff1e3-b18d-476d-af80-d39ddc07402a","nodeType":20,"position":{"x":-646.0,"y":-2456.0},"targetType":1,"skeletonDataAsset":null,"skeletonDataAssetPath":"Assets/Res/Spine/SP_Zhanshi/SP_Zhanshi_SkeletonData.asset","animationName":"Skill_attack_1009","animationDuration":"25","isAnimationLooping":false,"timeEffects":[{"triggerTime":4,"portIdValue":2315086,"legacyPortId":"de0ba361-3aba-4ef0-bb07-9b418fcae591"},{"triggerTime":25,"portIdValue":2000539,"legacyPortId":"f41c85e0-7f26-494e-9ffc-4a06c980f811"}],"timeCues":[{"startTime":0,"endTime":75,"portIdValue":2287012,"legacyPortId":"8dea1941-c520-4f9a-aee0-40932c8542ef"}]}</t>
+          <t>{"guid":"e33ab94c-1496-4d6a-ba5e-1afd38bb0c30","nodeType":4,"position":{"x":-452.0,"y":-1786.666748046875},"targetType":1,"searchShapeType":0,"searchLineType":0,"positionSource":0,"positionBindingName":"center","searchCircleRadius":4.0,"searchSectorRadius":2.0,"searchSectorAngle":180.0,"searchLineDirectionOffsetAngle":0.0,"searchLineDirectionWidth":1.0,"searchLineDirectionLength":10.0,"lineStartPositionSource":0,"lineStartBindingName":"","lineEndPositionSource":1,"lineEndBindingName":"","searchLineBetweenWidth":1.0,"searchLineAbsoluteAngle":0.0,"searchLineAbsoluteWidth":1.0,"searchLineAbsoluteLength":10.0,"maxTargets":999,"searchTargetTags":{"Tags":[{"Name":"unitType.monster","HashCode":-2021655864,"ShortName":"monster","AncestorHashCodes":[1600484460],"AncestorNames":["unitType"]}]},"searchExcludeTags":{"Tags":[]}}</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>{"outputNodeGuid":"432ff1e3-b18d-476d-af80-d39ddc07402a","outputPortId":2287012,"inputNodeGuid":"cde57fb8-b693-4da8-a4a8-fd61e56c5dcd","inputPortId":7001}</t>
+          <t>{"outputNodeGuid":"432ff1e3-b18d-476d-af80-d39ddc07402a","outputPortId":2315086,"inputNodeGuid":"e33ab94c-1496-4d6a-ba5e-1afd38bb0c30","inputPortId":7001}</t>
         </is>
       </c>
       <c r="H41"/>
@@ -1431,16 +1435,16 @@
       <c r="C42"/>
       <c r="D42"/>
       <c r="E42">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>{"guid":"356907e0-1488-4128-bfcc-7ff73cfc3330","nodeType":0,"position":{"x":-878.6666259765625,"y":-1853.3333740234375},"targetType":1,"skillId":1005,"assetTags":{"Tags":[]},"cancelAbilitiesWithTags":{"Tags":[]},"blockAbilitiesWithTags":{"Tags":[]},"activationOwnedTags":{"Tags":[{"Name":"Skill.Running","HashCode":-51601538,"ShortName":"Running","AncestorHashCodes":[1312877309],"AncestorNames":["Skill"]}]},"activationRequiredTags":{"Tags":[]},"activationBlockedTags":{"Tags":[{"Name":"CD.RecBlood","HashCode":1043024739,"ShortName":"RecBlood","AncestorHashCodes":[-1137859925],"AncestorNames":["CD"]},{"Name":"Skill.Running","HashCode":-51601538,"ShortName":"Running","AncestorHashCodes":[1312877309],"AncestorNames":["Skill"]}]},"ongoingBlockedTags":{"Tags":[]},"eventOutputPorts":[]}</t>
+          <t>{"guid":"432ff1e3-b18d-476d-af80-d39ddc07402a","nodeType":20,"position":{"x":-646.0,"y":-2456.0},"targetType":1,"skeletonDataAsset":null,"skeletonDataAssetPath":"Assets/Res/Spine/SP_Zhanshi/SP_Zhanshi_SkeletonData.asset","animationName":"Skill_attack_1009","animationDuration":"25","isAnimationLooping":false,"timeEffects":[{"triggerTime":4,"portIdValue":2315086,"legacyPortId":"de0ba361-3aba-4ef0-bb07-9b418fcae591"},{"triggerTime":25,"portIdValue":2000539,"legacyPortId":"f41c85e0-7f26-494e-9ffc-4a06c980f811"}],"timeCues":[{"startTime":0,"endTime":75,"portIdValue":2287012,"legacyPortId":"8dea1941-c520-4f9a-aee0-40932c8542ef"}]}</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>{"outputNodeGuid":"e33ab94c-1496-4d6a-ba5e-1afd38bb0c30","outputPortId":4001,"inputNodeGuid":"091ecddb-f80b-4c00-aa06-f9bc718618d2","inputPortId":7001}</t>
+          <t>{"outputNodeGuid":"432ff1e3-b18d-476d-af80-d39ddc07402a","outputPortId":2287012,"inputNodeGuid":"cde57fb8-b693-4da8-a4a8-fd61e56c5dcd","inputPortId":7001}</t>
         </is>
       </c>
       <c r="H42"/>
@@ -1451,58 +1455,58 @@
       <c r="C43"/>
       <c r="D43"/>
       <c r="E43">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>{"guid":"cde57fb8-b693-4da8-a4a8-fd61e56c5dcd","nodeType":12,"position":{"x":677.3333740234375,"y":-1998.666748046875},"targetType":1,"requiredTags":{"Tags":[]},"immunityTags":{"Tags":[]},"destroyWithNode":false,"positionSource":0,"particleEntityId":50009,"particlePrefab":null,"particlePrefabPath":"Assets/Res/Entity/Effect/ef_Zhanshi_zhandounuhou_01.prefab","particleBindingName":"down","particleOffset":{"x":0.0,"y":0.0,"z":0.0},"particleScale":{"x":1.0,"y":1.0,"z":1.0},"attachToTarget":false,"particleLoop":false}</t>
-        </is>
-      </c>
-      <c r="G43"/>
+          <t>{"guid":"356907e0-1488-4128-bfcc-7ff73cfc3330","nodeType":0,"position":{"x":-878.6666259765625,"y":-1853.3333740234375},"targetType":1,"skillId":1005,"assetTags":{"Tags":[]},"cancelAbilitiesWithTags":{"Tags":[]},"blockAbilitiesWithTags":{"Tags":[]},"activationOwnedTags":{"Tags":[{"Name":"Skill.Running","HashCode":-51601538,"ShortName":"Running","AncestorHashCodes":[1312877309],"AncestorNames":["Skill"]}]},"activationRequiredTags":{"Tags":[]},"activationBlockedTags":{"Tags":[{"Name":"CD.RecBlood","HashCode":1043024739,"ShortName":"RecBlood","AncestorHashCodes":[-1137859925],"AncestorNames":["CD"]},{"Name":"Skill.Running","HashCode":-51601538,"ShortName":"Running","AncestorHashCodes":[1312877309],"AncestorNames":["Skill"]}]},"ongoingBlockedTags":{"Tags":[]},"eventOutputPorts":[]}</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>{"outputNodeGuid":"e33ab94c-1496-4d6a-ba5e-1afd38bb0c30","outputPortId":4001,"inputNodeGuid":"091ecddb-f80b-4c00-aa06-f9bc718618d2","inputPortId":7001}</t>
+        </is>
+      </c>
       <c r="H43"/>
     </row>
     <row r="44">
       <c r="A44"/>
-      <c r="B44">
-        <v>1007</v>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>RecBlood</t>
-        </is>
-      </c>
+      <c r="B44"/>
+      <c r="C44"/>
       <c r="D44"/>
       <c r="E44">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>{"guid":"356907e0-1488-4128-bfcc-7ff73cfc3330","nodeType":0,"position":{"x":-924.6666259765625,"y":-1886.666748046875},"targetType":1,"skillId":1007,"assetTags":{"Tags":[]},"cancelAbilitiesWithTags":{"Tags":[]},"blockAbilitiesWithTags":{"Tags":[]},"activationOwnedTags":{"Tags":[]},"activationRequiredTags":{"Tags":[]},"activationBlockedTags":{"Tags":[{"Name":"CD.RecBlood","HashCode":1163914435,"ShortName":"回血","AncestorHashCodes":[-1137859925],"AncestorNames":["CD"]}]},"ongoingBlockedTags":{"Tags":[]},"eventOutputPorts":[]}</t>
-        </is>
-      </c>
-      <c r="G44" t="inlineStr">
-        <is>
-          <t>{"outputNodeGuid":"6d127270-5aeb-4542-9183-8d2d028d6786","outputPortId":3001,"inputNodeGuid":"cde57fb8-b693-4da8-a4a8-fd61e56c5dcd","inputPortId":7001}</t>
-        </is>
-      </c>
+          <t>{"guid":"cde57fb8-b693-4da8-a4a8-fd61e56c5dcd","nodeType":12,"position":{"x":677.3333740234375,"y":-1998.666748046875},"targetType":1,"requiredTags":{"Tags":[]},"immunityTags":{"Tags":[]},"destroyWithNode":false,"positionSource":0,"particleEntityId":50009,"particlePrefab":null,"particlePrefabPath":"Assets/Res/Entity/Effect/ef_Zhanshi_zhandounuhou_01.prefab","particleBindingName":"down","particleOffset":{"x":0.0,"y":0.0,"z":0.0},"particleScale":{"x":1.0,"y":1.0,"z":1.0},"attachToTarget":false,"particleLoop":false}</t>
+        </is>
+      </c>
+      <c r="G44"/>
       <c r="H44"/>
     </row>
     <row r="45">
       <c r="A45"/>
-      <c r="B45"/>
-      <c r="C45"/>
+      <c r="B45">
+        <v>1007</v>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>RecBlood</t>
+        </is>
+      </c>
       <c r="D45"/>
       <c r="E45">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>{"guid":"c28fb88d-51b1-47b2-be59-859e0ac638e3","nodeType":10,"position":{"x":-1156.0,"y":-1801.3333740234375},"targetType":1,"assetTags":{"Tags":[]},"grantedTags":{"Tags":[{"Name":"CD.RecBlood","HashCode":1163914435,"ShortName":"回血","AncestorHashCodes":[-1137859925],"AncestorNames":["CD"]}]},"applicationRequiredTags":{"Tags":[]},"applicationImmunityTags":{"Tags":[]},"removeGameEffectsWithTags":{"Tags":[]},"durationType":1,"duration":"3","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"Tags":[]},"cancelOnAbilityEnd":false,"cooldownType":0,"maxCharges":2,"chargeTime":"10"}</t>
+          <t>{"guid":"356907e0-1488-4128-bfcc-7ff73cfc3330","nodeType":0,"position":{"x":-924.6666259765625,"y":-1886.666748046875},"targetType":1,"skillId":1007,"assetTags":{"Tags":[]},"cancelAbilitiesWithTags":{"Tags":[]},"blockAbilitiesWithTags":{"Tags":[]},"activationOwnedTags":{"Tags":[]},"activationRequiredTags":{"Tags":[]},"activationBlockedTags":{"Tags":[{"Name":"CD.RecBlood","HashCode":1163914435,"ShortName":"回血","AncestorHashCodes":[-1137859925],"AncestorNames":["CD"]}]},"ongoingBlockedTags":{"Tags":[]},"eventOutputPorts":[]}</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>{"outputNodeGuid":"6d127270-5aeb-4542-9183-8d2d028d6786","outputPortId":3004,"inputNodeGuid":"becb4d53-8a9e-4dc0-95a3-618d1e79ecc7","inputPortId":7001}</t>
+          <t>{"outputNodeGuid":"6d127270-5aeb-4542-9183-8d2d028d6786","outputPortId":3001,"inputNodeGuid":"cde57fb8-b693-4da8-a4a8-fd61e56c5dcd","inputPortId":7001}</t>
         </is>
       </c>
       <c r="H45"/>
@@ -1513,16 +1517,16 @@
       <c r="C46"/>
       <c r="D46"/>
       <c r="E46">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>{"guid":"011aad56-e96c-41eb-9d85-e793d74a40bb","nodeType":7,"position":{"x":-333.33331298828125,"y":-1780.0},"targetType":1,"endType":0}</t>
+          <t>{"guid":"c28fb88d-51b1-47b2-be59-859e0ac638e3","nodeType":10,"position":{"x":-1156.0,"y":-1801.3333740234375},"targetType":1,"assetTags":{"Tags":[]},"grantedTags":{"Tags":[{"Name":"CD.RecBlood","HashCode":1163914435,"ShortName":"回血","AncestorHashCodes":[-1137859925],"AncestorNames":["CD"]}]},"applicationRequiredTags":{"Tags":[]},"applicationImmunityTags":{"Tags":[]},"removeGameEffectsWithTags":{"Tags":[]},"durationType":1,"duration":"3","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"Tags":[]},"cancelOnAbilityEnd":false,"cooldownType":0,"maxCharges":2,"chargeTime":"10"}</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>{"outputNodeGuid":"356907e0-1488-4128-bfcc-7ff73cfc3330","outputPortId":1001,"inputNodeGuid":"6d127270-5aeb-4542-9183-8d2d028d6786","inputPortId":7001}</t>
+          <t>{"outputNodeGuid":"6d127270-5aeb-4542-9183-8d2d028d6786","outputPortId":3004,"inputNodeGuid":"becb4d53-8a9e-4dc0-95a3-618d1e79ecc7","inputPortId":7001}</t>
         </is>
       </c>
       <c r="H46"/>
@@ -1533,16 +1537,16 @@
       <c r="C47"/>
       <c r="D47"/>
       <c r="E47">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>{"guid":"6d127270-5aeb-4542-9183-8d2d028d6786","nodeType":2,"position":{"x":-550.6666259765625,"y":-2050.0},"targetType":1,"assetTags":{"Tags":[]},"grantedTags":{"Tags":[]},"applicationRequiredTags":{"Tags":[]},"applicationImmunityTags":{"Tags":[]},"removeGameEffectsWithTags":{"Tags":[]},"durationType":0,"duration":"0","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"Tags":[]},"cancelOnAbilityEnd":false,"healSourceType":0,"healFixedValue":10.0,"healFormula":"","healMMCType":0,"healSetByCallerKey":"","healMMCCaptureAttribute":1007,"healMMCAttributeSource":0,"healMMCCoefficient":1.0,"healMMCUseSnapshot":true,"healMultiplyByStackCount":false,"healCalculationType":0}</t>
+          <t>{"guid":"011aad56-e96c-41eb-9d85-e793d74a40bb","nodeType":7,"position":{"x":-333.33331298828125,"y":-1780.0},"targetType":1,"endType":0}</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>{"outputNodeGuid":"356907e0-1488-4128-bfcc-7ff73cfc3330","outputPortId":1004,"inputNodeGuid":"c28fb88d-51b1-47b2-be59-859e0ac638e3","inputPortId":7001}</t>
+          <t>{"outputNodeGuid":"356907e0-1488-4128-bfcc-7ff73cfc3330","outputPortId":1001,"inputNodeGuid":"6d127270-5aeb-4542-9183-8d2d028d6786","inputPortId":7001}</t>
         </is>
       </c>
       <c r="H47"/>
@@ -1553,16 +1557,16 @@
       <c r="C48"/>
       <c r="D48"/>
       <c r="E48">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>{"guid":"becb4d53-8a9e-4dc0-95a3-618d1e79ecc7","nodeType":14,"position":{"x":-303.33331298828125,"y":-1952.666748046875},"targetType":1,"requiredTags":{"Tags":[]},"immunityTags":{"Tags":[]},"destroyWithNode":false,"positionSource":2,"positionBindingName":"head","textType":1,"fixedText":"","contextDataKey":"Heal","textColor":{"r":0.25257891416549683,"g":0.96226418018341064,"b":0.1180134117603302,"a":1.0},"criticalColor":{"r":1.0,"g":0.5,"b":0.0,"a":1.0},"missColor":{"r":0.5,"g":0.5,"b":0.5,"a":1.0},"fontSize":5.0,"criticalFontSize":60.0,"duration":1.5,"offset":{"x":0.0,"y":0.0},"moveDirection":{"x":0.0,"y":1.0}}</t>
+          <t>{"guid":"6d127270-5aeb-4542-9183-8d2d028d6786","nodeType":2,"position":{"x":-550.6666259765625,"y":-2050.0},"targetType":1,"assetTags":{"Tags":[]},"grantedTags":{"Tags":[]},"applicationRequiredTags":{"Tags":[]},"applicationImmunityTags":{"Tags":[]},"removeGameEffectsWithTags":{"Tags":[]},"durationType":0,"duration":"0","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"Tags":[]},"cancelOnAbilityEnd":false,"healSourceType":0,"healFixedValue":10.0,"healFormula":"","healMMCType":0,"healSetByCallerKey":"","healMMCCaptureAttribute":1007,"healMMCAttributeSource":0,"healMMCCoefficient":1.0,"healMMCUseSnapshot":true,"healMultiplyByStackCount":false,"healCalculationType":0}</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>{"outputNodeGuid":"6d127270-5aeb-4542-9183-8d2d028d6786","outputPortId":3004,"inputNodeGuid":"011aad56-e96c-41eb-9d85-e793d74a40bb","inputPortId":7001}</t>
+          <t>{"outputNodeGuid":"356907e0-1488-4128-bfcc-7ff73cfc3330","outputPortId":1004,"inputNodeGuid":"c28fb88d-51b1-47b2-be59-859e0ac638e3","inputPortId":7001}</t>
         </is>
       </c>
       <c r="H48"/>
@@ -1573,16 +1577,16 @@
       <c r="C49"/>
       <c r="D49"/>
       <c r="E49">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>{"guid":"3cc340e3-1583-428e-ada4-c4e8539725d6","nodeType":3,"position":{"x":-1256.0,"y":-2008.0},"targetType":1,"assetTags":{"Tags":[]},"grantedTags":{"Tags":[]},"applicationRequiredTags":{"Tags":[]},"applicationImmunityTags":{"Tags":[]},"removeGameEffectsWithTags":{"Tags":[]},"durationType":0,"duration":"0","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[{"attrType":1003,"operation":0,"magnitudeSourceType":0,"fixedValue":100.0,"formula":"","mmcType":0,"setByCallerKey":"","mmcCaptureAttribute":1006,"mmcAttributeSource":0,"mmcCoefficient":1.0,"mmcUseSnapshot":true}],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"Tags":[]},"cancelOnAbilityEnd":false}</t>
+          <t>{"guid":"becb4d53-8a9e-4dc0-95a3-618d1e79ecc7","nodeType":14,"position":{"x":-303.33331298828125,"y":-1952.666748046875},"targetType":1,"requiredTags":{"Tags":[]},"immunityTags":{"Tags":[]},"destroyWithNode":false,"positionSource":2,"positionBindingName":"head","textType":1,"fixedText":"","contextDataKey":"Heal","textColor":{"r":0.25257891416549683,"g":0.96226418018341064,"b":0.1180134117603302,"a":1.0},"criticalColor":{"r":1.0,"g":0.5,"b":0.0,"a":1.0},"missColor":{"r":0.5,"g":0.5,"b":0.5,"a":1.0},"fontSize":5.0,"criticalFontSize":60.0,"duration":1.5,"offset":{"x":0.0,"y":0.0},"moveDirection":{"x":0.0,"y":1.0}}</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>{"outputNodeGuid":"356907e0-1488-4128-bfcc-7ff73cfc3330","outputPortId":1003,"inputNodeGuid":"3cc340e3-1583-428e-ada4-c4e8539725d6","inputPortId":7001}</t>
+          <t>{"outputNodeGuid":"6d127270-5aeb-4542-9183-8d2d028d6786","outputPortId":3004,"inputNodeGuid":"011aad56-e96c-41eb-9d85-e793d74a40bb","inputPortId":7001}</t>
         </is>
       </c>
       <c r="H49"/>
@@ -1593,58 +1597,58 @@
       <c r="C50"/>
       <c r="D50"/>
       <c r="E50">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>{"guid":"cde57fb8-b693-4da8-a4a8-fd61e56c5dcd","nodeType":12,"position":{"x":-303.33331298828125,"y":-2072.666748046875},"targetType":1,"requiredTags":{"Tags":[]},"immunityTags":{"Tags":[]},"destroyWithNode":false,"positionSource":0,"particleEntityId":50004,"particlePrefab":null,"particlePrefabPath":"Assets/Res/Entity/Effect/ef_skill_zhanshi_huifunengliang.prefab","particleBindingName":"down","particleOffset":{"x":0.0,"y":0.0,"z":0.0},"particleScale":{"x":1.0,"y":1.0,"z":1.0},"attachToTarget":false,"particleLoop":false}</t>
-        </is>
-      </c>
-      <c r="G50"/>
+          <t>{"guid":"3cc340e3-1583-428e-ada4-c4e8539725d6","nodeType":3,"position":{"x":-1256.0,"y":-2008.0},"targetType":1,"assetTags":{"Tags":[]},"grantedTags":{"Tags":[]},"applicationRequiredTags":{"Tags":[]},"applicationImmunityTags":{"Tags":[]},"removeGameEffectsWithTags":{"Tags":[]},"durationType":0,"duration":"0","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[{"attrType":1003,"operation":0,"magnitudeSourceType":0,"fixedValue":100.0,"formula":"","mmcType":0,"setByCallerKey":"","mmcCaptureAttribute":1006,"mmcAttributeSource":0,"mmcCoefficient":1.0,"mmcUseSnapshot":true}],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"Tags":[]},"cancelOnAbilityEnd":false}</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>{"outputNodeGuid":"356907e0-1488-4128-bfcc-7ff73cfc3330","outputPortId":1003,"inputNodeGuid":"3cc340e3-1583-428e-ada4-c4e8539725d6","inputPortId":7001}</t>
+        </is>
+      </c>
       <c r="H50"/>
     </row>
     <row r="51">
       <c r="A51"/>
-      <c r="B51">
-        <v>1003</v>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>RuFood</t>
-        </is>
-      </c>
+      <c r="B51"/>
+      <c r="C51"/>
       <c r="D51"/>
       <c r="E51">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>{"guid":"9d6f459d-b588-4b64-843b-1b71e8f299ae","nodeType":3,"position":{"x":-1186.6666259765625,"y":-2011.3333740234375},"targetType":1,"assetTags":{"Tags":[]},"grantedTags":{"Tags":[]},"applicationRequiredTags":{"Tags":[]},"applicationImmunityTags":{"Tags":[]},"removeGameEffectsWithTags":{"Tags":[]},"durationType":0,"duration":"0","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[{"attrType":100,"operation":0,"magnitudeSourceType":0,"fixedValue":10.0,"formula":"","mmcType":0,"setByCallerKey":"","mmcCaptureAttribute":200,"mmcAttributeSource":0,"mmcCoefficient":1.0,"mmcUseSnapshot":true}],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"Tags":[]},"cancelOnAbilityEnd":true}</t>
-        </is>
-      </c>
-      <c r="G51" t="inlineStr">
-        <is>
-          <t>{"outputNodeGuid":"356907e0-1488-4128-bfcc-7ff73cfc3330","outputPortId":1002,"inputNodeGuid":"432ff1e3-b18d-476d-af80-d39ddc07402a","inputPortId":7001}</t>
-        </is>
-      </c>
+          <t>{"guid":"cde57fb8-b693-4da8-a4a8-fd61e56c5dcd","nodeType":12,"position":{"x":-303.33331298828125,"y":-2072.666748046875},"targetType":1,"requiredTags":{"Tags":[]},"immunityTags":{"Tags":[]},"destroyWithNode":false,"positionSource":0,"particleEntityId":50004,"particlePrefab":null,"particlePrefabPath":"Assets/Res/Entity/Effect/ef_skill_zhanshi_huifunengliang.prefab","particleBindingName":"down","particleOffset":{"x":0.0,"y":0.0,"z":0.0},"particleScale":{"x":1.0,"y":1.0,"z":1.0},"attachToTarget":false,"particleLoop":false}</t>
+        </is>
+      </c>
+      <c r="G51"/>
       <c r="H51"/>
     </row>
     <row r="52">
       <c r="A52"/>
-      <c r="B52"/>
-      <c r="C52"/>
+      <c r="B52">
+        <v>1003</v>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>RuFood</t>
+        </is>
+      </c>
       <c r="D52"/>
       <c r="E52">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>{"guid":"c28fb88d-51b1-47b2-be59-859e0ac638e3","nodeType":10,"position":{"x":-1186.6666259765625,"y":-1747.3333740234375},"targetType":1,"assetTags":{"Tags":[]},"grantedTags":{"Tags":[{"Name":"CD.RuFood","HashCode":-1045902856,"ShortName":"RuFood","AncestorHashCodes":[-1137859925],"AncestorNames":["CD"]}]},"applicationRequiredTags":{"Tags":[]},"applicationImmunityTags":{"Tags":[]},"removeGameEffectsWithTags":{"Tags":[]},"durationType":1,"duration":"5","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"Tags":[]},"cancelOnAbilityEnd":false,"cooldownType":0,"maxCharges":2,"chargeTime":"10"}</t>
+          <t>{"guid":"9d6f459d-b588-4b64-843b-1b71e8f299ae","nodeType":3,"position":{"x":-1186.6666259765625,"y":-2011.3333740234375},"targetType":1,"assetTags":{"Tags":[]},"grantedTags":{"Tags":[]},"applicationRequiredTags":{"Tags":[]},"applicationImmunityTags":{"Tags":[]},"removeGameEffectsWithTags":{"Tags":[]},"durationType":0,"duration":"0","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[{"attrType":100,"operation":0,"magnitudeSourceType":0,"fixedValue":10.0,"formula":"","mmcType":0,"setByCallerKey":"","mmcCaptureAttribute":200,"mmcAttributeSource":0,"mmcCoefficient":1.0,"mmcUseSnapshot":true}],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"Tags":[]},"cancelOnAbilityEnd":true}</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>{"outputNodeGuid":"356907e0-1488-4128-bfcc-7ff73cfc3330","outputPortId":1004,"inputNodeGuid":"c28fb88d-51b1-47b2-be59-859e0ac638e3","inputPortId":7001}</t>
+          <t>{"outputNodeGuid":"356907e0-1488-4128-bfcc-7ff73cfc3330","outputPortId":1002,"inputNodeGuid":"432ff1e3-b18d-476d-af80-d39ddc07402a","inputPortId":7001}</t>
         </is>
       </c>
       <c r="H52"/>
@@ -1655,16 +1659,16 @@
       <c r="C53"/>
       <c r="D53"/>
       <c r="E53">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>{"guid":"f73ba91e-a76b-456c-b19c-a5176809d5f5","nodeType":7,"position":{"x":700.0,"y":-1856.666748046875},"targetType":1,"endType":0}</t>
+          <t>{"guid":"c28fb88d-51b1-47b2-be59-859e0ac638e3","nodeType":10,"position":{"x":-1186.6666259765625,"y":-1747.3333740234375},"targetType":1,"assetTags":{"Tags":[]},"grantedTags":{"Tags":[{"Name":"CD.RuFood","HashCode":-1045902856,"ShortName":"RuFood","AncestorHashCodes":[-1137859925],"AncestorNames":["CD"]}]},"applicationRequiredTags":{"Tags":[]},"applicationImmunityTags":{"Tags":[]},"removeGameEffectsWithTags":{"Tags":[]},"durationType":1,"duration":"5","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"Tags":[]},"cancelOnAbilityEnd":false,"cooldownType":0,"maxCharges":2,"chargeTime":"10"}</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>{"outputNodeGuid":"356907e0-1488-4128-bfcc-7ff73cfc3330","outputPortId":1003,"inputNodeGuid":"9d6f459d-b588-4b64-843b-1b71e8f299ae","inputPortId":7001}</t>
+          <t>{"outputNodeGuid":"356907e0-1488-4128-bfcc-7ff73cfc3330","outputPortId":1004,"inputNodeGuid":"c28fb88d-51b1-47b2-be59-859e0ac638e3","inputPortId":7001}</t>
         </is>
       </c>
       <c r="H53"/>
@@ -1675,16 +1679,16 @@
       <c r="C54"/>
       <c r="D54"/>
       <c r="E54">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>{"guid":"432ff1e3-b18d-476d-af80-d39ddc07402a","nodeType":20,"position":{"x":-452.0,"y":-2375.333251953125},"targetType":1,"skeletonDataAsset":null,"skeletonDataAssetPath":"Assets/Res/Spine/SP_Zhanshi/SP_Zhanshi_SkeletonData.asset","animationName":"Skill_attack_1005","animationDuration":"16","isAnimationLooping":false,"timeEffects":[{"triggerTime":7,"portIdValue":2315086,"legacyPortId":"de0ba361-3aba-4ef0-bb07-9b418fcae591"},{"triggerTime":16,"portIdValue":2000539,"legacyPortId":"f41c85e0-7f26-494e-9ffc-4a06c980f811"}],"timeCues":[{"startTime":6,"endTime":55,"portIdValue":2287012,"legacyPortId":"8dea1941-c520-4f9a-aee0-40932c8542ef"}]}</t>
+          <t>{"guid":"f73ba91e-a76b-456c-b19c-a5176809d5f5","nodeType":7,"position":{"x":700.0,"y":-1856.666748046875},"targetType":1,"endType":0}</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>{"outputNodeGuid":"e33ab94c-1496-4d6a-ba5e-1afd38bb0c30","outputPortId":4001,"inputNodeGuid":"cb1df36f-5729-423e-9d1a-287db5a433f0","inputPortId":7001}</t>
+          <t>{"outputNodeGuid":"356907e0-1488-4128-bfcc-7ff73cfc3330","outputPortId":1003,"inputNodeGuid":"9d6f459d-b588-4b64-843b-1b71e8f299ae","inputPortId":7001}</t>
         </is>
       </c>
       <c r="H54"/>
@@ -1695,16 +1699,16 @@
       <c r="C55"/>
       <c r="D55"/>
       <c r="E55">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>{"guid":"356907e0-1488-4128-bfcc-7ff73cfc3330","nodeType":0,"position":{"x":-878.6666259765625,"y":-1853.3333740234375},"targetType":1,"skillId":1003,"assetTags":{"Tags":[]},"cancelAbilitiesWithTags":{"Tags":[]},"blockAbilitiesWithTags":{"Tags":[]},"activationOwnedTags":{"Tags":[{"Name":"Skill.Running","HashCode":-51601538,"ShortName":"Running","AncestorHashCodes":[1312877309],"AncestorNames":["Skill"]}]},"activationRequiredTags":{"Tags":[]},"activationBlockedTags":{"Tags":[{"Name":"CD.RuFood","HashCode":-1045902856,"ShortName":"RuFood","AncestorHashCodes":[-1137859925],"AncestorNames":["CD"]},{"Name":"Skill.Running","HashCode":-51601538,"ShortName":"Running","AncestorHashCodes":[1312877309],"AncestorNames":["Skill"]}]},"ongoingBlockedTags":{"Tags":[]},"eventOutputPorts":[]}</t>
+          <t>{"guid":"432ff1e3-b18d-476d-af80-d39ddc07402a","nodeType":20,"position":{"x":-452.0,"y":-2375.333251953125},"targetType":1,"skeletonDataAsset":null,"skeletonDataAssetPath":"Assets/Res/Spine/SP_Zhanshi/SP_Zhanshi_SkeletonData.asset","animationName":"Skill_attack_1005","animationDuration":"16","isAnimationLooping":false,"timeEffects":[{"triggerTime":7,"portIdValue":2315086,"legacyPortId":"de0ba361-3aba-4ef0-bb07-9b418fcae591"},{"triggerTime":16,"portIdValue":2000539,"legacyPortId":"f41c85e0-7f26-494e-9ffc-4a06c980f811"}],"timeCues":[{"startTime":6,"endTime":55,"portIdValue":2287012,"legacyPortId":"8dea1941-c520-4f9a-aee0-40932c8542ef"}]}</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>{"outputNodeGuid":"432ff1e3-b18d-476d-af80-d39ddc07402a","outputPortId":2000539,"inputNodeGuid":"f73ba91e-a76b-456c-b19c-a5176809d5f5","inputPortId":7001}</t>
+          <t>{"outputNodeGuid":"e33ab94c-1496-4d6a-ba5e-1afd38bb0c30","outputPortId":4001,"inputNodeGuid":"cb1df36f-5729-423e-9d1a-287db5a433f0","inputPortId":7001}</t>
         </is>
       </c>
       <c r="H55"/>
@@ -1715,16 +1719,16 @@
       <c r="C56"/>
       <c r="D56"/>
       <c r="E56">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>{"guid":"cde57fb8-b693-4da8-a4a8-fd61e56c5dcd","nodeType":12,"position":{"x":676.6666259765625,"y":-1998.0},"targetType":1,"requiredTags":{"Tags":[]},"immunityTags":{"Tags":[]},"destroyWithNode":false,"positionSource":0,"particleEntityId":50007,"particlePrefab":null,"particlePrefabPath":"Assets/Res/Entity/Effect/ef_zhanshi_jcjt_01.prefab","particleBindingName":"down","particleOffset":{"x":0.0,"y":0.0,"z":0.0},"particleScale":{"x":1.0,"y":1.0,"z":1.0},"attachToTarget":false,"particleLoop":false}</t>
+          <t>{"guid":"356907e0-1488-4128-bfcc-7ff73cfc3330","nodeType":0,"position":{"x":-878.6666259765625,"y":-1853.3333740234375},"targetType":1,"skillId":1003,"assetTags":{"Tags":[]},"cancelAbilitiesWithTags":{"Tags":[]},"blockAbilitiesWithTags":{"Tags":[]},"activationOwnedTags":{"Tags":[{"Name":"Skill.Running","HashCode":-51601538,"ShortName":"Running","AncestorHashCodes":[1312877309],"AncestorNames":["Skill"]}]},"activationRequiredTags":{"Tags":[]},"activationBlockedTags":{"Tags":[{"Name":"CD.RuFood","HashCode":-1045902856,"ShortName":"RuFood","AncestorHashCodes":[-1137859925],"AncestorNames":["CD"]},{"Name":"Skill.Running","HashCode":-51601538,"ShortName":"Running","AncestorHashCodes":[1312877309],"AncestorNames":["Skill"]}]},"ongoingBlockedTags":{"Tags":[]},"eventOutputPorts":[]}</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>{"outputNodeGuid":"432ff1e3-b18d-476d-af80-d39ddc07402a","outputPortId":2315086,"inputNodeGuid":"e33ab94c-1496-4d6a-ba5e-1afd38bb0c30","inputPortId":7001}</t>
+          <t>{"outputNodeGuid":"432ff1e3-b18d-476d-af80-d39ddc07402a","outputPortId":2000539,"inputNodeGuid":"f73ba91e-a76b-456c-b19c-a5176809d5f5","inputPortId":7001}</t>
         </is>
       </c>
       <c r="H56"/>
@@ -1735,16 +1739,16 @@
       <c r="C57"/>
       <c r="D57"/>
       <c r="E57">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>{"guid":"e33ab94c-1496-4d6a-ba5e-1afd38bb0c30","nodeType":4,"position":{"x":-452.0,"y":-1786.666748046875},"targetType":1,"searchShapeType":0,"searchLineType":0,"positionSource":0,"positionBindingName":"center","searchCircleRadius":5.0,"searchSectorRadius":2.0,"searchSectorAngle":180.0,"searchLineDirectionOffsetAngle":0.0,"searchLineDirectionWidth":1.0,"searchLineDirectionLength":10.0,"lineStartPositionSource":0,"lineStartBindingName":"","lineEndPositionSource":1,"lineEndBindingName":"","searchLineBetweenWidth":1.0,"searchLineAbsoluteAngle":0.0,"searchLineAbsoluteWidth":1.0,"searchLineAbsoluteLength":10.0,"maxTargets":999,"searchTargetTags":{"Tags":[{"Name":"unitType.monster","HashCode":-2021655864,"ShortName":"monster","AncestorHashCodes":[1600484460],"AncestorNames":["unitType"]}]},"searchExcludeTags":{"Tags":[]}}</t>
+          <t>{"guid":"cde57fb8-b693-4da8-a4a8-fd61e56c5dcd","nodeType":12,"position":{"x":676.6666259765625,"y":-1998.0},"targetType":1,"requiredTags":{"Tags":[]},"immunityTags":{"Tags":[]},"destroyWithNode":false,"positionSource":0,"particleEntityId":50007,"particlePrefab":null,"particlePrefabPath":"Assets/Res/Entity/Effect/ef_zhanshi_jcjt_01.prefab","particleBindingName":"down","particleOffset":{"x":0.0,"y":0.0,"z":0.0},"particleScale":{"x":1.0,"y":1.0,"z":1.0},"attachToTarget":false,"particleLoop":false}</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>{"outputNodeGuid":"432ff1e3-b18d-476d-af80-d39ddc07402a","outputPortId":2287012,"inputNodeGuid":"cde57fb8-b693-4da8-a4a8-fd61e56c5dcd","inputPortId":7001}</t>
+          <t>{"outputNodeGuid":"432ff1e3-b18d-476d-af80-d39ddc07402a","outputPortId":2315086,"inputNodeGuid":"e33ab94c-1496-4d6a-ba5e-1afd38bb0c30","inputPortId":7001}</t>
         </is>
       </c>
       <c r="H57"/>
@@ -1755,16 +1759,16 @@
       <c r="C58"/>
       <c r="D58"/>
       <c r="E58">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>{"guid":"cb1df36f-5729-423e-9d1a-287db5a433f0","nodeType":11,"position":{"x":18.66668701171875,"y":-1819.3333740234375},"targetType":0,"assetTags":{"Tags":[{"Name":"Buff.DeBuff.Stun","HashCode":1791562953,"ShortName":"Stun","AncestorHashCodes":[937056111,321157895],"AncestorNames":["Buff","Buff.DeBuff"]}]},"grantedTags":{"Tags":[{"Name":"Buff.DeBuff.Stun","HashCode":1791562953,"ShortName":"Stun","AncestorHashCodes":[937056111,321157895],"AncestorNames":["Buff","Buff.DeBuff"]}]},"applicationRequiredTags":{"Tags":[]},"applicationImmunityTags":{"Tags":[]},"removeGameEffectsWithTags":{"Tags":[]},"durationType":1,"duration":"4","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[],"stackType":1,"stackLimit":1,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":1,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"Tags":[]},"cancelOnAbilityEnd":false,"buffId":0}</t>
+          <t>{"guid":"e33ab94c-1496-4d6a-ba5e-1afd38bb0c30","nodeType":4,"position":{"x":-452.0,"y":-1786.666748046875},"targetType":1,"searchShapeType":0,"searchLineType":0,"positionSource":0,"positionBindingName":"center","searchCircleRadius":5.0,"searchSectorRadius":2.0,"searchSectorAngle":180.0,"searchLineDirectionOffsetAngle":0.0,"searchLineDirectionWidth":1.0,"searchLineDirectionLength":10.0,"lineStartPositionSource":0,"lineStartBindingName":"","lineEndPositionSource":1,"lineEndBindingName":"","searchLineBetweenWidth":1.0,"searchLineAbsoluteAngle":0.0,"searchLineAbsoluteWidth":1.0,"searchLineAbsoluteLength":10.0,"maxTargets":999,"searchTargetTags":{"Tags":[{"Name":"unitType.monster","HashCode":-2021655864,"ShortName":"monster","AncestorHashCodes":[1600484460],"AncestorNames":["unitType"]}]},"searchExcludeTags":{"Tags":[]}}</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>{"outputNodeGuid":"cb1df36f-5729-423e-9d1a-287db5a433f0","outputPortId":3001,"inputNodeGuid":"93ec5a43-cc34-4e4a-acb3-39da2f2c3010","inputPortId":7001}</t>
+          <t>{"outputNodeGuid":"432ff1e3-b18d-476d-af80-d39ddc07402a","outputPortId":2287012,"inputNodeGuid":"cde57fb8-b693-4da8-a4a8-fd61e56c5dcd","inputPortId":7001}</t>
         </is>
       </c>
       <c r="H58"/>
@@ -1775,58 +1779,58 @@
       <c r="C59"/>
       <c r="D59"/>
       <c r="E59">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>{"guid":"93ec5a43-cc34-4e4a-acb3-39da2f2c3010","nodeType":12,"position":{"x":408.66665649414063,"y":-1790.666748046875},"targetType":1,"requiredTags":{"Tags":[]},"immunityTags":{"Tags":[]},"destroyWithNode":true,"positionSource":2,"particleEntityId":50005,"particlePrefab":null,"particlePrefabPath":"Assets/Res/Entity/Effect/ef_Xuanyun_01.prefab","particleBindingName":"head","particleOffset":{"x":0.0,"y":0.0,"z":0.0},"particleScale":{"x":1.0,"y":1.0,"z":1.0},"attachToTarget":true,"particleLoop":true}</t>
-        </is>
-      </c>
-      <c r="G59"/>
+          <t>{"guid":"cb1df36f-5729-423e-9d1a-287db5a433f0","nodeType":11,"position":{"x":18.66668701171875,"y":-1819.3333740234375},"targetType":0,"assetTags":{"Tags":[{"Name":"Buff.DeBuff.Stun","HashCode":1791562953,"ShortName":"Stun","AncestorHashCodes":[937056111,321157895],"AncestorNames":["Buff","Buff.DeBuff"]}]},"grantedTags":{"Tags":[{"Name":"Buff.DeBuff.Stun","HashCode":1791562953,"ShortName":"Stun","AncestorHashCodes":[937056111,321157895],"AncestorNames":["Buff","Buff.DeBuff"]}]},"applicationRequiredTags":{"Tags":[]},"applicationImmunityTags":{"Tags":[]},"removeGameEffectsWithTags":{"Tags":[]},"durationType":1,"duration":"4","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[],"stackType":1,"stackLimit":1,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":1,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"Tags":[]},"cancelOnAbilityEnd":false,"buffId":0}</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>{"outputNodeGuid":"cb1df36f-5729-423e-9d1a-287db5a433f0","outputPortId":3001,"inputNodeGuid":"93ec5a43-cc34-4e4a-acb3-39da2f2c3010","inputPortId":7001}</t>
+        </is>
+      </c>
       <c r="H59"/>
     </row>
     <row r="60">
       <c r="A60"/>
-      <c r="B60">
-        <v>1009</v>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>SpeedUp</t>
-        </is>
-      </c>
+      <c r="B60"/>
+      <c r="C60"/>
       <c r="D60"/>
       <c r="E60">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>{"guid":"9d6f459d-b588-4b64-843b-1b71e8f299ae","nodeType":3,"position":{"x":-1186.6666259765625,"y":-2011.3333740234375},"targetType":1,"assetTags":{"Tags":[]},"grantedTags":{"Tags":[]},"applicationRequiredTags":{"Tags":[]},"applicationImmunityTags":{"Tags":[]},"removeGameEffectsWithTags":{"Tags":[]},"durationType":0,"duration":"0","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[{"attrType":100,"operation":0,"magnitudeSourceType":0,"fixedValue":10.0,"formula":"","mmcType":0,"setByCallerKey":"","mmcCaptureAttribute":200,"mmcAttributeSource":0,"mmcCoefficient":1.0,"mmcUseSnapshot":true}],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"Tags":[]},"cancelOnAbilityEnd":true}</t>
-        </is>
-      </c>
-      <c r="G60" t="inlineStr">
-        <is>
-          <t>{"outputNodeGuid":"356907e0-1488-4128-bfcc-7ff73cfc3330","outputPortId":1002,"inputNodeGuid":"432ff1e3-b18d-476d-af80-d39ddc07402a","inputPortId":7001}</t>
-        </is>
-      </c>
+          <t>{"guid":"93ec5a43-cc34-4e4a-acb3-39da2f2c3010","nodeType":12,"position":{"x":408.66665649414063,"y":-1790.666748046875},"targetType":1,"requiredTags":{"Tags":[]},"immunityTags":{"Tags":[]},"destroyWithNode":true,"positionSource":2,"particleEntityId":50005,"particlePrefab":null,"particlePrefabPath":"Assets/Res/Entity/Effect/ef_Xuanyun_01.prefab","particleBindingName":"head","particleOffset":{"x":0.0,"y":0.0,"z":0.0},"particleScale":{"x":1.0,"y":1.0,"z":1.0},"attachToTarget":true,"particleLoop":true}</t>
+        </is>
+      </c>
+      <c r="G60"/>
       <c r="H60"/>
     </row>
     <row r="61">
       <c r="A61"/>
-      <c r="B61"/>
-      <c r="C61"/>
+      <c r="B61">
+        <v>1009</v>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>SpeedUp</t>
+        </is>
+      </c>
       <c r="D61"/>
       <c r="E61">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>{"guid":"f73ba91e-a76b-456c-b19c-a5176809d5f5","nodeType":7,"position":{"x":700.0,"y":-1856.666748046875},"targetType":1,"endType":0}</t>
+          <t>{"guid":"9d6f459d-b588-4b64-843b-1b71e8f299ae","nodeType":3,"position":{"x":-1186.6666259765625,"y":-2011.3333740234375},"targetType":1,"assetTags":{"Tags":[]},"grantedTags":{"Tags":[]},"applicationRequiredTags":{"Tags":[]},"applicationImmunityTags":{"Tags":[]},"removeGameEffectsWithTags":{"Tags":[]},"durationType":0,"duration":"0","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[{"attrType":100,"operation":0,"magnitudeSourceType":0,"fixedValue":10.0,"formula":"","mmcType":0,"setByCallerKey":"","mmcCaptureAttribute":200,"mmcAttributeSource":0,"mmcCoefficient":1.0,"mmcUseSnapshot":true}],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"Tags":[]},"cancelOnAbilityEnd":true}</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>{"outputNodeGuid":"356907e0-1488-4128-bfcc-7ff73cfc3330","outputPortId":1004,"inputNodeGuid":"c28fb88d-51b1-47b2-be59-859e0ac638e3","inputPortId":7001}</t>
+          <t>{"outputNodeGuid":"356907e0-1488-4128-bfcc-7ff73cfc3330","outputPortId":1002,"inputNodeGuid":"432ff1e3-b18d-476d-af80-d39ddc07402a","inputPortId":7001}</t>
         </is>
       </c>
       <c r="H61"/>
@@ -1837,16 +1841,16 @@
       <c r="C62"/>
       <c r="D62"/>
       <c r="E62">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>{"guid":"c28fb88d-51b1-47b2-be59-859e0ac638e3","nodeType":10,"position":{"x":-1186.6666259765625,"y":-1747.3333740234375},"targetType":1,"assetTags":{"Tags":[]},"grantedTags":{"Tags":[{"Name":"CD.SpeedUp","HashCode":-605747253,"ShortName":"急速","AncestorHashCodes":[-1137859925],"AncestorNames":["CD"]}]},"applicationRequiredTags":{"Tags":[]},"applicationImmunityTags":{"Tags":[]},"removeGameEffectsWithTags":{"Tags":[]},"durationType":1,"duration":"10","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"Tags":[]},"cancelOnAbilityEnd":false,"cooldownType":0,"maxCharges":2,"chargeTime":"10"}</t>
+          <t>{"guid":"f73ba91e-a76b-456c-b19c-a5176809d5f5","nodeType":7,"position":{"x":700.0,"y":-1856.666748046875},"targetType":1,"endType":0}</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>{"outputNodeGuid":"356907e0-1488-4128-bfcc-7ff73cfc3330","outputPortId":1003,"inputNodeGuid":"9d6f459d-b588-4b64-843b-1b71e8f299ae","inputPortId":7001}</t>
+          <t>{"outputNodeGuid":"356907e0-1488-4128-bfcc-7ff73cfc3330","outputPortId":1004,"inputNodeGuid":"c28fb88d-51b1-47b2-be59-859e0ac638e3","inputPortId":7001}</t>
         </is>
       </c>
       <c r="H62"/>
@@ -1857,16 +1861,16 @@
       <c r="C63"/>
       <c r="D63"/>
       <c r="E63">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>{"guid":"356907e0-1488-4128-bfcc-7ff73cfc3330","nodeType":0,"position":{"x":-878.6666259765625,"y":-1853.3333740234375},"targetType":1,"skillId":1009,"assetTags":{"Tags":[]},"cancelAbilitiesWithTags":{"Tags":[]},"blockAbilitiesWithTags":{"Tags":[]},"activationOwnedTags":{"Tags":[]},"activationRequiredTags":{"Tags":[]},"activationBlockedTags":{"Tags":[{"Name":"CD.SpeedUp","HashCode":-605747253,"ShortName":"急速","AncestorHashCodes":[-1137859925],"AncestorNames":["CD"]}]},"ongoingBlockedTags":{"Tags":[]},"eventOutputPorts":[]}</t>
+          <t>{"guid":"c28fb88d-51b1-47b2-be59-859e0ac638e3","nodeType":10,"position":{"x":-1186.6666259765625,"y":-1747.3333740234375},"targetType":1,"assetTags":{"Tags":[]},"grantedTags":{"Tags":[{"Name":"CD.SpeedUp","HashCode":-605747253,"ShortName":"急速","AncestorHashCodes":[-1137859925],"AncestorNames":["CD"]}]},"applicationRequiredTags":{"Tags":[]},"applicationImmunityTags":{"Tags":[]},"removeGameEffectsWithTags":{"Tags":[]},"durationType":1,"duration":"10","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"Tags":[]},"cancelOnAbilityEnd":false,"cooldownType":0,"maxCharges":2,"chargeTime":"10"}</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>{"outputNodeGuid":"432ff1e3-b18d-476d-af80-d39ddc07402a","outputPortId":2000539,"inputNodeGuid":"f73ba91e-a76b-456c-b19c-a5176809d5f5","inputPortId":7001}</t>
+          <t>{"outputNodeGuid":"356907e0-1488-4128-bfcc-7ff73cfc3330","outputPortId":1003,"inputNodeGuid":"9d6f459d-b588-4b64-843b-1b71e8f299ae","inputPortId":7001}</t>
         </is>
       </c>
       <c r="H63"/>
@@ -1877,16 +1881,16 @@
       <c r="C64"/>
       <c r="D64"/>
       <c r="E64">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>{"guid":"632c75e2-152b-4376-8e9e-62c0e74f92d0","nodeType":11,"position":{"x":-502.66665649414063,"y":-1890.666748046875},"targetType":1,"assetTags":{"Tags":[]},"grantedTags":{"Tags":[]},"applicationRequiredTags":{"Tags":[]},"applicationImmunityTags":{"Tags":[]},"removeGameEffectsWithTags":{"Tags":[]},"durationType":1,"duration":"7","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[{"attrType":300,"operation":0,"magnitudeSourceType":0,"fixedValue":10.0,"formula":"","mmcType":0,"setByCallerKey":"","mmcCaptureAttribute":200,"mmcAttributeSource":0,"mmcCoefficient":1.0,"mmcUseSnapshot":true}],"stackType":2,"stackLimit":1,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"Tags":[]},"cancelOnAbilityEnd":false,"buffId":0}</t>
+          <t>{"guid":"356907e0-1488-4128-bfcc-7ff73cfc3330","nodeType":0,"position":{"x":-878.6666259765625,"y":-1853.3333740234375},"targetType":1,"skillId":1009,"assetTags":{"Tags":[]},"cancelAbilitiesWithTags":{"Tags":[]},"blockAbilitiesWithTags":{"Tags":[]},"activationOwnedTags":{"Tags":[]},"activationRequiredTags":{"Tags":[]},"activationBlockedTags":{"Tags":[{"Name":"CD.SpeedUp","HashCode":-605747253,"ShortName":"急速","AncestorHashCodes":[-1137859925],"AncestorNames":["CD"]}]},"ongoingBlockedTags":{"Tags":[]},"eventOutputPorts":[]}</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>{"outputNodeGuid":"356907e0-1488-4128-bfcc-7ff73cfc3330","outputPortId":1001,"inputNodeGuid":"632c75e2-152b-4376-8e9e-62c0e74f92d0","inputPortId":7001}</t>
+          <t>{"outputNodeGuid":"432ff1e3-b18d-476d-af80-d39ddc07402a","outputPortId":2000539,"inputNodeGuid":"f73ba91e-a76b-456c-b19c-a5176809d5f5","inputPortId":7001}</t>
         </is>
       </c>
       <c r="H64"/>
@@ -1897,58 +1901,58 @@
       <c r="C65"/>
       <c r="D65"/>
       <c r="E65">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>{"guid":"432ff1e3-b18d-476d-af80-d39ddc07402a","nodeType":20,"position":{"x":-502.66665649414063,"y":-2384.0},"targetType":1,"skeletonDataAsset":null,"skeletonDataAssetPath":"Assets/Res/Spine/SP_Zhanshi/SP_Zhanshi_SkeletonData.asset","animationName":"Stand","animationDuration":"24","isAnimationLooping":false,"timeEffects":[{"triggerTime":25,"portIdValue":2000539,"legacyPortId":"f41c85e0-7f26-494e-9ffc-4a06c980f811"}],"timeCues":[]}</t>
-        </is>
-      </c>
-      <c r="G65"/>
+          <t>{"guid":"632c75e2-152b-4376-8e9e-62c0e74f92d0","nodeType":11,"position":{"x":-502.66665649414063,"y":-1890.666748046875},"targetType":1,"assetTags":{"Tags":[]},"grantedTags":{"Tags":[]},"applicationRequiredTags":{"Tags":[]},"applicationImmunityTags":{"Tags":[]},"removeGameEffectsWithTags":{"Tags":[]},"durationType":1,"duration":"7","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[{"attrType":300,"operation":0,"magnitudeSourceType":0,"fixedValue":10.0,"formula":"","mmcType":0,"setByCallerKey":"","mmcCaptureAttribute":200,"mmcAttributeSource":0,"mmcCoefficient":1.0,"mmcUseSnapshot":true}],"stackType":2,"stackLimit":1,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"Tags":[]},"cancelOnAbilityEnd":false,"buffId":0}</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>{"outputNodeGuid":"356907e0-1488-4128-bfcc-7ff73cfc3330","outputPortId":1001,"inputNodeGuid":"632c75e2-152b-4376-8e9e-62c0e74f92d0","inputPortId":7001}</t>
+        </is>
+      </c>
       <c r="H65"/>
     </row>
     <row r="66">
       <c r="A66"/>
-      <c r="B66">
-        <v>1001</v>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>Sweep</t>
-        </is>
-      </c>
+      <c r="B66"/>
+      <c r="C66"/>
       <c r="D66"/>
       <c r="E66">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>{"guid":"356907e0-1488-4128-bfcc-7ff73cfc3330","nodeType":0,"position":{"x":-843.3333740234375,"y":-2480.0},"targetType":1,"skillId":1001,"assetTags":{"Tags":[]},"cancelAbilitiesWithTags":{"Tags":[]},"blockAbilitiesWithTags":{"Tags":[]},"activationOwnedTags":{"Tags":[]},"activationRequiredTags":{"Tags":[]},"activationBlockedTags":{"Tags":[{"Name":"CD.Sweep","HashCode":-303359587,"ShortName":"Sweep","AncestorHashCodes":[-1137859925],"AncestorNames":["CD"]}]},"ongoingBlockedTags":{"Tags":[]},"eventOutputPorts":[]}</t>
-        </is>
-      </c>
-      <c r="G66" t="inlineStr">
-        <is>
-          <t>{"outputNodeGuid":"356907e0-1488-4128-bfcc-7ff73cfc3330","outputPortId":1004,"inputNodeGuid":"c28fb88d-51b1-47b2-be59-859e0ac638e3","inputPortId":7001}</t>
-        </is>
-      </c>
+          <t>{"guid":"432ff1e3-b18d-476d-af80-d39ddc07402a","nodeType":20,"position":{"x":-502.66665649414063,"y":-2384.0},"targetType":1,"skeletonDataAsset":null,"skeletonDataAssetPath":"Assets/Res/Spine/SP_Zhanshi/SP_Zhanshi_SkeletonData.asset","animationName":"Stand","animationDuration":"24","isAnimationLooping":false,"timeEffects":[{"triggerTime":25,"portIdValue":2000539,"legacyPortId":"f41c85e0-7f26-494e-9ffc-4a06c980f811"}],"timeCues":[]}</t>
+        </is>
+      </c>
+      <c r="G66"/>
       <c r="H66"/>
     </row>
     <row r="67">
       <c r="A67"/>
-      <c r="B67"/>
-      <c r="C67"/>
+      <c r="B67">
+        <v>1001</v>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Sweep</t>
+        </is>
+      </c>
       <c r="D67"/>
       <c r="E67">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>{"guid":"2cfdacd2-0186-49dd-b177-4eb8c0ad87bd","nodeType":7,"position":{"x":731.3333740234375,"y":-2142.66650390625},"targetType":1,"endType":0}</t>
+          <t>{"guid":"356907e0-1488-4128-bfcc-7ff73cfc3330","nodeType":0,"position":{"x":-843.3333740234375,"y":-2480.0},"targetType":1,"skillId":1001,"assetTags":{"Tags":[]},"cancelAbilitiesWithTags":{"Tags":[]},"blockAbilitiesWithTags":{"Tags":[]},"activationOwnedTags":{"Tags":[]},"activationRequiredTags":{"Tags":[]},"activationBlockedTags":{"Tags":[{"Name":"CD.Sweep","HashCode":-303359587,"ShortName":"Sweep","AncestorHashCodes":[-1137859925],"AncestorNames":["CD"]}]},"ongoingBlockedTags":{"Tags":[]},"eventOutputPorts":[]}</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>{"outputNodeGuid":"356907e0-1488-4128-bfcc-7ff73cfc3330","outputPortId":1003,"inputNodeGuid":"9d6f459d-b588-4b64-843b-1b71e8f299ae","inputPortId":7001}</t>
+          <t>{"outputNodeGuid":"356907e0-1488-4128-bfcc-7ff73cfc3330","outputPortId":1004,"inputNodeGuid":"c28fb88d-51b1-47b2-be59-859e0ac638e3","inputPortId":7001}</t>
         </is>
       </c>
       <c r="H67"/>
@@ -1959,16 +1963,16 @@
       <c r="C68"/>
       <c r="D68"/>
       <c r="E68">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>{"guid":"c28fb88d-51b1-47b2-be59-859e0ac638e3","nodeType":10,"position":{"x":-843.3333740234375,"y":-2243.333251953125},"targetType":1,"assetTags":{"Tags":[]},"grantedTags":{"Tags":[{"Name":"CD.Sweep","HashCode":-303359587,"ShortName":"Sweep","AncestorHashCodes":[-1137859925],"AncestorNames":["CD"]}]},"applicationRequiredTags":{"Tags":[]},"applicationImmunityTags":{"Tags":[]},"removeGameEffectsWithTags":{"Tags":[]},"durationType":1,"duration":"1","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"Tags":[]},"cancelOnAbilityEnd":false,"cooldownType":0,"maxCharges":2,"chargeTime":"10"}</t>
+          <t>{"guid":"2cfdacd2-0186-49dd-b177-4eb8c0ad87bd","nodeType":7,"position":{"x":731.3333740234375,"y":-2142.66650390625},"targetType":1,"endType":0}</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>{"outputNodeGuid":"e33ab94c-1496-4d6a-ba5e-1afd38bb0c30","outputPortId":4001,"inputNodeGuid":"f8947676-1084-4228-b991-1509cc7fe851","inputPortId":7001}</t>
+          <t>{"outputNodeGuid":"356907e0-1488-4128-bfcc-7ff73cfc3330","outputPortId":1003,"inputNodeGuid":"9d6f459d-b588-4b64-843b-1b71e8f299ae","inputPortId":7001}</t>
         </is>
       </c>
       <c r="H68"/>
@@ -1979,16 +1983,16 @@
       <c r="C69"/>
       <c r="D69"/>
       <c r="E69">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>{"guid":"79dea24a-eaf5-45f2-b5a0-cbb8c4ad6df2","nodeType":23,"position":{"x":-460.66665649414063,"y":-2684.0},"targetType":1,"animationPrefab":null,"animationPrefabPath":"Assets/Res/Entity/Head/HeadItem.prefab","animationComponentPath":"HeadItem(Clone)/Root_Animation","animationName":"Attack","animationDuration":"15","isAnimationLooping":false,"timeEffects":[{"triggerTime":3,"portIdValue":2867116,"legacyPortId":""},{"triggerTime":10,"portIdValue":2095095,"legacyPortId":""}],"timeCues":[{"startTime":0,"endTime":41,"portIdValue":2893914,"legacyPortId":""}]}</t>
+          <t>{"guid":"c28fb88d-51b1-47b2-be59-859e0ac638e3","nodeType":10,"position":{"x":-843.3333740234375,"y":-2243.333251953125},"targetType":1,"assetTags":{"Tags":[]},"grantedTags":{"Tags":[{"Name":"CD.Sweep","HashCode":-303359587,"ShortName":"Sweep","AncestorHashCodes":[-1137859925],"AncestorNames":["CD"]}]},"applicationRequiredTags":{"Tags":[]},"applicationImmunityTags":{"Tags":[]},"removeGameEffectsWithTags":{"Tags":[]},"durationType":1,"duration":"1","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"Tags":[]},"cancelOnAbilityEnd":false,"cooldownType":0,"maxCharges":2,"chargeTime":"10"}</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>{"outputNodeGuid":"f8947676-1084-4228-b991-1509cc7fe851","outputPortId":3004,"inputNodeGuid":"c353e286-8ef0-460a-b917-887f2aeb390a","inputPortId":7001}</t>
+          <t>{"outputNodeGuid":"e33ab94c-1496-4d6a-ba5e-1afd38bb0c30","outputPortId":4001,"inputNodeGuid":"f8947676-1084-4228-b991-1509cc7fe851","inputPortId":7001}</t>
         </is>
       </c>
       <c r="H69"/>
@@ -1999,16 +2003,16 @@
       <c r="C70"/>
       <c r="D70"/>
       <c r="E70">
-        <v>3</v>
+        <v>23</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>{"guid":"9d6f459d-b588-4b64-843b-1b71e8f299ae","nodeType":3,"position":{"x":-1130.6666259765625,"y":-2479.333251953125},"targetType":1,"assetTags":{"Tags":[]},"grantedTags":{"Tags":[]},"applicationRequiredTags":{"Tags":[]},"applicationImmunityTags":{"Tags":[]},"removeGameEffectsWithTags":{"Tags":[]},"durationType":0,"duration":"0","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[{"attrType":1003,"operation":0,"magnitudeSourceType":0,"fixedValue":-10.0,"formula":"","mmcType":0,"setByCallerKey":"","mmcCaptureAttribute":200,"mmcAttributeSource":0,"mmcCoefficient":1.0,"mmcUseSnapshot":true}],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"Tags":[]},"cancelOnAbilityEnd":true}</t>
+          <t>{"guid":"79dea24a-eaf5-45f2-b5a0-cbb8c4ad6df2","nodeType":23,"position":{"x":-460.66665649414063,"y":-2684.0},"targetType":1,"animationPrefab":null,"animationPrefabPath":"Assets/Res/Entity/Head/HeadItem.prefab","animationComponentPath":"HeadItem(Clone)/Root_Animation","animationName":"Attack","animationDuration":"15","isAnimationLooping":false,"timeEffects":[{"triggerTime":3,"portIdValue":2867116,"legacyPortId":""},{"triggerTime":10,"portIdValue":2095095,"legacyPortId":""}],"timeCues":[{"startTime":0,"endTime":41,"portIdValue":2893914,"legacyPortId":""}]}</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>{"outputNodeGuid":"79dea24a-eaf5-45f2-b5a0-cbb8c4ad6df2","outputPortId":2867116,"inputNodeGuid":"e33ab94c-1496-4d6a-ba5e-1afd38bb0c30","inputPortId":7001}</t>
+          <t>{"outputNodeGuid":"f8947676-1084-4228-b991-1509cc7fe851","outputPortId":3004,"inputNodeGuid":"c353e286-8ef0-460a-b917-887f2aeb390a","inputPortId":7001}</t>
         </is>
       </c>
       <c r="H70"/>
@@ -2028,7 +2032,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>{"outputNodeGuid":"79dea24a-eaf5-45f2-b5a0-cbb8c4ad6df2","outputPortId":2095095,"inputNodeGuid":"2cfdacd2-0186-49dd-b177-4eb8c0ad87bd","inputPortId":7001}</t>
+          <t>{"outputNodeGuid":"79dea24a-eaf5-45f2-b5a0-cbb8c4ad6df2","outputPortId":2867116,"inputNodeGuid":"e33ab94c-1496-4d6a-ba5e-1afd38bb0c30","inputPortId":7001}</t>
         </is>
       </c>
       <c r="H71"/>
@@ -2039,16 +2043,16 @@
       <c r="C72"/>
       <c r="D72"/>
       <c r="E72">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>{"guid":"c353e286-8ef0-460a-b917-887f2aeb390a","nodeType":14,"position":{"x":1218.666748046875,"y":-2347.333251953125},"targetType":1,"requiredTags":{"Tags":[]},"immunityTags":{"Tags":[]},"destroyWithNode":false,"positionSource":2,"positionBindingName":"head","textType":0,"fixedText":"","contextDataKey":"DamageResult","textColor":{"r":1.0,"g":0.0,"b":0.0,"a":1.0},"criticalColor":{"r":1.0,"g":0.5,"b":0.0,"a":1.0},"missColor":{"r":0.5,"g":0.5,"b":0.5,"a":1.0},"fontSize":5.0,"criticalFontSize":60.0,"duration":1.5,"offset":{"x":0.0,"y":0.0},"moveDirection":{"x":0.0,"y":1.0}}</t>
+          <t>{"guid":"cde57fb8-b693-4da8-a4a8-fd61e56c5dcd","nodeType":12,"position":{"x":1005.3333740234375,"y":-2186.0},"targetType":1,"requiredTags":{"Tags":[]},"immunityTags":{"Tags":[]},"destroyWithNode":false,"positionSource":2,"particleEntityId":50006,"particlePrefab":null,"particlePrefabPath":"Assets/Res/Entity/Effect/ef_Zhanshi_attack_02.prefab","particleBindingName":"head","particleOffset":{"x":0.0,"y":0.0,"z":0.0},"particleScale":{"x":1.0,"y":1.0,"z":1.0},"attachToTarget":false,"particleLoop":false}</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>{"outputNodeGuid":"356907e0-1488-4128-bfcc-7ff73cfc3330","outputPortId":1002,"inputNodeGuid":"79dea24a-eaf5-45f2-b5a0-cbb8c4ad6df2","inputPortId":7001}</t>
+          <t>{"outputNodeGuid":"79dea24a-eaf5-45f2-b5a0-cbb8c4ad6df2","outputPortId":2095095,"inputNodeGuid":"2cfdacd2-0186-49dd-b177-4eb8c0ad87bd","inputPortId":7001}</t>
         </is>
       </c>
       <c r="H72"/>
@@ -2059,16 +2063,16 @@
       <c r="C73"/>
       <c r="D73"/>
       <c r="E73">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>{"guid":"cde57fb8-b693-4da8-a4a8-fd61e56c5dcd","nodeType":12,"position":{"x":1005.3333740234375,"y":-2186.0},"targetType":1,"requiredTags":{"Tags":[]},"immunityTags":{"Tags":[]},"destroyWithNode":false,"positionSource":2,"particleEntityId":50006,"particlePrefab":null,"particlePrefabPath":"Assets/Res/Entity/Effect/ef_Zhanshi_attack_02.prefab","particleBindingName":"head","particleOffset":{"x":0.0,"y":0.0,"z":0.0},"particleScale":{"x":1.0,"y":1.0,"z":1.0},"attachToTarget":false,"particleLoop":false}</t>
+          <t>{"guid":"e33ab94c-1496-4d6a-ba5e-1afd38bb0c30","nodeType":4,"position":{"x":731.3333740234375,"y":-2344.0},"targetType":1,"searchShapeType":3,"searchLineType":0,"positionSource":0,"positionBindingName":"center","searchCircleRadius":1.0,"searchSectorRadius":5.0,"searchSectorAngle":180.0,"searchLineDirectionOffsetAngle":0.0,"searchLineDirectionWidth":1.0,"searchLineDirectionLength":10.0,"lineStartPositionSource":0,"lineStartBindingName":"","lineEndPositionSource":1,"lineEndBindingName":"","searchLineBetweenWidth":1.0,"searchLineAbsoluteAngle":0.0,"searchLineAbsoluteWidth":1.0,"searchLineAbsoluteLength":10.0,"maxTargets":1,"searchTargetTags":{"Tags":[{"Name":"unitType.monster","HashCode":-2021655864,"ShortName":"monster","AncestorHashCodes":[1600484460],"AncestorNames":["unitType"]}]},"searchExcludeTags":{"Tags":[]}}</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>{"outputNodeGuid":"e33ab94c-1496-4d6a-ba5e-1afd38bb0c30","outputPortId":4001,"inputNodeGuid":"cde57fb8-b693-4da8-a4a8-fd61e56c5dcd","inputPortId":7001}</t>
+          <t>{"outputNodeGuid":"356907e0-1488-4128-bfcc-7ff73cfc3330","outputPortId":1002,"inputNodeGuid":"79dea24a-eaf5-45f2-b5a0-cbb8c4ad6df2","inputPortId":7001}</t>
         </is>
       </c>
       <c r="H73"/>
@@ -2079,58 +2083,58 @@
       <c r="C74"/>
       <c r="D74"/>
       <c r="E74">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>{"guid":"e33ab94c-1496-4d6a-ba5e-1afd38bb0c30","nodeType":4,"position":{"x":731.3333740234375,"y":-2344.0},"targetType":1,"searchShapeType":3,"searchLineType":0,"positionSource":0,"positionBindingName":"center","searchCircleRadius":1.0,"searchSectorRadius":5.0,"searchSectorAngle":180.0,"searchLineDirectionOffsetAngle":0.0,"searchLineDirectionWidth":1.0,"searchLineDirectionLength":10.0,"lineStartPositionSource":0,"lineStartBindingName":"","lineEndPositionSource":1,"lineEndBindingName":"","searchLineBetweenWidth":1.0,"searchLineAbsoluteAngle":0.0,"searchLineAbsoluteWidth":1.0,"searchLineAbsoluteLength":10.0,"maxTargets":1,"searchTargetTags":{"Tags":[{"Name":"unitType.monster","HashCode":-2021655864,"ShortName":"monster","AncestorHashCodes":[1600484460],"AncestorNames":["unitType"]}]},"searchExcludeTags":{"Tags":[]}}</t>
-        </is>
-      </c>
-      <c r="G74"/>
+          <t>{"guid":"9d6f459d-b588-4b64-843b-1b71e8f299ae","nodeType":3,"position":{"x":-843.3333740234375,"y":-2772.0},"targetType":1,"assetTags":{"Tags":[]},"grantedTags":{"Tags":[]},"applicationRequiredTags":{"Tags":[]},"applicationImmunityTags":{"Tags":[]},"removeGameEffectsWithTags":{"Tags":[]},"durationType":0,"duration":"0","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[{"attrType":1003,"operation":0,"magnitudeSourceType":0,"fixedValue":-10.0,"formula":"","mmcType":0,"setByCallerKey":"","mmcCaptureAttribute":200,"mmcAttributeSource":0,"mmcCoefficient":1.0,"mmcUseSnapshot":true}],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"Tags":[]},"cancelOnAbilityEnd":true}</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>{"outputNodeGuid":"e33ab94c-1496-4d6a-ba5e-1afd38bb0c30","outputPortId":4001,"inputNodeGuid":"cde57fb8-b693-4da8-a4a8-fd61e56c5dcd","inputPortId":7001}</t>
+        </is>
+      </c>
       <c r="H74"/>
     </row>
     <row r="75">
       <c r="A75"/>
-      <c r="B75">
-        <v>1008</v>
-      </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>ThreeFire</t>
-        </is>
-      </c>
+      <c r="B75"/>
+      <c r="C75"/>
       <c r="D75"/>
       <c r="E75">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>{"guid":"f8947676-1084-4228-b991-1509cc7fe851","nodeType":1,"position":{"x":1452.666748046875,"y":-2239.333251953125},"targetType":0,"assetTags":{"Tags":[]},"grantedTags":{"Tags":[]},"applicationRequiredTags":{"Tags":[]},"applicationImmunityTags":{"Tags":[]},"removeGameEffectsWithTags":{"Tags":[]},"durationType":0,"duration":"0","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"Tags":[]},"cancelOnAbilityEnd":true,"damageType":0,"damageSourceType":0,"damageFixedValue":10.0,"damageFormula":"","damageMMCType":0,"damageSetByCallerKey":"","damageMMCCaptureAttribute":200,"damageMMCAttributeSource":0,"damageMMCCoefficient":1.0,"damageMMCUseSnapshot":true,"damageMultiplyByStackCount":false,"damageCalculationType":0,"enableHitKnockback":false,"knockbackDistance":1.0,"knockbackSpeed":12.0}</t>
-        </is>
-      </c>
-      <c r="G75" t="inlineStr">
-        <is>
-          <t>{"outputNodeGuid":"356907e0-1488-4128-bfcc-7ff73cfc3330","outputPortId":1002,"inputNodeGuid":"432ff1e3-b18d-476d-af80-d39ddc07402a","inputPortId":7001}</t>
-        </is>
-      </c>
+          <t>{"guid":"c353e286-8ef0-460a-b917-887f2aeb390a","nodeType":14,"position":{"x":1224.666748046875,"y":-2347.333251953125},"targetType":1,"requiredTags":{"Tags":[]},"immunityTags":{"Tags":[]},"destroyWithNode":false,"positionSource":2,"positionBindingName":"head","textType":0,"fixedText":"","contextDataKey":"DamageResult","textColor":{"r":1.0,"g":0.0,"b":0.0,"a":1.0},"criticalColor":{"r":1.0,"g":0.5,"b":0.0,"a":1.0},"missColor":{"r":0.5,"g":0.5,"b":0.5,"a":1.0},"fontSize":5.0,"criticalFontSize":60.0,"duration":1.5,"offset":{"x":0.0,"y":0.0},"moveDirection":{"x":0.0,"y":1.0}}</t>
+        </is>
+      </c>
+      <c r="G75"/>
       <c r="H75"/>
     </row>
     <row r="76">
       <c r="A76"/>
-      <c r="B76"/>
-      <c r="C76"/>
+      <c r="B76">
+        <v>1008</v>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>ThreeFire</t>
+        </is>
+      </c>
       <c r="D76"/>
       <c r="E76">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>{"guid":"2cfdacd2-0186-49dd-b177-4eb8c0ad87bd","nodeType":7,"position":{"x":1052.666748046875,"y":-2551.333251953125},"targetType":1,"endType":0}</t>
+          <t>{"guid":"f8947676-1084-4228-b991-1509cc7fe851","nodeType":1,"position":{"x":1452.666748046875,"y":-2239.333251953125},"targetType":0,"assetTags":{"Tags":[]},"grantedTags":{"Tags":[]},"applicationRequiredTags":{"Tags":[]},"applicationImmunityTags":{"Tags":[]},"removeGameEffectsWithTags":{"Tags":[]},"durationType":0,"duration":"0","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"Tags":[]},"cancelOnAbilityEnd":true,"damageType":0,"damageSourceType":0,"damageFixedValue":10.0,"damageFormula":"","damageMMCType":0,"damageSetByCallerKey":"","damageMMCCaptureAttribute":200,"damageMMCAttributeSource":0,"damageMMCCoefficient":1.0,"damageMMCUseSnapshot":true,"damageMultiplyByStackCount":false,"damageCalculationType":0,"enableHitKnockback":false,"knockbackDistance":1.0,"knockbackSpeed":12.0}</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>{"outputNodeGuid":"356907e0-1488-4128-bfcc-7ff73cfc3330","outputPortId":1004,"inputNodeGuid":"c28fb88d-51b1-47b2-be59-859e0ac638e3","inputPortId":7001}</t>
+          <t>{"outputNodeGuid":"356907e0-1488-4128-bfcc-7ff73cfc3330","outputPortId":1002,"inputNodeGuid":"432ff1e3-b18d-476d-af80-d39ddc07402a","inputPortId":7001}</t>
         </is>
       </c>
       <c r="H76"/>
@@ -2141,16 +2145,16 @@
       <c r="C77"/>
       <c r="D77"/>
       <c r="E77">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>{"guid":"9d6f459d-b588-4b64-843b-1b71e8f299ae","nodeType":3,"position":{"x":-1144.0,"y":-2405.333251953125},"targetType":1,"assetTags":{"Tags":[]},"grantedTags":{"Tags":[]},"applicationRequiredTags":{"Tags":[]},"applicationImmunityTags":{"Tags":[]},"removeGameEffectsWithTags":{"Tags":[]},"durationType":0,"duration":"0","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[{"attrType":100,"operation":0,"magnitudeSourceType":0,"fixedValue":10.0,"formula":"","mmcType":0,"setByCallerKey":"","mmcCaptureAttribute":200,"mmcAttributeSource":0,"mmcCoefficient":1.0,"mmcUseSnapshot":true}],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"Tags":[]},"cancelOnAbilityEnd":true}</t>
+          <t>{"guid":"2cfdacd2-0186-49dd-b177-4eb8c0ad87bd","nodeType":7,"position":{"x":1052.666748046875,"y":-2551.333251953125},"targetType":1,"endType":0}</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>{"outputNodeGuid":"356907e0-1488-4128-bfcc-7ff73cfc3330","outputPortId":1003,"inputNodeGuid":"9d6f459d-b588-4b64-843b-1b71e8f299ae","inputPortId":7001}</t>
+          <t>{"outputNodeGuid":"356907e0-1488-4128-bfcc-7ff73cfc3330","outputPortId":1004,"inputNodeGuid":"c28fb88d-51b1-47b2-be59-859e0ac638e3","inputPortId":7001}</t>
         </is>
       </c>
       <c r="H77"/>
@@ -2161,16 +2165,16 @@
       <c r="C78"/>
       <c r="D78"/>
       <c r="E78">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>{"guid":"c28fb88d-51b1-47b2-be59-859e0ac638e3","nodeType":10,"position":{"x":-1067.3333740234375,"y":-2188.66650390625},"targetType":1,"assetTags":{"Tags":[]},"grantedTags":{"Tags":[{"Name":"CD.ThreeFire","HashCode":960327319,"ShortName":"ThreeFire","AncestorHashCodes":[-1137859925],"AncestorNames":["CD"]}]},"applicationRequiredTags":{"Tags":[]},"applicationImmunityTags":{"Tags":[]},"removeGameEffectsWithTags":{"Tags":[]},"durationType":1,"duration":"1","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"Tags":[]},"cancelOnAbilityEnd":false,"cooldownType":0,"maxCharges":2,"chargeTime":"10"}</t>
+          <t>{"guid":"9d6f459d-b588-4b64-843b-1b71e8f299ae","nodeType":3,"position":{"x":-1144.0,"y":-2405.333251953125},"targetType":1,"assetTags":{"Tags":[]},"grantedTags":{"Tags":[]},"applicationRequiredTags":{"Tags":[]},"applicationImmunityTags":{"Tags":[]},"removeGameEffectsWithTags":{"Tags":[]},"durationType":0,"duration":"0","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[{"attrType":100,"operation":0,"magnitudeSourceType":0,"fixedValue":10.0,"formula":"","mmcType":0,"setByCallerKey":"","mmcCaptureAttribute":200,"mmcAttributeSource":0,"mmcCoefficient":1.0,"mmcUseSnapshot":true}],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"Tags":[]},"cancelOnAbilityEnd":true}</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>{"outputNodeGuid":"f8947676-1084-4228-b991-1509cc7fe851","outputPortId":3004,"inputNodeGuid":"c353e286-8ef0-460a-b917-887f2aeb390a","inputPortId":7001}</t>
+          <t>{"outputNodeGuid":"356907e0-1488-4128-bfcc-7ff73cfc3330","outputPortId":1003,"inputNodeGuid":"9d6f459d-b588-4b64-843b-1b71e8f299ae","inputPortId":7001}</t>
         </is>
       </c>
       <c r="H78"/>
@@ -2181,16 +2185,16 @@
       <c r="C79"/>
       <c r="D79"/>
       <c r="E79">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>{"guid":"356907e0-1488-4128-bfcc-7ff73cfc3330","nodeType":0,"position":{"x":-746.6666259765625,"y":-2405.333251953125},"targetType":1,"skillId":1008,"assetTags":{"Tags":[]},"cancelAbilitiesWithTags":{"Tags":[]},"blockAbilitiesWithTags":{"Tags":[]},"activationOwnedTags":{"Tags":[]},"activationRequiredTags":{"Tags":[]},"activationBlockedTags":{"Tags":[{"Name":"CD.ThreeFire","HashCode":960327319,"ShortName":"ThreeFire","AncestorHashCodes":[-1137859925],"AncestorNames":["CD"]}]},"ongoingBlockedTags":{"Tags":[]},"eventOutputPorts":[]}</t>
+          <t>{"guid":"c28fb88d-51b1-47b2-be59-859e0ac638e3","nodeType":10,"position":{"x":-1067.3333740234375,"y":-2188.66650390625},"targetType":1,"assetTags":{"Tags":[]},"grantedTags":{"Tags":[{"Name":"CD.ThreeFire","HashCode":960327319,"ShortName":"ThreeFire","AncestorHashCodes":[-1137859925],"AncestorNames":["CD"]}]},"applicationRequiredTags":{"Tags":[]},"applicationImmunityTags":{"Tags":[]},"removeGameEffectsWithTags":{"Tags":[]},"durationType":1,"duration":"1","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"Tags":[]},"cancelOnAbilityEnd":false,"cooldownType":0,"maxCharges":2,"chargeTime":"10"}</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>{"outputNodeGuid":"ce857360-de7e-4457-b348-9c124ce98879","outputPortId":5001,"inputNodeGuid":"f8947676-1084-4228-b991-1509cc7fe851","inputPortId":7001}</t>
+          <t>{"outputNodeGuid":"f8947676-1084-4228-b991-1509cc7fe851","outputPortId":3004,"inputNodeGuid":"c353e286-8ef0-460a-b917-887f2aeb390a","inputPortId":7001}</t>
         </is>
       </c>
       <c r="H79"/>
@@ -2201,16 +2205,16 @@
       <c r="C80"/>
       <c r="D80"/>
       <c r="E80">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>{"guid":"432ff1e3-b18d-476d-af80-d39ddc07402a","nodeType":20,"position":{"x":-238.66665649414063,"y":-2405.333251953125},"targetType":1,"skeletonDataAsset":null,"skeletonDataAssetPath":"Assets/Res/Spine/SP_Zhanshi/SP_Zhanshi_SkeletonData.asset","animationName":"Attack_01","animationDuration":"18","isAnimationLooping":false,"timeEffects":[{"triggerTime":7,"portIdValue":2315086,"legacyPortId":"de0ba361-3aba-4ef0-bb07-9b418fcae591"},{"triggerTime":18,"portIdValue":2649436,"legacyPortId":"84e238a8-5baf-470e-829f-186695064945"}],"timeCues":[]}</t>
+          <t>{"guid":"356907e0-1488-4128-bfcc-7ff73cfc3330","nodeType":0,"position":{"x":-746.6666259765625,"y":-2405.333251953125},"targetType":1,"skillId":1008,"assetTags":{"Tags":[]},"cancelAbilitiesWithTags":{"Tags":[]},"blockAbilitiesWithTags":{"Tags":[]},"activationOwnedTags":{"Tags":[]},"activationRequiredTags":{"Tags":[]},"activationBlockedTags":{"Tags":[{"Name":"CD.ThreeFire","HashCode":960327319,"ShortName":"ThreeFire","AncestorHashCodes":[-1137859925],"AncestorNames":["CD"]}]},"ongoingBlockedTags":{"Tags":[]},"eventOutputPorts":[]}</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>{"outputNodeGuid":"9a695e91-e218-425e-82ed-1e157bf1b014","outputPortId":5001,"inputNodeGuid":"f8947676-1084-4228-b991-1509cc7fe851","inputPortId":7001}</t>
+          <t>{"outputNodeGuid":"ce857360-de7e-4457-b348-9c124ce98879","outputPortId":5001,"inputNodeGuid":"f8947676-1084-4228-b991-1509cc7fe851","inputPortId":7001}</t>
         </is>
       </c>
       <c r="H80"/>
@@ -2221,16 +2225,16 @@
       <c r="C81"/>
       <c r="D81"/>
       <c r="E81">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>{"guid":"ce857360-de7e-4457-b348-9c124ce98879","nodeType":8,"position":{"x":1040.666748046875,"y":-2305.333251953125},"targetType":2,"assetTags":{"Tags":[]},"grantedTags":{"Tags":[]},"applicationRequiredTags":{"Tags":[]},"applicationImmunityTags":{"Tags":[]},"removeGameEffectsWithTags":{"Tags":[]},"durationType":2,"duration":"0","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"Tags":[]},"cancelOnAbilityEnd":false,"launchPositionSource":0,"launchBindingName":"center","targetPositionSource":1,"targetBindingName":"center","projectileTargetType":0,"flyOver":true,"offsetAngle":30.0,"curveHeight":0.0,"projectileEntityId":50002,"projectilePrefab":null,"projectilePrefabPath":"Assets/Res/Entity/Effect/ef_fashi_huoyandan01.prefab","speed":10.0,"maxDistance":10.0,"collisionRadius":0.5,"isPiercing":false,"maxPierceCount":1,"collisionTargetTags":{"Tags":[]},"collisionExcludeTags":{"Tags":[]},"isBouncing":false,"bounceTargetMode":0,"maxBounceCount":3,"bounceSearchRadius":10.0,"canBounceToSameTarget":false,"excludeSourceCamp":true,"bounceAngleOffset":0.0}</t>
+          <t>{"guid":"432ff1e3-b18d-476d-af80-d39ddc07402a","nodeType":20,"position":{"x":-238.66665649414063,"y":-2405.333251953125},"targetType":1,"skeletonDataAsset":null,"skeletonDataAssetPath":"Assets/Res/Spine/SP_Zhanshi/SP_Zhanshi_SkeletonData.asset","animationName":"Attack_01","animationDuration":"18","isAnimationLooping":false,"timeEffects":[{"triggerTime":7,"portIdValue":2315086,"legacyPortId":"de0ba361-3aba-4ef0-bb07-9b418fcae591"},{"triggerTime":18,"portIdValue":2649436,"legacyPortId":"84e238a8-5baf-470e-829f-186695064945"}],"timeCues":[]}</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>{"outputNodeGuid":"d897a922-5756-42cf-ac65-90a48c1e5a17","outputPortId":5001,"inputNodeGuid":"f8947676-1084-4228-b991-1509cc7fe851","inputPortId":7001}</t>
+          <t>{"outputNodeGuid":"9a695e91-e218-425e-82ed-1e157bf1b014","outputPortId":5001,"inputNodeGuid":"f8947676-1084-4228-b991-1509cc7fe851","inputPortId":7001}</t>
         </is>
       </c>
       <c r="H81"/>
@@ -2245,12 +2249,12 @@
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>{"guid":"9a695e91-e218-425e-82ed-1e157bf1b014","nodeType":8,"position":{"x":1022.666748046875,"y":-2131.333251953125},"targetType":2,"assetTags":{"Tags":[]},"grantedTags":{"Tags":[]},"applicationRequiredTags":{"Tags":[]},"applicationImmunityTags":{"Tags":[]},"removeGameEffectsWithTags":{"Tags":[]},"durationType":2,"duration":"0","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"Tags":[]},"cancelOnAbilityEnd":false,"launchPositionSource":0,"launchBindingName":"center","targetPositionSource":1,"targetBindingName":"center","projectileTargetType":0,"flyOver":true,"offsetAngle":0.0,"curveHeight":0.0,"projectileEntityId":50002,"projectilePrefab":null,"projectilePrefabPath":"Assets/Res/Entity/Effect/ef_fashi_huoyandan01.prefab","speed":10.0,"maxDistance":10.0,"collisionRadius":0.5,"isPiercing":false,"maxPierceCount":1,"collisionTargetTags":{"Tags":[]},"collisionExcludeTags":{"Tags":[]},"isBouncing":false,"bounceTargetMode":0,"maxBounceCount":3,"bounceSearchRadius":10.0,"canBounceToSameTarget":false,"excludeSourceCamp":true,"bounceAngleOffset":0.0}</t>
+          <t>{"guid":"ce857360-de7e-4457-b348-9c124ce98879","nodeType":8,"position":{"x":1040.666748046875,"y":-2305.333251953125},"targetType":2,"assetTags":{"Tags":[]},"grantedTags":{"Tags":[]},"applicationRequiredTags":{"Tags":[]},"applicationImmunityTags":{"Tags":[]},"removeGameEffectsWithTags":{"Tags":[]},"durationType":2,"duration":"0","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"Tags":[]},"cancelOnAbilityEnd":false,"launchPositionSource":0,"launchBindingName":"center","targetPositionSource":1,"targetBindingName":"center","projectileTargetType":0,"flyOver":true,"offsetAngle":30.0,"curveHeight":0.0,"projectileEntityId":50002,"projectilePrefab":null,"projectilePrefabPath":"Assets/Res/Entity/Effect/ef_fashi_huoyandan01.prefab","speed":10.0,"maxDistance":10.0,"collisionRadius":0.5,"isPiercing":false,"maxPierceCount":1,"collisionTargetTags":{"Tags":[]},"collisionExcludeTags":{"Tags":[]},"isBouncing":false,"bounceTargetMode":0,"maxBounceCount":3,"bounceSearchRadius":10.0,"canBounceToSameTarget":false,"excludeSourceCamp":true,"bounceAngleOffset":0.0}</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>{"outputNodeGuid":"432ff1e3-b18d-476d-af80-d39ddc07402a","outputPortId":2649436,"inputNodeGuid":"2cfdacd2-0186-49dd-b177-4eb8c0ad87bd","inputPortId":7001}</t>
+          <t>{"outputNodeGuid":"d897a922-5756-42cf-ac65-90a48c1e5a17","outputPortId":5001,"inputNodeGuid":"f8947676-1084-4228-b991-1509cc7fe851","inputPortId":7001}</t>
         </is>
       </c>
       <c r="H82"/>
@@ -2265,12 +2269,12 @@
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>{"guid":"d897a922-5756-42cf-ac65-90a48c1e5a17","nodeType":8,"position":{"x":1022.666748046875,"y":-1951.3333740234375},"targetType":2,"assetTags":{"Tags":[]},"grantedTags":{"Tags":[]},"applicationRequiredTags":{"Tags":[]},"applicationImmunityTags":{"Tags":[]},"removeGameEffectsWithTags":{"Tags":[]},"durationType":2,"duration":"0","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"Tags":[]},"cancelOnAbilityEnd":false,"launchPositionSource":0,"launchBindingName":"center","targetPositionSource":1,"targetBindingName":"center","projectileTargetType":0,"flyOver":true,"offsetAngle":-30.0,"curveHeight":0.0,"projectileEntityId":50002,"projectilePrefab":null,"projectilePrefabPath":"Assets/Res/Entity/Effect/ef_fashi_huoyandan01.prefab","speed":10.0,"maxDistance":10.0,"collisionRadius":0.5,"isPiercing":false,"maxPierceCount":1,"collisionTargetTags":{"Tags":[]},"collisionExcludeTags":{"Tags":[]},"isBouncing":false,"bounceTargetMode":0,"maxBounceCount":3,"bounceSearchRadius":10.0,"canBounceToSameTarget":false,"excludeSourceCamp":true,"bounceAngleOffset":0.0}</t>
+          <t>{"guid":"9a695e91-e218-425e-82ed-1e157bf1b014","nodeType":8,"position":{"x":1022.666748046875,"y":-2131.333251953125},"targetType":2,"assetTags":{"Tags":[]},"grantedTags":{"Tags":[]},"applicationRequiredTags":{"Tags":[]},"applicationImmunityTags":{"Tags":[]},"removeGameEffectsWithTags":{"Tags":[]},"durationType":2,"duration":"0","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"Tags":[]},"cancelOnAbilityEnd":false,"launchPositionSource":0,"launchBindingName":"center","targetPositionSource":1,"targetBindingName":"center","projectileTargetType":0,"flyOver":true,"offsetAngle":0.0,"curveHeight":0.0,"projectileEntityId":50002,"projectilePrefab":null,"projectilePrefabPath":"Assets/Res/Entity/Effect/ef_fashi_huoyandan01.prefab","speed":10.0,"maxDistance":10.0,"collisionRadius":0.5,"isPiercing":false,"maxPierceCount":1,"collisionTargetTags":{"Tags":[]},"collisionExcludeTags":{"Tags":[]},"isBouncing":false,"bounceTargetMode":0,"maxBounceCount":3,"bounceSearchRadius":10.0,"canBounceToSameTarget":false,"excludeSourceCamp":true,"bounceAngleOffset":0.0}</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>{"outputNodeGuid":"432ff1e3-b18d-476d-af80-d39ddc07402a","outputPortId":2315086,"inputNodeGuid":"ce857360-de7e-4457-b348-9c124ce98879","inputPortId":7001}</t>
+          <t>{"outputNodeGuid":"432ff1e3-b18d-476d-af80-d39ddc07402a","outputPortId":2649436,"inputNodeGuid":"2cfdacd2-0186-49dd-b177-4eb8c0ad87bd","inputPortId":7001}</t>
         </is>
       </c>
       <c r="H83"/>
@@ -2281,16 +2285,16 @@
       <c r="C84"/>
       <c r="D84"/>
       <c r="E84">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>{"guid":"c353e286-8ef0-460a-b917-887f2aeb390a","nodeType":14,"position":{"x":1677.3333740234375,"y":-2239.333251953125},"targetType":1,"requiredTags":{"Tags":[]},"immunityTags":{"Tags":[]},"destroyWithNode":false,"positionSource":2,"positionBindingName":"head","textType":0,"fixedText":"","contextDataKey":"DamageResult","textColor":{"r":1.0,"g":0.0,"b":0.0,"a":1.0},"criticalColor":{"r":1.0,"g":0.5,"b":0.0,"a":1.0},"missColor":{"r":0.5,"g":0.5,"b":0.5,"a":1.0},"fontSize":5.0,"criticalFontSize":60.0,"duration":1.5,"offset":{"x":0.0,"y":0.0},"moveDirection":{"x":0.0,"y":1.0}}</t>
+          <t>{"guid":"d897a922-5756-42cf-ac65-90a48c1e5a17","nodeType":8,"position":{"x":1022.666748046875,"y":-1951.3333740234375},"targetType":2,"assetTags":{"Tags":[]},"grantedTags":{"Tags":[]},"applicationRequiredTags":{"Tags":[]},"applicationImmunityTags":{"Tags":[]},"removeGameEffectsWithTags":{"Tags":[]},"durationType":2,"duration":"0","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"Tags":[]},"cancelOnAbilityEnd":false,"launchPositionSource":0,"launchBindingName":"center","targetPositionSource":1,"targetBindingName":"center","projectileTargetType":0,"flyOver":true,"offsetAngle":-30.0,"curveHeight":0.0,"projectileEntityId":50002,"projectilePrefab":null,"projectilePrefabPath":"Assets/Res/Entity/Effect/ef_fashi_huoyandan01.prefab","speed":10.0,"maxDistance":10.0,"collisionRadius":0.5,"isPiercing":false,"maxPierceCount":1,"collisionTargetTags":{"Tags":[]},"collisionExcludeTags":{"Tags":[]},"isBouncing":false,"bounceTargetMode":0,"maxBounceCount":3,"bounceSearchRadius":10.0,"canBounceToSameTarget":false,"excludeSourceCamp":true,"bounceAngleOffset":0.0}</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>{"outputNodeGuid":"432ff1e3-b18d-476d-af80-d39ddc07402a","outputPortId":2315086,"inputNodeGuid":"9a695e91-e218-425e-82ed-1e157bf1b014","inputPortId":7001}</t>
+          <t>{"outputNodeGuid":"432ff1e3-b18d-476d-af80-d39ddc07402a","outputPortId":2315086,"inputNodeGuid":"ce857360-de7e-4457-b348-9c124ce98879","inputPortId":7001}</t>
         </is>
       </c>
       <c r="H84"/>
@@ -2300,57 +2304,57 @@
       <c r="B85"/>
       <c r="C85"/>
       <c r="D85"/>
-      <c r="E85"/>
-      <c r="F85"/>
+      <c r="E85">
+        <v>14</v>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>{"guid":"c353e286-8ef0-460a-b917-887f2aeb390a","nodeType":14,"position":{"x":1677.3333740234375,"y":-2239.333251953125},"targetType":1,"requiredTags":{"Tags":[]},"immunityTags":{"Tags":[]},"destroyWithNode":false,"positionSource":2,"positionBindingName":"head","textType":0,"fixedText":"","contextDataKey":"DamageResult","textColor":{"r":1.0,"g":0.0,"b":0.0,"a":1.0},"criticalColor":{"r":1.0,"g":0.5,"b":0.0,"a":1.0},"missColor":{"r":0.5,"g":0.5,"b":0.5,"a":1.0},"fontSize":5.0,"criticalFontSize":60.0,"duration":1.5,"offset":{"x":0.0,"y":0.0},"moveDirection":{"x":0.0,"y":1.0}}</t>
+        </is>
+      </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>{"outputNodeGuid":"432ff1e3-b18d-476d-af80-d39ddc07402a","outputPortId":2315086,"inputNodeGuid":"d897a922-5756-42cf-ac65-90a48c1e5a17","inputPortId":7001}</t>
+          <t>{"outputNodeGuid":"432ff1e3-b18d-476d-af80-d39ddc07402a","outputPortId":2315086,"inputNodeGuid":"9a695e91-e218-425e-82ed-1e157bf1b014","inputPortId":7001}</t>
         </is>
       </c>
       <c r="H85"/>
     </row>
     <row r="86">
       <c r="A86"/>
-      <c r="B86">
-        <v>1006</v>
-      </c>
-      <c r="C86" t="inlineStr">
-        <is>
-          <t>Wan</t>
-        </is>
-      </c>
+      <c r="B86"/>
+      <c r="C86"/>
       <c r="D86"/>
-      <c r="E86">
-        <v>3</v>
-      </c>
-      <c r="F86" t="inlineStr">
-        <is>
-          <t>{"guid":"9d6f459d-b588-4b64-843b-1b71e8f299ae","nodeType":3,"position":{"x":-1186.6666259765625,"y":-2011.3333740234375},"targetType":1,"assetTags":{"Tags":[]},"grantedTags":{"Tags":[]},"applicationRequiredTags":{"Tags":[]},"applicationImmunityTags":{"Tags":[]},"removeGameEffectsWithTags":{"Tags":[]},"durationType":0,"duration":"0","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[{"attrType":100,"operation":0,"magnitudeSourceType":0,"fixedValue":10.0,"formula":"","mmcType":0,"setByCallerKey":"","mmcCaptureAttribute":200,"mmcAttributeSource":0,"mmcCoefficient":1.0,"mmcUseSnapshot":true}],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"Tags":[]},"cancelOnAbilityEnd":true}</t>
-        </is>
-      </c>
+      <c r="E86"/>
+      <c r="F86"/>
       <c r="G86" t="inlineStr">
         <is>
-          <t>{"outputNodeGuid":"356907e0-1488-4128-bfcc-7ff73cfc3330","outputPortId":1002,"inputNodeGuid":"432ff1e3-b18d-476d-af80-d39ddc07402a","inputPortId":7001}</t>
+          <t>{"outputNodeGuid":"432ff1e3-b18d-476d-af80-d39ddc07402a","outputPortId":2315086,"inputNodeGuid":"d897a922-5756-42cf-ac65-90a48c1e5a17","inputPortId":7001}</t>
         </is>
       </c>
       <c r="H86"/>
     </row>
     <row r="87">
       <c r="A87"/>
-      <c r="B87"/>
-      <c r="C87"/>
+      <c r="B87">
+        <v>1006</v>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Wan</t>
+        </is>
+      </c>
       <c r="D87"/>
       <c r="E87">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>{"guid":"f73ba91e-a76b-456c-b19c-a5176809d5f5","nodeType":7,"position":{"x":700.0,"y":-1856.666748046875},"targetType":1,"endType":0}</t>
+          <t>{"guid":"9d6f459d-b588-4b64-843b-1b71e8f299ae","nodeType":3,"position":{"x":-1186.6666259765625,"y":-2011.3333740234375},"targetType":1,"assetTags":{"Tags":[]},"grantedTags":{"Tags":[]},"applicationRequiredTags":{"Tags":[]},"applicationImmunityTags":{"Tags":[]},"removeGameEffectsWithTags":{"Tags":[]},"durationType":0,"duration":"0","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[{"attrType":100,"operation":0,"magnitudeSourceType":0,"fixedValue":10.0,"formula":"","mmcType":0,"setByCallerKey":"","mmcCaptureAttribute":200,"mmcAttributeSource":0,"mmcCoefficient":1.0,"mmcUseSnapshot":true}],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"Tags":[]},"cancelOnAbilityEnd":true}</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>{"outputNodeGuid":"356907e0-1488-4128-bfcc-7ff73cfc3330","outputPortId":1004,"inputNodeGuid":"c28fb88d-51b1-47b2-be59-859e0ac638e3","inputPortId":7001}</t>
+          <t>{"outputNodeGuid":"356907e0-1488-4128-bfcc-7ff73cfc3330","outputPortId":1002,"inputNodeGuid":"432ff1e3-b18d-476d-af80-d39ddc07402a","inputPortId":7001}</t>
         </is>
       </c>
       <c r="H87"/>
@@ -2361,16 +2365,16 @@
       <c r="C88"/>
       <c r="D88"/>
       <c r="E88">
-        <v>22</v>
+        <v>7</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>{"guid":"091ecddb-f80b-4c00-aa06-f9bc718618d2","nodeType":22,"position":{"x":-93.333328247070313,"y":-1708.666748046875},"targetType":0,"assetTags":{"Tags":[]},"grantedTags":{"Tags":[]},"applicationRequiredTags":{"Tags":[]},"applicationImmunityTags":{"Tags":[]},"removeGameEffectsWithTags":{"Tags":[]},"durationType":1,"duration":"0.5","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"Tags":[]},"cancelOnAbilityEnd":false,"displaceType":0,"speed":10.0,"distance":3.0,"minDistance":0.5,"pointSource":0,"pointBindingName":""}</t>
+          <t>{"guid":"f73ba91e-a76b-456c-b19c-a5176809d5f5","nodeType":7,"position":{"x":700.0,"y":-1856.666748046875},"targetType":1,"endType":0}</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>{"outputNodeGuid":"356907e0-1488-4128-bfcc-7ff73cfc3330","outputPortId":1003,"inputNodeGuid":"9d6f459d-b588-4b64-843b-1b71e8f299ae","inputPortId":7001}</t>
+          <t>{"outputNodeGuid":"356907e0-1488-4128-bfcc-7ff73cfc3330","outputPortId":1004,"inputNodeGuid":"c28fb88d-51b1-47b2-be59-859e0ac638e3","inputPortId":7001}</t>
         </is>
       </c>
       <c r="H88"/>
@@ -2381,16 +2385,16 @@
       <c r="C89"/>
       <c r="D89"/>
       <c r="E89">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>{"guid":"c28fb88d-51b1-47b2-be59-859e0ac638e3","nodeType":10,"position":{"x":-1186.6666259765625,"y":-1747.3333740234375},"targetType":1,"assetTags":{"Tags":[]},"grantedTags":{"Tags":[{"Name":"CD.Wan","HashCode":87403585,"ShortName":"Wan","AncestorHashCodes":[-1137859925],"AncestorNames":["CD"]}]},"applicationRequiredTags":{"Tags":[]},"applicationImmunityTags":{"Tags":[]},"removeGameEffectsWithTags":{"Tags":[]},"durationType":1,"duration":"5","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"Tags":[]},"cancelOnAbilityEnd":false,"cooldownType":0,"maxCharges":2,"chargeTime":"10"}</t>
+          <t>{"guid":"091ecddb-f80b-4c00-aa06-f9bc718618d2","nodeType":22,"position":{"x":-93.333328247070313,"y":-1708.666748046875},"targetType":0,"assetTags":{"Tags":[]},"grantedTags":{"Tags":[]},"applicationRequiredTags":{"Tags":[]},"applicationImmunityTags":{"Tags":[]},"removeGameEffectsWithTags":{"Tags":[]},"durationType":1,"duration":"0.5","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"Tags":[]},"cancelOnAbilityEnd":false,"displaceType":0,"speed":10.0,"distance":3.0,"minDistance":0.5,"pointSource":0,"pointBindingName":""}</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>{"outputNodeGuid":"432ff1e3-b18d-476d-af80-d39ddc07402a","outputPortId":2000539,"inputNodeGuid":"f73ba91e-a76b-456c-b19c-a5176809d5f5","inputPortId":7001}</t>
+          <t>{"outputNodeGuid":"356907e0-1488-4128-bfcc-7ff73cfc3330","outputPortId":1003,"inputNodeGuid":"9d6f459d-b588-4b64-843b-1b71e8f299ae","inputPortId":7001}</t>
         </is>
       </c>
       <c r="H89"/>
@@ -2401,16 +2405,16 @@
       <c r="C90"/>
       <c r="D90"/>
       <c r="E90">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>{"guid":"e33ab94c-1496-4d6a-ba5e-1afd38bb0c30","nodeType":4,"position":{"x":-452.0,"y":-1786.666748046875},"targetType":1,"searchShapeType":0,"searchLineType":0,"positionSource":0,"positionBindingName":"center","searchCircleRadius":4.0,"searchSectorRadius":2.0,"searchSectorAngle":180.0,"searchLineDirectionOffsetAngle":0.0,"searchLineDirectionWidth":1.0,"searchLineDirectionLength":10.0,"lineStartPositionSource":0,"lineStartBindingName":"","lineEndPositionSource":1,"lineEndBindingName":"","searchLineBetweenWidth":1.0,"searchLineAbsoluteAngle":0.0,"searchLineAbsoluteWidth":1.0,"searchLineAbsoluteLength":10.0,"maxTargets":999,"searchTargetTags":{"Tags":[{"Name":"unitType.monster","HashCode":-2021655864,"ShortName":"monster","AncestorHashCodes":[1600484460],"AncestorNames":["unitType"]}]},"searchExcludeTags":{"Tags":[]}}</t>
+          <t>{"guid":"c28fb88d-51b1-47b2-be59-859e0ac638e3","nodeType":10,"position":{"x":-1186.6666259765625,"y":-1747.3333740234375},"targetType":1,"assetTags":{"Tags":[]},"grantedTags":{"Tags":[{"Name":"CD.Wan","HashCode":87403585,"ShortName":"Wan","AncestorHashCodes":[-1137859925],"AncestorNames":["CD"]}]},"applicationRequiredTags":{"Tags":[]},"applicationImmunityTags":{"Tags":[]},"removeGameEffectsWithTags":{"Tags":[]},"durationType":1,"duration":"5","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"Tags":[]},"cancelOnAbilityEnd":false,"cooldownType":0,"maxCharges":2,"chargeTime":"10"}</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>{"outputNodeGuid":"432ff1e3-b18d-476d-af80-d39ddc07402a","outputPortId":2315086,"inputNodeGuid":"e33ab94c-1496-4d6a-ba5e-1afd38bb0c30","inputPortId":7001}</t>
+          <t>{"outputNodeGuid":"432ff1e3-b18d-476d-af80-d39ddc07402a","outputPortId":2000539,"inputNodeGuid":"f73ba91e-a76b-456c-b19c-a5176809d5f5","inputPortId":7001}</t>
         </is>
       </c>
       <c r="H90"/>
@@ -2421,16 +2425,16 @@
       <c r="C91"/>
       <c r="D91"/>
       <c r="E91">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>{"guid":"432ff1e3-b18d-476d-af80-d39ddc07402a","nodeType":20,"position":{"x":-502.66665649414063,"y":-2384.0},"targetType":1,"skeletonDataAsset":null,"skeletonDataAssetPath":"Assets/Res/Spine/SP_Zhanshi/SP_Zhanshi_SkeletonData.asset","animationName":"Skill_attack_1009","animationDuration":"25","isAnimationLooping":false,"timeEffects":[{"triggerTime":4,"portIdValue":2315086,"legacyPortId":"de0ba361-3aba-4ef0-bb07-9b418fcae591"},{"triggerTime":25,"portIdValue":2000539,"legacyPortId":"f41c85e0-7f26-494e-9ffc-4a06c980f811"}],"timeCues":[{"startTime":0,"endTime":75,"portIdValue":2287012,"legacyPortId":"8dea1941-c520-4f9a-aee0-40932c8542ef"}]}</t>
+          <t>{"guid":"e33ab94c-1496-4d6a-ba5e-1afd38bb0c30","nodeType":4,"position":{"x":-452.0,"y":-1786.666748046875},"targetType":1,"searchShapeType":0,"searchLineType":0,"positionSource":0,"positionBindingName":"center","searchCircleRadius":4.0,"searchSectorRadius":2.0,"searchSectorAngle":180.0,"searchLineDirectionOffsetAngle":0.0,"searchLineDirectionWidth":1.0,"searchLineDirectionLength":10.0,"lineStartPositionSource":0,"lineStartBindingName":"","lineEndPositionSource":1,"lineEndBindingName":"","searchLineBetweenWidth":1.0,"searchLineAbsoluteAngle":0.0,"searchLineAbsoluteWidth":1.0,"searchLineAbsoluteLength":10.0,"maxTargets":999,"searchTargetTags":{"Tags":[{"Name":"unitType.monster","HashCode":-2021655864,"ShortName":"monster","AncestorHashCodes":[1600484460],"AncestorNames":["unitType"]}]},"searchExcludeTags":{"Tags":[]}}</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>{"outputNodeGuid":"432ff1e3-b18d-476d-af80-d39ddc07402a","outputPortId":2287012,"inputNodeGuid":"cde57fb8-b693-4da8-a4a8-fd61e56c5dcd","inputPortId":7001}</t>
+          <t>{"outputNodeGuid":"432ff1e3-b18d-476d-af80-d39ddc07402a","outputPortId":2315086,"inputNodeGuid":"e33ab94c-1496-4d6a-ba5e-1afd38bb0c30","inputPortId":7001}</t>
         </is>
       </c>
       <c r="H91"/>
@@ -2441,16 +2445,16 @@
       <c r="C92"/>
       <c r="D92"/>
       <c r="E92">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>{"guid":"356907e0-1488-4128-bfcc-7ff73cfc3330","nodeType":0,"position":{"x":-878.6666259765625,"y":-1853.3333740234375},"targetType":1,"skillId":1006,"assetTags":{"Tags":[]},"cancelAbilitiesWithTags":{"Tags":[]},"blockAbilitiesWithTags":{"Tags":[]},"activationOwnedTags":{"Tags":[{"Name":"Skill.Running","HashCode":-51601538,"ShortName":"Running","AncestorHashCodes":[1312877309],"AncestorNames":["Skill"]}]},"activationRequiredTags":{"Tags":[]},"activationBlockedTags":{"Tags":[{"Name":"CD.Wan","HashCode":87403585,"ShortName":"Wan","AncestorHashCodes":[-1137859925],"AncestorNames":["CD"]},{"Name":"Skill.Running","HashCode":-51601538,"ShortName":"Running","AncestorHashCodes":[1312877309],"AncestorNames":["Skill"]}]},"ongoingBlockedTags":{"Tags":[]},"eventOutputPorts":[]}</t>
+          <t>{"guid":"432ff1e3-b18d-476d-af80-d39ddc07402a","nodeType":20,"position":{"x":-502.66665649414063,"y":-2384.0},"targetType":1,"skeletonDataAsset":null,"skeletonDataAssetPath":"Assets/Res/Spine/SP_Zhanshi/SP_Zhanshi_SkeletonData.asset","animationName":"Skill_attack_1009","animationDuration":"25","isAnimationLooping":false,"timeEffects":[{"triggerTime":4,"portIdValue":2315086,"legacyPortId":"de0ba361-3aba-4ef0-bb07-9b418fcae591"},{"triggerTime":25,"portIdValue":2000539,"legacyPortId":"f41c85e0-7f26-494e-9ffc-4a06c980f811"}],"timeCues":[{"startTime":0,"endTime":75,"portIdValue":2287012,"legacyPortId":"8dea1941-c520-4f9a-aee0-40932c8542ef"}]}</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>{"outputNodeGuid":"e33ab94c-1496-4d6a-ba5e-1afd38bb0c30","outputPortId":4001,"inputNodeGuid":"091ecddb-f80b-4c00-aa06-f9bc718618d2","inputPortId":7001}</t>
+          <t>{"outputNodeGuid":"432ff1e3-b18d-476d-af80-d39ddc07402a","outputPortId":2287012,"inputNodeGuid":"cde57fb8-b693-4da8-a4a8-fd61e56c5dcd","inputPortId":7001}</t>
         </is>
       </c>
       <c r="H92"/>
@@ -2461,58 +2465,58 @@
       <c r="C93"/>
       <c r="D93"/>
       <c r="E93">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>{"guid":"cde57fb8-b693-4da8-a4a8-fd61e56c5dcd","nodeType":12,"position":{"x":677.3333740234375,"y":-1998.666748046875},"targetType":1,"requiredTags":{"Tags":[]},"immunityTags":{"Tags":[]},"destroyWithNode":false,"positionSource":0,"particleEntityId":50010,"particlePrefab":null,"particlePrefabPath":"Assets/Res/Entity/Effect/ef_Zhanshi_zhentianpaoxiao_01.prefab","particleBindingName":"down","particleOffset":{"x":0.0,"y":0.0,"z":0.0},"particleScale":{"x":1.0,"y":1.0,"z":1.0},"attachToTarget":false,"particleLoop":false}</t>
-        </is>
-      </c>
-      <c r="G93"/>
+          <t>{"guid":"356907e0-1488-4128-bfcc-7ff73cfc3330","nodeType":0,"position":{"x":-878.6666259765625,"y":-1853.3333740234375},"targetType":1,"skillId":1006,"assetTags":{"Tags":[]},"cancelAbilitiesWithTags":{"Tags":[]},"blockAbilitiesWithTags":{"Tags":[]},"activationOwnedTags":{"Tags":[{"Name":"Skill.Running","HashCode":-51601538,"ShortName":"Running","AncestorHashCodes":[1312877309],"AncestorNames":["Skill"]}]},"activationRequiredTags":{"Tags":[]},"activationBlockedTags":{"Tags":[{"Name":"CD.Wan","HashCode":87403585,"ShortName":"Wan","AncestorHashCodes":[-1137859925],"AncestorNames":["CD"]},{"Name":"Skill.Running","HashCode":-51601538,"ShortName":"Running","AncestorHashCodes":[1312877309],"AncestorNames":["Skill"]}]},"ongoingBlockedTags":{"Tags":[]},"eventOutputPorts":[]}</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>{"outputNodeGuid":"e33ab94c-1496-4d6a-ba5e-1afd38bb0c30","outputPortId":4001,"inputNodeGuid":"091ecddb-f80b-4c00-aa06-f9bc718618d2","inputPortId":7001}</t>
+        </is>
+      </c>
       <c r="H93"/>
     </row>
     <row r="94">
       <c r="A94"/>
-      <c r="B94">
-        <v>1004</v>
-      </c>
-      <c r="C94" t="inlineStr">
-        <is>
-          <t>Wind</t>
-        </is>
-      </c>
+      <c r="B94"/>
+      <c r="C94"/>
       <c r="D94"/>
       <c r="E94">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>{"guid":"9d6f459d-b588-4b64-843b-1b71e8f299ae","nodeType":3,"position":{"x":-1186.6666259765625,"y":-2011.3333740234375},"targetType":1,"assetTags":{"Tags":[]},"grantedTags":{"Tags":[]},"applicationRequiredTags":{"Tags":[]},"applicationImmunityTags":{"Tags":[]},"removeGameEffectsWithTags":{"Tags":[]},"durationType":0,"duration":"0","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[{"attrType":100,"operation":0,"magnitudeSourceType":0,"fixedValue":10.0,"formula":"","mmcType":0,"setByCallerKey":"","mmcCaptureAttribute":200,"mmcAttributeSource":0,"mmcCoefficient":1.0,"mmcUseSnapshot":true}],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"Tags":[]},"cancelOnAbilityEnd":true}</t>
-        </is>
-      </c>
-      <c r="G94" t="inlineStr">
-        <is>
-          <t>{"outputNodeGuid":"356907e0-1488-4128-bfcc-7ff73cfc3330","outputPortId":1002,"inputNodeGuid":"432ff1e3-b18d-476d-af80-d39ddc07402a","inputPortId":7001}</t>
-        </is>
-      </c>
+          <t>{"guid":"cde57fb8-b693-4da8-a4a8-fd61e56c5dcd","nodeType":12,"position":{"x":677.3333740234375,"y":-1998.666748046875},"targetType":1,"requiredTags":{"Tags":[]},"immunityTags":{"Tags":[]},"destroyWithNode":false,"positionSource":0,"particleEntityId":50010,"particlePrefab":null,"particlePrefabPath":"Assets/Res/Entity/Effect/ef_Zhanshi_zhentianpaoxiao_01.prefab","particleBindingName":"down","particleOffset":{"x":0.0,"y":0.0,"z":0.0},"particleScale":{"x":1.0,"y":1.0,"z":1.0},"attachToTarget":false,"particleLoop":false}</t>
+        </is>
+      </c>
+      <c r="G94"/>
       <c r="H94"/>
     </row>
     <row r="95">
       <c r="A95"/>
-      <c r="B95"/>
-      <c r="C95"/>
+      <c r="B95">
+        <v>1004</v>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Wind</t>
+        </is>
+      </c>
       <c r="D95"/>
       <c r="E95">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>{"guid":"c28fb88d-51b1-47b2-be59-859e0ac638e3","nodeType":10,"position":{"x":-1186.6666259765625,"y":-1747.3333740234375},"targetType":1,"assetTags":{"Tags":[]},"grantedTags":{"Tags":[{"Name":"CD.Wind","HashCode":1982736573,"ShortName":"Wind","AncestorHashCodes":[-1137859925],"AncestorNames":["CD"]}]},"applicationRequiredTags":{"Tags":[]},"applicationImmunityTags":{"Tags":[]},"removeGameEffectsWithTags":{"Tags":[]},"durationType":1,"duration":"15","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"Tags":[]},"cancelOnAbilityEnd":false,"cooldownType":0,"maxCharges":2,"chargeTime":"10"}</t>
+          <t>{"guid":"9d6f459d-b588-4b64-843b-1b71e8f299ae","nodeType":3,"position":{"x":-1186.6666259765625,"y":-2011.3333740234375},"targetType":1,"assetTags":{"Tags":[]},"grantedTags":{"Tags":[]},"applicationRequiredTags":{"Tags":[]},"applicationImmunityTags":{"Tags":[]},"removeGameEffectsWithTags":{"Tags":[]},"durationType":0,"duration":"0","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[{"attrType":100,"operation":0,"magnitudeSourceType":0,"fixedValue":10.0,"formula":"","mmcType":0,"setByCallerKey":"","mmcCaptureAttribute":200,"mmcAttributeSource":0,"mmcCoefficient":1.0,"mmcUseSnapshot":true}],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"Tags":[]},"cancelOnAbilityEnd":true}</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>{"outputNodeGuid":"356907e0-1488-4128-bfcc-7ff73cfc3330","outputPortId":1004,"inputNodeGuid":"c28fb88d-51b1-47b2-be59-859e0ac638e3","inputPortId":7001}</t>
+          <t>{"outputNodeGuid":"356907e0-1488-4128-bfcc-7ff73cfc3330","outputPortId":1002,"inputNodeGuid":"432ff1e3-b18d-476d-af80-d39ddc07402a","inputPortId":7001}</t>
         </is>
       </c>
       <c r="H95"/>
@@ -2523,16 +2527,16 @@
       <c r="C96"/>
       <c r="D96"/>
       <c r="E96">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>{"guid":"e33ab94c-1496-4d6a-ba5e-1afd38bb0c30","nodeType":4,"position":{"x":-182.0,"y":-1784.0},"targetType":1,"searchShapeType":0,"searchLineType":0,"positionSource":0,"positionBindingName":"center","searchCircleRadius":2.5,"searchSectorRadius":2.0,"searchSectorAngle":180.0,"searchLineDirectionOffsetAngle":0.0,"searchLineDirectionWidth":1.0,"searchLineDirectionLength":10.0,"lineStartPositionSource":0,"lineStartBindingName":"","lineEndPositionSource":1,"lineEndBindingName":"","searchLineBetweenWidth":1.0,"searchLineAbsoluteAngle":0.0,"searchLineAbsoluteWidth":1.0,"searchLineAbsoluteLength":10.0,"maxTargets":999,"searchTargetTags":{"Tags":[{"Name":"unitType.monster","HashCode":-2021655864,"ShortName":"monster","AncestorHashCodes":[1600484460],"AncestorNames":["unitType"]}]},"searchExcludeTags":{"Tags":[]}}</t>
+          <t>{"guid":"c28fb88d-51b1-47b2-be59-859e0ac638e3","nodeType":10,"position":{"x":-1186.6666259765625,"y":-1747.3333740234375},"targetType":1,"assetTags":{"Tags":[]},"grantedTags":{"Tags":[{"Name":"CD.Wind","HashCode":1982736573,"ShortName":"Wind","AncestorHashCodes":[-1137859925],"AncestorNames":["CD"]}]},"applicationRequiredTags":{"Tags":[]},"applicationImmunityTags":{"Tags":[]},"removeGameEffectsWithTags":{"Tags":[]},"durationType":1,"duration":"15","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"Tags":[]},"cancelOnAbilityEnd":false,"cooldownType":0,"maxCharges":2,"chargeTime":"10"}</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>{"outputNodeGuid":"356907e0-1488-4128-bfcc-7ff73cfc3330","outputPortId":1003,"inputNodeGuid":"9d6f459d-b588-4b64-843b-1b71e8f299ae","inputPortId":7001}</t>
+          <t>{"outputNodeGuid":"356907e0-1488-4128-bfcc-7ff73cfc3330","outputPortId":1004,"inputNodeGuid":"c28fb88d-51b1-47b2-be59-859e0ac638e3","inputPortId":7001}</t>
         </is>
       </c>
       <c r="H96"/>
@@ -2543,16 +2547,16 @@
       <c r="C97"/>
       <c r="D97"/>
       <c r="E97">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>{"guid":"a32d1135-94db-4f81-95ba-9d5f105ef8d0","nodeType":1,"position":{"x":93.333343505859375,"y":-1784.0},"targetType":0,"assetTags":{"Tags":[]},"grantedTags":{"Tags":[]},"applicationRequiredTags":{"Tags":[]},"applicationImmunityTags":{"Tags":[]},"removeGameEffectsWithTags":{"Tags":[]},"durationType":0,"duration":"0","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"Tags":[]},"cancelOnAbilityEnd":true,"damageType":0,"damageSourceType":0,"damageFixedValue":1.0,"damageFormula":"","damageMMCType":0,"damageSetByCallerKey":"","damageMMCCaptureAttribute":200,"damageMMCAttributeSource":0,"damageMMCCoefficient":1.0,"damageMMCUseSnapshot":true,"damageMultiplyByStackCount":false,"damageCalculationType":0,"enableHitKnockback":false,"knockbackDistance":1.0,"knockbackSpeed":12.0}</t>
+          <t>{"guid":"e33ab94c-1496-4d6a-ba5e-1afd38bb0c30","nodeType":4,"position":{"x":-182.0,"y":-1784.0},"targetType":1,"searchShapeType":0,"searchLineType":0,"positionSource":0,"positionBindingName":"center","searchCircleRadius":2.5,"searchSectorRadius":2.0,"searchSectorAngle":180.0,"searchLineDirectionOffsetAngle":0.0,"searchLineDirectionWidth":1.0,"searchLineDirectionLength":10.0,"lineStartPositionSource":0,"lineStartBindingName":"","lineEndPositionSource":1,"lineEndBindingName":"","searchLineBetweenWidth":1.0,"searchLineAbsoluteAngle":0.0,"searchLineAbsoluteWidth":1.0,"searchLineAbsoluteLength":10.0,"maxTargets":999,"searchTargetTags":{"Tags":[{"Name":"unitType.monster","HashCode":-2021655864,"ShortName":"monster","AncestorHashCodes":[1600484460],"AncestorNames":["unitType"]}]},"searchExcludeTags":{"Tags":[]}}</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>{"outputNodeGuid":"356907e0-1488-4128-bfcc-7ff73cfc3330","outputPortId":1001,"inputNodeGuid":"d8847c3e-459e-4589-a96b-37ebb5ec458b","inputPortId":7001}</t>
+          <t>{"outputNodeGuid":"356907e0-1488-4128-bfcc-7ff73cfc3330","outputPortId":1003,"inputNodeGuid":"9d6f459d-b588-4b64-843b-1b71e8f299ae","inputPortId":7001}</t>
         </is>
       </c>
       <c r="H97"/>
@@ -2563,16 +2567,16 @@
       <c r="C98"/>
       <c r="D98"/>
       <c r="E98">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>{"guid":"764289ea-065e-4f48-afc0-0f6963d18d57","nodeType":14,"position":{"x":306.66665649414063,"y":-1784.0},"targetType":1,"requiredTags":{"Tags":[]},"immunityTags":{"Tags":[]},"destroyWithNode":false,"positionSource":2,"positionBindingName":"head","textType":0,"fixedText":"","contextDataKey":"DamageResult","textColor":{"r":1.0,"g":0.0,"b":0.0,"a":1.0},"criticalColor":{"r":1.0,"g":0.5,"b":0.0,"a":1.0},"missColor":{"r":0.5,"g":0.5,"b":0.5,"a":1.0},"fontSize":5.0,"criticalFontSize":60.0,"duration":1.5,"offset":{"x":0.0,"y":0.0},"moveDirection":{"x":0.0,"y":1.0}}</t>
+          <t>{"guid":"a32d1135-94db-4f81-95ba-9d5f105ef8d0","nodeType":1,"position":{"x":93.333343505859375,"y":-1784.0},"targetType":0,"assetTags":{"Tags":[]},"grantedTags":{"Tags":[]},"applicationRequiredTags":{"Tags":[]},"applicationImmunityTags":{"Tags":[]},"removeGameEffectsWithTags":{"Tags":[]},"durationType":0,"duration":"0","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"Tags":[]},"cancelOnAbilityEnd":true,"damageType":0,"damageSourceType":0,"damageFixedValue":1.0,"damageFormula":"","damageMMCType":0,"damageSetByCallerKey":"","damageMMCCaptureAttribute":200,"damageMMCAttributeSource":0,"damageMMCCoefficient":1.0,"damageMMCUseSnapshot":true,"damageMultiplyByStackCount":false,"damageCalculationType":0,"enableHitKnockback":false,"knockbackDistance":1.0,"knockbackSpeed":12.0}</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>{"outputNodeGuid":"d8847c3e-459e-4589-a96b-37ebb5ec458b","outputPortId":3002,"inputNodeGuid":"e33ab94c-1496-4d6a-ba5e-1afd38bb0c30","inputPortId":7001}</t>
+          <t>{"outputNodeGuid":"356907e0-1488-4128-bfcc-7ff73cfc3330","outputPortId":1001,"inputNodeGuid":"d8847c3e-459e-4589-a96b-37ebb5ec458b","inputPortId":7001}</t>
         </is>
       </c>
       <c r="H98"/>
@@ -2583,16 +2587,16 @@
       <c r="C99"/>
       <c r="D99"/>
       <c r="E99">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>{"guid":"d8847c3e-459e-4589-a96b-37ebb5ec458b","nodeType":21,"position":{"x":-572.0,"y":-1804.0},"targetType":1,"assetTags":{"Tags":[]},"grantedTags":{"Tags":[]},"applicationRequiredTags":{"Tags":[]},"applicationImmunityTags":{"Tags":[]},"removeGameEffectsWithTags":{"Tags":[]},"durationType":2,"duration":"0","isPeriodic":true,"period":"0.3","executeOnApplication":false,"attributeModifiers":[],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"Tags":[]},"cancelOnAbilityEnd":true}</t>
+          <t>{"guid":"764289ea-065e-4f48-afc0-0f6963d18d57","nodeType":14,"position":{"x":306.66665649414063,"y":-1784.0},"targetType":1,"requiredTags":{"Tags":[]},"immunityTags":{"Tags":[]},"destroyWithNode":false,"positionSource":2,"positionBindingName":"head","textType":0,"fixedText":"","contextDataKey":"DamageResult","textColor":{"r":1.0,"g":0.0,"b":0.0,"a":1.0},"criticalColor":{"r":1.0,"g":0.5,"b":0.0,"a":1.0},"missColor":{"r":0.5,"g":0.5,"b":0.5,"a":1.0},"fontSize":5.0,"criticalFontSize":60.0,"duration":1.5,"offset":{"x":0.0,"y":0.0},"moveDirection":{"x":0.0,"y":1.0}}</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>{"outputNodeGuid":"e33ab94c-1496-4d6a-ba5e-1afd38bb0c30","outputPortId":4001,"inputNodeGuid":"a32d1135-94db-4f81-95ba-9d5f105ef8d0","inputPortId":7001}</t>
+          <t>{"outputNodeGuid":"d8847c3e-459e-4589-a96b-37ebb5ec458b","outputPortId":3002,"inputNodeGuid":"e33ab94c-1496-4d6a-ba5e-1afd38bb0c30","inputPortId":7001}</t>
         </is>
       </c>
       <c r="H99"/>
@@ -2603,16 +2607,16 @@
       <c r="C100"/>
       <c r="D100"/>
       <c r="E100">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>{"guid":"356907e0-1488-4128-bfcc-7ff73cfc3330","nodeType":0,"position":{"x":-911.3333740234375,"y":-2121.333251953125},"targetType":1,"skillId":1004,"assetTags":{"Tags":[]},"cancelAbilitiesWithTags":{"Tags":[]},"blockAbilitiesWithTags":{"Tags":[]},"activationOwnedTags":{"Tags":[{"Name":"Skill.Running","HashCode":-51601538,"ShortName":"Running","AncestorHashCodes":[1312877309],"AncestorNames":["Skill"]}]},"activationRequiredTags":{"Tags":[]},"activationBlockedTags":{"Tags":[{"Name":"CD.Wind","HashCode":1982736573,"ShortName":"Wind","AncestorHashCodes":[-1137859925],"AncestorNames":["CD"]},{"Name":"Skill.Running","HashCode":-51601538,"ShortName":"Running","AncestorHashCodes":[1312877309],"AncestorNames":["Skill"]}]},"ongoingBlockedTags":{"Tags":[]},"eventOutputPorts":[]}</t>
+          <t>{"guid":"d8847c3e-459e-4589-a96b-37ebb5ec458b","nodeType":21,"position":{"x":-572.0,"y":-1804.0},"targetType":1,"assetTags":{"Tags":[]},"grantedTags":{"Tags":[]},"applicationRequiredTags":{"Tags":[]},"applicationImmunityTags":{"Tags":[]},"removeGameEffectsWithTags":{"Tags":[]},"durationType":2,"duration":"0","isPeriodic":true,"period":"0.3","executeOnApplication":false,"attributeModifiers":[],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"Tags":[]},"cancelOnAbilityEnd":true}</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>{"outputNodeGuid":"a32d1135-94db-4f81-95ba-9d5f105ef8d0","outputPortId":3004,"inputNodeGuid":"764289ea-065e-4f48-afc0-0f6963d18d57","inputPortId":7001}</t>
+          <t>{"outputNodeGuid":"e33ab94c-1496-4d6a-ba5e-1afd38bb0c30","outputPortId":4001,"inputNodeGuid":"a32d1135-94db-4f81-95ba-9d5f105ef8d0","inputPortId":7001}</t>
         </is>
       </c>
       <c r="H100"/>
@@ -2623,16 +2627,16 @@
       <c r="C101"/>
       <c r="D101"/>
       <c r="E101">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>{"guid":"f73ba91e-a76b-456c-b19c-a5176809d5f5","nodeType":7,"position":{"x":522.0,"y":-1858.666748046875},"targetType":1,"endType":0}</t>
+          <t>{"guid":"356907e0-1488-4128-bfcc-7ff73cfc3330","nodeType":0,"position":{"x":-911.3333740234375,"y":-2121.333251953125},"targetType":1,"skillId":1004,"assetTags":{"Tags":[]},"cancelAbilitiesWithTags":{"Tags":[]},"blockAbilitiesWithTags":{"Tags":[]},"activationOwnedTags":{"Tags":[{"Name":"Skill.Running","HashCode":-51601538,"ShortName":"Running","AncestorHashCodes":[1312877309],"AncestorNames":["Skill"]}]},"activationRequiredTags":{"Tags":[]},"activationBlockedTags":{"Tags":[{"Name":"CD.Wind","HashCode":1982736573,"ShortName":"Wind","AncestorHashCodes":[-1137859925],"AncestorNames":["CD"]},{"Name":"Skill.Running","HashCode":-51601538,"ShortName":"Running","AncestorHashCodes":[1312877309],"AncestorNames":["Skill"]}]},"ongoingBlockedTags":{"Tags":[]},"eventOutputPorts":[]}</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>{"outputNodeGuid":"432ff1e3-b18d-476d-af80-d39ddc07402a","outputPortId":2287012,"inputNodeGuid":"cde57fb8-b693-4da8-a4a8-fd61e56c5dcd","inputPortId":7001}</t>
+          <t>{"outputNodeGuid":"a32d1135-94db-4f81-95ba-9d5f105ef8d0","outputPortId":3004,"inputNodeGuid":"764289ea-065e-4f48-afc0-0f6963d18d57","inputPortId":7001}</t>
         </is>
       </c>
       <c r="H101"/>
@@ -2643,16 +2647,16 @@
       <c r="C102"/>
       <c r="D102"/>
       <c r="E102">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>{"guid":"cde57fb8-b693-4da8-a4a8-fd61e56c5dcd","nodeType":12,"position":{"x":522.0,"y":-2026.666748046875},"targetType":1,"requiredTags":{"Tags":[]},"immunityTags":{"Tags":[]},"destroyWithNode":true,"positionSource":0,"particleEntityId":50008,"particlePrefab":null,"particlePrefabPath":"Assets/Res/Entity/Effect/ef_zhanshi_xfz_01.prefab","particleBindingName":"down","particleOffset":{"x":0.0,"y":0.0,"z":0.0},"particleScale":{"x":1.0,"y":1.0,"z":1.0},"attachToTarget":true,"particleLoop":true}</t>
+          <t>{"guid":"f73ba91e-a76b-456c-b19c-a5176809d5f5","nodeType":7,"position":{"x":522.0,"y":-1858.666748046875},"targetType":1,"endType":0}</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>{"outputNodeGuid":"432ff1e3-b18d-476d-af80-d39ddc07402a","outputPortId":2000539,"inputNodeGuid":"f73ba91e-a76b-456c-b19c-a5176809d5f5","inputPortId":7001}</t>
+          <t>{"outputNodeGuid":"432ff1e3-b18d-476d-af80-d39ddc07402a","outputPortId":2287012,"inputNodeGuid":"cde57fb8-b693-4da8-a4a8-fd61e56c5dcd","inputPortId":7001}</t>
         </is>
       </c>
       <c r="H102"/>
@@ -2663,15 +2667,35 @@
       <c r="C103"/>
       <c r="D103"/>
       <c r="E103">
+        <v>12</v>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>{"guid":"cde57fb8-b693-4da8-a4a8-fd61e56c5dcd","nodeType":12,"position":{"x":522.0,"y":-2026.666748046875},"targetType":1,"requiredTags":{"Tags":[]},"immunityTags":{"Tags":[]},"destroyWithNode":true,"positionSource":0,"particleEntityId":50008,"particlePrefab":null,"particlePrefabPath":"Assets/Res/Entity/Effect/ef_zhanshi_xfz_01.prefab","particleBindingName":"down","particleOffset":{"x":0.0,"y":0.0,"z":0.0},"particleScale":{"x":1.0,"y":1.0,"z":1.0},"attachToTarget":true,"particleLoop":true}</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>{"outputNodeGuid":"432ff1e3-b18d-476d-af80-d39ddc07402a","outputPortId":2000539,"inputNodeGuid":"f73ba91e-a76b-456c-b19c-a5176809d5f5","inputPortId":7001}</t>
+        </is>
+      </c>
+      <c r="H103"/>
+    </row>
+    <row r="104">
+      <c r="A104"/>
+      <c r="B104"/>
+      <c r="C104"/>
+      <c r="D104"/>
+      <c r="E104">
         <v>20</v>
       </c>
-      <c r="F103" t="inlineStr">
+      <c r="F104" t="inlineStr">
         <is>
           <t>{"guid":"432ff1e3-b18d-476d-af80-d39ddc07402a","nodeType":20,"position":{"x":-434.0,"y":-2553.333251953125},"targetType":1,"skeletonDataAsset":null,"skeletonDataAssetPath":"Assets/Res/Spine/SP_Zhanshi/SP_Zhanshi_SkeletonData.asset","animationName":"Skill_attack_1011","animationDuration":"12","isAnimationLooping":true,"timeEffects":[{"triggerTime":250,"portIdValue":2000539,"legacyPortId":"f41c85e0-7f26-494e-9ffc-4a06c980f811"}],"timeCues":[{"startTime":0,"endTime":255,"portIdValue":2287012,"legacyPortId":"8dea1941-c520-4f9a-aee0-40932c8542ef"}]}</t>
         </is>
       </c>
-      <c r="G103"/>
-      <c r="H103"/>
+      <c r="G104"/>
+      <c r="H104"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:G12"/>

--- a/Design/Excel/ET/Datas/Game/SkillGraph.xlsx
+++ b/Design/Excel/ET/Datas/Game/SkillGraph.xlsx
@@ -1011,11 +1011,11 @@
       <c r="C21"/>
       <c r="D21"/>
       <c r="E21">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>{"guid":"3aafa9a5-4766-4204-91ab-d797aeb3c0e1","nodeType":7,"position":{"x":301.33334350585938,"y":-1866.666748046875},"targetType":1,"endType":0}</t>
+          <t>{"guid":"2d7e41c4-8e90-4b61-879c-4b2e5b9486db","nodeType":14,"position":{"x":1200.0,"y":-2044.666748046875},"targetType":1,"requiredTags":{"Tags":[]},"immunityTags":{"Tags":[]},"destroyWithNode":false,"positionSource":2,"positionBindingName":"head","textType":0,"fixedText":"","contextDataKey":"DamageResult","textColor":{"r":1.0,"g":0.16293229162693024,"b":0.0,"a":1.0},"criticalColor":{"r":1.0,"g":0.5,"b":0.0,"a":1.0},"missColor":{"r":0.5,"g":0.5,"b":0.5,"a":1.0},"fontSize":5.0,"criticalFontSize":60.0,"duration":1.5,"offset":{"x":0.0,"y":0.0},"moveDirection":{"x":0.0,"y":1.0}}</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -1031,11 +1031,11 @@
       <c r="C22"/>
       <c r="D22"/>
       <c r="E22">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>{"guid":"93b489d8-3d60-4ded-9f04-789fe2990ece","nodeType":4,"position":{"x":492.66665649414063,"y":-1903.3333740234375},"targetType":1,"searchShapeType":3,"searchLineType":0,"positionSource":1,"positionBindingName":"","searchCircleRadius":5.0,"searchSectorRadius":5.0,"searchSectorAngle":90.0,"searchLineDirectionOffsetAngle":0.0,"searchLineDirectionWidth":1.0,"searchLineDirectionLength":10.0,"lineStartPositionSource":0,"lineStartBindingName":"","lineEndPositionSource":1,"lineEndBindingName":"","searchLineBetweenWidth":1.0,"searchLineAbsoluteAngle":0.0,"searchLineAbsoluteWidth":1.0,"searchLineAbsoluteLength":10.0,"maxTargets":1,"searchTargetTags":{"Tags":[{"Name":"unitType.monster","HashCode":-2021655864,"ShortName":"monster","AncestorHashCodes":[1600484460],"AncestorNames":["unitType"]}]},"searchExcludeTags":{"Tags":[]}}</t>
+          <t>{"guid":"356907e0-1488-4128-bfcc-7ff73cfc3330","nodeType":0,"position":{"x":-1013.3333740234375,"y":-2446.66650390625},"targetType":1,"skillId":7001,"assetTags":{"Tags":[]},"cancelAbilitiesWithTags":{"Tags":[]},"blockAbilitiesWithTags":{"Tags":[]},"activationOwnedTags":{"Tags":[]},"activationRequiredTags":{"Tags":[]},"activationBlockedTags":{"Tags":[{"Name":"CD.FireCircle","HashCode":522143731,"ShortName":"FireCircle","AncestorHashCodes":[-1137859925],"AncestorNames":["CD"]}]},"ongoingBlockedTags":{"Tags":[{"Name":"Buff.DeBuff.Stun","HashCode":1791562953,"ShortName":"Stun","AncestorHashCodes":[937056111,321157895],"AncestorNames":["Buff","Buff.DeBuff"]}]},"eventOutputPorts":[]}</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -1051,11 +1051,11 @@
       <c r="C23"/>
       <c r="D23"/>
       <c r="E23">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>{"guid":"2d7e41c4-8e90-4b61-879c-4b2e5b9486db","nodeType":14,"position":{"x":1200.0,"y":-2044.666748046875},"targetType":1,"requiredTags":{"Tags":[]},"immunityTags":{"Tags":[]},"destroyWithNode":false,"positionSource":2,"positionBindingName":"head","textType":0,"fixedText":"","contextDataKey":"DamageResult","textColor":{"r":1.0,"g":0.16293229162693024,"b":0.0,"a":1.0},"criticalColor":{"r":1.0,"g":0.5,"b":0.0,"a":1.0},"missColor":{"r":0.5,"g":0.5,"b":0.5,"a":1.0},"fontSize":5.0,"criticalFontSize":60.0,"duration":1.5,"offset":{"x":0.0,"y":0.0},"moveDirection":{"x":0.0,"y":1.0}}</t>
+          <t>{"guid":"9d6f459d-b588-4b64-843b-1b71e8f299ae","nodeType":3,"position":{"x":-1317.333251953125,"y":-2446.66650390625},"targetType":1,"assetTags":{"Tags":[]},"grantedTags":{"Tags":[]},"applicationRequiredTags":{"Tags":[]},"applicationImmunityTags":{"Tags":[]},"removeGameEffectsWithTags":{"Tags":[]},"durationType":0,"duration":"0","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[{"attrType":1003,"operation":0,"magnitudeSourceType":0,"fixedValue":-100.0,"formula":"","mmcType":0,"setByCallerKey":"","mmcCaptureAttribute":200,"mmcAttributeSource":0,"mmcCoefficient":1.0,"mmcUseSnapshot":true}],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"Tags":[]},"cancelOnAbilityEnd":true}</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -1071,11 +1071,11 @@
       <c r="C24"/>
       <c r="D24"/>
       <c r="E24">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>{"guid":"356907e0-1488-4128-bfcc-7ff73cfc3330","nodeType":0,"position":{"x":-1100.0,"y":-2288.66650390625},"targetType":1,"skillId":7001,"assetTags":{"Tags":[]},"cancelAbilitiesWithTags":{"Tags":[]},"blockAbilitiesWithTags":{"Tags":[]},"activationOwnedTags":{"Tags":[]},"activationRequiredTags":{"Tags":[]},"activationBlockedTags":{"Tags":[{"Name":"CD.FireCircle","HashCode":522143731,"ShortName":"FireCircle","AncestorHashCodes":[-1137859925],"AncestorNames":["CD"]}]},"ongoingBlockedTags":{"Tags":[{"Name":"Buff.DeBuff.Stun","HashCode":1791562953,"ShortName":"Stun","AncestorHashCodes":[937056111,321157895],"AncestorNames":["Buff","Buff.DeBuff"]}]},"eventOutputPorts":[]}</t>
+          <t>{"guid":"c28fb88d-51b1-47b2-be59-859e0ac638e3","nodeType":10,"position":{"x":-1257.3333740234375,"y":-2221.333251953125},"targetType":1,"assetTags":{"Tags":[]},"grantedTags":{"Tags":[{"Name":"CD.FireCircle","HashCode":522143731,"ShortName":"FireCircle","AncestorHashCodes":[-1137859925],"AncestorNames":["CD"]}]},"applicationRequiredTags":{"Tags":[]},"applicationImmunityTags":{"Tags":[]},"removeGameEffectsWithTags":{"Tags":[]},"durationType":1,"duration":"3","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"Tags":[]},"cancelOnAbilityEnd":false,"cooldownType":0,"maxCharges":2,"chargeTime":"10"}</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -1091,11 +1091,11 @@
       <c r="C25"/>
       <c r="D25"/>
       <c r="E25">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>{"guid":"9d6f459d-b588-4b64-843b-1b71e8f299ae","nodeType":3,"position":{"x":-1423.333251953125,"y":-2391.333251953125},"targetType":1,"assetTags":{"Tags":[]},"grantedTags":{"Tags":[]},"applicationRequiredTags":{"Tags":[]},"applicationImmunityTags":{"Tags":[]},"removeGameEffectsWithTags":{"Tags":[]},"durationType":0,"duration":"0","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[{"attrType":1003,"operation":0,"magnitudeSourceType":0,"fixedValue":-100.0,"formula":"","mmcType":0,"setByCallerKey":"","mmcCaptureAttribute":200,"mmcAttributeSource":0,"mmcCoefficient":1.0,"mmcUseSnapshot":true}],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"Tags":[]},"cancelOnAbilityEnd":true}</t>
+          <t>{"guid":"3aafa9a5-4766-4204-91ab-d797aeb3c0e1","nodeType":7,"position":{"x":322.66665649414063,"y":-1817.3333740234375},"targetType":1,"endType":0}</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -1111,11 +1111,11 @@
       <c r="C26"/>
       <c r="D26"/>
       <c r="E26">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>{"guid":"c28fb88d-51b1-47b2-be59-859e0ac638e3","nodeType":10,"position":{"x":-1363.333251953125,"y":-2166.0},"targetType":1,"assetTags":{"Tags":[]},"grantedTags":{"Tags":[{"Name":"CD.FireCircle","HashCode":522143731,"ShortName":"FireCircle","AncestorHashCodes":[-1137859925],"AncestorNames":["CD"]}]},"applicationRequiredTags":{"Tags":[]},"applicationImmunityTags":{"Tags":[]},"removeGameEffectsWithTags":{"Tags":[]},"durationType":1,"duration":"3","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"Tags":[]},"cancelOnAbilityEnd":false,"cooldownType":0,"maxCharges":2,"chargeTime":"10"}</t>
+          <t>{"guid":"93b489d8-3d60-4ded-9f04-789fe2990ece","nodeType":4,"position":{"x":510.66665649414063,"y":-1895.3333740234375},"targetType":1,"searchShapeType":3,"searchLineType":0,"positionSource":1,"positionBindingName":"","searchCircleRadius":5.0,"searchSectorRadius":5.0,"searchSectorAngle":90.0,"searchLineDirectionOffsetAngle":0.0,"searchLineDirectionWidth":1.0,"searchLineDirectionLength":10.0,"lineStartPositionSource":0,"lineStartBindingName":"","lineEndPositionSource":1,"lineEndBindingName":"","searchLineBetweenWidth":1.0,"searchLineAbsoluteAngle":0.0,"searchLineAbsoluteWidth":1.0,"searchLineAbsoluteLength":10.0,"maxTargets":1,"searchTargetTags":{"Tags":[{"Name":"unitType.monster","HashCode":-2021655864,"ShortName":"monster","AncestorHashCodes":[1600484460],"AncestorNames":["unitType"]}]},"searchExcludeTags":{"Tags":[]}}</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -1140,7 +1140,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>{"outputNodeGuid":"90bacd9f-d882-4bba-aaa8-41ed993ac3ff","outputPortId":5002,"inputNodeGuid":"eae41233-d297-46fe-a6c8-0b5c876fbb2a","inputPortId":7001}</t>
+          <t>{"outputNodeGuid":"90bacd9f-d882-4bba-aaa8-41ed993ac3ff","outputPortId":5001,"inputNodeGuid":"eae41233-d297-46fe-a6c8-0b5c876fbb2a","inputPortId":7001}</t>
         </is>
       </c>
       <c r="H27"/>
@@ -1155,7 +1155,7 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>{"guid":"90bacd9f-d882-4bba-aaa8-41ed993ac3ff","nodeType":8,"position":{"x":602.6666259765625,"y":-2102.666748046875},"targetType":1,"assetTags":{"Tags":[]},"grantedTags":{"Tags":[]},"applicationRequiredTags":{"Tags":[]},"applicationImmunityTags":{"Tags":[]},"removeGameEffectsWithTags":{"Tags":[]},"durationType":2,"duration":"0","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"Tags":[]},"cancelOnAbilityEnd":false,"launchPositionSource":0,"launchBindingName":"center","targetPositionSource":2,"targetBindingName":"center","projectileTargetType":1,"flyOver":false,"offsetAngle":0.0,"curveHeight":0.0,"projectileEntityId":50001,"projectilePrefab":null,"projectilePrefabPath":"Assets/Res/Entity/Effect/ef_fashi_gandian_buff.prefab","speed":3.0,"maxDistance":10.0,"collisionRadius":0.10000000149011612,"isPiercing":false,"maxPierceCount":1,"collisionTargetTags":{"Tags":[{"Name":"unitType.monster","HashCode":-2021655864,"ShortName":"monster","AncestorHashCodes":[1600484460],"AncestorNames":["unitType"]}]},"collisionExcludeTags":{"Tags":[]},"isBouncing":false,"bounceTargetMode":0,"maxBounceCount":3,"bounceSearchRadius":10.0,"canBounceToSameTarget":false,"excludeSourceCamp":true,"bounceAngleOffset":0.0}</t>
+          <t>{"guid":"90bacd9f-d882-4bba-aaa8-41ed993ac3ff","nodeType":8,"position":{"x":620.6666259765625,"y":-2102.666748046875},"targetType":1,"assetTags":{"Tags":[]},"grantedTags":{"Tags":[]},"applicationRequiredTags":{"Tags":[]},"applicationImmunityTags":{"Tags":[]},"removeGameEffectsWithTags":{"Tags":[]},"durationType":2,"duration":"0","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"Tags":[]},"cancelOnAbilityEnd":false,"launchPositionSource":0,"launchBindingName":"center","targetPositionSource":2,"targetBindingName":"center","projectileTargetType":1,"flyOver":false,"offsetAngle":0.0,"curveHeight":0.0,"projectileEntityId":50001,"projectilePrefab":null,"projectilePrefabPath":"Assets/Res/Entity/Effect/ef_fashi_gandian_buff.prefab","speed":3.0,"maxDistance":10.0,"collisionRadius":0.10000000149011612,"isPiercing":false,"maxPierceCount":1,"collisionTargetTags":{"Tags":[{"Name":"unitType.monster","HashCode":-2021655864,"ShortName":"monster","AncestorHashCodes":[1600484460],"AncestorNames":["unitType"]}]},"collisionExcludeTags":{"Tags":[]},"isBouncing":false,"bounceTargetMode":0,"maxBounceCount":3,"bounceSearchRadius":10.0,"canBounceToSameTarget":false,"excludeSourceCamp":true,"bounceAngleOffset":0.0}</t>
         </is>
       </c>
       <c r="G28"/>

--- a/Design/Excel/ET/Datas/Game/SkillGraph.xlsx
+++ b/Design/Excel/ET/Datas/Game/SkillGraph.xlsx
@@ -1111,11 +1111,11 @@
       <c r="C26"/>
       <c r="D26"/>
       <c r="E26">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>{"guid":"93b489d8-3d60-4ded-9f04-789fe2990ece","nodeType":4,"position":{"x":510.66665649414063,"y":-1895.3333740234375},"targetType":1,"searchShapeType":3,"searchLineType":0,"positionSource":1,"positionBindingName":"","searchCircleRadius":5.0,"searchSectorRadius":5.0,"searchSectorAngle":90.0,"searchLineDirectionOffsetAngle":0.0,"searchLineDirectionWidth":1.0,"searchLineDirectionLength":10.0,"lineStartPositionSource":0,"lineStartBindingName":"","lineEndPositionSource":1,"lineEndBindingName":"","searchLineBetweenWidth":1.0,"searchLineAbsoluteAngle":0.0,"searchLineAbsoluteWidth":1.0,"searchLineAbsoluteLength":10.0,"maxTargets":1,"searchTargetTags":{"Tags":[{"Name":"unitType.monster","HashCode":-2021655864,"ShortName":"monster","AncestorHashCodes":[1600484460],"AncestorNames":["unitType"]}]},"searchExcludeTags":{"Tags":[]}}</t>
+          <t>{"guid":"eae41233-d297-46fe-a6c8-0b5c876fbb2a","nodeType":1,"position":{"x":942.0,"y":-2072.666748046875},"targetType":0,"assetTags":{"Tags":[]},"grantedTags":{"Tags":[]},"applicationRequiredTags":{"Tags":[]},"applicationImmunityTags":{"Tags":[]},"removeGameEffectsWithTags":{"Tags":[]},"durationType":0,"duration":"0","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"Tags":[]},"cancelOnAbilityEnd":true,"damageType":1,"damageSourceType":0,"damageFixedValue":10.0,"damageFormula":"","damageMMCType":0,"damageSetByCallerKey":"","damageMMCCaptureAttribute":200,"damageMMCAttributeSource":0,"damageMMCCoefficient":1.0,"damageMMCUseSnapshot":true,"damageMultiplyByStackCount":false,"damageCalculationType":0,"enableHitKnockback":false,"knockbackDistance":1.0,"knockbackSpeed":12.0}</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -1131,11 +1131,11 @@
       <c r="C27"/>
       <c r="D27"/>
       <c r="E27">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>{"guid":"eae41233-d297-46fe-a6c8-0b5c876fbb2a","nodeType":1,"position":{"x":942.0,"y":-2072.666748046875},"targetType":0,"assetTags":{"Tags":[]},"grantedTags":{"Tags":[]},"applicationRequiredTags":{"Tags":[]},"applicationImmunityTags":{"Tags":[]},"removeGameEffectsWithTags":{"Tags":[]},"durationType":0,"duration":"0","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"Tags":[]},"cancelOnAbilityEnd":true,"damageType":1,"damageSourceType":0,"damageFixedValue":10.0,"damageFormula":"","damageMMCType":0,"damageSetByCallerKey":"","damageMMCCaptureAttribute":200,"damageMMCAttributeSource":0,"damageMMCCoefficient":1.0,"damageMMCUseSnapshot":true,"damageMultiplyByStackCount":false,"damageCalculationType":0,"enableHitKnockback":false,"knockbackDistance":1.0,"knockbackSpeed":12.0}</t>
+          <t>{"guid":"93b489d8-3d60-4ded-9f04-789fe2990ece","nodeType":4,"position":{"x":510.66665649414063,"y":-1895.3333740234375},"targetType":1,"searchShapeType":3,"searchLineType":0,"positionSource":1,"positionBindingName":"","searchCircleRadius":5.0,"searchSectorRadius":5.0,"searchSectorAngle":90.0,"searchLineDirectionOffsetAngle":0.0,"searchLineDirectionWidth":1.0,"searchLineDirectionLength":10.0,"lineStartPositionSource":0,"lineStartBindingName":"","lineEndPositionSource":1,"lineEndBindingName":"","searchLineBetweenWidth":1.0,"searchLineAbsoluteAngle":0.0,"searchLineAbsoluteWidth":1.0,"searchLineAbsoluteLength":10.0,"maxTargets":1,"searchTargetTags":{"Tags":[{"Name":"campType.EnemyCamp","HashCode":713889996,"ShortName":"EnemyCamp","AncestorHashCodes":[-312381257],"AncestorNames":["campType"]}]},"searchExcludeTags":{"Tags":[]}}</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -1155,7 +1155,7 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>{"guid":"90bacd9f-d882-4bba-aaa8-41ed993ac3ff","nodeType":8,"position":{"x":620.6666259765625,"y":-2102.666748046875},"targetType":1,"assetTags":{"Tags":[]},"grantedTags":{"Tags":[]},"applicationRequiredTags":{"Tags":[]},"applicationImmunityTags":{"Tags":[]},"removeGameEffectsWithTags":{"Tags":[]},"durationType":2,"duration":"0","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"Tags":[]},"cancelOnAbilityEnd":false,"launchPositionSource":0,"launchBindingName":"center","targetPositionSource":2,"targetBindingName":"center","projectileTargetType":1,"flyOver":false,"offsetAngle":0.0,"curveHeight":0.0,"projectileEntityId":50001,"projectilePrefab":null,"projectilePrefabPath":"Assets/Res/Entity/Effect/ef_fashi_gandian_buff.prefab","speed":3.0,"maxDistance":10.0,"collisionRadius":0.10000000149011612,"isPiercing":false,"maxPierceCount":1,"collisionTargetTags":{"Tags":[{"Name":"unitType.monster","HashCode":-2021655864,"ShortName":"monster","AncestorHashCodes":[1600484460],"AncestorNames":["unitType"]}]},"collisionExcludeTags":{"Tags":[]},"isBouncing":false,"bounceTargetMode":0,"maxBounceCount":3,"bounceSearchRadius":10.0,"canBounceToSameTarget":false,"excludeSourceCamp":true,"bounceAngleOffset":0.0}</t>
+          <t>{"guid":"90bacd9f-d882-4bba-aaa8-41ed993ac3ff","nodeType":8,"position":{"x":620.6666259765625,"y":-2102.666748046875},"targetType":1,"assetTags":{"Tags":[]},"grantedTags":{"Tags":[]},"applicationRequiredTags":{"Tags":[]},"applicationImmunityTags":{"Tags":[]},"removeGameEffectsWithTags":{"Tags":[]},"durationType":2,"duration":"0","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"Tags":[]},"cancelOnAbilityEnd":false,"launchPositionSource":0,"launchBindingName":"center","targetPositionSource":2,"targetBindingName":"center","projectileTargetType":1,"flyOver":false,"offsetAngle":0.0,"curveHeight":0.0,"projectileEntityId":50001,"projectilePrefab":null,"projectilePrefabPath":"Assets/Res/Entity/Effect/ef_fashi_gandian_buff.prefab","speed":3.0,"maxDistance":10.0,"collisionRadius":0.10000000149011612,"isPiercing":false,"maxPierceCount":1,"collisionTargetTags":{"Tags":[{"Name":"campType.EnemyCamp","HashCode":713889996,"ShortName":"EnemyCamp","AncestorHashCodes":[-312381257],"AncestorNames":["campType"]}]},"collisionExcludeTags":{"Tags":[]},"isBouncing":false,"bounceTargetMode":0,"maxBounceCount":3,"bounceSearchRadius":10.0,"canBounceToSameTarget":false,"excludeSourceCamp":true,"bounceAngleOffset":0.0}</t>
         </is>
       </c>
       <c r="G28"/>
@@ -2063,11 +2063,11 @@
       <c r="C73"/>
       <c r="D73"/>
       <c r="E73">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>{"guid":"e33ab94c-1496-4d6a-ba5e-1afd38bb0c30","nodeType":4,"position":{"x":731.3333740234375,"y":-2344.0},"targetType":1,"searchShapeType":3,"searchLineType":0,"positionSource":0,"positionBindingName":"center","searchCircleRadius":1.0,"searchSectorRadius":5.0,"searchSectorAngle":180.0,"searchLineDirectionOffsetAngle":0.0,"searchLineDirectionWidth":1.0,"searchLineDirectionLength":10.0,"lineStartPositionSource":0,"lineStartBindingName":"","lineEndPositionSource":1,"lineEndBindingName":"","searchLineBetweenWidth":1.0,"searchLineAbsoluteAngle":0.0,"searchLineAbsoluteWidth":1.0,"searchLineAbsoluteLength":10.0,"maxTargets":1,"searchTargetTags":{"Tags":[{"Name":"unitType.monster","HashCode":-2021655864,"ShortName":"monster","AncestorHashCodes":[1600484460],"AncestorNames":["unitType"]}]},"searchExcludeTags":{"Tags":[]}}</t>
+          <t>{"guid":"9d6f459d-b588-4b64-843b-1b71e8f299ae","nodeType":3,"position":{"x":-843.3333740234375,"y":-2772.0},"targetType":1,"assetTags":{"Tags":[]},"grantedTags":{"Tags":[]},"applicationRequiredTags":{"Tags":[]},"applicationImmunityTags":{"Tags":[]},"removeGameEffectsWithTags":{"Tags":[]},"durationType":0,"duration":"0","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[{"attrType":1003,"operation":0,"magnitudeSourceType":0,"fixedValue":-10.0,"formula":"","mmcType":0,"setByCallerKey":"","mmcCaptureAttribute":200,"mmcAttributeSource":0,"mmcCoefficient":1.0,"mmcUseSnapshot":true}],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"Tags":[]},"cancelOnAbilityEnd":true}</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
@@ -2083,11 +2083,11 @@
       <c r="C74"/>
       <c r="D74"/>
       <c r="E74">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>{"guid":"9d6f459d-b588-4b64-843b-1b71e8f299ae","nodeType":3,"position":{"x":-843.3333740234375,"y":-2772.0},"targetType":1,"assetTags":{"Tags":[]},"grantedTags":{"Tags":[]},"applicationRequiredTags":{"Tags":[]},"applicationImmunityTags":{"Tags":[]},"removeGameEffectsWithTags":{"Tags":[]},"durationType":0,"duration":"0","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[{"attrType":1003,"operation":0,"magnitudeSourceType":0,"fixedValue":-10.0,"formula":"","mmcType":0,"setByCallerKey":"","mmcCaptureAttribute":200,"mmcAttributeSource":0,"mmcCoefficient":1.0,"mmcUseSnapshot":true}],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"Tags":[]},"cancelOnAbilityEnd":true}</t>
+          <t>{"guid":"c353e286-8ef0-460a-b917-887f2aeb390a","nodeType":14,"position":{"x":1224.666748046875,"y":-2347.333251953125},"targetType":1,"requiredTags":{"Tags":[]},"immunityTags":{"Tags":[]},"destroyWithNode":false,"positionSource":2,"positionBindingName":"head","textType":0,"fixedText":"","contextDataKey":"DamageResult","textColor":{"r":1.0,"g":0.0,"b":0.0,"a":1.0},"criticalColor":{"r":1.0,"g":0.5,"b":0.0,"a":1.0},"missColor":{"r":0.5,"g":0.5,"b":0.5,"a":1.0},"fontSize":5.0,"criticalFontSize":60.0,"duration":1.5,"offset":{"x":0.0,"y":0.0},"moveDirection":{"x":0.0,"y":1.0}}</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
@@ -2103,11 +2103,11 @@
       <c r="C75"/>
       <c r="D75"/>
       <c r="E75">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>{"guid":"c353e286-8ef0-460a-b917-887f2aeb390a","nodeType":14,"position":{"x":1224.666748046875,"y":-2347.333251953125},"targetType":1,"requiredTags":{"Tags":[]},"immunityTags":{"Tags":[]},"destroyWithNode":false,"positionSource":2,"positionBindingName":"head","textType":0,"fixedText":"","contextDataKey":"DamageResult","textColor":{"r":1.0,"g":0.0,"b":0.0,"a":1.0},"criticalColor":{"r":1.0,"g":0.5,"b":0.0,"a":1.0},"missColor":{"r":0.5,"g":0.5,"b":0.5,"a":1.0},"fontSize":5.0,"criticalFontSize":60.0,"duration":1.5,"offset":{"x":0.0,"y":0.0},"moveDirection":{"x":0.0,"y":1.0}}</t>
+          <t>{"guid":"e33ab94c-1496-4d6a-ba5e-1afd38bb0c30","nodeType":4,"position":{"x":731.3333740234375,"y":-2344.0},"targetType":1,"searchShapeType":3,"searchLineType":0,"positionSource":0,"positionBindingName":"center","searchCircleRadius":1.0,"searchSectorRadius":5.0,"searchSectorAngle":180.0,"searchLineDirectionOffsetAngle":0.0,"searchLineDirectionWidth":1.0,"searchLineDirectionLength":10.0,"lineStartPositionSource":0,"lineStartBindingName":"","lineEndPositionSource":1,"lineEndBindingName":"","searchLineBetweenWidth":1.0,"searchLineAbsoluteAngle":0.0,"searchLineAbsoluteWidth":1.0,"searchLineAbsoluteLength":10.0,"maxTargets":1,"searchTargetTags":{"Tags":[{"Name":"campType.EnemyCamp","HashCode":713889996,"ShortName":"EnemyCamp","AncestorHashCodes":[-312381257],"AncestorNames":["campType"]}]},"searchExcludeTags":{"Tags":[]}}</t>
         </is>
       </c>
       <c r="G75"/>

--- a/Design/Excel/ET/Datas/Game/SkillGraph.xlsx
+++ b/Design/Excel/ET/Datas/Game/SkillGraph.xlsx
@@ -1051,11 +1051,11 @@
       <c r="C23"/>
       <c r="D23"/>
       <c r="E23">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>{"guid":"9d6f459d-b588-4b64-843b-1b71e8f299ae","nodeType":3,"position":{"x":-1317.333251953125,"y":-2446.66650390625},"targetType":1,"assetTags":{"Tags":[]},"grantedTags":{"Tags":[]},"applicationRequiredTags":{"Tags":[]},"applicationImmunityTags":{"Tags":[]},"removeGameEffectsWithTags":{"Tags":[]},"durationType":0,"duration":"0","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[{"attrType":1003,"operation":0,"magnitudeSourceType":0,"fixedValue":-100.0,"formula":"","mmcType":0,"setByCallerKey":"","mmcCaptureAttribute":200,"mmcAttributeSource":0,"mmcCoefficient":1.0,"mmcUseSnapshot":true}],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"Tags":[]},"cancelOnAbilityEnd":true}</t>
+          <t>{"guid":"c28fb88d-51b1-47b2-be59-859e0ac638e3","nodeType":10,"position":{"x":-1257.3333740234375,"y":-2221.333251953125},"targetType":1,"assetTags":{"Tags":[]},"grantedTags":{"Tags":[{"Name":"CD.FireCircle","HashCode":522143731,"ShortName":"FireCircle","AncestorHashCodes":[-1137859925],"AncestorNames":["CD"]}]},"applicationRequiredTags":{"Tags":[]},"applicationImmunityTags":{"Tags":[]},"removeGameEffectsWithTags":{"Tags":[]},"durationType":1,"duration":"3","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"Tags":[]},"cancelOnAbilityEnd":false,"cooldownType":0,"maxCharges":2,"chargeTime":"10"}</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -1071,11 +1071,11 @@
       <c r="C24"/>
       <c r="D24"/>
       <c r="E24">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>{"guid":"c28fb88d-51b1-47b2-be59-859e0ac638e3","nodeType":10,"position":{"x":-1257.3333740234375,"y":-2221.333251953125},"targetType":1,"assetTags":{"Tags":[]},"grantedTags":{"Tags":[{"Name":"CD.FireCircle","HashCode":522143731,"ShortName":"FireCircle","AncestorHashCodes":[-1137859925],"AncestorNames":["CD"]}]},"applicationRequiredTags":{"Tags":[]},"applicationImmunityTags":{"Tags":[]},"removeGameEffectsWithTags":{"Tags":[]},"durationType":1,"duration":"3","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"Tags":[]},"cancelOnAbilityEnd":false,"cooldownType":0,"maxCharges":2,"chargeTime":"10"}</t>
+          <t>{"guid":"3aafa9a5-4766-4204-91ab-d797aeb3c0e1","nodeType":7,"position":{"x":322.66665649414063,"y":-1817.3333740234375},"targetType":1,"endType":0}</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -1091,11 +1091,11 @@
       <c r="C25"/>
       <c r="D25"/>
       <c r="E25">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>{"guid":"3aafa9a5-4766-4204-91ab-d797aeb3c0e1","nodeType":7,"position":{"x":322.66665649414063,"y":-1817.3333740234375},"targetType":1,"endType":0}</t>
+          <t>{"guid":"93b489d8-3d60-4ded-9f04-789fe2990ece","nodeType":4,"position":{"x":510.66665649414063,"y":-1895.3333740234375},"targetType":1,"searchShapeType":3,"searchLineType":0,"positionSource":1,"positionBindingName":"","searchCircleRadius":5.0,"searchSectorRadius":5.0,"searchSectorAngle":90.0,"searchLineDirectionOffsetAngle":0.0,"searchLineDirectionWidth":1.0,"searchLineDirectionLength":10.0,"lineStartPositionSource":0,"lineStartBindingName":"","lineEndPositionSource":1,"lineEndBindingName":"","searchLineBetweenWidth":1.0,"searchLineAbsoluteAngle":0.0,"searchLineAbsoluteWidth":1.0,"searchLineAbsoluteLength":10.0,"maxTargets":1,"searchTargetTags":{"Tags":[{"Name":"campType.EnemyCamp","HashCode":713889996,"ShortName":"EnemyCamp","AncestorHashCodes":[-312381257],"AncestorNames":["campType"]}]},"searchExcludeTags":{"Tags":[]}}</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -1111,11 +1111,11 @@
       <c r="C26"/>
       <c r="D26"/>
       <c r="E26">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>{"guid":"eae41233-d297-46fe-a6c8-0b5c876fbb2a","nodeType":1,"position":{"x":942.0,"y":-2072.666748046875},"targetType":0,"assetTags":{"Tags":[]},"grantedTags":{"Tags":[]},"applicationRequiredTags":{"Tags":[]},"applicationImmunityTags":{"Tags":[]},"removeGameEffectsWithTags":{"Tags":[]},"durationType":0,"duration":"0","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"Tags":[]},"cancelOnAbilityEnd":true,"damageType":1,"damageSourceType":0,"damageFixedValue":10.0,"damageFormula":"","damageMMCType":0,"damageSetByCallerKey":"","damageMMCCaptureAttribute":200,"damageMMCAttributeSource":0,"damageMMCCoefficient":1.0,"damageMMCUseSnapshot":true,"damageMultiplyByStackCount":false,"damageCalculationType":0,"enableHitKnockback":false,"knockbackDistance":1.0,"knockbackSpeed":12.0}</t>
+          <t>{"guid":"9d6f459d-b588-4b64-843b-1b71e8f299ae","nodeType":3,"position":{"x":-1316.0,"y":-2446.66650390625},"targetType":1,"assetTags":{"Tags":[]},"grantedTags":{"Tags":[]},"applicationRequiredTags":{"Tags":[]},"applicationImmunityTags":{"Tags":[]},"removeGameEffectsWithTags":{"Tags":[]},"durationType":0,"duration":"0","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[{"attrType":1003,"operation":0,"magnitudeSourceType":0,"fixedValue":-100.0,"formula":"","mmcType":0,"setByCallerKey":"","mmcCaptureAttribute":200,"mmcAttributeSource":0,"mmcCoefficient":1.0,"mmcUseSnapshot":true}],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"Tags":[]},"cancelOnAbilityEnd":true}</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -1131,11 +1131,11 @@
       <c r="C27"/>
       <c r="D27"/>
       <c r="E27">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>{"guid":"93b489d8-3d60-4ded-9f04-789fe2990ece","nodeType":4,"position":{"x":510.66665649414063,"y":-1895.3333740234375},"targetType":1,"searchShapeType":3,"searchLineType":0,"positionSource":1,"positionBindingName":"","searchCircleRadius":5.0,"searchSectorRadius":5.0,"searchSectorAngle":90.0,"searchLineDirectionOffsetAngle":0.0,"searchLineDirectionWidth":1.0,"searchLineDirectionLength":10.0,"lineStartPositionSource":0,"lineStartBindingName":"","lineEndPositionSource":1,"lineEndBindingName":"","searchLineBetweenWidth":1.0,"searchLineAbsoluteAngle":0.0,"searchLineAbsoluteWidth":1.0,"searchLineAbsoluteLength":10.0,"maxTargets":1,"searchTargetTags":{"Tags":[{"Name":"campType.EnemyCamp","HashCode":713889996,"ShortName":"EnemyCamp","AncestorHashCodes":[-312381257],"AncestorNames":["campType"]}]},"searchExcludeTags":{"Tags":[]}}</t>
+          <t>{"guid":"90bacd9f-d882-4bba-aaa8-41ed993ac3ff","nodeType":8,"position":{"x":620.6666259765625,"y":-2102.666748046875},"targetType":1,"assetTags":{"Tags":[]},"grantedTags":{"Tags":[]},"applicationRequiredTags":{"Tags":[]},"applicationImmunityTags":{"Tags":[]},"removeGameEffectsWithTags":{"Tags":[]},"durationType":2,"duration":"0","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"Tags":[]},"cancelOnAbilityEnd":false,"launchPositionSource":0,"launchBindingName":"center","targetPositionSource":2,"targetBindingName":"center","projectileTargetType":1,"flyOver":false,"offsetAngle":0.0,"curveHeight":0.0,"projectileEntityId":50001,"projectilePrefab":null,"projectilePrefabPath":"Assets/Res/Entity/Effect/ef_fashi_gandian_buff.prefab","speed":3.0,"maxDistance":10.0,"collisionRadius":0.10000000149011612,"isPiercing":false,"maxPierceCount":1,"collisionTargetTags":{"Tags":[{"Name":"campType.EnemyCamp","HashCode":713889996,"ShortName":"EnemyCamp","AncestorHashCodes":[-312381257],"AncestorNames":["campType"]}]},"collisionExcludeTags":{"Tags":[]},"isBouncing":false,"bounceTargetMode":0,"maxBounceCount":3,"bounceSearchRadius":10.0,"canBounceToSameTarget":false,"excludeSourceCamp":true,"bounceAngleOffset":0.0}</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -1151,11 +1151,11 @@
       <c r="C28"/>
       <c r="D28"/>
       <c r="E28">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>{"guid":"90bacd9f-d882-4bba-aaa8-41ed993ac3ff","nodeType":8,"position":{"x":620.6666259765625,"y":-2102.666748046875},"targetType":1,"assetTags":{"Tags":[]},"grantedTags":{"Tags":[]},"applicationRequiredTags":{"Tags":[]},"applicationImmunityTags":{"Tags":[]},"removeGameEffectsWithTags":{"Tags":[]},"durationType":2,"duration":"0","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"Tags":[]},"cancelOnAbilityEnd":false,"launchPositionSource":0,"launchBindingName":"center","targetPositionSource":2,"targetBindingName":"center","projectileTargetType":1,"flyOver":false,"offsetAngle":0.0,"curveHeight":0.0,"projectileEntityId":50001,"projectilePrefab":null,"projectilePrefabPath":"Assets/Res/Entity/Effect/ef_fashi_gandian_buff.prefab","speed":3.0,"maxDistance":10.0,"collisionRadius":0.10000000149011612,"isPiercing":false,"maxPierceCount":1,"collisionTargetTags":{"Tags":[{"Name":"campType.EnemyCamp","HashCode":713889996,"ShortName":"EnemyCamp","AncestorHashCodes":[-312381257],"AncestorNames":["campType"]}]},"collisionExcludeTags":{"Tags":[]},"isBouncing":false,"bounceTargetMode":0,"maxBounceCount":3,"bounceSearchRadius":10.0,"canBounceToSameTarget":false,"excludeSourceCamp":true,"bounceAngleOffset":0.0}</t>
+          <t>{"guid":"eae41233-d297-46fe-a6c8-0b5c876fbb2a","nodeType":1,"position":{"x":942.0,"y":-2072.666748046875},"targetType":0,"assetTags":{"Tags":[]},"grantedTags":{"Tags":[]},"applicationRequiredTags":{"Tags":[]},"applicationImmunityTags":{"Tags":[]},"removeGameEffectsWithTags":{"Tags":[]},"durationType":0,"duration":"0","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"Tags":[]},"cancelOnAbilityEnd":true,"damageType":1,"damageSourceType":3,"damageFixedValue":50.0,"damageFormula":"","damageMMCType":0,"damageSetByCallerKey":"AttackDamage","damageMMCCaptureAttribute":1006,"damageMMCAttributeSource":0,"damageMMCCoefficient":1.0,"damageMMCUseSnapshot":false,"damageMultiplyByStackCount":false,"damageCalculationType":0,"enableHitKnockback":false,"knockbackDistance":1.0,"knockbackSpeed":12.0}</t>
         </is>
       </c>
       <c r="G28"/>
@@ -2023,11 +2023,11 @@
       <c r="C71"/>
       <c r="D71"/>
       <c r="E71">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>{"guid":"f8947676-1084-4228-b991-1509cc7fe851","nodeType":1,"position":{"x":975.3333740234375,"y":-2344.0},"targetType":0,"assetTags":{"Tags":[]},"grantedTags":{"Tags":[]},"applicationRequiredTags":{"Tags":[]},"applicationImmunityTags":{"Tags":[]},"removeGameEffectsWithTags":{"Tags":[]},"durationType":0,"duration":"0","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"Tags":[]},"cancelOnAbilityEnd":true,"damageType":1,"damageSourceType":0,"damageFixedValue":10.0,"damageFormula":"","damageMMCType":0,"damageSetByCallerKey":"","damageMMCCaptureAttribute":1006,"damageMMCAttributeSource":0,"damageMMCCoefficient":1.0,"damageMMCUseSnapshot":true,"damageMultiplyByStackCount":false,"damageCalculationType":0,"enableHitKnockback":false,"knockbackDistance":1.0,"knockbackSpeed":12.0}</t>
+          <t>{"guid":"cde57fb8-b693-4da8-a4a8-fd61e56c5dcd","nodeType":12,"position":{"x":1005.3333740234375,"y":-2186.0},"targetType":1,"requiredTags":{"Tags":[]},"immunityTags":{"Tags":[]},"destroyWithNode":false,"positionSource":2,"particleEntityId":50006,"particlePrefab":null,"particlePrefabPath":"Assets/Res/Entity/Effect/ef_Zhanshi_attack_02.prefab","particleBindingName":"head","particleOffset":{"x":0.0,"y":0.0,"z":0.0},"particleScale":{"x":1.0,"y":1.0,"z":1.0},"attachToTarget":false,"particleLoop":false}</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
@@ -2043,11 +2043,11 @@
       <c r="C72"/>
       <c r="D72"/>
       <c r="E72">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>{"guid":"cde57fb8-b693-4da8-a4a8-fd61e56c5dcd","nodeType":12,"position":{"x":1005.3333740234375,"y":-2186.0},"targetType":1,"requiredTags":{"Tags":[]},"immunityTags":{"Tags":[]},"destroyWithNode":false,"positionSource":2,"particleEntityId":50006,"particlePrefab":null,"particlePrefabPath":"Assets/Res/Entity/Effect/ef_Zhanshi_attack_02.prefab","particleBindingName":"head","particleOffset":{"x":0.0,"y":0.0,"z":0.0},"particleScale":{"x":1.0,"y":1.0,"z":1.0},"attachToTarget":false,"particleLoop":false}</t>
+          <t>{"guid":"c353e286-8ef0-460a-b917-887f2aeb390a","nodeType":14,"position":{"x":1224.666748046875,"y":-2347.333251953125},"targetType":1,"requiredTags":{"Tags":[]},"immunityTags":{"Tags":[]},"destroyWithNode":false,"positionSource":2,"positionBindingName":"head","textType":0,"fixedText":"","contextDataKey":"DamageResult","textColor":{"r":1.0,"g":0.0,"b":0.0,"a":1.0},"criticalColor":{"r":1.0,"g":0.5,"b":0.0,"a":1.0},"missColor":{"r":0.5,"g":0.5,"b":0.5,"a":1.0},"fontSize":5.0,"criticalFontSize":60.0,"duration":1.5,"offset":{"x":0.0,"y":0.0},"moveDirection":{"x":0.0,"y":1.0}}</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
@@ -2063,11 +2063,11 @@
       <c r="C73"/>
       <c r="D73"/>
       <c r="E73">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>{"guid":"9d6f459d-b588-4b64-843b-1b71e8f299ae","nodeType":3,"position":{"x":-843.3333740234375,"y":-2772.0},"targetType":1,"assetTags":{"Tags":[]},"grantedTags":{"Tags":[]},"applicationRequiredTags":{"Tags":[]},"applicationImmunityTags":{"Tags":[]},"removeGameEffectsWithTags":{"Tags":[]},"durationType":0,"duration":"0","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[{"attrType":1003,"operation":0,"magnitudeSourceType":0,"fixedValue":-10.0,"formula":"","mmcType":0,"setByCallerKey":"","mmcCaptureAttribute":200,"mmcAttributeSource":0,"mmcCoefficient":1.0,"mmcUseSnapshot":true}],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"Tags":[]},"cancelOnAbilityEnd":true}</t>
+          <t>{"guid":"e33ab94c-1496-4d6a-ba5e-1afd38bb0c30","nodeType":4,"position":{"x":731.3333740234375,"y":-2344.0},"targetType":1,"searchShapeType":3,"searchLineType":0,"positionSource":0,"positionBindingName":"center","searchCircleRadius":1.0,"searchSectorRadius":5.0,"searchSectorAngle":180.0,"searchLineDirectionOffsetAngle":0.0,"searchLineDirectionWidth":1.0,"searchLineDirectionLength":10.0,"lineStartPositionSource":0,"lineStartBindingName":"","lineEndPositionSource":1,"lineEndBindingName":"","searchLineBetweenWidth":1.0,"searchLineAbsoluteAngle":0.0,"searchLineAbsoluteWidth":1.0,"searchLineAbsoluteLength":10.0,"maxTargets":1,"searchTargetTags":{"Tags":[{"Name":"campType.EnemyCamp","HashCode":713889996,"ShortName":"EnemyCamp","AncestorHashCodes":[-312381257],"AncestorNames":["campType"]}]},"searchExcludeTags":{"Tags":[]}}</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
@@ -2083,11 +2083,11 @@
       <c r="C74"/>
       <c r="D74"/>
       <c r="E74">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>{"guid":"c353e286-8ef0-460a-b917-887f2aeb390a","nodeType":14,"position":{"x":1224.666748046875,"y":-2347.333251953125},"targetType":1,"requiredTags":{"Tags":[]},"immunityTags":{"Tags":[]},"destroyWithNode":false,"positionSource":2,"positionBindingName":"head","textType":0,"fixedText":"","contextDataKey":"DamageResult","textColor":{"r":1.0,"g":0.0,"b":0.0,"a":1.0},"criticalColor":{"r":1.0,"g":0.5,"b":0.0,"a":1.0},"missColor":{"r":0.5,"g":0.5,"b":0.5,"a":1.0},"fontSize":5.0,"criticalFontSize":60.0,"duration":1.5,"offset":{"x":0.0,"y":0.0},"moveDirection":{"x":0.0,"y":1.0}}</t>
+          <t>{"guid":"9d6f459d-b588-4b64-843b-1b71e8f299ae","nodeType":3,"position":{"x":-843.3333740234375,"y":-2772.0},"targetType":1,"assetTags":{"Tags":[]},"grantedTags":{"Tags":[]},"applicationRequiredTags":{"Tags":[]},"applicationImmunityTags":{"Tags":[]},"removeGameEffectsWithTags":{"Tags":[]},"durationType":0,"duration":"0","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[{"attrType":1003,"operation":0,"magnitudeSourceType":0,"fixedValue":-10.0,"formula":"","mmcType":0,"setByCallerKey":"","mmcCaptureAttribute":200,"mmcAttributeSource":0,"mmcCoefficient":1.0,"mmcUseSnapshot":true}],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"Tags":[]},"cancelOnAbilityEnd":true}</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
@@ -2103,11 +2103,11 @@
       <c r="C75"/>
       <c r="D75"/>
       <c r="E75">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>{"guid":"e33ab94c-1496-4d6a-ba5e-1afd38bb0c30","nodeType":4,"position":{"x":731.3333740234375,"y":-2344.0},"targetType":1,"searchShapeType":3,"searchLineType":0,"positionSource":0,"positionBindingName":"center","searchCircleRadius":1.0,"searchSectorRadius":5.0,"searchSectorAngle":180.0,"searchLineDirectionOffsetAngle":0.0,"searchLineDirectionWidth":1.0,"searchLineDirectionLength":10.0,"lineStartPositionSource":0,"lineStartBindingName":"","lineEndPositionSource":1,"lineEndBindingName":"","searchLineBetweenWidth":1.0,"searchLineAbsoluteAngle":0.0,"searchLineAbsoluteWidth":1.0,"searchLineAbsoluteLength":10.0,"maxTargets":1,"searchTargetTags":{"Tags":[{"Name":"campType.EnemyCamp","HashCode":713889996,"ShortName":"EnemyCamp","AncestorHashCodes":[-312381257],"AncestorNames":["campType"]}]},"searchExcludeTags":{"Tags":[]}}</t>
+          <t>{"guid":"f8947676-1084-4228-b991-1509cc7fe851","nodeType":1,"position":{"x":975.3333740234375,"y":-2344.0},"targetType":0,"assetTags":{"Tags":[]},"grantedTags":{"Tags":[]},"applicationRequiredTags":{"Tags":[]},"applicationImmunityTags":{"Tags":[]},"removeGameEffectsWithTags":{"Tags":[]},"durationType":0,"duration":"0","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"Tags":[]},"cancelOnAbilityEnd":true,"damageType":1,"damageSourceType":3,"damageFixedValue":10.0,"damageFormula":"","damageMMCType":1,"damageSetByCallerKey":"AttackDamage","damageMMCCaptureAttribute":1006,"damageMMCAttributeSource":0,"damageMMCCoefficient":1.0,"damageMMCUseSnapshot":true,"damageMultiplyByStackCount":false,"damageCalculationType":0,"enableHitKnockback":false,"knockbackDistance":1.0,"knockbackSpeed":12.0}</t>
         </is>
       </c>
       <c r="G75"/>

--- a/Design/Excel/ET/Datas/Game/SkillGraph.xlsx
+++ b/Design/Excel/ET/Datas/Game/SkillGraph.xlsx
@@ -991,11 +991,11 @@
       </c>
       <c r="D20"/>
       <c r="E20">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>{"guid":"08bcef27-5270-4668-be7d-bb9e9fc01e6a","nodeType":23,"position":{"x":-649.33331298828125,"y":-2446.66650390625},"targetType":1,"animationPrefab":null,"animationPrefabPath":"Assets/Res/Entity/Head/HeadItem.prefab","animationComponentPath":"HeadItem(Clone)/Root_Animation","animationName":"Attack","animationDuration":"15","isAnimationLooping":false,"timeEffects":[{"triggerTime":1,"portIdValue":2131464,"legacyPortId":""},{"triggerTime":15,"portIdValue":2547623,"legacyPortId":""}],"timeCues":[{"startTime":0,"endTime":15,"portIdValue":2247261,"legacyPortId":""}]}</t>
+          <t>{"guid":"2d7e41c4-8e90-4b61-879c-4b2e5b9486db","nodeType":14,"position":{"x":1200.0,"y":-2044.666748046875},"targetType":1,"requiredTags":{"Tags":[]},"immunityTags":{"Tags":[]},"destroyWithNode":false,"positionSource":2,"positionBindingName":"head","textType":0,"fixedText":"","contextDataKey":"DamageResult","textColor":{"r":1.0,"g":0.16293229162693024,"b":0.0,"a":1.0},"criticalColor":{"r":1.0,"g":0.5,"b":0.0,"a":1.0},"missColor":{"r":0.5,"g":0.5,"b":0.5,"a":1.0},"fontSize":5.0,"criticalFontSize":60.0,"duration":1.5,"offset":{"x":0.0,"y":0.0},"moveDirection":{"x":0.0,"y":1.0}}</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -1011,11 +1011,11 @@
       <c r="C21"/>
       <c r="D21"/>
       <c r="E21">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>{"guid":"2d7e41c4-8e90-4b61-879c-4b2e5b9486db","nodeType":14,"position":{"x":1200.0,"y":-2044.666748046875},"targetType":1,"requiredTags":{"Tags":[]},"immunityTags":{"Tags":[]},"destroyWithNode":false,"positionSource":2,"positionBindingName":"head","textType":0,"fixedText":"","contextDataKey":"DamageResult","textColor":{"r":1.0,"g":0.16293229162693024,"b":0.0,"a":1.0},"criticalColor":{"r":1.0,"g":0.5,"b":0.0,"a":1.0},"missColor":{"r":0.5,"g":0.5,"b":0.5,"a":1.0},"fontSize":5.0,"criticalFontSize":60.0,"duration":1.5,"offset":{"x":0.0,"y":0.0},"moveDirection":{"x":0.0,"y":1.0}}</t>
+          <t>{"guid":"356907e0-1488-4128-bfcc-7ff73cfc3330","nodeType":0,"position":{"x":-1013.3333740234375,"y":-2446.66650390625},"targetType":1,"skillId":7001,"assetTags":{"Tags":[]},"cancelAbilitiesWithTags":{"Tags":[]},"blockAbilitiesWithTags":{"Tags":[]},"activationOwnedTags":{"Tags":[]},"activationRequiredTags":{"Tags":[]},"activationBlockedTags":{"Tags":[{"Name":"CD.FireCircle","HashCode":522143731,"ShortName":"FireCircle","AncestorHashCodes":[-1137859925],"AncestorNames":["CD"]}]},"ongoingBlockedTags":{"Tags":[{"Name":"Buff.DeBuff.Stun","HashCode":1791562953,"ShortName":"Stun","AncestorHashCodes":[937056111,321157895],"AncestorNames":["Buff","Buff.DeBuff"]}]},"eventOutputPorts":[]}</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -1031,11 +1031,11 @@
       <c r="C22"/>
       <c r="D22"/>
       <c r="E22">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>{"guid":"356907e0-1488-4128-bfcc-7ff73cfc3330","nodeType":0,"position":{"x":-1013.3333740234375,"y":-2446.66650390625},"targetType":1,"skillId":7001,"assetTags":{"Tags":[]},"cancelAbilitiesWithTags":{"Tags":[]},"blockAbilitiesWithTags":{"Tags":[]},"activationOwnedTags":{"Tags":[]},"activationRequiredTags":{"Tags":[]},"activationBlockedTags":{"Tags":[{"Name":"CD.FireCircle","HashCode":522143731,"ShortName":"FireCircle","AncestorHashCodes":[-1137859925],"AncestorNames":["CD"]}]},"ongoingBlockedTags":{"Tags":[{"Name":"Buff.DeBuff.Stun","HashCode":1791562953,"ShortName":"Stun","AncestorHashCodes":[937056111,321157895],"AncestorNames":["Buff","Buff.DeBuff"]}]},"eventOutputPorts":[]}</t>
+          <t>{"guid":"c28fb88d-51b1-47b2-be59-859e0ac638e3","nodeType":10,"position":{"x":-1257.3333740234375,"y":-2221.333251953125},"targetType":1,"assetTags":{"Tags":[]},"grantedTags":{"Tags":[{"Name":"CD.FireCircle","HashCode":522143731,"ShortName":"FireCircle","AncestorHashCodes":[-1137859925],"AncestorNames":["CD"]}]},"applicationRequiredTags":{"Tags":[]},"applicationImmunityTags":{"Tags":[]},"removeGameEffectsWithTags":{"Tags":[]},"durationType":1,"duration":"3","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"Tags":[]},"cancelOnAbilityEnd":false,"cooldownType":0,"maxCharges":2,"chargeTime":"10"}</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -1051,11 +1051,11 @@
       <c r="C23"/>
       <c r="D23"/>
       <c r="E23">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>{"guid":"c28fb88d-51b1-47b2-be59-859e0ac638e3","nodeType":10,"position":{"x":-1257.3333740234375,"y":-2221.333251953125},"targetType":1,"assetTags":{"Tags":[]},"grantedTags":{"Tags":[{"Name":"CD.FireCircle","HashCode":522143731,"ShortName":"FireCircle","AncestorHashCodes":[-1137859925],"AncestorNames":["CD"]}]},"applicationRequiredTags":{"Tags":[]},"applicationImmunityTags":{"Tags":[]},"removeGameEffectsWithTags":{"Tags":[]},"durationType":1,"duration":"3","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"Tags":[]},"cancelOnAbilityEnd":false,"cooldownType":0,"maxCharges":2,"chargeTime":"10"}</t>
+          <t>{"guid":"3aafa9a5-4766-4204-91ab-d797aeb3c0e1","nodeType":7,"position":{"x":322.66665649414063,"y":-1817.3333740234375},"targetType":1,"endType":0}</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -1071,11 +1071,11 @@
       <c r="C24"/>
       <c r="D24"/>
       <c r="E24">
-        <v>7</v>
+        <v>23</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>{"guid":"3aafa9a5-4766-4204-91ab-d797aeb3c0e1","nodeType":7,"position":{"x":322.66665649414063,"y":-1817.3333740234375},"targetType":1,"endType":0}</t>
+          <t>{"guid":"08bcef27-5270-4668-be7d-bb9e9fc01e6a","nodeType":23,"position":{"x":-649.33331298828125,"y":-2446.66650390625},"targetType":1,"animationPrefab":null,"animationPrefabPath":"Assets/Res/Entity/Head/HeadItem.prefab","animationComponentPath":"HeadItem(Clone)/Root_Animation","animationName":"Attack","animationDuration":"15","isAnimationLooping":false,"timeEffects":[{"triggerTime":1,"portIdValue":2131464,"legacyPortId":""},{"triggerTime":15,"portIdValue":2547623,"legacyPortId":""}],"timeCues":[{"startTime":0,"endTime":15,"portIdValue":2247261,"legacyPortId":""}]}</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -1091,11 +1091,11 @@
       <c r="C25"/>
       <c r="D25"/>
       <c r="E25">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>{"guid":"93b489d8-3d60-4ded-9f04-789fe2990ece","nodeType":4,"position":{"x":510.66665649414063,"y":-1895.3333740234375},"targetType":1,"searchShapeType":3,"searchLineType":0,"positionSource":1,"positionBindingName":"","searchCircleRadius":5.0,"searchSectorRadius":5.0,"searchSectorAngle":90.0,"searchLineDirectionOffsetAngle":0.0,"searchLineDirectionWidth":1.0,"searchLineDirectionLength":10.0,"lineStartPositionSource":0,"lineStartBindingName":"","lineEndPositionSource":1,"lineEndBindingName":"","searchLineBetweenWidth":1.0,"searchLineAbsoluteAngle":0.0,"searchLineAbsoluteWidth":1.0,"searchLineAbsoluteLength":10.0,"maxTargets":1,"searchTargetTags":{"Tags":[{"Name":"campType.EnemyCamp","HashCode":713889996,"ShortName":"EnemyCamp","AncestorHashCodes":[-312381257],"AncestorNames":["campType"]}]},"searchExcludeTags":{"Tags":[]}}</t>
+          <t>{"guid":"9d6f459d-b588-4b64-843b-1b71e8f299ae","nodeType":3,"position":{"x":-1316.0,"y":-2446.66650390625},"targetType":1,"assetTags":{"Tags":[]},"grantedTags":{"Tags":[]},"applicationRequiredTags":{"Tags":[]},"applicationImmunityTags":{"Tags":[]},"removeGameEffectsWithTags":{"Tags":[]},"durationType":0,"duration":"0","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[{"attrType":1003,"operation":0,"magnitudeSourceType":0,"fixedValue":-10.0,"formula":"","mmcType":0,"setByCallerKey":"","mmcCaptureAttribute":200,"mmcAttributeSource":0,"mmcCoefficient":1.0,"mmcUseSnapshot":true}],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"Tags":[]},"cancelOnAbilityEnd":true}</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -1111,11 +1111,11 @@
       <c r="C26"/>
       <c r="D26"/>
       <c r="E26">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>{"guid":"9d6f459d-b588-4b64-843b-1b71e8f299ae","nodeType":3,"position":{"x":-1316.0,"y":-2446.66650390625},"targetType":1,"assetTags":{"Tags":[]},"grantedTags":{"Tags":[]},"applicationRequiredTags":{"Tags":[]},"applicationImmunityTags":{"Tags":[]},"removeGameEffectsWithTags":{"Tags":[]},"durationType":0,"duration":"0","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[{"attrType":1003,"operation":0,"magnitudeSourceType":0,"fixedValue":-100.0,"formula":"","mmcType":0,"setByCallerKey":"","mmcCaptureAttribute":200,"mmcAttributeSource":0,"mmcCoefficient":1.0,"mmcUseSnapshot":true}],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"Tags":[]},"cancelOnAbilityEnd":true}</t>
+          <t>{"guid":"93b489d8-3d60-4ded-9f04-789fe2990ece","nodeType":4,"position":{"x":510.66665649414063,"y":-1895.3333740234375},"targetType":1,"searchShapeType":3,"searchLineType":0,"positionSource":1,"positionBindingName":"","searchCircleRadius":5.0,"searchSectorRadius":5.0,"searchSectorAngle":90.0,"searchLineDirectionOffsetAngle":0.0,"searchLineDirectionWidth":1.0,"searchLineDirectionLength":10.0,"lineStartPositionSource":0,"lineStartBindingName":"","lineEndPositionSource":1,"lineEndBindingName":"","searchLineBetweenWidth":1.0,"searchLineAbsoluteAngle":0.0,"searchLineAbsoluteWidth":1.0,"searchLineAbsoluteLength":10.0,"maxTargets":1,"searchTargetTags":{"Tags":[{"Name":"campType.EnemyCamp","HashCode":713889996,"ShortName":"EnemyCamp","AncestorHashCodes":[-312381257],"AncestorNames":["campType"]}]},"searchExcludeTags":{"Tags":[]}}</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -1131,11 +1131,11 @@
       <c r="C27"/>
       <c r="D27"/>
       <c r="E27">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>{"guid":"90bacd9f-d882-4bba-aaa8-41ed993ac3ff","nodeType":8,"position":{"x":620.6666259765625,"y":-2102.666748046875},"targetType":1,"assetTags":{"Tags":[]},"grantedTags":{"Tags":[]},"applicationRequiredTags":{"Tags":[]},"applicationImmunityTags":{"Tags":[]},"removeGameEffectsWithTags":{"Tags":[]},"durationType":2,"duration":"0","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"Tags":[]},"cancelOnAbilityEnd":false,"launchPositionSource":0,"launchBindingName":"center","targetPositionSource":2,"targetBindingName":"center","projectileTargetType":1,"flyOver":false,"offsetAngle":0.0,"curveHeight":0.0,"projectileEntityId":50001,"projectilePrefab":null,"projectilePrefabPath":"Assets/Res/Entity/Effect/ef_fashi_gandian_buff.prefab","speed":3.0,"maxDistance":10.0,"collisionRadius":0.10000000149011612,"isPiercing":false,"maxPierceCount":1,"collisionTargetTags":{"Tags":[{"Name":"campType.EnemyCamp","HashCode":713889996,"ShortName":"EnemyCamp","AncestorHashCodes":[-312381257],"AncestorNames":["campType"]}]},"collisionExcludeTags":{"Tags":[]},"isBouncing":false,"bounceTargetMode":0,"maxBounceCount":3,"bounceSearchRadius":10.0,"canBounceToSameTarget":false,"excludeSourceCamp":true,"bounceAngleOffset":0.0}</t>
+          <t>{"guid":"eae41233-d297-46fe-a6c8-0b5c876fbb2a","nodeType":1,"position":{"x":942.0,"y":-2072.666748046875},"targetType":0,"assetTags":{"Tags":[]},"grantedTags":{"Tags":[]},"applicationRequiredTags":{"Tags":[]},"applicationImmunityTags":{"Tags":[]},"removeGameEffectsWithTags":{"Tags":[]},"durationType":0,"duration":"0","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"Tags":[]},"cancelOnAbilityEnd":true,"damageType":1,"damageSourceType":3,"damageFixedValue":50.0,"damageFormula":"","damageMMCType":0,"damageSetByCallerKey":"AttackDamage","damageMMCCaptureAttribute":1006,"damageMMCAttributeSource":0,"damageMMCCoefficient":1.0,"damageMMCUseSnapshot":false,"damageMultiplyByStackCount":false,"damageCalculationType":0,"enableHitKnockback":false,"knockbackDistance":1.0,"knockbackSpeed":12.0}</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -1151,14 +1151,18 @@
       <c r="C28"/>
       <c r="D28"/>
       <c r="E28">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>{"guid":"eae41233-d297-46fe-a6c8-0b5c876fbb2a","nodeType":1,"position":{"x":942.0,"y":-2072.666748046875},"targetType":0,"assetTags":{"Tags":[]},"grantedTags":{"Tags":[]},"applicationRequiredTags":{"Tags":[]},"applicationImmunityTags":{"Tags":[]},"removeGameEffectsWithTags":{"Tags":[]},"durationType":0,"duration":"0","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"Tags":[]},"cancelOnAbilityEnd":true,"damageType":1,"damageSourceType":3,"damageFixedValue":50.0,"damageFormula":"","damageMMCType":0,"damageSetByCallerKey":"AttackDamage","damageMMCCaptureAttribute":1006,"damageMMCAttributeSource":0,"damageMMCCoefficient":1.0,"damageMMCUseSnapshot":false,"damageMultiplyByStackCount":false,"damageCalculationType":0,"enableHitKnockback":false,"knockbackDistance":1.0,"knockbackSpeed":12.0}</t>
-        </is>
-      </c>
-      <c r="G28"/>
+          <t>{"guid":"90bacd9f-d882-4bba-aaa8-41ed993ac3ff","nodeType":8,"position":{"x":620.6666259765625,"y":-2102.666748046875},"targetType":1,"assetTags":{"Tags":[]},"grantedTags":{"Tags":[]},"applicationRequiredTags":{"Tags":[]},"applicationImmunityTags":{"Tags":[]},"removeGameEffectsWithTags":{"Tags":[]},"durationType":2,"duration":"0","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"Tags":[]},"cancelOnAbilityEnd":false,"launchPositionSource":0,"launchBindingName":"center","targetPositionSource":2,"targetBindingName":"center","projectileTargetType":1,"flyOver":false,"offsetAngle":0.0,"curveHeight":0.0,"projectileEntityId":50001,"projectilePrefab":null,"projectilePrefabPath":"Assets/Res/Entity/Effect/ef_fashi_gandian_buff.prefab","speed":3.0,"maxDistance":10.0,"collisionRadius":0.20000000298023224,"isPiercing":false,"maxPierceCount":1,"collisionTargetTags":{"Tags":[{"Name":"campType.EnemyCamp","HashCode":713889996,"ShortName":"EnemyCamp","AncestorHashCodes":[-312381257],"AncestorNames":["campType"]}]},"collisionExcludeTags":{"Tags":[]},"isBouncing":false,"bounceTargetMode":0,"maxBounceCount":3,"bounceSearchRadius":10.0,"canBounceToSameTarget":false,"excludeSourceCamp":true,"bounceAngleOffset":0.0}</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>{"outputNodeGuid":"90bacd9f-d882-4bba-aaa8-41ed993ac3ff","outputPortId":5002,"inputNodeGuid":"eae41233-d297-46fe-a6c8-0b5c876fbb2a","inputPortId":7001}</t>
+        </is>
+      </c>
       <c r="H28"/>
     </row>
     <row r="29">

--- a/Design/Excel/ET/Datas/Game/SkillGraph.xlsx
+++ b/Design/Excel/ET/Datas/Game/SkillGraph.xlsx
@@ -1131,16 +1131,16 @@
       <c r="C27"/>
       <c r="D27"/>
       <c r="E27">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>{"guid":"eae41233-d297-46fe-a6c8-0b5c876fbb2a","nodeType":1,"position":{"x":942.0,"y":-2072.666748046875},"targetType":0,"assetTags":{"Tags":[]},"grantedTags":{"Tags":[]},"applicationRequiredTags":{"Tags":[]},"applicationImmunityTags":{"Tags":[]},"removeGameEffectsWithTags":{"Tags":[]},"durationType":0,"duration":"0","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"Tags":[]},"cancelOnAbilityEnd":true,"damageType":1,"damageSourceType":3,"damageFixedValue":50.0,"damageFormula":"","damageMMCType":0,"damageSetByCallerKey":"AttackDamage","damageMMCCaptureAttribute":1006,"damageMMCAttributeSource":0,"damageMMCCoefficient":1.0,"damageMMCUseSnapshot":false,"damageMultiplyByStackCount":false,"damageCalculationType":0,"enableHitKnockback":false,"knockbackDistance":1.0,"knockbackSpeed":12.0}</t>
+          <t>{"guid":"90bacd9f-d882-4bba-aaa8-41ed993ac3ff","nodeType":8,"position":{"x":620.6666259765625,"y":-2102.666748046875},"targetType":1,"assetTags":{"Tags":[]},"grantedTags":{"Tags":[]},"applicationRequiredTags":{"Tags":[]},"applicationImmunityTags":{"Tags":[]},"removeGameEffectsWithTags":{"Tags":[]},"durationType":2,"duration":"0","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"Tags":[]},"cancelOnAbilityEnd":false,"launchPositionSource":0,"launchBindingName":"center","targetPositionSource":2,"targetBindingName":"center","projectileTargetType":1,"flyOver":false,"offsetAngle":0.0,"curveHeight":0.0,"projectileEntityId":50001,"projectilePrefab":null,"projectilePrefabPath":"Assets/Res/Entity/Effect/ef_fashi_gandian_buff.prefab","speed":3.0,"maxDistance":10.0,"collisionRadius":0.20000000298023224,"isPiercing":false,"maxPierceCount":1,"collisionTargetTags":{"Tags":[{"Name":"campType.EnemyCamp","HashCode":713889996,"ShortName":"EnemyCamp","AncestorHashCodes":[-312381257],"AncestorNames":["campType"]}]},"collisionExcludeTags":{"Tags":[]},"isBouncing":false,"bounceTargetMode":0,"maxBounceCount":3,"bounceSearchRadius":10.0,"canBounceToSameTarget":false,"excludeSourceCamp":true,"bounceAngleOffset":0.0}</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>{"outputNodeGuid":"90bacd9f-d882-4bba-aaa8-41ed993ac3ff","outputPortId":5001,"inputNodeGuid":"eae41233-d297-46fe-a6c8-0b5c876fbb2a","inputPortId":7001}</t>
+          <t>{"outputNodeGuid":"90bacd9f-d882-4bba-aaa8-41ed993ac3ff","outputPortId":5002,"inputNodeGuid":"eae41233-d297-46fe-a6c8-0b5c876fbb2a","inputPortId":7001}</t>
         </is>
       </c>
       <c r="H27"/>
@@ -1151,18 +1151,14 @@
       <c r="C28"/>
       <c r="D28"/>
       <c r="E28">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>{"guid":"90bacd9f-d882-4bba-aaa8-41ed993ac3ff","nodeType":8,"position":{"x":620.6666259765625,"y":-2102.666748046875},"targetType":1,"assetTags":{"Tags":[]},"grantedTags":{"Tags":[]},"applicationRequiredTags":{"Tags":[]},"applicationImmunityTags":{"Tags":[]},"removeGameEffectsWithTags":{"Tags":[]},"durationType":2,"duration":"0","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"Tags":[]},"cancelOnAbilityEnd":false,"launchPositionSource":0,"launchBindingName":"center","targetPositionSource":2,"targetBindingName":"center","projectileTargetType":1,"flyOver":false,"offsetAngle":0.0,"curveHeight":0.0,"projectileEntityId":50001,"projectilePrefab":null,"projectilePrefabPath":"Assets/Res/Entity/Effect/ef_fashi_gandian_buff.prefab","speed":3.0,"maxDistance":10.0,"collisionRadius":0.20000000298023224,"isPiercing":false,"maxPierceCount":1,"collisionTargetTags":{"Tags":[{"Name":"campType.EnemyCamp","HashCode":713889996,"ShortName":"EnemyCamp","AncestorHashCodes":[-312381257],"AncestorNames":["campType"]}]},"collisionExcludeTags":{"Tags":[]},"isBouncing":false,"bounceTargetMode":0,"maxBounceCount":3,"bounceSearchRadius":10.0,"canBounceToSameTarget":false,"excludeSourceCamp":true,"bounceAngleOffset":0.0}</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>{"outputNodeGuid":"90bacd9f-d882-4bba-aaa8-41ed993ac3ff","outputPortId":5002,"inputNodeGuid":"eae41233-d297-46fe-a6c8-0b5c876fbb2a","inputPortId":7001}</t>
-        </is>
-      </c>
+          <t>{"guid":"eae41233-d297-46fe-a6c8-0b5c876fbb2a","nodeType":1,"position":{"x":942.0,"y":-2072.666748046875},"targetType":0,"assetTags":{"Tags":[]},"grantedTags":{"Tags":[]},"applicationRequiredTags":{"Tags":[]},"applicationImmunityTags":{"Tags":[]},"removeGameEffectsWithTags":{"Tags":[]},"durationType":0,"duration":"0","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"Tags":[]},"cancelOnAbilityEnd":true,"damageType":1,"damageSourceType":3,"damageFixedValue":50.0,"damageFormula":"","damageMMCType":0,"damageSetByCallerKey":"AttackDamage","damageMMCCaptureAttribute":1006,"damageMMCAttributeSource":0,"damageMMCCoefficient":1.0,"damageMMCUseSnapshot":false,"damageMultiplyByStackCount":false,"damageCalculationType":0,"enableHitKnockback":false,"knockbackDistance":1.0,"knockbackSpeed":12.0}</t>
+        </is>
+      </c>
+      <c r="G28"/>
       <c r="H28"/>
     </row>
     <row r="29">

--- a/Design/Excel/ET/Datas/Game/SkillGraph.xlsx
+++ b/Design/Excel/ET/Datas/Game/SkillGraph.xlsx
@@ -1111,11 +1111,11 @@
       <c r="C26"/>
       <c r="D26"/>
       <c r="E26">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>{"guid":"93b489d8-3d60-4ded-9f04-789fe2990ece","nodeType":4,"position":{"x":510.66665649414063,"y":-1895.3333740234375},"targetType":1,"searchShapeType":3,"searchLineType":0,"positionSource":1,"positionBindingName":"","searchCircleRadius":5.0,"searchSectorRadius":5.0,"searchSectorAngle":90.0,"searchLineDirectionOffsetAngle":0.0,"searchLineDirectionWidth":1.0,"searchLineDirectionLength":10.0,"lineStartPositionSource":0,"lineStartBindingName":"","lineEndPositionSource":1,"lineEndBindingName":"","searchLineBetweenWidth":1.0,"searchLineAbsoluteAngle":0.0,"searchLineAbsoluteWidth":1.0,"searchLineAbsoluteLength":10.0,"maxTargets":1,"searchTargetTags":{"Tags":[{"Name":"campType.EnemyCamp","HashCode":713889996,"ShortName":"EnemyCamp","AncestorHashCodes":[-312381257],"AncestorNames":["campType"]}]},"searchExcludeTags":{"Tags":[]}}</t>
+          <t>{"guid":"eae41233-d297-46fe-a6c8-0b5c876fbb2a","nodeType":1,"position":{"x":942.0,"y":-2072.666748046875},"targetType":0,"assetTags":{"Tags":[]},"grantedTags":{"Tags":[]},"applicationRequiredTags":{"Tags":[]},"applicationImmunityTags":{"Tags":[]},"removeGameEffectsWithTags":{"Tags":[]},"durationType":0,"duration":"0","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"Tags":[]},"cancelOnAbilityEnd":true,"damageType":1,"damageSourceType":3,"damageFixedValue":50.0,"damageFormula":"","damageMMCType":0,"damageSetByCallerKey":"AttackDamage","damageMMCCaptureAttribute":1006,"damageMMCAttributeSource":0,"damageMMCCoefficient":1.0,"damageMMCUseSnapshot":false,"damageMultiplyByStackCount":false,"damageCalculationType":0,"enableHitKnockback":false,"knockbackDistance":1.0,"knockbackSpeed":12.0}</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -1135,7 +1135,7 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>{"guid":"90bacd9f-d882-4bba-aaa8-41ed993ac3ff","nodeType":8,"position":{"x":620.6666259765625,"y":-2102.666748046875},"targetType":1,"assetTags":{"Tags":[]},"grantedTags":{"Tags":[]},"applicationRequiredTags":{"Tags":[]},"applicationImmunityTags":{"Tags":[]},"removeGameEffectsWithTags":{"Tags":[]},"durationType":2,"duration":"0","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"Tags":[]},"cancelOnAbilityEnd":false,"launchPositionSource":0,"launchBindingName":"center","targetPositionSource":2,"targetBindingName":"center","projectileTargetType":1,"flyOver":false,"offsetAngle":0.0,"curveHeight":0.0,"projectileEntityId":50001,"projectilePrefab":null,"projectilePrefabPath":"Assets/Res/Entity/Effect/ef_fashi_gandian_buff.prefab","speed":3.0,"maxDistance":10.0,"collisionRadius":0.20000000298023224,"isPiercing":false,"maxPierceCount":1,"collisionTargetTags":{"Tags":[{"Name":"campType.EnemyCamp","HashCode":713889996,"ShortName":"EnemyCamp","AncestorHashCodes":[-312381257],"AncestorNames":["campType"]}]},"collisionExcludeTags":{"Tags":[]},"isBouncing":false,"bounceTargetMode":0,"maxBounceCount":3,"bounceSearchRadius":10.0,"canBounceToSameTarget":false,"excludeSourceCamp":true,"bounceAngleOffset":0.0}</t>
+          <t>{"guid":"90bacd9f-d882-4bba-aaa8-41ed993ac3ff","nodeType":8,"position":{"x":620.6666259765625,"y":-2103.333251953125},"targetType":1,"assetTags":{"Tags":[]},"grantedTags":{"Tags":[]},"applicationRequiredTags":{"Tags":[]},"applicationImmunityTags":{"Tags":[]},"removeGameEffectsWithTags":{"Tags":[]},"durationType":2,"duration":"0","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"Tags":[]},"cancelOnAbilityEnd":false,"launchPositionSource":0,"launchBindingName":"center","targetPositionSource":2,"targetBindingName":"center","projectileTargetType":1,"flyOver":false,"offsetAngle":0.0,"curveHeight":0.0,"projectileEntityId":50001,"projectilePrefab":null,"projectilePrefabPath":"Assets/Res/Entity/Effect/ef_fashi_gandian_buff.prefab","speed":3.0,"maxDistance":10.0,"collisionRadius":0.20000000298023224,"isPiercing":false,"maxPierceCount":1,"collisionTargetTags":{"Tags":[{"Name":"campType.EnemyCamp","HashCode":713889996,"ShortName":"EnemyCamp","AncestorHashCodes":[-312381257],"AncestorNames":["campType"]}]},"collisionExcludeTags":{"Tags":[]},"isBouncing":false,"bounceTargetMode":0,"maxBounceCount":3,"bounceSearchRadius":10.0,"canBounceToSameTarget":false,"excludeSourceCamp":true,"bounceAngleOffset":0.0}</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -1151,11 +1151,11 @@
       <c r="C28"/>
       <c r="D28"/>
       <c r="E28">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>{"guid":"eae41233-d297-46fe-a6c8-0b5c876fbb2a","nodeType":1,"position":{"x":942.0,"y":-2072.666748046875},"targetType":0,"assetTags":{"Tags":[]},"grantedTags":{"Tags":[]},"applicationRequiredTags":{"Tags":[]},"applicationImmunityTags":{"Tags":[]},"removeGameEffectsWithTags":{"Tags":[]},"durationType":0,"duration":"0","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"Tags":[]},"cancelOnAbilityEnd":true,"damageType":1,"damageSourceType":3,"damageFixedValue":50.0,"damageFormula":"","damageMMCType":0,"damageSetByCallerKey":"AttackDamage","damageMMCCaptureAttribute":1006,"damageMMCAttributeSource":0,"damageMMCCoefficient":1.0,"damageMMCUseSnapshot":false,"damageMultiplyByStackCount":false,"damageCalculationType":0,"enableHitKnockback":false,"knockbackDistance":1.0,"knockbackSpeed":12.0}</t>
+          <t>{"guid":"93b489d8-3d60-4ded-9f04-789fe2990ece","nodeType":4,"position":{"x":510.66665649414063,"y":-1895.3333740234375},"targetType":1,"searchShapeType":3,"searchLineType":0,"positionSource":1,"positionBindingName":"","searchCircleRadius":5.0,"searchSectorRadius":5.0,"searchSectorAngle":90.0,"searchLineDirectionOffsetAngle":0.0,"searchLineDirectionWidth":1.0,"searchLineDirectionLength":10.0,"lineStartPositionSource":0,"lineStartBindingName":"","lineEndPositionSource":1,"lineEndBindingName":"","searchLineBetweenWidth":1.0,"searchLineAbsoluteAngle":0.0,"searchLineAbsoluteWidth":1.0,"searchLineAbsoluteLength":10.0,"maxTargets":2,"searchTargetTags":{"Tags":[{"Name":"campType.EnemyCamp","HashCode":713889996,"ShortName":"EnemyCamp","AncestorHashCodes":[-312381257],"AncestorNames":["campType"]}]},"searchExcludeTags":{"Tags":[]}}</t>
         </is>
       </c>
       <c r="G28"/>
@@ -1273,11 +1273,11 @@
       <c r="C34"/>
       <c r="D34"/>
       <c r="E34">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>{"guid":"eae41233-d297-46fe-a6c8-0b5c876fbb2a","nodeType":1,"position":{"x":45.333343505859375,"y":-1806.666748046875},"targetType":0,"assetTags":{"Tags":[]},"grantedTags":{"Tags":[]},"applicationRequiredTags":{"Tags":[]},"applicationImmunityTags":{"Tags":[]},"removeGameEffectsWithTags":{"Tags":[]},"durationType":0,"duration":"0","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"Tags":[]},"cancelOnAbilityEnd":true,"damageType":0,"damageSourceType":0,"damageFixedValue":10.0,"damageFormula":"","damageMMCType":0,"damageSetByCallerKey":"","damageMMCCaptureAttribute":200,"damageMMCAttributeSource":0,"damageMMCCoefficient":1.0,"damageMMCUseSnapshot":true,"damageMultiplyByStackCount":false,"damageCalculationType":0,"enableHitKnockback":true,"knockbackDistance":1.0,"knockbackSpeed":12.0}</t>
+          <t>{"guid":"90bacd9f-d882-4bba-aaa8-41ed993ac3ff","nodeType":8,"position":{"x":-400.66665649414063,"y":-1836.666748046875},"targetType":2,"assetTags":{"Tags":[]},"grantedTags":{"Tags":[]},"applicationRequiredTags":{"Tags":[]},"applicationImmunityTags":{"Tags":[]},"removeGameEffectsWithTags":{"Tags":[]},"durationType":2,"duration":"0","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"Tags":[]},"cancelOnAbilityEnd":false,"launchPositionSource":0,"launchBindingName":"center","targetPositionSource":1,"targetBindingName":"center","projectileTargetType":0,"flyOver":false,"offsetAngle":0.0,"curveHeight":0.0,"projectileEntityId":50001,"projectilePrefab":null,"projectilePrefabPath":"Assets/Res/Entity/Effect/ef_fashi_gandian_buff.prefab","speed":3.0,"maxDistance":10.0,"collisionRadius":0.5,"isPiercing":false,"maxPierceCount":1,"collisionTargetTags":{"Tags":[]},"collisionExcludeTags":{"Tags":[]},"isBouncing":true,"bounceTargetMode":0,"maxBounceCount":2,"bounceSearchRadius":10.0,"canBounceToSameTarget":false,"excludeSourceCamp":true,"bounceAngleOffset":50.0}</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -1293,11 +1293,11 @@
       <c r="C35"/>
       <c r="D35"/>
       <c r="E35">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>{"guid":"90bacd9f-d882-4bba-aaa8-41ed993ac3ff","nodeType":8,"position":{"x":-400.66665649414063,"y":-1836.666748046875},"targetType":2,"assetTags":{"Tags":[]},"grantedTags":{"Tags":[]},"applicationRequiredTags":{"Tags":[]},"applicationImmunityTags":{"Tags":[]},"removeGameEffectsWithTags":{"Tags":[]},"durationType":2,"duration":"0","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"Tags":[]},"cancelOnAbilityEnd":false,"launchPositionSource":0,"launchBindingName":"center","targetPositionSource":1,"targetBindingName":"center","projectileTargetType":0,"flyOver":false,"offsetAngle":0.0,"curveHeight":0.0,"projectileEntityId":50001,"projectilePrefab":null,"projectilePrefabPath":"Assets/Res/Entity/Effect/ef_fashi_gandian_buff.prefab","speed":3.0,"maxDistance":10.0,"collisionRadius":0.5,"isPiercing":false,"maxPierceCount":1,"collisionTargetTags":{"Tags":[]},"collisionExcludeTags":{"Tags":[]},"isBouncing":true,"bounceTargetMode":0,"maxBounceCount":2,"bounceSearchRadius":10.0,"canBounceToSameTarget":false,"excludeSourceCamp":true,"bounceAngleOffset":50.0}</t>
+          <t>{"guid":"eae41233-d297-46fe-a6c8-0b5c876fbb2a","nodeType":1,"position":{"x":52.0,"y":-1836.666748046875},"targetType":0,"assetTags":{"Tags":[]},"grantedTags":{"Tags":[]},"applicationRequiredTags":{"Tags":[]},"applicationImmunityTags":{"Tags":[]},"removeGameEffectsWithTags":{"Tags":[]},"durationType":0,"duration":"0","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"Tags":[]},"cancelOnAbilityEnd":true,"damageType":0,"damageSourceType":0,"damageFixedValue":10.0,"damageFormula":"","damageMMCType":0,"damageSetByCallerKey":"","damageMMCCaptureAttribute":200,"damageMMCAttributeSource":0,"damageMMCCoefficient":1.0,"damageMMCUseSnapshot":true,"damageMultiplyByStackCount":false,"damageCalculationType":0,"enableHitKnockback":true,"knockbackDistance":1.0,"knockbackSpeed":12.0}</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -1317,7 +1317,7 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>{"guid":"2d7e41c4-8e90-4b61-879c-4b2e5b9486db","nodeType":14,"position":{"x":408.66665649414063,"y":-1747.3333740234375},"targetType":1,"requiredTags":{"Tags":[]},"immunityTags":{"Tags":[]},"destroyWithNode":false,"positionSource":2,"positionBindingName":"head","textType":0,"fixedText":"","contextDataKey":"DamageResult","textColor":{"r":0.0,"g":0.323091983795166,"b":1.0,"a":1.0},"criticalColor":{"r":1.0,"g":0.5,"b":0.0,"a":1.0},"missColor":{"r":0.5,"g":0.5,"b":0.5,"a":1.0},"fontSize":5.0,"criticalFontSize":60.0,"duration":1.5,"offset":{"x":0.0,"y":0.0},"moveDirection":{"x":0.0,"y":1.0}}</t>
+          <t>{"guid":"2d7e41c4-8e90-4b61-879c-4b2e5b9486db","nodeType":14,"position":{"x":378.00003051757813,"y":-1836.666748046875},"targetType":1,"requiredTags":{"Tags":[]},"immunityTags":{"Tags":[]},"destroyWithNode":false,"positionSource":2,"positionBindingName":"head","textType":0,"fixedText":"","contextDataKey":"DamageResult","textColor":{"r":0.0,"g":0.323091983795166,"b":1.0,"a":1.0},"criticalColor":{"r":1.0,"g":0.5,"b":0.0,"a":1.0},"missColor":{"r":0.5,"g":0.5,"b":0.5,"a":1.0},"fontSize":5.0,"criticalFontSize":60.0,"duration":1.5,"offset":{"x":0.0,"y":0.0},"moveDirection":{"x":0.0,"y":1.0}}</t>
         </is>
       </c>
       <c r="G36"/>
@@ -2125,11 +2125,11 @@
       </c>
       <c r="D76"/>
       <c r="E76">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>{"guid":"f8947676-1084-4228-b991-1509cc7fe851","nodeType":1,"position":{"x":1452.666748046875,"y":-2239.333251953125},"targetType":0,"assetTags":{"Tags":[]},"grantedTags":{"Tags":[]},"applicationRequiredTags":{"Tags":[]},"applicationImmunityTags":{"Tags":[]},"removeGameEffectsWithTags":{"Tags":[]},"durationType":0,"duration":"0","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"Tags":[]},"cancelOnAbilityEnd":true,"damageType":0,"damageSourceType":0,"damageFixedValue":10.0,"damageFormula":"","damageMMCType":0,"damageSetByCallerKey":"","damageMMCCaptureAttribute":200,"damageMMCAttributeSource":0,"damageMMCCoefficient":1.0,"damageMMCUseSnapshot":true,"damageMultiplyByStackCount":false,"damageCalculationType":0,"enableHitKnockback":false,"knockbackDistance":1.0,"knockbackSpeed":12.0}</t>
+          <t>{"guid":"2cfdacd2-0186-49dd-b177-4eb8c0ad87bd","nodeType":7,"position":{"x":1052.666748046875,"y":-2551.333251953125},"targetType":1,"endType":0}</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
@@ -2145,11 +2145,11 @@
       <c r="C77"/>
       <c r="D77"/>
       <c r="E77">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>{"guid":"2cfdacd2-0186-49dd-b177-4eb8c0ad87bd","nodeType":7,"position":{"x":1052.666748046875,"y":-2551.333251953125},"targetType":1,"endType":0}</t>
+          <t>{"guid":"9d6f459d-b588-4b64-843b-1b71e8f299ae","nodeType":3,"position":{"x":-1144.0,"y":-2405.333251953125},"targetType":1,"assetTags":{"Tags":[]},"grantedTags":{"Tags":[]},"applicationRequiredTags":{"Tags":[]},"applicationImmunityTags":{"Tags":[]},"removeGameEffectsWithTags":{"Tags":[]},"durationType":0,"duration":"0","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[{"attrType":100,"operation":0,"magnitudeSourceType":0,"fixedValue":10.0,"formula":"","mmcType":0,"setByCallerKey":"","mmcCaptureAttribute":200,"mmcAttributeSource":0,"mmcCoefficient":1.0,"mmcUseSnapshot":true}],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"Tags":[]},"cancelOnAbilityEnd":true}</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
@@ -2165,11 +2165,11 @@
       <c r="C78"/>
       <c r="D78"/>
       <c r="E78">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>{"guid":"9d6f459d-b588-4b64-843b-1b71e8f299ae","nodeType":3,"position":{"x":-1144.0,"y":-2405.333251953125},"targetType":1,"assetTags":{"Tags":[]},"grantedTags":{"Tags":[]},"applicationRequiredTags":{"Tags":[]},"applicationImmunityTags":{"Tags":[]},"removeGameEffectsWithTags":{"Tags":[]},"durationType":0,"duration":"0","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[{"attrType":100,"operation":0,"magnitudeSourceType":0,"fixedValue":10.0,"formula":"","mmcType":0,"setByCallerKey":"","mmcCaptureAttribute":200,"mmcAttributeSource":0,"mmcCoefficient":1.0,"mmcUseSnapshot":true}],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"Tags":[]},"cancelOnAbilityEnd":true}</t>
+          <t>{"guid":"c28fb88d-51b1-47b2-be59-859e0ac638e3","nodeType":10,"position":{"x":-1067.3333740234375,"y":-2188.66650390625},"targetType":1,"assetTags":{"Tags":[]},"grantedTags":{"Tags":[{"Name":"CD.ThreeFire","HashCode":960327319,"ShortName":"ThreeFire","AncestorHashCodes":[-1137859925],"AncestorNames":["CD"]}]},"applicationRequiredTags":{"Tags":[]},"applicationImmunityTags":{"Tags":[]},"removeGameEffectsWithTags":{"Tags":[]},"durationType":1,"duration":"1","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"Tags":[]},"cancelOnAbilityEnd":false,"cooldownType":0,"maxCharges":2,"chargeTime":"10"}</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
@@ -2185,11 +2185,11 @@
       <c r="C79"/>
       <c r="D79"/>
       <c r="E79">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>{"guid":"c28fb88d-51b1-47b2-be59-859e0ac638e3","nodeType":10,"position":{"x":-1067.3333740234375,"y":-2188.66650390625},"targetType":1,"assetTags":{"Tags":[]},"grantedTags":{"Tags":[{"Name":"CD.ThreeFire","HashCode":960327319,"ShortName":"ThreeFire","AncestorHashCodes":[-1137859925],"AncestorNames":["CD"]}]},"applicationRequiredTags":{"Tags":[]},"applicationImmunityTags":{"Tags":[]},"removeGameEffectsWithTags":{"Tags":[]},"durationType":1,"duration":"1","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"Tags":[]},"cancelOnAbilityEnd":false,"cooldownType":0,"maxCharges":2,"chargeTime":"10"}</t>
+          <t>{"guid":"356907e0-1488-4128-bfcc-7ff73cfc3330","nodeType":0,"position":{"x":-746.6666259765625,"y":-2405.333251953125},"targetType":1,"skillId":1008,"assetTags":{"Tags":[]},"cancelAbilitiesWithTags":{"Tags":[]},"blockAbilitiesWithTags":{"Tags":[]},"activationOwnedTags":{"Tags":[]},"activationRequiredTags":{"Tags":[]},"activationBlockedTags":{"Tags":[{"Name":"CD.ThreeFire","HashCode":960327319,"ShortName":"ThreeFire","AncestorHashCodes":[-1137859925],"AncestorNames":["CD"]}]},"ongoingBlockedTags":{"Tags":[]},"eventOutputPorts":[]}</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
@@ -2205,11 +2205,11 @@
       <c r="C80"/>
       <c r="D80"/>
       <c r="E80">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>{"guid":"356907e0-1488-4128-bfcc-7ff73cfc3330","nodeType":0,"position":{"x":-746.6666259765625,"y":-2405.333251953125},"targetType":1,"skillId":1008,"assetTags":{"Tags":[]},"cancelAbilitiesWithTags":{"Tags":[]},"blockAbilitiesWithTags":{"Tags":[]},"activationOwnedTags":{"Tags":[]},"activationRequiredTags":{"Tags":[]},"activationBlockedTags":{"Tags":[{"Name":"CD.ThreeFire","HashCode":960327319,"ShortName":"ThreeFire","AncestorHashCodes":[-1137859925],"AncestorNames":["CD"]}]},"ongoingBlockedTags":{"Tags":[]},"eventOutputPorts":[]}</t>
+          <t>{"guid":"9a695e91-e218-425e-82ed-1e157bf1b014","nodeType":8,"position":{"x":1022.666748046875,"y":-2131.333251953125},"targetType":2,"assetTags":{"Tags":[]},"grantedTags":{"Tags":[]},"applicationRequiredTags":{"Tags":[]},"applicationImmunityTags":{"Tags":[]},"removeGameEffectsWithTags":{"Tags":[]},"durationType":2,"duration":"0","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"Tags":[]},"cancelOnAbilityEnd":false,"launchPositionSource":0,"launchBindingName":"center","targetPositionSource":1,"targetBindingName":"center","projectileTargetType":0,"flyOver":true,"offsetAngle":0.0,"curveHeight":0.0,"projectileEntityId":50002,"projectilePrefab":null,"projectilePrefabPath":"Assets/Res/Entity/Effect/ef_fashi_huoyandan01.prefab","speed":10.0,"maxDistance":10.0,"collisionRadius":0.5,"isPiercing":false,"maxPierceCount":1,"collisionTargetTags":{"Tags":[]},"collisionExcludeTags":{"Tags":[]},"isBouncing":false,"bounceTargetMode":0,"maxBounceCount":3,"bounceSearchRadius":10.0,"canBounceToSameTarget":false,"excludeSourceCamp":true,"bounceAngleOffset":0.0}</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
@@ -2225,11 +2225,11 @@
       <c r="C81"/>
       <c r="D81"/>
       <c r="E81">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>{"guid":"432ff1e3-b18d-476d-af80-d39ddc07402a","nodeType":20,"position":{"x":-238.66665649414063,"y":-2405.333251953125},"targetType":1,"skeletonDataAsset":null,"skeletonDataAssetPath":"Assets/Res/Spine/SP_Zhanshi/SP_Zhanshi_SkeletonData.asset","animationName":"Attack_01","animationDuration":"18","isAnimationLooping":false,"timeEffects":[{"triggerTime":7,"portIdValue":2315086,"legacyPortId":"de0ba361-3aba-4ef0-bb07-9b418fcae591"},{"triggerTime":18,"portIdValue":2649436,"legacyPortId":"84e238a8-5baf-470e-829f-186695064945"}],"timeCues":[]}</t>
+          <t>{"guid":"d897a922-5756-42cf-ac65-90a48c1e5a17","nodeType":8,"position":{"x":1022.666748046875,"y":-1951.3333740234375},"targetType":2,"assetTags":{"Tags":[]},"grantedTags":{"Tags":[]},"applicationRequiredTags":{"Tags":[]},"applicationImmunityTags":{"Tags":[]},"removeGameEffectsWithTags":{"Tags":[]},"durationType":2,"duration":"0","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"Tags":[]},"cancelOnAbilityEnd":false,"launchPositionSource":0,"launchBindingName":"center","targetPositionSource":1,"targetBindingName":"center","projectileTargetType":0,"flyOver":true,"offsetAngle":-30.0,"curveHeight":0.0,"projectileEntityId":50002,"projectilePrefab":null,"projectilePrefabPath":"Assets/Res/Entity/Effect/ef_fashi_huoyandan01.prefab","speed":10.0,"maxDistance":10.0,"collisionRadius":0.5,"isPiercing":false,"maxPierceCount":1,"collisionTargetTags":{"Tags":[]},"collisionExcludeTags":{"Tags":[]},"isBouncing":false,"bounceTargetMode":0,"maxBounceCount":3,"bounceSearchRadius":10.0,"canBounceToSameTarget":false,"excludeSourceCamp":true,"bounceAngleOffset":0.0}</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
@@ -2245,11 +2245,11 @@
       <c r="C82"/>
       <c r="D82"/>
       <c r="E82">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>{"guid":"ce857360-de7e-4457-b348-9c124ce98879","nodeType":8,"position":{"x":1040.666748046875,"y":-2305.333251953125},"targetType":2,"assetTags":{"Tags":[]},"grantedTags":{"Tags":[]},"applicationRequiredTags":{"Tags":[]},"applicationImmunityTags":{"Tags":[]},"removeGameEffectsWithTags":{"Tags":[]},"durationType":2,"duration":"0","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"Tags":[]},"cancelOnAbilityEnd":false,"launchPositionSource":0,"launchBindingName":"center","targetPositionSource":1,"targetBindingName":"center","projectileTargetType":0,"flyOver":true,"offsetAngle":30.0,"curveHeight":0.0,"projectileEntityId":50002,"projectilePrefab":null,"projectilePrefabPath":"Assets/Res/Entity/Effect/ef_fashi_huoyandan01.prefab","speed":10.0,"maxDistance":10.0,"collisionRadius":0.5,"isPiercing":false,"maxPierceCount":1,"collisionTargetTags":{"Tags":[]},"collisionExcludeTags":{"Tags":[]},"isBouncing":false,"bounceTargetMode":0,"maxBounceCount":3,"bounceSearchRadius":10.0,"canBounceToSameTarget":false,"excludeSourceCamp":true,"bounceAngleOffset":0.0}</t>
+          <t>{"guid":"c353e286-8ef0-460a-b917-887f2aeb390a","nodeType":14,"position":{"x":1677.3333740234375,"y":-2239.333251953125},"targetType":1,"requiredTags":{"Tags":[]},"immunityTags":{"Tags":[]},"destroyWithNode":false,"positionSource":2,"positionBindingName":"head","textType":0,"fixedText":"","contextDataKey":"DamageResult","textColor":{"r":1.0,"g":0.0,"b":0.0,"a":1.0},"criticalColor":{"r":1.0,"g":0.5,"b":0.0,"a":1.0},"missColor":{"r":0.5,"g":0.5,"b":0.5,"a":1.0},"fontSize":5.0,"criticalFontSize":60.0,"duration":1.5,"offset":{"x":0.0,"y":0.0},"moveDirection":{"x":0.0,"y":1.0}}</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
@@ -2265,11 +2265,11 @@
       <c r="C83"/>
       <c r="D83"/>
       <c r="E83">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>{"guid":"9a695e91-e218-425e-82ed-1e157bf1b014","nodeType":8,"position":{"x":1022.666748046875,"y":-2131.333251953125},"targetType":2,"assetTags":{"Tags":[]},"grantedTags":{"Tags":[]},"applicationRequiredTags":{"Tags":[]},"applicationImmunityTags":{"Tags":[]},"removeGameEffectsWithTags":{"Tags":[]},"durationType":2,"duration":"0","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"Tags":[]},"cancelOnAbilityEnd":false,"launchPositionSource":0,"launchBindingName":"center","targetPositionSource":1,"targetBindingName":"center","projectileTargetType":0,"flyOver":true,"offsetAngle":0.0,"curveHeight":0.0,"projectileEntityId":50002,"projectilePrefab":null,"projectilePrefabPath":"Assets/Res/Entity/Effect/ef_fashi_huoyandan01.prefab","speed":10.0,"maxDistance":10.0,"collisionRadius":0.5,"isPiercing":false,"maxPierceCount":1,"collisionTargetTags":{"Tags":[]},"collisionExcludeTags":{"Tags":[]},"isBouncing":false,"bounceTargetMode":0,"maxBounceCount":3,"bounceSearchRadius":10.0,"canBounceToSameTarget":false,"excludeSourceCamp":true,"bounceAngleOffset":0.0}</t>
+          <t>{"guid":"432ff1e3-b18d-476d-af80-d39ddc07402a","nodeType":20,"position":{"x":-238.66665649414063,"y":-2405.333251953125},"targetType":1,"skeletonDataAsset":null,"skeletonDataAssetPath":"Assets/Res/Spine/SP_Zhanshi/SP_Zhanshi_SkeletonData.asset","animationName":"Attack_01","animationDuration":"18","isAnimationLooping":false,"timeEffects":[{"triggerTime":7,"portIdValue":2315086,"legacyPortId":"de0ba361-3aba-4ef0-bb07-9b418fcae591"},{"triggerTime":18,"portIdValue":2649436,"legacyPortId":"84e238a8-5baf-470e-829f-186695064945"}],"timeCues":[]}</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
@@ -2285,11 +2285,11 @@
       <c r="C84"/>
       <c r="D84"/>
       <c r="E84">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>{"guid":"d897a922-5756-42cf-ac65-90a48c1e5a17","nodeType":8,"position":{"x":1022.666748046875,"y":-1951.3333740234375},"targetType":2,"assetTags":{"Tags":[]},"grantedTags":{"Tags":[]},"applicationRequiredTags":{"Tags":[]},"applicationImmunityTags":{"Tags":[]},"removeGameEffectsWithTags":{"Tags":[]},"durationType":2,"duration":"0","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"Tags":[]},"cancelOnAbilityEnd":false,"launchPositionSource":0,"launchBindingName":"center","targetPositionSource":1,"targetBindingName":"center","projectileTargetType":0,"flyOver":true,"offsetAngle":-30.0,"curveHeight":0.0,"projectileEntityId":50002,"projectilePrefab":null,"projectilePrefabPath":"Assets/Res/Entity/Effect/ef_fashi_huoyandan01.prefab","speed":10.0,"maxDistance":10.0,"collisionRadius":0.5,"isPiercing":false,"maxPierceCount":1,"collisionTargetTags":{"Tags":[]},"collisionExcludeTags":{"Tags":[]},"isBouncing":false,"bounceTargetMode":0,"maxBounceCount":3,"bounceSearchRadius":10.0,"canBounceToSameTarget":false,"excludeSourceCamp":true,"bounceAngleOffset":0.0}</t>
+          <t>{"guid":"f8947676-1084-4228-b991-1509cc7fe851","nodeType":1,"position":{"x":1453.3333740234375,"y":-2239.333251953125},"targetType":0,"assetTags":{"Tags":[]},"grantedTags":{"Tags":[]},"applicationRequiredTags":{"Tags":[]},"applicationImmunityTags":{"Tags":[]},"removeGameEffectsWithTags":{"Tags":[]},"durationType":0,"duration":"0","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"Tags":[]},"cancelOnAbilityEnd":true,"damageType":0,"damageSourceType":0,"damageFixedValue":10.0,"damageFormula":"","damageMMCType":0,"damageSetByCallerKey":"","damageMMCCaptureAttribute":200,"damageMMCAttributeSource":0,"damageMMCCoefficient":1.0,"damageMMCUseSnapshot":true,"damageMultiplyByStackCount":false,"damageCalculationType":0,"enableHitKnockback":false,"knockbackDistance":1.0,"knockbackSpeed":12.0}</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
@@ -2305,11 +2305,11 @@
       <c r="C85"/>
       <c r="D85"/>
       <c r="E85">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>{"guid":"c353e286-8ef0-460a-b917-887f2aeb390a","nodeType":14,"position":{"x":1677.3333740234375,"y":-2239.333251953125},"targetType":1,"requiredTags":{"Tags":[]},"immunityTags":{"Tags":[]},"destroyWithNode":false,"positionSource":2,"positionBindingName":"head","textType":0,"fixedText":"","contextDataKey":"DamageResult","textColor":{"r":1.0,"g":0.0,"b":0.0,"a":1.0},"criticalColor":{"r":1.0,"g":0.5,"b":0.0,"a":1.0},"missColor":{"r":0.5,"g":0.5,"b":0.5,"a":1.0},"fontSize":5.0,"criticalFontSize":60.0,"duration":1.5,"offset":{"x":0.0,"y":0.0},"moveDirection":{"x":0.0,"y":1.0}}</t>
+          <t>{"guid":"ce857360-de7e-4457-b348-9c124ce98879","nodeType":8,"position":{"x":1040.0,"y":-2306.0},"targetType":2,"assetTags":{"Tags":[]},"grantedTags":{"Tags":[]},"applicationRequiredTags":{"Tags":[]},"applicationImmunityTags":{"Tags":[]},"removeGameEffectsWithTags":{"Tags":[]},"durationType":2,"duration":"0","isPeriodic":false,"period":"1","executeOnApplication":false,"attributeModifiers":[],"stackType":0,"stackLimit":0,"stackDurationRefreshPolicy":0,"stackPeriodResetPolicy":0,"stackExpirationPolicy":0,"stackOverflowPolicy":0,"ongoingRequiredTags":{"Tags":[]},"cancelOnAbilityEnd":false,"launchPositionSource":0,"launchBindingName":"center","targetPositionSource":1,"targetBindingName":"center","projectileTargetType":0,"flyOver":true,"offsetAngle":30.0,"curveHeight":0.0,"projectileEntityId":50002,"projectilePrefab":null,"projectilePrefabPath":"Assets/Res/Entity/Effect/ef_fashi_huoyandan01.prefab","speed":10.0,"maxDistance":10.0,"collisionRadius":0.5,"isPiercing":false,"maxPierceCount":1,"collisionTargetTags":{"Tags":[]},"collisionExcludeTags":{"Tags":[]},"isBouncing":false,"bounceTargetMode":0,"maxBounceCount":3,"bounceSearchRadius":10.0,"canBounceToSameTarget":false,"excludeSourceCamp":true,"bounceAngleOffset":0.0}</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
